--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>bangla</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>বদ্দা, কি অবস্থা অঁনোর?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">আপনি ভালো আছেন ম্যাম? </t>
+  </si>
+  <si>
+    <t>অঁনে গম আছন ম্যাম?</t>
   </si>
 </sst>
 </file>
@@ -705,12 +711,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1263,124 +1266,128 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
   <si>
     <t>bangla</t>
   </si>
@@ -90,6 +90,234 @@
   </si>
   <si>
     <t>অঁনে গম আছন ম্যাম?</t>
+  </si>
+  <si>
+    <t>ঘরের সবাই কেমন আছে?</t>
+  </si>
+  <si>
+    <t>ঘরোর বিয়াজ্ঞুন কেন আছে?</t>
+  </si>
+  <si>
+    <t>আরে হাছান, কি খবর?</t>
+  </si>
+  <si>
+    <t>আরে হাছান, কি হবর?</t>
+  </si>
+  <si>
+    <t>আমি ভালো আছি, তুমি কেমন আছো?</t>
+  </si>
+  <si>
+    <t>আঁই গম আছি, তুঁই কেন আছো?</t>
+  </si>
+  <si>
+    <t>ধন্যবাদ তোমাকে</t>
+  </si>
+  <si>
+    <t>ধইন্যবাদ তোঁয়ারে</t>
+  </si>
+  <si>
+    <t xml:space="preserve">আপনি কেমন আছেন? </t>
+  </si>
+  <si>
+    <t>অঁনে কেন আছন?</t>
+  </si>
+  <si>
+    <t>আপনার কি মন খারাপ?</t>
+  </si>
+  <si>
+    <t>অঁনোর কি মন হারাপ?</t>
+  </si>
+  <si>
+    <t>কি খবর সবার, সবাই কেমন আছো?</t>
+  </si>
+  <si>
+    <t>কি হবর বিয়াজ্ঞুনোর, বিয়াজ্ঞুন কেন আছো?</t>
+  </si>
+  <si>
+    <t>কি খবর বন্ধু, কেমন আছিস?</t>
+  </si>
+  <si>
+    <t>কি হবর বন্ধু, কেন আছোস?</t>
+  </si>
+  <si>
+    <t>হ্যালো রাকিব, কোথায় যাচ্ছো?</t>
+  </si>
+  <si>
+    <t>হ্যালো রাকিব, হনডে যর?</t>
+  </si>
+  <si>
+    <t>তোমাকে অনেকদিন দেখিনায়</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে বতদিন ন দেহি</t>
+  </si>
+  <si>
+    <t>এতদিন কোথায় ছিলে?</t>
+  </si>
+  <si>
+    <t>এতদিন হনডে আছিলে?</t>
+  </si>
+  <si>
+    <t>আমার ভাল লাগছেনা, তুমি এখন যাও</t>
+  </si>
+  <si>
+    <t>আত্তুন গম নলার, তুঁই এহন যো</t>
+  </si>
+  <si>
+    <t>তুমি এখন যাও, আমি আসছি</t>
+  </si>
+  <si>
+    <t>তুঁই এহন যো, আঁই আইর</t>
+  </si>
+  <si>
+    <t>তুমি কখন আসবে?</t>
+  </si>
+  <si>
+    <t>তুঁই হত্তে আইবে?</t>
+  </si>
+  <si>
+    <t>তুমি কি আসবে?</t>
+  </si>
+  <si>
+    <t>তুঁই কি আইবে?</t>
+  </si>
+  <si>
+    <t>সে কি আসছে? নাকি আমি চলে যাব?</t>
+  </si>
+  <si>
+    <t>ইতে আইয়্যির না? নাকি আঁই চলি যাইয়্যুম?</t>
+  </si>
+  <si>
+    <t>সমস্যা নাই, আমি তোমার জন্য অপেক্ষা করব</t>
+  </si>
+  <si>
+    <t>সমস্যা নাই, আঁই তোঁয়ার লাই অপেক্ষা গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমি আগামিকাল আসব</t>
+  </si>
+  <si>
+    <t>আঁই হালিইয়্যে আইসসুম</t>
+  </si>
+  <si>
+    <t>সমস্যা নাই, তুমি আগামিকাল আসতে পারবে</t>
+  </si>
+  <si>
+    <t>সমস্যা নাই, তুঁই হালিইয়্যে আইত পারিবে</t>
+  </si>
+  <si>
+    <t>আমার আজকে একটু শরীর খারাপ</t>
+  </si>
+  <si>
+    <t>আত্তুন আজিয়ে এক্কানা শরীর হারাপ</t>
+  </si>
+  <si>
+    <t>আমি আছি কোনরকম, তোমার কি অবস্থা?</t>
+  </si>
+  <si>
+    <t>আঁই আছি হনোরহম, তোঁয়ার কি অবস্থা?</t>
+  </si>
+  <si>
+    <t>আমার একটু ক্লান্ত লাগতাছে, তোমার সাথে পরে কথা বলব</t>
+  </si>
+  <si>
+    <t>আত্তুন এক্কানা জিমেনি আইয়্যির, তোঁয়ার লগে পরে হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আপনার জন্য অপেক্ষা করব আমি</t>
+  </si>
+  <si>
+    <t>অঁনোর লাই অপেক্ষা গইজ্জুম আঁই</t>
+  </si>
+  <si>
+    <t>আমার জন্য অপেক্ষা করতে হবেনা</t>
+  </si>
+  <si>
+    <t>আঁর লাই অপেক্ষা গরন পইত্তোনো</t>
+  </si>
+  <si>
+    <t>তোমার দিনকাল কেমন যাচ্ছে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার দিনহাল কেন যার?</t>
+  </si>
+  <si>
+    <t>আপনি আগামিকাল আসতে পারবেন?</t>
+  </si>
+  <si>
+    <t>অঁনে হালিইয়্যে আইত পারিবেন?</t>
+  </si>
+  <si>
+    <t>স্যার, আমি কি আসতে পারি?</t>
+  </si>
+  <si>
+    <t>স্যার, আঁই কি আইত পারি?</t>
+  </si>
+  <si>
+    <t>জ্বি, আসেন</t>
+  </si>
+  <si>
+    <t>জ্বি, আইয়ুন</t>
+  </si>
+  <si>
+    <t>ধন্যবাদ, আবার আসবেন</t>
+  </si>
+  <si>
+    <t>ধইন্যবাদ, আবার আইস্যুন</t>
+  </si>
+  <si>
+    <t>তারেক আমাকে বলেছিল তুমি আসবে</t>
+  </si>
+  <si>
+    <t>তারেক আঁরে হইয়্যিল দে তুঁই আইবে</t>
+  </si>
+  <si>
+    <t>তুমি একটু পরে আসো</t>
+  </si>
+  <si>
+    <t>তুঁই এক্কানা পরে আইয়্যু</t>
+  </si>
+  <si>
+    <t>আমি এখন চলে  যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই এহন  চলি যাইর</t>
+  </si>
+  <si>
+    <t>আসার সময় কষ্ট হয়নি তো?</t>
+  </si>
+  <si>
+    <t>আইবের সময় হষ্ট অইয়্যি না হনো?</t>
+  </si>
+  <si>
+    <t>কিছু মনে করিয়েন না, আজকে আমার দেরি হবে আসতে</t>
+  </si>
+  <si>
+    <t>কিছু মনে নগইজ্জুন, আজিয়ে আত্তুন দেরি অইবু আইতে</t>
+  </si>
+  <si>
+    <t>আমার দেরি হবে, তুমি চলে যাও</t>
+  </si>
+  <si>
+    <t>আত্তুন দেরি অইবু, তুঁই চলি যো</t>
+  </si>
+  <si>
+    <t>তোমাকে খুব সুন্দর লাগতাছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে বত সুন্দর লাগের</t>
+  </si>
+  <si>
+    <t>ব্যাপার কি, আজকে তোমাকে অনেক সুন্দর লাগতাছে</t>
+  </si>
+  <si>
+    <t>ব্যাপার কি, আজিয়ে তো তোঁইয়ারা বত সুন্দার লাগের</t>
+  </si>
+  <si>
+    <t>আপনি কি একটু সাহায্য করতে পারবেন?</t>
+  </si>
+  <si>
+    <t>অঁনে কি এক্কানা সাহাইয্য গরিত পারিবেন?</t>
   </si>
 </sst>
 </file>
@@ -711,9 +939,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1251,7 +1485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="90.7777777777778" customWidth="1"/>
@@ -1266,128 +1500,600 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:2">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:2">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:2">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:2">
+      <c r="A24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1" spans="1:2">
+      <c r="A25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1" spans="1:2">
+      <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1" spans="1:2">
+      <c r="A27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1" spans="1:2">
+      <c r="A28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1" spans="1:2">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:2">
+      <c r="A30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:2">
+      <c r="A31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:2">
+      <c r="A32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:2">
+      <c r="A33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:2">
+      <c r="A34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:2">
+      <c r="A35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:2">
+      <c r="A36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:2">
+      <c r="A37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:2">
+      <c r="A38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:2">
+      <c r="A39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:2">
+      <c r="A40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:2">
+      <c r="A41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:2">
+      <c r="A42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:2">
+      <c r="A43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:2">
+      <c r="A44" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:2">
+      <c r="A45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:2">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:2">
+      <c r="A47" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:2">
+      <c r="A48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:2">
+      <c r="A49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:2">
+      <c r="A50" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:2">
+      <c r="A51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:2">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:2">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:2">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:2">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:2">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:2">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:2">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:2">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:2">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:2">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:2">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:2">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:2">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:2">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:2">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" ht="25" customHeight="1" spans="1:2">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" ht="25" customHeight="1" spans="1:2">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:2">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:2">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" ht="25" customHeight="1" spans="1:2">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" ht="25" customHeight="1" spans="1:2">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" ht="25" customHeight="1" spans="1:2">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" ht="25" customHeight="1" spans="1:2">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" ht="25" customHeight="1" spans="1:2">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" ht="25" customHeight="1" spans="1:2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" ht="25" customHeight="1" spans="1:2">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" ht="25" customHeight="1" spans="1:2">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" ht="25" customHeight="1" spans="1:2">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" ht="25" customHeight="1" spans="1:2">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" ht="25" customHeight="1" spans="1:2">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" ht="25" customHeight="1" spans="1:2">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" ht="25" customHeight="1" spans="1:2">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" ht="25" customHeight="1" spans="1:2">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" ht="25" customHeight="1" spans="1:2">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" ht="25" customHeight="1" spans="1:2">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" ht="25" customHeight="1" spans="1:2">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" ht="25" customHeight="1" spans="1:2">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" ht="25" customHeight="1" spans="1:2">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" ht="25" customHeight="1" spans="1:2">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" ht="25" customHeight="1" spans="1:2">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" ht="25" customHeight="1" spans="1:2">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" ht="25" customHeight="1" spans="1:2">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" ht="25" customHeight="1" spans="1:2">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" ht="25" customHeight="1" spans="1:2">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" ht="25" customHeight="1" spans="1:2">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" ht="25" customHeight="1" spans="1:2">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" ht="25" customHeight="1" spans="1:2">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" ht="25" customHeight="1" spans="1:2">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" ht="25" customHeight="1" spans="1:2">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="197">
   <si>
     <t>bangla</t>
   </si>
@@ -155,7 +155,7 @@
     <t>এতদিন কোথায় ছিলে?</t>
   </si>
   <si>
-    <t>এতদিন হনডে আছিলে?</t>
+    <t>এতোদিন হনডে আছিলে?</t>
   </si>
   <si>
     <t>আমার ভাল লাগছেনা, তুমি এখন যাও</t>
@@ -221,7 +221,7 @@
     <t>আমার একটু ক্লান্ত লাগতাছে, তোমার সাথে পরে কথা বলব</t>
   </si>
   <si>
-    <t>আত্তুন এক্কানা জিমেনি আইয়্যির, তোঁয়ার লগে পরে হতা হইয়্যুম</t>
+    <t>আত্তুন এক্কানা ঝিমেনি আইয়্যির, তোঁয়ার লগে পরে হতা হইয়্যুম</t>
   </si>
   <si>
     <t>আপনার জন্য অপেক্ষা করব আমি</t>
@@ -318,6 +318,306 @@
   </si>
   <si>
     <t>অঁনে কি এক্কানা সাহাইয্য গরিত পারিবেন?</t>
+  </si>
+  <si>
+    <t>আমি একটা বিপদে পড়েছি</t>
+  </si>
+  <si>
+    <t>আঁই এক্কান বিপোদত পইজ্জি</t>
+  </si>
+  <si>
+    <t>আমাকে এই বিপদ থেকে উদ্ধার করো</t>
+  </si>
+  <si>
+    <t>আঁরে এই বিপোদত্তুন উদ্ধার গরো</t>
+  </si>
+  <si>
+    <t>আজকে তোমাকে এত খুশি দেখাচ্ছে কেন?</t>
+  </si>
+  <si>
+    <t>আজিয়ে তোঁয়ারে এল্লেত খুশি লাগের কা?</t>
+  </si>
+  <si>
+    <t>আজকে তোমাকে এত খুশি কেন দেখাচ্ছে?</t>
+  </si>
+  <si>
+    <t>আজিয়ে তোঁয়ারে এল্লেত খুশি কা লাগের?</t>
+  </si>
+  <si>
+    <t>আমি তোমার সাথে কথা বলতে চাই</t>
+  </si>
+  <si>
+    <t>আঁই তোঁয়ার লগে হতা হইতাম চাই</t>
+  </si>
+  <si>
+    <t>তুমি কি আমার কথা শুনছো?</t>
+  </si>
+  <si>
+    <t>তুঁই কি আঁর হতা উইন্তে লাইজ্ঞু?</t>
+  </si>
+  <si>
+    <t>দয়া করে আবার একটু বলো</t>
+  </si>
+  <si>
+    <t>দয়া গরি আবার এক্কানা হনা</t>
+  </si>
+  <si>
+    <t>আপনি কি আমার কথা শুনছেন?</t>
+  </si>
+  <si>
+    <t>অঁনে কি আঁর হতা উইনতে লাইজ্ঞুন?</t>
+  </si>
+  <si>
+    <t>আশা করি খুব শীঘ্রই আবার দেখা হবে, ভালো থাকবেন</t>
+  </si>
+  <si>
+    <t xml:space="preserve">আশা গরি বত জলদি আবার দেহা অইবু, ভালা থাইক্কুন </t>
+  </si>
+  <si>
+    <t>দিনকাল কেমন যাচ্ছে? সবকিছু ঠিকাছে?</t>
+  </si>
+  <si>
+    <t>দিনহাল কেন যার? বেজ্ঞিন ঠিকাছেনা?</t>
+  </si>
+  <si>
+    <t>আরে বন্ধু! কতোদিন পর তুর সাথে দেখা!</t>
+  </si>
+  <si>
+    <t>আরে বন্ধু! হতোদিন পর তুর লগে দেহা!</t>
+  </si>
+  <si>
+    <t>দীর্ঘদিন পর আপনাকে দেখে সত্যিই খুব ভালো লাগল</t>
+  </si>
+  <si>
+    <t>বতদিন পর অঁনোরে দেহি সত্যিই বত ভালা লাইজ্ঞি</t>
+  </si>
+  <si>
+    <t>আপনাকে অনেকদিন দেখিনায়, এতদিন কোথায় ছিলেন?</t>
+  </si>
+  <si>
+    <t>অঁনোরে বতদিন নো দেহি, এতোদিন হনডে আছিলেন?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">কিরে বন্ধু! কি হয়েছে তুর? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">কিরে বন্ধু! কি অইয়্যিদে তুর? </t>
+  </si>
+  <si>
+    <t>তোকে দেখে অসুস্থ মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>তোরে দেহি রে অসুস্থ মনে অর</t>
+  </si>
+  <si>
+    <t>আপনার সাথে আরেকদিন কথা বলব</t>
+  </si>
+  <si>
+    <t>অঁনোর লাই আরেকদিন হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমি এখন চলে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই এহন চলি যাইর</t>
+  </si>
+  <si>
+    <t>আজকে একটু ক্লান্ত লাগতাছে, তুর সাথে পরে কথা বলব</t>
+  </si>
+  <si>
+    <t>আজিয়ে এক্কানা ঝিমেনি আইয়্যির, তুর লগে পরে হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আবার পরে দেখা হবে</t>
+  </si>
+  <si>
+    <t>আবার পরে দেহা অইব্যু</t>
+  </si>
+  <si>
+    <t>আপনার নাম অনেকবার শুনেছি, আজকে সরাসরি পরিচয় হতে পেরে খুশি হলাম</t>
+  </si>
+  <si>
+    <t>অঁনোর নাম বতবার উইন্নি, আজিয়ে সামনাসামনি পরিচয় অইত পারি খুশি অইলাম</t>
+  </si>
+  <si>
+    <t>মাথা ঠান্ডা করে আমরা কি বলতে চাই শুনেন</t>
+  </si>
+  <si>
+    <t>মাথা ঠান্ডা গরি আঁরা কি হইতাম চাই উনন</t>
+  </si>
+  <si>
+    <t>মাথা ঠান্ডা করো, আমি কি বলি মনোযোগ দিয়ে শোনো</t>
+  </si>
+  <si>
+    <t>মাথা ঠান্ডা গরো, আঁই কি হইর মন দি উনো</t>
+  </si>
+  <si>
+    <t>এই শোন, তুমি একটু বোঝার চেষ্টা করো</t>
+  </si>
+  <si>
+    <t>এই উনো না, তুঁই এক্কানা বুঝিবের চেষ্টা গরো</t>
+  </si>
+  <si>
+    <t>এখন তুমি বলো আমি কি করব</t>
+  </si>
+  <si>
+    <t>এহন তুঁই হ্‌ আঁই কি গইজ্জুম</t>
+  </si>
+  <si>
+    <t>এই শোনেন, আপনি একটু বোঝার চেষ্টা করেন</t>
+  </si>
+  <si>
+    <t>এই উনন না, অঁনে এক্কানা বুঝিবের চেষ্টা গরন</t>
+  </si>
+  <si>
+    <t>তোমার কথা শুনে আমার বুকে ব্যাথা শুরু হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হতা উনি রে আঁর বুকোত ব্যাথা শুরু অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আগামিকাল আমার সাথে দেখা করিও</t>
+  </si>
+  <si>
+    <t>হালিয়্যে আঁর লগে দেহা গইজ্জো</t>
+  </si>
+  <si>
+    <t>তারপর বলব কি করতে হবে</t>
+  </si>
+  <si>
+    <t>তারপর হইয়্যুম কি গরন পরিবু</t>
+  </si>
+  <si>
+    <t>আমি কতবার বললাম সাকিব, আমার কাজ আছে</t>
+  </si>
+  <si>
+    <t>আঁই হতবার হইলাম সাকিব, আত্তুন হাজ আছে</t>
+  </si>
+  <si>
+    <t>আমার কাজ আছে, আমি এখন করতে পারব না</t>
+  </si>
+  <si>
+    <t>আত্তুন হাম আছে, আঁই এহন গরিত ন পাইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমি এখন ব্যস্ত, আমার দেরি হবে</t>
+  </si>
+  <si>
+    <t>আঁই এহন বিজি, আত্তুন দেরি অইবু</t>
+  </si>
+  <si>
+    <t>সত্যি বলছেন?</t>
+  </si>
+  <si>
+    <t>আঁছা হইতে লাইজ্ঞুন?</t>
+  </si>
+  <si>
+    <t>সত্যি মানে, মিথ্যা বলব নাকি আপনাকে!</t>
+  </si>
+  <si>
+    <t>আঁছা মানি, মিছে হইয়্যুম না অঁনোরে!</t>
+  </si>
+  <si>
+    <t>তুমি সবকিছু আমার উপার ছেড়ে দাও</t>
+  </si>
+  <si>
+    <t>তুঁই বিয়াক কিছু আঁর উদ্দি ছারি দো</t>
+  </si>
+  <si>
+    <t>পরিবারের সবার জন্য কিছু উপহার নিয়ে এসেছি, আশা করি পছন্দ হবে</t>
+  </si>
+  <si>
+    <t>পরিবারর বিয়াজ্ঞুনুর লাই কিছু উপহার লই আইলাম, আশা গরি পছন্দ অইবু</t>
+  </si>
+  <si>
+    <t>কেমন আছেন মামা? আপনাকে অনেকদিন পর দেখতাছি</t>
+  </si>
+  <si>
+    <t>কেন আছন মামা? অঁনোরে বতদিন পর দেহিদ্দি</t>
+  </si>
+  <si>
+    <t>কেমন আছিস বন্ধু? তোকে অনেকদিন পর দেখতাছি</t>
+  </si>
+  <si>
+    <t>কেন আছস বন্ধু, তোরে বতদিন পর দেহিদ্দি</t>
+  </si>
+  <si>
+    <t>আমি কি চাই সেটা তুমি আমার চেহারা দেখে বলতে পারবেনা?</t>
+  </si>
+  <si>
+    <t>আঁই কি চাই ইয়েন তুঁই আঁর চিয়ারা দেহি হইত নপারিবে?</t>
+  </si>
+  <si>
+    <t>তোমার চেহেরা দেখে আমি বুঝছি, একদম শুকায় গেছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার চিয়ারা দেহি আঁই বুইজ্জি, এব্বেরে পুয়াই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার পরিচিত মানুষ আছে, আমি তাদের সাথে কথা বলব</t>
+  </si>
+  <si>
+    <t>আত্তুন পরিচিত মানুষ আছে, আঁই ইতারার লগে হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আপনি কোন চিন্তা করিয়েন না</t>
+  </si>
+  <si>
+    <t>অঁনে হনো চিন্তে নগইজ্জোন</t>
+  </si>
+  <si>
+    <t>মাসুদ সাহেব, কেমন লাগতাছে আমাদের আয়োজন?</t>
+  </si>
+  <si>
+    <t>তো মাসুদ সাব, কেন লার আঁরার আয়োজন?</t>
+  </si>
+  <si>
+    <t>শুনে খুবই খুশি হলাম যে আপনার শারিরীক অবস্থার ব্যাপক উন্নতি হয়েছে, আরও দ্রুত সুস্থ হোন</t>
+  </si>
+  <si>
+    <t>উনিয়েরে বত খুশি অইলাম যে অঁনোর শারিরীক অবস্থার বত উন্নতি অইয়্যি, আরও তারাতারি সুস্থ অই যন</t>
+  </si>
+  <si>
+    <t>সেটা কি আমার মন রাখার জন্য বলেছেন নাকি নিজের মন থেকেই বলেছেন</t>
+  </si>
+  <si>
+    <t>ইয়েন কি আঁর মন রাহিবের লাই হইয়্যুন নাকি নিজোর মনত্তোন হইয়্যুন</t>
+  </si>
+  <si>
+    <t>আপনাকে আজকে আমার খুব ভালো লাগলো</t>
+  </si>
+  <si>
+    <t>অঁনোরে আজিয়ে আত্তুন বত ভালা লাগিলো</t>
+  </si>
+  <si>
+    <t>সেটা কি আমার মন রাখার জন্য বলছ নাকি মানুষ কিছু বলবে সেজন্য বলছ?</t>
+  </si>
+  <si>
+    <t>ইয়েন কি আঁর মন রাহিবের লাই হইয়্যু নাকি মাইনষে কিছু হইবু এতেল্লে হইয়্যু?</t>
+  </si>
+  <si>
+    <t>আপনি চাটগাইয়া কথা বলতে পারেন না?</t>
+  </si>
+  <si>
+    <t>অঁনে চাটগাইয়া হতা হইত নপারন?</t>
+  </si>
+  <si>
+    <t>এটা অবশ্য ঠিক বলছ</t>
+  </si>
+  <si>
+    <t>ইয়েন অবশ্য ঠিক হইয়্যু</t>
+  </si>
+  <si>
+    <t>তুমি অনেক দুষ্টু আছো, তোমাকে আমার ভাল লেগেছে</t>
+  </si>
+  <si>
+    <t>তুঁই বত জারগো আছো, তোঁয়ারে আত্তুন ভালা লেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>তাহলে কি আমি চলে যাব?</t>
+  </si>
+  <si>
+    <t>তইলি কি আঁই চলি যাইয়্যুম?</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1785,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="90.7777777777778" customWidth="1"/>
@@ -1652,448 +1952,1052 @@
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:2">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:2">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:2">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:2">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
+      <c r="A52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+      <c r="A53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
+      <c r="A54" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+      <c r="A55" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+      <c r="A56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+      <c r="A57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
+      <c r="A58" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
+      <c r="A59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+      <c r="A60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+      <c r="A61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+      <c r="A62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="A63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+      <c r="A64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="A69" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+      <c r="A71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+      <c r="A72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
+      <c r="A73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
+      <c r="A74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
+      <c r="A75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
+      <c r="A76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+      <c r="A77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
+      <c r="A78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
+      <c r="A79" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
+      <c r="A80" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
+      <c r="A81" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
+      <c r="A82" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="83" ht="25" customHeight="1" spans="1:2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+      <c r="A83" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="84" ht="25" customHeight="1" spans="1:2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
+      <c r="A84" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="85" ht="25" customHeight="1" spans="1:2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
+      <c r="A85" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="86" ht="25" customHeight="1" spans="1:2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
+      <c r="A86" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="87" ht="25" customHeight="1" spans="1:2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
+      <c r="A87" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="88" ht="25" customHeight="1" spans="1:2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
+      <c r="A88" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="89" ht="25" customHeight="1" spans="1:2">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
+      <c r="A89" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="90" ht="25" customHeight="1" spans="1:2">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
+      <c r="A90" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="91" ht="25" customHeight="1" spans="1:2">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
+      <c r="A91" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="92" ht="25" customHeight="1" spans="1:2">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
+      <c r="A92" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="93" ht="25" customHeight="1" spans="1:2">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
+      <c r="A93" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="94" ht="25" customHeight="1" spans="1:2">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
+      <c r="A94" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="95" ht="25" customHeight="1" spans="1:2">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
+      <c r="A95" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="96" ht="25" customHeight="1" spans="1:2">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
+      <c r="A96" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="97" ht="25" customHeight="1" spans="1:2">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
+      <c r="A97" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="98" ht="25" customHeight="1" spans="1:2">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
+      <c r="A98" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="99" ht="25" customHeight="1" spans="1:2">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
+      <c r="A99" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="100" ht="25" customHeight="1" spans="1:2">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
+      <c r="A100" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="101" ht="25" customHeight="1" spans="1:2">
+      <c r="A101" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="102" ht="25" customHeight="1" spans="1:2">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" ht="25" customHeight="1" spans="1:2">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" ht="25" customHeight="1" spans="1:2">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" ht="25" customHeight="1" spans="1:2">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" ht="25" customHeight="1" spans="1:2">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" ht="25" customHeight="1" spans="1:2">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" ht="25" customHeight="1" spans="1:2">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" ht="25" customHeight="1" spans="1:2">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" ht="25" customHeight="1" spans="1:2">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" ht="25" customHeight="1" spans="1:2">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" ht="25" customHeight="1" spans="1:2">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" ht="25" customHeight="1" spans="1:2">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" ht="25" customHeight="1" spans="1:2">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" ht="25" customHeight="1" spans="1:2">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" ht="25" customHeight="1" spans="1:2">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" ht="25" customHeight="1" spans="1:2">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" ht="25" customHeight="1" spans="1:2">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" ht="25" customHeight="1" spans="1:2">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" ht="25" customHeight="1" spans="1:2">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" ht="25" customHeight="1" spans="1:2">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" ht="25" customHeight="1" spans="1:2">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" ht="25" customHeight="1" spans="1:2">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" ht="25" customHeight="1" spans="1:2">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" ht="25" customHeight="1" spans="1:2">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" ht="25" customHeight="1" spans="1:2">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" ht="25" customHeight="1" spans="1:2">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" ht="25" customHeight="1" spans="1:2">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" ht="25" customHeight="1" spans="1:2">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" ht="25" customHeight="1" spans="1:2">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" ht="25" customHeight="1" spans="1:2">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" ht="25" customHeight="1" spans="1:2">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" ht="25" customHeight="1" spans="1:2">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" ht="25" customHeight="1" spans="1:2">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" ht="25" customHeight="1" spans="1:2">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" ht="25" customHeight="1" spans="1:2">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" ht="25" customHeight="1" spans="1:2">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" ht="25" customHeight="1" spans="1:2">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" ht="25" customHeight="1" spans="1:2">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" ht="25" customHeight="1" spans="1:2">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" ht="25" customHeight="1" spans="1:2">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" ht="25" customHeight="1" spans="1:2">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" ht="25" customHeight="1" spans="1:2">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" ht="25" customHeight="1" spans="1:2">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" ht="25" customHeight="1" spans="1:2">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" ht="25" customHeight="1" spans="1:2">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" ht="25" customHeight="1" spans="1:2">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" ht="25" customHeight="1" spans="1:2">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" ht="25" customHeight="1" spans="1:2">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" ht="25" customHeight="1" spans="1:2">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" ht="25" customHeight="1" spans="1:2">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" ht="25" customHeight="1" spans="1:2">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" ht="25" customHeight="1" spans="1:2">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" ht="25" customHeight="1" spans="1:2">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" ht="25" customHeight="1" spans="1:2">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" ht="25" customHeight="1" spans="1:2">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" ht="25" customHeight="1" spans="1:2">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" ht="25" customHeight="1" spans="1:2">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" ht="25" customHeight="1" spans="1:2">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" ht="25" customHeight="1" spans="1:2">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" ht="25" customHeight="1" spans="1:2">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" ht="25" customHeight="1" spans="1:2">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" ht="25" customHeight="1" spans="1:2">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" ht="25" customHeight="1" spans="1:2">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" ht="25" customHeight="1" spans="1:2">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" ht="25" customHeight="1" spans="1:2">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" ht="25" customHeight="1" spans="1:2">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" ht="25" customHeight="1" spans="1:2">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" ht="25" customHeight="1" spans="1:2">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" ht="25" customHeight="1" spans="1:2">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" ht="25" customHeight="1" spans="1:2">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" ht="25" customHeight="1" spans="1:2">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" ht="25" customHeight="1" spans="1:2">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" ht="25" customHeight="1" spans="1:2">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" ht="25" customHeight="1" spans="1:2">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" ht="25" customHeight="1" spans="1:2">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" ht="25" customHeight="1" spans="1:2">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" ht="25" customHeight="1" spans="1:2">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" ht="25" customHeight="1" spans="1:2">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" ht="25" customHeight="1" spans="1:2">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" ht="25" customHeight="1" spans="1:2">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" ht="25" customHeight="1" spans="1:2">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" ht="25" customHeight="1" spans="1:2">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" ht="25" customHeight="1" spans="1:2">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" ht="25" customHeight="1" spans="1:2">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" ht="25" customHeight="1" spans="1:2">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" ht="25" customHeight="1" spans="1:2">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" ht="25" customHeight="1" spans="1:2">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" ht="25" customHeight="1" spans="1:2">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" ht="25" customHeight="1" spans="1:2">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" ht="25" customHeight="1" spans="1:2">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+    </row>
+    <row r="192" ht="25" customHeight="1" spans="1:2">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+    </row>
+    <row r="193" ht="25" customHeight="1" spans="1:2">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+    </row>
+    <row r="194" ht="25" customHeight="1" spans="1:2">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+    </row>
+    <row r="195" ht="25" customHeight="1" spans="1:2">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+    </row>
+    <row r="196" ht="25" customHeight="1" spans="1:2">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+    </row>
+    <row r="197" ht="25" customHeight="1" spans="1:2">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+    </row>
+    <row r="198" ht="25" customHeight="1" spans="1:2">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+    </row>
+    <row r="199" ht="25" customHeight="1" spans="1:2">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+    </row>
+    <row r="200" ht="25" customHeight="1" spans="1:2">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+    </row>
+    <row r="201" ht="25" customHeight="1" spans="1:2">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="397">
   <si>
     <t>bangla</t>
   </si>
@@ -587,7 +587,7 @@
     <t>আপনাকে আজকে আমার খুব ভালো লাগলো</t>
   </si>
   <si>
-    <t>অঁনোরে আজিয়ে আত্তুন বত ভালা লাগিলো</t>
+    <t>অঁনোরে আজিয়ে আত্তুন বত ভালা লাইজ্ঞি</t>
   </si>
   <si>
     <t>সেটা কি আমার মন রাখার জন্য বলছ নাকি মানুষ কিছু বলবে সেজন্য বলছ?</t>
@@ -618,6 +618,658 @@
   </si>
   <si>
     <t>তইলি কি আঁই চলি যাইয়্যুম?</t>
+  </si>
+  <si>
+    <t>আমার একটু শরীর খারাপ লাগছে, আমি কি চলে যেতে পারব?</t>
+  </si>
+  <si>
+    <t>আত্তুন এক্কানা শরীর হারাপ লাগের, আঁই কি চলি যাইত পাইজ্জুম?</t>
+  </si>
+  <si>
+    <t>তোমাকে দেখে অসুস্থ মনে হচ্ছে, তুমি না হয় এখন চলে যাও</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে দেহি রে অসুস্থ মনে অর, তুঁই নয়তো এহন চলি যো</t>
+  </si>
+  <si>
+    <t>সাবধানে যাস, বাসায় পৌঁছে কল দিস</t>
+  </si>
+  <si>
+    <t>সাবধানে যাইস, বাসাত পৌছি কল দিস</t>
+  </si>
+  <si>
+    <t>চলে যাবেন? কেন চলে যাবেন?</t>
+  </si>
+  <si>
+    <t>চলি যাইবেন? কিল্লে চলি যাইবেন?</t>
+  </si>
+  <si>
+    <t>এই শুনছো, দেখে যাও আমি কি করেছি</t>
+  </si>
+  <si>
+    <t>এই উনো না, চো না আঁই কি গইজ্জি</t>
+  </si>
+  <si>
+    <t>আচ্ছা, যদি কিছু মনে না করেন একটা কথা জিজ্ঞেস করব?</t>
+  </si>
+  <si>
+    <t>আইচ্ছে, যদি কিছু মনে নগোরন এক্কান হতা ফুস গইজ্জুম?</t>
+  </si>
+  <si>
+    <t>দেখে যাও, কত জিনিস!</t>
+  </si>
+  <si>
+    <t>চাই য, হদিজ্ঞিন জিনিস!</t>
+  </si>
+  <si>
+    <t>ওরা যদি যেতে না চায়, তাহলে আমাদের কিছু করার নাই</t>
+  </si>
+  <si>
+    <t>ইতারা যদি যাইতো ন চায়, তইলি আরাত্তুন কিছু গরার নাই</t>
+  </si>
+  <si>
+    <t>এই গরমের দিনে বেশি করে পানি পান করুন এবং যথাসম্ভব বাইরের রোদ এড়িয়ে চলুন</t>
+  </si>
+  <si>
+    <t>এই গরোমর দিনোত বেশি গরি পানি হন আর যেদ্দুর পারন বাদ্দির রইদুত্তুন দূরে থাহন</t>
+  </si>
+  <si>
+    <t>আসেন আসেন, এত দেরি হলো কেন?</t>
+  </si>
+  <si>
+    <t>আইয়্যুন আইয়্যুন, এল্লেত দেরি অইয়্যি কা?</t>
+  </si>
+  <si>
+    <t>এখন একটু শান্ত হও, আর কত কাঁদবে?</t>
+  </si>
+  <si>
+    <t>এহন এক্কানা শান্ত অও, আর হত হাঁদিবে?</t>
+  </si>
+  <si>
+    <t>আমি ওদের সাথে কথা বলব, তুমি এখন শান্ত হও</t>
+  </si>
+  <si>
+    <t>আঁই ইতারার লগে হতা হইয়্যুম, তুঁই এহন শান্ত অও</t>
+  </si>
+  <si>
+    <t>সাথে এটাও নিয়ে যাও</t>
+  </si>
+  <si>
+    <t>লগে ইবেও লই যো</t>
+  </si>
+  <si>
+    <t>তোমার নতুন রান্নার রেসিপিটা আমাদেরও শিখাবে বলেছিলে, মনে আছে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার নয়া রান্নার রেসিপি ইবে আঁরারেও শিখাইবে হইলে, মনোত আছেনা?</t>
+  </si>
+  <si>
+    <t>আবহাওয়া আজ একটু ঠাণ্ডা, এডজাস্ট করতে না পারলে জ্যাকেটটা পরে নিলে ভালো হয়</t>
+  </si>
+  <si>
+    <t>আবাহাওয়া আজিয়ে এক্কানা ঠাণ্ডা, এডজাস্ট গরিত ন পারিলি জ্যাকেট ইবে পরি লইলি ভালা অই</t>
+  </si>
+  <si>
+    <t>আজকের মতো এখানেই শেষ করছি, তোমার সাথে কথা বলে ভাল লাগল</t>
+  </si>
+  <si>
+    <t>আজিয়ের মতো এনডে শেষ গরির, তোঁয়ার লগে হতা হইরে ভালা লেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>যেভাবেই হোক, আমাদেরকে এই বিপদ থেকে বের হতে হবে</t>
+  </si>
+  <si>
+    <t>যেনগরি অক, আরাত্তুন এই বিপদত্তোন বাইর অন পরিবো</t>
+  </si>
+  <si>
+    <t>অনেক্ষন কথা হলো, এবার উঠি</t>
+  </si>
+  <si>
+    <t>বত হতক্ষন হতা অইয়্যি, এবার উডি</t>
+  </si>
+  <si>
+    <t>এদের দুজনকে মিলিয়ে দিতে হবে</t>
+  </si>
+  <si>
+    <t>ইতারা দুনুজনোরে মিলাই দন পরিবো</t>
+  </si>
+  <si>
+    <t>আরে ভাই! তুই এখানে? আমি কি ঠিক দেখতাছি নাকি চোখের ভুল</t>
+  </si>
+  <si>
+    <t>আরে বদ্দা! তুই এনডে? আই কি ঠিক দেহির নাকি চখোর ভুল</t>
+  </si>
+  <si>
+    <t>আসো ভাই, আসো! বসো আগে, তারপর গল্প করবো আমরা</t>
+  </si>
+  <si>
+    <t>আইয়্যু বদ্দা, আইয়্যু! বইয়্যু আগে, তারপর গল্প গাইজ্জুম আঁরা</t>
+  </si>
+  <si>
+    <t>দেখি এবার বলো, এতদিন কোথায় ছিলে?</t>
+  </si>
+  <si>
+    <t>সাই এবার হ, এতদিন হন্ডে আছিলে</t>
+  </si>
+  <si>
+    <t>কেমন আছো জরিনা? তোমাকে অনেক মিস করতাছি</t>
+  </si>
+  <si>
+    <t>কেন আছো জরিনা? তোঁয়ার লাই বত পেট পুরের</t>
+  </si>
+  <si>
+    <t>কিরে! আজকে তুই সময়মতো চলে আসছোস! সুর্য কোনদিকে উঠছে</t>
+  </si>
+  <si>
+    <t>অবুক! আজিয়্যে তুই সময়মতো চলি আইস্যুস দে! সুর্য হুনদি উইঠ্যি</t>
+  </si>
+  <si>
+    <t>কি হয়েছে? তুমি আমাকে ডেকেছো কেন?</t>
+  </si>
+  <si>
+    <t>কি অইয়্যি দে? তুঁই আঁরে ডাইক্কো কিল্লে?</t>
+  </si>
+  <si>
+    <t>যা হওয়ার হয়ে গেছে, এগুলো পুরাতন কথা, এগুলো এখন বলে লাভ আছে?</t>
+  </si>
+  <si>
+    <t>যা অইবের অই গেইয়্যি, এগিন পুরন হতা, এগিন এহন হয় রে লাভ আছে না?</t>
+  </si>
+  <si>
+    <t>তুমি কি পাগল? মানুষজন দেখলে কি বলবে?</t>
+  </si>
+  <si>
+    <t>তুঁই কি পল না? মাইনসে দেহিলি কি হইবু?</t>
+  </si>
+  <si>
+    <t>আমার ভাল লাগছেনা, আমি এখন চলে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আত্তুন গম নলার, আঁই এহন চলি যাইর</t>
+  </si>
+  <si>
+    <t>বলুন, আমি আপনার জন্য কি করতে পারি?</t>
+  </si>
+  <si>
+    <t>হন, আঁই অঁনোর লাই কি গরিত পারি?</t>
+  </si>
+  <si>
+    <t>তুমি যেটা বলবে ওটা করবো</t>
+  </si>
+  <si>
+    <t>তুঁই যিইয়্যেন হইবে ইয়েন গইজ্জুম</t>
+  </si>
+  <si>
+    <t>যদি তুমি আসো তাহলে আমি অনেক খুশি হবো, অনেকদিন তুমাকে দেখি নাই</t>
+  </si>
+  <si>
+    <t>যদি তুঁই আইয়্যু তইলি আঁই বত খুশি অইয়্যুম, বতদিন তোঁয়ারে ন দেহি</t>
+  </si>
+  <si>
+    <t>তুই না আসলে বন্ধু আমি রাগ করব</t>
+  </si>
+  <si>
+    <t>তুই নো আইলি বন্ধু আই গুসসা অইয়্যুম</t>
+  </si>
+  <si>
+    <t>তুই আসলে ভাই আমি অনেক খুশি হব</t>
+  </si>
+  <si>
+    <t>তুই আইলি বদ্দা আই বত খুশি অইয়্যুম</t>
+  </si>
+  <si>
+    <t>তুই একদম আমাকে ভুলে গেছিস, একটা কল পর্যন্ত দেস না</t>
+  </si>
+  <si>
+    <t>তুই এব্বেরে আঁরে ভুলি গেইয়্যুস, ওজ্ঞো কল পর্যন্ত নো দস</t>
+  </si>
+  <si>
+    <t>রফিক সাহেব কেমন আছেন? অনেকদিন তাঁর সাথে দেখা হয় নাই, আমার চিন্তা হচ্ছে এখন</t>
+  </si>
+  <si>
+    <t>রফিক সাব কেন আছে? বতদিন ইবের লগে দেহা ন আই, আত্তোন চিন্তে লাগের এহন</t>
+  </si>
+  <si>
+    <t>উনার কথা মনে পড়লে চিন্তা হয়</t>
+  </si>
+  <si>
+    <t>ইবের হতা মনোত পরিলি চিন্তে অই</t>
+  </si>
+  <si>
+    <t>উনার কি আমার কথা এখনো মনে আছে?</t>
+  </si>
+  <si>
+    <t>ইবেত্তুন কি আঁর হতা এহনো মনোত আছে?</t>
+  </si>
+  <si>
+    <t>তোমার কি সমাস্যা? মানতে কেন পারছো না?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার কি সমাস্যা? মানিত কা ন পারো?</t>
+  </si>
+  <si>
+    <t>তুমি তো অনেক বড় জ্ঞানী হয়ে গেছো!</t>
+  </si>
+  <si>
+    <t>তুঁই তো বত বরো পন্ডিত আই গেইয়্যু!</t>
+  </si>
+  <si>
+    <t>তোমার জন্য এই ওষুধটা রেখেছি, মনে করে খাবে কিন্তু, ঠিক আছে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার লাই ওষুধ ইবে রাইক্কি, মনোত গরি হাইবে কিন্তু, ঠিক আছে না?</t>
+  </si>
+  <si>
+    <t>মা, তুমি একটু বসো, আমি সব করছি, আজকে তোমাকে কিছু করতে দিব না</t>
+  </si>
+  <si>
+    <t>আম্মু, তুঁই এক্কানা বইয়্যু, আঁই বিয়াজ্ঞিন গরির, আজিয়্যে তোঁয়ারে কিছু গইত্তাম দিতাম নো</t>
+  </si>
+  <si>
+    <t>ভাই, তোর জন্য কিছু মিষ্টি এনেছি, নিয়ে যা, তোর অনেক পছন্দের জিনিস!</t>
+  </si>
+  <si>
+    <t>বদ্দা, তোর লাই কিছু মিষ্টি আইন্নি, লই যা, তোর বত পছন্দের জিনিস!</t>
+  </si>
+  <si>
+    <t>চাচা, গাড়ি চালানোর সময় একটু স্লো করুন, রাস্তাটা একটু খারাপ</t>
+  </si>
+  <si>
+    <t>চাচা, গারি চালাইবের সময় এক্কানা স্লো গরোন, রাস্তা ইবে এক্কানা হারাপ</t>
+  </si>
+  <si>
+    <t>গরম কাপড় পড়ে বের হয়েছেন তো? আজকে বাইরে বেশি ঠাণ্ডা</t>
+  </si>
+  <si>
+    <t>গরম হর পরি বাইর অইয়্যুন তো? আজিয়্যে বাইরে বেশি ঠাণ্ডা</t>
+  </si>
+  <si>
+    <t>ওষুধটা সময়মতো খেয়ো, নয়তো আবার জ্বর আসবে, আমার কথা শোনো</t>
+  </si>
+  <si>
+    <t>ওষুধ ইবে সময়মতো হাইয়্যু, নইলি আবার জ্বর আইবু, আঁর হতা উনো</t>
+  </si>
+  <si>
+    <t>একটু হাসো, এত চিন্তা করে কী হবে? সব ঠিক হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এক্কানা আ'সো, এত চিন্তে গরি কি অইবু? বিয়াক ঠিক আই যাইবু</t>
+  </si>
+  <si>
+    <t>তোমাকে হাসলে অনেক সুন্দর লাগে</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে আ'সিলি বত সুন্দর লাগে</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> যদি তুমি ঠিক করে ফেলো কোন পথে যেতে চাও, আমি পুরো যাত্রায় তোমার সঙ্গ দিতে প্রস্তুত আছি</t>
+  </si>
+  <si>
+    <t>যদি তুঁই ঠিক গরি ফেলো হন পথোত যাইতো চো, আঁই পুরো যাত্রাত তোঁয়ার সঙ্গ দিবের লাই প্রস্তুত আছি</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>যখনই মনে হবে হারিয়ে ফেলেছ, তখনই একটু থেমে নিজেকে জিজ্ঞেস করো</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>তুমি কেন শুরু করেছিলে</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>যহনই মনে অইবু হারায় ফেলাইয়্যো, তহনই এক্কানা থামি রে নিজোরে ফুসর গরো</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>তুঁই কিল্লে শুরু গইজ্জিলে</t>
+    </r>
+  </si>
+  <si>
+    <t>বাগানে তোমার লাগানো নতুন গাছটা কত দ্রুত বাড়ছে, দেখলে সত্যিই মন ভরে যায়</t>
+  </si>
+  <si>
+    <t>বাগানোত তোঁয়ার লাগানো নয়া গাছ ইবে হত দ্রুত বরো অর, দেহিলি সত্যিই মন ভরি যায়</t>
+  </si>
+  <si>
+    <t>দেখো আমার বাগানটা কত সুন্দর!</t>
+  </si>
+  <si>
+    <t>সো আঁর বাগান ইয়েন হতো সুন্দর!</t>
+  </si>
+  <si>
+    <t>মারজানের কি খবর? শুনেছি তার নাকি বিয়ে ঠিক হয়ে গেছে, এটা কি সত্যি?</t>
+  </si>
+  <si>
+    <t>মারজানোর কি হবর? উইন্নিলাম তার নাকি বিয়ে ঠিক অই গেইয়্যি, ইয়েন কি আঁছা?</t>
+  </si>
+  <si>
+    <t>মালিহার নাকি বিয়ে ঠিক হয়েছে? তার এত জলদি বিয়ে হবে চিন্তা করিনায়</t>
+  </si>
+  <si>
+    <t>মালিহার বলে বিয়ে ঠিক অইয়্যি? ইতির এল্লেত তারাতারি বিয়ে অইবু ইয়েন চিন্তে নো গরি</t>
+  </si>
+  <si>
+    <t>তোর ছোট ভাই নাকি বিয়ে করেছে? তার এত জলদি বিয়ে হবে চিন্তা করিনায়</t>
+  </si>
+  <si>
+    <t xml:space="preserve">তুর ছোডো ভাই বলে বিয়ে গইজ্জি? ইতের এল্লেত তারাতারি বিয়ে অইবু ইয়েন চিন্তে নো গরি </t>
+  </si>
+  <si>
+    <t>তোমার ছোট ভাই সামিরের কি খবর? এখন কোন ক্লাসে পড়ে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার ছোডো ভাই সামিরোর কি হবর? এহন হন ক্লাসোত পরে?</t>
+  </si>
+  <si>
+    <t>তোমার বড় ভাই এখন কি করে, জব করে নাকি ব্যাবসা করে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার বদ্দা এহন কি গরে? ছরি গরে নাকি ব্যাবসা গরে?</t>
+  </si>
+  <si>
+    <t>যদি তুই তাড়াতাড়ি ধনী হতে ছাস তাহলে জব না করে ব্যাবসা কর</t>
+  </si>
+  <si>
+    <t>যদি তুই তারাতারি বরোলোক অইতো ছস তইলি ছরি নগোরি ব্যাবসা গর</t>
+  </si>
+  <si>
+    <t>আজকে শুক্রবার, আজকে বেশি কাজ, সেজন্য বেশি ব্যস্ত থাকব</t>
+  </si>
+  <si>
+    <t>আজিয়্যে শুক্কুরবার, আজিয়্যে বেশি হাম, এতেল্লে বেশি বিজি থাইক্কুম</t>
+  </si>
+  <si>
+    <t>আসুন আমরা আমাদের ছোট ছোট প্রচেষ্টার মাধ্যমে একটি বড় পার্থক্য তৈরি করার চেষ্টা করি</t>
+  </si>
+  <si>
+    <t>আইয়্যুন আঁরা আঁরার ছোডো ছোডো প্রচেষ্টার মাইধ্যমে এক্কান বরো পার্থইক্যো তৈরি গরিবের চেষ্টা গরি</t>
+  </si>
+  <si>
+    <t>তুমি অনেক পরিবর্তন হয়ে গেছো, আমাকে আর আগের মতো ভালোবাসো না</t>
+  </si>
+  <si>
+    <t>তুঁই বত বদলাই গেইয়্যু, আঁরে আর আগোর মতোন ভালো নবাসো</t>
+  </si>
+  <si>
+    <t>আজকে শুক্রবার, সেজন্য আজকে জুমার নামাজ পড়তে হবে</t>
+  </si>
+  <si>
+    <t>আজিয়ে শুক্রবার, এতেল্লে আজিয়ে জুমার নামাজ পরন পরিবো</t>
+  </si>
+  <si>
+    <t>হ্যালো আসসালামু আলাইকু্ম, কেমন আছেন? কতোদিন পর</t>
+  </si>
+  <si>
+    <t>হ্যালো আসসালামু আলাইকুম, কেন আছন? হতোদিন পর</t>
+  </si>
+  <si>
+    <t>তোমাকে ফোন দিলে ধরো না, বেশি ব্যস্ত মনে হয়</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে ফোন দিলি ন ধরো, বেশি বিজি ফানলা</t>
+  </si>
+  <si>
+    <t>এতদিন পর আমার কথা মনে পড়ছে, একটা কল ও দাও না</t>
+  </si>
+  <si>
+    <t>এতোদিন পরে আঁর হতা মনোত পইজ্জি, ওজ্ঞো কল ও ন দো</t>
+  </si>
+  <si>
+    <t>এই প্রকল্পটি শুধু আমাদের নয়, বরং আগামী প্রজন্মের জন্য একটি উজ্জ্বল ভবিষ্যৎ তৈরি করবে</t>
+  </si>
+  <si>
+    <t>এই  প্রকল্প ইবে শুধু আঁরার নো, বরং আগামী প্রজন্মোর লাই এক্কান উজ্জল ভবিষ্যৎ তৈরি গরিবো</t>
+  </si>
+  <si>
+    <t>তুমি আমার সাথে এরকম কেমনে করলা! আমার কি দোষ ছিল?</t>
+  </si>
+  <si>
+    <t>তুঁই আঁর লগে এরহম কেনে গরিলে! আঁর কি দোষ আছিল?</t>
+  </si>
+  <si>
+    <t>আমার যদি দোষ থাকতো তাহলে আমি মেনে নিতাম</t>
+  </si>
+  <si>
+    <t>আঁর যদি দোষ থাইকতো তইলি আঁই মানি লইতাম</t>
+  </si>
+  <si>
+    <t>যেখানে আমার কোন দোষ নাই সেখানে তুমি এটা কেমনে করলা</t>
+  </si>
+  <si>
+    <t>যেনডে আঁর হনো দোষ নাই এনডে তুঁই ইয়েন কেনে গরিলে</t>
+  </si>
+  <si>
+    <t>আমার কথা বুঝার চেষ্টা করো, আমি করিনাই এটা</t>
+  </si>
+  <si>
+    <t>আঁর হতা বুঝিবের চেষ্টা গরো, আঁই নোগরি ইয়েন</t>
+  </si>
+  <si>
+    <t>কেমন আছিস বন্ধু? ঢাকা থেকে কখন আসছোস?</t>
+  </si>
+  <si>
+    <t>কেন আছোস বন্ধু? ঢাহাত্তুন হত্তে আইস্যুস?</t>
+  </si>
+  <si>
+    <t>এবার ঢাকা থেকে আসার সময় আমার জন্য একটা পাঞ্জাবি আনিস</t>
+  </si>
+  <si>
+    <t>এবার ঢাহাত্তুন আইবের সমোত আঁর লাই ওজ্ঞো পাঞ্জাবি আনিস</t>
+  </si>
+  <si>
+    <t>কতোদিন পর তুর সাথে দেখা!</t>
+  </si>
+  <si>
+    <t>হতোদিন পর তুর লাগে দেহা!</t>
+  </si>
+  <si>
+    <t>ঢাকায় গিয়ে তো আমাদেরকে ভুলে গেছিস</t>
+  </si>
+  <si>
+    <t>ঢাহাত যায় রে তো আরারে ভুলি গেইয়্যুস</t>
+  </si>
+  <si>
+    <t>তুমি আজকে কোথায় গিয়েছিলে?</t>
+  </si>
+  <si>
+    <t>তুঁই আজিয়ে হনডে গেইয়্যো?</t>
+  </si>
+  <si>
+    <t>আমার ফুল ভাল লাগে এবং আমি বাগান করতে পছন্দ করি</t>
+  </si>
+  <si>
+    <t>আত্তুন ফুল গম লাগে আর আঁই বাগান গত্তে পছন্দ গরি</t>
+  </si>
+  <si>
+    <t>তুই কি মেলায় যাচ্ছিস? আমিও যাব</t>
+  </si>
+  <si>
+    <t>তুই কি মেলাত যোর? আই অ যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>কি হয়েছে! কি হয়েছে জানিস না?</t>
+  </si>
+  <si>
+    <t>কি অইয়্যি দে! কি অইয়্যি দে ন জানোস?</t>
+  </si>
+  <si>
+    <t>তাহলে এতোদিন পর আমার কথা মনে পড়ছে</t>
+  </si>
+  <si>
+    <t>তইলি এতোদিন পর আঁর হতা মনোত পইজ্জি</t>
+  </si>
+  <si>
+    <t>এতোদিন পর আমার খবর নিচ্ছো! একবারের জন্য আমার কথা মনেও পড়ে নাই</t>
+  </si>
+  <si>
+    <t>এতোদিন পর আঁর হবর লইতে লাইজ্ঞো! একবারোর লাই আঁর হতা মনোত'অ নো পরে</t>
+  </si>
+  <si>
+    <t>ফোন রিসভ করছেনা, মনে হয় ব্যস্ত</t>
+  </si>
+  <si>
+    <t>ফোন রিসিভ ন গরের, মনে অয় বিজি</t>
+  </si>
+  <si>
+    <t>কি আর বলব, তুমি তো আমাকে ভুলে গেছো</t>
+  </si>
+  <si>
+    <t>কি আর হইয়্যুম, তুঁই তো আঁরে ভুলি গেইয়্যো</t>
+  </si>
+  <si>
+    <t>তুমি কি আমার সাথে কথা বলবা নাকি রাগ করে থাকবা?</t>
+  </si>
+  <si>
+    <t>তুঁই কি আঁর লগে হতা হইবে নাকি গুসসা গরি তাহিবে?</t>
+  </si>
+  <si>
+    <t>রাগ করলে কিন্তু আমার ভাল লাগেনা</t>
+  </si>
+  <si>
+    <t>গুসসা অইলি কিন্তু আত্তুন গম ন লাগে</t>
+  </si>
+  <si>
+    <t>খুব মনে পড়ছে কিন্তু কাকে মনে পড়ছে সেটাই মনে পড়ছে না</t>
+  </si>
+  <si>
+    <t>বত মনোত পরের কিন্তু হারে মনোত পরের ইয়েন ই মনোত ন পরের</t>
+  </si>
+  <si>
+    <t>আমি এখন চলে যাচ্ছি, তুমি পরে আসিও</t>
+  </si>
+  <si>
+    <t>আঁই এহন চলি যাইর, তুঁই পরে আইস্যো</t>
+  </si>
+  <si>
+    <t>আমি এখন নিছে যাবো</t>
+  </si>
+  <si>
+    <t>আঁই এহন নিছে যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>তুমি কি জান আজকে কি হয়েছে?</t>
+  </si>
+  <si>
+    <t>তুঁই কি হইত পারো আজিয়ে কি অইয়্যি?</t>
+  </si>
+  <si>
+    <t>আমি জানিনা আজকে কি হয়েছে</t>
+  </si>
+  <si>
+    <t>আঁই ন জানি আজিয়ে কি অইয়্যি</t>
+  </si>
+  <si>
+    <t>আজকে তুর একদিন কি আমার একদিন</t>
+  </si>
+  <si>
+    <t>আজিয়ে তুর একদিন কি আর একদিন</t>
+  </si>
+  <si>
+    <t>তুই আমাকে বলিস নাই কেন?</t>
+  </si>
+  <si>
+    <t>তুই আঁরে নহস কা?</t>
+  </si>
+  <si>
+    <t>আমি ডক্তারের কাছে যাচ্ছি, তুমি কি আমার সাথে যাবে?</t>
+  </si>
+  <si>
+    <t>আঁই ডাক্তারোর হাছে যাইর, তুঁই কি আঁর ফুয়ারে যাইবে?</t>
+  </si>
+  <si>
+    <t>তুমি একটু মামুনের সাথে যাও</t>
+  </si>
+  <si>
+    <t>তুই এক্কানা মামুনোর লগে যো</t>
+  </si>
+  <si>
+    <t>আমার একটু খারাপ লাগছে, আমি যেতে পারব না</t>
+  </si>
+  <si>
+    <t>আত্তুন এক্কানা হারাপ লার, আঁই যাইত পাইত্তাম নো</t>
+  </si>
+  <si>
+    <t>আমি বাজার করতে যাচ্ছি ভাই, তুই কোথায় যাচ্ছিস?</t>
+  </si>
+  <si>
+    <t>আই বাজার গইত্তাম যাইর বদ্দা, তুই হনডে যোর?</t>
+  </si>
+  <si>
+    <t>যাওয়ার সময় আলিয়াকেও সাথে নিয়ে যেও</t>
+  </si>
+  <si>
+    <t>যাইবের সমোত আলিয়ারেও ওয়ারে লই যাইয়্যো</t>
+  </si>
+  <si>
+    <t>আর একটু বাকি, হয়ে যাবে এখন</t>
+  </si>
+  <si>
+    <t>আর এক্কানা বাকি, অই যাইবু এহন</t>
+  </si>
+  <si>
+    <t>তুই একটা কাজ কর, আমাকে একটু বিষ এনে দে</t>
+  </si>
+  <si>
+    <t>তুই এক্কান হাজ গর, আঁরে এক্কানা বিষ আনি দে</t>
+  </si>
+  <si>
+    <t>সব দোষ তোমার, তোমার জন্য এসব হচ্ছে</t>
+  </si>
+  <si>
+    <t>বিয়াক দোষ তোঁয়ার, তোঁয়ার হারোনে এগিন অর</t>
+  </si>
+  <si>
+    <t>দোয়া করিস বন্ধু, সামনে অনেক কাজ</t>
+  </si>
+  <si>
+    <t>দোয়া গরিস বন্ধু, সামনে বত হাম</t>
+  </si>
+  <si>
+    <t>ভালো থাকিস, আবার দেখা হবে, আল্লাহ হাফেজ</t>
+  </si>
+  <si>
+    <t>ভালা থাহিস, আবার দেহা অইবু, আল্লাহ হাফেজ</t>
   </si>
 </sst>
 </file>
@@ -630,7 +1282,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,6 +1439,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1239,14 +1897,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2592,412 +3247,812 @@
       </c>
     </row>
     <row r="101" ht="25" customHeight="1" spans="1:2">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="102" ht="25" customHeight="1" spans="1:2">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
+      <c r="A102" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="103" ht="25" customHeight="1" spans="1:2">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
+      <c r="A103" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="104" ht="25" customHeight="1" spans="1:2">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
+      <c r="A104" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="105" ht="25" customHeight="1" spans="1:2">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
+      <c r="A105" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="106" ht="25" customHeight="1" spans="1:2">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
+      <c r="A106" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="107" ht="25" customHeight="1" spans="1:2">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
+      <c r="A107" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="108" ht="25" customHeight="1" spans="1:2">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
+      <c r="A108" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="109" ht="25" customHeight="1" spans="1:2">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
+      <c r="A109" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="110" ht="25" customHeight="1" spans="1:2">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
+      <c r="A110" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="111" ht="25" customHeight="1" spans="1:2">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
+      <c r="A111" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="112" ht="25" customHeight="1" spans="1:2">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
+      <c r="A112" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="113" ht="25" customHeight="1" spans="1:2">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
+      <c r="A113" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="114" ht="25" customHeight="1" spans="1:2">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
+      <c r="A114" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="115" ht="25" customHeight="1" spans="1:2">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
+      <c r="A115" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="116" ht="25" customHeight="1" spans="1:2">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
+      <c r="A116" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="117" ht="25" customHeight="1" spans="1:2">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
+      <c r="A117" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="118" ht="25" customHeight="1" spans="1:2">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
+      <c r="A118" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="119" ht="25" customHeight="1" spans="1:2">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
+      <c r="A119" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="120" ht="25" customHeight="1" spans="1:2">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
+      <c r="A120" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="121" ht="25" customHeight="1" spans="1:2">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
+      <c r="A121" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="122" ht="25" customHeight="1" spans="1:2">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
+      <c r="A122" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="123" ht="25" customHeight="1" spans="1:2">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
+      <c r="A123" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="124" ht="25" customHeight="1" spans="1:2">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
+      <c r="A124" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="125" ht="25" customHeight="1" spans="1:2">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
+      <c r="A125" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="126" ht="25" customHeight="1" spans="1:2">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
+      <c r="A126" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="127" ht="25" customHeight="1" spans="1:2">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
+      <c r="A127" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="128" ht="25" customHeight="1" spans="1:2">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
+      <c r="A128" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="129" ht="25" customHeight="1" spans="1:2">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
+      <c r="A129" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="130" ht="25" customHeight="1" spans="1:2">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
+      <c r="A130" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="131" ht="25" customHeight="1" spans="1:2">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
+      <c r="A131" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="132" ht="25" customHeight="1" spans="1:2">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
+      <c r="A132" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="133" ht="25" customHeight="1" spans="1:2">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
+      <c r="A133" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="134" ht="25" customHeight="1" spans="1:2">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
+      <c r="A134" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="135" ht="25" customHeight="1" spans="1:2">
-      <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
+      <c r="A135" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="136" ht="25" customHeight="1" spans="1:2">
-      <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
+      <c r="A136" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="137" ht="25" customHeight="1" spans="1:2">
-      <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
+      <c r="A137" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="138" ht="25" customHeight="1" spans="1:2">
-      <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
+      <c r="A138" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="139" ht="25" customHeight="1" spans="1:2">
-      <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
+      <c r="A139" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="140" ht="25" customHeight="1" spans="1:2">
-      <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
+      <c r="A140" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="141" ht="25" customHeight="1" spans="1:2">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
+      <c r="A141" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="142" ht="25" customHeight="1" spans="1:2">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
+      <c r="A142" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="143" ht="25" customHeight="1" spans="1:2">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
+      <c r="A143" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="144" ht="25" customHeight="1" spans="1:2">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
+      <c r="A144" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="145" ht="25" customHeight="1" spans="1:2">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
+      <c r="A145" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="146" ht="25" customHeight="1" spans="1:2">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
+      <c r="A146" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="147" ht="25" customHeight="1" spans="1:2">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
+      <c r="A147" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="148" ht="25" customHeight="1" spans="1:2">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
+      <c r="A148" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="149" ht="25" customHeight="1" spans="1:2">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
+      <c r="A149" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="150" ht="25" customHeight="1" spans="1:2">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
+      <c r="A150" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="151" ht="25" customHeight="1" spans="1:2">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
+      <c r="A151" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="152" ht="25" customHeight="1" spans="1:2">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
+      <c r="A152" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="153" ht="25" customHeight="1" spans="1:2">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
+      <c r="A153" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="154" ht="25" customHeight="1" spans="1:2">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
+      <c r="A154" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="155" ht="25" customHeight="1" spans="1:2">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
+      <c r="A155" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="156" ht="25" customHeight="1" spans="1:2">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
+      <c r="A156" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="157" ht="25" customHeight="1" spans="1:2">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
+      <c r="A157" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="158" ht="25" customHeight="1" spans="1:2">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
+      <c r="A158" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="159" ht="25" customHeight="1" spans="1:2">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
+      <c r="A159" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="160" ht="25" customHeight="1" spans="1:2">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
+      <c r="A160" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="161" ht="25" customHeight="1" spans="1:2">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
+      <c r="A161" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="162" ht="25" customHeight="1" spans="1:2">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
+      <c r="A162" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="163" ht="25" customHeight="1" spans="1:2">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
+      <c r="A163" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="164" ht="25" customHeight="1" spans="1:2">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
+      <c r="A164" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="165" ht="25" customHeight="1" spans="1:2">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
+      <c r="A165" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="166" ht="25" customHeight="1" spans="1:2">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
+      <c r="A166" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="167" ht="25" customHeight="1" spans="1:2">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
+      <c r="A167" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="168" ht="25" customHeight="1" spans="1:2">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
+      <c r="A168" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="169" ht="25" customHeight="1" spans="1:2">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
+      <c r="A169" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="170" ht="25" customHeight="1" spans="1:2">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
+      <c r="A170" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="171" ht="25" customHeight="1" spans="1:2">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
+      <c r="A171" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="172" ht="25" customHeight="1" spans="1:2">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
+      <c r="A172" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="173" ht="25" customHeight="1" spans="1:2">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
+      <c r="A173" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="174" ht="25" customHeight="1" spans="1:2">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
+      <c r="A174" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="175" ht="25" customHeight="1" spans="1:2">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
+      <c r="A175" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="176" ht="25" customHeight="1" spans="1:2">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
+      <c r="A176" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="177" ht="25" customHeight="1" spans="1:2">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
+      <c r="A177" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="178" ht="25" customHeight="1" spans="1:2">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
+      <c r="A178" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="179" ht="25" customHeight="1" spans="1:2">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
+      <c r="A179" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="180" ht="25" customHeight="1" spans="1:2">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
+      <c r="A180" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="181" ht="25" customHeight="1" spans="1:2">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
+      <c r="A181" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="182" ht="25" customHeight="1" spans="1:2">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
+      <c r="A182" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="183" ht="25" customHeight="1" spans="1:2">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
+      <c r="A183" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="184" ht="25" customHeight="1" spans="1:2">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
+      <c r="A184" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="185" ht="25" customHeight="1" spans="1:2">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
+      <c r="A185" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="186" ht="25" customHeight="1" spans="1:2">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
+      <c r="A186" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="187" ht="25" customHeight="1" spans="1:2">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
+      <c r="A187" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="188" ht="25" customHeight="1" spans="1:2">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
+      <c r="A188" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="189" ht="25" customHeight="1" spans="1:2">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
+      <c r="A189" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="190" ht="25" customHeight="1" spans="1:2">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
+      <c r="A190" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="191" ht="25" customHeight="1" spans="1:2">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
+      <c r="A191" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="192" ht="25" customHeight="1" spans="1:2">
-      <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
+      <c r="A192" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="193" ht="25" customHeight="1" spans="1:2">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
+      <c r="A193" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="194" ht="25" customHeight="1" spans="1:2">
-      <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
+      <c r="A194" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="195" ht="25" customHeight="1" spans="1:2">
-      <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
+      <c r="A195" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="196" ht="25" customHeight="1" spans="1:2">
-      <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
+      <c r="A196" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="197" ht="25" customHeight="1" spans="1:2">
-      <c r="A197" s="3"/>
-      <c r="B197" s="3"/>
+      <c r="A197" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="198" ht="25" customHeight="1" spans="1:2">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
+      <c r="A198" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="199" ht="25" customHeight="1" spans="1:2">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
+      <c r="A199" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="200" ht="25" customHeight="1" spans="1:2">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
+      <c r="A200" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="201" ht="25" customHeight="1" spans="1:2">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
+      <c r="A201" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>396</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="498">
   <si>
     <t>bangla</t>
   </si>
@@ -975,7 +975,7 @@
     <t>দেখো আমার বাগানটা কত সুন্দর!</t>
   </si>
   <si>
-    <t>সো আঁর বাগান ইয়েন হতো সুন্দর!</t>
+    <t>স আঁর বাগান ইয়েন হতো সুন্দর!</t>
   </si>
   <si>
     <t>মারজানের কি খবর? শুনেছি তার নাকি বিয়ে ঠিক হয়ে গেছে, এটা কি সত্যি?</t>
@@ -1270,6 +1270,309 @@
   </si>
   <si>
     <t>ভালা থাহিস, আবার দেহা অইবু, আল্লাহ হাফেজ</t>
+  </si>
+  <si>
+    <t>আমি সকালে তাড়াতাড়ি উঠি</t>
+  </si>
+  <si>
+    <t>আঁই বেইন্নে তারাতারি উডি</t>
+  </si>
+  <si>
+    <t>ভোরে সূর্য ওঠার আগেই আমি উঠে পড়ি, তারপর নামাজ পড়ি</t>
+  </si>
+  <si>
+    <t>ফোয়াত্তে সূর্য উডিবের আগেই আঁই উডি যায়, তারপর নামাজ পরি</t>
+  </si>
+  <si>
+    <t>সকালের সূর্য অনেক সুন্দর</t>
+  </si>
+  <si>
+    <t>বেইন্নের সূর্য ইবে বত সুন্দর</t>
+  </si>
+  <si>
+    <t>আজকে সকালে উঠতে দেরি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেইন্নে উঠতে দেরি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সকালে নামাজ পড়ে হাটলে অনেক ভাল লাগে</t>
+  </si>
+  <si>
+    <t>ফজোরত নামাজ পরি আডিলি বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>আগামিকাল পরিক্ষা, সেজন্য সকালে জলদি উঠতে হবে</t>
+  </si>
+  <si>
+    <t>হালিয়ে পরিক্ষে, এতেল্লে বেইন্নে তারাতারি উডোন পরিবো</t>
+  </si>
+  <si>
+    <t>আজকে বাসায় মেহমান আসবে, সেজন্য তাড়াতাড়ি উঠে গেছি</t>
+  </si>
+  <si>
+    <t>আজিয়ে বাসাত মেমান আইবো, এতেল্লে তারাতারি উডি গেই</t>
+  </si>
+  <si>
+    <t>নাস্তা করতে আসো, ঠান্ডা হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>নাস্তা গইত্তো আইয়্যু, ঠান্ডা অই যার</t>
+  </si>
+  <si>
+    <t>আমি এখন খাব না, একটু পরে খাব</t>
+  </si>
+  <si>
+    <t>আঁই এহন হাইতাম নো, এক্কানা পরে হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>সকালে এক কাপ চা না খেলে হয় না</t>
+  </si>
+  <si>
+    <t>ফজোরত এক হাপ চা নো হাইলি নো অই</t>
+  </si>
+  <si>
+    <t>রুটি ঠান্ডা হয়ে যাচ্ছে, খেতে আয়</t>
+  </si>
+  <si>
+    <t>রুটি ঠান্ডা অই যার, হাইতো আয়</t>
+  </si>
+  <si>
+    <t>আজকে আমি রুটি খাব না, ভাত খাব আজকে</t>
+  </si>
+  <si>
+    <t>আজিয়ে আঁই রুটি হাইতাম নো, ভাত হাইয়্যুম আজিয়ে</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> আপনি কখন সকালের নাস্তা করেন?</t>
+  </si>
+  <si>
+    <t>অঁনে হত্তে বেইন্নের নাস্তা গরোন?</t>
+  </si>
+  <si>
+    <t>আমি প্রতিদিন সকালে তাড়াতাড়ি উঠে যায়</t>
+  </si>
+  <si>
+    <t>আঁই পইত্তোদিন ফজোরত তারাতারি উডি যায়</t>
+  </si>
+  <si>
+    <t>সকালে ব্যায়াম করলে শরীর ভালো থাকে</t>
+  </si>
+  <si>
+    <t>বেইন্নে বিয়াম গরিলি শরীর ভালা থাহে</t>
+  </si>
+  <si>
+    <t>আমি নাস্তার পরে চা খেতে পছন্দ করি</t>
+  </si>
+  <si>
+    <t>আঁই নাস্তার পরে চা হাইতাম পছন্দ গরি</t>
+  </si>
+  <si>
+    <t>আমি সকালে উঠে খালি পেঠে এক গ্লাস পানি খায়</t>
+  </si>
+  <si>
+    <t>আঁই বেইন্নে উডি হালি ফেডে এক গ্লাস পানি হায়</t>
+  </si>
+  <si>
+    <t>মুরগির ডাক শুনে ঘুম ভেঙ্গে গেছে</t>
+  </si>
+  <si>
+    <t>কুরোর ডাক উনি ঘুম ভাঙ্গি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>মুরগি এটা এত চিৎকার কেন করে, ঘুমাতে পারছিনা</t>
+  </si>
+  <si>
+    <t>কুরো ইবে এল্লেত চিল্লের কা, ঘুম যাইত ন পারির</t>
+  </si>
+  <si>
+    <t>সকালে উঠে কিছুক্ষণ হাঁটলে শরীর ভালো থাকে</t>
+  </si>
+  <si>
+    <t>সকালে উডি হতক্ষন আডিলি শরীর ভালা থাহে</t>
+  </si>
+  <si>
+    <t>তাড়াতাড়ি উঠো ঘুম থেকে, বাজারে যেতে হবে মাছ আনার জন্য</t>
+  </si>
+  <si>
+    <t>তারাতারি উডো ঘুমোত্তন, বাজারোত যন পরিবো মাছ আনিবের লাই</t>
+  </si>
+  <si>
+    <t>আসো সবাই একসাথে নাস্তা করি</t>
+  </si>
+  <si>
+    <t>আইয়্যু বিয়াজ্ঞুন এক্কত্তরে নাস্তা গরি</t>
+  </si>
+  <si>
+    <t>আমি প্রতিদিন রাত দশটায় ঘুমায় যায় যেন সকালে তাড়াতাড়ি উঠতে পারি</t>
+  </si>
+  <si>
+    <t>আঁই পইত্তোদিন রাতিয়ে দশটা বাজে ঘুমায় যায় যাতে বেইন্নে তারাতারি উঢিত পারি</t>
+  </si>
+  <si>
+    <t>আজকে সকালে আমি ভাত খাব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে ফজরত আঁই ভাত ন হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমার পেঠ ব্যাথা করছে সেজন্য খেতে পারবনা</t>
+  </si>
+  <si>
+    <t>আত্তুন পেঠ ব্যাথা গরের দে এতেল্লে হাইত ন পাইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমার মাথা ব্যাথা করছে বেশি, মনে হয় ঠাণ্ডা লেগে গেছে</t>
+  </si>
+  <si>
+    <t>আত্তুন মাথা ব্যাথা গরের বেশি, মনে অয় ঠাণ্ডা লাগি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এখন সকাল দশটা বাজে, এখনো কেন ঘুম থেকে উঠছিস না!</t>
+  </si>
+  <si>
+    <t>এহন বেইন্নে দশটা বাজের, এহনো কিল্লে ঘুমত্তোন ন উডর দে!</t>
+  </si>
+  <si>
+    <t>এই শোন, আজকে যদি বাজারে না যাস তাহলে তুর খবর আছে</t>
+  </si>
+  <si>
+    <t>এই উন, আজিয়ে যদি বাজারোত ন যস তইলি তুর হবর আছে</t>
+  </si>
+  <si>
+    <t>আজকে দুপুরে কি রান্না করবে?</t>
+  </si>
+  <si>
+    <t>আজিয়ে দুইজ্জে কি রাদিবে?</t>
+  </si>
+  <si>
+    <t>আজকে মুরগি দিয়ে আলু এবং টমেটো ভর্তা করব</t>
+  </si>
+  <si>
+    <t>আজিয়ে কুরো দি আলু আর হাট্টা বেইয়্যুন চান্নি গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আজকে মেহমান আসছে, বাজার থেকে গরুর মাংস আর চিংড়ি মাছ নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তন গরু গুস্ত আর ইছে মাছ আনো</t>
+  </si>
+  <si>
+    <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি একটা চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
+  </si>
+  <si>
+    <t>আজকে অফিসে কাজের চাপ কম, তাই জলদি চলে আসছি</t>
+  </si>
+  <si>
+    <t>অফিস থেকে আসার সময় বাজার থেকে টমেটো আর চিংড়ি মাছ নিয়ে আসিও</t>
+  </si>
+  <si>
+    <t>আজকে নিউ মার্কেট থেকে একটা পাঞ্জাবি কিনেছি</t>
+  </si>
+  <si>
+    <t>আজকে অফিসে অনেক কাজ, তাই আমার আসতে দেরি হবে</t>
+  </si>
+  <si>
+    <t>মার্কেটে অনেক ভিড়, তাই আসতে দেরি হবে</t>
+  </si>
+  <si>
+    <t>ডাক্তার বলেছে সময়মতো খাবার খেতে</t>
+  </si>
+  <si>
+    <t>আজকে আমার পা ব্যথা করছে, রান্না না হয় তুমি কর</t>
+  </si>
+  <si>
+    <t>আজিয়ে আঁর টেং ব্যথা গরের, রান্না নয়তো তুঁই গরো</t>
+  </si>
+  <si>
+    <t>চল, আজকে বাইরে থেকে খেয়ে আসি, ঘরের খাবার আর ভাল লাগছেনা</t>
+  </si>
+  <si>
+    <t>সময়মতো খাবার না খেলে শরীর দুর্বল হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এভাবে মরার মতো কে ঘুমায়! জলদি উঠ ঘুম থেকে</t>
+  </si>
+  <si>
+    <t>এল্লেত মরার মতোন হনে ঘুম যায়! হারা উঠ ঘুমুত্তোন</t>
+  </si>
+  <si>
+    <t xml:space="preserve">যেভাবেই হোক সন্ধার আগে সব কাজ শেষ করতে হবে </t>
+  </si>
+  <si>
+    <t>যেনগরি অক আজুইন্নের আগে বিয়াক হাম শেষ গরন পরিবো</t>
+  </si>
+  <si>
+    <t>সকালে আমি ভাত খাবো না</t>
+  </si>
+  <si>
+    <t>বেইন্নে আঁই ভাত হাইতাম নো</t>
+  </si>
+  <si>
+    <t>সকালে আমি রুটি খাব</t>
+  </si>
+  <si>
+    <t>বেইন্নে আঁই রুটি হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>চলেন, আজকে দুপুরে একসাথে খাবার খায়</t>
+  </si>
+  <si>
+    <t>চলন, আজিয়ে দুইজ্জে এক্কোত্তরে হানা হায়</t>
+  </si>
+  <si>
+    <t>আমার এখন খেতে ইচ্ছে করছে না, তুমি খেয়ে নাও, আমি পরে খাব</t>
+  </si>
+  <si>
+    <t>আত্তুন এহন হাইতু মনে ন হর, তুঁই হায় লও, আঁই পরে হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমার খুব ক্ষুদা লেগেছে, জলদি ভাত নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>আত্তুন বেশি ভুক লেইজ্ঞি, হারা ভাত আনো</t>
+  </si>
+  <si>
+    <t>এভাবে রাগ করে থাকলে হবে? খাবার ঠান্ডা হয়ে যাচ্ছে, খেয়ে নাও</t>
+  </si>
+  <si>
+    <t>এন গরি গুসসা অই থাহিলি অইবুনা? হানা ঠান্ডা অই যার, হায় লও</t>
+  </si>
+  <si>
+    <t>আমরা সন্ধ্যায় চা আর নাস্তা খাব</t>
+  </si>
+  <si>
+    <t>আঁরা আজুইন্নে চা আর নাস্তা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আজকে আমি নিজে তোমার জন্য রান্না করেছি, খেয়ে কেমন হয়েছে জানাবে</t>
+  </si>
+  <si>
+    <t>আজিয়ে আঁই নিজে তোঁইয়ার লাই রান্না গইজ্জি, হাইয়্যিরে কেন অইয়্যি হইয়্যু</t>
+  </si>
+  <si>
+    <t>তোমার রান্না অনেক মজা হয়েছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার রান্না বত মজা অইয়্যি</t>
+  </si>
+  <si>
+    <t>এখন ক্ষুদা নাই, পরে খাবো</t>
+  </si>
+  <si>
+    <t>এহন ভুক নাই, পরে হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>সন্ধ্যায় চা খাবে নাকি কফি খাবে?</t>
+  </si>
+  <si>
+    <t>আজুইন্নে চা হাইবে নাকি কফি হাইবে?</t>
+  </si>
+  <si>
+    <t>সকালে দেরিতে ঘুম থেকে উঠলে নাশতা ঠিকমতো খাওয়া হয় না</t>
+  </si>
+  <si>
+    <t>বেইন্নে দেরি গরি ঘুমোত্তন উডিলি নাস্তা গম গরি হন ন যায়</t>
   </si>
 </sst>
 </file>
@@ -1897,11 +2200,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2440,7 +2746,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="90.7777777777778" customWidth="1"/>
@@ -4054,6 +4360,1408 @@
         <v>396</v>
       </c>
     </row>
+    <row r="202" ht="25" customHeight="1" spans="1:2">
+      <c r="A202" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="203" ht="25" customHeight="1" spans="1:2">
+      <c r="A203" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="204" ht="25" customHeight="1" spans="1:2">
+      <c r="A204" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="205" ht="25" customHeight="1" spans="1:2">
+      <c r="A205" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="206" ht="25" customHeight="1" spans="1:2">
+      <c r="A206" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="207" ht="25" customHeight="1" spans="1:2">
+      <c r="A207" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="208" ht="25" customHeight="1" spans="1:2">
+      <c r="A208" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="209" ht="25" customHeight="1" spans="1:2">
+      <c r="A209" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="210" ht="25" customHeight="1" spans="1:2">
+      <c r="A210" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="211" ht="25" customHeight="1" spans="1:2">
+      <c r="A211" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="212" ht="25" customHeight="1" spans="1:2">
+      <c r="A212" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="213" ht="25" customHeight="1" spans="1:2">
+      <c r="A213" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="214" ht="25" customHeight="1" spans="1:2">
+      <c r="A214" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="215" ht="25" customHeight="1" spans="1:2">
+      <c r="A215" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="216" ht="25" customHeight="1" spans="1:2">
+      <c r="A216" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="217" ht="25" customHeight="1" spans="1:2">
+      <c r="A217" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="218" ht="25" customHeight="1" spans="1:2">
+      <c r="A218" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="219" ht="25" customHeight="1" spans="1:2">
+      <c r="A219" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="220" ht="25" customHeight="1" spans="1:2">
+      <c r="A220" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="221" ht="25" customHeight="1" spans="1:2">
+      <c r="A221" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="222" ht="25" customHeight="1" spans="1:2">
+      <c r="A222" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="223" ht="25" customHeight="1" spans="1:2">
+      <c r="A223" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="224" ht="25" customHeight="1" spans="1:2">
+      <c r="A224" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="225" ht="25" customHeight="1" spans="1:2">
+      <c r="A225" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="226" ht="25" customHeight="1" spans="1:2">
+      <c r="A226" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="227" ht="25" customHeight="1" spans="1:2">
+      <c r="A227" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="228" ht="25" customHeight="1" spans="1:2">
+      <c r="A228" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="229" ht="25" customHeight="1" spans="1:2">
+      <c r="A229" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="230" ht="25" customHeight="1" spans="1:2">
+      <c r="A230" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="231" ht="25" customHeight="1" spans="1:2">
+      <c r="A231" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="232" ht="25" customHeight="1" spans="1:2">
+      <c r="A232" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="233" ht="25" customHeight="1" spans="1:2">
+      <c r="A233" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B233" s="3"/>
+    </row>
+    <row r="234" ht="25" customHeight="1" spans="1:2">
+      <c r="A234" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B234" s="3"/>
+    </row>
+    <row r="235" ht="25" customHeight="1" spans="1:2">
+      <c r="A235" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B235" s="3"/>
+    </row>
+    <row r="236" ht="25" customHeight="1" spans="1:2">
+      <c r="A236" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B236" s="3"/>
+    </row>
+    <row r="237" ht="25" customHeight="1" spans="1:2">
+      <c r="A237" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B237" s="3"/>
+    </row>
+    <row r="238" ht="25" customHeight="1" spans="1:2">
+      <c r="A238" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B238" s="3"/>
+    </row>
+    <row r="239" ht="25" customHeight="1" spans="1:2">
+      <c r="A239" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B239" s="3"/>
+    </row>
+    <row r="240" ht="25" customHeight="1" spans="1:2">
+      <c r="A240" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="241" ht="25" customHeight="1" spans="1:2">
+      <c r="A241" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B241" s="3"/>
+    </row>
+    <row r="242" ht="25" customHeight="1" spans="1:2">
+      <c r="A242" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B242" s="3"/>
+    </row>
+    <row r="243" ht="25" customHeight="1" spans="1:2">
+      <c r="A243" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="244" ht="25" customHeight="1" spans="1:2">
+      <c r="A244" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="245" ht="25" customHeight="1" spans="1:2">
+      <c r="A245" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="246" ht="25" customHeight="1" spans="1:2">
+      <c r="A246" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="247" ht="25" customHeight="1" spans="1:2">
+      <c r="A247" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="248" ht="25" customHeight="1" spans="1:2">
+      <c r="A248" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="249" ht="25" customHeight="1" spans="1:2">
+      <c r="A249" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="250" ht="25" customHeight="1" spans="1:2">
+      <c r="A250" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="251" ht="25" customHeight="1" spans="1:2">
+      <c r="A251" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="252" ht="25" customHeight="1" spans="1:2">
+      <c r="A252" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="253" ht="25" customHeight="1" spans="1:2">
+      <c r="A253" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="254" ht="25" customHeight="1" spans="1:2">
+      <c r="A254" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="255" ht="25" customHeight="1" spans="1:2">
+      <c r="A255" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="256" ht="25" customHeight="1" spans="1:2">
+      <c r="A256" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="257" ht="25" customHeight="1" spans="1:2">
+      <c r="A257" s="3"/>
+      <c r="B257" s="3"/>
+    </row>
+    <row r="258" ht="25" customHeight="1" spans="1:2">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3"/>
+    </row>
+    <row r="259" ht="25" customHeight="1" spans="1:2">
+      <c r="A259" s="3"/>
+      <c r="B259" s="3"/>
+    </row>
+    <row r="260" ht="25" customHeight="1" spans="1:2">
+      <c r="A260" s="3"/>
+      <c r="B260" s="3"/>
+    </row>
+    <row r="261" ht="25" customHeight="1" spans="1:2">
+      <c r="A261" s="3"/>
+      <c r="B261" s="3"/>
+    </row>
+    <row r="262" ht="25" customHeight="1" spans="1:2">
+      <c r="A262" s="3"/>
+      <c r="B262" s="3"/>
+    </row>
+    <row r="263" ht="25" customHeight="1" spans="1:2">
+      <c r="A263" s="3"/>
+      <c r="B263" s="3"/>
+    </row>
+    <row r="264" ht="25" customHeight="1" spans="1:2">
+      <c r="A264" s="3"/>
+      <c r="B264" s="3"/>
+    </row>
+    <row r="265" ht="25" customHeight="1" spans="1:2">
+      <c r="A265" s="3"/>
+      <c r="B265" s="3"/>
+    </row>
+    <row r="266" ht="25" customHeight="1" spans="1:2">
+      <c r="A266" s="3"/>
+      <c r="B266" s="3"/>
+    </row>
+    <row r="267" ht="25" customHeight="1" spans="1:2">
+      <c r="A267" s="3"/>
+      <c r="B267" s="3"/>
+    </row>
+    <row r="268" ht="25" customHeight="1" spans="1:2">
+      <c r="A268" s="3"/>
+      <c r="B268" s="3"/>
+    </row>
+    <row r="269" ht="25" customHeight="1" spans="1:2">
+      <c r="A269" s="3"/>
+      <c r="B269" s="3"/>
+    </row>
+    <row r="270" ht="25" customHeight="1" spans="1:2">
+      <c r="A270" s="3"/>
+      <c r="B270" s="3"/>
+    </row>
+    <row r="271" ht="25" customHeight="1" spans="1:2">
+      <c r="A271" s="3"/>
+      <c r="B271" s="3"/>
+    </row>
+    <row r="272" ht="25" customHeight="1" spans="1:2">
+      <c r="A272" s="3"/>
+      <c r="B272" s="3"/>
+    </row>
+    <row r="273" ht="25" customHeight="1" spans="1:2">
+      <c r="A273" s="3"/>
+      <c r="B273" s="3"/>
+    </row>
+    <row r="274" ht="25" customHeight="1" spans="1:2">
+      <c r="A274" s="3"/>
+      <c r="B274" s="3"/>
+    </row>
+    <row r="275" ht="25" customHeight="1" spans="1:2">
+      <c r="A275" s="3"/>
+      <c r="B275" s="3"/>
+    </row>
+    <row r="276" ht="25" customHeight="1" spans="1:2">
+      <c r="A276" s="3"/>
+      <c r="B276" s="3"/>
+    </row>
+    <row r="277" ht="25" customHeight="1" spans="1:2">
+      <c r="A277" s="3"/>
+      <c r="B277" s="3"/>
+    </row>
+    <row r="278" ht="25" customHeight="1" spans="1:2">
+      <c r="A278" s="3"/>
+      <c r="B278" s="3"/>
+    </row>
+    <row r="279" ht="25" customHeight="1" spans="1:2">
+      <c r="A279" s="3"/>
+      <c r="B279" s="3"/>
+    </row>
+    <row r="280" ht="25" customHeight="1" spans="1:2">
+      <c r="A280" s="3"/>
+      <c r="B280" s="3"/>
+    </row>
+    <row r="281" ht="25" customHeight="1" spans="1:2">
+      <c r="A281" s="3"/>
+      <c r="B281" s="3"/>
+    </row>
+    <row r="282" ht="25" customHeight="1" spans="1:2">
+      <c r="A282" s="3"/>
+      <c r="B282" s="3"/>
+    </row>
+    <row r="283" ht="25" customHeight="1" spans="1:2">
+      <c r="A283" s="3"/>
+      <c r="B283" s="3"/>
+    </row>
+    <row r="284" ht="25" customHeight="1" spans="1:2">
+      <c r="A284" s="3"/>
+      <c r="B284" s="3"/>
+    </row>
+    <row r="285" ht="25" customHeight="1" spans="1:2">
+      <c r="A285" s="3"/>
+      <c r="B285" s="3"/>
+    </row>
+    <row r="286" ht="25" customHeight="1" spans="1:2">
+      <c r="A286" s="3"/>
+      <c r="B286" s="3"/>
+    </row>
+    <row r="287" ht="25" customHeight="1" spans="1:2">
+      <c r="A287" s="3"/>
+      <c r="B287" s="3"/>
+    </row>
+    <row r="288" ht="25" customHeight="1" spans="1:2">
+      <c r="A288" s="3"/>
+      <c r="B288" s="3"/>
+    </row>
+    <row r="289" ht="25" customHeight="1" spans="1:2">
+      <c r="A289" s="3"/>
+      <c r="B289" s="3"/>
+    </row>
+    <row r="290" ht="25" customHeight="1" spans="1:2">
+      <c r="A290" s="3"/>
+      <c r="B290" s="3"/>
+    </row>
+    <row r="291" ht="25" customHeight="1" spans="1:2">
+      <c r="A291" s="3"/>
+      <c r="B291" s="3"/>
+    </row>
+    <row r="292" ht="25" customHeight="1" spans="1:2">
+      <c r="A292" s="3"/>
+      <c r="B292" s="3"/>
+    </row>
+    <row r="293" ht="25" customHeight="1" spans="1:2">
+      <c r="A293" s="3"/>
+      <c r="B293" s="3"/>
+    </row>
+    <row r="294" ht="25" customHeight="1" spans="1:2">
+      <c r="A294" s="3"/>
+      <c r="B294" s="3"/>
+    </row>
+    <row r="295" ht="25" customHeight="1" spans="1:2">
+      <c r="A295" s="3"/>
+      <c r="B295" s="3"/>
+    </row>
+    <row r="296" ht="25" customHeight="1" spans="1:2">
+      <c r="A296" s="3"/>
+      <c r="B296" s="3"/>
+    </row>
+    <row r="297" ht="25" customHeight="1" spans="1:2">
+      <c r="A297" s="3"/>
+      <c r="B297" s="3"/>
+    </row>
+    <row r="298" ht="25" customHeight="1" spans="1:2">
+      <c r="A298" s="3"/>
+      <c r="B298" s="3"/>
+    </row>
+    <row r="299" ht="25" customHeight="1" spans="1:2">
+      <c r="A299" s="3"/>
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" ht="25" customHeight="1" spans="1:2">
+      <c r="A300" s="3"/>
+      <c r="B300" s="3"/>
+    </row>
+    <row r="301" ht="25" customHeight="1" spans="1:2">
+      <c r="A301" s="3"/>
+      <c r="B301" s="3"/>
+    </row>
+    <row r="302" ht="25" customHeight="1" spans="1:2">
+      <c r="A302" s="3"/>
+      <c r="B302" s="3"/>
+    </row>
+    <row r="303" ht="25" customHeight="1" spans="1:2">
+      <c r="A303" s="3"/>
+      <c r="B303" s="3"/>
+    </row>
+    <row r="304" ht="25" customHeight="1" spans="1:2">
+      <c r="A304" s="3"/>
+      <c r="B304" s="3"/>
+    </row>
+    <row r="305" ht="25" customHeight="1" spans="1:2">
+      <c r="A305" s="3"/>
+      <c r="B305" s="3"/>
+    </row>
+    <row r="306" ht="25" customHeight="1" spans="1:2">
+      <c r="A306" s="3"/>
+      <c r="B306" s="3"/>
+    </row>
+    <row r="307" ht="25" customHeight="1" spans="1:2">
+      <c r="A307" s="3"/>
+      <c r="B307" s="3"/>
+    </row>
+    <row r="308" ht="25" customHeight="1" spans="1:2">
+      <c r="A308" s="3"/>
+      <c r="B308" s="3"/>
+    </row>
+    <row r="309" ht="25" customHeight="1" spans="1:2">
+      <c r="A309" s="3"/>
+      <c r="B309" s="3"/>
+    </row>
+    <row r="310" ht="25" customHeight="1" spans="1:2">
+      <c r="A310" s="3"/>
+      <c r="B310" s="3"/>
+    </row>
+    <row r="311" ht="25" customHeight="1" spans="1:2">
+      <c r="A311" s="3"/>
+      <c r="B311" s="3"/>
+    </row>
+    <row r="312" ht="25" customHeight="1" spans="1:2">
+      <c r="A312" s="3"/>
+      <c r="B312" s="3"/>
+    </row>
+    <row r="313" ht="25" customHeight="1" spans="1:2">
+      <c r="A313" s="3"/>
+      <c r="B313" s="3"/>
+    </row>
+    <row r="314" ht="25" customHeight="1" spans="1:2">
+      <c r="A314" s="3"/>
+      <c r="B314" s="3"/>
+    </row>
+    <row r="315" ht="25" customHeight="1" spans="1:2">
+      <c r="A315" s="3"/>
+      <c r="B315" s="3"/>
+    </row>
+    <row r="316" ht="25" customHeight="1" spans="1:2">
+      <c r="A316" s="3"/>
+      <c r="B316" s="3"/>
+    </row>
+    <row r="317" ht="25" customHeight="1" spans="1:2">
+      <c r="A317" s="3"/>
+      <c r="B317" s="3"/>
+    </row>
+    <row r="318" ht="25" customHeight="1" spans="1:2">
+      <c r="A318" s="3"/>
+      <c r="B318" s="3"/>
+    </row>
+    <row r="319" ht="25" customHeight="1" spans="1:2">
+      <c r="A319" s="3"/>
+      <c r="B319" s="3"/>
+    </row>
+    <row r="320" ht="25" customHeight="1" spans="1:2">
+      <c r="A320" s="3"/>
+      <c r="B320" s="3"/>
+    </row>
+    <row r="321" ht="25" customHeight="1" spans="1:2">
+      <c r="A321" s="3"/>
+      <c r="B321" s="3"/>
+    </row>
+    <row r="322" ht="25" customHeight="1" spans="1:2">
+      <c r="A322" s="3"/>
+      <c r="B322" s="3"/>
+    </row>
+    <row r="323" ht="25" customHeight="1" spans="1:2">
+      <c r="A323" s="3"/>
+      <c r="B323" s="3"/>
+    </row>
+    <row r="324" ht="25" customHeight="1" spans="1:2">
+      <c r="A324" s="3"/>
+      <c r="B324" s="3"/>
+    </row>
+    <row r="325" ht="25" customHeight="1" spans="1:2">
+      <c r="A325" s="3"/>
+      <c r="B325" s="3"/>
+    </row>
+    <row r="326" ht="25" customHeight="1" spans="1:2">
+      <c r="A326" s="3"/>
+      <c r="B326" s="3"/>
+    </row>
+    <row r="327" ht="25" customHeight="1" spans="1:2">
+      <c r="A327" s="3"/>
+      <c r="B327" s="3"/>
+    </row>
+    <row r="328" ht="25" customHeight="1" spans="1:2">
+      <c r="A328" s="3"/>
+      <c r="B328" s="3"/>
+    </row>
+    <row r="329" ht="25" customHeight="1" spans="1:2">
+      <c r="A329" s="3"/>
+      <c r="B329" s="3"/>
+    </row>
+    <row r="330" ht="25" customHeight="1" spans="1:2">
+      <c r="A330" s="3"/>
+      <c r="B330" s="3"/>
+    </row>
+    <row r="331" ht="25" customHeight="1" spans="1:2">
+      <c r="A331" s="3"/>
+      <c r="B331" s="3"/>
+    </row>
+    <row r="332" ht="25" customHeight="1" spans="1:2">
+      <c r="A332" s="3"/>
+      <c r="B332" s="3"/>
+    </row>
+    <row r="333" ht="25" customHeight="1" spans="1:2">
+      <c r="A333" s="3"/>
+      <c r="B333" s="3"/>
+    </row>
+    <row r="334" ht="25" customHeight="1" spans="1:2">
+      <c r="A334" s="3"/>
+      <c r="B334" s="3"/>
+    </row>
+    <row r="335" ht="25" customHeight="1" spans="1:2">
+      <c r="A335" s="3"/>
+      <c r="B335" s="3"/>
+    </row>
+    <row r="336" ht="25" customHeight="1" spans="1:2">
+      <c r="A336" s="3"/>
+      <c r="B336" s="3"/>
+    </row>
+    <row r="337" ht="25" customHeight="1" spans="1:2">
+      <c r="A337" s="3"/>
+      <c r="B337" s="3"/>
+    </row>
+    <row r="338" ht="25" customHeight="1" spans="1:2">
+      <c r="A338" s="3"/>
+      <c r="B338" s="3"/>
+    </row>
+    <row r="339" ht="25" customHeight="1" spans="1:2">
+      <c r="A339" s="3"/>
+      <c r="B339" s="3"/>
+    </row>
+    <row r="340" ht="25" customHeight="1" spans="1:2">
+      <c r="A340" s="3"/>
+      <c r="B340" s="3"/>
+    </row>
+    <row r="341" ht="25" customHeight="1" spans="1:2">
+      <c r="A341" s="3"/>
+      <c r="B341" s="3"/>
+    </row>
+    <row r="342" ht="25" customHeight="1" spans="1:2">
+      <c r="A342" s="3"/>
+      <c r="B342" s="3"/>
+    </row>
+    <row r="343" ht="25" customHeight="1" spans="1:2">
+      <c r="A343" s="3"/>
+      <c r="B343" s="3"/>
+    </row>
+    <row r="344" ht="25" customHeight="1" spans="1:2">
+      <c r="A344" s="3"/>
+      <c r="B344" s="3"/>
+    </row>
+    <row r="345" ht="25" customHeight="1" spans="1:2">
+      <c r="A345" s="3"/>
+      <c r="B345" s="3"/>
+    </row>
+    <row r="346" ht="25" customHeight="1" spans="1:2">
+      <c r="A346" s="3"/>
+      <c r="B346" s="3"/>
+    </row>
+    <row r="347" ht="25" customHeight="1" spans="1:2">
+      <c r="A347" s="3"/>
+      <c r="B347" s="3"/>
+    </row>
+    <row r="348" ht="25" customHeight="1" spans="1:2">
+      <c r="A348" s="3"/>
+      <c r="B348" s="3"/>
+    </row>
+    <row r="349" ht="25" customHeight="1" spans="1:2">
+      <c r="A349" s="3"/>
+      <c r="B349" s="3"/>
+    </row>
+    <row r="350" ht="25" customHeight="1" spans="1:2">
+      <c r="A350" s="3"/>
+      <c r="B350" s="3"/>
+    </row>
+    <row r="351" ht="25" customHeight="1" spans="1:2">
+      <c r="A351" s="3"/>
+      <c r="B351" s="3"/>
+    </row>
+    <row r="352" ht="25" customHeight="1" spans="1:2">
+      <c r="A352" s="3"/>
+      <c r="B352" s="3"/>
+    </row>
+    <row r="353" ht="25" customHeight="1" spans="1:2">
+      <c r="A353" s="3"/>
+      <c r="B353" s="3"/>
+    </row>
+    <row r="354" ht="25" customHeight="1" spans="1:2">
+      <c r="A354" s="3"/>
+      <c r="B354" s="3"/>
+    </row>
+    <row r="355" ht="25" customHeight="1" spans="1:2">
+      <c r="A355" s="3"/>
+      <c r="B355" s="3"/>
+    </row>
+    <row r="356" ht="25" customHeight="1" spans="1:2">
+      <c r="A356" s="3"/>
+      <c r="B356" s="3"/>
+    </row>
+    <row r="357" ht="25" customHeight="1" spans="1:2">
+      <c r="A357" s="3"/>
+      <c r="B357" s="3"/>
+    </row>
+    <row r="358" ht="25" customHeight="1" spans="1:2">
+      <c r="A358" s="3"/>
+      <c r="B358" s="3"/>
+    </row>
+    <row r="359" ht="25" customHeight="1" spans="1:2">
+      <c r="A359" s="3"/>
+      <c r="B359" s="3"/>
+    </row>
+    <row r="360" ht="25" customHeight="1" spans="1:2">
+      <c r="A360" s="3"/>
+      <c r="B360" s="3"/>
+    </row>
+    <row r="361" ht="25" customHeight="1" spans="1:2">
+      <c r="A361" s="3"/>
+      <c r="B361" s="3"/>
+    </row>
+    <row r="362" ht="25" customHeight="1" spans="1:2">
+      <c r="A362" s="3"/>
+      <c r="B362" s="3"/>
+    </row>
+    <row r="363" ht="25" customHeight="1" spans="1:2">
+      <c r="A363" s="3"/>
+      <c r="B363" s="3"/>
+    </row>
+    <row r="364" ht="25" customHeight="1" spans="1:2">
+      <c r="A364" s="3"/>
+      <c r="B364" s="3"/>
+    </row>
+    <row r="365" ht="25" customHeight="1" spans="1:2">
+      <c r="A365" s="3"/>
+      <c r="B365" s="3"/>
+    </row>
+    <row r="366" ht="25" customHeight="1" spans="1:2">
+      <c r="A366" s="3"/>
+      <c r="B366" s="3"/>
+    </row>
+    <row r="367" ht="25" customHeight="1" spans="1:2">
+      <c r="A367" s="3"/>
+      <c r="B367" s="3"/>
+    </row>
+    <row r="368" ht="25" customHeight="1" spans="1:2">
+      <c r="A368" s="3"/>
+      <c r="B368" s="3"/>
+    </row>
+    <row r="369" ht="25" customHeight="1" spans="1:2">
+      <c r="A369" s="3"/>
+      <c r="B369" s="3"/>
+    </row>
+    <row r="370" ht="25" customHeight="1" spans="1:2">
+      <c r="A370" s="3"/>
+      <c r="B370" s="3"/>
+    </row>
+    <row r="371" ht="25" customHeight="1" spans="1:2">
+      <c r="A371" s="3"/>
+      <c r="B371" s="3"/>
+    </row>
+    <row r="372" ht="25" customHeight="1" spans="1:2">
+      <c r="A372" s="3"/>
+      <c r="B372" s="3"/>
+    </row>
+    <row r="373" ht="25" customHeight="1" spans="1:2">
+      <c r="A373" s="3"/>
+      <c r="B373" s="3"/>
+    </row>
+    <row r="374" ht="25" customHeight="1" spans="1:2">
+      <c r="A374" s="3"/>
+      <c r="B374" s="3"/>
+    </row>
+    <row r="375" ht="25" customHeight="1" spans="1:2">
+      <c r="A375" s="3"/>
+      <c r="B375" s="3"/>
+    </row>
+    <row r="376" ht="25" customHeight="1" spans="1:2">
+      <c r="A376" s="3"/>
+      <c r="B376" s="3"/>
+    </row>
+    <row r="377" ht="25" customHeight="1" spans="1:2">
+      <c r="A377" s="3"/>
+      <c r="B377" s="3"/>
+    </row>
+    <row r="378" ht="25" customHeight="1" spans="1:2">
+      <c r="A378" s="3"/>
+      <c r="B378" s="3"/>
+    </row>
+    <row r="379" ht="25" customHeight="1" spans="1:2">
+      <c r="A379" s="3"/>
+      <c r="B379" s="3"/>
+    </row>
+    <row r="380" ht="25" customHeight="1" spans="1:2">
+      <c r="A380" s="3"/>
+      <c r="B380" s="3"/>
+    </row>
+    <row r="381" ht="25" customHeight="1" spans="1:2">
+      <c r="A381" s="3"/>
+      <c r="B381" s="3"/>
+    </row>
+    <row r="382" ht="25" customHeight="1" spans="1:2">
+      <c r="A382" s="3"/>
+      <c r="B382" s="3"/>
+    </row>
+    <row r="383" ht="25" customHeight="1" spans="1:2">
+      <c r="A383" s="3"/>
+      <c r="B383" s="3"/>
+    </row>
+    <row r="384" ht="25" customHeight="1" spans="1:2">
+      <c r="A384" s="3"/>
+      <c r="B384" s="3"/>
+    </row>
+    <row r="385" ht="25" customHeight="1" spans="1:2">
+      <c r="A385" s="3"/>
+      <c r="B385" s="3"/>
+    </row>
+    <row r="386" ht="25" customHeight="1" spans="1:2">
+      <c r="A386" s="3"/>
+      <c r="B386" s="3"/>
+    </row>
+    <row r="387" ht="25" customHeight="1" spans="1:2">
+      <c r="A387" s="3"/>
+      <c r="B387" s="3"/>
+    </row>
+    <row r="388" ht="25" customHeight="1" spans="1:2">
+      <c r="A388" s="3"/>
+      <c r="B388" s="3"/>
+    </row>
+    <row r="389" ht="25" customHeight="1" spans="1:2">
+      <c r="A389" s="3"/>
+      <c r="B389" s="3"/>
+    </row>
+    <row r="390" ht="25" customHeight="1" spans="1:2">
+      <c r="A390" s="3"/>
+      <c r="B390" s="3"/>
+    </row>
+    <row r="391" ht="25" customHeight="1" spans="1:2">
+      <c r="A391" s="3"/>
+      <c r="B391" s="3"/>
+    </row>
+    <row r="392" ht="25" customHeight="1" spans="1:2">
+      <c r="A392" s="3"/>
+      <c r="B392" s="3"/>
+    </row>
+    <row r="393" ht="25" customHeight="1" spans="1:2">
+      <c r="A393" s="3"/>
+      <c r="B393" s="3"/>
+    </row>
+    <row r="394" ht="25" customHeight="1" spans="1:2">
+      <c r="A394" s="3"/>
+      <c r="B394" s="3"/>
+    </row>
+    <row r="395" ht="25" customHeight="1" spans="1:2">
+      <c r="A395" s="3"/>
+      <c r="B395" s="3"/>
+    </row>
+    <row r="396" ht="25" customHeight="1" spans="1:2">
+      <c r="A396" s="3"/>
+      <c r="B396" s="3"/>
+    </row>
+    <row r="397" ht="25" customHeight="1" spans="1:2">
+      <c r="A397" s="3"/>
+      <c r="B397" s="3"/>
+    </row>
+    <row r="398" ht="25" customHeight="1" spans="1:2">
+      <c r="A398" s="3"/>
+      <c r="B398" s="3"/>
+    </row>
+    <row r="399" ht="25" customHeight="1" spans="1:2">
+      <c r="A399" s="3"/>
+      <c r="B399" s="3"/>
+    </row>
+    <row r="400" ht="25" customHeight="1" spans="1:2">
+      <c r="A400" s="3"/>
+      <c r="B400" s="3"/>
+    </row>
+    <row r="401" ht="25" customHeight="1" spans="1:2">
+      <c r="A401" s="3"/>
+      <c r="B401" s="3"/>
+    </row>
+    <row r="402" ht="25" customHeight="1" spans="1:2">
+      <c r="A402" s="3"/>
+      <c r="B402" s="3"/>
+    </row>
+    <row r="403" ht="25" customHeight="1" spans="1:2">
+      <c r="A403" s="3"/>
+      <c r="B403" s="3"/>
+    </row>
+    <row r="404" ht="25" customHeight="1" spans="1:2">
+      <c r="A404" s="3"/>
+      <c r="B404" s="3"/>
+    </row>
+    <row r="405" ht="25" customHeight="1" spans="1:2">
+      <c r="A405" s="3"/>
+      <c r="B405" s="3"/>
+    </row>
+    <row r="406" ht="25" customHeight="1" spans="1:2">
+      <c r="A406" s="3"/>
+      <c r="B406" s="3"/>
+    </row>
+    <row r="407" ht="25" customHeight="1" spans="1:2">
+      <c r="A407" s="3"/>
+      <c r="B407" s="3"/>
+    </row>
+    <row r="408" ht="25" customHeight="1" spans="1:2">
+      <c r="A408" s="3"/>
+      <c r="B408" s="3"/>
+    </row>
+    <row r="409" ht="25" customHeight="1" spans="1:2">
+      <c r="A409" s="3"/>
+      <c r="B409" s="3"/>
+    </row>
+    <row r="410" ht="25" customHeight="1" spans="1:2">
+      <c r="A410" s="3"/>
+      <c r="B410" s="3"/>
+    </row>
+    <row r="411" ht="25" customHeight="1" spans="1:2">
+      <c r="A411" s="3"/>
+      <c r="B411" s="3"/>
+    </row>
+    <row r="412" ht="25" customHeight="1" spans="1:2">
+      <c r="A412" s="3"/>
+      <c r="B412" s="3"/>
+    </row>
+    <row r="413" ht="25" customHeight="1" spans="1:2">
+      <c r="A413" s="3"/>
+      <c r="B413" s="3"/>
+    </row>
+    <row r="414" ht="25" customHeight="1" spans="1:2">
+      <c r="A414" s="3"/>
+      <c r="B414" s="3"/>
+    </row>
+    <row r="415" ht="25" customHeight="1" spans="1:2">
+      <c r="A415" s="3"/>
+      <c r="B415" s="3"/>
+    </row>
+    <row r="416" ht="25" customHeight="1" spans="1:2">
+      <c r="A416" s="3"/>
+      <c r="B416" s="3"/>
+    </row>
+    <row r="417" ht="25" customHeight="1" spans="1:2">
+      <c r="A417" s="3"/>
+      <c r="B417" s="3"/>
+    </row>
+    <row r="418" ht="25" customHeight="1" spans="1:2">
+      <c r="A418" s="3"/>
+      <c r="B418" s="3"/>
+    </row>
+    <row r="419" ht="25" customHeight="1" spans="1:2">
+      <c r="A419" s="3"/>
+      <c r="B419" s="3"/>
+    </row>
+    <row r="420" ht="25" customHeight="1" spans="1:2">
+      <c r="A420" s="3"/>
+      <c r="B420" s="3"/>
+    </row>
+    <row r="421" ht="25" customHeight="1" spans="1:2">
+      <c r="A421" s="3"/>
+      <c r="B421" s="3"/>
+    </row>
+    <row r="422" ht="25" customHeight="1" spans="1:2">
+      <c r="A422" s="3"/>
+      <c r="B422" s="3"/>
+    </row>
+    <row r="423" ht="25" customHeight="1" spans="1:2">
+      <c r="A423" s="3"/>
+      <c r="B423" s="3"/>
+    </row>
+    <row r="424" ht="25" customHeight="1" spans="1:2">
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
+    </row>
+    <row r="425" ht="25" customHeight="1" spans="1:2">
+      <c r="A425" s="3"/>
+      <c r="B425" s="3"/>
+    </row>
+    <row r="426" ht="25" customHeight="1" spans="1:2">
+      <c r="A426" s="3"/>
+      <c r="B426" s="3"/>
+    </row>
+    <row r="427" ht="25" customHeight="1" spans="1:2">
+      <c r="A427" s="3"/>
+      <c r="B427" s="3"/>
+    </row>
+    <row r="428" ht="25" customHeight="1" spans="1:2">
+      <c r="A428" s="3"/>
+      <c r="B428" s="3"/>
+    </row>
+    <row r="429" ht="25" customHeight="1" spans="1:2">
+      <c r="A429" s="3"/>
+      <c r="B429" s="3"/>
+    </row>
+    <row r="430" ht="25" customHeight="1" spans="1:2">
+      <c r="A430" s="3"/>
+      <c r="B430" s="3"/>
+    </row>
+    <row r="431" ht="25" customHeight="1" spans="1:2">
+      <c r="A431" s="3"/>
+      <c r="B431" s="3"/>
+    </row>
+    <row r="432" ht="25" customHeight="1" spans="1:2">
+      <c r="A432" s="3"/>
+      <c r="B432" s="3"/>
+    </row>
+    <row r="433" ht="25" customHeight="1" spans="1:2">
+      <c r="A433" s="3"/>
+      <c r="B433" s="3"/>
+    </row>
+    <row r="434" ht="25" customHeight="1" spans="1:2">
+      <c r="A434" s="3"/>
+      <c r="B434" s="3"/>
+    </row>
+    <row r="435" ht="25" customHeight="1" spans="1:2">
+      <c r="A435" s="3"/>
+      <c r="B435" s="3"/>
+    </row>
+    <row r="436" ht="25" customHeight="1" spans="1:2">
+      <c r="A436" s="3"/>
+      <c r="B436" s="3"/>
+    </row>
+    <row r="437" ht="25" customHeight="1" spans="1:2">
+      <c r="A437" s="3"/>
+      <c r="B437" s="3"/>
+    </row>
+    <row r="438" ht="25" customHeight="1" spans="1:2">
+      <c r="A438" s="3"/>
+      <c r="B438" s="3"/>
+    </row>
+    <row r="439" ht="25" customHeight="1" spans="1:2">
+      <c r="A439" s="3"/>
+      <c r="B439" s="3"/>
+    </row>
+    <row r="440" ht="25" customHeight="1" spans="1:2">
+      <c r="A440" s="3"/>
+      <c r="B440" s="3"/>
+    </row>
+    <row r="441" ht="25" customHeight="1" spans="1:2">
+      <c r="A441" s="3"/>
+      <c r="B441" s="3"/>
+    </row>
+    <row r="442" ht="25" customHeight="1" spans="1:2">
+      <c r="A442" s="3"/>
+      <c r="B442" s="3"/>
+    </row>
+    <row r="443" ht="25" customHeight="1" spans="1:2">
+      <c r="A443" s="3"/>
+      <c r="B443" s="3"/>
+    </row>
+    <row r="444" ht="25" customHeight="1" spans="1:2">
+      <c r="A444" s="3"/>
+      <c r="B444" s="3"/>
+    </row>
+    <row r="445" ht="25" customHeight="1" spans="1:2">
+      <c r="A445" s="3"/>
+      <c r="B445" s="3"/>
+    </row>
+    <row r="446" ht="25" customHeight="1" spans="1:2">
+      <c r="A446" s="3"/>
+      <c r="B446" s="3"/>
+    </row>
+    <row r="447" ht="25" customHeight="1" spans="1:2">
+      <c r="A447" s="3"/>
+      <c r="B447" s="3"/>
+    </row>
+    <row r="448" ht="25" customHeight="1" spans="1:2">
+      <c r="A448" s="3"/>
+      <c r="B448" s="3"/>
+    </row>
+    <row r="449" ht="25" customHeight="1" spans="1:2">
+      <c r="A449" s="3"/>
+      <c r="B449" s="3"/>
+    </row>
+    <row r="450" ht="25" customHeight="1" spans="1:2">
+      <c r="A450" s="3"/>
+      <c r="B450" s="3"/>
+    </row>
+    <row r="451" ht="25" customHeight="1" spans="1:2">
+      <c r="A451" s="3"/>
+      <c r="B451" s="3"/>
+    </row>
+    <row r="452" ht="25" customHeight="1" spans="1:2">
+      <c r="A452" s="3"/>
+      <c r="B452" s="3"/>
+    </row>
+    <row r="453" ht="25" customHeight="1" spans="1:2">
+      <c r="A453" s="3"/>
+      <c r="B453" s="3"/>
+    </row>
+    <row r="454" ht="25" customHeight="1" spans="1:2">
+      <c r="A454" s="3"/>
+      <c r="B454" s="3"/>
+    </row>
+    <row r="455" ht="25" customHeight="1" spans="1:2">
+      <c r="A455" s="3"/>
+      <c r="B455" s="3"/>
+    </row>
+    <row r="456" ht="25" customHeight="1" spans="1:2">
+      <c r="A456" s="3"/>
+      <c r="B456" s="3"/>
+    </row>
+    <row r="457" ht="25" customHeight="1" spans="1:2">
+      <c r="A457" s="3"/>
+      <c r="B457" s="3"/>
+    </row>
+    <row r="458" ht="25" customHeight="1" spans="1:2">
+      <c r="A458" s="3"/>
+      <c r="B458" s="3"/>
+    </row>
+    <row r="459" ht="25" customHeight="1" spans="1:2">
+      <c r="A459" s="3"/>
+      <c r="B459" s="3"/>
+    </row>
+    <row r="460" ht="25" customHeight="1" spans="1:2">
+      <c r="A460" s="3"/>
+      <c r="B460" s="3"/>
+    </row>
+    <row r="461" ht="25" customHeight="1" spans="1:2">
+      <c r="A461" s="3"/>
+      <c r="B461" s="3"/>
+    </row>
+    <row r="462" ht="25" customHeight="1" spans="1:2">
+      <c r="A462" s="3"/>
+      <c r="B462" s="3"/>
+    </row>
+    <row r="463" ht="25" customHeight="1" spans="1:2">
+      <c r="A463" s="3"/>
+      <c r="B463" s="3"/>
+    </row>
+    <row r="464" ht="25" customHeight="1" spans="1:2">
+      <c r="A464" s="3"/>
+      <c r="B464" s="3"/>
+    </row>
+    <row r="465" ht="25" customHeight="1" spans="1:2">
+      <c r="A465" s="3"/>
+      <c r="B465" s="3"/>
+    </row>
+    <row r="466" ht="25" customHeight="1" spans="1:2">
+      <c r="A466" s="3"/>
+      <c r="B466" s="3"/>
+    </row>
+    <row r="467" ht="25" customHeight="1" spans="1:2">
+      <c r="A467" s="3"/>
+      <c r="B467" s="3"/>
+    </row>
+    <row r="468" ht="25" customHeight="1" spans="1:2">
+      <c r="A468" s="3"/>
+      <c r="B468" s="3"/>
+    </row>
+    <row r="469" ht="25" customHeight="1" spans="1:2">
+      <c r="A469" s="3"/>
+      <c r="B469" s="3"/>
+    </row>
+    <row r="470" ht="25" customHeight="1" spans="1:2">
+      <c r="A470" s="3"/>
+      <c r="B470" s="3"/>
+    </row>
+    <row r="471" ht="25" customHeight="1" spans="1:2">
+      <c r="A471" s="3"/>
+      <c r="B471" s="3"/>
+    </row>
+    <row r="472" ht="25" customHeight="1" spans="1:2">
+      <c r="A472" s="3"/>
+      <c r="B472" s="3"/>
+    </row>
+    <row r="473" ht="25" customHeight="1" spans="1:2">
+      <c r="A473" s="3"/>
+      <c r="B473" s="3"/>
+    </row>
+    <row r="474" ht="25" customHeight="1" spans="1:2">
+      <c r="A474" s="3"/>
+      <c r="B474" s="3"/>
+    </row>
+    <row r="475" ht="25" customHeight="1" spans="1:2">
+      <c r="A475" s="3"/>
+      <c r="B475" s="3"/>
+    </row>
+    <row r="476" ht="25" customHeight="1" spans="1:2">
+      <c r="A476" s="3"/>
+      <c r="B476" s="3"/>
+    </row>
+    <row r="477" ht="25" customHeight="1" spans="1:2">
+      <c r="A477" s="3"/>
+      <c r="B477" s="3"/>
+    </row>
+    <row r="478" ht="25" customHeight="1" spans="1:2">
+      <c r="A478" s="3"/>
+      <c r="B478" s="3"/>
+    </row>
+    <row r="479" ht="25" customHeight="1" spans="1:2">
+      <c r="A479" s="3"/>
+      <c r="B479" s="3"/>
+    </row>
+    <row r="480" ht="25" customHeight="1" spans="1:2">
+      <c r="A480" s="3"/>
+      <c r="B480" s="3"/>
+    </row>
+    <row r="481" ht="25" customHeight="1" spans="1:2">
+      <c r="A481" s="3"/>
+      <c r="B481" s="3"/>
+    </row>
+    <row r="482" ht="25" customHeight="1" spans="1:2">
+      <c r="A482" s="3"/>
+      <c r="B482" s="3"/>
+    </row>
+    <row r="483" ht="25" customHeight="1" spans="1:2">
+      <c r="A483" s="3"/>
+      <c r="B483" s="3"/>
+    </row>
+    <row r="484" ht="25" customHeight="1" spans="1:2">
+      <c r="A484" s="3"/>
+      <c r="B484" s="3"/>
+    </row>
+    <row r="485" ht="25" customHeight="1" spans="1:2">
+      <c r="A485" s="3"/>
+      <c r="B485" s="3"/>
+    </row>
+    <row r="486" ht="25" customHeight="1" spans="1:2">
+      <c r="A486" s="3"/>
+      <c r="B486" s="3"/>
+    </row>
+    <row r="487" ht="25" customHeight="1" spans="1:2">
+      <c r="A487" s="3"/>
+      <c r="B487" s="3"/>
+    </row>
+    <row r="488" ht="25" customHeight="1" spans="1:2">
+      <c r="A488" s="3"/>
+      <c r="B488" s="3"/>
+    </row>
+    <row r="489" ht="25" customHeight="1" spans="1:2">
+      <c r="A489" s="3"/>
+      <c r="B489" s="3"/>
+    </row>
+    <row r="490" ht="25" customHeight="1" spans="1:2">
+      <c r="A490" s="3"/>
+      <c r="B490" s="3"/>
+    </row>
+    <row r="491" ht="25" customHeight="1" spans="1:2">
+      <c r="A491" s="3"/>
+      <c r="B491" s="3"/>
+    </row>
+    <row r="492" ht="25" customHeight="1" spans="1:2">
+      <c r="A492" s="3"/>
+      <c r="B492" s="3"/>
+    </row>
+    <row r="493" ht="25" customHeight="1" spans="1:2">
+      <c r="A493" s="3"/>
+      <c r="B493" s="3"/>
+    </row>
+    <row r="494" ht="25" customHeight="1" spans="1:2">
+      <c r="A494" s="3"/>
+      <c r="B494" s="3"/>
+    </row>
+    <row r="495" ht="25" customHeight="1" spans="1:2">
+      <c r="A495" s="3"/>
+      <c r="B495" s="3"/>
+    </row>
+    <row r="496" ht="25" customHeight="1" spans="1:2">
+      <c r="A496" s="3"/>
+      <c r="B496" s="3"/>
+    </row>
+    <row r="497" ht="25" customHeight="1" spans="1:2">
+      <c r="A497" s="3"/>
+      <c r="B497" s="3"/>
+    </row>
+    <row r="498" ht="25" customHeight="1" spans="1:2">
+      <c r="A498" s="3"/>
+      <c r="B498" s="3"/>
+    </row>
+    <row r="499" ht="25" customHeight="1" spans="1:2">
+      <c r="A499" s="3"/>
+      <c r="B499" s="3"/>
+    </row>
+    <row r="500" ht="25" customHeight="1" spans="1:2">
+      <c r="A500" s="3"/>
+      <c r="B500" s="3"/>
+    </row>
+    <row r="501" ht="25" customHeight="1" spans="1:2">
+      <c r="A501" s="3"/>
+      <c r="B501" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="597">
   <si>
     <t>bangla</t>
   </si>
@@ -821,7 +821,7 @@
     <t>তুই একদম আমাকে ভুলে গেছিস, একটা কল পর্যন্ত দেস না</t>
   </si>
   <si>
-    <t>তুই এব্বেরে আঁরে ভুলি গেইয়্যুস, ওজ্ঞো কল পর্যন্ত নো দস</t>
+    <t>তুই এব্বেরে আঁরে ভুলি গেইয়্যুস, উজ্ঞো কল পর্যন্ত নো দস</t>
   </si>
   <si>
     <t>রফিক সাহেব কেমন আছেন? অনেকদিন তাঁর সাথে দেখা হয় নাই, আমার চিন্তা হচ্ছে এখন</t>
@@ -1458,27 +1458,48 @@
     <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তন গরু গুস্ত আর ইছে মাছ আনো</t>
   </si>
   <si>
-    <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি একটা চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
+    <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি এক কাপ চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
+  </si>
+  <si>
+    <t>অফিস উত্তুন আইয়্যিরে অরান লাগের বাজি, এহন যদি এক কাপ চা ন হায় মাথা ঘুরাই পরি যাইয়্যুম</t>
   </si>
   <si>
     <t>আজকে অফিসে কাজের চাপ কম, তাই জলদি চলে আসছি</t>
   </si>
   <si>
+    <t>আজিয়ে অফিসুত হাজুর চাপ হম, এতাল্লে হারা চলি আইস্যি</t>
+  </si>
+  <si>
     <t>অফিস থেকে আসার সময় বাজার থেকে টমেটো আর চিংড়ি মাছ নিয়ে আসিও</t>
   </si>
   <si>
+    <t>অফিস উত্তুন আইবের সময় বাজার উত্তুন হাট্টা বেইয়্যুন আর ইছে মাছ লই আইস্যু</t>
+  </si>
+  <si>
     <t>আজকে নিউ মার্কেট থেকে একটা পাঞ্জাবি কিনেছি</t>
   </si>
   <si>
+    <t>আজিয়ে নিউ মার্কেটুত্তুন উজ্ঞো পাঞ্জাবি কিন্নি</t>
+  </si>
+  <si>
     <t>আজকে অফিসে অনেক কাজ, তাই আমার আসতে দেরি হবে</t>
   </si>
   <si>
+    <t>আজিয়ে অফিসুত বত হাম, এতেল্লে আত্তুন আসতে দেরি অইবু</t>
+  </si>
+  <si>
     <t>মার্কেটে অনেক ভিড়, তাই আসতে দেরি হবে</t>
   </si>
   <si>
+    <t>মার্কেটুত বত জাম, এতেল্লে আসতে দেরি অইবু</t>
+  </si>
+  <si>
     <t>ডাক্তার বলেছে সময়মতো খাবার খেতে</t>
   </si>
   <si>
+    <t>ডাক্তার হইয়্যিদে সময়মতো হানা হাইবেল্লাই</t>
+  </si>
+  <si>
     <t>আজকে আমার পা ব্যথা করছে, রান্না না হয় তুমি কর</t>
   </si>
   <si>
@@ -1488,9 +1509,15 @@
     <t>চল, আজকে বাইরে থেকে খেয়ে আসি, ঘরের খাবার আর ভাল লাগছেনা</t>
   </si>
   <si>
+    <t>চল, আজিয়ে বাইরেত্তুন হায় আই, ঘরোর হানা আর ভালা নলাগের</t>
+  </si>
+  <si>
     <t>সময়মতো খাবার না খেলে শরীর দুর্বল হয়ে যাবে</t>
   </si>
   <si>
+    <t>সময়মতো হানা ন হাইলি শরীর দুর্বল অই যাইবু</t>
+  </si>
+  <si>
     <t>এভাবে মরার মতো কে ঘুমায়! জলদি উঠ ঘুম থেকে</t>
   </si>
   <si>
@@ -1573,6 +1600,276 @@
   </si>
   <si>
     <t>বেইন্নে দেরি গরি ঘুমোত্তন উডিলি নাস্তা গম গরি হন ন যায়</t>
+  </si>
+  <si>
+    <t>বাজারের তালিকা আগে থেকে তৈরি না করলে অনেক সময় দরকারি জিনিস কিনতে ভুলে যায়</t>
+  </si>
+  <si>
+    <t>বাজারোর লিস্ট আগেত্তোন তৈরি ন গরিলি বত সময় দরহারি জিনিস কিনতে ভুলি যায়</t>
+  </si>
+  <si>
+    <t>আগামিকাল পরিক্ষা, কিন্তু আমার পড়তে মন চাচ্ছে না</t>
+  </si>
+  <si>
+    <t>হালিয়ে পরিক্ষে, কিন্তু আত্তুন  পইত্তো মনে ন হর</t>
+  </si>
+  <si>
+    <t>অনেক পড়া জমে আছে</t>
+  </si>
+  <si>
+    <t>বত পরা জমি আছে</t>
+  </si>
+  <si>
+    <t>এই পরিক্ষাটা খারাপ হয়েছে</t>
+  </si>
+  <si>
+    <t>এই পরিক্ষে ইবে হারাপ অইয়্যি</t>
+  </si>
+  <si>
+    <t>প্রশ্ন দেখে আমার মাথা ঘুরে গেছে</t>
+  </si>
+  <si>
+    <t>প্রশ্ন দেহি রে আঁর মাথা ঘুরি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এই পরিক্ষাটা খারাপ হয়েছে, সামনের পরিক্ষাটা ভাল করে দিতে হবে</t>
+  </si>
+  <si>
+    <t>এই পরিক্ষে ইবে হারাপ অইয়্যি, সামনোর পরিক্ষে ইবে ভালা গরি দন পরিবো</t>
+  </si>
+  <si>
+    <t>আজকে কাজে একদম মন বাসছেনা</t>
+  </si>
+  <si>
+    <t>আজিয়ে হাজোত এব্বেরে মন ন বইয়্যির</t>
+  </si>
+  <si>
+    <t>আরো অনেক কাজ বাকি আছে</t>
+  </si>
+  <si>
+    <t>আরো বত হাজ বাকি আছে</t>
+  </si>
+  <si>
+    <t>যে সময়ের কাজ ঐ সময় শেষ করতে হবে</t>
+  </si>
+  <si>
+    <t>যেই সময়োর হাজ এই সময় শেষ গরন পরিবো</t>
+  </si>
+  <si>
+    <t>বাগানের কিছু কাজ এখনো বাকি আছে</t>
+  </si>
+  <si>
+    <t>বাগানোর কিছু হাম এহনো বাকি আছে</t>
+  </si>
+  <si>
+    <t>জলদি যাও, সূর্য ডোবার আগে কাজ শেষ কর</t>
+  </si>
+  <si>
+    <t>হারা যও, সূর্য ডোফিবের আগে হাম শেষ গরো</t>
+  </si>
+  <si>
+    <t>এবারের মরিচ ক্ষেত অনেক ভাল হয়েছে</t>
+  </si>
+  <si>
+    <t>এবারোর মরিচ ক্ষেতি বত ভালা অইয়্যি</t>
+  </si>
+  <si>
+    <t>ক্ষেত থেকে পাকা মরিচ গুলো নিয়ে আয়</t>
+  </si>
+  <si>
+    <t>ক্ষেতিত্তুন ফোয়ানা মরিচ এগুন লই আয়</t>
+  </si>
+  <si>
+    <t>মাঠে খুব বেশি রোদ, আমি এখন খেলব না</t>
+  </si>
+  <si>
+    <t>মাডোত বত বেশি রইদ, আঁই এহন খেইলতাম ন</t>
+  </si>
+  <si>
+    <t>তোরা খেলতে যাওয়ার পর আমাকে বলিস</t>
+  </si>
+  <si>
+    <t>তোরা খেইলতো যাইবের পরে আঁরে হইস</t>
+  </si>
+  <si>
+    <t>আমি ক্রিকেট খেলব না, ফুটবল খেলব</t>
+  </si>
+  <si>
+    <t>আঁই ক্রিকেট খেইলতাম নো, ফুটবল খেইল্লোম</t>
+  </si>
+  <si>
+    <t>মারুফ প্রথম বলেই আউট হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>মারুফ পইল্লের বলেই আউট অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আজকে আমি অনেক বড় একটা ছক্কা মেরেছি</t>
+  </si>
+  <si>
+    <t>আজিয়ে বত বরো উজ্ঞো ছক্কা মেইজ্জি</t>
+  </si>
+  <si>
+    <t>একটানা তিনটা ছক্কা মারার পর আউট হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>এক লগে তিন্নো ছক্কা মারিবের পরে আউট অই গেই</t>
+  </si>
+  <si>
+    <t>কোথায় যাস সেলিম?</t>
+  </si>
+  <si>
+    <t>হনডে যর সেলিম?</t>
+  </si>
+  <si>
+    <t>আমি মাঠে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই মাডোত যাইর</t>
+  </si>
+  <si>
+    <t>মাঠে গেলে চল</t>
+  </si>
+  <si>
+    <t>মাডোত যাইলি চল</t>
+  </si>
+  <si>
+    <t>আমি যাব না, কারন বেশি রোদ</t>
+  </si>
+  <si>
+    <t>আঁই যাইতাম নো, হারন বেশি রইদ</t>
+  </si>
+  <si>
+    <t>এরকম রোদে বের হলে কালো হয়ে যাব</t>
+  </si>
+  <si>
+    <t>এরহম রইদোত বাইর অইলি হালা অই যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমরা সবাই মাঠে, তুই এখন কোথায়?</t>
+  </si>
+  <si>
+    <t>আঁরা বিয়াজ্ঞুন মাডোত, তুই এহন হনডে?</t>
+  </si>
+  <si>
+    <t>বলটি সরাসরি আমার কাছে দে</t>
+  </si>
+  <si>
+    <t>বল ইবে সরাসরি আঁর হাছে দে</t>
+  </si>
+  <si>
+    <t>ওইদিকে মারিস না, আমার দিকে পাস দে</t>
+  </si>
+  <si>
+    <t>ইক্কে ন মারিস, আঁর মিক্কে পাস দে</t>
+  </si>
+  <si>
+    <t>বলটি যদি আমার দিকে পাস দিতি তাহলে গোল দিতে পারতাম</t>
+  </si>
+  <si>
+    <t>বল ইবে যদি আঁম মিক্কে পাস দিতি তইলি গোল দিত পাইত্তাম</t>
+  </si>
+  <si>
+    <t>বলটি কোনদিকে মারছো? খোজে পাচ্ছিনা</t>
+  </si>
+  <si>
+    <t>বল ইবে হুনদি মাইজ্জো? তোওয়াই ন পাইদ্দি</t>
+  </si>
+  <si>
+    <t>এখন সন্ধ্যা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>এহন আজুইন্নে অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এবার বাড়ি যায়, সন্ধ্যা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>এবার বারিত যায়, আজুইন্নে অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>জলদি আই, দেরি হলে মা গালি দিবে</t>
+  </si>
+  <si>
+    <t>হারা আই, দেরি অইলি আম্মু গাইল দিবো</t>
+  </si>
+  <si>
+    <t>অনেকগুলো কাপড় জমে আছে</t>
+  </si>
+  <si>
+    <t>বত হদিজ্ঞিন হর জমি আছে</t>
+  </si>
+  <si>
+    <t>সব কাপড় তোমাকে ধুতে হবে</t>
+  </si>
+  <si>
+    <t>বিয়াক হর তোঁয়াত্তুন ধোয়ন পরিবো</t>
+  </si>
+  <si>
+    <t>কাপড় গুলো বিছানার উপর কেন জমা করে রাখছো?</t>
+  </si>
+  <si>
+    <t>হর এগিন বিছানার উদ্দি কা টালায় রাইক্কো?</t>
+  </si>
+  <si>
+    <t>আজকে আম্মু পিঠা বানাচ্ছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে আম্মু পিডে বানার</t>
+  </si>
+  <si>
+    <t>শীতকালে ভাপা পিঠা খেতে অনেক মজা</t>
+  </si>
+  <si>
+    <t>শীতহালে ধু পিডে হাইতে বত মজা</t>
+  </si>
+  <si>
+    <t>আমাকে আরো কিছু গরম গরম ভাপা পিঠা দাও</t>
+  </si>
+  <si>
+    <t>আঁরে আরো কিছু গরম গরম ধু পিডে দও</t>
+  </si>
+  <si>
+    <t>আমার পেটে আর জায়গা নাই, আর দিও না</t>
+  </si>
+  <si>
+    <t>আঁর পেডোত আর জাগা নাই, আর নইদ্দো</t>
+  </si>
+  <si>
+    <t>বাইরের খাবার থেকে ঘরের খাবার বেশি নিরাপদ</t>
+  </si>
+  <si>
+    <t>বাইরোর হানাত্তুন বর ঘরোর হানা বেশি নিরাপদ</t>
+  </si>
+  <si>
+    <t>কথা না বলে চুপ চাপ খাবার খাও</t>
+  </si>
+  <si>
+    <t>হতা ন হইরে চুপ চাপ হানা হ</t>
+  </si>
+  <si>
+    <t>সকালে চা না খেলে মাথা একদম কাজ করেনা</t>
+  </si>
+  <si>
+    <t>বেইন্নে চা ন হাইলি মাথা এব্বেরে হাম ন গরে</t>
+  </si>
+  <si>
+    <t>ঘুম কম হওয়ার কারণে এখন মাথা ব্যাথা করছে</t>
+  </si>
+  <si>
+    <t>ঘুম হম অইবের হারনে এহন মাথা ব্যাথা গরের</t>
+  </si>
+  <si>
+    <t>শুটকি দিয়ে আলুর তরকারি অনেক মজা</t>
+  </si>
+  <si>
+    <t>উনি দি আলুর তরহারি বত মজা</t>
+  </si>
+  <si>
+    <t>আমাকে আরেকটু শুটকি দাও</t>
+  </si>
+  <si>
+    <t>আঁরে আরেক্কানা শুটকি দও</t>
   </si>
 </sst>
 </file>
@@ -2200,14 +2497,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4361,1406 +4655,1604 @@
       </c>
     </row>
     <row r="202" ht="25" customHeight="1" spans="1:2">
-      <c r="A202" s="3" t="s">
+      <c r="A202" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="203" ht="25" customHeight="1" spans="1:2">
-      <c r="A203" s="3" t="s">
+      <c r="A203" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="204" ht="25" customHeight="1" spans="1:2">
-      <c r="A204" s="3" t="s">
+      <c r="A204" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="205" ht="25" customHeight="1" spans="1:2">
-      <c r="A205" s="3" t="s">
+      <c r="A205" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="206" ht="25" customHeight="1" spans="1:2">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="207" ht="25" customHeight="1" spans="1:2">
-      <c r="A207" s="3" t="s">
+      <c r="A207" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="208" ht="25" customHeight="1" spans="1:2">
-      <c r="A208" s="3" t="s">
+      <c r="A208" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="209" ht="25" customHeight="1" spans="1:2">
-      <c r="A209" s="3" t="s">
+      <c r="A209" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="210" ht="25" customHeight="1" spans="1:2">
-      <c r="A210" s="3" t="s">
+      <c r="A210" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="211" ht="25" customHeight="1" spans="1:2">
-      <c r="A211" s="3" t="s">
+      <c r="A211" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="212" ht="25" customHeight="1" spans="1:2">
-      <c r="A212" s="3" t="s">
+      <c r="A212" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="213" ht="25" customHeight="1" spans="1:2">
-      <c r="A213" s="3" t="s">
+      <c r="A213" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="214" ht="25" customHeight="1" spans="1:2">
-      <c r="A214" s="3" t="s">
+      <c r="A214" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="2" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="215" ht="25" customHeight="1" spans="1:2">
-      <c r="A215" s="3" t="s">
+      <c r="A215" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="216" ht="25" customHeight="1" spans="1:2">
-      <c r="A216" s="3" t="s">
+      <c r="A216" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="2" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="217" ht="25" customHeight="1" spans="1:2">
-      <c r="A217" s="3" t="s">
+      <c r="A217" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="218" ht="25" customHeight="1" spans="1:2">
-      <c r="A218" s="3" t="s">
+      <c r="A218" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="2" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="219" ht="25" customHeight="1" spans="1:2">
-      <c r="A219" s="3" t="s">
+      <c r="A219" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="220" ht="25" customHeight="1" spans="1:2">
-      <c r="A220" s="3" t="s">
+      <c r="A220" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="221" ht="25" customHeight="1" spans="1:2">
-      <c r="A221" s="3" t="s">
+      <c r="A221" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="222" ht="25" customHeight="1" spans="1:2">
-      <c r="A222" s="3" t="s">
+      <c r="A222" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="223" ht="25" customHeight="1" spans="1:2">
-      <c r="A223" s="3" t="s">
+      <c r="A223" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="224" ht="25" customHeight="1" spans="1:2">
-      <c r="A224" s="3" t="s">
+      <c r="A224" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="225" ht="25" customHeight="1" spans="1:2">
-      <c r="A225" s="3" t="s">
+      <c r="A225" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="226" ht="25" customHeight="1" spans="1:2">
-      <c r="A226" s="3" t="s">
+      <c r="A226" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="227" ht="25" customHeight="1" spans="1:2">
-      <c r="A227" s="3" t="s">
+      <c r="A227" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="228" ht="25" customHeight="1" spans="1:2">
-      <c r="A228" s="3" t="s">
+      <c r="A228" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="229" ht="25" customHeight="1" spans="1:2">
-      <c r="A229" s="3" t="s">
+      <c r="A229" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="2" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="230" ht="25" customHeight="1" spans="1:2">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="231" ht="25" customHeight="1" spans="1:2">
-      <c r="A231" s="3" t="s">
+      <c r="A231" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="232" ht="25" customHeight="1" spans="1:2">
-      <c r="A232" s="3" t="s">
+      <c r="A232" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="233" ht="25" customHeight="1" spans="1:2">
-      <c r="A233" s="3" t="s">
+      <c r="A233" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B233" s="3"/>
+      <c r="B233" s="2" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="234" ht="25" customHeight="1" spans="1:2">
-      <c r="A234" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B234" s="3"/>
+      <c r="A234" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="235" ht="25" customHeight="1" spans="1:2">
-      <c r="A235" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="B235" s="3"/>
+      <c r="A235" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="236" ht="25" customHeight="1" spans="1:2">
-      <c r="A236" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="B236" s="3"/>
+      <c r="A236" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="237" ht="25" customHeight="1" spans="1:2">
-      <c r="A237" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="B237" s="3"/>
+      <c r="A237" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="238" ht="25" customHeight="1" spans="1:2">
-      <c r="A238" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B238" s="3"/>
+      <c r="A238" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="239" ht="25" customHeight="1" spans="1:2">
-      <c r="A239" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B239" s="3"/>
+      <c r="A239" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="240" ht="25" customHeight="1" spans="1:2">
-      <c r="A240" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>467</v>
+      <c r="A240" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="241" ht="25" customHeight="1" spans="1:2">
-      <c r="A241" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B241" s="3"/>
+      <c r="A241" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="242" ht="25" customHeight="1" spans="1:2">
-      <c r="A242" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="B242" s="3"/>
+      <c r="A242" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="243" ht="25" customHeight="1" spans="1:2">
-      <c r="A243" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>471</v>
+      <c r="A243" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="244" ht="25" customHeight="1" spans="1:2">
-      <c r="A244" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>473</v>
+      <c r="A244" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="245" ht="25" customHeight="1" spans="1:2">
-      <c r="A245" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>475</v>
+      <c r="A245" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="246" ht="25" customHeight="1" spans="1:2">
-      <c r="A246" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>477</v>
+      <c r="A246" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="247" ht="25" customHeight="1" spans="1:2">
-      <c r="A247" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>479</v>
+      <c r="A247" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="248" ht="25" customHeight="1" spans="1:2">
-      <c r="A248" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>481</v>
+      <c r="A248" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="249" ht="25" customHeight="1" spans="1:2">
-      <c r="A249" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>483</v>
+      <c r="A249" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="250" ht="25" customHeight="1" spans="1:2">
-      <c r="A250" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>485</v>
+      <c r="A250" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="251" ht="25" customHeight="1" spans="1:2">
-      <c r="A251" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>487</v>
+      <c r="A251" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="252" ht="25" customHeight="1" spans="1:2">
-      <c r="A252" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>489</v>
+      <c r="A252" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="253" ht="25" customHeight="1" spans="1:2">
-      <c r="A253" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>491</v>
+      <c r="A253" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="254" ht="25" customHeight="1" spans="1:2">
-      <c r="A254" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>493</v>
+      <c r="A254" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="255" ht="25" customHeight="1" spans="1:2">
-      <c r="A255" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>495</v>
+      <c r="A255" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="256" ht="25" customHeight="1" spans="1:2">
-      <c r="A256" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>497</v>
+      <c r="A256" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="257" ht="25" customHeight="1" spans="1:2">
-      <c r="A257" s="3"/>
-      <c r="B257" s="3"/>
+      <c r="A257" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="258" ht="25" customHeight="1" spans="1:2">
-      <c r="A258" s="3"/>
-      <c r="B258" s="3"/>
+      <c r="A258" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="259" ht="25" customHeight="1" spans="1:2">
-      <c r="A259" s="3"/>
-      <c r="B259" s="3"/>
+      <c r="A259" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="260" ht="25" customHeight="1" spans="1:2">
-      <c r="A260" s="3"/>
-      <c r="B260" s="3"/>
+      <c r="A260" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="261" ht="25" customHeight="1" spans="1:2">
-      <c r="A261" s="3"/>
-      <c r="B261" s="3"/>
+      <c r="A261" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="262" ht="25" customHeight="1" spans="1:2">
-      <c r="A262" s="3"/>
-      <c r="B262" s="3"/>
+      <c r="A262" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="263" ht="25" customHeight="1" spans="1:2">
-      <c r="A263" s="3"/>
-      <c r="B263" s="3"/>
+      <c r="A263" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="264" ht="25" customHeight="1" spans="1:2">
-      <c r="A264" s="3"/>
-      <c r="B264" s="3"/>
+      <c r="A264" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="265" ht="25" customHeight="1" spans="1:2">
-      <c r="A265" s="3"/>
-      <c r="B265" s="3"/>
+      <c r="A265" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="266" ht="25" customHeight="1" spans="1:2">
-      <c r="A266" s="3"/>
-      <c r="B266" s="3"/>
+      <c r="A266" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="267" ht="25" customHeight="1" spans="1:2">
-      <c r="A267" s="3"/>
-      <c r="B267" s="3"/>
+      <c r="A267" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="268" ht="25" customHeight="1" spans="1:2">
-      <c r="A268" s="3"/>
-      <c r="B268" s="3"/>
+      <c r="A268" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="269" ht="25" customHeight="1" spans="1:2">
-      <c r="A269" s="3"/>
-      <c r="B269" s="3"/>
+      <c r="A269" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="270" ht="25" customHeight="1" spans="1:2">
-      <c r="A270" s="3"/>
-      <c r="B270" s="3"/>
+      <c r="A270" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="271" ht="25" customHeight="1" spans="1:2">
-      <c r="A271" s="3"/>
-      <c r="B271" s="3"/>
+      <c r="A271" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="272" ht="25" customHeight="1" spans="1:2">
-      <c r="A272" s="3"/>
-      <c r="B272" s="3"/>
+      <c r="A272" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="273" ht="25" customHeight="1" spans="1:2">
-      <c r="A273" s="3"/>
-      <c r="B273" s="3"/>
+      <c r="A273" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="274" ht="25" customHeight="1" spans="1:2">
-      <c r="A274" s="3"/>
-      <c r="B274" s="3"/>
+      <c r="A274" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="275" ht="25" customHeight="1" spans="1:2">
-      <c r="A275" s="3"/>
-      <c r="B275" s="3"/>
+      <c r="A275" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="276" ht="25" customHeight="1" spans="1:2">
-      <c r="A276" s="3"/>
-      <c r="B276" s="3"/>
+      <c r="A276" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="277" ht="25" customHeight="1" spans="1:2">
-      <c r="A277" s="3"/>
-      <c r="B277" s="3"/>
+      <c r="A277" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="278" ht="25" customHeight="1" spans="1:2">
-      <c r="A278" s="3"/>
-      <c r="B278" s="3"/>
+      <c r="A278" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="279" ht="25" customHeight="1" spans="1:2">
-      <c r="A279" s="3"/>
-      <c r="B279" s="3"/>
+      <c r="A279" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="280" ht="25" customHeight="1" spans="1:2">
-      <c r="A280" s="3"/>
-      <c r="B280" s="3"/>
+      <c r="A280" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="281" ht="25" customHeight="1" spans="1:2">
-      <c r="A281" s="3"/>
-      <c r="B281" s="3"/>
+      <c r="A281" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="282" ht="25" customHeight="1" spans="1:2">
-      <c r="A282" s="3"/>
-      <c r="B282" s="3"/>
+      <c r="A282" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="283" ht="25" customHeight="1" spans="1:2">
-      <c r="A283" s="3"/>
-      <c r="B283" s="3"/>
+      <c r="A283" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="284" ht="25" customHeight="1" spans="1:2">
-      <c r="A284" s="3"/>
-      <c r="B284" s="3"/>
+      <c r="A284" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="285" ht="25" customHeight="1" spans="1:2">
-      <c r="A285" s="3"/>
-      <c r="B285" s="3"/>
+      <c r="A285" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="286" ht="25" customHeight="1" spans="1:2">
-      <c r="A286" s="3"/>
-      <c r="B286" s="3"/>
+      <c r="A286" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="287" ht="25" customHeight="1" spans="1:2">
-      <c r="A287" s="3"/>
-      <c r="B287" s="3"/>
+      <c r="A287" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="288" ht="25" customHeight="1" spans="1:2">
-      <c r="A288" s="3"/>
-      <c r="B288" s="3"/>
+      <c r="A288" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="289" ht="25" customHeight="1" spans="1:2">
-      <c r="A289" s="3"/>
-      <c r="B289" s="3"/>
+      <c r="A289" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="290" ht="25" customHeight="1" spans="1:2">
-      <c r="A290" s="3"/>
-      <c r="B290" s="3"/>
+      <c r="A290" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="291" ht="25" customHeight="1" spans="1:2">
-      <c r="A291" s="3"/>
-      <c r="B291" s="3"/>
+      <c r="A291" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="292" ht="25" customHeight="1" spans="1:2">
-      <c r="A292" s="3"/>
-      <c r="B292" s="3"/>
+      <c r="A292" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="293" ht="25" customHeight="1" spans="1:2">
-      <c r="A293" s="3"/>
-      <c r="B293" s="3"/>
+      <c r="A293" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="294" ht="25" customHeight="1" spans="1:2">
-      <c r="A294" s="3"/>
-      <c r="B294" s="3"/>
+      <c r="A294" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="295" ht="25" customHeight="1" spans="1:2">
-      <c r="A295" s="3"/>
-      <c r="B295" s="3"/>
+      <c r="A295" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="296" ht="25" customHeight="1" spans="1:2">
-      <c r="A296" s="3"/>
-      <c r="B296" s="3"/>
+      <c r="A296" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="297" ht="25" customHeight="1" spans="1:2">
-      <c r="A297" s="3"/>
-      <c r="B297" s="3"/>
+      <c r="A297" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="298" ht="25" customHeight="1" spans="1:2">
-      <c r="A298" s="3"/>
-      <c r="B298" s="3"/>
+      <c r="A298" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="299" ht="25" customHeight="1" spans="1:2">
-      <c r="A299" s="3"/>
-      <c r="B299" s="3"/>
+      <c r="A299" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="300" ht="25" customHeight="1" spans="1:2">
-      <c r="A300" s="3"/>
-      <c r="B300" s="3"/>
+      <c r="A300" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="301" ht="25" customHeight="1" spans="1:2">
-      <c r="A301" s="3"/>
-      <c r="B301" s="3"/>
+      <c r="A301" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="302" ht="25" customHeight="1" spans="1:2">
-      <c r="A302" s="3"/>
-      <c r="B302" s="3"/>
+      <c r="A302" s="2"/>
+      <c r="B302" s="2"/>
     </row>
     <row r="303" ht="25" customHeight="1" spans="1:2">
-      <c r="A303" s="3"/>
-      <c r="B303" s="3"/>
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
     </row>
     <row r="304" ht="25" customHeight="1" spans="1:2">
-      <c r="A304" s="3"/>
-      <c r="B304" s="3"/>
+      <c r="A304" s="2"/>
+      <c r="B304" s="2"/>
     </row>
     <row r="305" ht="25" customHeight="1" spans="1:2">
-      <c r="A305" s="3"/>
-      <c r="B305" s="3"/>
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
     </row>
     <row r="306" ht="25" customHeight="1" spans="1:2">
-      <c r="A306" s="3"/>
-      <c r="B306" s="3"/>
+      <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
     </row>
     <row r="307" ht="25" customHeight="1" spans="1:2">
-      <c r="A307" s="3"/>
-      <c r="B307" s="3"/>
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
     </row>
     <row r="308" ht="25" customHeight="1" spans="1:2">
-      <c r="A308" s="3"/>
-      <c r="B308" s="3"/>
+      <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
     </row>
     <row r="309" ht="25" customHeight="1" spans="1:2">
-      <c r="A309" s="3"/>
-      <c r="B309" s="3"/>
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
     </row>
     <row r="310" ht="25" customHeight="1" spans="1:2">
-      <c r="A310" s="3"/>
-      <c r="B310" s="3"/>
+      <c r="A310" s="2"/>
+      <c r="B310" s="2"/>
     </row>
     <row r="311" ht="25" customHeight="1" spans="1:2">
-      <c r="A311" s="3"/>
-      <c r="B311" s="3"/>
+      <c r="A311" s="2"/>
+      <c r="B311" s="2"/>
     </row>
     <row r="312" ht="25" customHeight="1" spans="1:2">
-      <c r="A312" s="3"/>
-      <c r="B312" s="3"/>
+      <c r="A312" s="2"/>
+      <c r="B312" s="2"/>
     </row>
     <row r="313" ht="25" customHeight="1" spans="1:2">
-      <c r="A313" s="3"/>
-      <c r="B313" s="3"/>
+      <c r="A313" s="2"/>
+      <c r="B313" s="2"/>
     </row>
     <row r="314" ht="25" customHeight="1" spans="1:2">
-      <c r="A314" s="3"/>
-      <c r="B314" s="3"/>
+      <c r="A314" s="2"/>
+      <c r="B314" s="2"/>
     </row>
     <row r="315" ht="25" customHeight="1" spans="1:2">
-      <c r="A315" s="3"/>
-      <c r="B315" s="3"/>
+      <c r="A315" s="2"/>
+      <c r="B315" s="2"/>
     </row>
     <row r="316" ht="25" customHeight="1" spans="1:2">
-      <c r="A316" s="3"/>
-      <c r="B316" s="3"/>
+      <c r="A316" s="2"/>
+      <c r="B316" s="2"/>
     </row>
     <row r="317" ht="25" customHeight="1" spans="1:2">
-      <c r="A317" s="3"/>
-      <c r="B317" s="3"/>
+      <c r="A317" s="2"/>
+      <c r="B317" s="2"/>
     </row>
     <row r="318" ht="25" customHeight="1" spans="1:2">
-      <c r="A318" s="3"/>
-      <c r="B318" s="3"/>
+      <c r="A318" s="2"/>
+      <c r="B318" s="2"/>
     </row>
     <row r="319" ht="25" customHeight="1" spans="1:2">
-      <c r="A319" s="3"/>
-      <c r="B319" s="3"/>
+      <c r="A319" s="2"/>
+      <c r="B319" s="2"/>
     </row>
     <row r="320" ht="25" customHeight="1" spans="1:2">
-      <c r="A320" s="3"/>
-      <c r="B320" s="3"/>
+      <c r="A320" s="2"/>
+      <c r="B320" s="2"/>
     </row>
     <row r="321" ht="25" customHeight="1" spans="1:2">
-      <c r="A321" s="3"/>
-      <c r="B321" s="3"/>
+      <c r="A321" s="2"/>
+      <c r="B321" s="2"/>
     </row>
     <row r="322" ht="25" customHeight="1" spans="1:2">
-      <c r="A322" s="3"/>
-      <c r="B322" s="3"/>
+      <c r="A322" s="2"/>
+      <c r="B322" s="2"/>
     </row>
     <row r="323" ht="25" customHeight="1" spans="1:2">
-      <c r="A323" s="3"/>
-      <c r="B323" s="3"/>
+      <c r="A323" s="2"/>
+      <c r="B323" s="2"/>
     </row>
     <row r="324" ht="25" customHeight="1" spans="1:2">
-      <c r="A324" s="3"/>
-      <c r="B324" s="3"/>
+      <c r="A324" s="2"/>
+      <c r="B324" s="2"/>
     </row>
     <row r="325" ht="25" customHeight="1" spans="1:2">
-      <c r="A325" s="3"/>
-      <c r="B325" s="3"/>
+      <c r="A325" s="2"/>
+      <c r="B325" s="2"/>
     </row>
     <row r="326" ht="25" customHeight="1" spans="1:2">
-      <c r="A326" s="3"/>
-      <c r="B326" s="3"/>
+      <c r="A326" s="2"/>
+      <c r="B326" s="2"/>
     </row>
     <row r="327" ht="25" customHeight="1" spans="1:2">
-      <c r="A327" s="3"/>
-      <c r="B327" s="3"/>
+      <c r="A327" s="2"/>
+      <c r="B327" s="2"/>
     </row>
     <row r="328" ht="25" customHeight="1" spans="1:2">
-      <c r="A328" s="3"/>
-      <c r="B328" s="3"/>
+      <c r="A328" s="2"/>
+      <c r="B328" s="2"/>
     </row>
     <row r="329" ht="25" customHeight="1" spans="1:2">
-      <c r="A329" s="3"/>
-      <c r="B329" s="3"/>
+      <c r="A329" s="2"/>
+      <c r="B329" s="2"/>
     </row>
     <row r="330" ht="25" customHeight="1" spans="1:2">
-      <c r="A330" s="3"/>
-      <c r="B330" s="3"/>
+      <c r="A330" s="2"/>
+      <c r="B330" s="2"/>
     </row>
     <row r="331" ht="25" customHeight="1" spans="1:2">
-      <c r="A331" s="3"/>
-      <c r="B331" s="3"/>
+      <c r="A331" s="2"/>
+      <c r="B331" s="2"/>
     </row>
     <row r="332" ht="25" customHeight="1" spans="1:2">
-      <c r="A332" s="3"/>
-      <c r="B332" s="3"/>
+      <c r="A332" s="2"/>
+      <c r="B332" s="2"/>
     </row>
     <row r="333" ht="25" customHeight="1" spans="1:2">
-      <c r="A333" s="3"/>
-      <c r="B333" s="3"/>
+      <c r="A333" s="2"/>
+      <c r="B333" s="2"/>
     </row>
     <row r="334" ht="25" customHeight="1" spans="1:2">
-      <c r="A334" s="3"/>
-      <c r="B334" s="3"/>
+      <c r="A334" s="2"/>
+      <c r="B334" s="2"/>
     </row>
     <row r="335" ht="25" customHeight="1" spans="1:2">
-      <c r="A335" s="3"/>
-      <c r="B335" s="3"/>
+      <c r="A335" s="2"/>
+      <c r="B335" s="2"/>
     </row>
     <row r="336" ht="25" customHeight="1" spans="1:2">
-      <c r="A336" s="3"/>
-      <c r="B336" s="3"/>
+      <c r="A336" s="2"/>
+      <c r="B336" s="2"/>
     </row>
     <row r="337" ht="25" customHeight="1" spans="1:2">
-      <c r="A337" s="3"/>
-      <c r="B337" s="3"/>
+      <c r="A337" s="2"/>
+      <c r="B337" s="2"/>
     </row>
     <row r="338" ht="25" customHeight="1" spans="1:2">
-      <c r="A338" s="3"/>
-      <c r="B338" s="3"/>
+      <c r="A338" s="2"/>
+      <c r="B338" s="2"/>
     </row>
     <row r="339" ht="25" customHeight="1" spans="1:2">
-      <c r="A339" s="3"/>
-      <c r="B339" s="3"/>
+      <c r="A339" s="2"/>
+      <c r="B339" s="2"/>
     </row>
     <row r="340" ht="25" customHeight="1" spans="1:2">
-      <c r="A340" s="3"/>
-      <c r="B340" s="3"/>
+      <c r="A340" s="2"/>
+      <c r="B340" s="2"/>
     </row>
     <row r="341" ht="25" customHeight="1" spans="1:2">
-      <c r="A341" s="3"/>
-      <c r="B341" s="3"/>
+      <c r="A341" s="2"/>
+      <c r="B341" s="2"/>
     </row>
     <row r="342" ht="25" customHeight="1" spans="1:2">
-      <c r="A342" s="3"/>
-      <c r="B342" s="3"/>
+      <c r="A342" s="2"/>
+      <c r="B342" s="2"/>
     </row>
     <row r="343" ht="25" customHeight="1" spans="1:2">
-      <c r="A343" s="3"/>
-      <c r="B343" s="3"/>
+      <c r="A343" s="2"/>
+      <c r="B343" s="2"/>
     </row>
     <row r="344" ht="25" customHeight="1" spans="1:2">
-      <c r="A344" s="3"/>
-      <c r="B344" s="3"/>
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
     </row>
     <row r="345" ht="25" customHeight="1" spans="1:2">
-      <c r="A345" s="3"/>
-      <c r="B345" s="3"/>
+      <c r="A345" s="2"/>
+      <c r="B345" s="2"/>
     </row>
     <row r="346" ht="25" customHeight="1" spans="1:2">
-      <c r="A346" s="3"/>
-      <c r="B346" s="3"/>
+      <c r="A346" s="2"/>
+      <c r="B346" s="2"/>
     </row>
     <row r="347" ht="25" customHeight="1" spans="1:2">
-      <c r="A347" s="3"/>
-      <c r="B347" s="3"/>
+      <c r="A347" s="2"/>
+      <c r="B347" s="2"/>
     </row>
     <row r="348" ht="25" customHeight="1" spans="1:2">
-      <c r="A348" s="3"/>
-      <c r="B348" s="3"/>
+      <c r="A348" s="2"/>
+      <c r="B348" s="2"/>
     </row>
     <row r="349" ht="25" customHeight="1" spans="1:2">
-      <c r="A349" s="3"/>
-      <c r="B349" s="3"/>
+      <c r="A349" s="2"/>
+      <c r="B349" s="2"/>
     </row>
     <row r="350" ht="25" customHeight="1" spans="1:2">
-      <c r="A350" s="3"/>
-      <c r="B350" s="3"/>
+      <c r="A350" s="2"/>
+      <c r="B350" s="2"/>
     </row>
     <row r="351" ht="25" customHeight="1" spans="1:2">
-      <c r="A351" s="3"/>
-      <c r="B351" s="3"/>
+      <c r="A351" s="2"/>
+      <c r="B351" s="2"/>
     </row>
     <row r="352" ht="25" customHeight="1" spans="1:2">
-      <c r="A352" s="3"/>
-      <c r="B352" s="3"/>
+      <c r="A352" s="2"/>
+      <c r="B352" s="2"/>
     </row>
     <row r="353" ht="25" customHeight="1" spans="1:2">
-      <c r="A353" s="3"/>
-      <c r="B353" s="3"/>
+      <c r="A353" s="2"/>
+      <c r="B353" s="2"/>
     </row>
     <row r="354" ht="25" customHeight="1" spans="1:2">
-      <c r="A354" s="3"/>
-      <c r="B354" s="3"/>
+      <c r="A354" s="2"/>
+      <c r="B354" s="2"/>
     </row>
     <row r="355" ht="25" customHeight="1" spans="1:2">
-      <c r="A355" s="3"/>
-      <c r="B355" s="3"/>
+      <c r="A355" s="2"/>
+      <c r="B355" s="2"/>
     </row>
     <row r="356" ht="25" customHeight="1" spans="1:2">
-      <c r="A356" s="3"/>
-      <c r="B356" s="3"/>
+      <c r="A356" s="2"/>
+      <c r="B356" s="2"/>
     </row>
     <row r="357" ht="25" customHeight="1" spans="1:2">
-      <c r="A357" s="3"/>
-      <c r="B357" s="3"/>
+      <c r="A357" s="2"/>
+      <c r="B357" s="2"/>
     </row>
     <row r="358" ht="25" customHeight="1" spans="1:2">
-      <c r="A358" s="3"/>
-      <c r="B358" s="3"/>
+      <c r="A358" s="2"/>
+      <c r="B358" s="2"/>
     </row>
     <row r="359" ht="25" customHeight="1" spans="1:2">
-      <c r="A359" s="3"/>
-      <c r="B359" s="3"/>
+      <c r="A359" s="2"/>
+      <c r="B359" s="2"/>
     </row>
     <row r="360" ht="25" customHeight="1" spans="1:2">
-      <c r="A360" s="3"/>
-      <c r="B360" s="3"/>
+      <c r="A360" s="2"/>
+      <c r="B360" s="2"/>
     </row>
     <row r="361" ht="25" customHeight="1" spans="1:2">
-      <c r="A361" s="3"/>
-      <c r="B361" s="3"/>
+      <c r="A361" s="2"/>
+      <c r="B361" s="2"/>
     </row>
     <row r="362" ht="25" customHeight="1" spans="1:2">
-      <c r="A362" s="3"/>
-      <c r="B362" s="3"/>
+      <c r="A362" s="2"/>
+      <c r="B362" s="2"/>
     </row>
     <row r="363" ht="25" customHeight="1" spans="1:2">
-      <c r="A363" s="3"/>
-      <c r="B363" s="3"/>
+      <c r="A363" s="2"/>
+      <c r="B363" s="2"/>
     </row>
     <row r="364" ht="25" customHeight="1" spans="1:2">
-      <c r="A364" s="3"/>
-      <c r="B364" s="3"/>
+      <c r="A364" s="2"/>
+      <c r="B364" s="2"/>
     </row>
     <row r="365" ht="25" customHeight="1" spans="1:2">
-      <c r="A365" s="3"/>
-      <c r="B365" s="3"/>
+      <c r="A365" s="2"/>
+      <c r="B365" s="2"/>
     </row>
     <row r="366" ht="25" customHeight="1" spans="1:2">
-      <c r="A366" s="3"/>
-      <c r="B366" s="3"/>
+      <c r="A366" s="2"/>
+      <c r="B366" s="2"/>
     </row>
     <row r="367" ht="25" customHeight="1" spans="1:2">
-      <c r="A367" s="3"/>
-      <c r="B367" s="3"/>
+      <c r="A367" s="2"/>
+      <c r="B367" s="2"/>
     </row>
     <row r="368" ht="25" customHeight="1" spans="1:2">
-      <c r="A368" s="3"/>
-      <c r="B368" s="3"/>
+      <c r="A368" s="2"/>
+      <c r="B368" s="2"/>
     </row>
     <row r="369" ht="25" customHeight="1" spans="1:2">
-      <c r="A369" s="3"/>
-      <c r="B369" s="3"/>
+      <c r="A369" s="2"/>
+      <c r="B369" s="2"/>
     </row>
     <row r="370" ht="25" customHeight="1" spans="1:2">
-      <c r="A370" s="3"/>
-      <c r="B370" s="3"/>
+      <c r="A370" s="2"/>
+      <c r="B370" s="2"/>
     </row>
     <row r="371" ht="25" customHeight="1" spans="1:2">
-      <c r="A371" s="3"/>
-      <c r="B371" s="3"/>
+      <c r="A371" s="2"/>
+      <c r="B371" s="2"/>
     </row>
     <row r="372" ht="25" customHeight="1" spans="1:2">
-      <c r="A372" s="3"/>
-      <c r="B372" s="3"/>
+      <c r="A372" s="2"/>
+      <c r="B372" s="2"/>
     </row>
     <row r="373" ht="25" customHeight="1" spans="1:2">
-      <c r="A373" s="3"/>
-      <c r="B373" s="3"/>
+      <c r="A373" s="2"/>
+      <c r="B373" s="2"/>
     </row>
     <row r="374" ht="25" customHeight="1" spans="1:2">
-      <c r="A374" s="3"/>
-      <c r="B374" s="3"/>
+      <c r="A374" s="2"/>
+      <c r="B374" s="2"/>
     </row>
     <row r="375" ht="25" customHeight="1" spans="1:2">
-      <c r="A375" s="3"/>
-      <c r="B375" s="3"/>
+      <c r="A375" s="2"/>
+      <c r="B375" s="2"/>
     </row>
     <row r="376" ht="25" customHeight="1" spans="1:2">
-      <c r="A376" s="3"/>
-      <c r="B376" s="3"/>
+      <c r="A376" s="2"/>
+      <c r="B376" s="2"/>
     </row>
     <row r="377" ht="25" customHeight="1" spans="1:2">
-      <c r="A377" s="3"/>
-      <c r="B377" s="3"/>
+      <c r="A377" s="2"/>
+      <c r="B377" s="2"/>
     </row>
     <row r="378" ht="25" customHeight="1" spans="1:2">
-      <c r="A378" s="3"/>
-      <c r="B378" s="3"/>
+      <c r="A378" s="2"/>
+      <c r="B378" s="2"/>
     </row>
     <row r="379" ht="25" customHeight="1" spans="1:2">
-      <c r="A379" s="3"/>
-      <c r="B379" s="3"/>
+      <c r="A379" s="2"/>
+      <c r="B379" s="2"/>
     </row>
     <row r="380" ht="25" customHeight="1" spans="1:2">
-      <c r="A380" s="3"/>
-      <c r="B380" s="3"/>
+      <c r="A380" s="2"/>
+      <c r="B380" s="2"/>
     </row>
     <row r="381" ht="25" customHeight="1" spans="1:2">
-      <c r="A381" s="3"/>
-      <c r="B381" s="3"/>
+      <c r="A381" s="2"/>
+      <c r="B381" s="2"/>
     </row>
     <row r="382" ht="25" customHeight="1" spans="1:2">
-      <c r="A382" s="3"/>
-      <c r="B382" s="3"/>
+      <c r="A382" s="2"/>
+      <c r="B382" s="2"/>
     </row>
     <row r="383" ht="25" customHeight="1" spans="1:2">
-      <c r="A383" s="3"/>
-      <c r="B383" s="3"/>
+      <c r="A383" s="2"/>
+      <c r="B383" s="2"/>
     </row>
     <row r="384" ht="25" customHeight="1" spans="1:2">
-      <c r="A384" s="3"/>
-      <c r="B384" s="3"/>
+      <c r="A384" s="2"/>
+      <c r="B384" s="2"/>
     </row>
     <row r="385" ht="25" customHeight="1" spans="1:2">
-      <c r="A385" s="3"/>
-      <c r="B385" s="3"/>
+      <c r="A385" s="2"/>
+      <c r="B385" s="2"/>
     </row>
     <row r="386" ht="25" customHeight="1" spans="1:2">
-      <c r="A386" s="3"/>
-      <c r="B386" s="3"/>
+      <c r="A386" s="2"/>
+      <c r="B386" s="2"/>
     </row>
     <row r="387" ht="25" customHeight="1" spans="1:2">
-      <c r="A387" s="3"/>
-      <c r="B387" s="3"/>
+      <c r="A387" s="2"/>
+      <c r="B387" s="2"/>
     </row>
     <row r="388" ht="25" customHeight="1" spans="1:2">
-      <c r="A388" s="3"/>
-      <c r="B388" s="3"/>
+      <c r="A388" s="2"/>
+      <c r="B388" s="2"/>
     </row>
     <row r="389" ht="25" customHeight="1" spans="1:2">
-      <c r="A389" s="3"/>
-      <c r="B389" s="3"/>
+      <c r="A389" s="2"/>
+      <c r="B389" s="2"/>
     </row>
     <row r="390" ht="25" customHeight="1" spans="1:2">
-      <c r="A390" s="3"/>
-      <c r="B390" s="3"/>
+      <c r="A390" s="2"/>
+      <c r="B390" s="2"/>
     </row>
     <row r="391" ht="25" customHeight="1" spans="1:2">
-      <c r="A391" s="3"/>
-      <c r="B391" s="3"/>
+      <c r="A391" s="2"/>
+      <c r="B391" s="2"/>
     </row>
     <row r="392" ht="25" customHeight="1" spans="1:2">
-      <c r="A392" s="3"/>
-      <c r="B392" s="3"/>
+      <c r="A392" s="2"/>
+      <c r="B392" s="2"/>
     </row>
     <row r="393" ht="25" customHeight="1" spans="1:2">
-      <c r="A393" s="3"/>
-      <c r="B393" s="3"/>
+      <c r="A393" s="2"/>
+      <c r="B393" s="2"/>
     </row>
     <row r="394" ht="25" customHeight="1" spans="1:2">
-      <c r="A394" s="3"/>
-      <c r="B394" s="3"/>
+      <c r="A394" s="2"/>
+      <c r="B394" s="2"/>
     </row>
     <row r="395" ht="25" customHeight="1" spans="1:2">
-      <c r="A395" s="3"/>
-      <c r="B395" s="3"/>
+      <c r="A395" s="2"/>
+      <c r="B395" s="2"/>
     </row>
     <row r="396" ht="25" customHeight="1" spans="1:2">
-      <c r="A396" s="3"/>
-      <c r="B396" s="3"/>
+      <c r="A396" s="2"/>
+      <c r="B396" s="2"/>
     </row>
     <row r="397" ht="25" customHeight="1" spans="1:2">
-      <c r="A397" s="3"/>
-      <c r="B397" s="3"/>
+      <c r="A397" s="2"/>
+      <c r="B397" s="2"/>
     </row>
     <row r="398" ht="25" customHeight="1" spans="1:2">
-      <c r="A398" s="3"/>
-      <c r="B398" s="3"/>
+      <c r="A398" s="2"/>
+      <c r="B398" s="2"/>
     </row>
     <row r="399" ht="25" customHeight="1" spans="1:2">
-      <c r="A399" s="3"/>
-      <c r="B399" s="3"/>
+      <c r="A399" s="2"/>
+      <c r="B399" s="2"/>
     </row>
     <row r="400" ht="25" customHeight="1" spans="1:2">
-      <c r="A400" s="3"/>
-      <c r="B400" s="3"/>
+      <c r="A400" s="2"/>
+      <c r="B400" s="2"/>
     </row>
     <row r="401" ht="25" customHeight="1" spans="1:2">
-      <c r="A401" s="3"/>
-      <c r="B401" s="3"/>
+      <c r="A401" s="2"/>
+      <c r="B401" s="2"/>
     </row>
     <row r="402" ht="25" customHeight="1" spans="1:2">
-      <c r="A402" s="3"/>
-      <c r="B402" s="3"/>
+      <c r="A402" s="2"/>
+      <c r="B402" s="2"/>
     </row>
     <row r="403" ht="25" customHeight="1" spans="1:2">
-      <c r="A403" s="3"/>
-      <c r="B403" s="3"/>
+      <c r="A403" s="2"/>
+      <c r="B403" s="2"/>
     </row>
     <row r="404" ht="25" customHeight="1" spans="1:2">
-      <c r="A404" s="3"/>
-      <c r="B404" s="3"/>
+      <c r="A404" s="2"/>
+      <c r="B404" s="2"/>
     </row>
     <row r="405" ht="25" customHeight="1" spans="1:2">
-      <c r="A405" s="3"/>
-      <c r="B405" s="3"/>
+      <c r="A405" s="2"/>
+      <c r="B405" s="2"/>
     </row>
     <row r="406" ht="25" customHeight="1" spans="1:2">
-      <c r="A406" s="3"/>
-      <c r="B406" s="3"/>
+      <c r="A406" s="2"/>
+      <c r="B406" s="2"/>
     </row>
     <row r="407" ht="25" customHeight="1" spans="1:2">
-      <c r="A407" s="3"/>
-      <c r="B407" s="3"/>
+      <c r="A407" s="2"/>
+      <c r="B407" s="2"/>
     </row>
     <row r="408" ht="25" customHeight="1" spans="1:2">
-      <c r="A408" s="3"/>
-      <c r="B408" s="3"/>
+      <c r="A408" s="2"/>
+      <c r="B408" s="2"/>
     </row>
     <row r="409" ht="25" customHeight="1" spans="1:2">
-      <c r="A409" s="3"/>
-      <c r="B409" s="3"/>
+      <c r="A409" s="2"/>
+      <c r="B409" s="2"/>
     </row>
     <row r="410" ht="25" customHeight="1" spans="1:2">
-      <c r="A410" s="3"/>
-      <c r="B410" s="3"/>
+      <c r="A410" s="2"/>
+      <c r="B410" s="2"/>
     </row>
     <row r="411" ht="25" customHeight="1" spans="1:2">
-      <c r="A411" s="3"/>
-      <c r="B411" s="3"/>
+      <c r="A411" s="2"/>
+      <c r="B411" s="2"/>
     </row>
     <row r="412" ht="25" customHeight="1" spans="1:2">
-      <c r="A412" s="3"/>
-      <c r="B412" s="3"/>
+      <c r="A412" s="2"/>
+      <c r="B412" s="2"/>
     </row>
     <row r="413" ht="25" customHeight="1" spans="1:2">
-      <c r="A413" s="3"/>
-      <c r="B413" s="3"/>
+      <c r="A413" s="2"/>
+      <c r="B413" s="2"/>
     </row>
     <row r="414" ht="25" customHeight="1" spans="1:2">
-      <c r="A414" s="3"/>
-      <c r="B414" s="3"/>
+      <c r="A414" s="2"/>
+      <c r="B414" s="2"/>
     </row>
     <row r="415" ht="25" customHeight="1" spans="1:2">
-      <c r="A415" s="3"/>
-      <c r="B415" s="3"/>
+      <c r="A415" s="2"/>
+      <c r="B415" s="2"/>
     </row>
     <row r="416" ht="25" customHeight="1" spans="1:2">
-      <c r="A416" s="3"/>
-      <c r="B416" s="3"/>
+      <c r="A416" s="2"/>
+      <c r="B416" s="2"/>
     </row>
     <row r="417" ht="25" customHeight="1" spans="1:2">
-      <c r="A417" s="3"/>
-      <c r="B417" s="3"/>
+      <c r="A417" s="2"/>
+      <c r="B417" s="2"/>
     </row>
     <row r="418" ht="25" customHeight="1" spans="1:2">
-      <c r="A418" s="3"/>
-      <c r="B418" s="3"/>
+      <c r="A418" s="2"/>
+      <c r="B418" s="2"/>
     </row>
     <row r="419" ht="25" customHeight="1" spans="1:2">
-      <c r="A419" s="3"/>
-      <c r="B419" s="3"/>
+      <c r="A419" s="2"/>
+      <c r="B419" s="2"/>
     </row>
     <row r="420" ht="25" customHeight="1" spans="1:2">
-      <c r="A420" s="3"/>
-      <c r="B420" s="3"/>
+      <c r="A420" s="2"/>
+      <c r="B420" s="2"/>
     </row>
     <row r="421" ht="25" customHeight="1" spans="1:2">
-      <c r="A421" s="3"/>
-      <c r="B421" s="3"/>
+      <c r="A421" s="2"/>
+      <c r="B421" s="2"/>
     </row>
     <row r="422" ht="25" customHeight="1" spans="1:2">
-      <c r="A422" s="3"/>
-      <c r="B422" s="3"/>
+      <c r="A422" s="2"/>
+      <c r="B422" s="2"/>
     </row>
     <row r="423" ht="25" customHeight="1" spans="1:2">
-      <c r="A423" s="3"/>
-      <c r="B423" s="3"/>
+      <c r="A423" s="2"/>
+      <c r="B423" s="2"/>
     </row>
     <row r="424" ht="25" customHeight="1" spans="1:2">
-      <c r="A424" s="3"/>
-      <c r="B424" s="3"/>
+      <c r="A424" s="2"/>
+      <c r="B424" s="2"/>
     </row>
     <row r="425" ht="25" customHeight="1" spans="1:2">
-      <c r="A425" s="3"/>
-      <c r="B425" s="3"/>
+      <c r="A425" s="2"/>
+      <c r="B425" s="2"/>
     </row>
     <row r="426" ht="25" customHeight="1" spans="1:2">
-      <c r="A426" s="3"/>
-      <c r="B426" s="3"/>
+      <c r="A426" s="2"/>
+      <c r="B426" s="2"/>
     </row>
     <row r="427" ht="25" customHeight="1" spans="1:2">
-      <c r="A427" s="3"/>
-      <c r="B427" s="3"/>
+      <c r="A427" s="2"/>
+      <c r="B427" s="2"/>
     </row>
     <row r="428" ht="25" customHeight="1" spans="1:2">
-      <c r="A428" s="3"/>
-      <c r="B428" s="3"/>
+      <c r="A428" s="2"/>
+      <c r="B428" s="2"/>
     </row>
     <row r="429" ht="25" customHeight="1" spans="1:2">
-      <c r="A429" s="3"/>
-      <c r="B429" s="3"/>
+      <c r="A429" s="2"/>
+      <c r="B429" s="2"/>
     </row>
     <row r="430" ht="25" customHeight="1" spans="1:2">
-      <c r="A430" s="3"/>
-      <c r="B430" s="3"/>
+      <c r="A430" s="2"/>
+      <c r="B430" s="2"/>
     </row>
     <row r="431" ht="25" customHeight="1" spans="1:2">
-      <c r="A431" s="3"/>
-      <c r="B431" s="3"/>
+      <c r="A431" s="2"/>
+      <c r="B431" s="2"/>
     </row>
     <row r="432" ht="25" customHeight="1" spans="1:2">
-      <c r="A432" s="3"/>
-      <c r="B432" s="3"/>
+      <c r="A432" s="2"/>
+      <c r="B432" s="2"/>
     </row>
     <row r="433" ht="25" customHeight="1" spans="1:2">
-      <c r="A433" s="3"/>
-      <c r="B433" s="3"/>
+      <c r="A433" s="2"/>
+      <c r="B433" s="2"/>
     </row>
     <row r="434" ht="25" customHeight="1" spans="1:2">
-      <c r="A434" s="3"/>
-      <c r="B434" s="3"/>
+      <c r="A434" s="2"/>
+      <c r="B434" s="2"/>
     </row>
     <row r="435" ht="25" customHeight="1" spans="1:2">
-      <c r="A435" s="3"/>
-      <c r="B435" s="3"/>
+      <c r="A435" s="2"/>
+      <c r="B435" s="2"/>
     </row>
     <row r="436" ht="25" customHeight="1" spans="1:2">
-      <c r="A436" s="3"/>
-      <c r="B436" s="3"/>
+      <c r="A436" s="2"/>
+      <c r="B436" s="2"/>
     </row>
     <row r="437" ht="25" customHeight="1" spans="1:2">
-      <c r="A437" s="3"/>
-      <c r="B437" s="3"/>
+      <c r="A437" s="2"/>
+      <c r="B437" s="2"/>
     </row>
     <row r="438" ht="25" customHeight="1" spans="1:2">
-      <c r="A438" s="3"/>
-      <c r="B438" s="3"/>
+      <c r="A438" s="2"/>
+      <c r="B438" s="2"/>
     </row>
     <row r="439" ht="25" customHeight="1" spans="1:2">
-      <c r="A439" s="3"/>
-      <c r="B439" s="3"/>
+      <c r="A439" s="2"/>
+      <c r="B439" s="2"/>
     </row>
     <row r="440" ht="25" customHeight="1" spans="1:2">
-      <c r="A440" s="3"/>
-      <c r="B440" s="3"/>
+      <c r="A440" s="2"/>
+      <c r="B440" s="2"/>
     </row>
     <row r="441" ht="25" customHeight="1" spans="1:2">
-      <c r="A441" s="3"/>
-      <c r="B441" s="3"/>
+      <c r="A441" s="2"/>
+      <c r="B441" s="2"/>
     </row>
     <row r="442" ht="25" customHeight="1" spans="1:2">
-      <c r="A442" s="3"/>
-      <c r="B442" s="3"/>
+      <c r="A442" s="2"/>
+      <c r="B442" s="2"/>
     </row>
     <row r="443" ht="25" customHeight="1" spans="1:2">
-      <c r="A443" s="3"/>
-      <c r="B443" s="3"/>
+      <c r="A443" s="2"/>
+      <c r="B443" s="2"/>
     </row>
     <row r="444" ht="25" customHeight="1" spans="1:2">
-      <c r="A444" s="3"/>
-      <c r="B444" s="3"/>
+      <c r="A444" s="2"/>
+      <c r="B444" s="2"/>
     </row>
     <row r="445" ht="25" customHeight="1" spans="1:2">
-      <c r="A445" s="3"/>
-      <c r="B445" s="3"/>
+      <c r="A445" s="2"/>
+      <c r="B445" s="2"/>
     </row>
     <row r="446" ht="25" customHeight="1" spans="1:2">
-      <c r="A446" s="3"/>
-      <c r="B446" s="3"/>
+      <c r="A446" s="2"/>
+      <c r="B446" s="2"/>
     </row>
     <row r="447" ht="25" customHeight="1" spans="1:2">
-      <c r="A447" s="3"/>
-      <c r="B447" s="3"/>
+      <c r="A447" s="2"/>
+      <c r="B447" s="2"/>
     </row>
     <row r="448" ht="25" customHeight="1" spans="1:2">
-      <c r="A448" s="3"/>
-      <c r="B448" s="3"/>
+      <c r="A448" s="2"/>
+      <c r="B448" s="2"/>
     </row>
     <row r="449" ht="25" customHeight="1" spans="1:2">
-      <c r="A449" s="3"/>
-      <c r="B449" s="3"/>
+      <c r="A449" s="2"/>
+      <c r="B449" s="2"/>
     </row>
     <row r="450" ht="25" customHeight="1" spans="1:2">
-      <c r="A450" s="3"/>
-      <c r="B450" s="3"/>
+      <c r="A450" s="2"/>
+      <c r="B450" s="2"/>
     </row>
     <row r="451" ht="25" customHeight="1" spans="1:2">
-      <c r="A451" s="3"/>
-      <c r="B451" s="3"/>
+      <c r="A451" s="2"/>
+      <c r="B451" s="2"/>
     </row>
     <row r="452" ht="25" customHeight="1" spans="1:2">
-      <c r="A452" s="3"/>
-      <c r="B452" s="3"/>
+      <c r="A452" s="2"/>
+      <c r="B452" s="2"/>
     </row>
     <row r="453" ht="25" customHeight="1" spans="1:2">
-      <c r="A453" s="3"/>
-      <c r="B453" s="3"/>
+      <c r="A453" s="2"/>
+      <c r="B453" s="2"/>
     </row>
     <row r="454" ht="25" customHeight="1" spans="1:2">
-      <c r="A454" s="3"/>
-      <c r="B454" s="3"/>
+      <c r="A454" s="2"/>
+      <c r="B454" s="2"/>
     </row>
     <row r="455" ht="25" customHeight="1" spans="1:2">
-      <c r="A455" s="3"/>
-      <c r="B455" s="3"/>
+      <c r="A455" s="2"/>
+      <c r="B455" s="2"/>
     </row>
     <row r="456" ht="25" customHeight="1" spans="1:2">
-      <c r="A456" s="3"/>
-      <c r="B456" s="3"/>
+      <c r="A456" s="2"/>
+      <c r="B456" s="2"/>
     </row>
     <row r="457" ht="25" customHeight="1" spans="1:2">
-      <c r="A457" s="3"/>
-      <c r="B457" s="3"/>
+      <c r="A457" s="2"/>
+      <c r="B457" s="2"/>
     </row>
     <row r="458" ht="25" customHeight="1" spans="1:2">
-      <c r="A458" s="3"/>
-      <c r="B458" s="3"/>
+      <c r="A458" s="2"/>
+      <c r="B458" s="2"/>
     </row>
     <row r="459" ht="25" customHeight="1" spans="1:2">
-      <c r="A459" s="3"/>
-      <c r="B459" s="3"/>
+      <c r="A459" s="2"/>
+      <c r="B459" s="2"/>
     </row>
     <row r="460" ht="25" customHeight="1" spans="1:2">
-      <c r="A460" s="3"/>
-      <c r="B460" s="3"/>
+      <c r="A460" s="2"/>
+      <c r="B460" s="2"/>
     </row>
     <row r="461" ht="25" customHeight="1" spans="1:2">
-      <c r="A461" s="3"/>
-      <c r="B461" s="3"/>
+      <c r="A461" s="2"/>
+      <c r="B461" s="2"/>
     </row>
     <row r="462" ht="25" customHeight="1" spans="1:2">
-      <c r="A462" s="3"/>
-      <c r="B462" s="3"/>
+      <c r="A462" s="2"/>
+      <c r="B462" s="2"/>
     </row>
     <row r="463" ht="25" customHeight="1" spans="1:2">
-      <c r="A463" s="3"/>
-      <c r="B463" s="3"/>
+      <c r="A463" s="2"/>
+      <c r="B463" s="2"/>
     </row>
     <row r="464" ht="25" customHeight="1" spans="1:2">
-      <c r="A464" s="3"/>
-      <c r="B464" s="3"/>
+      <c r="A464" s="2"/>
+      <c r="B464" s="2"/>
     </row>
     <row r="465" ht="25" customHeight="1" spans="1:2">
-      <c r="A465" s="3"/>
-      <c r="B465" s="3"/>
+      <c r="A465" s="2"/>
+      <c r="B465" s="2"/>
     </row>
     <row r="466" ht="25" customHeight="1" spans="1:2">
-      <c r="A466" s="3"/>
-      <c r="B466" s="3"/>
+      <c r="A466" s="2"/>
+      <c r="B466" s="2"/>
     </row>
     <row r="467" ht="25" customHeight="1" spans="1:2">
-      <c r="A467" s="3"/>
-      <c r="B467" s="3"/>
+      <c r="A467" s="2"/>
+      <c r="B467" s="2"/>
     </row>
     <row r="468" ht="25" customHeight="1" spans="1:2">
-      <c r="A468" s="3"/>
-      <c r="B468" s="3"/>
+      <c r="A468" s="2"/>
+      <c r="B468" s="2"/>
     </row>
     <row r="469" ht="25" customHeight="1" spans="1:2">
-      <c r="A469" s="3"/>
-      <c r="B469" s="3"/>
+      <c r="A469" s="2"/>
+      <c r="B469" s="2"/>
     </row>
     <row r="470" ht="25" customHeight="1" spans="1:2">
-      <c r="A470" s="3"/>
-      <c r="B470" s="3"/>
+      <c r="A470" s="2"/>
+      <c r="B470" s="2"/>
     </row>
     <row r="471" ht="25" customHeight="1" spans="1:2">
-      <c r="A471" s="3"/>
-      <c r="B471" s="3"/>
+      <c r="A471" s="2"/>
+      <c r="B471" s="2"/>
     </row>
     <row r="472" ht="25" customHeight="1" spans="1:2">
-      <c r="A472" s="3"/>
-      <c r="B472" s="3"/>
+      <c r="A472" s="2"/>
+      <c r="B472" s="2"/>
     </row>
     <row r="473" ht="25" customHeight="1" spans="1:2">
-      <c r="A473" s="3"/>
-      <c r="B473" s="3"/>
+      <c r="A473" s="2"/>
+      <c r="B473" s="2"/>
     </row>
     <row r="474" ht="25" customHeight="1" spans="1:2">
-      <c r="A474" s="3"/>
-      <c r="B474" s="3"/>
+      <c r="A474" s="2"/>
+      <c r="B474" s="2"/>
     </row>
     <row r="475" ht="25" customHeight="1" spans="1:2">
-      <c r="A475" s="3"/>
-      <c r="B475" s="3"/>
+      <c r="A475" s="2"/>
+      <c r="B475" s="2"/>
     </row>
     <row r="476" ht="25" customHeight="1" spans="1:2">
-      <c r="A476" s="3"/>
-      <c r="B476" s="3"/>
+      <c r="A476" s="2"/>
+      <c r="B476" s="2"/>
     </row>
     <row r="477" ht="25" customHeight="1" spans="1:2">
-      <c r="A477" s="3"/>
-      <c r="B477" s="3"/>
+      <c r="A477" s="2"/>
+      <c r="B477" s="2"/>
     </row>
     <row r="478" ht="25" customHeight="1" spans="1:2">
-      <c r="A478" s="3"/>
-      <c r="B478" s="3"/>
+      <c r="A478" s="2"/>
+      <c r="B478" s="2"/>
     </row>
     <row r="479" ht="25" customHeight="1" spans="1:2">
-      <c r="A479" s="3"/>
-      <c r="B479" s="3"/>
+      <c r="A479" s="2"/>
+      <c r="B479" s="2"/>
     </row>
     <row r="480" ht="25" customHeight="1" spans="1:2">
-      <c r="A480" s="3"/>
-      <c r="B480" s="3"/>
+      <c r="A480" s="2"/>
+      <c r="B480" s="2"/>
     </row>
     <row r="481" ht="25" customHeight="1" spans="1:2">
-      <c r="A481" s="3"/>
-      <c r="B481" s="3"/>
+      <c r="A481" s="2"/>
+      <c r="B481" s="2"/>
     </row>
     <row r="482" ht="25" customHeight="1" spans="1:2">
-      <c r="A482" s="3"/>
-      <c r="B482" s="3"/>
+      <c r="A482" s="2"/>
+      <c r="B482" s="2"/>
     </row>
     <row r="483" ht="25" customHeight="1" spans="1:2">
-      <c r="A483" s="3"/>
-      <c r="B483" s="3"/>
+      <c r="A483" s="2"/>
+      <c r="B483" s="2"/>
     </row>
     <row r="484" ht="25" customHeight="1" spans="1:2">
-      <c r="A484" s="3"/>
-      <c r="B484" s="3"/>
+      <c r="A484" s="2"/>
+      <c r="B484" s="2"/>
     </row>
     <row r="485" ht="25" customHeight="1" spans="1:2">
-      <c r="A485" s="3"/>
-      <c r="B485" s="3"/>
+      <c r="A485" s="2"/>
+      <c r="B485" s="2"/>
     </row>
     <row r="486" ht="25" customHeight="1" spans="1:2">
-      <c r="A486" s="3"/>
-      <c r="B486" s="3"/>
+      <c r="A486" s="2"/>
+      <c r="B486" s="2"/>
     </row>
     <row r="487" ht="25" customHeight="1" spans="1:2">
-      <c r="A487" s="3"/>
-      <c r="B487" s="3"/>
+      <c r="A487" s="2"/>
+      <c r="B487" s="2"/>
     </row>
     <row r="488" ht="25" customHeight="1" spans="1:2">
-      <c r="A488" s="3"/>
-      <c r="B488" s="3"/>
+      <c r="A488" s="2"/>
+      <c r="B488" s="2"/>
     </row>
     <row r="489" ht="25" customHeight="1" spans="1:2">
-      <c r="A489" s="3"/>
-      <c r="B489" s="3"/>
+      <c r="A489" s="2"/>
+      <c r="B489" s="2"/>
     </row>
     <row r="490" ht="25" customHeight="1" spans="1:2">
-      <c r="A490" s="3"/>
-      <c r="B490" s="3"/>
+      <c r="A490" s="2"/>
+      <c r="B490" s="2"/>
     </row>
     <row r="491" ht="25" customHeight="1" spans="1:2">
-      <c r="A491" s="3"/>
-      <c r="B491" s="3"/>
+      <c r="A491" s="2"/>
+      <c r="B491" s="2"/>
     </row>
     <row r="492" ht="25" customHeight="1" spans="1:2">
-      <c r="A492" s="3"/>
-      <c r="B492" s="3"/>
+      <c r="A492" s="2"/>
+      <c r="B492" s="2"/>
     </row>
     <row r="493" ht="25" customHeight="1" spans="1:2">
-      <c r="A493" s="3"/>
-      <c r="B493" s="3"/>
+      <c r="A493" s="2"/>
+      <c r="B493" s="2"/>
     </row>
     <row r="494" ht="25" customHeight="1" spans="1:2">
-      <c r="A494" s="3"/>
-      <c r="B494" s="3"/>
+      <c r="A494" s="2"/>
+      <c r="B494" s="2"/>
     </row>
     <row r="495" ht="25" customHeight="1" spans="1:2">
-      <c r="A495" s="3"/>
-      <c r="B495" s="3"/>
+      <c r="A495" s="2"/>
+      <c r="B495" s="2"/>
     </row>
     <row r="496" ht="25" customHeight="1" spans="1:2">
-      <c r="A496" s="3"/>
-      <c r="B496" s="3"/>
+      <c r="A496" s="2"/>
+      <c r="B496" s="2"/>
     </row>
     <row r="497" ht="25" customHeight="1" spans="1:2">
-      <c r="A497" s="3"/>
-      <c r="B497" s="3"/>
+      <c r="A497" s="2"/>
+      <c r="B497" s="2"/>
     </row>
     <row r="498" ht="25" customHeight="1" spans="1:2">
-      <c r="A498" s="3"/>
-      <c r="B498" s="3"/>
+      <c r="A498" s="2"/>
+      <c r="B498" s="2"/>
     </row>
     <row r="499" ht="25" customHeight="1" spans="1:2">
-      <c r="A499" s="3"/>
-      <c r="B499" s="3"/>
+      <c r="A499" s="2"/>
+      <c r="B499" s="2"/>
     </row>
     <row r="500" ht="25" customHeight="1" spans="1:2">
-      <c r="A500" s="3"/>
-      <c r="B500" s="3"/>
+      <c r="A500" s="2"/>
+      <c r="B500" s="2"/>
     </row>
     <row r="501" ht="25" customHeight="1" spans="1:2">
-      <c r="A501" s="3"/>
-      <c r="B501" s="3"/>
+      <c r="A501" s="2"/>
+      <c r="B501" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="637">
   <si>
     <t>bangla</t>
   </si>
@@ -1869,7 +1869,127 @@
     <t>আমাকে আরেকটু শুটকি দাও</t>
   </si>
   <si>
-    <t>আঁরে আরেক্কানা শুটকি দও</t>
+    <t>আঁরে আরেক্কানা উনি দও</t>
+  </si>
+  <si>
+    <t>সকালে দেরি করে উঠা ঠিক না</t>
+  </si>
+  <si>
+    <t>বেইন্নে দেরি গরি উডন ঠিক ন</t>
+  </si>
+  <si>
+    <t>রাতে দেরি করে ঘুমানো উচিত না</t>
+  </si>
+  <si>
+    <t>রাতিয়ে দেরি গরি ঘুম যন উচিত ন</t>
+  </si>
+  <si>
+    <t>আমি প্রতিদিন চেষ্টা করি রাতে জলদি ঘুমানোর, কিন্তু কেমনে জানি দেরি হয়ে যায়</t>
+  </si>
+  <si>
+    <t>আঁই পইত্তোদিন চেষ্টা গরি রাতিয়ে জলদি ঘুম যাইবের লাই, কিন্তু কেনে জানি দেরি অই যায়</t>
+  </si>
+  <si>
+    <t>তোমার স্বভাব আমার একদম ভাল লাগছে না</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হাইচ্চুত আত্তুন এব্বেরে গম ন লার</t>
+  </si>
+  <si>
+    <t>তুর বাবা মাঠে গেছে কাজ করতে</t>
+  </si>
+  <si>
+    <t>তুর বাপ মাডোত গেইয়্যি হাম গইত্তো</t>
+  </si>
+  <si>
+    <t>তুর ভাইকে বলিস আসার সময় বাজার থেকে চিংড়ি শুটকি নিয়ে আসার জন্য</t>
+  </si>
+  <si>
+    <t>তুর বদ্দারে হইস আইবের সমোত বাজারোত্তন ইছে উনি লই আইবের লাই</t>
+  </si>
+  <si>
+    <t>তোর বাবাকে মাঠ থেকে ডেকে নিয়ে আয়</t>
+  </si>
+  <si>
+    <t>তোর বাপোরে মাডোত্তন ডাহি আন</t>
+  </si>
+  <si>
+    <t>আমি ভাত দিচ্ছি, তুমি মুখ ধুয়ে আসো</t>
+  </si>
+  <si>
+    <t>আঁই ভাত দির, তুঁই মুখ ধুয় আইয়্যু</t>
+  </si>
+  <si>
+    <t>তুমি আজকে জলদি চলে এলে যে?</t>
+  </si>
+  <si>
+    <t>তুঁই আজিয়ে হারা চলি আইস্যু দে?</t>
+  </si>
+  <si>
+    <t>আমার রান্না এখনো শেষ হয় নায়, আরেকটু অপেক্ষা কর</t>
+  </si>
+  <si>
+    <t>আঁর রান্না এহনো শেষ ন অই, আরেক্কানা অপেক্ষা গরো</t>
+  </si>
+  <si>
+    <t>তোমাকে কতক্ষণ ধরে কল দিচ্ছি, ফোন উঠাচ্ছো না কেন?</t>
+  </si>
+  <si>
+    <t>তোয়ারে হতক্ষণ ধরি কল দির, ফোন ন উডার কা?</t>
+  </si>
+  <si>
+    <t>আমাদের বাড়িতে এত এত মেহমান আসে, তাদের খাওয়াতে খাওয়াতে সব চাওল শেষ হয়ে যায়</t>
+  </si>
+  <si>
+    <t>আঁরো বারিত এত এত মেমান আইয়্যি, ইতারারে হাবাইতে হাবাইতে বিয়াক চইল শেষ অই যায়</t>
+  </si>
+  <si>
+    <t>সেজন্য এক বস্তা চাল নিয়ে আসছি</t>
+  </si>
+  <si>
+    <t>এতেল্লে এক বস্তা চইল লই আইস্যি</t>
+  </si>
+  <si>
+    <t>বাজার থেকে পুঁই শাক নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>বাজারোত্তন পিয়েশ শাক লই আইস</t>
+  </si>
+  <si>
+    <t>ডাক্তার বলেছে মাছ আর বেশি বেশি শাক সবজি খেতে</t>
+  </si>
+  <si>
+    <t>ডাক্তার হইয়্যিদে মাছ আর বেশি বেশি শাক সবজি হাইতো</t>
+  </si>
+  <si>
+    <t>সারাদিন ফোন টিপা ছাড়া আর কোন কাজ আছে?</t>
+  </si>
+  <si>
+    <t>সারাদিন ফোন টিপন ছাড়া আর হনো হাম আছে?</t>
+  </si>
+  <si>
+    <t>আজকের দিনটি এমনি এমনি চলে গেল</t>
+  </si>
+  <si>
+    <t>আজিয়ের দিন ইয়েন এনে এনে চলি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>পরীক্ষার আর বেশি দিন বাকি নাই, কিন্তু এখনো কোনো পড়ালেখা করছিনা</t>
+  </si>
+  <si>
+    <t>পরীক্ষের আর বেশি দিন বাকি নেই, কিন্তু এহনো হনো পরালেহা ন গরির</t>
+  </si>
+  <si>
+    <t>জারিফকে বলো তাড়াতাড়ি বাজারে যেতে</t>
+  </si>
+  <si>
+    <t>জারিফ উরে হ তারাতারি বাজারোত যাইতো</t>
+  </si>
+  <si>
+    <t>মুদির দোকানের সামনে গিয়ে একটা কল দিয়েন</t>
+  </si>
+  <si>
+    <t>মুদির দোয়ানোর সামনে যায় রে উজ্ঞো কল দিয়্যুন</t>
   </si>
 </sst>
 </file>
@@ -5455,84 +5575,164 @@
       </c>
     </row>
     <row r="302" ht="25" customHeight="1" spans="1:2">
-      <c r="A302" s="2"/>
-      <c r="B302" s="2"/>
+      <c r="A302" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="303" ht="25" customHeight="1" spans="1:2">
-      <c r="A303" s="2"/>
-      <c r="B303" s="2"/>
+      <c r="A303" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="304" ht="25" customHeight="1" spans="1:2">
-      <c r="A304" s="2"/>
-      <c r="B304" s="2"/>
+      <c r="A304" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="305" ht="25" customHeight="1" spans="1:2">
-      <c r="A305" s="2"/>
-      <c r="B305" s="2"/>
+      <c r="A305" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="306" ht="25" customHeight="1" spans="1:2">
-      <c r="A306" s="2"/>
-      <c r="B306" s="2"/>
+      <c r="A306" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="307" ht="25" customHeight="1" spans="1:2">
-      <c r="A307" s="2"/>
-      <c r="B307" s="2"/>
+      <c r="A307" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="308" ht="25" customHeight="1" spans="1:2">
-      <c r="A308" s="2"/>
-      <c r="B308" s="2"/>
+      <c r="A308" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="309" ht="25" customHeight="1" spans="1:2">
-      <c r="A309" s="2"/>
-      <c r="B309" s="2"/>
+      <c r="A309" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="310" ht="25" customHeight="1" spans="1:2">
-      <c r="A310" s="2"/>
-      <c r="B310" s="2"/>
+      <c r="A310" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="311" ht="25" customHeight="1" spans="1:2">
-      <c r="A311" s="2"/>
-      <c r="B311" s="2"/>
+      <c r="A311" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="312" ht="25" customHeight="1" spans="1:2">
-      <c r="A312" s="2"/>
-      <c r="B312" s="2"/>
+      <c r="A312" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="313" ht="25" customHeight="1" spans="1:2">
-      <c r="A313" s="2"/>
-      <c r="B313" s="2"/>
+      <c r="A313" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="314" ht="25" customHeight="1" spans="1:2">
-      <c r="A314" s="2"/>
-      <c r="B314" s="2"/>
+      <c r="A314" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="315" ht="25" customHeight="1" spans="1:2">
-      <c r="A315" s="2"/>
-      <c r="B315" s="2"/>
+      <c r="A315" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="316" ht="25" customHeight="1" spans="1:2">
-      <c r="A316" s="2"/>
-      <c r="B316" s="2"/>
+      <c r="A316" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="317" ht="25" customHeight="1" spans="1:2">
-      <c r="A317" s="2"/>
-      <c r="B317" s="2"/>
+      <c r="A317" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="318" ht="25" customHeight="1" spans="1:2">
-      <c r="A318" s="2"/>
-      <c r="B318" s="2"/>
+      <c r="A318" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="319" ht="25" customHeight="1" spans="1:2">
-      <c r="A319" s="2"/>
-      <c r="B319" s="2"/>
+      <c r="A319" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="320" ht="25" customHeight="1" spans="1:2">
-      <c r="A320" s="2"/>
-      <c r="B320" s="2"/>
+      <c r="A320" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="321" ht="25" customHeight="1" spans="1:2">
-      <c r="A321" s="2"/>
-      <c r="B321" s="2"/>
+      <c r="A321" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="322" ht="25" customHeight="1" spans="1:2">
       <c r="A322" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="757">
   <si>
     <t>bangla</t>
   </si>
@@ -1990,6 +1990,366 @@
   </si>
   <si>
     <t>মুদির দোয়ানোর সামনে যায় রে উজ্ঞো কল দিয়্যুন</t>
+  </si>
+  <si>
+    <t>এগুলো খেয়ো না, এগুলো বেশি ঠাণ্ডা</t>
+  </si>
+  <si>
+    <t>এগিন ন হাইয়্যো, এগিন বেশি ঠাণ্ডা</t>
+  </si>
+  <si>
+    <t>গতকাল বেশি ঠাণ্ডা ছিল বাইরে</t>
+  </si>
+  <si>
+    <t>গত হালিয়ে বেশি ঠাণ্ডা আছিল বাদ্দি</t>
+  </si>
+  <si>
+    <t>আমার এক আত্মীয় আসছে</t>
+  </si>
+  <si>
+    <t>আঁর উজ্ঞো আত্মীয় আইয়্যির</t>
+  </si>
+  <si>
+    <t>আজকে ঘরে মেহমান আসছে তাই স্কুলে যাব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে ঘরোত মেমান আইয়্যির এতেল্লে স্কুলোত যাইতাম নো</t>
+  </si>
+  <si>
+    <t>বাজার থেকে একটা কাঁঠাল নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>বাজারোত্তন উজ্ঞো হাট্টল লই আইয়্যো</t>
+  </si>
+  <si>
+    <t>ভাঙার পর দেখলাম কাঁঠালটি কাঁচা</t>
+  </si>
+  <si>
+    <t>ভাঙিবের পরে দেহিলাম হাট্টল ইবে কেঁছা</t>
+  </si>
+  <si>
+    <t>মাঠে গিয়ে দেখি সেখানে কেও নাই</t>
+  </si>
+  <si>
+    <t>মাডোত যাইরে দেহি এনডে কিয়াই নাই</t>
+  </si>
+  <si>
+    <t>সবাই বাড়িতে চলে গেছে, শুধু আমি একা আছি</t>
+  </si>
+  <si>
+    <t>বিয়াজ্ঞুন বারিত চলি গেইয়্যি, শুধু আঁই এহেল্লে আছি</t>
+  </si>
+  <si>
+    <t>বারান্দায় মেহমান বসে আছে, গিয়ে নাস্তা দিয়ে আসো</t>
+  </si>
+  <si>
+    <t>বারান্দাত মেমান বইঁ থেইক্কি, যায়্যিরে নাস্তা দি আইয়্যো</t>
+  </si>
+  <si>
+    <t>আমি বসে আছি, তুমি কি করো?</t>
+  </si>
+  <si>
+    <t>আঁই বইঁ থেইক্কি, তুঁই কি গরো?</t>
+  </si>
+  <si>
+    <t>বার বার বলি যে বাজার থেকে কিছু নিলে ভালভাবে দেখে নিতে, এখন দোকানদার সব পঁচা আম দিয়ে দিছে তোমাকে</t>
+  </si>
+  <si>
+    <t>বার বার হয়দি বাজারোত্তন কিছু লইলি ভালা গরি চায় লইবের লাই, এহন দোয়ানদার বিয়াক পুঁচা আম দি দিয়ি তোঁয়ারে</t>
+  </si>
+  <si>
+    <t>অনেকদি ধরে ঘরে বসে বসে বিরক্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>বতদিন ধরি ঘরোত বইঁ বইঁ বিরক্ত অই গেই</t>
+  </si>
+  <si>
+    <t>বাইরে কোথাও থেকে ঘুরে আসলে মন ভাল হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>বাইরে হনোমিক্কেত্তুন ঘুরি আইলি মন ভালা অই যাইবো</t>
+  </si>
+  <si>
+    <t>যাওয়ার সময় আমাকে বলিও, আমিও যাব তোমার সাথে</t>
+  </si>
+  <si>
+    <t>যাইবের সমোত আঁরেও হইয়্যো, আঁই ও যাইয়্যুম তোঁয়ার লগে</t>
+  </si>
+  <si>
+    <t>এখন যাব না, আর কিছুদিন পর যাব</t>
+  </si>
+  <si>
+    <t>এহন ন যাইয়্যুম, আর কিছুদিন পর যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমার এখনো অনেক কাজ বাকি</t>
+  </si>
+  <si>
+    <t>আঁর এহনো বত হাম বাকি</t>
+  </si>
+  <si>
+    <t>তুমি আমাকে আগে এক হাজার টাকা হাদিয়া দাও, আমি তোমার কাজ করে দিব</t>
+  </si>
+  <si>
+    <t>তুঁই আঁরে আগে এহাজার টিয়া হাদিয়ে দ, আঁই তোঁয়ার হাম গরি দিয়্যুম</t>
+  </si>
+  <si>
+    <t>বড় ভাই, কাজ হবে তো?</t>
+  </si>
+  <si>
+    <t>বদ্দা, হাম অইবু না?</t>
+  </si>
+  <si>
+    <t>কাজ না হলে টাকা ফেরত দিব</t>
+  </si>
+  <si>
+    <t>হাম ন অইলি টিয়া ফেরত দিয়্যুম</t>
+  </si>
+  <si>
+    <t>কতদিনের মধ্যে কাজ হবে ভাই?</t>
+  </si>
+  <si>
+    <t>হতদিনোর মধ্যে হাম অইবু বদ্দা?</t>
+  </si>
+  <si>
+    <t>আপু, আমি তোমাকে অনেক বিরক্ত করছি</t>
+  </si>
+  <si>
+    <t>আফা, আঁই তোঁয়ারে বত বিরক্ত গরির</t>
+  </si>
+  <si>
+    <t>আমার আপু অনেক ভাল</t>
+  </si>
+  <si>
+    <t>আঁর আফা বত গম</t>
+  </si>
+  <si>
+    <t>আমার আপ আমাকে অনেক সাহায্য করে</t>
+  </si>
+  <si>
+    <t>আঁর আফা আঁরে বত সাহাইয্য গরে</t>
+  </si>
+  <si>
+    <t>আল্লাহ আমার আপুকে একটা সুন্দর জামাই দিক</t>
+  </si>
+  <si>
+    <t>আল্লাহ আঁর আফারে উজ্ঞো সুন্দর জামাই দক</t>
+  </si>
+  <si>
+    <t>আমার মনে হচ্ছে আজকে তোমার মন মেজাজ অনেক ভাল</t>
+  </si>
+  <si>
+    <t>আত্তুন মনে অদ্দে আজিয়ে তোঁয়ার মন মেজাজ বত ভালা</t>
+  </si>
+  <si>
+    <t>আমি একটা কথা বলতে চাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই এক্কান হতা হইতাম চাইদ্দি</t>
+  </si>
+  <si>
+    <t>তোমার এত চিন্তা করতে হবেনা, আমার চিন্তা আমি করব</t>
+  </si>
+  <si>
+    <t>তোঁয়াত্তুন এত চিন্তে গরন পইত্তু ন, আঁর চিন্তে আঁই গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আচ্ছা ঠিক আছে, এসব নিয়ে আমি তোর সাথে তর্ক করতে চায় না</t>
+  </si>
+  <si>
+    <t>আইচ্ছে ঠিক আছে, এগিন লই রে আঁই তোর লগে তর্ক গইত্তাম ন চায়</t>
+  </si>
+  <si>
+    <t>তোর কথা ঠিক, আমি বুঝিনি প্রথমে</t>
+  </si>
+  <si>
+    <t>তোর হতা ঠিক, আঁই নো বুঝিদি পইল্লে</t>
+  </si>
+  <si>
+    <t>আমি কি বধির? আমি সব শুনি</t>
+  </si>
+  <si>
+    <t>আঁই ই বোরা না? আঁই বিয়া উনি</t>
+  </si>
+  <si>
+    <t>ঠিক আছে, ভুলে গেলেই ভাল</t>
+  </si>
+  <si>
+    <t>ঠিক আছে, ভুলি গেলিই ভালা</t>
+  </si>
+  <si>
+    <t>পাশের বাসা থেকে মিষ্টি দিছে</t>
+  </si>
+  <si>
+    <t>পাশোর বাসাত্তুন মিষ্টি দিয়ি</t>
+  </si>
+  <si>
+    <t>একবার খেয়ে দেখ কেমন হয়েছে</t>
+  </si>
+  <si>
+    <t>একবার হায় স কেন অইয়্যি</t>
+  </si>
+  <si>
+    <t>বাগানের ফুল গুলো মরে যাচ্ছে, একটু পানি দিয়ে আসো</t>
+  </si>
+  <si>
+    <t>বাগানোর ফুল এগুন মরি যার, এক্কানা পানি দি আইয়্যু</t>
+  </si>
+  <si>
+    <t>প্রতিদিন সকালে উঠে বাগানের সব ফুল গাছে পানি দিও</t>
+  </si>
+  <si>
+    <t>পইত্তোদিন বেইন্নে উডি বাগানোর বিয়াক ফুল গাছোত পানি দিবে</t>
+  </si>
+  <si>
+    <t>তোমার কাছে টাকা আছে? আমাকে কিছু টাকা ধার দাও</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হাছে টিয়া আছে? আঁরে কিছু টিয়া উধোর দও</t>
+  </si>
+  <si>
+    <t>আমাকে এখন কিছু টাকা ধার দাও, আমি তোমাকে এক সপ্তাহ পরে দিয়ে দিব</t>
+  </si>
+  <si>
+    <t>আঁরে এহন কিছু টিয়া উধোর দও, আঁই তোঁয়ারে এক সাপ্তাহ পরে দি দিয়্যুম</t>
+  </si>
+  <si>
+    <t>সামনের সপ্তাহে কক্সবাজার বেড়াতে যাব</t>
+  </si>
+  <si>
+    <t>সামনুর সপ্তাত কক্সবাজার বেরাইতাম যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>রাঙামাটি না গিয়ে বান্দরবান গেলে ভাল হবে</t>
+  </si>
+  <si>
+    <t>রাঙামাটি ন যায় বান্দরবান যাইলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>বাবা আমার কিছু টাকা লাগবে, বন্ধুদের সাথে বান্দরবান ঘুরতে যাব</t>
+  </si>
+  <si>
+    <t>আব্বু আত্তুন কিছু টিয়া লাগিবো, বন্ধু অক্কলোর লাই বান্দরবান ঘুইত্তাম যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>কানের নিছে দুইটা থাপ্পর দিব যদি আবার টাকার কথা বলিস</t>
+  </si>
+  <si>
+    <t>হানোর নিছে দুওয়ো চোয়ার দিয়্যুম যদি আবার টিয়ার হতা হস</t>
+  </si>
+  <si>
+    <t>নিজের রুমটি নিজে গুছিয়ে রাখতে পার না?</t>
+  </si>
+  <si>
+    <t>নিজোর রুম ইয়েন নিজে গুছায় রাহিত ন পারো?</t>
+  </si>
+  <si>
+    <t>আমি আজকে শেষবারের মত গুছিয়ে দিচ্ছি, সামনের বার থেকে নিজের কাজ নিজে করবে</t>
+  </si>
+  <si>
+    <t>আঁই আজিয়ে শেষবারোর মতন গুছায় দির, সামনোর বারোত্তুন নিজোর হাজ নিজে গরিবে</t>
+  </si>
+  <si>
+    <t>ইরফানকে একদিন বাসায় বেড়াতে আসতে বল, অনেক দিন ধরে ছেলেটা বাসায় আসেনা</t>
+  </si>
+  <si>
+    <t>ইরফান উরে একদিন বাসাত বেরাইতু আইসতো হ, বতদিন ধরি ফুয়া ইবে বাসাত ন আইয়্যি</t>
+  </si>
+  <si>
+    <t>আমি একটু মিনহাজের বাসায় যাচ্ছি, আসতে দেরি হবে</t>
+  </si>
+  <si>
+    <t>আঁই এক্কানা মিনহাজুর বাসাত যাইর, আইতে দেরি অইব্যু</t>
+  </si>
+  <si>
+    <t>আজকে বাসায় যাব না, আমি আমার বন্ধুর বাসায় থেকে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আজিয়ে বাসাত ন যাইয়্যুম, আঁই আঁর বন্ধুর বাসাত থাহি যাইর</t>
+  </si>
+  <si>
+    <t>আমার এক আন্টি আমাকে অনেক দেখতে পারে, একদম নিজের ছেলের মত মনে করে</t>
+  </si>
+  <si>
+    <t>আঁর উজ্ঞো আন্টি আঁরে বত দেইত পারে, এব্বেরে নিজোর ফুয়ার মতন মনে গরে</t>
+  </si>
+  <si>
+    <t>সারাদিন এত কাজ করি তাও কাজ গুলো শেষ হচ্ছে না</t>
+  </si>
+  <si>
+    <t>পুরোদিন এত হাজ গরি ত হাজ এগিন শেষ ন অর</t>
+  </si>
+  <si>
+    <t>আমাকে কিছু কাজ করে দাও, আমি টাকা দিব তোমাকে</t>
+  </si>
+  <si>
+    <t>আঁরে কিছু হাম গরি দ, আঁই টিয়া দিয়্যুম তোঁয়ারে</t>
+  </si>
+  <si>
+    <t>মা, আমি এখন ভাত খাব না, তুমি খেয়ে নাও</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁই এহন ভাত ন হাইয়্যুম, তুঁই হায় লও</t>
+  </si>
+  <si>
+    <t>তোমার কথা শুনে মন খারাপ হয়ে গেল</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হতা উনি রে মন হারাপ অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>তোর বড় ভাই নাকি বিদেশ চলে গেছে?</t>
+  </si>
+  <si>
+    <t>তোর বদ্দা বলে বিদেশ চলি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আম্মু বলছে তোকে আর আন্টিকে একদিন বেড়াতে আসতে</t>
+  </si>
+  <si>
+    <t>আম্মু হদ্দে তোরে আর আন্টি রে একদিন বেরাইতো আইবের লাই</t>
+  </si>
+  <si>
+    <t>আমার বুক জ্বালা করছে, মনে হয় গ্যাস্ট্রিক বেড়ে গেছে</t>
+  </si>
+  <si>
+    <t>আঁর বুক জ্বলের, মনে অই গ্যাস্ট্রিক বারি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আসলে আমি যেটা বলতে চাচ্ছিলাম</t>
+  </si>
+  <si>
+    <t>আসলে আঁই যিয়েন হইতাম চাইর</t>
+  </si>
+  <si>
+    <t>আমি কি বলতে চাচ্ছি সেটা শুনো আগে</t>
+  </si>
+  <si>
+    <t>আঁই কি হইতাম চাইর ইয়েন উনো আগে</t>
+  </si>
+  <si>
+    <t>তুমি আমার কথায় কান না দিয়ে ওই দিকে কি দেখো?</t>
+  </si>
+  <si>
+    <t>তুঁই আঁর হতাত হান ন দি উইক্কে কি চায় থেইক্কো?</t>
+  </si>
+  <si>
+    <t>তোমার কি কি লাগবে একটা লিস্ট করো</t>
+  </si>
+  <si>
+    <t>তোঁয়াত্তুন কি কি লাগিবু এক্কান লিস্ট গরো</t>
+  </si>
+  <si>
+    <t>আমি আজকে রিয়াজ উদ্দিন বাজার থেকে সব নিয়ে আসব</t>
+  </si>
+  <si>
+    <t>আঁই আজিয়ে রিয়াজ উদ্দিন বাজারোত্তুন বিয়াক লই আসসুম</t>
+  </si>
+  <si>
+    <t>বন্ধু চল, আজকে বহাদ্দারহাট থেকে ওরশ বিরিয়ানি খেয়ে আসি</t>
+  </si>
+  <si>
+    <t>বন্ধু চল, আজিয়ে বহাদ্দারহাটুত্তুন ওরশ বিরেনি হায় আই</t>
   </si>
 </sst>
 </file>
@@ -5735,244 +6095,484 @@
       </c>
     </row>
     <row r="322" ht="25" customHeight="1" spans="1:2">
-      <c r="A322" s="2"/>
-      <c r="B322" s="2"/>
+      <c r="A322" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="323" ht="25" customHeight="1" spans="1:2">
-      <c r="A323" s="2"/>
-      <c r="B323" s="2"/>
+      <c r="A323" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="324" ht="25" customHeight="1" spans="1:2">
-      <c r="A324" s="2"/>
-      <c r="B324" s="2"/>
+      <c r="A324" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="325" ht="25" customHeight="1" spans="1:2">
-      <c r="A325" s="2"/>
-      <c r="B325" s="2"/>
+      <c r="A325" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="326" ht="25" customHeight="1" spans="1:2">
-      <c r="A326" s="2"/>
-      <c r="B326" s="2"/>
+      <c r="A326" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>646</v>
+      </c>
     </row>
     <row r="327" ht="25" customHeight="1" spans="1:2">
-      <c r="A327" s="2"/>
-      <c r="B327" s="2"/>
+      <c r="A327" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="328" ht="25" customHeight="1" spans="1:2">
-      <c r="A328" s="2"/>
-      <c r="B328" s="2"/>
+      <c r="A328" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="329" ht="25" customHeight="1" spans="1:2">
-      <c r="A329" s="2"/>
-      <c r="B329" s="2"/>
+      <c r="A329" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="330" ht="25" customHeight="1" spans="1:2">
-      <c r="A330" s="2"/>
-      <c r="B330" s="2"/>
+      <c r="A330" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="331" ht="25" customHeight="1" spans="1:2">
-      <c r="A331" s="2"/>
-      <c r="B331" s="2"/>
+      <c r="A331" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="332" ht="25" customHeight="1" spans="1:2">
-      <c r="A332" s="2"/>
-      <c r="B332" s="2"/>
+      <c r="A332" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="333" ht="25" customHeight="1" spans="1:2">
-      <c r="A333" s="2"/>
-      <c r="B333" s="2"/>
+      <c r="A333" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="334" ht="25" customHeight="1" spans="1:2">
-      <c r="A334" s="2"/>
-      <c r="B334" s="2"/>
+      <c r="A334" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>662</v>
+      </c>
     </row>
     <row r="335" ht="25" customHeight="1" spans="1:2">
-      <c r="A335" s="2"/>
-      <c r="B335" s="2"/>
+      <c r="A335" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="336" ht="25" customHeight="1" spans="1:2">
-      <c r="A336" s="2"/>
-      <c r="B336" s="2"/>
+      <c r="A336" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="337" ht="25" customHeight="1" spans="1:2">
-      <c r="A337" s="2"/>
-      <c r="B337" s="2"/>
+      <c r="A337" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="338" ht="25" customHeight="1" spans="1:2">
-      <c r="A338" s="2"/>
-      <c r="B338" s="2"/>
+      <c r="A338" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="339" ht="25" customHeight="1" spans="1:2">
-      <c r="A339" s="2"/>
-      <c r="B339" s="2"/>
+      <c r="A339" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="340" ht="25" customHeight="1" spans="1:2">
-      <c r="A340" s="2"/>
-      <c r="B340" s="2"/>
+      <c r="A340" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="341" ht="25" customHeight="1" spans="1:2">
-      <c r="A341" s="2"/>
-      <c r="B341" s="2"/>
+      <c r="A341" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="342" ht="25" customHeight="1" spans="1:2">
-      <c r="A342" s="2"/>
-      <c r="B342" s="2"/>
+      <c r="A342" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="343" ht="25" customHeight="1" spans="1:2">
-      <c r="A343" s="2"/>
-      <c r="B343" s="2"/>
+      <c r="A343" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="344" ht="25" customHeight="1" spans="1:2">
-      <c r="A344" s="2"/>
-      <c r="B344" s="2"/>
+      <c r="A344" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>682</v>
+      </c>
     </row>
     <row r="345" ht="25" customHeight="1" spans="1:2">
-      <c r="A345" s="2"/>
-      <c r="B345" s="2"/>
+      <c r="A345" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="346" ht="25" customHeight="1" spans="1:2">
-      <c r="A346" s="2"/>
-      <c r="B346" s="2"/>
+      <c r="A346" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="347" ht="25" customHeight="1" spans="1:2">
-      <c r="A347" s="2"/>
-      <c r="B347" s="2"/>
+      <c r="A347" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="348" ht="25" customHeight="1" spans="1:2">
-      <c r="A348" s="2"/>
-      <c r="B348" s="2"/>
+      <c r="A348" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="349" ht="25" customHeight="1" spans="1:2">
-      <c r="A349" s="2"/>
-      <c r="B349" s="2"/>
+      <c r="A349" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="350" ht="25" customHeight="1" spans="1:2">
-      <c r="A350" s="2"/>
-      <c r="B350" s="2"/>
+      <c r="A350" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="351" ht="25" customHeight="1" spans="1:2">
-      <c r="A351" s="2"/>
-      <c r="B351" s="2"/>
+      <c r="A351" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>696</v>
+      </c>
     </row>
     <row r="352" ht="25" customHeight="1" spans="1:2">
-      <c r="A352" s="2"/>
-      <c r="B352" s="2"/>
+      <c r="A352" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="353" ht="25" customHeight="1" spans="1:2">
-      <c r="A353" s="2"/>
-      <c r="B353" s="2"/>
+      <c r="A353" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="354" ht="25" customHeight="1" spans="1:2">
-      <c r="A354" s="2"/>
-      <c r="B354" s="2"/>
+      <c r="A354" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="355" ht="25" customHeight="1" spans="1:2">
-      <c r="A355" s="2"/>
-      <c r="B355" s="2"/>
+      <c r="A355" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="356" ht="25" customHeight="1" spans="1:2">
-      <c r="A356" s="2"/>
-      <c r="B356" s="2"/>
+      <c r="A356" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="357" ht="25" customHeight="1" spans="1:2">
-      <c r="A357" s="2"/>
-      <c r="B357" s="2"/>
+      <c r="A357" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="358" ht="25" customHeight="1" spans="1:2">
-      <c r="A358" s="2"/>
-      <c r="B358" s="2"/>
+      <c r="A358" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="359" ht="25" customHeight="1" spans="1:2">
-      <c r="A359" s="2"/>
-      <c r="B359" s="2"/>
+      <c r="A359" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="360" ht="25" customHeight="1" spans="1:2">
-      <c r="A360" s="2"/>
-      <c r="B360" s="2"/>
+      <c r="A360" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>714</v>
+      </c>
     </row>
     <row r="361" ht="25" customHeight="1" spans="1:2">
-      <c r="A361" s="2"/>
-      <c r="B361" s="2"/>
+      <c r="A361" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="362" ht="25" customHeight="1" spans="1:2">
-      <c r="A362" s="2"/>
-      <c r="B362" s="2"/>
+      <c r="A362" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="363" ht="25" customHeight="1" spans="1:2">
-      <c r="A363" s="2"/>
-      <c r="B363" s="2"/>
+      <c r="A363" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="364" ht="25" customHeight="1" spans="1:2">
-      <c r="A364" s="2"/>
-      <c r="B364" s="2"/>
+      <c r="A364" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="365" ht="25" customHeight="1" spans="1:2">
-      <c r="A365" s="2"/>
-      <c r="B365" s="2"/>
+      <c r="A365" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>724</v>
+      </c>
     </row>
     <row r="366" ht="25" customHeight="1" spans="1:2">
-      <c r="A366" s="2"/>
-      <c r="B366" s="2"/>
+      <c r="A366" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>726</v>
+      </c>
     </row>
     <row r="367" ht="25" customHeight="1" spans="1:2">
-      <c r="A367" s="2"/>
-      <c r="B367" s="2"/>
+      <c r="A367" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>728</v>
+      </c>
     </row>
     <row r="368" ht="25" customHeight="1" spans="1:2">
-      <c r="A368" s="2"/>
-      <c r="B368" s="2"/>
+      <c r="A368" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="369" ht="25" customHeight="1" spans="1:2">
-      <c r="A369" s="2"/>
-      <c r="B369" s="2"/>
+      <c r="A369" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="370" ht="25" customHeight="1" spans="1:2">
-      <c r="A370" s="2"/>
-      <c r="B370" s="2"/>
+      <c r="A370" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>734</v>
+      </c>
     </row>
     <row r="371" ht="25" customHeight="1" spans="1:2">
-      <c r="A371" s="2"/>
-      <c r="B371" s="2"/>
+      <c r="A371" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>736</v>
+      </c>
     </row>
     <row r="372" ht="25" customHeight="1" spans="1:2">
-      <c r="A372" s="2"/>
-      <c r="B372" s="2"/>
+      <c r="A372" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>738</v>
+      </c>
     </row>
     <row r="373" ht="25" customHeight="1" spans="1:2">
-      <c r="A373" s="2"/>
-      <c r="B373" s="2"/>
+      <c r="A373" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>740</v>
+      </c>
     </row>
     <row r="374" ht="25" customHeight="1" spans="1:2">
-      <c r="A374" s="2"/>
-      <c r="B374" s="2"/>
+      <c r="A374" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>742</v>
+      </c>
     </row>
     <row r="375" ht="25" customHeight="1" spans="1:2">
-      <c r="A375" s="2"/>
-      <c r="B375" s="2"/>
+      <c r="A375" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="376" ht="25" customHeight="1" spans="1:2">
-      <c r="A376" s="2"/>
-      <c r="B376" s="2"/>
+      <c r="A376" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="377" ht="25" customHeight="1" spans="1:2">
-      <c r="A377" s="2"/>
-      <c r="B377" s="2"/>
+      <c r="A377" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>748</v>
+      </c>
     </row>
     <row r="378" ht="25" customHeight="1" spans="1:2">
-      <c r="A378" s="2"/>
-      <c r="B378" s="2"/>
+      <c r="A378" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>750</v>
+      </c>
     </row>
     <row r="379" ht="25" customHeight="1" spans="1:2">
-      <c r="A379" s="2"/>
-      <c r="B379" s="2"/>
+      <c r="A379" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>752</v>
+      </c>
     </row>
     <row r="380" ht="25" customHeight="1" spans="1:2">
-      <c r="A380" s="2"/>
-      <c r="B380" s="2"/>
+      <c r="A380" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>754</v>
+      </c>
     </row>
     <row r="381" ht="25" customHeight="1" spans="1:2">
-      <c r="A381" s="2"/>
-      <c r="B381" s="2"/>
+      <c r="A381" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>756</v>
+      </c>
     </row>
     <row r="382" ht="25" customHeight="1" spans="1:2">
       <c r="A382" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="797">
   <si>
     <t>bangla</t>
   </si>
@@ -779,7 +779,7 @@
     <t>তুমি কি পাগল? মানুষজন দেখলে কি বলবে?</t>
   </si>
   <si>
-    <t>তুঁই কি পল না? মাইনসে দেহিলি কি হইবু?</t>
+    <t>তুঁই কি ফঅল না? মাইনসে দেহিলি কি হইবু?</t>
   </si>
   <si>
     <t>আমার ভাল লাগছেনা, আমি এখন চলে যাচ্ছি</t>
@@ -1137,7 +1137,7 @@
     <t>তাহলে এতোদিন পর আমার কথা মনে পড়ছে</t>
   </si>
   <si>
-    <t>তইলি এতোদিন পর আঁর হতা মনোত পইজ্জি</t>
+    <t>তইলি এতোদিন পর আঁর হতা মনোত ফইজ্জি</t>
   </si>
   <si>
     <t>এতোদিন পর আমার খবর নিচ্ছো! একবারের জন্য আমার কথা মনেও পড়ে নাই</t>
@@ -2350,6 +2350,126 @@
   </si>
   <si>
     <t>বন্ধু চল, আজিয়ে বহাদ্দারহাটুত্তুন ওরশ বিরেনি হায় আই</t>
+  </si>
+  <si>
+    <t>আজকে বন্ধুর বাসায় দাওয়াত আছে, তাই দুপুরে খাব না</t>
+  </si>
+  <si>
+    <t>আজয়ি বন্ধুর বাসাত দত আছে, এতেল্লে দুইজ্জে হাইতাম নো</t>
+  </si>
+  <si>
+    <t>বাইরে কেন দাঁড়ায় আছিস, ভিতরে আই</t>
+  </si>
+  <si>
+    <t>বাদ্দি কা থিয়েই থেইক্কুস, ভিতুরে আই</t>
+  </si>
+  <si>
+    <t>আমার দেরি হয়ে যাচ্ছে, তাই চলে যাচ্চি</t>
+  </si>
+  <si>
+    <t>আত্তুন দেরি অই যার, এতেল্লে চলি যাইর</t>
+  </si>
+  <si>
+    <t>আমার স্কুলের জন্য দেরি হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>আত্তুন স্কুলুর লাই দেরি অই যার</t>
+  </si>
+  <si>
+    <t>আজকে আসতে পারব না, অন্য আরেকদিন আসব</t>
+  </si>
+  <si>
+    <t>আজিয়ে আইত পাইত্তাম ন, অন্য আরেকদিন আইসসুম</t>
+  </si>
+  <si>
+    <t>আজকে অফিসে যেতে হবে যে তাই আসতে পারব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে অফিসুত যন পরিবু দে এতেল্লে আইসতাম পাইত্তাম নো</t>
+  </si>
+  <si>
+    <t>তোমার ভাই কে বলিও আমাকে কিছু টাকা ধার দিতে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার ভাইরে হইয়্যো আঁরে কিছু টিয়া উধোর দিতো</t>
+  </si>
+  <si>
+    <t>আল্লাহ যা করেন ভালোর জন্য করেন</t>
+  </si>
+  <si>
+    <t>আল্লাহ যা গরে ভালার লাই গরে</t>
+  </si>
+  <si>
+    <t>অনেক আশা নিয়ে গেছিলাম কিন্তু কাজটা হলো না</t>
+  </si>
+  <si>
+    <t>বত আশা লই রে গেইলাম কিন্তু হাজগান ন অই</t>
+  </si>
+  <si>
+    <t>আমার মাথা এখন গরম, তোমার সাথে পরে কথা বলব</t>
+  </si>
+  <si>
+    <t>আঁর মাথা এহন গরম, তোঁয়ার লগে পরে হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>মাথা ঠাণ্ডা হলে তারপর কথা বলব</t>
+  </si>
+  <si>
+    <t>মাথা ঠাণ্ডা অইলি তারপর হতা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আজকে শেষবারের মত বলছি, আর বলব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে শেষবারোর মতন হইদ্দি, আর হইতাম ন</t>
+  </si>
+  <si>
+    <t>আমি ভাত খাব না রাগ করব আমার মনে জ্বালা</t>
+  </si>
+  <si>
+    <t>আঁই ভাত ন হাইয়্যুম গুসসা অইয়্যুম আঁর মনোত জ্বালা</t>
+  </si>
+  <si>
+    <t>একটু মনে কষ্ট পেয়েছি কিন্তু রাগ করি নাই</t>
+  </si>
+  <si>
+    <t>এক্কানা মনোত হষ্ট ফাই কিন্তু গুসসা ন অই</t>
+  </si>
+  <si>
+    <t>আজকে আর না, আর পারছি না ভাই</t>
+  </si>
+  <si>
+    <t>আজিয়ে আর ন, আর ন পারির বদ্দা</t>
+  </si>
+  <si>
+    <t>আচ্ছা তুমি কাজ শেষ কর, আমি বাইরে অপেক্ষা করছি</t>
+  </si>
+  <si>
+    <t>আইচ্ছে তুঁই হাজ শেষ গরো, আঁই বাদ্দি অপেক্ষা গরির</t>
+  </si>
+  <si>
+    <t>আমার কোন দোষ নাই, এটা আমি করি নাই</t>
+  </si>
+  <si>
+    <t>আঁর হনো দোষ নাই, ইয়েন আঁই ন গরি</t>
+  </si>
+  <si>
+    <t>কোমরে বেশি ব্যথা করছে</t>
+  </si>
+  <si>
+    <t>কেইলুত বেশি ব্যথা গরের</t>
+  </si>
+  <si>
+    <t>এমনভাবে মাথা ঘুরাচ্ছে যেন মনে হচ্ছে দুনিয়াটা ঘুরতাছে</t>
+  </si>
+  <si>
+    <t>এন গরি মাথা ঘুরাদ্দে যেন মনে অর দুনিয়ে ইয়েন ঘুরের</t>
+  </si>
+  <si>
+    <t>তুই পাগল হয়েছিস যে ঘরে যানে?</t>
+  </si>
+  <si>
+    <t>তুই ফ অল অইয়্যুস যে ঘরোত যানে?</t>
   </si>
 </sst>
 </file>
@@ -6575,84 +6695,164 @@
       </c>
     </row>
     <row r="382" ht="25" customHeight="1" spans="1:2">
-      <c r="A382" s="2"/>
-      <c r="B382" s="2"/>
+      <c r="A382" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>758</v>
+      </c>
     </row>
     <row r="383" ht="25" customHeight="1" spans="1:2">
-      <c r="A383" s="2"/>
-      <c r="B383" s="2"/>
+      <c r="A383" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>760</v>
+      </c>
     </row>
     <row r="384" ht="25" customHeight="1" spans="1:2">
-      <c r="A384" s="2"/>
-      <c r="B384" s="2"/>
+      <c r="A384" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>762</v>
+      </c>
     </row>
     <row r="385" ht="25" customHeight="1" spans="1:2">
-      <c r="A385" s="2"/>
-      <c r="B385" s="2"/>
+      <c r="A385" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="386" ht="25" customHeight="1" spans="1:2">
-      <c r="A386" s="2"/>
-      <c r="B386" s="2"/>
+      <c r="A386" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>766</v>
+      </c>
     </row>
     <row r="387" ht="25" customHeight="1" spans="1:2">
-      <c r="A387" s="2"/>
-      <c r="B387" s="2"/>
+      <c r="A387" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>768</v>
+      </c>
     </row>
     <row r="388" ht="25" customHeight="1" spans="1:2">
-      <c r="A388" s="2"/>
-      <c r="B388" s="2"/>
+      <c r="A388" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="389" ht="25" customHeight="1" spans="1:2">
-      <c r="A389" s="2"/>
-      <c r="B389" s="2"/>
+      <c r="A389" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>772</v>
+      </c>
     </row>
     <row r="390" ht="25" customHeight="1" spans="1:2">
-      <c r="A390" s="2"/>
-      <c r="B390" s="2"/>
+      <c r="A390" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>774</v>
+      </c>
     </row>
     <row r="391" ht="25" customHeight="1" spans="1:2">
-      <c r="A391" s="2"/>
-      <c r="B391" s="2"/>
+      <c r="A391" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="392" ht="25" customHeight="1" spans="1:2">
-      <c r="A392" s="2"/>
-      <c r="B392" s="2"/>
+      <c r="A392" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>778</v>
+      </c>
     </row>
     <row r="393" ht="25" customHeight="1" spans="1:2">
-      <c r="A393" s="2"/>
-      <c r="B393" s="2"/>
+      <c r="A393" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="394" ht="25" customHeight="1" spans="1:2">
-      <c r="A394" s="2"/>
-      <c r="B394" s="2"/>
+      <c r="A394" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>782</v>
+      </c>
     </row>
     <row r="395" ht="25" customHeight="1" spans="1:2">
-      <c r="A395" s="2"/>
-      <c r="B395" s="2"/>
+      <c r="A395" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>784</v>
+      </c>
     </row>
     <row r="396" ht="25" customHeight="1" spans="1:2">
-      <c r="A396" s="2"/>
-      <c r="B396" s="2"/>
+      <c r="A396" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="397" ht="25" customHeight="1" spans="1:2">
-      <c r="A397" s="2"/>
-      <c r="B397" s="2"/>
+      <c r="A397" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>788</v>
+      </c>
     </row>
     <row r="398" ht="25" customHeight="1" spans="1:2">
-      <c r="A398" s="2"/>
-      <c r="B398" s="2"/>
+      <c r="A398" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>790</v>
+      </c>
     </row>
     <row r="399" ht="25" customHeight="1" spans="1:2">
-      <c r="A399" s="2"/>
-      <c r="B399" s="2"/>
+      <c r="A399" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="400" ht="25" customHeight="1" spans="1:2">
-      <c r="A400" s="2"/>
-      <c r="B400" s="2"/>
+      <c r="A400" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="401" ht="25" customHeight="1" spans="1:2">
-      <c r="A401" s="2"/>
-      <c r="B401" s="2"/>
+      <c r="A401" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="402" ht="25" customHeight="1" spans="1:2">
       <c r="A402" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="897">
   <si>
     <t>bangla</t>
   </si>
@@ -1965,7 +1965,7 @@
     <t>সারাদিন ফোন টিপা ছাড়া আর কোন কাজ আছে?</t>
   </si>
   <si>
-    <t>সারাদিন ফোন টিপন ছাড়া আর হনো হাম আছে?</t>
+    <t>ফুরোদিন ফোন টিপন ছাড়া আর হনো হাম আছে?</t>
   </si>
   <si>
     <t>আজকের দিনটি এমনি এমনি চলে গেল</t>
@@ -2470,6 +2470,306 @@
   </si>
   <si>
     <t>তুই ফ অল অইয়্যুস যে ঘরোত যানে?</t>
+  </si>
+  <si>
+    <t>খাবার তো সব ঠান্ডা হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>হানা তো বিয়াক ঠান্ডা অই যার</t>
+  </si>
+  <si>
+    <t>বেশি গরম লাগছে, পাখাটা অন করো</t>
+  </si>
+  <si>
+    <t>বেশি গরম লার, ফ্যান ইবে চালু গরো</t>
+  </si>
+  <si>
+    <t>বেশি ঠান্ডা লাগছে, ফ্যানটা বন্ধ করো</t>
+  </si>
+  <si>
+    <t>বেশি ঠান্ডা লার, ফ্যান ইবে বন গরো</t>
+  </si>
+  <si>
+    <t>এবার ঠান্ডা একটু বেশি পড়ছে</t>
+  </si>
+  <si>
+    <t>এবার ঠান্ডা এক্কানা বেশি পরের</t>
+  </si>
+  <si>
+    <t>গরমকালে ডাবের পানি খেলে অনেক শান্তি লাগে</t>
+  </si>
+  <si>
+    <t>গরমহালোত ডাবোর পানি হাইলি বত শান্তি লাগে</t>
+  </si>
+  <si>
+    <t>এবার গাছে অনেক আম ধরেছে</t>
+  </si>
+  <si>
+    <t>এবার গাছোত বত আম ধইজ্জি</t>
+  </si>
+  <si>
+    <t>তুর মাকে বলিস এবার আমাদের কে কিছু আম দিতে</t>
+  </si>
+  <si>
+    <t>তুর মারে হইস এবার আঁরারে কিছু আম দিতো</t>
+  </si>
+  <si>
+    <t>সাথে একটা কাঁঠাল দিতে বলিও</t>
+  </si>
+  <si>
+    <t>ওয়ারে উজ্ঞো হাট্টল দিতো হইয়্যো</t>
+  </si>
+  <si>
+    <t>কাঁঠাল এটা তো কাঁচা</t>
+  </si>
+  <si>
+    <t>হাট্টল ইবে তো কেঁচা</t>
+  </si>
+  <si>
+    <t>নানুর বাড়িতে গেলে এবার বেশি বেশি আম খাবো</t>
+  </si>
+  <si>
+    <t>নানারো বারিত যাইলি এবার বেশি বেশি আম হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>নানুর বাড়ির গাছের বরই অনেক মিষ্টি</t>
+  </si>
+  <si>
+    <t>নানারো বারির গাছোর বরই বত মিডে</t>
+  </si>
+  <si>
+    <t>মায়ের বোন খালা, মায়ের থেকেও ভালো</t>
+  </si>
+  <si>
+    <t>মা'র বইন হাআলা, মাত্তুন অও ভালা</t>
+  </si>
+  <si>
+    <t>মানুষটা সারাদিন মাঠে কাজ করে</t>
+  </si>
+  <si>
+    <t>মানুষ ইবে ফুরোদিন মাডোত হাজ গরে</t>
+  </si>
+  <si>
+    <t>মানুষটা সারাদিন ক্ষেতে কাজ করে</t>
+  </si>
+  <si>
+    <t>মানুষ ইবে ফুরোদিন ক্ষেতিত হাজ গরে</t>
+  </si>
+  <si>
+    <t>এবার ধান ক্ষেতে পোকা ধরছে বেশি</t>
+  </si>
+  <si>
+    <t>এবার ধান ক্ষেতিত ফুকে ধইজ্জি বেশি</t>
+  </si>
+  <si>
+    <t>এবার ধান ক্ষেতে পোকা হয়েছে বেশি, সেজন্য বিষ দিতে হবে</t>
+  </si>
+  <si>
+    <t>এবার ধান ক্ষেতিত ফুক অইয়্যি বেশি, এতেল্লে বিষ দন পরিবু</t>
+  </si>
+  <si>
+    <t>কারেন্ট বেশি ডিস্টার্ব করছে, একবার যাচ্ছে আবার আসছে</t>
+  </si>
+  <si>
+    <t>কারোন বেশি ডিস্টার্ব গরের, একবার যার আবার আইয়্যির</t>
+  </si>
+  <si>
+    <t>শীতকালের দিন তাড়াতাড়ি চলে যায়</t>
+  </si>
+  <si>
+    <t>শীতহাইল্লে দিন তারাতারি চলি যায়</t>
+  </si>
+  <si>
+    <t>শীতকাল গিয়ে এখন গরমকাল চলে আসছে</t>
+  </si>
+  <si>
+    <t>শীতহাল যাইরে এহন গরমহাল চলি আইস্যি</t>
+  </si>
+  <si>
+    <t>আজকে বেশি ঠান্ডা, সেজন্য গরম পানি দিয়ে গোসল করব</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেশি ঠান্ডা, এতেল্লে গরম পানি দি গোসল গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমি ঠিকমতো নাস্তা করতে পারিনি, সেজন্য জলদি খিদে লেগেছে</t>
+  </si>
+  <si>
+    <t>আঁই ঠিকগরি নাস্তা গরিত ন ফারি, এতেল্লে হারা ভুক লেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>দুপুরে কি দিয়ে ভাত খেয়েছো?</t>
+  </si>
+  <si>
+    <t>দুইজ্জে কি দি ভাত হাইয়্যো?</t>
+  </si>
+  <si>
+    <t>সামনের সপ্তাহ থেকে ক্লাসে যাবে?</t>
+  </si>
+  <si>
+    <t>সামনোর সপ্তাত্তুন ক্লাসোত যাইবে?</t>
+  </si>
+  <si>
+    <t>এই সপ্তাহ যাব না, সামনের সপ্তাহ থেকে যাব ইনশাআল্লাহ</t>
+  </si>
+  <si>
+    <t>এই সপ্তাত যাইতাম ন, সামনোর সপ্তাত্তুন যাইয়্যুম ইনশাআল্লাহ</t>
+  </si>
+  <si>
+    <t>বৃষ্টি আসবে একটু পর, জলদি বাইরের সব কাপড় নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>ঝর আইবু এক্কানা পর, হারা বাইরোর বিয়াক হর লই আইয়্যু</t>
+  </si>
+  <si>
+    <t>বৃষ্টি পড়ে বাইরের সব কাপড় ভিজে গেছে</t>
+  </si>
+  <si>
+    <t>ঝর পরি বাইরোর বিয়াক হর ভিজি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>গোসল করে আসার সময় তোর বাবার লুঙ্গিটাও ধুয়ে আনিস</t>
+  </si>
+  <si>
+    <t>গোসল গরি আইবের সমত তোর বাফোর লুঙ্গি ইয়েন অ ধুয় আনিস</t>
+  </si>
+  <si>
+    <t>আমার এখন ঘুম আসছে, কিছুক্ষণ ঘুমিয়ে নি</t>
+  </si>
+  <si>
+    <t>আত্তুন এহন ঘুম আইয়্যির, হতক্ষন ঘুম যায়</t>
+  </si>
+  <si>
+    <t>শীতকালে পুকুরের পানি বেশি ঠান্ডা</t>
+  </si>
+  <si>
+    <t>শীতহালে ফইরোর ফানি বেশি ঠান্ডা</t>
+  </si>
+  <si>
+    <t>বাইরে রোদ উঠেছে, কাপড় গুলো শুকাতে দাও</t>
+  </si>
+  <si>
+    <t>বাদ্দি রইদ উট্টি, হরগিন ফুঅত দও</t>
+  </si>
+  <si>
+    <t>চোখ কানা নাকি? সামনে কি আছে দেখছো না?</t>
+  </si>
+  <si>
+    <t>চোখ হানা না? সাম্মোদ্দি কি আছে ন দেহর?</t>
+  </si>
+  <si>
+    <t>আজ এত গরম যে রান্না করতে মন চাইছে না</t>
+  </si>
+  <si>
+    <t>আজিয়ে এত গরম যে রান্না গইত্তো মন ন চার</t>
+  </si>
+  <si>
+    <t>আজ এত ক্লান্ত লাগছে যে কারও সাথে কথা বলারও ইচ্ছা করছে না</t>
+  </si>
+  <si>
+    <t>আজিয়ে এত অরান লাগেদ্দে কিয়ার লগে হতা হইতেও ইচ্ছে ন গরের</t>
+  </si>
+  <si>
+    <t>সকালে উঠে ফোন দেখতে বসলে কখন যে সময় চলে যায় বোঝাই যায় না</t>
+  </si>
+  <si>
+    <t>বেইন্নে উডি ফোন চাইতো বইলি হত্তে যে সময় চলি যায় বুঝায় ন যায়</t>
+  </si>
+  <si>
+    <t>একটা নাপা ট্যাবলেট খেয়ে ফেলো, নাহয় রাতে জ্বর চলে আসবে</t>
+  </si>
+  <si>
+    <t>উজ্ঞো নাপা ট্যাবেট হায় ফেলো, নইলি রাতিয়ে জ্বর চলি আইবু</t>
+  </si>
+  <si>
+    <t>এখন বাইরে যাব না, বাইরে গেলে অনেক সময় নষ্ট হবে</t>
+  </si>
+  <si>
+    <t>এহন বাদ্দি যাইতাম ন, বাদ্দি গেলি বত সময় নষ্ট অইবু</t>
+  </si>
+  <si>
+    <t>কাপড়টা বেশি ময়লা হয়ে গেছে, ধুয়ে ফেলতে হবে আজকে</t>
+  </si>
+  <si>
+    <t>হর ইবে বেশি হাচারা অই গেইয়্যি, আজিয়ে ধুই ফেলন পরিবু</t>
+  </si>
+  <si>
+    <t>আজকে সব কিছু আনতে ভুলে গেছি, কাল আবারও বাজার করতে হবে</t>
+  </si>
+  <si>
+    <t>আজিয়ে কিছু জিনিস আনিবের লাই ভুলি গেই, হালিয়ে আবারও বাজার গরন পরিবু</t>
+  </si>
+  <si>
+    <t>আজকে অনেক ক্লান্ত লাগছে, কাল থেকে আবারও শুরু করব</t>
+  </si>
+  <si>
+    <t>আজিয়ে বত অরান লাগের, হালিয়েত্তুন আবারও শুরু গইজ্জুম</t>
+  </si>
+  <si>
+    <t>কি কিনব বাজার থেকে! সবকিছুর যে দাম!</t>
+  </si>
+  <si>
+    <t>কি কিননুম বাজারোত্তন! বিয়াক কিছুর যে দাম!</t>
+  </si>
+  <si>
+    <t>সকালে জলদি ঘুম থেকে না উঠলে ক্লাসে যেতে দেরি হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>বেইন্নে জলদি ঘুমোত্তুন ন উডিলি ক্লাসোত যাইতে দেরি অই যাইবু</t>
+  </si>
+  <si>
+    <t>আচ্ছা ঠিক আছে, আমি এখন যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আইচ্ছে ঠিক আছে, আঁই এহন যাইর</t>
+  </si>
+  <si>
+    <t>তুমি আমার পিছন পিছন আসো</t>
+  </si>
+  <si>
+    <t>তুঁই আঁর পিছে পিছে আইয়্যু</t>
+  </si>
+  <si>
+    <t>দাঁড়িয়ে থেকো না, আমার দেরি হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>থিয়েই ন থাইক্কো, আত্তুন দেরি অই যার</t>
+  </si>
+  <si>
+    <t>কাজের চাপ বেশি ছিল বলে তোমার ফোন ধরতে পারিনি</t>
+  </si>
+  <si>
+    <t>হাজুর চাপ বেশি আছিল দি এতেল্লে তোঁয়ার ফোন ধরিত ন ফারি</t>
+  </si>
+  <si>
+    <t>আমি কি বলেছি সেটা তুমি একটু ভাল করে চিন্তা করে দেখ</t>
+  </si>
+  <si>
+    <t>আঁই কি হইয়্যি ইয়েন তুঁই এক্কানা ভালা গরি চিন্তে গরি স</t>
+  </si>
+  <si>
+    <t>সাদা পাঞ্জাবিটা আমার অনেক প্রিয়</t>
+  </si>
+  <si>
+    <t>সাদা পাঞ্জাবি ইবে আঁর বত প্রিয়</t>
+  </si>
+  <si>
+    <t>কালো রঙ আমার পছন্দের রঙ</t>
+  </si>
+  <si>
+    <t>হালা রঙ আঁর পছন্দর রঙ</t>
+  </si>
+  <si>
+    <t>আমার হাত ব্যথা করছে, আজকে আর পারছি না</t>
+  </si>
+  <si>
+    <t>আঁর আত ব্যথা গরের, আজিয়ে আর ন পারির</t>
+  </si>
+  <si>
+    <t>বাকি কাজগুলো আগামিকাল দেখব</t>
+  </si>
+  <si>
+    <t>বাকি হাম এগিন হালিয়ে চাইয়্যুম</t>
   </si>
 </sst>
 </file>
@@ -6855,204 +7155,404 @@
       </c>
     </row>
     <row r="402" ht="25" customHeight="1" spans="1:2">
-      <c r="A402" s="2"/>
-      <c r="B402" s="2"/>
+      <c r="A402" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="403" ht="25" customHeight="1" spans="1:2">
-      <c r="A403" s="2"/>
-      <c r="B403" s="2"/>
+      <c r="A403" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>800</v>
+      </c>
     </row>
     <row r="404" ht="25" customHeight="1" spans="1:2">
-      <c r="A404" s="2"/>
-      <c r="B404" s="2"/>
+      <c r="A404" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="405" ht="25" customHeight="1" spans="1:2">
-      <c r="A405" s="2"/>
-      <c r="B405" s="2"/>
+      <c r="A405" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>804</v>
+      </c>
     </row>
     <row r="406" ht="25" customHeight="1" spans="1:2">
-      <c r="A406" s="2"/>
-      <c r="B406" s="2"/>
+      <c r="A406" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="407" ht="25" customHeight="1" spans="1:2">
-      <c r="A407" s="2"/>
-      <c r="B407" s="2"/>
+      <c r="A407" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="408" ht="25" customHeight="1" spans="1:2">
-      <c r="A408" s="2"/>
-      <c r="B408" s="2"/>
+      <c r="A408" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>810</v>
+      </c>
     </row>
     <row r="409" ht="25" customHeight="1" spans="1:2">
-      <c r="A409" s="2"/>
-      <c r="B409" s="2"/>
+      <c r="A409" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="410" ht="25" customHeight="1" spans="1:2">
-      <c r="A410" s="2"/>
-      <c r="B410" s="2"/>
+      <c r="A410" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>814</v>
+      </c>
     </row>
     <row r="411" ht="25" customHeight="1" spans="1:2">
-      <c r="A411" s="2"/>
-      <c r="B411" s="2"/>
+      <c r="A411" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="412" ht="25" customHeight="1" spans="1:2">
-      <c r="A412" s="2"/>
-      <c r="B412" s="2"/>
+      <c r="A412" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>818</v>
+      </c>
     </row>
     <row r="413" ht="25" customHeight="1" spans="1:2">
-      <c r="A413" s="2"/>
-      <c r="B413" s="2"/>
+      <c r="A413" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="414" ht="25" customHeight="1" spans="1:2">
-      <c r="A414" s="2"/>
-      <c r="B414" s="2"/>
+      <c r="A414" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="415" ht="25" customHeight="1" spans="1:2">
-      <c r="A415" s="2"/>
-      <c r="B415" s="2"/>
+      <c r="A415" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>824</v>
+      </c>
     </row>
     <row r="416" ht="25" customHeight="1" spans="1:2">
-      <c r="A416" s="2"/>
-      <c r="B416" s="2"/>
+      <c r="A416" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>826</v>
+      </c>
     </row>
     <row r="417" ht="25" customHeight="1" spans="1:2">
-      <c r="A417" s="2"/>
-      <c r="B417" s="2"/>
+      <c r="A417" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="418" ht="25" customHeight="1" spans="1:2">
-      <c r="A418" s="2"/>
-      <c r="B418" s="2"/>
+      <c r="A418" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="419" ht="25" customHeight="1" spans="1:2">
-      <c r="A419" s="2"/>
-      <c r="B419" s="2"/>
+      <c r="A419" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="420" ht="25" customHeight="1" spans="1:2">
-      <c r="A420" s="2"/>
-      <c r="B420" s="2"/>
+      <c r="A420" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="421" ht="25" customHeight="1" spans="1:2">
-      <c r="A421" s="2"/>
-      <c r="B421" s="2"/>
+      <c r="A421" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="422" ht="25" customHeight="1" spans="1:2">
-      <c r="A422" s="2"/>
-      <c r="B422" s="2"/>
+      <c r="A422" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="423" ht="25" customHeight="1" spans="1:2">
-      <c r="A423" s="2"/>
-      <c r="B423" s="2"/>
+      <c r="A423" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="424" ht="25" customHeight="1" spans="1:2">
-      <c r="A424" s="2"/>
-      <c r="B424" s="2"/>
+      <c r="A424" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="425" ht="25" customHeight="1" spans="1:2">
-      <c r="A425" s="2"/>
-      <c r="B425" s="2"/>
+      <c r="A425" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="426" ht="25" customHeight="1" spans="1:2">
-      <c r="A426" s="2"/>
-      <c r="B426" s="2"/>
+      <c r="A426" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="427" ht="25" customHeight="1" spans="1:2">
-      <c r="A427" s="2"/>
-      <c r="B427" s="2"/>
+      <c r="A427" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="428" ht="25" customHeight="1" spans="1:2">
-      <c r="A428" s="2"/>
-      <c r="B428" s="2"/>
+      <c r="A428" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>850</v>
+      </c>
     </row>
     <row r="429" ht="25" customHeight="1" spans="1:2">
-      <c r="A429" s="2"/>
-      <c r="B429" s="2"/>
+      <c r="A429" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="430" ht="25" customHeight="1" spans="1:2">
-      <c r="A430" s="2"/>
-      <c r="B430" s="2"/>
+      <c r="A430" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="431" ht="25" customHeight="1" spans="1:2">
-      <c r="A431" s="2"/>
-      <c r="B431" s="2"/>
+      <c r="A431" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="432" ht="25" customHeight="1" spans="1:2">
-      <c r="A432" s="2"/>
-      <c r="B432" s="2"/>
+      <c r="A432" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>858</v>
+      </c>
     </row>
     <row r="433" ht="25" customHeight="1" spans="1:2">
-      <c r="A433" s="2"/>
-      <c r="B433" s="2"/>
+      <c r="A433" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="434" ht="25" customHeight="1" spans="1:2">
-      <c r="A434" s="2"/>
-      <c r="B434" s="2"/>
+      <c r="A434" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="435" ht="25" customHeight="1" spans="1:2">
-      <c r="A435" s="2"/>
-      <c r="B435" s="2"/>
+      <c r="A435" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>864</v>
+      </c>
     </row>
     <row r="436" ht="25" customHeight="1" spans="1:2">
-      <c r="A436" s="2"/>
-      <c r="B436" s="2"/>
+      <c r="A436" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="437" ht="25" customHeight="1" spans="1:2">
-      <c r="A437" s="2"/>
-      <c r="B437" s="2"/>
+      <c r="A437" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="438" ht="25" customHeight="1" spans="1:2">
-      <c r="A438" s="2"/>
-      <c r="B438" s="2"/>
+      <c r="A438" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>870</v>
+      </c>
     </row>
     <row r="439" ht="25" customHeight="1" spans="1:2">
-      <c r="A439" s="2"/>
-      <c r="B439" s="2"/>
+      <c r="A439" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>872</v>
+      </c>
     </row>
     <row r="440" ht="25" customHeight="1" spans="1:2">
-      <c r="A440" s="2"/>
-      <c r="B440" s="2"/>
+      <c r="A440" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="441" ht="25" customHeight="1" spans="1:2">
-      <c r="A441" s="2"/>
-      <c r="B441" s="2"/>
+      <c r="A441" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>876</v>
+      </c>
     </row>
     <row r="442" ht="25" customHeight="1" spans="1:2">
-      <c r="A442" s="2"/>
-      <c r="B442" s="2"/>
+      <c r="A442" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="443" ht="25" customHeight="1" spans="1:2">
-      <c r="A443" s="2"/>
-      <c r="B443" s="2"/>
+      <c r="A443" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="444" ht="25" customHeight="1" spans="1:2">
-      <c r="A444" s="2"/>
-      <c r="B444" s="2"/>
+      <c r="A444" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="445" ht="25" customHeight="1" spans="1:2">
-      <c r="A445" s="2"/>
-      <c r="B445" s="2"/>
+      <c r="A445" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>884</v>
+      </c>
     </row>
     <row r="446" ht="25" customHeight="1" spans="1:2">
-      <c r="A446" s="2"/>
-      <c r="B446" s="2"/>
+      <c r="A446" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="447" ht="25" customHeight="1" spans="1:2">
-      <c r="A447" s="2"/>
-      <c r="B447" s="2"/>
+      <c r="A447" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="448" ht="25" customHeight="1" spans="1:2">
-      <c r="A448" s="2"/>
-      <c r="B448" s="2"/>
+      <c r="A448" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="449" ht="25" customHeight="1" spans="1:2">
-      <c r="A449" s="2"/>
-      <c r="B449" s="2"/>
+      <c r="A449" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="450" ht="25" customHeight="1" spans="1:2">
-      <c r="A450" s="2"/>
-      <c r="B450" s="2"/>
+      <c r="A450" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="451" ht="25" customHeight="1" spans="1:2">
-      <c r="A451" s="2"/>
-      <c r="B451" s="2"/>
+      <c r="A451" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="452" ht="25" customHeight="1" spans="1:2">
       <c r="A452" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="997">
   <si>
     <t>bangla</t>
   </si>
@@ -1455,7 +1455,7 @@
     <t>আজকে মেহমান আসছে, বাজার থেকে গরুর মাংস আর চিংড়ি মাছ নিয়ে আসো</t>
   </si>
   <si>
-    <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তন গরু গুস্ত আর ইছে মাছ আনো</t>
+    <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তন গরু গোস্ত আর ইছে মাছ আনো</t>
   </si>
   <si>
     <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি এক কাপ চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
@@ -2043,13 +2043,13 @@
     <t>বারান্দায় মেহমান বসে আছে, গিয়ে নাস্তা দিয়ে আসো</t>
   </si>
   <si>
-    <t>বারান্দাত মেমান বইঁ থেইক্কি, যায়্যিরে নাস্তা দি আইয়্যো</t>
+    <t>বারান্দাত মেমান বই থেইক্কি, যায়্যিরে নাস্তা দি আইয়্যো</t>
   </si>
   <si>
     <t>আমি বসে আছি, তুমি কি করো?</t>
   </si>
   <si>
-    <t>আঁই বইঁ থেইক্কি, তুঁই কি গরো?</t>
+    <t>আঁই বই থেইক্কি, তুঁই কি গরো?</t>
   </si>
   <si>
     <t>বার বার বলি যে বাজার থেকে কিছু নিলে ভালভাবে দেখে নিতে, এখন দোকানদার সব পঁচা আম দিয়ে দিছে তোমাকে</t>
@@ -2061,7 +2061,7 @@
     <t>অনেকদি ধরে ঘরে বসে বসে বিরক্ত হয়ে গেছি</t>
   </si>
   <si>
-    <t>বতদিন ধরি ঘরোত বইঁ বইঁ বিরক্ত অই গেই</t>
+    <t>বতদিন ধরি ঘরোত বই বই বিরক্ত অই গেই</t>
   </si>
   <si>
     <t>বাইরে কোথাও থেকে ঘুরে আসলে মন ভাল হয়ে যাবে</t>
@@ -2679,7 +2679,7 @@
     <t>একটা নাপা ট্যাবলেট খেয়ে ফেলো, নাহয় রাতে জ্বর চলে আসবে</t>
   </si>
   <si>
-    <t>উজ্ঞো নাপা ট্যাবেট হায় ফেলো, নইলি রাতিয়ে জ্বর চলি আইবু</t>
+    <t>উজ্ঞো নাপা ট্যাবলেট হায় ফেলো, নইলি রাতিয়ে জ্বর চলি আইবু</t>
   </si>
   <si>
     <t>এখন বাইরে যাব না, বাইরে গেলে অনেক সময় নষ্ট হবে</t>
@@ -2770,6 +2770,306 @@
   </si>
   <si>
     <t>বাকি হাম এগিন হালিয়ে চাইয়্যুম</t>
+  </si>
+  <si>
+    <t>সকালে ঘুম ভাঙার পর জানালা খুলে দিলাম, তারপর দেখি সূর্য উঠে গেছে</t>
+  </si>
+  <si>
+    <t>ফজোরত ঘুম ভাঙিবের পর জানালা খুলি দি, তারপর দেহিদ্দি সূর্য উডি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>রুমে ঠান্ডা বাতাস ঢুকছে, তাড়াতাড়ি জানালা বন্ধ করে দাও</t>
+  </si>
+  <si>
+    <t>রুমোত ঠান্ডা বাতাস ঢুকের, হারা জানালা বন্ধ গরি দ</t>
+  </si>
+  <si>
+    <t>ঘরে রোদ ঢুকছে, জানালার পর্দাটা টেনে দাও</t>
+  </si>
+  <si>
+    <t>ঘরোত রইদ ঢুকের, জনালার পর্দাগান টানি দ</t>
+  </si>
+  <si>
+    <t>বাতাসের কারনে জানালার পর্দাটা দোলছে</t>
+  </si>
+  <si>
+    <t>বাতাসোর হারনে জানালার পর্দা ইয়েন দোলের</t>
+  </si>
+  <si>
+    <t>মেহমানদের বারান্দায় বসতে দাও এবং দরজার পর্দাটা টেনে দাও</t>
+  </si>
+  <si>
+    <t>মেমান অক্কলোরে বারান্দাত বইসতো দ আর দরজার পর্দাগান টানি দ</t>
+  </si>
+  <si>
+    <t>দরজার পর্দাটা টেনে দিলে কি সমস্যা? আমার লজ্জা লাগছে তো</t>
+  </si>
+  <si>
+    <t>দরজার পর্দাগান টানি দিলি কি সমস্যা? আত্তুন শরম লাগের তো</t>
+  </si>
+  <si>
+    <t>দরজা খুলে দেখি একটা সুন্দরী মেয়ে দাঁড়িয়ে আছে</t>
+  </si>
+  <si>
+    <t>দরজা খুলি দেহি উজ্ঞো সুন্দরী মাইফোয়া থিয়েই আছে</t>
+  </si>
+  <si>
+    <t>দরজার বাইরে একটা ভিক্কুক দাঁড়ায় আছে, চাল গুলো উনাকে দিয়ে আসো</t>
+  </si>
+  <si>
+    <t>দরজার বাদ্দি উজ্ঞো ফইর থিয়েই থেইক্কি, চইল এগুন ইবেরে দি আইয়্যু</t>
+  </si>
+  <si>
+    <t>প্রতিদিন নিয়ম করে দাঁত মাজা উচিত</t>
+  </si>
+  <si>
+    <t>পইত্তোদিন নিয়ম গরি দাঁত মাজন উচিত</t>
+  </si>
+  <si>
+    <t>দাঁত না মাজলে দাঁতে পোকা হবে</t>
+  </si>
+  <si>
+    <t>দাত ন মাজিলি দাতুত ফুক অইবু</t>
+  </si>
+  <si>
+    <t>আমি ঘুমানোর আগে ব্রাশ দিয়ে দাঁত মাজি</t>
+  </si>
+  <si>
+    <t>আঁই ঘুম যাইবের আগে ব্রাশ দি দাত মাজি</t>
+  </si>
+  <si>
+    <t>মা, আমি দাঁত ব্রাশ করে আসছি, আপনি আমার জন্য নাস্তা রেডি করেন</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁই দাঁত ব্রাশ গরি আইর, অঁনে আঁর লাই নাস্তা রেডি গরন</t>
+  </si>
+  <si>
+    <t>আমার বেশি কাশি হচ্ছে, আমার জন্য আদা দিয়ে এক কাপ রং চা বানাও</t>
+  </si>
+  <si>
+    <t>আত্তুন বেশি হাশি অর, আঁর লাই আদা দি এক হাপ রং চা বানো</t>
+  </si>
+  <si>
+    <t>তোর আপুর প্রেশার বেড়ে গেছে, জলদি একটা ডাক্তার নিয়ে আয়</t>
+  </si>
+  <si>
+    <t>তোর আফার প্রেশার বারি গেইয়্যি, হারা উজ্ঞো ডাক্তোর লই আয়</t>
+  </si>
+  <si>
+    <t>তোর বাবা খবরের কাগজ পড়ছে, চা-টা দিয়ে আয়</t>
+  </si>
+  <si>
+    <t>তোর বাফ হবরোর হাগজ পরের, চা ইবে দি আয়</t>
+  </si>
+  <si>
+    <t>সবাই টেবিলে চলে আসো, আজকে সবাই একসাথে নাস্তা করি</t>
+  </si>
+  <si>
+    <t>বিয়াজ্ঞুন টেবিলুত চলি আইয়্যু, আজিয়ে বিয়াজ্ঞুন এক্কোওয়ারে নাস্তা গরি</t>
+  </si>
+  <si>
+    <t>পিকনিকে গিয়ে আমরা একসাথে অনেক মজা করেছি</t>
+  </si>
+  <si>
+    <t>পিকনিকুত যায় রে আঁরা এক্কোওয়ারে বত মজা গইজ্জি</t>
+  </si>
+  <si>
+    <t>ভাত রান্নার আগে চালগুলো ভালভাবে ধুয়ে নিতে হবে</t>
+  </si>
+  <si>
+    <t>ভাত রান্দিবের আগে চইল এগুন ভালা গরি ধুই লন পরিবো</t>
+  </si>
+  <si>
+    <t>আমার কালো শার্টটি কোথায়? খুঁজে পাচ্ছি না যে</t>
+  </si>
+  <si>
+    <t>আঁর হালা শার্ট ইবে হনডে? থোয়াই ন পাইদ্দি</t>
+  </si>
+  <si>
+    <t>আমার হাত পা ব্যথা করছে</t>
+  </si>
+  <si>
+    <t>আঁর আত পা ব্যথা গরের</t>
+  </si>
+  <si>
+    <t>কয়েকদিন ঠিকমতো ঘুম না হলে মেজাজ এমনিতেই খিটখিটে হয়ে থাকে</t>
+  </si>
+  <si>
+    <t>হয়েকদিন ঠিকমতো ঘুম ন অইলি মেজাজ এনেই খিটখিট্টে অই যায়।</t>
+  </si>
+  <si>
+    <t>নাস্তা করে স্কুলের জন্য রেডি হও</t>
+  </si>
+  <si>
+    <t>নাস্তা গরি স্কুলুর লাই রেডি অও</t>
+  </si>
+  <si>
+    <t>স্যার যে হোমওয়ার্ক দিয়েছে সেগুলো করেছ?</t>
+  </si>
+  <si>
+    <t>স্যার যে হোমওয়ার্ক দিয়ি এগিন গইজ্জো?</t>
+  </si>
+  <si>
+    <t>প্রতিদিনের হোমওয়ার্ক প্রতিদিনই শেষ করে ফেলবে</t>
+  </si>
+  <si>
+    <t>পইত্তোদিনোর হোমওয়ার্ক পইত্তোদিনই শেষ গরি ফেলাইবে</t>
+  </si>
+  <si>
+    <t>হোমওয়ার্ক না করলে আমি ম্যাডামকে বলে দেবো</t>
+  </si>
+  <si>
+    <t>হোমওয়ার্ক ন গরিলি আঁই ম্যাডাম উরে হই দিয়্যুম</t>
+  </si>
+  <si>
+    <t>সারাদিন কম্পিউটারে বসে বসে কী করো?</t>
+  </si>
+  <si>
+    <t>পুরোদিন কম্পিউটারোত বই বই কি গরো?</t>
+  </si>
+  <si>
+    <t>বাসে বসে অনেকক্ষণ অপেক্ষা করতে হয়েছে</t>
+  </si>
+  <si>
+    <t>বাসোত বই রে বত হতক্ষন অপেক্ষা গরন পইজ্জি</t>
+  </si>
+  <si>
+    <t>রাস্তায় অনেক জ্যাম, আমার আসতে দেরি হবে</t>
+  </si>
+  <si>
+    <t>বাস্তাত বত জ্যাম, আত্তুন আইতে দেরি অইবু</t>
+  </si>
+  <si>
+    <t>জ্যামে বসে থাকতে থাকতে বিরক্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>জ্যামোত বই থাকতে থাকতে বিরক্ত অই গেই</t>
+  </si>
+  <si>
+    <t>আমার কার্টুন দেখতে অনেক ভাল লাগে</t>
+  </si>
+  <si>
+    <t>আত্তুন কার্টুন চাইতে বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>মা দুপুরে ভাতের সঙ্গে মাছ রান্না করেছেন</t>
+  </si>
+  <si>
+    <t>আম্মু দুইজ্জে ভাতোর লগে মাছ রান্না গইজ্জি</t>
+  </si>
+  <si>
+    <t>আজকে দুপুরে একটা বিয়ের দাওয়াত ছিল</t>
+  </si>
+  <si>
+    <t>আজিয়ে দুইজ্জে এক্কান বিয়ের দত আছিল</t>
+  </si>
+  <si>
+    <t>বিয়ে বাড়ির খাবারগুলো অনেক ভালো ছিল</t>
+  </si>
+  <si>
+    <t>বিয়ে বারির হানা এগিন বত ভালা আছিল</t>
+  </si>
+  <si>
+    <t>কারেন্ট এখনো আসেনি, এখন বসে বসে অপেক্ষা করা ছাড়া আর কী করার আছে?</t>
+  </si>
+  <si>
+    <t>কারোন এহনো ন আইয়্যি, এহন বই বই অপেক্ষা গরন ছারা আর কি গরিবের আছে?</t>
+  </si>
+  <si>
+    <t>রাতের জন্য ফুলকপির তরকারি আর বেগুন ভর্তা আছে</t>
+  </si>
+  <si>
+    <t>রাতিয়ের লাই ফুলহপির তরহারি আর বেইয়ুন চান্নি আছে</t>
+  </si>
+  <si>
+    <t>দুপুরে ভাত খেয়ে একটু বিশ্রাম নিলে ভাল লাগে</t>
+  </si>
+  <si>
+    <t>দুইজ্জে ভাত হায় এক্কানা জিরেই লইলি ভালা লাগে</t>
+  </si>
+  <si>
+    <t>দুপুরের পর ঘুমালে আমার মাথা ব্যথা করে</t>
+  </si>
+  <si>
+    <t>দুইরগের পর ঘুম যাইলি আত্তুন মাথা ব্যথা গরে</t>
+  </si>
+  <si>
+    <t>দুপুরে ভাত খেয়ে একটু ঘুমিয়েছিলাম, কিছুক্ষণ পর উঠে দেখি সন্ধ্যা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>দুইজ্জে ভাত হায় এক্কানা ঘুম গেইলাম, হতক্ষন পরে উডি দেহি আজুইন্নে অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>মা, আমি বন্ধুর সাথে বিকেলে একটু হাঁটতে বের হব</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁই বন্ধুর লগে বিয়েলে এক্কানা আইটতাম বাইর অইয়্যুম</t>
+  </si>
+  <si>
+    <t>ইশতিয়াক একটু শোনো, তোমার ছোট ভাইকে একটু পার্ক থেকে ঘুরিয়ে নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>ইশতিয়াক এক্কানা উনো, তোঁয়ার ছোডো ভাই রে এক্কানা পার্ক উত্তুন ঘুরাই আনো</t>
+  </si>
+  <si>
+    <t>আর বেশি সময় বাকি নেই, আরেকটু পরে অনুষ্ঠান শুরু হবে</t>
+  </si>
+  <si>
+    <t>আর বেশি সময় বাকি নেই, আরেক্কানা পরে অনুষ্ঠান শুরু অইবু</t>
+  </si>
+  <si>
+    <t>সারাদিন বন্ধুদের সাথে ঘুরাঘুরি করলে পড়ালেখা কখন করবে?</t>
+  </si>
+  <si>
+    <t>পুরোদিন বন্ধু অক্কলোর লগে ঘুরাঘুরি গরিলি পরালেহা হত্তে গরিবে?</t>
+  </si>
+  <si>
+    <t>বন্ধুদের সাথে আড্ডা না দিয়ে জলদি ঘরে এসে পড়তে বস</t>
+  </si>
+  <si>
+    <t>বন্ধু অক্কলোর লগে আড্ডা ন দি হারা ঘরোত আই রে পইত্তো বই</t>
+  </si>
+  <si>
+    <t>সূর্য ডোবার আগেই ঘরে আয়, নাহয় মার খাবি আমার হাতে</t>
+  </si>
+  <si>
+    <t>সূর্য ডোফিবের আগেই ঘরোত আই, নইলি মাইর হাবি আঁর আতুত</t>
+  </si>
+  <si>
+    <t>মুখ হাত ধোয়ে তোর আপুর কাছে পড়তে বস</t>
+  </si>
+  <si>
+    <t>মুখ আত ধুয় রে তোর আফাত্তুন পইত্তো বই</t>
+  </si>
+  <si>
+    <t>আমি সবজি দিয়ে ভাত খাব না, আমাকে মাংস দাও</t>
+  </si>
+  <si>
+    <t>আঁই সবজি দি ভাত হাইতাম ন, আঁরে গোস্ত দও</t>
+  </si>
+  <si>
+    <t>মুরগির মাংসের চেয়ে ডাল আর আলু ভর্তা বেশি ভালো লাগে</t>
+  </si>
+  <si>
+    <t>কুরো গোস্তত্তুন বর ডেইল আর আলুচ চান্নি বেশি ভালা লাগে</t>
+  </si>
+  <si>
+    <t>রান্নাঘরটা বেশি ময়লা হয়ে গেছে, আজকে পরিষ্কার করতে হবে</t>
+  </si>
+  <si>
+    <t>রান্নাঘর ইয়েন বেশি হাচারা অই গেইয়্যি, আজিয়ে পরিষ্কার গরি ফেলন পরিবু</t>
+  </si>
+  <si>
+    <t>খাওয়ার পর থালাবাসন ধোয়ে রান্নাঘরটা পরিষ্কার করে রাখিও</t>
+  </si>
+  <si>
+    <t>হন'উর পর থালবাসোন ধুয় রে রান্নাঘর ইয়েন পরিষ্কার গরি রাইক্কো</t>
+  </si>
+  <si>
+    <t>তুমি ঘুমাতে যাও, আজকে আমি পরিষ্কার করে দিচ্ছি</t>
+  </si>
+  <si>
+    <t>তুঁই ঘুমাইতো যও, আজিয়ে আঁই পরিষ্কার গরি দির</t>
   </si>
 </sst>
 </file>
@@ -7555,204 +7855,404 @@
       </c>
     </row>
     <row r="452" ht="25" customHeight="1" spans="1:2">
-      <c r="A452" s="2"/>
-      <c r="B452" s="2"/>
+      <c r="A452" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="453" ht="25" customHeight="1" spans="1:2">
-      <c r="A453" s="2"/>
-      <c r="B453" s="2"/>
+      <c r="A453" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="454" ht="25" customHeight="1" spans="1:2">
-      <c r="A454" s="2"/>
-      <c r="B454" s="2"/>
+      <c r="A454" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="455" ht="25" customHeight="1" spans="1:2">
-      <c r="A455" s="2"/>
-      <c r="B455" s="2"/>
+      <c r="A455" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="456" ht="25" customHeight="1" spans="1:2">
-      <c r="A456" s="2"/>
-      <c r="B456" s="2"/>
+      <c r="A456" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="457" ht="25" customHeight="1" spans="1:2">
-      <c r="A457" s="2"/>
-      <c r="B457" s="2"/>
+      <c r="A457" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="458" ht="25" customHeight="1" spans="1:2">
-      <c r="A458" s="2"/>
-      <c r="B458" s="2"/>
+      <c r="A458" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="459" ht="25" customHeight="1" spans="1:2">
-      <c r="A459" s="2"/>
-      <c r="B459" s="2"/>
+      <c r="A459" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="460" ht="25" customHeight="1" spans="1:2">
-      <c r="A460" s="2"/>
-      <c r="B460" s="2"/>
+      <c r="A460" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="461" ht="25" customHeight="1" spans="1:2">
-      <c r="A461" s="2"/>
-      <c r="B461" s="2"/>
+      <c r="A461" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="462" ht="25" customHeight="1" spans="1:2">
-      <c r="A462" s="2"/>
-      <c r="B462" s="2"/>
+      <c r="A462" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="463" ht="25" customHeight="1" spans="1:2">
-      <c r="A463" s="2"/>
-      <c r="B463" s="2"/>
+      <c r="A463" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="464" ht="25" customHeight="1" spans="1:2">
-      <c r="A464" s="2"/>
-      <c r="B464" s="2"/>
+      <c r="A464" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="465" ht="25" customHeight="1" spans="1:2">
-      <c r="A465" s="2"/>
-      <c r="B465" s="2"/>
+      <c r="A465" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="466" ht="25" customHeight="1" spans="1:2">
-      <c r="A466" s="2"/>
-      <c r="B466" s="2"/>
+      <c r="A466" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="467" ht="25" customHeight="1" spans="1:2">
-      <c r="A467" s="2"/>
-      <c r="B467" s="2"/>
+      <c r="A467" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="468" ht="25" customHeight="1" spans="1:2">
-      <c r="A468" s="2"/>
-      <c r="B468" s="2"/>
+      <c r="A468" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="469" ht="25" customHeight="1" spans="1:2">
-      <c r="A469" s="2"/>
-      <c r="B469" s="2"/>
+      <c r="A469" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="470" ht="25" customHeight="1" spans="1:2">
-      <c r="A470" s="2"/>
-      <c r="B470" s="2"/>
+      <c r="A470" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="471" ht="25" customHeight="1" spans="1:2">
-      <c r="A471" s="2"/>
-      <c r="B471" s="2"/>
+      <c r="A471" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="472" ht="25" customHeight="1" spans="1:2">
-      <c r="A472" s="2"/>
-      <c r="B472" s="2"/>
+      <c r="A472" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="473" ht="25" customHeight="1" spans="1:2">
-      <c r="A473" s="2"/>
-      <c r="B473" s="2"/>
+      <c r="A473" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="474" ht="25" customHeight="1" spans="1:2">
-      <c r="A474" s="2"/>
-      <c r="B474" s="2"/>
+      <c r="A474" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>942</v>
+      </c>
     </row>
     <row r="475" ht="25" customHeight="1" spans="1:2">
-      <c r="A475" s="2"/>
-      <c r="B475" s="2"/>
+      <c r="A475" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>944</v>
+      </c>
     </row>
     <row r="476" ht="25" customHeight="1" spans="1:2">
-      <c r="A476" s="2"/>
-      <c r="B476" s="2"/>
+      <c r="A476" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>946</v>
+      </c>
     </row>
     <row r="477" ht="25" customHeight="1" spans="1:2">
-      <c r="A477" s="2"/>
-      <c r="B477" s="2"/>
+      <c r="A477" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="478" ht="25" customHeight="1" spans="1:2">
-      <c r="A478" s="2"/>
-      <c r="B478" s="2"/>
+      <c r="A478" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="479" ht="25" customHeight="1" spans="1:2">
-      <c r="A479" s="2"/>
-      <c r="B479" s="2"/>
+      <c r="A479" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="480" ht="25" customHeight="1" spans="1:2">
-      <c r="A480" s="2"/>
-      <c r="B480" s="2"/>
+      <c r="A480" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>954</v>
+      </c>
     </row>
     <row r="481" ht="25" customHeight="1" spans="1:2">
-      <c r="A481" s="2"/>
-      <c r="B481" s="2"/>
+      <c r="A481" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="482" ht="25" customHeight="1" spans="1:2">
-      <c r="A482" s="2"/>
-      <c r="B482" s="2"/>
+      <c r="A482" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="483" ht="25" customHeight="1" spans="1:2">
-      <c r="A483" s="2"/>
-      <c r="B483" s="2"/>
+      <c r="A483" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>960</v>
+      </c>
     </row>
     <row r="484" ht="25" customHeight="1" spans="1:2">
-      <c r="A484" s="2"/>
-      <c r="B484" s="2"/>
+      <c r="A484" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="485" ht="25" customHeight="1" spans="1:2">
-      <c r="A485" s="2"/>
-      <c r="B485" s="2"/>
+      <c r="A485" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="486" ht="25" customHeight="1" spans="1:2">
-      <c r="A486" s="2"/>
-      <c r="B486" s="2"/>
+      <c r="A486" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="487" ht="25" customHeight="1" spans="1:2">
-      <c r="A487" s="2"/>
-      <c r="B487" s="2"/>
+      <c r="A487" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="488" ht="25" customHeight="1" spans="1:2">
-      <c r="A488" s="2"/>
-      <c r="B488" s="2"/>
+      <c r="A488" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>970</v>
+      </c>
     </row>
     <row r="489" ht="25" customHeight="1" spans="1:2">
-      <c r="A489" s="2"/>
-      <c r="B489" s="2"/>
+      <c r="A489" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="490" ht="25" customHeight="1" spans="1:2">
-      <c r="A490" s="2"/>
-      <c r="B490" s="2"/>
+      <c r="A490" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="491" ht="25" customHeight="1" spans="1:2">
-      <c r="A491" s="2"/>
-      <c r="B491" s="2"/>
+      <c r="A491" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="492" ht="25" customHeight="1" spans="1:2">
-      <c r="A492" s="2"/>
-      <c r="B492" s="2"/>
+      <c r="A492" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="493" ht="25" customHeight="1" spans="1:2">
-      <c r="A493" s="2"/>
-      <c r="B493" s="2"/>
+      <c r="A493" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="494" ht="25" customHeight="1" spans="1:2">
-      <c r="A494" s="2"/>
-      <c r="B494" s="2"/>
+      <c r="A494" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="495" ht="25" customHeight="1" spans="1:2">
-      <c r="A495" s="2"/>
-      <c r="B495" s="2"/>
+      <c r="A495" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>984</v>
+      </c>
     </row>
     <row r="496" ht="25" customHeight="1" spans="1:2">
-      <c r="A496" s="2"/>
-      <c r="B496" s="2"/>
+      <c r="A496" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>986</v>
+      </c>
     </row>
     <row r="497" ht="25" customHeight="1" spans="1:2">
-      <c r="A497" s="2"/>
-      <c r="B497" s="2"/>
+      <c r="A497" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="498" ht="25" customHeight="1" spans="1:2">
-      <c r="A498" s="2"/>
-      <c r="B498" s="2"/>
+      <c r="A498" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="499" ht="25" customHeight="1" spans="1:2">
-      <c r="A499" s="2"/>
-      <c r="B499" s="2"/>
+      <c r="A499" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>992</v>
+      </c>
     </row>
     <row r="500" ht="25" customHeight="1" spans="1:2">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
+      <c r="A500" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="501" ht="25" customHeight="1" spans="1:2">
-      <c r="A501" s="2"/>
-      <c r="B501" s="2"/>
+      <c r="A501" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>996</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="1007">
   <si>
     <t>bangla</t>
   </si>
@@ -485,7 +485,7 @@
     <t>তারপর বলব কি করতে হবে</t>
   </si>
   <si>
-    <t>তারপর হইয়্যুম কি গরন পরিবু</t>
+    <t>তারপর হইয়্যুম কি গরন ফরিবু</t>
   </si>
   <si>
     <t>আমি কতবার বললাম সাকিব, আমার কাজ আছে</t>
@@ -1422,10 +1422,10 @@
     <t>আত্তুন পেঠ ব্যাথা গরের দে এতেল্লে হাইত ন পাইজ্জুম</t>
   </si>
   <si>
-    <t>আমার মাথা ব্যাথা করছে বেশি, মনে হয় ঠাণ্ডা লেগে গেছে</t>
-  </si>
-  <si>
-    <t>আত্তুন মাথা ব্যাথা গরের বেশি, মনে অয় ঠাণ্ডা লাগি গেইয়্যি</t>
+    <t>আমার মাথা ব্যথা করছে বেশি, মনে হয় ঠাণ্ডা লেগে গেছে</t>
+  </si>
+  <si>
+    <t>আত্তুন মাথা ব্যথা গরের বেশি, মনে অয় ঠাণ্ডা লাগি গেইয়্যি</t>
   </si>
   <si>
     <t>এখন সকাল দশটা বাজে, এখনো কেন ঘুম থেকে উঠছিস না!</t>
@@ -1665,7 +1665,7 @@
     <t>জলদি যাও, সূর্য ডোবার আগে কাজ শেষ কর</t>
   </si>
   <si>
-    <t>হারা যও, সূর্য ডোফিবের আগে হাম শেষ গরো</t>
+    <t>হারা যও, সূর্য ডুবিবের আগে হাম শেষ গরো</t>
   </si>
   <si>
     <t>এবারের মরিচ ক্ষেত অনেক ভাল হয়েছে</t>
@@ -2385,7 +2385,7 @@
     <t>আজকে অফিসে যেতে হবে যে তাই আসতে পারব না</t>
   </si>
   <si>
-    <t>আজিয়ে অফিসুত যন পরিবু দে এতেল্লে আইসতাম পাইত্তাম নো</t>
+    <t>আজিয়ে অফিসুত যন ফরিবু দে এতেল্লে আইসতাম পাইত্তাম নো</t>
   </si>
   <si>
     <t>তোমার ভাই কে বলিও আমাকে কিছু টাকা ধার দিতে</t>
@@ -2547,7 +2547,7 @@
     <t>মানুষটা সারাদিন মাঠে কাজ করে</t>
   </si>
   <si>
-    <t>মানুষ ইবে ফুরোদিন মাডোত হাজ গরে</t>
+    <t>মানুষ ইবে আরাদিন মাডোত হাজ গরে</t>
   </si>
   <si>
     <t>মানুষটা সারাদিন ক্ষেতে কাজ করে</t>
@@ -2565,7 +2565,7 @@
     <t>এবার ধান ক্ষেতে পোকা হয়েছে বেশি, সেজন্য বিষ দিতে হবে</t>
   </si>
   <si>
-    <t>এবার ধান ক্ষেতিত ফুক অইয়্যি বেশি, এতেল্লে বিষ দন পরিবু</t>
+    <t>এবার ধান ক্ষেতিত ফুক অইয়্যি বেশি, এতেল্লে বিষ দন ফরিবু</t>
   </si>
   <si>
     <t>কারেন্ট বেশি ডিস্টার্ব করছে, একবার যাচ্ছে আবার আসছে</t>
@@ -2691,13 +2691,13 @@
     <t>কাপড়টা বেশি ময়লা হয়ে গেছে, ধুয়ে ফেলতে হবে আজকে</t>
   </si>
   <si>
-    <t>হর ইবে বেশি হাচারা অই গেইয়্যি, আজিয়ে ধুই ফেলন পরিবু</t>
+    <t>হর ইবে বেশি হাচারা অই গেইয়্যি, আজিয়ে ধুই ফেলন ফরিবু</t>
   </si>
   <si>
     <t>আজকে সব কিছু আনতে ভুলে গেছি, কাল আবারও বাজার করতে হবে</t>
   </si>
   <si>
-    <t>আজিয়ে কিছু জিনিস আনিবের লাই ভুলি গেই, হালিয়ে আবারও বাজার গরন পরিবু</t>
+    <t>আজিয়ে কিছু জিনিস আনিবের লাই ভুলি গেই, হালিয়ে আবারও বাজার গরন ফরিবু</t>
   </si>
   <si>
     <t>আজকে অনেক ক্লান্ত লাগছে, কাল থেকে আবারও শুরু করব</t>
@@ -3021,7 +3021,7 @@
     <t>সারাদিন বন্ধুদের সাথে ঘুরাঘুরি করলে পড়ালেখা কখন করবে?</t>
   </si>
   <si>
-    <t>পুরোদিন বন্ধু অক্কলোর লগে ঘুরাঘুরি গরিলি পরালেহা হত্তে গরিবে?</t>
+    <t>আরাদিন বন্ধু অক্কলোর লগে ঘুরাঘুরি গরিলি পরালেহা হত্তে গরিবে?</t>
   </si>
   <si>
     <t>বন্ধুদের সাথে আড্ডা না দিয়ে জলদি ঘরে এসে পড়তে বস</t>
@@ -3033,7 +3033,7 @@
     <t>সূর্য ডোবার আগেই ঘরে আয়, নাহয় মার খাবি আমার হাতে</t>
   </si>
   <si>
-    <t>সূর্য ডোফিবের আগেই ঘরোত আই, নইলি মাইর হাবি আঁর আতুত</t>
+    <t>সূর্য ডুবিবের আগেই ঘরোত আই, নইলি মাইর হাবি আঁর আতুত</t>
   </si>
   <si>
     <t>মুখ হাত ধোয়ে তোর আপুর কাছে পড়তে বস</t>
@@ -3057,19 +3057,49 @@
     <t>রান্নাঘরটা বেশি ময়লা হয়ে গেছে, আজকে পরিষ্কার করতে হবে</t>
   </si>
   <si>
-    <t>রান্নাঘর ইয়েন বেশি হাচারা অই গেইয়্যি, আজিয়ে পরিষ্কার গরি ফেলন পরিবু</t>
+    <t>বসহানা ইয়েন বেশি হাচারা অই গেইয়্যি, আজিয়ে সাফ গরি ফেলন ফরিবু</t>
   </si>
   <si>
     <t>খাওয়ার পর থালাবাসন ধোয়ে রান্নাঘরটা পরিষ্কার করে রাখিও</t>
   </si>
   <si>
-    <t>হন'উর পর থালবাসোন ধুয় রে রান্নাঘর ইয়েন পরিষ্কার গরি রাইক্কো</t>
+    <t>হন'উর পর বাসনহুটারা ধুয় রে বসহানা ইয়েন পরিষ্কার গরি রাইক্কো</t>
   </si>
   <si>
     <t>তুমি ঘুমাতে যাও, আজকে আমি পরিষ্কার করে দিচ্ছি</t>
   </si>
   <si>
-    <t>তুঁই ঘুমাইতো যও, আজিয়ে আঁই পরিষ্কার গরি দির</t>
+    <t>তুঁই ঘুমাইতো যও, আজিয়ে আঁই সাফ গরি দির</t>
+  </si>
+  <si>
+    <t>উঠানে অনেক ময়লা হয়েছে, ঝাড়ু দিতে হবে আজকে</t>
+  </si>
+  <si>
+    <t>উডোনোত বত হাচারা অইয়্যি, ঝারু দন ফরিবু আজিয়ে</t>
+  </si>
+  <si>
+    <t>এত বড় উঠানে ঝাড়ু দেওয়া অনেক কষ্টকর</t>
+  </si>
+  <si>
+    <t>এত্ত বরো উডোনোত ঝারু দন বত হষ্ট</t>
+  </si>
+  <si>
+    <t>বাতাসের কারনে আম গাছের আমগুলো সব উঠানে পড়ে গেছে</t>
+  </si>
+  <si>
+    <t>বাতাসোর হারনে আম গাছোর আম এগুন বিয়াক উডোনোত পরি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বিকালে উঠোনে বসে বসে চা খেতে অনেক ভাল লাগে</t>
+  </si>
+  <si>
+    <t>বিয়েলে উডোনোত বই বই চা হাইতে বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>আমার যখন মন খারাপ থাকে তখন আমি উঠোনে পুকুরের পাশে বসে থাকি</t>
+  </si>
+  <si>
+    <t>আত্তুন যহন মন হারাপ থাহে তহন আঁই উডোনোত ফইরোর পাশে বই থাহি</t>
   </si>
 </sst>
 </file>
@@ -4240,7 +4270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B1001"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="90.7777777777778" customWidth="1"/>
@@ -8254,6 +8284,2026 @@
         <v>996</v>
       </c>
     </row>
+    <row r="502" ht="25" customHeight="1" spans="1:2">
+      <c r="A502" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="503" ht="25" customHeight="1" spans="1:2">
+      <c r="A503" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="504" ht="25" customHeight="1" spans="1:2">
+      <c r="A504" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="505" ht="25" customHeight="1" spans="1:2">
+      <c r="A505" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="506" ht="25" customHeight="1" spans="1:2">
+      <c r="A506" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="507" ht="25" customHeight="1" spans="1:2">
+      <c r="A507" s="2"/>
+      <c r="B507" s="2"/>
+    </row>
+    <row r="508" ht="25" customHeight="1" spans="1:2">
+      <c r="A508" s="2"/>
+      <c r="B508" s="2"/>
+    </row>
+    <row r="509" ht="25" customHeight="1" spans="1:2">
+      <c r="A509" s="2"/>
+      <c r="B509" s="2"/>
+    </row>
+    <row r="510" ht="25" customHeight="1" spans="1:2">
+      <c r="A510" s="2"/>
+      <c r="B510" s="2"/>
+    </row>
+    <row r="511" ht="25" customHeight="1" spans="1:2">
+      <c r="A511" s="2"/>
+      <c r="B511" s="2"/>
+    </row>
+    <row r="512" ht="25" customHeight="1" spans="1:2">
+      <c r="A512" s="2"/>
+      <c r="B512" s="2"/>
+    </row>
+    <row r="513" ht="25" customHeight="1" spans="1:2">
+      <c r="A513" s="2"/>
+      <c r="B513" s="2"/>
+    </row>
+    <row r="514" ht="25" customHeight="1" spans="1:2">
+      <c r="A514" s="2"/>
+      <c r="B514" s="2"/>
+    </row>
+    <row r="515" ht="25" customHeight="1" spans="1:2">
+      <c r="A515" s="2"/>
+      <c r="B515" s="2"/>
+    </row>
+    <row r="516" ht="25" customHeight="1" spans="1:2">
+      <c r="A516" s="2"/>
+      <c r="B516" s="2"/>
+    </row>
+    <row r="517" ht="25" customHeight="1" spans="1:2">
+      <c r="A517" s="2"/>
+      <c r="B517" s="2"/>
+    </row>
+    <row r="518" ht="25" customHeight="1" spans="1:2">
+      <c r="A518" s="2"/>
+      <c r="B518" s="2"/>
+    </row>
+    <row r="519" ht="25" customHeight="1" spans="1:2">
+      <c r="A519" s="2"/>
+      <c r="B519" s="2"/>
+    </row>
+    <row r="520" ht="25" customHeight="1" spans="1:2">
+      <c r="A520" s="2"/>
+      <c r="B520" s="2"/>
+    </row>
+    <row r="521" ht="25" customHeight="1" spans="1:2">
+      <c r="A521" s="2"/>
+      <c r="B521" s="2"/>
+    </row>
+    <row r="522" ht="25" customHeight="1" spans="1:2">
+      <c r="A522" s="2"/>
+      <c r="B522" s="2"/>
+    </row>
+    <row r="523" ht="25" customHeight="1" spans="1:2">
+      <c r="A523" s="2"/>
+      <c r="B523" s="2"/>
+    </row>
+    <row r="524" ht="25" customHeight="1" spans="1:2">
+      <c r="A524" s="2"/>
+      <c r="B524" s="2"/>
+    </row>
+    <row r="525" ht="25" customHeight="1" spans="1:2">
+      <c r="A525" s="2"/>
+      <c r="B525" s="2"/>
+    </row>
+    <row r="526" ht="25" customHeight="1" spans="1:2">
+      <c r="A526" s="2"/>
+      <c r="B526" s="2"/>
+    </row>
+    <row r="527" ht="25" customHeight="1" spans="1:2">
+      <c r="A527" s="2"/>
+      <c r="B527" s="2"/>
+    </row>
+    <row r="528" ht="25" customHeight="1" spans="1:2">
+      <c r="A528" s="2"/>
+      <c r="B528" s="2"/>
+    </row>
+    <row r="529" ht="25" customHeight="1" spans="1:2">
+      <c r="A529" s="2"/>
+      <c r="B529" s="2"/>
+    </row>
+    <row r="530" ht="25" customHeight="1" spans="1:2">
+      <c r="A530" s="2"/>
+      <c r="B530" s="2"/>
+    </row>
+    <row r="531" ht="25" customHeight="1" spans="1:2">
+      <c r="A531" s="2"/>
+      <c r="B531" s="2"/>
+    </row>
+    <row r="532" ht="25" customHeight="1" spans="1:2">
+      <c r="A532" s="2"/>
+      <c r="B532" s="2"/>
+    </row>
+    <row r="533" ht="25" customHeight="1" spans="1:2">
+      <c r="A533" s="2"/>
+      <c r="B533" s="2"/>
+    </row>
+    <row r="534" ht="25" customHeight="1" spans="1:2">
+      <c r="A534" s="2"/>
+      <c r="B534" s="2"/>
+    </row>
+    <row r="535" ht="25" customHeight="1" spans="1:2">
+      <c r="A535" s="2"/>
+      <c r="B535" s="2"/>
+    </row>
+    <row r="536" ht="25" customHeight="1" spans="1:2">
+      <c r="A536" s="2"/>
+      <c r="B536" s="2"/>
+    </row>
+    <row r="537" ht="25" customHeight="1" spans="1:2">
+      <c r="A537" s="2"/>
+      <c r="B537" s="2"/>
+    </row>
+    <row r="538" ht="25" customHeight="1" spans="1:2">
+      <c r="A538" s="2"/>
+      <c r="B538" s="2"/>
+    </row>
+    <row r="539" ht="25" customHeight="1" spans="1:2">
+      <c r="A539" s="2"/>
+      <c r="B539" s="2"/>
+    </row>
+    <row r="540" ht="25" customHeight="1" spans="1:2">
+      <c r="A540" s="2"/>
+      <c r="B540" s="2"/>
+    </row>
+    <row r="541" ht="25" customHeight="1" spans="1:2">
+      <c r="A541" s="2"/>
+      <c r="B541" s="2"/>
+    </row>
+    <row r="542" ht="25" customHeight="1" spans="1:2">
+      <c r="A542" s="2"/>
+      <c r="B542" s="2"/>
+    </row>
+    <row r="543" ht="25" customHeight="1" spans="1:2">
+      <c r="A543" s="2"/>
+      <c r="B543" s="2"/>
+    </row>
+    <row r="544" ht="25" customHeight="1" spans="1:2">
+      <c r="A544" s="2"/>
+      <c r="B544" s="2"/>
+    </row>
+    <row r="545" ht="25" customHeight="1" spans="1:2">
+      <c r="A545" s="2"/>
+      <c r="B545" s="2"/>
+    </row>
+    <row r="546" ht="25" customHeight="1" spans="1:2">
+      <c r="A546" s="2"/>
+      <c r="B546" s="2"/>
+    </row>
+    <row r="547" ht="25" customHeight="1" spans="1:2">
+      <c r="A547" s="2"/>
+      <c r="B547" s="2"/>
+    </row>
+    <row r="548" ht="25" customHeight="1" spans="1:2">
+      <c r="A548" s="2"/>
+      <c r="B548" s="2"/>
+    </row>
+    <row r="549" ht="25" customHeight="1" spans="1:2">
+      <c r="A549" s="2"/>
+      <c r="B549" s="2"/>
+    </row>
+    <row r="550" ht="25" customHeight="1" spans="1:2">
+      <c r="A550" s="2"/>
+      <c r="B550" s="2"/>
+    </row>
+    <row r="551" ht="25" customHeight="1" spans="1:2">
+      <c r="A551" s="2"/>
+      <c r="B551" s="2"/>
+    </row>
+    <row r="552" ht="25" customHeight="1" spans="1:2">
+      <c r="A552" s="2"/>
+      <c r="B552" s="2"/>
+    </row>
+    <row r="553" ht="25" customHeight="1" spans="1:2">
+      <c r="A553" s="2"/>
+      <c r="B553" s="2"/>
+    </row>
+    <row r="554" ht="25" customHeight="1" spans="1:2">
+      <c r="A554" s="2"/>
+      <c r="B554" s="2"/>
+    </row>
+    <row r="555" ht="25" customHeight="1" spans="1:2">
+      <c r="A555" s="2"/>
+      <c r="B555" s="2"/>
+    </row>
+    <row r="556" ht="25" customHeight="1" spans="1:2">
+      <c r="A556" s="2"/>
+      <c r="B556" s="2"/>
+    </row>
+    <row r="557" ht="25" customHeight="1" spans="1:2">
+      <c r="A557" s="2"/>
+      <c r="B557" s="2"/>
+    </row>
+    <row r="558" ht="25" customHeight="1" spans="1:2">
+      <c r="A558" s="2"/>
+      <c r="B558" s="2"/>
+    </row>
+    <row r="559" ht="25" customHeight="1" spans="1:2">
+      <c r="A559" s="2"/>
+      <c r="B559" s="2"/>
+    </row>
+    <row r="560" ht="25" customHeight="1" spans="1:2">
+      <c r="A560" s="2"/>
+      <c r="B560" s="2"/>
+    </row>
+    <row r="561" ht="25" customHeight="1" spans="1:2">
+      <c r="A561" s="2"/>
+      <c r="B561" s="2"/>
+    </row>
+    <row r="562" ht="25" customHeight="1" spans="1:2">
+      <c r="A562" s="2"/>
+      <c r="B562" s="2"/>
+    </row>
+    <row r="563" ht="25" customHeight="1" spans="1:2">
+      <c r="A563" s="2"/>
+      <c r="B563" s="2"/>
+    </row>
+    <row r="564" ht="25" customHeight="1" spans="1:2">
+      <c r="A564" s="2"/>
+      <c r="B564" s="2"/>
+    </row>
+    <row r="565" ht="25" customHeight="1" spans="1:2">
+      <c r="A565" s="2"/>
+      <c r="B565" s="2"/>
+    </row>
+    <row r="566" ht="25" customHeight="1" spans="1:2">
+      <c r="A566" s="2"/>
+      <c r="B566" s="2"/>
+    </row>
+    <row r="567" ht="25" customHeight="1" spans="1:2">
+      <c r="A567" s="2"/>
+      <c r="B567" s="2"/>
+    </row>
+    <row r="568" ht="25" customHeight="1" spans="1:2">
+      <c r="A568" s="2"/>
+      <c r="B568" s="2"/>
+    </row>
+    <row r="569" ht="25" customHeight="1" spans="1:2">
+      <c r="A569" s="2"/>
+      <c r="B569" s="2"/>
+    </row>
+    <row r="570" ht="25" customHeight="1" spans="1:2">
+      <c r="A570" s="2"/>
+      <c r="B570" s="2"/>
+    </row>
+    <row r="571" ht="25" customHeight="1" spans="1:2">
+      <c r="A571" s="2"/>
+      <c r="B571" s="2"/>
+    </row>
+    <row r="572" ht="25" customHeight="1" spans="1:2">
+      <c r="A572" s="2"/>
+      <c r="B572" s="2"/>
+    </row>
+    <row r="573" ht="25" customHeight="1" spans="1:2">
+      <c r="A573" s="2"/>
+      <c r="B573" s="2"/>
+    </row>
+    <row r="574" ht="25" customHeight="1" spans="1:2">
+      <c r="A574" s="2"/>
+      <c r="B574" s="2"/>
+    </row>
+    <row r="575" ht="25" customHeight="1" spans="1:2">
+      <c r="A575" s="2"/>
+      <c r="B575" s="2"/>
+    </row>
+    <row r="576" ht="25" customHeight="1" spans="1:2">
+      <c r="A576" s="2"/>
+      <c r="B576" s="2"/>
+    </row>
+    <row r="577" ht="25" customHeight="1" spans="1:2">
+      <c r="A577" s="2"/>
+      <c r="B577" s="2"/>
+    </row>
+    <row r="578" ht="25" customHeight="1" spans="1:2">
+      <c r="A578" s="2"/>
+      <c r="B578" s="2"/>
+    </row>
+    <row r="579" ht="25" customHeight="1" spans="1:2">
+      <c r="A579" s="2"/>
+      <c r="B579" s="2"/>
+    </row>
+    <row r="580" ht="25" customHeight="1" spans="1:2">
+      <c r="A580" s="2"/>
+      <c r="B580" s="2"/>
+    </row>
+    <row r="581" ht="25" customHeight="1" spans="1:2">
+      <c r="A581" s="2"/>
+      <c r="B581" s="2"/>
+    </row>
+    <row r="582" ht="25" customHeight="1" spans="1:2">
+      <c r="A582" s="2"/>
+      <c r="B582" s="2"/>
+    </row>
+    <row r="583" ht="25" customHeight="1" spans="1:2">
+      <c r="A583" s="2"/>
+      <c r="B583" s="2"/>
+    </row>
+    <row r="584" ht="25" customHeight="1" spans="1:2">
+      <c r="A584" s="2"/>
+      <c r="B584" s="2"/>
+    </row>
+    <row r="585" ht="25" customHeight="1" spans="1:2">
+      <c r="A585" s="2"/>
+      <c r="B585" s="2"/>
+    </row>
+    <row r="586" ht="25" customHeight="1" spans="1:2">
+      <c r="A586" s="2"/>
+      <c r="B586" s="2"/>
+    </row>
+    <row r="587" ht="25" customHeight="1" spans="1:2">
+      <c r="A587" s="2"/>
+      <c r="B587" s="2"/>
+    </row>
+    <row r="588" ht="25" customHeight="1" spans="1:2">
+      <c r="A588" s="2"/>
+      <c r="B588" s="2"/>
+    </row>
+    <row r="589" ht="25" customHeight="1" spans="1:2">
+      <c r="A589" s="2"/>
+      <c r="B589" s="2"/>
+    </row>
+    <row r="590" ht="25" customHeight="1" spans="1:2">
+      <c r="A590" s="2"/>
+      <c r="B590" s="2"/>
+    </row>
+    <row r="591" ht="25" customHeight="1" spans="1:2">
+      <c r="A591" s="2"/>
+      <c r="B591" s="2"/>
+    </row>
+    <row r="592" ht="25" customHeight="1" spans="1:2">
+      <c r="A592" s="2"/>
+      <c r="B592" s="2"/>
+    </row>
+    <row r="593" ht="25" customHeight="1" spans="1:2">
+      <c r="A593" s="2"/>
+      <c r="B593" s="2"/>
+    </row>
+    <row r="594" ht="25" customHeight="1" spans="1:2">
+      <c r="A594" s="2"/>
+      <c r="B594" s="2"/>
+    </row>
+    <row r="595" ht="25" customHeight="1" spans="1:2">
+      <c r="A595" s="2"/>
+      <c r="B595" s="2"/>
+    </row>
+    <row r="596" ht="25" customHeight="1" spans="1:2">
+      <c r="A596" s="2"/>
+      <c r="B596" s="2"/>
+    </row>
+    <row r="597" ht="25" customHeight="1" spans="1:2">
+      <c r="A597" s="2"/>
+      <c r="B597" s="2"/>
+    </row>
+    <row r="598" ht="25" customHeight="1" spans="1:2">
+      <c r="A598" s="2"/>
+      <c r="B598" s="2"/>
+    </row>
+    <row r="599" ht="25" customHeight="1" spans="1:2">
+      <c r="A599" s="2"/>
+      <c r="B599" s="2"/>
+    </row>
+    <row r="600" ht="25" customHeight="1" spans="1:2">
+      <c r="A600" s="2"/>
+      <c r="B600" s="2"/>
+    </row>
+    <row r="601" ht="25" customHeight="1" spans="1:2">
+      <c r="A601" s="2"/>
+      <c r="B601" s="2"/>
+    </row>
+    <row r="602" ht="25" customHeight="1" spans="1:2">
+      <c r="A602" s="2"/>
+      <c r="B602" s="2"/>
+    </row>
+    <row r="603" ht="25" customHeight="1" spans="1:2">
+      <c r="A603" s="2"/>
+      <c r="B603" s="2"/>
+    </row>
+    <row r="604" ht="25" customHeight="1" spans="1:2">
+      <c r="A604" s="2"/>
+      <c r="B604" s="2"/>
+    </row>
+    <row r="605" ht="25" customHeight="1" spans="1:2">
+      <c r="A605" s="2"/>
+      <c r="B605" s="2"/>
+    </row>
+    <row r="606" ht="25" customHeight="1" spans="1:2">
+      <c r="A606" s="2"/>
+      <c r="B606" s="2"/>
+    </row>
+    <row r="607" ht="25" customHeight="1" spans="1:2">
+      <c r="A607" s="2"/>
+      <c r="B607" s="2"/>
+    </row>
+    <row r="608" ht="25" customHeight="1" spans="1:2">
+      <c r="A608" s="2"/>
+      <c r="B608" s="2"/>
+    </row>
+    <row r="609" ht="25" customHeight="1" spans="1:2">
+      <c r="A609" s="2"/>
+      <c r="B609" s="2"/>
+    </row>
+    <row r="610" ht="25" customHeight="1" spans="1:2">
+      <c r="A610" s="2"/>
+      <c r="B610" s="2"/>
+    </row>
+    <row r="611" ht="25" customHeight="1" spans="1:2">
+      <c r="A611" s="2"/>
+      <c r="B611" s="2"/>
+    </row>
+    <row r="612" ht="25" customHeight="1" spans="1:2">
+      <c r="A612" s="2"/>
+      <c r="B612" s="2"/>
+    </row>
+    <row r="613" ht="25" customHeight="1" spans="1:2">
+      <c r="A613" s="2"/>
+      <c r="B613" s="2"/>
+    </row>
+    <row r="614" ht="25" customHeight="1" spans="1:2">
+      <c r="A614" s="2"/>
+      <c r="B614" s="2"/>
+    </row>
+    <row r="615" ht="25" customHeight="1" spans="1:2">
+      <c r="A615" s="2"/>
+      <c r="B615" s="2"/>
+    </row>
+    <row r="616" ht="25" customHeight="1" spans="1:2">
+      <c r="A616" s="2"/>
+      <c r="B616" s="2"/>
+    </row>
+    <row r="617" ht="25" customHeight="1" spans="1:2">
+      <c r="A617" s="2"/>
+      <c r="B617" s="2"/>
+    </row>
+    <row r="618" ht="25" customHeight="1" spans="1:2">
+      <c r="A618" s="2"/>
+      <c r="B618" s="2"/>
+    </row>
+    <row r="619" ht="25" customHeight="1" spans="1:2">
+      <c r="A619" s="2"/>
+      <c r="B619" s="2"/>
+    </row>
+    <row r="620" ht="25" customHeight="1" spans="1:2">
+      <c r="A620" s="2"/>
+      <c r="B620" s="2"/>
+    </row>
+    <row r="621" ht="25" customHeight="1" spans="1:2">
+      <c r="A621" s="2"/>
+      <c r="B621" s="2"/>
+    </row>
+    <row r="622" ht="25" customHeight="1" spans="1:2">
+      <c r="A622" s="2"/>
+      <c r="B622" s="2"/>
+    </row>
+    <row r="623" ht="25" customHeight="1" spans="1:2">
+      <c r="A623" s="2"/>
+      <c r="B623" s="2"/>
+    </row>
+    <row r="624" ht="25" customHeight="1" spans="1:2">
+      <c r="A624" s="2"/>
+      <c r="B624" s="2"/>
+    </row>
+    <row r="625" ht="25" customHeight="1" spans="1:2">
+      <c r="A625" s="2"/>
+      <c r="B625" s="2"/>
+    </row>
+    <row r="626" ht="25" customHeight="1" spans="1:2">
+      <c r="A626" s="2"/>
+      <c r="B626" s="2"/>
+    </row>
+    <row r="627" ht="25" customHeight="1" spans="1:2">
+      <c r="A627" s="2"/>
+      <c r="B627" s="2"/>
+    </row>
+    <row r="628" ht="25" customHeight="1" spans="1:2">
+      <c r="A628" s="2"/>
+      <c r="B628" s="2"/>
+    </row>
+    <row r="629" ht="25" customHeight="1" spans="1:2">
+      <c r="A629" s="2"/>
+      <c r="B629" s="2"/>
+    </row>
+    <row r="630" ht="25" customHeight="1" spans="1:2">
+      <c r="A630" s="2"/>
+      <c r="B630" s="2"/>
+    </row>
+    <row r="631" ht="25" customHeight="1" spans="1:2">
+      <c r="A631" s="2"/>
+      <c r="B631" s="2"/>
+    </row>
+    <row r="632" ht="25" customHeight="1" spans="1:2">
+      <c r="A632" s="2"/>
+      <c r="B632" s="2"/>
+    </row>
+    <row r="633" ht="25" customHeight="1" spans="1:2">
+      <c r="A633" s="2"/>
+      <c r="B633" s="2"/>
+    </row>
+    <row r="634" ht="25" customHeight="1" spans="1:2">
+      <c r="A634" s="2"/>
+      <c r="B634" s="2"/>
+    </row>
+    <row r="635" ht="25" customHeight="1" spans="1:2">
+      <c r="A635" s="2"/>
+      <c r="B635" s="2"/>
+    </row>
+    <row r="636" ht="25" customHeight="1" spans="1:2">
+      <c r="A636" s="2"/>
+      <c r="B636" s="2"/>
+    </row>
+    <row r="637" ht="25" customHeight="1" spans="1:2">
+      <c r="A637" s="2"/>
+      <c r="B637" s="2"/>
+    </row>
+    <row r="638" ht="25" customHeight="1" spans="1:2">
+      <c r="A638" s="2"/>
+      <c r="B638" s="2"/>
+    </row>
+    <row r="639" ht="25" customHeight="1" spans="1:2">
+      <c r="A639" s="2"/>
+      <c r="B639" s="2"/>
+    </row>
+    <row r="640" ht="25" customHeight="1" spans="1:2">
+      <c r="A640" s="2"/>
+      <c r="B640" s="2"/>
+    </row>
+    <row r="641" ht="25" customHeight="1" spans="1:2">
+      <c r="A641" s="2"/>
+      <c r="B641" s="2"/>
+    </row>
+    <row r="642" ht="25" customHeight="1" spans="1:2">
+      <c r="A642" s="2"/>
+      <c r="B642" s="2"/>
+    </row>
+    <row r="643" ht="25" customHeight="1" spans="1:2">
+      <c r="A643" s="2"/>
+      <c r="B643" s="2"/>
+    </row>
+    <row r="644" ht="25" customHeight="1" spans="1:2">
+      <c r="A644" s="2"/>
+      <c r="B644" s="2"/>
+    </row>
+    <row r="645" ht="25" customHeight="1" spans="1:2">
+      <c r="A645" s="2"/>
+      <c r="B645" s="2"/>
+    </row>
+    <row r="646" ht="25" customHeight="1" spans="1:2">
+      <c r="A646" s="2"/>
+      <c r="B646" s="2"/>
+    </row>
+    <row r="647" ht="25" customHeight="1" spans="1:2">
+      <c r="A647" s="2"/>
+      <c r="B647" s="2"/>
+    </row>
+    <row r="648" ht="25" customHeight="1" spans="1:2">
+      <c r="A648" s="2"/>
+      <c r="B648" s="2"/>
+    </row>
+    <row r="649" ht="25" customHeight="1" spans="1:2">
+      <c r="A649" s="2"/>
+      <c r="B649" s="2"/>
+    </row>
+    <row r="650" ht="25" customHeight="1" spans="1:2">
+      <c r="A650" s="2"/>
+      <c r="B650" s="2"/>
+    </row>
+    <row r="651" ht="25" customHeight="1" spans="1:2">
+      <c r="A651" s="2"/>
+      <c r="B651" s="2"/>
+    </row>
+    <row r="652" ht="25" customHeight="1" spans="1:2">
+      <c r="A652" s="2"/>
+      <c r="B652" s="2"/>
+    </row>
+    <row r="653" ht="25" customHeight="1" spans="1:2">
+      <c r="A653" s="2"/>
+      <c r="B653" s="2"/>
+    </row>
+    <row r="654" ht="25" customHeight="1" spans="1:2">
+      <c r="A654" s="2"/>
+      <c r="B654" s="2"/>
+    </row>
+    <row r="655" ht="25" customHeight="1" spans="1:2">
+      <c r="A655" s="2"/>
+      <c r="B655" s="2"/>
+    </row>
+    <row r="656" ht="25" customHeight="1" spans="1:2">
+      <c r="A656" s="2"/>
+      <c r="B656" s="2"/>
+    </row>
+    <row r="657" ht="25" customHeight="1" spans="1:2">
+      <c r="A657" s="2"/>
+      <c r="B657" s="2"/>
+    </row>
+    <row r="658" ht="25" customHeight="1" spans="1:2">
+      <c r="A658" s="2"/>
+      <c r="B658" s="2"/>
+    </row>
+    <row r="659" ht="25" customHeight="1" spans="1:2">
+      <c r="A659" s="2"/>
+      <c r="B659" s="2"/>
+    </row>
+    <row r="660" ht="25" customHeight="1" spans="1:2">
+      <c r="A660" s="2"/>
+      <c r="B660" s="2"/>
+    </row>
+    <row r="661" ht="25" customHeight="1" spans="1:2">
+      <c r="A661" s="2"/>
+      <c r="B661" s="2"/>
+    </row>
+    <row r="662" ht="25" customHeight="1" spans="1:2">
+      <c r="A662" s="2"/>
+      <c r="B662" s="2"/>
+    </row>
+    <row r="663" ht="25" customHeight="1" spans="1:2">
+      <c r="A663" s="2"/>
+      <c r="B663" s="2"/>
+    </row>
+    <row r="664" ht="25" customHeight="1" spans="1:2">
+      <c r="A664" s="2"/>
+      <c r="B664" s="2"/>
+    </row>
+    <row r="665" ht="25" customHeight="1" spans="1:2">
+      <c r="A665" s="2"/>
+      <c r="B665" s="2"/>
+    </row>
+    <row r="666" ht="25" customHeight="1" spans="1:2">
+      <c r="A666" s="2"/>
+      <c r="B666" s="2"/>
+    </row>
+    <row r="667" ht="25" customHeight="1" spans="1:2">
+      <c r="A667" s="2"/>
+      <c r="B667" s="2"/>
+    </row>
+    <row r="668" ht="25" customHeight="1" spans="1:2">
+      <c r="A668" s="2"/>
+      <c r="B668" s="2"/>
+    </row>
+    <row r="669" ht="25" customHeight="1" spans="1:2">
+      <c r="A669" s="2"/>
+      <c r="B669" s="2"/>
+    </row>
+    <row r="670" ht="25" customHeight="1" spans="1:2">
+      <c r="A670" s="2"/>
+      <c r="B670" s="2"/>
+    </row>
+    <row r="671" ht="25" customHeight="1" spans="1:2">
+      <c r="A671" s="2"/>
+      <c r="B671" s="2"/>
+    </row>
+    <row r="672" ht="25" customHeight="1" spans="1:2">
+      <c r="A672" s="2"/>
+      <c r="B672" s="2"/>
+    </row>
+    <row r="673" ht="25" customHeight="1" spans="1:2">
+      <c r="A673" s="2"/>
+      <c r="B673" s="2"/>
+    </row>
+    <row r="674" ht="25" customHeight="1" spans="1:2">
+      <c r="A674" s="2"/>
+      <c r="B674" s="2"/>
+    </row>
+    <row r="675" ht="25" customHeight="1" spans="1:2">
+      <c r="A675" s="2"/>
+      <c r="B675" s="2"/>
+    </row>
+    <row r="676" ht="25" customHeight="1" spans="1:2">
+      <c r="A676" s="2"/>
+      <c r="B676" s="2"/>
+    </row>
+    <row r="677" ht="25" customHeight="1" spans="1:2">
+      <c r="A677" s="2"/>
+      <c r="B677" s="2"/>
+    </row>
+    <row r="678" ht="25" customHeight="1" spans="1:2">
+      <c r="A678" s="2"/>
+      <c r="B678" s="2"/>
+    </row>
+    <row r="679" ht="25" customHeight="1" spans="1:2">
+      <c r="A679" s="2"/>
+      <c r="B679" s="2"/>
+    </row>
+    <row r="680" ht="25" customHeight="1" spans="1:2">
+      <c r="A680" s="2"/>
+      <c r="B680" s="2"/>
+    </row>
+    <row r="681" ht="25" customHeight="1" spans="1:2">
+      <c r="A681" s="2"/>
+      <c r="B681" s="2"/>
+    </row>
+    <row r="682" ht="25" customHeight="1" spans="1:2">
+      <c r="A682" s="2"/>
+      <c r="B682" s="2"/>
+    </row>
+    <row r="683" ht="25" customHeight="1" spans="1:2">
+      <c r="A683" s="2"/>
+      <c r="B683" s="2"/>
+    </row>
+    <row r="684" ht="25" customHeight="1" spans="1:2">
+      <c r="A684" s="2"/>
+      <c r="B684" s="2"/>
+    </row>
+    <row r="685" ht="25" customHeight="1" spans="1:2">
+      <c r="A685" s="2"/>
+      <c r="B685" s="2"/>
+    </row>
+    <row r="686" ht="25" customHeight="1" spans="1:2">
+      <c r="A686" s="2"/>
+      <c r="B686" s="2"/>
+    </row>
+    <row r="687" ht="25" customHeight="1" spans="1:2">
+      <c r="A687" s="2"/>
+      <c r="B687" s="2"/>
+    </row>
+    <row r="688" ht="25" customHeight="1" spans="1:2">
+      <c r="A688" s="2"/>
+      <c r="B688" s="2"/>
+    </row>
+    <row r="689" ht="25" customHeight="1" spans="1:2">
+      <c r="A689" s="2"/>
+      <c r="B689" s="2"/>
+    </row>
+    <row r="690" ht="25" customHeight="1" spans="1:2">
+      <c r="A690" s="2"/>
+      <c r="B690" s="2"/>
+    </row>
+    <row r="691" ht="25" customHeight="1" spans="1:2">
+      <c r="A691" s="2"/>
+      <c r="B691" s="2"/>
+    </row>
+    <row r="692" ht="25" customHeight="1" spans="1:2">
+      <c r="A692" s="2"/>
+      <c r="B692" s="2"/>
+    </row>
+    <row r="693" ht="25" customHeight="1" spans="1:2">
+      <c r="A693" s="2"/>
+      <c r="B693" s="2"/>
+    </row>
+    <row r="694" ht="25" customHeight="1" spans="1:2">
+      <c r="A694" s="2"/>
+      <c r="B694" s="2"/>
+    </row>
+    <row r="695" ht="25" customHeight="1" spans="1:2">
+      <c r="A695" s="2"/>
+      <c r="B695" s="2"/>
+    </row>
+    <row r="696" ht="25" customHeight="1" spans="1:2">
+      <c r="A696" s="2"/>
+      <c r="B696" s="2"/>
+    </row>
+    <row r="697" ht="25" customHeight="1" spans="1:2">
+      <c r="A697" s="2"/>
+      <c r="B697" s="2"/>
+    </row>
+    <row r="698" ht="25" customHeight="1" spans="1:2">
+      <c r="A698" s="2"/>
+      <c r="B698" s="2"/>
+    </row>
+    <row r="699" ht="25" customHeight="1" spans="1:2">
+      <c r="A699" s="2"/>
+      <c r="B699" s="2"/>
+    </row>
+    <row r="700" ht="25" customHeight="1" spans="1:2">
+      <c r="A700" s="2"/>
+      <c r="B700" s="2"/>
+    </row>
+    <row r="701" ht="25" customHeight="1" spans="1:2">
+      <c r="A701" s="2"/>
+      <c r="B701" s="2"/>
+    </row>
+    <row r="702" ht="25" customHeight="1" spans="1:2">
+      <c r="A702" s="2"/>
+      <c r="B702" s="2"/>
+    </row>
+    <row r="703" ht="25" customHeight="1" spans="1:2">
+      <c r="A703" s="2"/>
+      <c r="B703" s="2"/>
+    </row>
+    <row r="704" ht="25" customHeight="1" spans="1:2">
+      <c r="A704" s="2"/>
+      <c r="B704" s="2"/>
+    </row>
+    <row r="705" ht="25" customHeight="1" spans="1:2">
+      <c r="A705" s="2"/>
+      <c r="B705" s="2"/>
+    </row>
+    <row r="706" ht="25" customHeight="1" spans="1:2">
+      <c r="A706" s="2"/>
+      <c r="B706" s="2"/>
+    </row>
+    <row r="707" ht="25" customHeight="1" spans="1:2">
+      <c r="A707" s="2"/>
+      <c r="B707" s="2"/>
+    </row>
+    <row r="708" ht="25" customHeight="1" spans="1:2">
+      <c r="A708" s="2"/>
+      <c r="B708" s="2"/>
+    </row>
+    <row r="709" ht="25" customHeight="1" spans="1:2">
+      <c r="A709" s="2"/>
+      <c r="B709" s="2"/>
+    </row>
+    <row r="710" ht="25" customHeight="1" spans="1:2">
+      <c r="A710" s="2"/>
+      <c r="B710" s="2"/>
+    </row>
+    <row r="711" ht="25" customHeight="1" spans="1:2">
+      <c r="A711" s="2"/>
+      <c r="B711" s="2"/>
+    </row>
+    <row r="712" ht="25" customHeight="1" spans="1:2">
+      <c r="A712" s="2"/>
+      <c r="B712" s="2"/>
+    </row>
+    <row r="713" ht="25" customHeight="1" spans="1:2">
+      <c r="A713" s="2"/>
+      <c r="B713" s="2"/>
+    </row>
+    <row r="714" ht="25" customHeight="1" spans="1:2">
+      <c r="A714" s="2"/>
+      <c r="B714" s="2"/>
+    </row>
+    <row r="715" ht="25" customHeight="1" spans="1:2">
+      <c r="A715" s="2"/>
+      <c r="B715" s="2"/>
+    </row>
+    <row r="716" ht="25" customHeight="1" spans="1:2">
+      <c r="A716" s="2"/>
+      <c r="B716" s="2"/>
+    </row>
+    <row r="717" ht="25" customHeight="1" spans="1:2">
+      <c r="A717" s="2"/>
+      <c r="B717" s="2"/>
+    </row>
+    <row r="718" ht="25" customHeight="1" spans="1:2">
+      <c r="A718" s="2"/>
+      <c r="B718" s="2"/>
+    </row>
+    <row r="719" ht="25" customHeight="1" spans="1:2">
+      <c r="A719" s="2"/>
+      <c r="B719" s="2"/>
+    </row>
+    <row r="720" ht="25" customHeight="1" spans="1:2">
+      <c r="A720" s="2"/>
+      <c r="B720" s="2"/>
+    </row>
+    <row r="721" ht="25" customHeight="1" spans="1:2">
+      <c r="A721" s="2"/>
+      <c r="B721" s="2"/>
+    </row>
+    <row r="722" ht="25" customHeight="1" spans="1:2">
+      <c r="A722" s="2"/>
+      <c r="B722" s="2"/>
+    </row>
+    <row r="723" ht="25" customHeight="1" spans="1:2">
+      <c r="A723" s="2"/>
+      <c r="B723" s="2"/>
+    </row>
+    <row r="724" ht="25" customHeight="1" spans="1:2">
+      <c r="A724" s="2"/>
+      <c r="B724" s="2"/>
+    </row>
+    <row r="725" ht="25" customHeight="1" spans="1:2">
+      <c r="A725" s="2"/>
+      <c r="B725" s="2"/>
+    </row>
+    <row r="726" ht="25" customHeight="1" spans="1:2">
+      <c r="A726" s="2"/>
+      <c r="B726" s="2"/>
+    </row>
+    <row r="727" ht="25" customHeight="1" spans="1:2">
+      <c r="A727" s="2"/>
+      <c r="B727" s="2"/>
+    </row>
+    <row r="728" ht="25" customHeight="1" spans="1:2">
+      <c r="A728" s="2"/>
+      <c r="B728" s="2"/>
+    </row>
+    <row r="729" ht="25" customHeight="1" spans="1:2">
+      <c r="A729" s="2"/>
+      <c r="B729" s="2"/>
+    </row>
+    <row r="730" ht="25" customHeight="1" spans="1:2">
+      <c r="A730" s="2"/>
+      <c r="B730" s="2"/>
+    </row>
+    <row r="731" ht="25" customHeight="1" spans="1:2">
+      <c r="A731" s="2"/>
+      <c r="B731" s="2"/>
+    </row>
+    <row r="732" ht="25" customHeight="1" spans="1:2">
+      <c r="A732" s="2"/>
+      <c r="B732" s="2"/>
+    </row>
+    <row r="733" ht="25" customHeight="1" spans="1:2">
+      <c r="A733" s="2"/>
+      <c r="B733" s="2"/>
+    </row>
+    <row r="734" ht="25" customHeight="1" spans="1:2">
+      <c r="A734" s="2"/>
+      <c r="B734" s="2"/>
+    </row>
+    <row r="735" ht="25" customHeight="1" spans="1:2">
+      <c r="A735" s="2"/>
+      <c r="B735" s="2"/>
+    </row>
+    <row r="736" ht="25" customHeight="1" spans="1:2">
+      <c r="A736" s="2"/>
+      <c r="B736" s="2"/>
+    </row>
+    <row r="737" ht="25" customHeight="1" spans="1:2">
+      <c r="A737" s="2"/>
+      <c r="B737" s="2"/>
+    </row>
+    <row r="738" ht="25" customHeight="1" spans="1:2">
+      <c r="A738" s="2"/>
+      <c r="B738" s="2"/>
+    </row>
+    <row r="739" ht="25" customHeight="1" spans="1:2">
+      <c r="A739" s="2"/>
+      <c r="B739" s="2"/>
+    </row>
+    <row r="740" ht="25" customHeight="1" spans="1:2">
+      <c r="A740" s="2"/>
+      <c r="B740" s="2"/>
+    </row>
+    <row r="741" ht="25" customHeight="1" spans="1:2">
+      <c r="A741" s="2"/>
+      <c r="B741" s="2"/>
+    </row>
+    <row r="742" ht="25" customHeight="1" spans="1:2">
+      <c r="A742" s="2"/>
+      <c r="B742" s="2"/>
+    </row>
+    <row r="743" ht="25" customHeight="1" spans="1:2">
+      <c r="A743" s="2"/>
+      <c r="B743" s="2"/>
+    </row>
+    <row r="744" ht="25" customHeight="1" spans="1:2">
+      <c r="A744" s="2"/>
+      <c r="B744" s="2"/>
+    </row>
+    <row r="745" ht="25" customHeight="1" spans="1:2">
+      <c r="A745" s="2"/>
+      <c r="B745" s="2"/>
+    </row>
+    <row r="746" ht="25" customHeight="1" spans="1:2">
+      <c r="A746" s="2"/>
+      <c r="B746" s="2"/>
+    </row>
+    <row r="747" ht="25" customHeight="1" spans="1:2">
+      <c r="A747" s="2"/>
+      <c r="B747" s="2"/>
+    </row>
+    <row r="748" ht="25" customHeight="1" spans="1:2">
+      <c r="A748" s="2"/>
+      <c r="B748" s="2"/>
+    </row>
+    <row r="749" ht="25" customHeight="1" spans="1:2">
+      <c r="A749" s="2"/>
+      <c r="B749" s="2"/>
+    </row>
+    <row r="750" ht="25" customHeight="1" spans="1:2">
+      <c r="A750" s="2"/>
+      <c r="B750" s="2"/>
+    </row>
+    <row r="751" ht="25" customHeight="1" spans="1:2">
+      <c r="A751" s="2"/>
+      <c r="B751" s="2"/>
+    </row>
+    <row r="752" ht="25" customHeight="1" spans="1:2">
+      <c r="A752" s="2"/>
+      <c r="B752" s="2"/>
+    </row>
+    <row r="753" ht="25" customHeight="1" spans="1:2">
+      <c r="A753" s="2"/>
+      <c r="B753" s="2"/>
+    </row>
+    <row r="754" ht="25" customHeight="1" spans="1:2">
+      <c r="A754" s="2"/>
+      <c r="B754" s="2"/>
+    </row>
+    <row r="755" ht="25" customHeight="1" spans="1:2">
+      <c r="A755" s="2"/>
+      <c r="B755" s="2"/>
+    </row>
+    <row r="756" ht="25" customHeight="1" spans="1:2">
+      <c r="A756" s="2"/>
+      <c r="B756" s="2"/>
+    </row>
+    <row r="757" ht="25" customHeight="1" spans="1:2">
+      <c r="A757" s="2"/>
+      <c r="B757" s="2"/>
+    </row>
+    <row r="758" ht="25" customHeight="1" spans="1:2">
+      <c r="A758" s="2"/>
+      <c r="B758" s="2"/>
+    </row>
+    <row r="759" ht="25" customHeight="1" spans="1:2">
+      <c r="A759" s="2"/>
+      <c r="B759" s="2"/>
+    </row>
+    <row r="760" ht="25" customHeight="1" spans="1:2">
+      <c r="A760" s="2"/>
+      <c r="B760" s="2"/>
+    </row>
+    <row r="761" ht="25" customHeight="1" spans="1:2">
+      <c r="A761" s="2"/>
+      <c r="B761" s="2"/>
+    </row>
+    <row r="762" ht="25" customHeight="1" spans="1:2">
+      <c r="A762" s="2"/>
+      <c r="B762" s="2"/>
+    </row>
+    <row r="763" ht="25" customHeight="1" spans="1:2">
+      <c r="A763" s="2"/>
+      <c r="B763" s="2"/>
+    </row>
+    <row r="764" ht="25" customHeight="1" spans="1:2">
+      <c r="A764" s="2"/>
+      <c r="B764" s="2"/>
+    </row>
+    <row r="765" ht="25" customHeight="1" spans="1:2">
+      <c r="A765" s="2"/>
+      <c r="B765" s="2"/>
+    </row>
+    <row r="766" ht="25" customHeight="1" spans="1:2">
+      <c r="A766" s="2"/>
+      <c r="B766" s="2"/>
+    </row>
+    <row r="767" ht="25" customHeight="1" spans="1:2">
+      <c r="A767" s="2"/>
+      <c r="B767" s="2"/>
+    </row>
+    <row r="768" ht="25" customHeight="1" spans="1:2">
+      <c r="A768" s="2"/>
+      <c r="B768" s="2"/>
+    </row>
+    <row r="769" ht="25" customHeight="1" spans="1:2">
+      <c r="A769" s="2"/>
+      <c r="B769" s="2"/>
+    </row>
+    <row r="770" ht="25" customHeight="1" spans="1:2">
+      <c r="A770" s="2"/>
+      <c r="B770" s="2"/>
+    </row>
+    <row r="771" ht="25" customHeight="1" spans="1:2">
+      <c r="A771" s="2"/>
+      <c r="B771" s="2"/>
+    </row>
+    <row r="772" ht="25" customHeight="1" spans="1:2">
+      <c r="A772" s="2"/>
+      <c r="B772" s="2"/>
+    </row>
+    <row r="773" ht="25" customHeight="1" spans="1:2">
+      <c r="A773" s="2"/>
+      <c r="B773" s="2"/>
+    </row>
+    <row r="774" ht="25" customHeight="1" spans="1:2">
+      <c r="A774" s="2"/>
+      <c r="B774" s="2"/>
+    </row>
+    <row r="775" ht="25" customHeight="1" spans="1:2">
+      <c r="A775" s="2"/>
+      <c r="B775" s="2"/>
+    </row>
+    <row r="776" ht="25" customHeight="1" spans="1:2">
+      <c r="A776" s="2"/>
+      <c r="B776" s="2"/>
+    </row>
+    <row r="777" ht="25" customHeight="1" spans="1:2">
+      <c r="A777" s="2"/>
+      <c r="B777" s="2"/>
+    </row>
+    <row r="778" ht="25" customHeight="1" spans="1:2">
+      <c r="A778" s="2"/>
+      <c r="B778" s="2"/>
+    </row>
+    <row r="779" ht="25" customHeight="1" spans="1:2">
+      <c r="A779" s="2"/>
+      <c r="B779" s="2"/>
+    </row>
+    <row r="780" ht="25" customHeight="1" spans="1:2">
+      <c r="A780" s="2"/>
+      <c r="B780" s="2"/>
+    </row>
+    <row r="781" ht="25" customHeight="1" spans="1:2">
+      <c r="A781" s="2"/>
+      <c r="B781" s="2"/>
+    </row>
+    <row r="782" ht="25" customHeight="1" spans="1:2">
+      <c r="A782" s="2"/>
+      <c r="B782" s="2"/>
+    </row>
+    <row r="783" ht="25" customHeight="1" spans="1:2">
+      <c r="A783" s="2"/>
+      <c r="B783" s="2"/>
+    </row>
+    <row r="784" ht="25" customHeight="1" spans="1:2">
+      <c r="A784" s="2"/>
+      <c r="B784" s="2"/>
+    </row>
+    <row r="785" ht="25" customHeight="1" spans="1:2">
+      <c r="A785" s="2"/>
+      <c r="B785" s="2"/>
+    </row>
+    <row r="786" ht="25" customHeight="1" spans="1:2">
+      <c r="A786" s="2"/>
+      <c r="B786" s="2"/>
+    </row>
+    <row r="787" ht="25" customHeight="1" spans="1:2">
+      <c r="A787" s="2"/>
+      <c r="B787" s="2"/>
+    </row>
+    <row r="788" ht="25" customHeight="1" spans="1:2">
+      <c r="A788" s="2"/>
+      <c r="B788" s="2"/>
+    </row>
+    <row r="789" ht="25" customHeight="1" spans="1:2">
+      <c r="A789" s="2"/>
+      <c r="B789" s="2"/>
+    </row>
+    <row r="790" ht="25" customHeight="1" spans="1:2">
+      <c r="A790" s="2"/>
+      <c r="B790" s="2"/>
+    </row>
+    <row r="791" ht="25" customHeight="1" spans="1:2">
+      <c r="A791" s="2"/>
+      <c r="B791" s="2"/>
+    </row>
+    <row r="792" ht="25" customHeight="1" spans="1:2">
+      <c r="A792" s="2"/>
+      <c r="B792" s="2"/>
+    </row>
+    <row r="793" ht="25" customHeight="1" spans="1:2">
+      <c r="A793" s="2"/>
+      <c r="B793" s="2"/>
+    </row>
+    <row r="794" ht="25" customHeight="1" spans="1:2">
+      <c r="A794" s="2"/>
+      <c r="B794" s="2"/>
+    </row>
+    <row r="795" ht="25" customHeight="1" spans="1:2">
+      <c r="A795" s="2"/>
+      <c r="B795" s="2"/>
+    </row>
+    <row r="796" ht="25" customHeight="1" spans="1:2">
+      <c r="A796" s="2"/>
+      <c r="B796" s="2"/>
+    </row>
+    <row r="797" ht="25" customHeight="1" spans="1:2">
+      <c r="A797" s="2"/>
+      <c r="B797" s="2"/>
+    </row>
+    <row r="798" ht="25" customHeight="1" spans="1:2">
+      <c r="A798" s="2"/>
+      <c r="B798" s="2"/>
+    </row>
+    <row r="799" ht="25" customHeight="1" spans="1:2">
+      <c r="A799" s="2"/>
+      <c r="B799" s="2"/>
+    </row>
+    <row r="800" ht="25" customHeight="1" spans="1:2">
+      <c r="A800" s="2"/>
+      <c r="B800" s="2"/>
+    </row>
+    <row r="801" ht="25" customHeight="1" spans="1:2">
+      <c r="A801" s="2"/>
+      <c r="B801" s="2"/>
+    </row>
+    <row r="802" ht="25" customHeight="1" spans="1:2">
+      <c r="A802" s="2"/>
+      <c r="B802" s="2"/>
+    </row>
+    <row r="803" ht="25" customHeight="1" spans="1:2">
+      <c r="A803" s="2"/>
+      <c r="B803" s="2"/>
+    </row>
+    <row r="804" ht="25" customHeight="1" spans="1:2">
+      <c r="A804" s="2"/>
+      <c r="B804" s="2"/>
+    </row>
+    <row r="805" ht="25" customHeight="1" spans="1:2">
+      <c r="A805" s="2"/>
+      <c r="B805" s="2"/>
+    </row>
+    <row r="806" ht="25" customHeight="1" spans="1:2">
+      <c r="A806" s="2"/>
+      <c r="B806" s="2"/>
+    </row>
+    <row r="807" ht="25" customHeight="1" spans="1:2">
+      <c r="A807" s="2"/>
+      <c r="B807" s="2"/>
+    </row>
+    <row r="808" ht="25" customHeight="1" spans="1:2">
+      <c r="A808" s="2"/>
+      <c r="B808" s="2"/>
+    </row>
+    <row r="809" ht="25" customHeight="1" spans="1:2">
+      <c r="A809" s="2"/>
+      <c r="B809" s="2"/>
+    </row>
+    <row r="810" ht="25" customHeight="1" spans="1:2">
+      <c r="A810" s="2"/>
+      <c r="B810" s="2"/>
+    </row>
+    <row r="811" ht="25" customHeight="1" spans="1:2">
+      <c r="A811" s="2"/>
+      <c r="B811" s="2"/>
+    </row>
+    <row r="812" ht="25" customHeight="1" spans="1:2">
+      <c r="A812" s="2"/>
+      <c r="B812" s="2"/>
+    </row>
+    <row r="813" ht="25" customHeight="1" spans="1:2">
+      <c r="A813" s="2"/>
+      <c r="B813" s="2"/>
+    </row>
+    <row r="814" ht="25" customHeight="1" spans="1:2">
+      <c r="A814" s="2"/>
+      <c r="B814" s="2"/>
+    </row>
+    <row r="815" ht="25" customHeight="1" spans="1:2">
+      <c r="A815" s="2"/>
+      <c r="B815" s="2"/>
+    </row>
+    <row r="816" ht="25" customHeight="1" spans="1:2">
+      <c r="A816" s="2"/>
+      <c r="B816" s="2"/>
+    </row>
+    <row r="817" ht="25" customHeight="1" spans="1:2">
+      <c r="A817" s="2"/>
+      <c r="B817" s="2"/>
+    </row>
+    <row r="818" ht="25" customHeight="1" spans="1:2">
+      <c r="A818" s="2"/>
+      <c r="B818" s="2"/>
+    </row>
+    <row r="819" ht="25" customHeight="1" spans="1:2">
+      <c r="A819" s="2"/>
+      <c r="B819" s="2"/>
+    </row>
+    <row r="820" ht="25" customHeight="1" spans="1:2">
+      <c r="A820" s="2"/>
+      <c r="B820" s="2"/>
+    </row>
+    <row r="821" ht="25" customHeight="1" spans="1:2">
+      <c r="A821" s="2"/>
+      <c r="B821" s="2"/>
+    </row>
+    <row r="822" ht="25" customHeight="1" spans="1:2">
+      <c r="A822" s="2"/>
+      <c r="B822" s="2"/>
+    </row>
+    <row r="823" ht="25" customHeight="1" spans="1:2">
+      <c r="A823" s="2"/>
+      <c r="B823" s="2"/>
+    </row>
+    <row r="824" ht="25" customHeight="1" spans="1:2">
+      <c r="A824" s="2"/>
+      <c r="B824" s="2"/>
+    </row>
+    <row r="825" ht="25" customHeight="1" spans="1:2">
+      <c r="A825" s="2"/>
+      <c r="B825" s="2"/>
+    </row>
+    <row r="826" ht="25" customHeight="1" spans="1:2">
+      <c r="A826" s="2"/>
+      <c r="B826" s="2"/>
+    </row>
+    <row r="827" ht="25" customHeight="1" spans="1:2">
+      <c r="A827" s="2"/>
+      <c r="B827" s="2"/>
+    </row>
+    <row r="828" ht="25" customHeight="1" spans="1:2">
+      <c r="A828" s="2"/>
+      <c r="B828" s="2"/>
+    </row>
+    <row r="829" ht="25" customHeight="1" spans="1:2">
+      <c r="A829" s="2"/>
+      <c r="B829" s="2"/>
+    </row>
+    <row r="830" ht="25" customHeight="1" spans="1:2">
+      <c r="A830" s="2"/>
+      <c r="B830" s="2"/>
+    </row>
+    <row r="831" ht="25" customHeight="1" spans="1:2">
+      <c r="A831" s="2"/>
+      <c r="B831" s="2"/>
+    </row>
+    <row r="832" ht="25" customHeight="1" spans="1:2">
+      <c r="A832" s="2"/>
+      <c r="B832" s="2"/>
+    </row>
+    <row r="833" ht="25" customHeight="1" spans="1:2">
+      <c r="A833" s="2"/>
+      <c r="B833" s="2"/>
+    </row>
+    <row r="834" ht="25" customHeight="1" spans="1:2">
+      <c r="A834" s="2"/>
+      <c r="B834" s="2"/>
+    </row>
+    <row r="835" ht="25" customHeight="1" spans="1:2">
+      <c r="A835" s="2"/>
+      <c r="B835" s="2"/>
+    </row>
+    <row r="836" ht="25" customHeight="1" spans="1:2">
+      <c r="A836" s="2"/>
+      <c r="B836" s="2"/>
+    </row>
+    <row r="837" ht="25" customHeight="1" spans="1:2">
+      <c r="A837" s="2"/>
+      <c r="B837" s="2"/>
+    </row>
+    <row r="838" ht="25" customHeight="1" spans="1:2">
+      <c r="A838" s="2"/>
+      <c r="B838" s="2"/>
+    </row>
+    <row r="839" ht="25" customHeight="1" spans="1:2">
+      <c r="A839" s="2"/>
+      <c r="B839" s="2"/>
+    </row>
+    <row r="840" ht="25" customHeight="1" spans="1:2">
+      <c r="A840" s="2"/>
+      <c r="B840" s="2"/>
+    </row>
+    <row r="841" ht="25" customHeight="1" spans="1:2">
+      <c r="A841" s="2"/>
+      <c r="B841" s="2"/>
+    </row>
+    <row r="842" ht="25" customHeight="1" spans="1:2">
+      <c r="A842" s="2"/>
+      <c r="B842" s="2"/>
+    </row>
+    <row r="843" ht="25" customHeight="1" spans="1:2">
+      <c r="A843" s="2"/>
+      <c r="B843" s="2"/>
+    </row>
+    <row r="844" ht="25" customHeight="1" spans="1:2">
+      <c r="A844" s="2"/>
+      <c r="B844" s="2"/>
+    </row>
+    <row r="845" ht="25" customHeight="1" spans="1:2">
+      <c r="A845" s="2"/>
+      <c r="B845" s="2"/>
+    </row>
+    <row r="846" ht="25" customHeight="1" spans="1:2">
+      <c r="A846" s="2"/>
+      <c r="B846" s="2"/>
+    </row>
+    <row r="847" ht="25" customHeight="1" spans="1:2">
+      <c r="A847" s="2"/>
+      <c r="B847" s="2"/>
+    </row>
+    <row r="848" ht="25" customHeight="1" spans="1:2">
+      <c r="A848" s="2"/>
+      <c r="B848" s="2"/>
+    </row>
+    <row r="849" ht="25" customHeight="1" spans="1:2">
+      <c r="A849" s="2"/>
+      <c r="B849" s="2"/>
+    </row>
+    <row r="850" ht="25" customHeight="1" spans="1:2">
+      <c r="A850" s="2"/>
+      <c r="B850" s="2"/>
+    </row>
+    <row r="851" ht="25" customHeight="1" spans="1:2">
+      <c r="A851" s="2"/>
+      <c r="B851" s="2"/>
+    </row>
+    <row r="852" ht="25" customHeight="1" spans="1:2">
+      <c r="A852" s="2"/>
+      <c r="B852" s="2"/>
+    </row>
+    <row r="853" ht="25" customHeight="1" spans="1:2">
+      <c r="A853" s="2"/>
+      <c r="B853" s="2"/>
+    </row>
+    <row r="854" ht="25" customHeight="1" spans="1:2">
+      <c r="A854" s="2"/>
+      <c r="B854" s="2"/>
+    </row>
+    <row r="855" ht="25" customHeight="1" spans="1:2">
+      <c r="A855" s="2"/>
+      <c r="B855" s="2"/>
+    </row>
+    <row r="856" ht="25" customHeight="1" spans="1:2">
+      <c r="A856" s="2"/>
+      <c r="B856" s="2"/>
+    </row>
+    <row r="857" ht="25" customHeight="1" spans="1:2">
+      <c r="A857" s="2"/>
+      <c r="B857" s="2"/>
+    </row>
+    <row r="858" ht="25" customHeight="1" spans="1:2">
+      <c r="A858" s="2"/>
+      <c r="B858" s="2"/>
+    </row>
+    <row r="859" ht="25" customHeight="1" spans="1:2">
+      <c r="A859" s="2"/>
+      <c r="B859" s="2"/>
+    </row>
+    <row r="860" ht="25" customHeight="1" spans="1:2">
+      <c r="A860" s="2"/>
+      <c r="B860" s="2"/>
+    </row>
+    <row r="861" ht="25" customHeight="1" spans="1:2">
+      <c r="A861" s="2"/>
+      <c r="B861" s="2"/>
+    </row>
+    <row r="862" ht="25" customHeight="1" spans="1:2">
+      <c r="A862" s="2"/>
+      <c r="B862" s="2"/>
+    </row>
+    <row r="863" ht="25" customHeight="1" spans="1:2">
+      <c r="A863" s="2"/>
+      <c r="B863" s="2"/>
+    </row>
+    <row r="864" ht="25" customHeight="1" spans="1:2">
+      <c r="A864" s="2"/>
+      <c r="B864" s="2"/>
+    </row>
+    <row r="865" ht="25" customHeight="1" spans="1:2">
+      <c r="A865" s="2"/>
+      <c r="B865" s="2"/>
+    </row>
+    <row r="866" ht="25" customHeight="1" spans="1:2">
+      <c r="A866" s="2"/>
+      <c r="B866" s="2"/>
+    </row>
+    <row r="867" ht="25" customHeight="1" spans="1:2">
+      <c r="A867" s="2"/>
+      <c r="B867" s="2"/>
+    </row>
+    <row r="868" ht="25" customHeight="1" spans="1:2">
+      <c r="A868" s="2"/>
+      <c r="B868" s="2"/>
+    </row>
+    <row r="869" ht="25" customHeight="1" spans="1:2">
+      <c r="A869" s="2"/>
+      <c r="B869" s="2"/>
+    </row>
+    <row r="870" ht="25" customHeight="1" spans="1:2">
+      <c r="A870" s="2"/>
+      <c r="B870" s="2"/>
+    </row>
+    <row r="871" ht="25" customHeight="1" spans="1:2">
+      <c r="A871" s="2"/>
+      <c r="B871" s="2"/>
+    </row>
+    <row r="872" ht="25" customHeight="1" spans="1:2">
+      <c r="A872" s="2"/>
+      <c r="B872" s="2"/>
+    </row>
+    <row r="873" ht="25" customHeight="1" spans="1:2">
+      <c r="A873" s="2"/>
+      <c r="B873" s="2"/>
+    </row>
+    <row r="874" ht="25" customHeight="1" spans="1:2">
+      <c r="A874" s="2"/>
+      <c r="B874" s="2"/>
+    </row>
+    <row r="875" ht="25" customHeight="1" spans="1:2">
+      <c r="A875" s="2"/>
+      <c r="B875" s="2"/>
+    </row>
+    <row r="876" ht="25" customHeight="1" spans="1:2">
+      <c r="A876" s="2"/>
+      <c r="B876" s="2"/>
+    </row>
+    <row r="877" ht="25" customHeight="1" spans="1:2">
+      <c r="A877" s="2"/>
+      <c r="B877" s="2"/>
+    </row>
+    <row r="878" ht="25" customHeight="1" spans="1:2">
+      <c r="A878" s="2"/>
+      <c r="B878" s="2"/>
+    </row>
+    <row r="879" ht="25" customHeight="1" spans="1:2">
+      <c r="A879" s="2"/>
+      <c r="B879" s="2"/>
+    </row>
+    <row r="880" ht="25" customHeight="1" spans="1:2">
+      <c r="A880" s="2"/>
+      <c r="B880" s="2"/>
+    </row>
+    <row r="881" ht="25" customHeight="1" spans="1:2">
+      <c r="A881" s="2"/>
+      <c r="B881" s="2"/>
+    </row>
+    <row r="882" ht="25" customHeight="1" spans="1:2">
+      <c r="A882" s="2"/>
+      <c r="B882" s="2"/>
+    </row>
+    <row r="883" ht="25" customHeight="1" spans="1:2">
+      <c r="A883" s="2"/>
+      <c r="B883" s="2"/>
+    </row>
+    <row r="884" ht="25" customHeight="1" spans="1:2">
+      <c r="A884" s="2"/>
+      <c r="B884" s="2"/>
+    </row>
+    <row r="885" ht="25" customHeight="1" spans="1:2">
+      <c r="A885" s="2"/>
+      <c r="B885" s="2"/>
+    </row>
+    <row r="886" ht="25" customHeight="1" spans="1:2">
+      <c r="A886" s="2"/>
+      <c r="B886" s="2"/>
+    </row>
+    <row r="887" ht="25" customHeight="1" spans="1:2">
+      <c r="A887" s="2"/>
+      <c r="B887" s="2"/>
+    </row>
+    <row r="888" ht="25" customHeight="1" spans="1:2">
+      <c r="A888" s="2"/>
+      <c r="B888" s="2"/>
+    </row>
+    <row r="889" ht="25" customHeight="1" spans="1:2">
+      <c r="A889" s="2"/>
+      <c r="B889" s="2"/>
+    </row>
+    <row r="890" ht="25" customHeight="1" spans="1:2">
+      <c r="A890" s="2"/>
+      <c r="B890" s="2"/>
+    </row>
+    <row r="891" ht="25" customHeight="1" spans="1:2">
+      <c r="A891" s="2"/>
+      <c r="B891" s="2"/>
+    </row>
+    <row r="892" ht="25" customHeight="1" spans="1:2">
+      <c r="A892" s="2"/>
+      <c r="B892" s="2"/>
+    </row>
+    <row r="893" ht="25" customHeight="1" spans="1:2">
+      <c r="A893" s="2"/>
+      <c r="B893" s="2"/>
+    </row>
+    <row r="894" ht="25" customHeight="1" spans="1:2">
+      <c r="A894" s="2"/>
+      <c r="B894" s="2"/>
+    </row>
+    <row r="895" ht="25" customHeight="1" spans="1:2">
+      <c r="A895" s="2"/>
+      <c r="B895" s="2"/>
+    </row>
+    <row r="896" ht="25" customHeight="1" spans="1:2">
+      <c r="A896" s="2"/>
+      <c r="B896" s="2"/>
+    </row>
+    <row r="897" ht="25" customHeight="1" spans="1:2">
+      <c r="A897" s="2"/>
+      <c r="B897" s="2"/>
+    </row>
+    <row r="898" ht="25" customHeight="1" spans="1:2">
+      <c r="A898" s="2"/>
+      <c r="B898" s="2"/>
+    </row>
+    <row r="899" ht="25" customHeight="1" spans="1:2">
+      <c r="A899" s="2"/>
+      <c r="B899" s="2"/>
+    </row>
+    <row r="900" ht="25" customHeight="1" spans="1:2">
+      <c r="A900" s="2"/>
+      <c r="B900" s="2"/>
+    </row>
+    <row r="901" ht="25" customHeight="1" spans="1:2">
+      <c r="A901" s="2"/>
+      <c r="B901" s="2"/>
+    </row>
+    <row r="902" ht="25" customHeight="1" spans="1:2">
+      <c r="A902" s="2"/>
+      <c r="B902" s="2"/>
+    </row>
+    <row r="903" ht="25" customHeight="1" spans="1:2">
+      <c r="A903" s="2"/>
+      <c r="B903" s="2"/>
+    </row>
+    <row r="904" ht="25" customHeight="1" spans="1:2">
+      <c r="A904" s="2"/>
+      <c r="B904" s="2"/>
+    </row>
+    <row r="905" ht="25" customHeight="1" spans="1:2">
+      <c r="A905" s="2"/>
+      <c r="B905" s="2"/>
+    </row>
+    <row r="906" ht="25" customHeight="1" spans="1:2">
+      <c r="A906" s="2"/>
+      <c r="B906" s="2"/>
+    </row>
+    <row r="907" ht="25" customHeight="1" spans="1:2">
+      <c r="A907" s="2"/>
+      <c r="B907" s="2"/>
+    </row>
+    <row r="908" ht="25" customHeight="1" spans="1:2">
+      <c r="A908" s="2"/>
+      <c r="B908" s="2"/>
+    </row>
+    <row r="909" ht="25" customHeight="1" spans="1:2">
+      <c r="A909" s="2"/>
+      <c r="B909" s="2"/>
+    </row>
+    <row r="910" ht="25" customHeight="1" spans="1:2">
+      <c r="A910" s="2"/>
+      <c r="B910" s="2"/>
+    </row>
+    <row r="911" ht="25" customHeight="1" spans="1:2">
+      <c r="A911" s="2"/>
+      <c r="B911" s="2"/>
+    </row>
+    <row r="912" ht="25" customHeight="1" spans="1:2">
+      <c r="A912" s="2"/>
+      <c r="B912" s="2"/>
+    </row>
+    <row r="913" ht="25" customHeight="1" spans="1:2">
+      <c r="A913" s="2"/>
+      <c r="B913" s="2"/>
+    </row>
+    <row r="914" ht="25" customHeight="1" spans="1:2">
+      <c r="A914" s="2"/>
+      <c r="B914" s="2"/>
+    </row>
+    <row r="915" ht="25" customHeight="1" spans="1:2">
+      <c r="A915" s="2"/>
+      <c r="B915" s="2"/>
+    </row>
+    <row r="916" ht="25" customHeight="1" spans="1:2">
+      <c r="A916" s="2"/>
+      <c r="B916" s="2"/>
+    </row>
+    <row r="917" ht="25" customHeight="1" spans="1:2">
+      <c r="A917" s="2"/>
+      <c r="B917" s="2"/>
+    </row>
+    <row r="918" ht="25" customHeight="1" spans="1:2">
+      <c r="A918" s="2"/>
+      <c r="B918" s="2"/>
+    </row>
+    <row r="919" ht="25" customHeight="1" spans="1:2">
+      <c r="A919" s="2"/>
+      <c r="B919" s="2"/>
+    </row>
+    <row r="920" ht="25" customHeight="1" spans="1:2">
+      <c r="A920" s="2"/>
+      <c r="B920" s="2"/>
+    </row>
+    <row r="921" ht="25" customHeight="1" spans="1:2">
+      <c r="A921" s="2"/>
+      <c r="B921" s="2"/>
+    </row>
+    <row r="922" ht="25" customHeight="1" spans="1:2">
+      <c r="A922" s="2"/>
+      <c r="B922" s="2"/>
+    </row>
+    <row r="923" ht="25" customHeight="1" spans="1:2">
+      <c r="A923" s="2"/>
+      <c r="B923" s="2"/>
+    </row>
+    <row r="924" ht="25" customHeight="1" spans="1:2">
+      <c r="A924" s="2"/>
+      <c r="B924" s="2"/>
+    </row>
+    <row r="925" ht="25" customHeight="1" spans="1:2">
+      <c r="A925" s="2"/>
+      <c r="B925" s="2"/>
+    </row>
+    <row r="926" ht="25" customHeight="1" spans="1:2">
+      <c r="A926" s="2"/>
+      <c r="B926" s="2"/>
+    </row>
+    <row r="927" ht="25" customHeight="1" spans="1:2">
+      <c r="A927" s="2"/>
+      <c r="B927" s="2"/>
+    </row>
+    <row r="928" ht="25" customHeight="1" spans="1:2">
+      <c r="A928" s="2"/>
+      <c r="B928" s="2"/>
+    </row>
+    <row r="929" ht="25" customHeight="1" spans="1:2">
+      <c r="A929" s="2"/>
+      <c r="B929" s="2"/>
+    </row>
+    <row r="930" ht="25" customHeight="1" spans="1:2">
+      <c r="A930" s="2"/>
+      <c r="B930" s="2"/>
+    </row>
+    <row r="931" ht="25" customHeight="1" spans="1:2">
+      <c r="A931" s="2"/>
+      <c r="B931" s="2"/>
+    </row>
+    <row r="932" ht="25" customHeight="1" spans="1:2">
+      <c r="A932" s="2"/>
+      <c r="B932" s="2"/>
+    </row>
+    <row r="933" ht="25" customHeight="1" spans="1:2">
+      <c r="A933" s="2"/>
+      <c r="B933" s="2"/>
+    </row>
+    <row r="934" ht="25" customHeight="1" spans="1:2">
+      <c r="A934" s="2"/>
+      <c r="B934" s="2"/>
+    </row>
+    <row r="935" ht="25" customHeight="1" spans="1:2">
+      <c r="A935" s="2"/>
+      <c r="B935" s="2"/>
+    </row>
+    <row r="936" ht="25" customHeight="1" spans="1:2">
+      <c r="A936" s="2"/>
+      <c r="B936" s="2"/>
+    </row>
+    <row r="937" ht="25" customHeight="1" spans="1:2">
+      <c r="A937" s="2"/>
+      <c r="B937" s="2"/>
+    </row>
+    <row r="938" ht="25" customHeight="1" spans="1:2">
+      <c r="A938" s="2"/>
+      <c r="B938" s="2"/>
+    </row>
+    <row r="939" ht="25" customHeight="1" spans="1:2">
+      <c r="A939" s="2"/>
+      <c r="B939" s="2"/>
+    </row>
+    <row r="940" ht="25" customHeight="1" spans="1:2">
+      <c r="A940" s="2"/>
+      <c r="B940" s="2"/>
+    </row>
+    <row r="941" ht="25" customHeight="1" spans="1:2">
+      <c r="A941" s="2"/>
+      <c r="B941" s="2"/>
+    </row>
+    <row r="942" ht="25" customHeight="1" spans="1:2">
+      <c r="A942" s="2"/>
+      <c r="B942" s="2"/>
+    </row>
+    <row r="943" ht="25" customHeight="1" spans="1:2">
+      <c r="A943" s="2"/>
+      <c r="B943" s="2"/>
+    </row>
+    <row r="944" ht="25" customHeight="1" spans="1:2">
+      <c r="A944" s="2"/>
+      <c r="B944" s="2"/>
+    </row>
+    <row r="945" ht="25" customHeight="1" spans="1:2">
+      <c r="A945" s="2"/>
+      <c r="B945" s="2"/>
+    </row>
+    <row r="946" ht="25" customHeight="1" spans="1:2">
+      <c r="A946" s="2"/>
+      <c r="B946" s="2"/>
+    </row>
+    <row r="947" ht="25" customHeight="1" spans="1:2">
+      <c r="A947" s="2"/>
+      <c r="B947" s="2"/>
+    </row>
+    <row r="948" ht="25" customHeight="1" spans="1:2">
+      <c r="A948" s="2"/>
+      <c r="B948" s="2"/>
+    </row>
+    <row r="949" ht="25" customHeight="1" spans="1:2">
+      <c r="A949" s="2"/>
+      <c r="B949" s="2"/>
+    </row>
+    <row r="950" ht="25" customHeight="1" spans="1:2">
+      <c r="A950" s="2"/>
+      <c r="B950" s="2"/>
+    </row>
+    <row r="951" ht="25" customHeight="1" spans="1:2">
+      <c r="A951" s="2"/>
+      <c r="B951" s="2"/>
+    </row>
+    <row r="952" ht="25" customHeight="1" spans="1:2">
+      <c r="A952" s="2"/>
+      <c r="B952" s="2"/>
+    </row>
+    <row r="953" ht="25" customHeight="1" spans="1:2">
+      <c r="A953" s="2"/>
+      <c r="B953" s="2"/>
+    </row>
+    <row r="954" ht="25" customHeight="1" spans="1:2">
+      <c r="A954" s="2"/>
+      <c r="B954" s="2"/>
+    </row>
+    <row r="955" ht="25" customHeight="1" spans="1:2">
+      <c r="A955" s="2"/>
+      <c r="B955" s="2"/>
+    </row>
+    <row r="956" ht="25" customHeight="1" spans="1:2">
+      <c r="A956" s="2"/>
+      <c r="B956" s="2"/>
+    </row>
+    <row r="957" ht="25" customHeight="1" spans="1:2">
+      <c r="A957" s="2"/>
+      <c r="B957" s="2"/>
+    </row>
+    <row r="958" ht="25" customHeight="1" spans="1:2">
+      <c r="A958" s="2"/>
+      <c r="B958" s="2"/>
+    </row>
+    <row r="959" ht="25" customHeight="1" spans="1:2">
+      <c r="A959" s="2"/>
+      <c r="B959" s="2"/>
+    </row>
+    <row r="960" ht="25" customHeight="1" spans="1:2">
+      <c r="A960" s="2"/>
+      <c r="B960" s="2"/>
+    </row>
+    <row r="961" ht="25" customHeight="1" spans="1:2">
+      <c r="A961" s="2"/>
+      <c r="B961" s="2"/>
+    </row>
+    <row r="962" ht="25" customHeight="1" spans="1:2">
+      <c r="A962" s="2"/>
+      <c r="B962" s="2"/>
+    </row>
+    <row r="963" ht="25" customHeight="1" spans="1:2">
+      <c r="A963" s="2"/>
+      <c r="B963" s="2"/>
+    </row>
+    <row r="964" ht="25" customHeight="1" spans="1:2">
+      <c r="A964" s="2"/>
+      <c r="B964" s="2"/>
+    </row>
+    <row r="965" ht="25" customHeight="1" spans="1:2">
+      <c r="A965" s="2"/>
+      <c r="B965" s="2"/>
+    </row>
+    <row r="966" ht="25" customHeight="1" spans="1:2">
+      <c r="A966" s="2"/>
+      <c r="B966" s="2"/>
+    </row>
+    <row r="967" ht="25" customHeight="1" spans="1:2">
+      <c r="A967" s="2"/>
+      <c r="B967" s="2"/>
+    </row>
+    <row r="968" ht="25" customHeight="1" spans="1:2">
+      <c r="A968" s="2"/>
+      <c r="B968" s="2"/>
+    </row>
+    <row r="969" ht="25" customHeight="1" spans="1:2">
+      <c r="A969" s="2"/>
+      <c r="B969" s="2"/>
+    </row>
+    <row r="970" ht="25" customHeight="1" spans="1:2">
+      <c r="A970" s="2"/>
+      <c r="B970" s="2"/>
+    </row>
+    <row r="971" ht="25" customHeight="1" spans="1:2">
+      <c r="A971" s="2"/>
+      <c r="B971" s="2"/>
+    </row>
+    <row r="972" ht="25" customHeight="1" spans="1:2">
+      <c r="A972" s="2"/>
+      <c r="B972" s="2"/>
+    </row>
+    <row r="973" ht="25" customHeight="1" spans="1:2">
+      <c r="A973" s="2"/>
+      <c r="B973" s="2"/>
+    </row>
+    <row r="974" ht="25" customHeight="1" spans="1:2">
+      <c r="A974" s="2"/>
+      <c r="B974" s="2"/>
+    </row>
+    <row r="975" ht="25" customHeight="1" spans="1:2">
+      <c r="A975" s="2"/>
+      <c r="B975" s="2"/>
+    </row>
+    <row r="976" ht="25" customHeight="1" spans="1:2">
+      <c r="A976" s="2"/>
+      <c r="B976" s="2"/>
+    </row>
+    <row r="977" ht="25" customHeight="1" spans="1:2">
+      <c r="A977" s="2"/>
+      <c r="B977" s="2"/>
+    </row>
+    <row r="978" ht="25" customHeight="1" spans="1:2">
+      <c r="A978" s="2"/>
+      <c r="B978" s="2"/>
+    </row>
+    <row r="979" ht="25" customHeight="1" spans="1:2">
+      <c r="A979" s="2"/>
+      <c r="B979" s="2"/>
+    </row>
+    <row r="980" ht="25" customHeight="1" spans="1:2">
+      <c r="A980" s="2"/>
+      <c r="B980" s="2"/>
+    </row>
+    <row r="981" ht="25" customHeight="1" spans="1:2">
+      <c r="A981" s="2"/>
+      <c r="B981" s="2"/>
+    </row>
+    <row r="982" ht="25" customHeight="1" spans="1:2">
+      <c r="A982" s="2"/>
+      <c r="B982" s="2"/>
+    </row>
+    <row r="983" ht="25" customHeight="1" spans="1:2">
+      <c r="A983" s="2"/>
+      <c r="B983" s="2"/>
+    </row>
+    <row r="984" ht="25" customHeight="1" spans="1:2">
+      <c r="A984" s="2"/>
+      <c r="B984" s="2"/>
+    </row>
+    <row r="985" ht="25" customHeight="1" spans="1:2">
+      <c r="A985" s="2"/>
+      <c r="B985" s="2"/>
+    </row>
+    <row r="986" ht="25" customHeight="1" spans="1:2">
+      <c r="A986" s="2"/>
+      <c r="B986" s="2"/>
+    </row>
+    <row r="987" ht="25" customHeight="1" spans="1:2">
+      <c r="A987" s="2"/>
+      <c r="B987" s="2"/>
+    </row>
+    <row r="988" ht="25" customHeight="1" spans="1:2">
+      <c r="A988" s="2"/>
+      <c r="B988" s="2"/>
+    </row>
+    <row r="989" ht="25" customHeight="1" spans="1:2">
+      <c r="A989" s="2"/>
+      <c r="B989" s="2"/>
+    </row>
+    <row r="990" ht="25" customHeight="1" spans="1:2">
+      <c r="A990" s="2"/>
+      <c r="B990" s="2"/>
+    </row>
+    <row r="991" ht="25" customHeight="1" spans="1:2">
+      <c r="A991" s="2"/>
+      <c r="B991" s="2"/>
+    </row>
+    <row r="992" ht="25" customHeight="1" spans="1:2">
+      <c r="A992" s="2"/>
+      <c r="B992" s="2"/>
+    </row>
+    <row r="993" ht="25" customHeight="1" spans="1:2">
+      <c r="A993" s="2"/>
+      <c r="B993" s="2"/>
+    </row>
+    <row r="994" ht="25" customHeight="1" spans="1:2">
+      <c r="A994" s="2"/>
+      <c r="B994" s="2"/>
+    </row>
+    <row r="995" ht="25" customHeight="1" spans="1:2">
+      <c r="A995" s="2"/>
+      <c r="B995" s="2"/>
+    </row>
+    <row r="996" ht="25" customHeight="1" spans="1:2">
+      <c r="A996" s="2"/>
+      <c r="B996" s="2"/>
+    </row>
+    <row r="997" ht="25" customHeight="1" spans="1:2">
+      <c r="A997" s="2"/>
+      <c r="B997" s="2"/>
+    </row>
+    <row r="998" ht="25" customHeight="1" spans="1:2">
+      <c r="A998" s="2"/>
+      <c r="B998" s="2"/>
+    </row>
+    <row r="999" ht="25" customHeight="1" spans="1:2">
+      <c r="A999" s="2"/>
+      <c r="B999" s="2"/>
+    </row>
+    <row r="1000" ht="25" customHeight="1" spans="1:2">
+      <c r="A1000" s="2"/>
+      <c r="B1000" s="2"/>
+    </row>
+    <row r="1001" ht="25" customHeight="1" spans="1:2">
+      <c r="A1001" s="2"/>
+      <c r="B1001" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="1025">
   <si>
     <t>bangla</t>
   </si>
@@ -3100,6 +3100,60 @@
   </si>
   <si>
     <t>আত্তুন যহন মন হারাপ থাহে তহন আঁই উডোনোত ফইরোর পাশে বই থাহি</t>
+  </si>
+  <si>
+    <t>পুকুর ঘাঠে বসে বড়শি দিয়ে মাছ ধরব</t>
+  </si>
+  <si>
+    <t>ফইরোর ঘাটোত বই রে বরকি দি মাছ ধইজ্জুম</t>
+  </si>
+  <si>
+    <t>কতক্ষণ ধরে বরশি নিয়ে বসে আছি, একটা মাছও ধরতে পারিনি</t>
+  </si>
+  <si>
+    <t>হতক্ষন ধরি বরকি লই বই থেইক্কি, উজ্ঞো মাছও ধরিত ন পারি</t>
+  </si>
+  <si>
+    <t>পুকুরে এবার অনেক বড় বড় মাছ হয়েছে</t>
+  </si>
+  <si>
+    <t>ফইরোত এবার বত বরো বরো মাছ অইয়্যি</t>
+  </si>
+  <si>
+    <t>অনেকগুলো মাছ মরে গিয়ে পুকুরে ভাসছে</t>
+  </si>
+  <si>
+    <t>বত হদুজ্ঞুন মাছ মরি ফইরুত ভা'আর</t>
+  </si>
+  <si>
+    <t>জেলেরা নদীতে গিয়ে জাল দিয়ে মাছ ধরে</t>
+  </si>
+  <si>
+    <t>জেইল্লে অক্কল দইজ্জেত যাই জাল দি মাছ ধরে</t>
+  </si>
+  <si>
+    <t>আজকে নদীতে স্রোত বেশি, মাছ ধরতে যাওয়া ঠিক হবে না</t>
+  </si>
+  <si>
+    <t>আজিয়ে দইজ্জেত উত বেশি, মাছ ধইত্তু যন ঠিক অইতুনো</t>
+  </si>
+  <si>
+    <t>স্রোত বেশি হওয়ার কারনে নৌকা চালাতে কষ্ট হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>উত বেশি অ'নোর হারনে নৌকো চলাতে হষ্ট অই যার</t>
+  </si>
+  <si>
+    <t>নৌকার মাঝি গান গেয়ে গেয়ে নৌকা চালাচ্ছে</t>
+  </si>
+  <si>
+    <t>নৌকোর মাঝি গান গাই গাই নৌকো চলার</t>
+  </si>
+  <si>
+    <t>নৌকাটি একটু ঘুরাও, আমরা উঠবো</t>
+  </si>
+  <si>
+    <t>নৌকো ইয়েন এক্কানা ঘুরো, আঁরা উইট্টুম</t>
   </si>
 </sst>
 </file>
@@ -8325,40 +8379,76 @@
       </c>
     </row>
     <row r="507" ht="25" customHeight="1" spans="1:2">
-      <c r="A507" s="2"/>
-      <c r="B507" s="2"/>
+      <c r="A507" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="508" ht="25" customHeight="1" spans="1:2">
-      <c r="A508" s="2"/>
-      <c r="B508" s="2"/>
+      <c r="A508" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="509" ht="25" customHeight="1" spans="1:2">
-      <c r="A509" s="2"/>
-      <c r="B509" s="2"/>
+      <c r="A509" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="510" ht="25" customHeight="1" spans="1:2">
-      <c r="A510" s="2"/>
-      <c r="B510" s="2"/>
+      <c r="A510" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>1014</v>
+      </c>
     </row>
     <row r="511" ht="25" customHeight="1" spans="1:2">
-      <c r="A511" s="2"/>
-      <c r="B511" s="2"/>
+      <c r="A511" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>1016</v>
+      </c>
     </row>
     <row r="512" ht="25" customHeight="1" spans="1:2">
-      <c r="A512" s="2"/>
-      <c r="B512" s="2"/>
+      <c r="A512" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>1018</v>
+      </c>
     </row>
     <row r="513" ht="25" customHeight="1" spans="1:2">
-      <c r="A513" s="2"/>
-      <c r="B513" s="2"/>
+      <c r="A513" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>1020</v>
+      </c>
     </row>
     <row r="514" ht="25" customHeight="1" spans="1:2">
-      <c r="A514" s="2"/>
-      <c r="B514" s="2"/>
+      <c r="A514" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>1022</v>
+      </c>
     </row>
     <row r="515" ht="25" customHeight="1" spans="1:2">
-      <c r="A515" s="2"/>
-      <c r="B515" s="2"/>
+      <c r="A515" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="516" ht="25" customHeight="1" spans="1:2">
       <c r="A516" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="1096">
   <si>
     <t>bangla</t>
   </si>
@@ -1035,7 +1035,7 @@
     <t>আজকে শুক্রবার, সেজন্য আজকে জুমার নামাজ পড়তে হবে</t>
   </si>
   <si>
-    <t>আজিয়ে শুক্রবার, এতেল্লে আজিয়ে জুমার নামাজ পরন পরিবো</t>
+    <t>আজিয়ে শুক্রবার, এতেল্লে আজিয়ে জুমার নামাজ ফরন ফরিবো</t>
   </si>
   <si>
     <t>হ্যালো আসসালামু আলাইকু্ম, কেমন আছেন? কতোদিন পর</t>
@@ -1353,7 +1353,7 @@
     <t>আমি প্রতিদিন সকালে তাড়াতাড়ি উঠে যায়</t>
   </si>
   <si>
-    <t>আঁই পইত্তোদিন ফজোরত তারাতারি উডি যায়</t>
+    <t>আঁই ফইত্তোদিন ফজোরত তারাতারি উডি যায়</t>
   </si>
   <si>
     <t>সকালে ব্যায়াম করলে শরীর ভালো থাকে</t>
@@ -1407,7 +1407,7 @@
     <t>আমি প্রতিদিন রাত দশটায় ঘুমায় যায় যেন সকালে তাড়াতাড়ি উঠতে পারি</t>
   </si>
   <si>
-    <t>আঁই পইত্তোদিন রাতিয়ে দশটা বাজে ঘুমায় যায় যাতে বেইন্নে তারাতারি উঢিত পারি</t>
+    <t>আঁই ফইত্তোদিন রাতিয়ে দশটা বাজে ঘুমায় যায় যাতে বেইন্নে তারাতারি উঢিত পারি</t>
   </si>
   <si>
     <t>আজকে সকালে আমি ভাত খাব না</t>
@@ -1455,7 +1455,7 @@
     <t>আজকে মেহমান আসছে, বাজার থেকে গরুর মাংস আর চিংড়ি মাছ নিয়ে আসো</t>
   </si>
   <si>
-    <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তন গরু গোস্ত আর ইছে মাছ আনো</t>
+    <t>আজিয়ে মেমান আইয়্যির, বাজারোত্তুন গরু গোস্ত আর ইছে মাছ আনো</t>
   </si>
   <si>
     <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি এক কাপ চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
@@ -1473,7 +1473,7 @@
     <t>অফিস থেকে আসার সময় বাজার থেকে টমেটো আর চিংড়ি মাছ নিয়ে আসিও</t>
   </si>
   <si>
-    <t>অফিস উত্তুন আইবের সময় বাজার উত্তুন হাট্টা বেইয়্যুন আর ইছে মাছ লই আইস্যু</t>
+    <t>অফিস উত্তুন আইবের সময় বাজারোত্তুন হাট্টা বেইয়্যুন আর ইছে মাছ লই আইস্যু</t>
   </si>
   <si>
     <t>আজকে নিউ মার্কেট থেকে একটা পাঞ্জাবি কিনেছি</t>
@@ -1887,7 +1887,7 @@
     <t>আমি প্রতিদিন চেষ্টা করি রাতে জলদি ঘুমানোর, কিন্তু কেমনে জানি দেরি হয়ে যায়</t>
   </si>
   <si>
-    <t>আঁই পইত্তোদিন চেষ্টা গরি রাতিয়ে জলদি ঘুম যাইবের লাই, কিন্তু কেনে জানি দেরি অই যায়</t>
+    <t>আঁই ফইত্তোদিন চেষ্টা গরি রাতিয়ে জলদি ঘুম যাইবের লাই, কিন্তু কেনে জানি দেরি অই যায়</t>
   </si>
   <si>
     <t>তোমার স্বভাব আমার একদম ভাল লাগছে না</t>
@@ -1905,7 +1905,7 @@
     <t>তুর ভাইকে বলিস আসার সময় বাজার থেকে চিংড়ি শুটকি নিয়ে আসার জন্য</t>
   </si>
   <si>
-    <t>তুর বদ্দারে হইস আইবের সমোত বাজারোত্তন ইছে উনি লই আইবের লাই</t>
+    <t>তুর বদ্দারে হইস আইবের সমোত বাজারোত্তুন ইছে উনি লই আইবের লাই</t>
   </si>
   <si>
     <t>তোর বাবাকে মাঠ থেকে ডেকে নিয়ে আয়</t>
@@ -1953,7 +1953,7 @@
     <t>বাজার থেকে পুঁই শাক নিয়ে আসো</t>
   </si>
   <si>
-    <t>বাজারোত্তন পিয়েশ শাক লই আইস</t>
+    <t>বাজারোত্তুন পিয়েশ শাক লই আইস</t>
   </si>
   <si>
     <t>ডাক্তার বলেছে মাছ আর বেশি বেশি শাক সবজি খেতে</t>
@@ -2019,7 +2019,7 @@
     <t>বাজার থেকে একটা কাঁঠাল নিয়ে আসো</t>
   </si>
   <si>
-    <t>বাজারোত্তন উজ্ঞো হাট্টল লই আইয়্যো</t>
+    <t>বাজারোত্তুন উজ্ঞো হাট্টল লই আইয়্যো</t>
   </si>
   <si>
     <t>ভাঙার পর দেখলাম কাঁঠালটি কাঁচা</t>
@@ -2055,7 +2055,7 @@
     <t>বার বার বলি যে বাজার থেকে কিছু নিলে ভালভাবে দেখে নিতে, এখন দোকানদার সব পঁচা আম দিয়ে দিছে তোমাকে</t>
   </si>
   <si>
-    <t>বার বার হয়দি বাজারোত্তন কিছু লইলি ভালা গরি চায় লইবের লাই, এহন দোয়ানদার বিয়াক পুঁচা আম দি দিয়ি তোঁয়ারে</t>
+    <t>বার বার হয়দি বাজারোত্তুন কিছু লইলি ভালা গরি চায় লইবের লাই, এহন দোয়ানদার বিয়াক পুঁচা আম দি দিয়ি তোঁয়ারে</t>
   </si>
   <si>
     <t>অনেকদি ধরে ঘরে বসে বসে বিরক্ত হয়ে গেছি</t>
@@ -2199,7 +2199,7 @@
     <t>প্রতিদিন সকালে উঠে বাগানের সব ফুল গাছে পানি দিও</t>
   </si>
   <si>
-    <t>পইত্তোদিন বেইন্নে উডি বাগানোর বিয়াক ফুল গাছোত পানি দিবে</t>
+    <t>ফইত্তোদিন বেইন্নে উডি বাগানোর বিয়াক ফুল গাছোত পানি দিবে</t>
   </si>
   <si>
     <t>তোমার কাছে টাকা আছে? আমাকে কিছু টাকা ধার দাও</t>
@@ -2709,7 +2709,7 @@
     <t>কি কিনব বাজার থেকে! সবকিছুর যে দাম!</t>
   </si>
   <si>
-    <t>কি কিননুম বাজারোত্তন! বিয়াক কিছুর যে দাম!</t>
+    <t>কি কিননুম বাজারোত্তুন! বিয়াক কিছুর যে দাম!</t>
   </si>
   <si>
     <t>সকালে জলদি ঘুম থেকে না উঠলে ক্লাসে যেতে দেরি হয়ে যাবে</t>
@@ -2823,7 +2823,7 @@
     <t>প্রতিদিন নিয়ম করে দাঁত মাজা উচিত</t>
   </si>
   <si>
-    <t>পইত্তোদিন নিয়ম গরি দাঁত মাজন উচিত</t>
+    <t>ফইত্তোদিন নিয়ম গরি দাঁত মাজন উচিত</t>
   </si>
   <si>
     <t>দাঁত না মাজলে দাঁতে পোকা হবে</t>
@@ -2913,7 +2913,7 @@
     <t>প্রতিদিনের হোমওয়ার্ক প্রতিদিনই শেষ করে ফেলবে</t>
   </si>
   <si>
-    <t>পইত্তোদিনোর হোমওয়ার্ক পইত্তোদিনই শেষ গরি ফেলাইবে</t>
+    <t>ফইত্তোদিনোর হোমওয়ার্ক পইত্তোদিনই শেষ গরি ফেলাইবে</t>
   </si>
   <si>
     <t>হোমওয়ার্ক না করলে আমি ম্যাডামকে বলে দেবো</t>
@@ -2937,7 +2937,7 @@
     <t>রাস্তায় অনেক জ্যাম, আমার আসতে দেরি হবে</t>
   </si>
   <si>
-    <t>বাস্তাত বত জ্যাম, আত্তুন আইতে দেরি অইবু</t>
+    <t>রাস্তাত বত জ্যাম, আত্তুন আইতে দেরি অইবু</t>
   </si>
   <si>
     <t>জ্যামে বসে থাকতে থাকতে বিরক্ত হয়ে গেছি</t>
@@ -3154,6 +3154,219 @@
   </si>
   <si>
     <t>নৌকো ইয়েন এক্কানা ঘুরো, আঁরা উইট্টুম</t>
+  </si>
+  <si>
+    <t>ওষুধটা কাজে দিয়েছে, খাওয়ার পর এখন পেট ব্যথা অনেক কমে গেছে</t>
+  </si>
+  <si>
+    <t>ওষুধ ইবে হাজোত দিয়ি, হায়বের পর এহন পেট ব্যথা বত হমি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>মা, খাওয়ার জন্য কি আছে?</t>
+  </si>
+  <si>
+    <t>আম্মু, হায়বের লাই কি আছে?</t>
+  </si>
+  <si>
+    <t>খাবারগুলো ওদের দুজনকে ভাগ করে দাও যেন একজন আরেকজনের সাথে ঝগড়া না করে</t>
+  </si>
+  <si>
+    <t>হানা এগিন ইতারা দুনুজনোরে ভাগ গরি দও যেন একজন আরেকজনোর লগে হইজ্জে ন গরে</t>
+  </si>
+  <si>
+    <t>বাজার থেকে শিম এনেছি, আজকে দুপুরে শিম ভর্তা করো</t>
+  </si>
+  <si>
+    <t>বৃষ্টির দিনে ঘর থেকে বের হতে ইচ্ছা করে না</t>
+  </si>
+  <si>
+    <t>ঝরোর দিনোত ঘরোত্তুন বাইর অইতু ইচ্ছে ন গরের</t>
+  </si>
+  <si>
+    <t>বৃষ্টির দিনে জানালার পাশে বসে গল্পের বই পড়তে অনেক ভাল লাগে</t>
+  </si>
+  <si>
+    <t>ঝরোর দিনোত জানালার পাশে বই রে গল্পোর বই ফইত্তে বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>বৃষ্টির দিনে কাপড় শুকাতে অনেক কষ্ট হয়ে যায়</t>
+  </si>
+  <si>
+    <t>ঝরোর দিনোত হর ফুঅতে বত হষ্ট অই যায়</t>
+  </si>
+  <si>
+    <t>মাছের ঝোলে লবণ বেশি হয়ে গেছে, খাওয়া যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>মাছুর সুরগোত নুন বেশি অই গেইয়্যি, হন ন যার</t>
+  </si>
+  <si>
+    <t>বারবার বলি যে তরকারিতে লবণ কম দেওয়ার জন্য, আমি বেশি লবণ খেতে পারি না</t>
+  </si>
+  <si>
+    <t>বারবার হয়দি তরহারিত নুন হম দিবের লাই, আঁই নুন বেশি হাইত ন ফারি</t>
+  </si>
+  <si>
+    <t>তরকারিতে লবণ আরেকটু কম দেবে, তাহলে তরকারি অনেক মজা হবে</t>
+  </si>
+  <si>
+    <t>তরহারিত নুন আরেক্কানা হম দিবে, তইলি তরহারি বত মজা অইবু</t>
+  </si>
+  <si>
+    <t>সারাদিন ফোন দেখলে তো মাথা এমনিতেই ব্যথা করবে</t>
+  </si>
+  <si>
+    <t>আরাদিন ফোন চাইলি তো মাথা এনেই ব্যথা গরিবু</t>
+  </si>
+  <si>
+    <t>সারাদিন মন অনেক খারাপ ছিল, নামাজ পড়ার পর মন ভাল হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আরাদিন মন বত হারাপ আছিল, নামাজ পরিবের পর মন ভালা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সারাদিন বসে বসে টিভিতে কার্টুন দেখলে পড়ালেখা কখন করবে?</t>
+  </si>
+  <si>
+    <t>আরাদিন বই বই টিভিত কার্টুন চাইলি পরালেহা হত্তে গরিবি?</t>
+  </si>
+  <si>
+    <t>তোর আপুকে ঘুম থেকে ডেকে দে</t>
+  </si>
+  <si>
+    <t>তোর আফারে ঘুমুত্তুন ডাহি দে</t>
+  </si>
+  <si>
+    <t>তোর আপুকে ডাক্তারের কাছে নিয়ে যেতে হবে, একটা সিএনজি নিয়ে আয়</t>
+  </si>
+  <si>
+    <t>তোর আফারে ডাক্তারোর হাছে লই যন পরিবু, এক্কান সিএনজি লই আয়</t>
+  </si>
+  <si>
+    <t>খিদে না থাকলে খাবার খাওয়া উচিত নয়</t>
+  </si>
+  <si>
+    <t>ভুক ন থাহিলি হানা হন উচিত ন</t>
+  </si>
+  <si>
+    <t>ঘরের কাজে সারাদিন অনেক ব্যস্ত ছিলাম, তাই অনলাইনে আসতে পারিনি</t>
+  </si>
+  <si>
+    <t>ঘরোর হাজে আরাদিন বত বিজি আছিলাম, এতেল্লে অনলাইনুত আইত ন পারি</t>
+  </si>
+  <si>
+    <t>এবার বেশি করে আম কাঁঠাল নিয়ে তোর বড় আপুকে দেখে আসিস</t>
+  </si>
+  <si>
+    <t>এবার বেশি গরি আম হাট্টল লই রে তোর বরো আফারে চায় আইস</t>
+  </si>
+  <si>
+    <t>সারাদিন একটানা বসে থাকিও না, কিছুক্ষণ পর পর উঠে একটু হাঁটিও</t>
+  </si>
+  <si>
+    <t>আরাদিন একটানা বই ন থাইক্কো, হতক্ষন পর পর উডি এক্কানা আইট্টো</t>
+  </si>
+  <si>
+    <t>একটা দিতে গিয়ে ভুলে আরেকটা চলে গেছে</t>
+  </si>
+  <si>
+    <t>এক্কান দিতাম যায় রে ভুলে আরেক্কান চলি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার বাসায় মাত্র একটা টিভি আছে, তাই সবাইকে একসাথেই দেখতে হবে</t>
+  </si>
+  <si>
+    <t>আঁর বাসাত উধো উজ্ঞ টিভি আছে, এতেল্লে বিয়াজ্ঞুনুত্তুন এক্কোওয়ারেই  চন পরিবু</t>
+  </si>
+  <si>
+    <t>আমি কি বলেছি আমার খিদে লেগেছে?</t>
+  </si>
+  <si>
+    <t>আঁই কি হই আত্তুন ভুক লেইজ্ঞি?</t>
+  </si>
+  <si>
+    <t>আমার খিদে লাগলে আমি নিজ থেকেই খেয়ে নিব</t>
+  </si>
+  <si>
+    <t>আত্তুন ভুক লাগিলি আঁই নিজুত্তুন হায় লইয়্যুম</t>
+  </si>
+  <si>
+    <t>তুই জানিস আমি কে? কি আমার পরিচয়?</t>
+  </si>
+  <si>
+    <t>তুই জানোস আই হন? কি আঁর পরিচয়?</t>
+  </si>
+  <si>
+    <t>তুমি কার সামনে দাঁড়িয়ে কোন সাহসে কী বলছ, সেটা কি বুঝতে পারছ?</t>
+  </si>
+  <si>
+    <t>তুঁই হার সাম্মোদ্দি থিয়েই হন সাহসে কি হর, ইয়েন কি বুঝিত ফারোর?</t>
+  </si>
+  <si>
+    <t>হাত থেকে পড়ে কাপটা ভেঙে গেল</t>
+  </si>
+  <si>
+    <t>আতুত্তুন ফরি হাপ ইবে ভাঙি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>টাকা দিয়ে সবকিছু কেনা যায় না</t>
+  </si>
+  <si>
+    <t>টিয়া দি বিয়াক কিছু কিনন ন যায়</t>
+  </si>
+  <si>
+    <t>ওরা এই রাস্তা দিয়ে গেছে, কিছুক্ষণ হাঁটলে সামনে দেখতে পাবেন</t>
+  </si>
+  <si>
+    <t>ইতারা রাস্তা ইবে দি গেইয়্যি, হতক্ষন আডিলি সাম্মোদ্দি দেহিবেন</t>
+  </si>
+  <si>
+    <t>এই রাস্তাটা অনেক খারাপ, এটা দিয়ে যাওয়া ঠিক হবে না</t>
+  </si>
+  <si>
+    <t>এই রাস্তা ইবে বত হারাফ, ইবে দি যন ঠিক ন অইবু</t>
+  </si>
+  <si>
+    <t>প্রতিদিন এক তরকারি খেতে ভালো লাগে না</t>
+  </si>
+  <si>
+    <t>ফইত্তোদিন এক তরহারি হাইতে ভালা ন লাগে</t>
+  </si>
+  <si>
+    <t>প্রতিদিন ডিম আর ডাল খেতে খেতে বিরক্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>ফইত্তোদিন ডিম আর ডেইল হাইতে হাইতে বিরক্ত অই গেই</t>
+  </si>
+  <si>
+    <t>প্রথমে পেঁয়াজ ভালো করে ভেজে নিতে হবে, তারপর মসলা দিতে হবে</t>
+  </si>
+  <si>
+    <t>ফইল্লে পিয়েজ ভালা গরি ভাজি লন পরিবু, তারপর মসল্লা দন পরিবু</t>
+  </si>
+  <si>
+    <t>রান্নাঘর থেকে বিরিয়ানির সুগন্ধি আসছে</t>
+  </si>
+  <si>
+    <t>বসহানাত্তুন বিরেনির হুসবো আইয়্যির</t>
+  </si>
+  <si>
+    <t>টিনের ঘরে বৃষ্টির শব্দ শুনতে অনেক ভাল লাগে</t>
+  </si>
+  <si>
+    <t>টইনোর ঘরোত ঝরোর আওয়াজ উনতে বেশি গম লাগে</t>
+  </si>
+  <si>
+    <t>গরমকালে মাটির ঘরে গরম কম লাগে</t>
+  </si>
+  <si>
+    <t>গরমহালে মেডির ঘরোত গরম হম লাগে</t>
+  </si>
+  <si>
+    <t>বেশি গরম লাগলে একটু ঠান্ডা পানি খাও</t>
+  </si>
+  <si>
+    <t>বেশি গরম লাগিলি এক্কানা ঠান্ডা পানি হ</t>
   </si>
 </sst>
 </file>
@@ -8451,148 +8664,290 @@
       </c>
     </row>
     <row r="516" ht="25" customHeight="1" spans="1:2">
-      <c r="A516" s="2"/>
-      <c r="B516" s="2"/>
+      <c r="A516" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>1026</v>
+      </c>
     </row>
     <row r="517" ht="25" customHeight="1" spans="1:2">
-      <c r="A517" s="2"/>
-      <c r="B517" s="2"/>
+      <c r="A517" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="518" ht="25" customHeight="1" spans="1:2">
-      <c r="A518" s="2"/>
-      <c r="B518" s="2"/>
+      <c r="A518" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>1030</v>
+      </c>
     </row>
     <row r="519" ht="25" customHeight="1" spans="1:2">
-      <c r="A519" s="2"/>
+      <c r="A519" s="2" t="s">
+        <v>1031</v>
+      </c>
       <c r="B519" s="2"/>
     </row>
     <row r="520" ht="25" customHeight="1" spans="1:2">
-      <c r="A520" s="2"/>
-      <c r="B520" s="2"/>
+      <c r="A520" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>1033</v>
+      </c>
     </row>
     <row r="521" ht="25" customHeight="1" spans="1:2">
-      <c r="A521" s="2"/>
-      <c r="B521" s="2"/>
+      <c r="A521" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="522" ht="25" customHeight="1" spans="1:2">
-      <c r="A522" s="2"/>
-      <c r="B522" s="2"/>
+      <c r="A522" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>1037</v>
+      </c>
     </row>
     <row r="523" ht="25" customHeight="1" spans="1:2">
-      <c r="A523" s="2"/>
-      <c r="B523" s="2"/>
+      <c r="A523" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>1039</v>
+      </c>
     </row>
     <row r="524" ht="25" customHeight="1" spans="1:2">
-      <c r="A524" s="2"/>
-      <c r="B524" s="2"/>
+      <c r="A524" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="525" ht="25" customHeight="1" spans="1:2">
-      <c r="A525" s="2"/>
-      <c r="B525" s="2"/>
+      <c r="A525" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="526" ht="25" customHeight="1" spans="1:2">
-      <c r="A526" s="2"/>
-      <c r="B526" s="2"/>
+      <c r="A526" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="527" ht="25" customHeight="1" spans="1:2">
-      <c r="A527" s="2"/>
-      <c r="B527" s="2"/>
+      <c r="A527" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>1047</v>
+      </c>
     </row>
     <row r="528" ht="25" customHeight="1" spans="1:2">
-      <c r="A528" s="2"/>
-      <c r="B528" s="2"/>
+      <c r="A528" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>1049</v>
+      </c>
     </row>
     <row r="529" ht="25" customHeight="1" spans="1:2">
-      <c r="A529" s="2"/>
-      <c r="B529" s="2"/>
+      <c r="A529" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="530" ht="25" customHeight="1" spans="1:2">
-      <c r="A530" s="2"/>
-      <c r="B530" s="2"/>
+      <c r="A530" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>1053</v>
+      </c>
     </row>
     <row r="531" ht="25" customHeight="1" spans="1:2">
-      <c r="A531" s="2"/>
-      <c r="B531" s="2"/>
+      <c r="A531" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="532" ht="25" customHeight="1" spans="1:2">
-      <c r="A532" s="2"/>
-      <c r="B532" s="2"/>
+      <c r="A532" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="533" ht="25" customHeight="1" spans="1:2">
-      <c r="A533" s="2"/>
-      <c r="B533" s="2"/>
+      <c r="A533" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>1059</v>
+      </c>
     </row>
     <row r="534" ht="25" customHeight="1" spans="1:2">
-      <c r="A534" s="2"/>
-      <c r="B534" s="2"/>
+      <c r="A534" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>1061</v>
+      </c>
     </row>
     <row r="535" ht="25" customHeight="1" spans="1:2">
-      <c r="A535" s="2"/>
-      <c r="B535" s="2"/>
+      <c r="A535" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>1063</v>
+      </c>
     </row>
     <row r="536" ht="25" customHeight="1" spans="1:2">
-      <c r="A536" s="2"/>
-      <c r="B536" s="2"/>
+      <c r="A536" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>1065</v>
+      </c>
     </row>
     <row r="537" ht="25" customHeight="1" spans="1:2">
-      <c r="A537" s="2"/>
-      <c r="B537" s="2"/>
+      <c r="A537" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="538" ht="25" customHeight="1" spans="1:2">
-      <c r="A538" s="2"/>
-      <c r="B538" s="2"/>
+      <c r="A538" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>1069</v>
+      </c>
     </row>
     <row r="539" ht="25" customHeight="1" spans="1:2">
-      <c r="A539" s="2"/>
-      <c r="B539" s="2"/>
+      <c r="A539" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="540" ht="25" customHeight="1" spans="1:2">
-      <c r="A540" s="2"/>
-      <c r="B540" s="2"/>
+      <c r="A540" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>1073</v>
+      </c>
     </row>
     <row r="541" ht="25" customHeight="1" spans="1:2">
-      <c r="A541" s="2"/>
-      <c r="B541" s="2"/>
+      <c r="A541" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="542" ht="25" customHeight="1" spans="1:2">
-      <c r="A542" s="2"/>
-      <c r="B542" s="2"/>
+      <c r="A542" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="543" ht="25" customHeight="1" spans="1:2">
-      <c r="A543" s="2"/>
-      <c r="B543" s="2"/>
+      <c r="A543" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="544" ht="25" customHeight="1" spans="1:2">
-      <c r="A544" s="2"/>
-      <c r="B544" s="2"/>
+      <c r="A544" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="545" ht="25" customHeight="1" spans="1:2">
-      <c r="A545" s="2"/>
-      <c r="B545" s="2"/>
+      <c r="A545" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>1083</v>
+      </c>
     </row>
     <row r="546" ht="25" customHeight="1" spans="1:2">
-      <c r="A546" s="2"/>
-      <c r="B546" s="2"/>
+      <c r="A546" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>1085</v>
+      </c>
     </row>
     <row r="547" ht="25" customHeight="1" spans="1:2">
-      <c r="A547" s="2"/>
-      <c r="B547" s="2"/>
+      <c r="A547" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="548" ht="25" customHeight="1" spans="1:2">
-      <c r="A548" s="2"/>
-      <c r="B548" s="2"/>
+      <c r="A548" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>1089</v>
+      </c>
     </row>
     <row r="549" ht="25" customHeight="1" spans="1:2">
-      <c r="A549" s="2"/>
-      <c r="B549" s="2"/>
+      <c r="A549" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>1091</v>
+      </c>
     </row>
     <row r="550" ht="25" customHeight="1" spans="1:2">
-      <c r="A550" s="2"/>
-      <c r="B550" s="2"/>
+      <c r="A550" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="551" ht="25" customHeight="1" spans="1:2">
-      <c r="A551" s="2"/>
-      <c r="B551" s="2"/>
+      <c r="A551" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="552" ht="25" customHeight="1" spans="1:2">
       <c r="A552" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="1165">
   <si>
     <t>bangla</t>
   </si>
@@ -311,7 +311,7 @@
     <t>ব্যাপার কি, আজকে তোমাকে অনেক সুন্দর লাগতাছে</t>
   </si>
   <si>
-    <t>ব্যাপার কি, আজিয়ে তো তোঁইয়ারা বত সুন্দার লাগের</t>
+    <t>ব্যাপার কি, আজিয়ে তো তোঁয়ারে বত সুন্দার লাগের</t>
   </si>
   <si>
     <t>আপনি কি একটু সাহায্য করতে পারবেন?</t>
@@ -407,7 +407,7 @@
     <t>তোকে দেখে অসুস্থ মনে হচ্ছে</t>
   </si>
   <si>
-    <t>তোরে দেহি রে অসুস্থ মনে অর</t>
+    <t>তুরে দেহি রে অসুস্থ মনে অর</t>
   </si>
   <si>
     <t>আপনার সাথে আরেকদিন কথা বলব</t>
@@ -539,7 +539,7 @@
     <t>কেমন আছিস বন্ধু? তোকে অনেকদিন পর দেখতাছি</t>
   </si>
   <si>
-    <t>কেন আছস বন্ধু, তোরে বতদিন পর দেহিদ্দি</t>
+    <t>কেন আছস বন্ধু, তুরে বতদিন পর দেহিদ্দি</t>
   </si>
   <si>
     <t>আমি কি চাই সেটা তুমি আমার চেহারা দেখে বলতে পারবেনা?</t>
@@ -869,7 +869,7 @@
     <t>ভাই, তোর জন্য কিছু মিষ্টি এনেছি, নিয়ে যা, তোর অনেক পছন্দের জিনিস!</t>
   </si>
   <si>
-    <t>বদ্দা, তোর লাই কিছু মিষ্টি আইন্নি, লই যা, তোর বত পছন্দের জিনিস!</t>
+    <t>বদ্দা, তুর লাই কিছু মিষ্টি আইন্নি, লই যা, তুর বত পছন্দের জিনিস!</t>
   </si>
   <si>
     <t>চাচা, গাড়ি চালানোর সময় একটু স্লো করুন, রাস্তাটা একটু খারাপ</t>
@@ -1461,7 +1461,7 @@
     <t>অফিস থেকে এসে ক্লান্ত লাগছে, এখন যদি এক কাপ চা না খায় তাহলে মাথা ঘুরে পড়ে যাব</t>
   </si>
   <si>
-    <t>অফিস উত্তুন আইয়্যিরে অরান লাগের বাজি, এহন যদি এক কাপ চা ন হায় মাথা ঘুরাই পরি যাইয়্যুম</t>
+    <t>অফিস উত্তুন আইয়্যিরে অরান লাগের বাজি, এহন যদি এক হাপ চা ন হায় মাথা ঘুরাই পরি যাইয়্যুম</t>
   </si>
   <si>
     <t>আজকে অফিসে কাজের চাপ কম, তাই জলদি চলে আসছি</t>
@@ -1575,7 +1575,7 @@
     <t>আজকে আমি নিজে তোমার জন্য রান্না করেছি, খেয়ে কেমন হয়েছে জানাবে</t>
   </si>
   <si>
-    <t>আজিয়ে আঁই নিজে তোঁইয়ার লাই রান্না গইজ্জি, হাইয়্যিরে কেন অইয়্যি হইয়্যু</t>
+    <t>আজিয়ে আঁই নিজে তোঁয়ার লাই রান্না গইজ্জি, হাইয়্যিরে কেন অইয়্যি হইয়্যু</t>
   </si>
   <si>
     <t>তোমার রান্না অনেক মজা হয়েছে</t>
@@ -1689,7 +1689,7 @@
     <t>তোরা খেলতে যাওয়ার পর আমাকে বলিস</t>
   </si>
   <si>
-    <t>তোরা খেইলতো যাইবের পরে আঁরে হইস</t>
+    <t>তুরা খেইলতো যাইবের পরে আঁরে হইস</t>
   </si>
   <si>
     <t>আমি ক্রিকেট খেলব না, ফুটবল খেলব</t>
@@ -1767,7 +1767,7 @@
     <t>বলটি যদি আমার দিকে পাস দিতি তাহলে গোল দিতে পারতাম</t>
   </si>
   <si>
-    <t>বল ইবে যদি আঁম মিক্কে পাস দিতি তইলি গোল দিত পাইত্তাম</t>
+    <t>বল ইবে যদি আঁর মিক্কে পাস দিতি তইলি গোল দিত পাইত্তাম</t>
   </si>
   <si>
     <t>বলটি কোনদিকে মারছো? খোজে পাচ্ছিনা</t>
@@ -1911,7 +1911,7 @@
     <t>তোর বাবাকে মাঠ থেকে ডেকে নিয়ে আয়</t>
   </si>
   <si>
-    <t>তোর বাপোরে মাডোত্তন ডাহি আন</t>
+    <t>তুর বাপোরে মাডোত্তন ডাহি আন</t>
   </si>
   <si>
     <t>আমি ভাত দিচ্ছি, তুমি মুখ ধুয়ে আসো</t>
@@ -2157,13 +2157,13 @@
     <t>আচ্ছা ঠিক আছে, এসব নিয়ে আমি তোর সাথে তর্ক করতে চায় না</t>
   </si>
   <si>
-    <t>আইচ্ছে ঠিক আছে, এগিন লই রে আঁই তোর লগে তর্ক গইত্তাম ন চায়</t>
+    <t>আইচ্ছে ঠিক আছে, এগিন লই রে আঁই তুর লগে তর্ক গইত্তাম ন চায়</t>
   </si>
   <si>
     <t>তোর কথা ঠিক, আমি বুঝিনি প্রথমে</t>
   </si>
   <si>
-    <t>তোর হতা ঠিক, আঁই নো বুঝিদি পইল্লে</t>
+    <t>তুর হতা ঠিক, আঁই নো বুঝিদি পইল্লে</t>
   </si>
   <si>
     <t>আমি কি বধির? আমি সব শুনি</t>
@@ -2301,13 +2301,13 @@
     <t>তোর বড় ভাই নাকি বিদেশ চলে গেছে?</t>
   </si>
   <si>
-    <t>তোর বদ্দা বলে বিদেশ চলি গেইয়্যি</t>
+    <t>তুর বদ্দা বলে বিদেশ চলি গেইয়্যি</t>
   </si>
   <si>
     <t>আম্মু বলছে তোকে আর আন্টিকে একদিন বেড়াতে আসতে</t>
   </si>
   <si>
-    <t>আম্মু হদ্দে তোরে আর আন্টি রে একদিন বেরাইতো আইবের লাই</t>
+    <t>আম্মু হদ্দে তুরে আর আন্টি রে একদিন বেরাইতো আইবের লাই</t>
   </si>
   <si>
     <t>আমার বুক জ্বালা করছে, মনে হয় গ্যাস্ট্রিক বেড়ে গেছে</t>
@@ -2631,7 +2631,7 @@
     <t>গোসল করে আসার সময় তোর বাবার লুঙ্গিটাও ধুয়ে আনিস</t>
   </si>
   <si>
-    <t>গোসল গরি আইবের সমত তোর বাফোর লুঙ্গি ইয়েন অ ধুয় আনিস</t>
+    <t>গোসল গরি আইবের সমত তুর বাফোর লুঙ্গি ইয়েন অ ধুয় আনিস</t>
   </si>
   <si>
     <t>আমার এখন ঘুম আসছে, কিছুক্ষণ ঘুমিয়ে নি</t>
@@ -2853,13 +2853,13 @@
     <t>তোর আপুর প্রেশার বেড়ে গেছে, জলদি একটা ডাক্তার নিয়ে আয়</t>
   </si>
   <si>
-    <t>তোর আফার প্রেশার বারি গেইয়্যি, হারা উজ্ঞো ডাক্তোর লই আয়</t>
+    <t>তুর আফার প্রেশার বারি গেইয়্যি, হারা উজ্ঞো ডাক্তোর লই আয়</t>
   </si>
   <si>
     <t>তোর বাবা খবরের কাগজ পড়ছে, চা-টা দিয়ে আয়</t>
   </si>
   <si>
-    <t>তোর বাফ হবরোর হাগজ পরের, চা ইবে দি আয়</t>
+    <t>তুর বাফ হবরোর হাগজ পরের, চা ইবে দি আয়</t>
   </si>
   <si>
     <t>সবাই টেবিলে চলে আসো, আজকে সবাই একসাথে নাস্তা করি</t>
@@ -3039,7 +3039,7 @@
     <t>মুখ হাত ধোয়ে তোর আপুর কাছে পড়তে বস</t>
   </si>
   <si>
-    <t>মুখ আত ধুয় রে তোর আফাত্তুন পইত্তো বই</t>
+    <t>মুখ আত ধুয় রে তুর আফাত্তুন পইত্তো বই</t>
   </si>
   <si>
     <t>আমি সবজি দিয়ে ভাত খাব না, আমাকে মাংস দাও</t>
@@ -3177,6 +3177,9 @@
     <t>বাজার থেকে শিম এনেছি, আজকে দুপুরে শিম ভর্তা করো</t>
   </si>
   <si>
+    <t>বাজারোত্তুন ছৈই আইন্নি, আজিয়ে দুইজ্জে ছৈই ভত্তা গরো</t>
+  </si>
+  <si>
     <t>বৃষ্টির দিনে ঘর থেকে বের হতে ইচ্ছা করে না</t>
   </si>
   <si>
@@ -3234,13 +3237,13 @@
     <t>তোর আপুকে ঘুম থেকে ডেকে দে</t>
   </si>
   <si>
-    <t>তোর আফারে ঘুমুত্তুন ডাহি দে</t>
+    <t>তুর আফারে ঘুমুত্তুন ডাহি দে</t>
   </si>
   <si>
     <t>তোর আপুকে ডাক্তারের কাছে নিয়ে যেতে হবে, একটা সিএনজি নিয়ে আয়</t>
   </si>
   <si>
-    <t>তোর আফারে ডাক্তারোর হাছে লই যন পরিবু, এক্কান সিএনজি লই আয়</t>
+    <t>তুর আফারে ডাক্তারোর হাছে লই যন ফরিবু, এক্কান সিএনজি লই আয়</t>
   </si>
   <si>
     <t>খিদে না থাকলে খাবার খাওয়া উচিত নয়</t>
@@ -3258,7 +3261,7 @@
     <t>এবার বেশি করে আম কাঁঠাল নিয়ে তোর বড় আপুকে দেখে আসিস</t>
   </si>
   <si>
-    <t>এবার বেশি গরি আম হাট্টল লই রে তোর বরো আফারে চায় আইস</t>
+    <t>এবার বেশি গরি আম হাট্টল লই রে তুর বরো আফারে চায় আইস</t>
   </si>
   <si>
     <t>সারাদিন একটানা বসে থাকিও না, কিছুক্ষণ পর পর উঠে একটু হাঁটিও</t>
@@ -3276,7 +3279,7 @@
     <t>আমার বাসায় মাত্র একটা টিভি আছে, তাই সবাইকে একসাথেই দেখতে হবে</t>
   </si>
   <si>
-    <t>আঁর বাসাত উধো উজ্ঞ টিভি আছে, এতেল্লে বিয়াজ্ঞুনুত্তুন এক্কোওয়ারেই  চন পরিবু</t>
+    <t>আঁর বাসাত উধো উজ্ঞ টিভি আছে, এতেল্লে বিয়াজ্ঞুনুত্তুন এক্কোওয়ারেই  চন ফরিবু</t>
   </si>
   <si>
     <t>আমি কি বলেছি আমার খিদে লেগেছে?</t>
@@ -3342,7 +3345,7 @@
     <t>প্রথমে পেঁয়াজ ভালো করে ভেজে নিতে হবে, তারপর মসলা দিতে হবে</t>
   </si>
   <si>
-    <t>ফইল্লে পিয়েজ ভালা গরি ভাজি লন পরিবু, তারপর মসল্লা দন পরিবু</t>
+    <t>ফইল্লে পিয়েজ ভালা গরি ভাজি লন ফরিবু, তারপর মসল্লা দন ফরিবু</t>
   </si>
   <si>
     <t>রান্নাঘর থেকে বিরিয়ানির সুগন্ধি আসছে</t>
@@ -3367,6 +3370,210 @@
   </si>
   <si>
     <t>বেশি গরম লাগিলি এক্কানা ঠান্ডা পানি হ</t>
+  </si>
+  <si>
+    <t>মনে থাকবে কি কি আনতে হবে?</t>
+  </si>
+  <si>
+    <t>মনোত থাহিবু কি কি আনন ফরিবু?</t>
+  </si>
+  <si>
+    <t>ছেলেটাকে ডিম দিতে হবে, বেশি দুর্বল হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>ফুয়া ইবেরে ডিম দন ফরিবু, বেশি দুর্বল অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বারবার বারণ করি, তাও আমার কথা শোনো না</t>
+  </si>
+  <si>
+    <t>বারবার মানা গরি, তো আঁর হতা ন উনো</t>
+  </si>
+  <si>
+    <t>তোমাকে যেটা বলি, সবসময় সেটার উল্টোটা বলো</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে যিয়েন হই, সবসময় ইয়েনুর উল্ডো ইয়েন হও</t>
+  </si>
+  <si>
+    <t>কিছু মানুষ আছে যারা রাতে কাজ করে এবং দিনে ঘুমায়</t>
+  </si>
+  <si>
+    <t>কিছু মানুষ আছে যারা রাতিয়ে হাম গরে আর দিনোত ঘুম যায়</t>
+  </si>
+  <si>
+    <t>রাতে না ঘুমালে আমার মাথা ঘোরে</t>
+  </si>
+  <si>
+    <t>রাতিয়ে ঘুম ন যাইলি আত্তুন মাথা ঘোরাই</t>
+  </si>
+  <si>
+    <t>নিজেকে একবার আমার জায়গায় বসিয়ে দেখ, তাহলে বুঝবি আমার কেমন লাগছে</t>
+  </si>
+  <si>
+    <t>নিজোরে একবার আঁর জাগাত বুওয়াই চা, তইলি বুঝিবি আত্তুন কেন লাগের</t>
+  </si>
+  <si>
+    <t>আজকের দিনটি এমনি এমনি চলে গেল, কিছুই করতে পারলাম না</t>
+  </si>
+  <si>
+    <t>আজিয়ের দিন ইয়েন এনে এনে চলি গেইয়্যি, কিছুই গরিত ন ফারি</t>
+  </si>
+  <si>
+    <t>আমার কিছু জিনিস তোমার কাছে থেকে গেছে, সেগুলো দিয়ে দিলে খুশি হতাম</t>
+  </si>
+  <si>
+    <t>আঁর কিছু জিনিস তোঁয়ার হাছে থাহি গেইয়্যি, এগিন দি দিলি খুশি অইতাম</t>
+  </si>
+  <si>
+    <t>বিকালের আগে কাজ শেষ করতে না পারলে টাকা দিব না</t>
+  </si>
+  <si>
+    <t>বিয়েলোর আগে হাম শেষ গরিত ন ফারিলি টিয়া দিতাম ন</t>
+  </si>
+  <si>
+    <t>কাজ শেষ করে কত টাকা পাবি বুঝে নিস</t>
+  </si>
+  <si>
+    <t>হাম শেষ গরি হত টিয়া পাবি বুঝি লইস</t>
+  </si>
+  <si>
+    <t>তুই আমার কাছ থেকে আর কোনো টাকা পাবি না, তোর সব টাকা আমি দিয়ে দিছি</t>
+  </si>
+  <si>
+    <t>তুই আত্তুন আর হনো টিয়া ন পাবি, তুর বিয়াক টিয়া আঁই দি দিই</t>
+  </si>
+  <si>
+    <t>বাকি টাকাগুলো ফেরত দিলে ভাল হবে</t>
+  </si>
+  <si>
+    <t>বেইক্কে টিয়াগুন ফেরত দিলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>আমি সত্যি বলছি, আমার মনে কোনো ময়লা নেই</t>
+  </si>
+  <si>
+    <t>আঁই সত্যি হইদ্দি, আঁর মনোত হনো হাচারা নেই</t>
+  </si>
+  <si>
+    <t>আমার শরীর একদম ভাল না, আমার জন্য একটু দোয়া করিও</t>
+  </si>
+  <si>
+    <t>আঁর শরীর এব্বেরে ভালা ন, আঁর লাই এক্কানা দোয়া গইজ্জো</t>
+  </si>
+  <si>
+    <t>চুলায় আগুন জ্বালিয়ে দাও, এখন রান্না করব</t>
+  </si>
+  <si>
+    <t>চুলোত অইন জলাই দ, এহন রান্না গইজ্জুম</t>
+  </si>
+  <si>
+    <t>রান্না করা শেষ, এখন আগুন নিভিয়ে দাও</t>
+  </si>
+  <si>
+    <t xml:space="preserve">রান্না গরা শেষ, এহন অইন নিফেই দ </t>
+  </si>
+  <si>
+    <t>এটা কি বাসার দারোয়ান?</t>
+  </si>
+  <si>
+    <t>ইবে কি বাসার দারোয়ান?</t>
+  </si>
+  <si>
+    <t>দারোয়ানের ভাব দেখে মনে হচ্ছে যেন বাসার মালিক</t>
+  </si>
+  <si>
+    <t>দারোয়ানুর ভাব দেহি মনে অদ্দে বাসার মালিক</t>
+  </si>
+  <si>
+    <t>অফিসের বসকে বলে কিছুদিনের জন্য ছুটি নাও, সবাই মিলে দূরে কোথাও ঘুরতে যাব</t>
+  </si>
+  <si>
+    <t>অফিসুর বস উরে হই কিছুদিনুর লাই ছুটি লও, বিয়াজ্ঞুন মিলি দূরে হনোমিক্কে ঘুইত্তাম যায়</t>
+  </si>
+  <si>
+    <t>এভাবে বললে ওরা মানবে না ভাই</t>
+  </si>
+  <si>
+    <t>এনগরি হইলি ইতারা ন মানিবু বদ্দা</t>
+  </si>
+  <si>
+    <t>আমাকে কী করতে হবে বল, আমি আমার পরিবারের জন্য সবকিছু করতে রাজি আছি</t>
+  </si>
+  <si>
+    <t>আত্তুন কি গরন ফরিবু হ, আঁই আঁর পরিবারোর লাই বিয়াক কিছু গইত্তে রাজি আছি</t>
+  </si>
+  <si>
+    <t>আমার বউ অসুস্থ, আমাকে কিছুদিনের জন্য ছুটি দিন</t>
+  </si>
+  <si>
+    <t>আঁর বউ আসুস্থ, আঁরে কিছুদিনুর লাই ছুটি দন</t>
+  </si>
+  <si>
+    <t>আমি যখন শহরে থাকতাম তখন নিজের রান্না নিজে করে খেতাম</t>
+  </si>
+  <si>
+    <t>আঁই যহন শ'রুত থাইকতাম তহন নিজোর রান্না নিজে গরি হাইতাম</t>
+  </si>
+  <si>
+    <t>আমাকে একটু রান্নাঘর কোনদিকে সেটা দেখিয়ে দিন</t>
+  </si>
+  <si>
+    <t>আঁরে এক্কানা রান্নাঘর হুনদি ইয়েন দেহায় দন</t>
+  </si>
+  <si>
+    <t>আমাকে একটু চিনি কম দিয়ে এক কাপ চা দিও</t>
+  </si>
+  <si>
+    <t>আঁরে এক্কানা চিনি হম দি এক হাপ চা দিও</t>
+  </si>
+  <si>
+    <t>আমার এখন কোন কিছু মনে থাকে না, সব ভুলে যাই</t>
+  </si>
+  <si>
+    <t>আঁর এহন হনো কিছু মনোত ন থাহে, বিয়াক ভুলি যাই</t>
+  </si>
+  <si>
+    <t>তুই যেটা করেছিস সেটার ফল কিন্তু ভাল হবে না</t>
+  </si>
+  <si>
+    <t>তুই যিয়েন গইজ্জুস ইয়েন উর ফল কিন্তু ভালা অইতু ন</t>
+  </si>
+  <si>
+    <t>কেন করব না, অবশ্যই করব</t>
+  </si>
+  <si>
+    <t>ন গইত্তাম কা, অবশ্যই গইজ্জুম</t>
+  </si>
+  <si>
+    <t>সেটাই তো চিন্তা করছি, কিভাবে এত বড় ভুল করলাম</t>
+  </si>
+  <si>
+    <t>ইয়েন ই তো চিন্তে গরির, কেন গরি এত বরো ভুল গরিলাম</t>
+  </si>
+  <si>
+    <t>তোমার সাথে ওর কাজ কি?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার লগে ইবের হাম কি?</t>
+  </si>
+  <si>
+    <t>কি বলেন এসব! আমাদের বাড়িতে থাকবে কেন?</t>
+  </si>
+  <si>
+    <t>কি হন এগিন! আঁরার বারিত কিল্লে থাহিবু?</t>
+  </si>
+  <si>
+    <t>ও যদি এখানে থাকে তাহলে আমি বাড়িতে থাকব না</t>
+  </si>
+  <si>
+    <t>ইবে যদি এনডে থাহে তইলি আঁই বারিত ন থাইক্কুম</t>
+  </si>
+  <si>
+    <t>আমার তো আর খেয়ে দেয়ে কাজ নাই</t>
+  </si>
+  <si>
+    <t>আত্তুন তো আর হায় দায় হাজ নাই</t>
   </si>
 </sst>
 </file>
@@ -8691,399 +8898,537 @@
       <c r="A519" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="B519" s="2"/>
+      <c r="B519" s="2" t="s">
+        <v>1032</v>
+      </c>
     </row>
     <row r="520" ht="25" customHeight="1" spans="1:2">
       <c r="A520" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="521" ht="25" customHeight="1" spans="1:2">
       <c r="A521" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="522" ht="25" customHeight="1" spans="1:2">
       <c r="A522" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="523" ht="25" customHeight="1" spans="1:2">
       <c r="A523" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="524" ht="25" customHeight="1" spans="1:2">
       <c r="A524" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="525" ht="25" customHeight="1" spans="1:2">
       <c r="A525" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="526" ht="25" customHeight="1" spans="1:2">
       <c r="A526" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="527" ht="25" customHeight="1" spans="1:2">
       <c r="A527" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="528" ht="25" customHeight="1" spans="1:2">
       <c r="A528" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="529" ht="25" customHeight="1" spans="1:2">
       <c r="A529" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="530" ht="25" customHeight="1" spans="1:2">
       <c r="A530" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="531" ht="25" customHeight="1" spans="1:2">
       <c r="A531" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="532" ht="25" customHeight="1" spans="1:2">
       <c r="A532" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="533" ht="25" customHeight="1" spans="1:2">
       <c r="A533" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="534" ht="25" customHeight="1" spans="1:2">
       <c r="A534" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="535" ht="25" customHeight="1" spans="1:2">
       <c r="A535" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="536" ht="25" customHeight="1" spans="1:2">
       <c r="A536" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="537" ht="25" customHeight="1" spans="1:2">
       <c r="A537" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="538" ht="25" customHeight="1" spans="1:2">
       <c r="A538" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="539" ht="25" customHeight="1" spans="1:2">
       <c r="A539" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="540" ht="25" customHeight="1" spans="1:2">
       <c r="A540" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="541" ht="25" customHeight="1" spans="1:2">
       <c r="A541" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="542" ht="25" customHeight="1" spans="1:2">
       <c r="A542" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="543" ht="25" customHeight="1" spans="1:2">
       <c r="A543" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="544" ht="25" customHeight="1" spans="1:2">
       <c r="A544" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="545" ht="25" customHeight="1" spans="1:2">
       <c r="A545" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="546" ht="25" customHeight="1" spans="1:2">
       <c r="A546" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="547" ht="25" customHeight="1" spans="1:2">
       <c r="A547" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="548" ht="25" customHeight="1" spans="1:2">
       <c r="A548" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="549" ht="25" customHeight="1" spans="1:2">
       <c r="A549" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="550" ht="25" customHeight="1" spans="1:2">
       <c r="A550" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="551" ht="25" customHeight="1" spans="1:2">
       <c r="A551" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="552" ht="25" customHeight="1" spans="1:2">
-      <c r="A552" s="2"/>
-      <c r="B552" s="2"/>
+      <c r="A552" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>1098</v>
+      </c>
     </row>
     <row r="553" ht="25" customHeight="1" spans="1:2">
-      <c r="A553" s="2"/>
-      <c r="B553" s="2"/>
+      <c r="A553" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="554" ht="25" customHeight="1" spans="1:2">
-      <c r="A554" s="2"/>
-      <c r="B554" s="2"/>
+      <c r="A554" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>1102</v>
+      </c>
     </row>
     <row r="555" ht="25" customHeight="1" spans="1:2">
-      <c r="A555" s="2"/>
-      <c r="B555" s="2"/>
+      <c r="A555" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>1104</v>
+      </c>
     </row>
     <row r="556" ht="25" customHeight="1" spans="1:2">
-      <c r="A556" s="2"/>
-      <c r="B556" s="2"/>
+      <c r="A556" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="557" ht="25" customHeight="1" spans="1:2">
-      <c r="A557" s="2"/>
-      <c r="B557" s="2"/>
+      <c r="A557" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="558" ht="25" customHeight="1" spans="1:2">
-      <c r="A558" s="2"/>
-      <c r="B558" s="2"/>
+      <c r="A558" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="559" ht="25" customHeight="1" spans="1:2">
-      <c r="A559" s="2"/>
-      <c r="B559" s="2"/>
+      <c r="A559" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>1112</v>
+      </c>
     </row>
     <row r="560" ht="25" customHeight="1" spans="1:2">
-      <c r="A560" s="2"/>
-      <c r="B560" s="2"/>
+      <c r="A560" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="561" ht="25" customHeight="1" spans="1:2">
-      <c r="A561" s="2"/>
-      <c r="B561" s="2"/>
+      <c r="A561" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="562" ht="25" customHeight="1" spans="1:2">
-      <c r="A562" s="2"/>
-      <c r="B562" s="2"/>
+      <c r="A562" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="563" ht="25" customHeight="1" spans="1:2">
-      <c r="A563" s="2"/>
-      <c r="B563" s="2"/>
+      <c r="A563" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="564" ht="25" customHeight="1" spans="1:2">
-      <c r="A564" s="2"/>
-      <c r="B564" s="2"/>
+      <c r="A564" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="565" ht="25" customHeight="1" spans="1:2">
-      <c r="A565" s="2"/>
-      <c r="B565" s="2"/>
+      <c r="A565" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>1124</v>
+      </c>
     </row>
     <row r="566" ht="25" customHeight="1" spans="1:2">
-      <c r="A566" s="2"/>
-      <c r="B566" s="2"/>
+      <c r="A566" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>1126</v>
+      </c>
     </row>
     <row r="567" ht="25" customHeight="1" spans="1:2">
-      <c r="A567" s="2"/>
-      <c r="B567" s="2"/>
+      <c r="A567" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>1128</v>
+      </c>
     </row>
     <row r="568" ht="25" customHeight="1" spans="1:2">
-      <c r="A568" s="2"/>
-      <c r="B568" s="2"/>
+      <c r="A568" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>1130</v>
+      </c>
     </row>
     <row r="569" ht="25" customHeight="1" spans="1:2">
-      <c r="A569" s="2"/>
-      <c r="B569" s="2"/>
+      <c r="A569" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>1132</v>
+      </c>
     </row>
     <row r="570" ht="25" customHeight="1" spans="1:2">
-      <c r="A570" s="2"/>
-      <c r="B570" s="2"/>
+      <c r="A570" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="571" ht="25" customHeight="1" spans="1:2">
-      <c r="A571" s="2"/>
-      <c r="B571" s="2"/>
+      <c r="A571" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="572" ht="25" customHeight="1" spans="1:2">
-      <c r="A572" s="2"/>
-      <c r="B572" s="2"/>
+      <c r="A572" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>1138</v>
+      </c>
     </row>
     <row r="573" ht="25" customHeight="1" spans="1:2">
-      <c r="A573" s="2"/>
-      <c r="B573" s="2"/>
+      <c r="A573" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="574" ht="25" customHeight="1" spans="1:2">
-      <c r="A574" s="2"/>
-      <c r="B574" s="2"/>
+      <c r="A574" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>1142</v>
+      </c>
     </row>
     <row r="575" ht="25" customHeight="1" spans="1:2">
-      <c r="A575" s="2"/>
-      <c r="B575" s="2"/>
+      <c r="A575" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="576" ht="25" customHeight="1" spans="1:2">
-      <c r="A576" s="2"/>
-      <c r="B576" s="2"/>
+      <c r="A576" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="577" ht="25" customHeight="1" spans="1:2">
-      <c r="A577" s="2"/>
-      <c r="B577" s="2"/>
+      <c r="A577" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="578" ht="25" customHeight="1" spans="1:2">
-      <c r="A578" s="2"/>
-      <c r="B578" s="2"/>
+      <c r="A578" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="579" ht="25" customHeight="1" spans="1:2">
-      <c r="A579" s="2"/>
-      <c r="B579" s="2"/>
+      <c r="A579" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>1152</v>
+      </c>
     </row>
     <row r="580" ht="25" customHeight="1" spans="1:2">
-      <c r="A580" s="2"/>
-      <c r="B580" s="2"/>
+      <c r="A580" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="581" ht="25" customHeight="1" spans="1:2">
-      <c r="A581" s="2"/>
-      <c r="B581" s="2"/>
+      <c r="A581" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="582" ht="25" customHeight="1" spans="1:2">
-      <c r="A582" s="2"/>
-      <c r="B582" s="2"/>
+      <c r="A582" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="583" ht="25" customHeight="1" spans="1:2">
-      <c r="A583" s="2"/>
-      <c r="B583" s="2"/>
+      <c r="A583" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="584" ht="25" customHeight="1" spans="1:2">
-      <c r="A584" s="2"/>
-      <c r="B584" s="2"/>
+      <c r="A584" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="585" ht="25" customHeight="1" spans="1:2">
-      <c r="A585" s="2"/>
-      <c r="B585" s="2"/>
+      <c r="A585" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>1164</v>
+      </c>
     </row>
     <row r="586" ht="25" customHeight="1" spans="1:2">
       <c r="A586" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1217">
   <si>
     <t>bangla</t>
   </si>
@@ -1227,7 +1227,7 @@
     <t>আমার একটু খারাপ লাগছে, আমি যেতে পারব না</t>
   </si>
   <si>
-    <t>আত্তুন এক্কানা হারাপ লার, আঁই যাইত পাইত্তাম নো</t>
+    <t>আত্তুন এক্কানা হারাপ লার, আঁই যাইত ফাইত্তাম নো</t>
   </si>
   <si>
     <t>আমি বাজার করতে যাচ্ছি ভাই, তুই কোথায় যাচ্ছিস?</t>
@@ -1767,7 +1767,7 @@
     <t>বলটি যদি আমার দিকে পাস দিতি তাহলে গোল দিতে পারতাম</t>
   </si>
   <si>
-    <t>বল ইবে যদি আঁর মিক্কে পাস দিতি তইলি গোল দিত পাইত্তাম</t>
+    <t>বল ইবে যদি আঁর মিক্কে পাস দিতি তইলি গোল দিত ফাইত্তাম</t>
   </si>
   <si>
     <t>বলটি কোনদিকে মারছো? খোজে পাচ্ছিনা</t>
@@ -2379,13 +2379,13 @@
     <t>আজকে আসতে পারব না, অন্য আরেকদিন আসব</t>
   </si>
   <si>
-    <t>আজিয়ে আইত পাইত্তাম ন, অন্য আরেকদিন আইসসুম</t>
+    <t>আজিয়ে আইত ফাইত্তাম ন, অন্য আরেকদিন আইসসুম</t>
   </si>
   <si>
     <t>আজকে অফিসে যেতে হবে যে তাই আসতে পারব না</t>
   </si>
   <si>
-    <t>আজিয়ে অফিসুত যন ফরিবু দে এতেল্লে আইসতাম পাইত্তাম নো</t>
+    <t>আজিয়ে অফিসুত যন ফরিবু দে এতেল্লে আইসতাম ফাইত্তাম নো</t>
   </si>
   <si>
     <t>তোমার ভাই কে বলিও আমাকে কিছু টাকা ধার দিতে</t>
@@ -3574,6 +3574,162 @@
   </si>
   <si>
     <t>আত্তুন তো আর হায় দায় হাজ নাই</t>
+  </si>
+  <si>
+    <t>তোমার এই কাপড়টা এখানে কেন? অন্যদিকে নিয়ে যাও জলদি</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হর ইবে এনডে কা? অন্যমিক্কে লই য হারা</t>
+  </si>
+  <si>
+    <t>তুমি টাকাগুলো এখন রাখ, পরে আমার লাগলে তোমার কাছ থেকে নেব</t>
+  </si>
+  <si>
+    <t>তুঁই টিয়া এগুন এহন রাহো, পরে আত্তুন লাগিলি তোঁয়াত্তুন লইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমি বলেছি যখন অবশ্যই সাহায্য করব</t>
+  </si>
+  <si>
+    <t>আঁই হইয়্যি যহন অবশ্যই সাহাইয্য গইজ্জুম</t>
+  </si>
+  <si>
+    <t>জুতাগুলো পাপোসের উপর রাখো</t>
+  </si>
+  <si>
+    <t>জুতা এগিন ফাফোসুর উদ্দি রাহো</t>
+  </si>
+  <si>
+    <t>ঘরে ঢোকার পূর্বে পাপোশে একবার পাগুলো মুছে তারপর ঢুকিও</t>
+  </si>
+  <si>
+    <t>ঘরোত ঢোকিবের আগে ফাফোসুত একবার টেং এগিন মুছি তারপর ঢুইক্কো</t>
+  </si>
+  <si>
+    <t>সকালের রোদে নাকি ভিটামিন ডি আছে</t>
+  </si>
+  <si>
+    <t>বেইন্নের রইদোত বলে ভিটেমিন ডি আছে</t>
+  </si>
+  <si>
+    <t>আমি আগেও বলেছি এবং এখনও বলছি, এই কাজ করা আমার পক্ষে সম্ভব না</t>
+  </si>
+  <si>
+    <t>আঁই আগেও হই আর এহনও হইর, হাম ইয়েন গরন আঁর পক্ষে সম্ভব ন</t>
+  </si>
+  <si>
+    <t>আপনি এই কাজটা অন্য কাউকে দেন, আমি করতে পারব না</t>
+  </si>
+  <si>
+    <t>অঁনে হাজ ইয়েন অন্য কিয়ারে দন, আঁই গরিত ফাইত্তাম ন</t>
+  </si>
+  <si>
+    <t>যা হয়েছে অনেক বেশি হয়েছে, আর করতে হবে না</t>
+  </si>
+  <si>
+    <t>যা অইয়্যি বত বেশি অইয়্যি, আর গরন ফইত্তো ন</t>
+  </si>
+  <si>
+    <t>আমি ওখানে যাওয়ার জন্য লাফাচ্ছি না</t>
+  </si>
+  <si>
+    <t>আঁই অনডে যাইবের লাই ন ফালাইর</t>
+  </si>
+  <si>
+    <t>আচ্ছা ঠিক আছে, একটু পর আমার অফিস শেষ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আইচ্ছে ঠিক আছে, এক্কানা পরে আঁর অফিস শেষ অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমার মাথায় একটা বুদ্ধি আসছে</t>
+  </si>
+  <si>
+    <t>আঁর মাথাত এক্কান বুদ্ধি আইসসি</t>
+  </si>
+  <si>
+    <t>এগুলো কি আমি কিছু বুঝতে পারছিনা</t>
+  </si>
+  <si>
+    <t>এগুন কি আঁই কিছু বুঝিত ন ফারির</t>
+  </si>
+  <si>
+    <t>আসলে সমস্যাটা আমার না, আমার বন্ধুর সমস্যা</t>
+  </si>
+  <si>
+    <t>আসলে সমস্যা ইয়েন আঁর ন, আঁর বন্ধুর সমস্যা</t>
+  </si>
+  <si>
+    <t>কার কপালে কি লিখা আছে সেটা একমাত্র আল্লাহ ভাল জানেন</t>
+  </si>
+  <si>
+    <t>হার হোওয়ালুত কি লেহা আছে ইয়েন একমাত্র আল্লাহ ভালা জানে</t>
+  </si>
+  <si>
+    <t>আশা করি ওরা একসাথে ভাল থাকবে</t>
+  </si>
+  <si>
+    <t>আশা গরি ইতারা এক্কোওয়ারে ভালা থাহিবু</t>
+  </si>
+  <si>
+    <t>বন্ধুকে বললাম একা একা না থেকে একটা বিয়ে করে নিতে</t>
+  </si>
+  <si>
+    <t>বন্ধুরে হইলাম এহেল্লে এহেল্লে ন থাহি উজ্ঞো বিয়ে গরি লইতো</t>
+  </si>
+  <si>
+    <t>আমার বোন আমাকে বলে আমি নাকি বিয়ে করলে তাকে ভুলে যাব</t>
+  </si>
+  <si>
+    <t>আঁর বইন আঁরে হয়দে আঁই বলে বিয়ে গরিলি ইতিরে ভুলি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় আব্বুর পকেট থেকে অনেকবার টাকা চুরি করেছিলাম</t>
+  </si>
+  <si>
+    <t>ছোডোবেলাত আব্বুর পকেট উত্তুন বতবার টিয়া চুরি গইজ্জিলাম</t>
+  </si>
+  <si>
+    <t>ডাব চুরি করতে গিয়ে একবার বাবার হাতে মার খেয়েছিলাম</t>
+  </si>
+  <si>
+    <t>ডাফ চুরি গইত্তো যায় একবার বাফুর আতুত মাইর হাইলাম</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় প্রতিদিন রাতে আব্বু আমাদেরকে গল্প শোনাত</t>
+  </si>
+  <si>
+    <t>ছো্ডোবেলাত ফইত্তোদিন রাতিয়ে আব্বু আঁরারে গল্প উনাইতু</t>
+  </si>
+  <si>
+    <t>আমার পাঁচটা মামাতো বোন আছে</t>
+  </si>
+  <si>
+    <t>আত্তুন পাঁচচো মঅতু বইন আছে</t>
+  </si>
+  <si>
+    <t>নানুর বাড়ি গেলে মামাতো ভাইবোনদের সাথে অনেক গল্প হয়</t>
+  </si>
+  <si>
+    <t>নানারো বারিত যাইলি মঅতু ভাই বইন অক্কলুর লগে বত গল্প অই</t>
+  </si>
+  <si>
+    <t>আমার নানুর বাড়ি থেকে খালুর বাড়ি বেশি দূরে না</t>
+  </si>
+  <si>
+    <t>আঁর নানারো বারিত্তুন হালারো বারি বেশি দুরে ন</t>
+  </si>
+  <si>
+    <t>নানুর বাড়ি থেকে খালুর বাড়ি কম যাওয়া হয়</t>
+  </si>
+  <si>
+    <t>নানারো বারিত্তুন হালারো বারিত হম যায়</t>
+  </si>
+  <si>
+    <t>প্রতিবার ঈদের দিন নানুর বাড়িতে যায়</t>
+  </si>
+  <si>
+    <t>পইত্তোবার ঈদুর দিন নানারো বারিত যায়</t>
   </si>
 </sst>
 </file>
@@ -9431,108 +9587,212 @@
       </c>
     </row>
     <row r="586" ht="25" customHeight="1" spans="1:2">
-      <c r="A586" s="2"/>
-      <c r="B586" s="2"/>
+      <c r="A586" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="587" ht="25" customHeight="1" spans="1:2">
-      <c r="A587" s="2"/>
-      <c r="B587" s="2"/>
+      <c r="A587" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>1168</v>
+      </c>
     </row>
     <row r="588" ht="25" customHeight="1" spans="1:2">
-      <c r="A588" s="2"/>
-      <c r="B588" s="2"/>
+      <c r="A588" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>1170</v>
+      </c>
     </row>
     <row r="589" ht="25" customHeight="1" spans="1:2">
-      <c r="A589" s="2"/>
-      <c r="B589" s="2"/>
+      <c r="A589" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="590" ht="25" customHeight="1" spans="1:2">
-      <c r="A590" s="2"/>
-      <c r="B590" s="2"/>
+      <c r="A590" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>1174</v>
+      </c>
     </row>
     <row r="591" ht="25" customHeight="1" spans="1:2">
-      <c r="A591" s="2"/>
-      <c r="B591" s="2"/>
+      <c r="A591" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="592" ht="25" customHeight="1" spans="1:2">
-      <c r="A592" s="2"/>
-      <c r="B592" s="2"/>
+      <c r="A592" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>1178</v>
+      </c>
     </row>
     <row r="593" ht="25" customHeight="1" spans="1:2">
-      <c r="A593" s="2"/>
-      <c r="B593" s="2"/>
+      <c r="A593" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>1180</v>
+      </c>
     </row>
     <row r="594" ht="25" customHeight="1" spans="1:2">
-      <c r="A594" s="2"/>
-      <c r="B594" s="2"/>
+      <c r="A594" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>1182</v>
+      </c>
     </row>
     <row r="595" ht="25" customHeight="1" spans="1:2">
-      <c r="A595" s="2"/>
-      <c r="B595" s="2"/>
+      <c r="A595" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>1184</v>
+      </c>
     </row>
     <row r="596" ht="25" customHeight="1" spans="1:2">
-      <c r="A596" s="2"/>
-      <c r="B596" s="2"/>
+      <c r="A596" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>1186</v>
+      </c>
     </row>
     <row r="597" ht="25" customHeight="1" spans="1:2">
-      <c r="A597" s="2"/>
-      <c r="B597" s="2"/>
+      <c r="A597" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>1188</v>
+      </c>
     </row>
     <row r="598" ht="25" customHeight="1" spans="1:2">
-      <c r="A598" s="2"/>
-      <c r="B598" s="2"/>
+      <c r="A598" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>1190</v>
+      </c>
     </row>
     <row r="599" ht="25" customHeight="1" spans="1:2">
-      <c r="A599" s="2"/>
-      <c r="B599" s="2"/>
+      <c r="A599" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>1192</v>
+      </c>
     </row>
     <row r="600" ht="25" customHeight="1" spans="1:2">
-      <c r="A600" s="2"/>
-      <c r="B600" s="2"/>
+      <c r="A600" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="601" ht="25" customHeight="1" spans="1:2">
-      <c r="A601" s="2"/>
-      <c r="B601" s="2"/>
+      <c r="A601" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>1196</v>
+      </c>
     </row>
     <row r="602" ht="25" customHeight="1" spans="1:2">
-      <c r="A602" s="2"/>
-      <c r="B602" s="2"/>
+      <c r="A602" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>1198</v>
+      </c>
     </row>
     <row r="603" ht="25" customHeight="1" spans="1:2">
-      <c r="A603" s="2"/>
-      <c r="B603" s="2"/>
+      <c r="A603" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>1200</v>
+      </c>
     </row>
     <row r="604" ht="25" customHeight="1" spans="1:2">
-      <c r="A604" s="2"/>
-      <c r="B604" s="2"/>
+      <c r="A604" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>1202</v>
+      </c>
     </row>
     <row r="605" ht="25" customHeight="1" spans="1:2">
-      <c r="A605" s="2"/>
-      <c r="B605" s="2"/>
+      <c r="A605" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>1204</v>
+      </c>
     </row>
     <row r="606" ht="25" customHeight="1" spans="1:2">
-      <c r="A606" s="2"/>
-      <c r="B606" s="2"/>
+      <c r="A606" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>1206</v>
+      </c>
     </row>
     <row r="607" ht="25" customHeight="1" spans="1:2">
-      <c r="A607" s="2"/>
-      <c r="B607" s="2"/>
+      <c r="A607" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>1208</v>
+      </c>
     </row>
     <row r="608" ht="25" customHeight="1" spans="1:2">
-      <c r="A608" s="2"/>
-      <c r="B608" s="2"/>
+      <c r="A608" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="609" ht="25" customHeight="1" spans="1:2">
-      <c r="A609" s="2"/>
-      <c r="B609" s="2"/>
+      <c r="A609" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="610" ht="25" customHeight="1" spans="1:2">
-      <c r="A610" s="2"/>
-      <c r="B610" s="2"/>
+      <c r="A610" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>1214</v>
+      </c>
     </row>
     <row r="611" ht="25" customHeight="1" spans="1:2">
-      <c r="A611" s="2"/>
-      <c r="B611" s="2"/>
+      <c r="A611" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="612" ht="25" customHeight="1" spans="1:2">
       <c r="A612" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1221">
   <si>
     <t>bangla</t>
   </si>
@@ -3730,6 +3730,18 @@
   </si>
   <si>
     <t>পইত্তোবার ঈদুর দিন নানারো বারিত যায়</t>
+  </si>
+  <si>
+    <t>আমি একবার পুকুরে পড়ে গিয়েছিলাম</t>
+  </si>
+  <si>
+    <t>আঁই একবার ফইরোত ফরি গেইলাম</t>
+  </si>
+  <si>
+    <t>তখন আল্লাহ আমাকে বাঁচিয়েছিলেন</t>
+  </si>
+  <si>
+    <t>তহন আল্লাহ আঁরে বাচাইয়্যিল</t>
   </si>
 </sst>
 </file>
@@ -9795,12 +9807,20 @@
       </c>
     </row>
     <row r="612" ht="25" customHeight="1" spans="1:2">
-      <c r="A612" s="2"/>
-      <c r="B612" s="2"/>
+      <c r="A612" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="613" ht="25" customHeight="1" spans="1:2">
-      <c r="A613" s="2"/>
-      <c r="B613" s="2"/>
+      <c r="A613" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="614" ht="25" customHeight="1" spans="1:2">
       <c r="A614" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1233">
   <si>
     <t>bangla</t>
   </si>
@@ -2355,7 +2355,7 @@
     <t>আজকে বন্ধুর বাসায় দাওয়াত আছে, তাই দুপুরে খাব না</t>
   </si>
   <si>
-    <t>আজয়ি বন্ধুর বাসাত দত আছে, এতেল্লে দুইজ্জে হাইতাম নো</t>
+    <t>আজয়ি বন্ধুর বাসাত দঅত আছে, এতেল্লে দুইজ্জে হাইতাম নো</t>
   </si>
   <si>
     <t>বাইরে কেন দাঁড়ায় আছিস, ভিতরে আই</t>
@@ -2961,7 +2961,7 @@
     <t>আজকে দুপুরে একটা বিয়ের দাওয়াত ছিল</t>
   </si>
   <si>
-    <t>আজিয়ে দুইজ্জে এক্কান বিয়ের দত আছিল</t>
+    <t>আজিয়ে দুইজ্জে এক্কান বিয়ের দঅত আছিল</t>
   </si>
   <si>
     <t>বিয়ে বাড়ির খাবারগুলো অনেক ভালো ছিল</t>
@@ -3742,6 +3742,42 @@
   </si>
   <si>
     <t>তহন আল্লাহ আঁরে বাচাইয়্যিল</t>
+  </si>
+  <si>
+    <t>আমার চাচারা আমাদের দেখে হিংসা করে</t>
+  </si>
+  <si>
+    <t>আঁর চাচা অক্কল আঁরারে দেহি হিংসে গরে</t>
+  </si>
+  <si>
+    <t>ওরা সবসময় আমাদের পিছনে লেগে থাকে</t>
+  </si>
+  <si>
+    <t>ইতারা সবসময় আঁরার পিছুদ্দি লাগি থাহে</t>
+  </si>
+  <si>
+    <t>লুকিয়ে থেকে লাভ নাই, আমি তোমাকে দেখে ফেলেছি</t>
+  </si>
+  <si>
+    <t>গুজি থাহি লাভ নাই, আঁই তোঁয়ারে দেহি ফেলাই</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে আম্মুর সাথে অনেক ঝগড়া হয়</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে আম্মুর লগে বত হইজ্জে অই</t>
+  </si>
+  <si>
+    <t>আমার খালাতো ভাই মিজান অনেক দুষ্টু, ছোটবেলায় ওর সাথে অনেক ঝগড়া হতো</t>
+  </si>
+  <si>
+    <t>আঁর হালতু ভাই মিজান বত জারগো, গুরো থাকতে ইতের লগে বত হইজ্জে অইতু</t>
+  </si>
+  <si>
+    <t>আজকে আমার এক আত্মীয়ের বাড়িতে দাওয়াত আছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে আঁর উজ্ঞো আত্মীয়র বারিত দঅত আছে</t>
   </si>
 </sst>
 </file>
@@ -9823,28 +9859,52 @@
       </c>
     </row>
     <row r="614" ht="25" customHeight="1" spans="1:2">
-      <c r="A614" s="2"/>
-      <c r="B614" s="2"/>
+      <c r="A614" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="615" ht="25" customHeight="1" spans="1:2">
-      <c r="A615" s="2"/>
-      <c r="B615" s="2"/>
+      <c r="A615" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>1224</v>
+      </c>
     </row>
     <row r="616" ht="25" customHeight="1" spans="1:2">
-      <c r="A616" s="2"/>
-      <c r="B616" s="2"/>
+      <c r="A616" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="617" ht="25" customHeight="1" spans="1:2">
-      <c r="A617" s="2"/>
-      <c r="B617" s="2"/>
+      <c r="A617" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="618" ht="25" customHeight="1" spans="1:2">
-      <c r="A618" s="2"/>
-      <c r="B618" s="2"/>
+      <c r="A618" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="619" ht="25" customHeight="1" spans="1:2">
-      <c r="A619" s="2"/>
-      <c r="B619" s="2"/>
+      <c r="A619" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>1232</v>
+      </c>
     </row>
     <row r="620" ht="25" customHeight="1" spans="1:2">
       <c r="A620" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="1297">
   <si>
     <t>bangla</t>
   </si>
@@ -203,7 +203,7 @@
     <t>সমস্যা নাই, তুমি আগামিকাল আসতে পারবে</t>
   </si>
   <si>
-    <t>সমস্যা নাই, তুঁই হালিইয়্যে আইত পারিবে</t>
+    <t>সমস্যা নাই, তুঁই হালিইয়্যে আইত ফারিবে</t>
   </si>
   <si>
     <t>আমার আজকে একটু শরীর খারাপ</t>
@@ -245,7 +245,7 @@
     <t>আপনি আগামিকাল আসতে পারবেন?</t>
   </si>
   <si>
-    <t>অঁনে হালিইয়্যে আইত পারিবেন?</t>
+    <t>অঁনে হালিইয়্যে আইত ফারিবেন?</t>
   </si>
   <si>
     <t>স্যার, আমি কি আসতে পারি?</t>
@@ -317,7 +317,7 @@
     <t>আপনি কি একটু সাহায্য করতে পারবেন?</t>
   </si>
   <si>
-    <t>অঁনে কি এক্কানা সাহাইয্য গরিত পারিবেন?</t>
+    <t>অঁনে কি এক্কানা সাহাইয্য গরিত ফারিবেন?</t>
   </si>
   <si>
     <t>আমি একটা বিপদে পড়েছি</t>
@@ -545,7 +545,7 @@
     <t>আমি কি চাই সেটা তুমি আমার চেহারা দেখে বলতে পারবেনা?</t>
   </si>
   <si>
-    <t>আঁই কি চাই ইয়েন তুঁই আঁর চিয়ারা দেহি হইত নপারিবে?</t>
+    <t>আঁই কি চাই ইয়েন তুঁই আঁর চিয়ারা দেহি হইত ন ফারিবে?</t>
   </si>
   <si>
     <t>তোমার চেহেরা দেখে আমি বুঝছি, একদম শুকায় গেছে</t>
@@ -3687,7 +3687,7 @@
     <t>ছোটবেলায় আব্বুর পকেট থেকে অনেকবার টাকা চুরি করেছিলাম</t>
   </si>
   <si>
-    <t>ছোডোবেলাত আব্বুর পকেট উত্তুন বতবার টিয়া চুরি গইজ্জিলাম</t>
+    <t>গুরো থাকতে আব্বুর পকেট উত্তুন বতবার টিয়া চুরি গইজ্জিলাম</t>
   </si>
   <si>
     <t>ডাব চুরি করতে গিয়ে একবার বাবার হাতে মার খেয়েছিলাম</t>
@@ -3699,7 +3699,7 @@
     <t>ছোটবেলায় প্রতিদিন রাতে আব্বু আমাদেরকে গল্প শোনাত</t>
   </si>
   <si>
-    <t>ছো্ডোবেলাত ফইত্তোদিন রাতিয়ে আব্বু আঁরারে গল্প উনাইতু</t>
+    <t>গুরো থাকতে ফইত্তোদিন রাতিয়ে আব্বু আঁরারে গল্প উনাইতু</t>
   </si>
   <si>
     <t>আমার পাঁচটা মামাতো বোন আছে</t>
@@ -3778,6 +3778,198 @@
   </si>
   <si>
     <t>আজিয়ে আঁর উজ্ঞো আত্মীয়র বারিত দঅত আছে</t>
+  </si>
+  <si>
+    <t>সামনের মাস থেকে আমার মামিরা শহরে চলে যাবে</t>
+  </si>
+  <si>
+    <t>সামনুর মাসুত্তুন আঁর মামি অক্কল শ'রুত চলি যাইবু</t>
+  </si>
+  <si>
+    <t>গতকাল ফুফাতো ভাইয়ের সাথে অনেক জায়গায় বাসা খুঁজেছি</t>
+  </si>
+  <si>
+    <t>গত হালিয়ে ফোতু ভাইয়ুর লগে বত জাগাত বাসা তোওয়াই</t>
+  </si>
+  <si>
+    <t>বাসা খুঁজতে খুঁজতে পা ব্যথা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>বাসা তোওয়াইতে তোওয়াইতে টেং ব্যথা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার ছোট ভাই শুধু বাবাকে ভয় পায়</t>
+  </si>
+  <si>
+    <t>আঁর ছোডো ভাই উদো আব্বুরে ডরাই দে</t>
+  </si>
+  <si>
+    <t>আমার বড় আপু আর ছোট আপু সবসময় ঝগড়া করে</t>
+  </si>
+  <si>
+    <t>আঁর বরো আফা আর ছোডো আফা সবসময় হইজ্জে গরে</t>
+  </si>
+  <si>
+    <t>একবার আম্মু ওদের দুজনকে অনেক মেরেছিল</t>
+  </si>
+  <si>
+    <t>একবার আম্মু ইতারা দুনুজনোরে বত মেইজ্জিল</t>
+  </si>
+  <si>
+    <t>আমি একবার বেহুঁশ হয়ে গিয়েছিলাম</t>
+  </si>
+  <si>
+    <t>আঁই একবার বেউশ অই গেইলাম</t>
+  </si>
+  <si>
+    <t>যখন আমার জ্ঞান ফিরে, তখন দেখি আম্মু আমার সামনে দাঁড়িয়ে আছে</t>
+  </si>
+  <si>
+    <t>যহন আঁর উশ আইয়্যি, তহন দেহি আম্মু আঁর সাম্মোদ্দি থিয়েই থেইক্কি</t>
+  </si>
+  <si>
+    <t>শুনেছি তোমার বড় ভাইয়ের নাকি চাকরি হয়েছে?</t>
+  </si>
+  <si>
+    <t>উইন্নি তোঁয়ার বদ্দার বলে ছরি অইয়্যি?</t>
+  </si>
+  <si>
+    <t>বড় ভাইয়ের শ্বশুরবাড়ি অনেক দূরে</t>
+  </si>
+  <si>
+    <t>বদ্দার অরো বারি বত দুরে</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় নানুর বাড়ি, যৌবনকালে শ্বশুরবাড়ি</t>
+  </si>
+  <si>
+    <t>গুরো হালে নানারো বারি, যোওয়ান হালে অরো বারি</t>
+  </si>
+  <si>
+    <t>আপনার ছোট ছেলে তো সাত সকালে বের হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>অঁনোর গুরো ফুয়া ইবে তো বেইন্নে ফজোরত বাইর অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সারাদিন শুধু এই বাগান আর ওই বাগানে ঘুরাঘুরি করো</t>
+  </si>
+  <si>
+    <t>আরাদিন উদো এই বাগান আর ওই বাগানুত ঘুরোঘুরি গরো</t>
+  </si>
+  <si>
+    <t>নিজের ঘরে থাকলে নিজের মতো করে থাকা যায়</t>
+  </si>
+  <si>
+    <t>নিজোর ঘরোত থাহিলি নিজোর মতোন গরি থাহন যায়</t>
+  </si>
+  <si>
+    <t>এখন আর নানুর বাড়িতে আগের মতো ভালো লাগে না</t>
+  </si>
+  <si>
+    <t>এহন আর নানারো বারিত আগোর মতোন ভালা ন লাগে</t>
+  </si>
+  <si>
+    <t>বান্দরের মতো শুধু গাছে গাছে ঘোরে, কোনোদিন পরে হাত পা ভাঙবে কে জানে</t>
+  </si>
+  <si>
+    <t>বান্দরোর মতোন উদো গাছে গাছে ঘুরে, হনদিন ফরি আত টেং ভাঙিবু হনে জানে</t>
+  </si>
+  <si>
+    <t>আমি ছোটবেলায় তোদের মতো এত দুষ্টু ছিলাম না</t>
+  </si>
+  <si>
+    <t>আঁই গুরো থাকতে তোরার মতোন এল্লেত জারগো ন আছিলাম</t>
+  </si>
+  <si>
+    <t>এই মাঠে কাদা বেশি, এখানে খেলা যাবে না</t>
+  </si>
+  <si>
+    <t>এই মাডোত ফুট বেশি, এনডে খেলন যাইতু ন</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় আপুদের সাথে কাদা মাটি দিয়ে নানা রকম জিনিস বানাতাম</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে আফা তারার লগে ফুট দি নানা রহম জিনিস বানাইতাম</t>
+  </si>
+  <si>
+    <t>মুরগি দুটো হাটে নিয়ে গিয়ে বিক্রি করে আয়</t>
+  </si>
+  <si>
+    <t>কুরো দুনু অ আডোত লই যায় রে বেছি আয়</t>
+  </si>
+  <si>
+    <t>গ্রামের মেয়েরা হাঁস মুরগি পালন করে</t>
+  </si>
+  <si>
+    <t>গ্রামোর মাইফুয়া অক্কলে আঁস কুরো ফালে</t>
+  </si>
+  <si>
+    <t>পুকুরে অনেক বড় একটা শোল মাছ দেখেছি</t>
+  </si>
+  <si>
+    <t>ফইরোত বত বরো উজ্ঞো অলি মাছি দেইক্কি</t>
+  </si>
+  <si>
+    <t>নানুর বয়স হয়েছে, সেজন্য সবকিছু ভুলে যায়</t>
+  </si>
+  <si>
+    <t>নানির বয়স অইয়্যি, এতেল্লে বিয়াক ভুলি যায়</t>
+  </si>
+  <si>
+    <t>নানু থাকলে আম্মু আর আমাদেরকে বকা দিতে পারে না</t>
+  </si>
+  <si>
+    <t>নানি থাহিলি আম্মু আর আঁরারে গেইল দিত ন ফারে</t>
+  </si>
+  <si>
+    <t>নানা যখন বেঁচে ছিলেন, তখন আমাদেরকে অনেক দেখতে পারতেন</t>
+  </si>
+  <si>
+    <t>নানা যহন বাঁছি আছিল, তহন আঁরারে বত দেইত ফাইত্তো</t>
+  </si>
+  <si>
+    <t>নানা বেঁচে থাকতে আমাদেরকে অনেক দেখতে পারতেন</t>
+  </si>
+  <si>
+    <t>নানা বাঁছি থাইকতে আঁরারে বত দেইত ফাইত্তো</t>
+  </si>
+  <si>
+    <t>প্রতিদিন এতো দেরি করে ঘুম থেকে উঠলে তো কিছু জানতে পারবে না</t>
+  </si>
+  <si>
+    <t>ফইত্তোদিন এল্লেত দেরি গরি ঘুমোত্তুন উডিলি তো কিছু জানিত ন ফারিবে</t>
+  </si>
+  <si>
+    <t>সূর্য কখন উঠছে কোন খবর আছে? এখনো ঘুমাচ্ছো</t>
+  </si>
+  <si>
+    <t>সূর্য হত্তে  উইট্টি হনো হবর আছে? এহনো ঘুম যার</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে প্রতিবেশীদেরও খোঁজখবর নিতে হয়</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে প্রতিবেশী অক্কলোরও হোচ হবর লন ফরে</t>
+  </si>
+  <si>
+    <t>কল দেব ভাইয়া? আমি এখন বাইরে আছি</t>
+  </si>
+  <si>
+    <t>কল দিয়্যুম ভাইয়ে? আঁই এহন বাইরে আছি</t>
+  </si>
+  <si>
+    <t>প্রতিবেশীদের হক আদায় করা উচিত</t>
+  </si>
+  <si>
+    <t>প্রতিবেশী অক্কলোর হক আদায় গরন উচিত</t>
+  </si>
+  <si>
+    <t>বিপদে অনেক সময় প্রতিবেশীরা কাজে আসে</t>
+  </si>
+  <si>
+    <t>বিপদুত বত সময় প্রতিবেশী অক্কল হাজোত আইয়্যি</t>
   </si>
 </sst>
 </file>
@@ -9907,132 +10099,260 @@
       </c>
     </row>
     <row r="620" ht="25" customHeight="1" spans="1:2">
-      <c r="A620" s="2"/>
-      <c r="B620" s="2"/>
+      <c r="A620" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="621" ht="25" customHeight="1" spans="1:2">
-      <c r="A621" s="2"/>
-      <c r="B621" s="2"/>
+      <c r="A621" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="622" ht="25" customHeight="1" spans="1:2">
-      <c r="A622" s="2"/>
-      <c r="B622" s="2"/>
+      <c r="A622" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="623" ht="25" customHeight="1" spans="1:2">
-      <c r="A623" s="2"/>
-      <c r="B623" s="2"/>
+      <c r="A623" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>1240</v>
+      </c>
     </row>
     <row r="624" ht="25" customHeight="1" spans="1:2">
-      <c r="A624" s="2"/>
-      <c r="B624" s="2"/>
+      <c r="A624" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="625" ht="25" customHeight="1" spans="1:2">
-      <c r="A625" s="2"/>
-      <c r="B625" s="2"/>
+      <c r="A625" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="626" ht="25" customHeight="1" spans="1:2">
-      <c r="A626" s="2"/>
-      <c r="B626" s="2"/>
+      <c r="A626" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="627" ht="25" customHeight="1" spans="1:2">
-      <c r="A627" s="2"/>
-      <c r="B627" s="2"/>
+      <c r="A627" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="628" ht="25" customHeight="1" spans="1:2">
-      <c r="A628" s="2"/>
-      <c r="B628" s="2"/>
+      <c r="A628" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>1250</v>
+      </c>
     </row>
     <row r="629" ht="25" customHeight="1" spans="1:2">
-      <c r="A629" s="2"/>
-      <c r="B629" s="2"/>
+      <c r="A629" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="630" ht="25" customHeight="1" spans="1:2">
-      <c r="A630" s="2"/>
-      <c r="B630" s="2"/>
+      <c r="A630" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="631" ht="25" customHeight="1" spans="1:2">
-      <c r="A631" s="2"/>
-      <c r="B631" s="2"/>
+      <c r="A631" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="632" ht="25" customHeight="1" spans="1:2">
-      <c r="A632" s="2"/>
-      <c r="B632" s="2"/>
+      <c r="A632" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>1258</v>
+      </c>
     </row>
     <row r="633" ht="25" customHeight="1" spans="1:2">
-      <c r="A633" s="2"/>
-      <c r="B633" s="2"/>
+      <c r="A633" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>1260</v>
+      </c>
     </row>
     <row r="634" ht="25" customHeight="1" spans="1:2">
-      <c r="A634" s="2"/>
-      <c r="B634" s="2"/>
+      <c r="A634" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>1262</v>
+      </c>
     </row>
     <row r="635" ht="25" customHeight="1" spans="1:2">
-      <c r="A635" s="2"/>
-      <c r="B635" s="2"/>
+      <c r="A635" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>1264</v>
+      </c>
     </row>
     <row r="636" ht="25" customHeight="1" spans="1:2">
-      <c r="A636" s="2"/>
-      <c r="B636" s="2"/>
+      <c r="A636" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>1266</v>
+      </c>
     </row>
     <row r="637" ht="25" customHeight="1" spans="1:2">
-      <c r="A637" s="2"/>
-      <c r="B637" s="2"/>
+      <c r="A637" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="638" ht="25" customHeight="1" spans="1:2">
-      <c r="A638" s="2"/>
-      <c r="B638" s="2"/>
+      <c r="A638" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>1270</v>
+      </c>
     </row>
     <row r="639" ht="25" customHeight="1" spans="1:2">
-      <c r="A639" s="2"/>
-      <c r="B639" s="2"/>
+      <c r="A639" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>1272</v>
+      </c>
     </row>
     <row r="640" ht="25" customHeight="1" spans="1:2">
-      <c r="A640" s="2"/>
-      <c r="B640" s="2"/>
+      <c r="A640" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>1274</v>
+      </c>
     </row>
     <row r="641" ht="25" customHeight="1" spans="1:2">
-      <c r="A641" s="2"/>
-      <c r="B641" s="2"/>
+      <c r="A641" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1276</v>
+      </c>
     </row>
     <row r="642" ht="25" customHeight="1" spans="1:2">
-      <c r="A642" s="2"/>
-      <c r="B642" s="2"/>
+      <c r="A642" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="643" ht="25" customHeight="1" spans="1:2">
-      <c r="A643" s="2"/>
-      <c r="B643" s="2"/>
+      <c r="A643" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="644" ht="25" customHeight="1" spans="1:2">
-      <c r="A644" s="2"/>
-      <c r="B644" s="2"/>
+      <c r="A644" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="645" ht="25" customHeight="1" spans="1:2">
-      <c r="A645" s="2"/>
-      <c r="B645" s="2"/>
+      <c r="A645" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>1284</v>
+      </c>
     </row>
     <row r="646" ht="25" customHeight="1" spans="1:2">
-      <c r="A646" s="2"/>
-      <c r="B646" s="2"/>
+      <c r="A646" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="647" ht="25" customHeight="1" spans="1:2">
-      <c r="A647" s="2"/>
-      <c r="B647" s="2"/>
+      <c r="A647" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>1288</v>
+      </c>
     </row>
     <row r="648" ht="25" customHeight="1" spans="1:2">
-      <c r="A648" s="2"/>
-      <c r="B648" s="2"/>
+      <c r="A648" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="649" ht="25" customHeight="1" spans="1:2">
-      <c r="A649" s="2"/>
-      <c r="B649" s="2"/>
+      <c r="A649" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>1292</v>
+      </c>
     </row>
     <row r="650" ht="25" customHeight="1" spans="1:2">
-      <c r="A650" s="2"/>
-      <c r="B650" s="2"/>
+      <c r="A650" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1294</v>
+      </c>
     </row>
     <row r="651" ht="25" customHeight="1" spans="1:2">
-      <c r="A651" s="2"/>
-      <c r="B651" s="2"/>
+      <c r="A651" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="652" ht="25" customHeight="1" spans="1:2">
       <c r="A652" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="1397">
   <si>
     <t>bangla</t>
   </si>
@@ -1281,7 +1281,7 @@
     <t>ভোরে সূর্য ওঠার আগেই আমি উঠে পড়ি, তারপর নামাজ পড়ি</t>
   </si>
   <si>
-    <t>ফোয়াত্তে সূর্য উডিবের আগেই আঁই উডি যায়, তারপর নামাজ পরি</t>
+    <t>ফোওয়াত্তে সূর্য উডিবের আগেই আঁই উডি যায়, তারপর নামাজ পরি</t>
   </si>
   <si>
     <t>সকালের সূর্য অনেক সুন্দর</t>
@@ -2823,7 +2823,7 @@
     <t>প্রতিদিন নিয়ম করে দাঁত মাজা উচিত</t>
   </si>
   <si>
-    <t>ফইত্তোদিন নিয়ম গরি দাঁত মাজন উচিত</t>
+    <t>ফইত্তোদিন নিয়ম গরি দাত মাজন উচিত</t>
   </si>
   <si>
     <t>দাঁত না মাজলে দাঁতে পোকা হবে</t>
@@ -3519,7 +3519,7 @@
     <t>আমাকে একটু রান্নাঘর কোনদিকে সেটা দেখিয়ে দিন</t>
   </si>
   <si>
-    <t>আঁরে এক্কানা রান্নাঘর হুনদি ইয়েন দেহায় দন</t>
+    <t>আঁরে এক্কানা বসহানা হুনদি ইয়েন দেহায় দন</t>
   </si>
   <si>
     <t>আমাকে একটু চিনি কম দিয়ে এক কাপ চা দিও</t>
@@ -3970,6 +3970,332 @@
   </si>
   <si>
     <t>বিপদুত বত সময় প্রতিবেশী অক্কল হাজোত আইয়্যি</t>
+  </si>
+  <si>
+    <t>দাঁতের মাজনটা কোথায় আম্মু?</t>
+  </si>
+  <si>
+    <t>দাতোর মাজন ইবে হনডে আম্মু?</t>
+  </si>
+  <si>
+    <t>দাঁতের মাজনটা তোর মেজো ভাইয়ের রুমে</t>
+  </si>
+  <si>
+    <t>দাতোর মাজন ইবে তুর মেজো ভাইয়োর রোমুত</t>
+  </si>
+  <si>
+    <t>মানুষ নাকি দাঁত থাকতে দাঁতের মর্যাদা বুঝে না</t>
+  </si>
+  <si>
+    <t>মানুষ বলে দাত থাইকতে দাতোর মুইল্য ন বুঝে</t>
+  </si>
+  <si>
+    <t>বাবা যেরকম ছেলেও সেরকম হয়েছে</t>
+  </si>
+  <si>
+    <t>বাফ যেরহম ফোয়া ও সেরহম অইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার মা সবসময় চায় যেন আমরা তিন ভাই একসাথে থাকি</t>
+  </si>
+  <si>
+    <t>আঁর মা সবসময় চায় যেন্‌ আরা তিন ভাই এক্কোওয়ারে থাহি</t>
+  </si>
+  <si>
+    <t>আমি রমিজের মা, রাতুলের দাদি</t>
+  </si>
+  <si>
+    <t>আঁই রমিজুর মা, রাতুলুর দাদি</t>
+  </si>
+  <si>
+    <t>মেয়েটা একদম তার মায়ের মতো হয়েছে</t>
+  </si>
+  <si>
+    <t>মাইফোয়া একদম ইতির মা'র মতন অইয়্যি</t>
+  </si>
+  <si>
+    <t>স্বভাব চরিত্র তো সব তোর ভাইয়ের মতো হয়েছে</t>
+  </si>
+  <si>
+    <t>হাস্তা হাসিলত তো বিয়াক তুর ভাইয়ুর মতন অইয়্যি</t>
+  </si>
+  <si>
+    <t>এভাবে চলাফেরা করলে গ্রামের মানুষজন আমাদেরকে খারাপ বলবে</t>
+  </si>
+  <si>
+    <t>এন গরি চালাফেরা গরিলি গ্রামুর মানুষজন আঁরারে হারাফ হইবু</t>
+  </si>
+  <si>
+    <t>মারুফ, তোর আপুকে একটু মেহেদি লাগিয়ে দে</t>
+  </si>
+  <si>
+    <t>মারুফ, তুর আফারে এক্কানা মে'দি লাগায় দে</t>
+  </si>
+  <si>
+    <t>তোর বাবা আমার চাচা এবং আমার বাবা তোর চাচা</t>
+  </si>
+  <si>
+    <t>তুর বাফ আঁর চাচা আর আঁর বাফ তুর চাচা</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>আমার আর খেয়ে</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>দেয়ে কাজ নেই, দশজনের জন্য দশরকম রান্না করব!</t>
+    </r>
+  </si>
+  <si>
+    <t>আত্তুন আর হায় দায় হাম নাই, দশজনোর লাই দশরহম রান্না গইজ্জুম!</t>
+  </si>
+  <si>
+    <t>ঝাল অনেক বেশি হয়েছে, একটু পানি দাও</t>
+  </si>
+  <si>
+    <t>ঝাল বত বেশি অইয়্যি, এক্কানা পানি দ</t>
+  </si>
+  <si>
+    <t>বন্ধু, বিড়ি খাওয়া ভাল না</t>
+  </si>
+  <si>
+    <t>বন্ধু, বিরি হন ভালা ন</t>
+  </si>
+  <si>
+    <t>আমি যদি আরেকবার তোকে বিড়ি খেতে দেখি, তাহলে তোর আব্বুকে বলে দেব</t>
+  </si>
+  <si>
+    <t>আঁই যদি আরেকবার তুরে বিরি হাইতু দেহি, তইলি তুর আব্বুরে হই দিয়্যুম</t>
+  </si>
+  <si>
+    <t>আজকের পর থেকে তরকারিতে ঝাল কম দিবা</t>
+  </si>
+  <si>
+    <t>আজিয়ের ফরোত্তুন তরহারিত ঝাল হম দিবে</t>
+  </si>
+  <si>
+    <t>আচ্ছা মা একটা কথা বলি?</t>
+  </si>
+  <si>
+    <t>আইচ্ছে মা এক্কান হতা হই?</t>
+  </si>
+  <si>
+    <t>আপনি তো আমার থেকেও আপনার মেয়েকেই বেশি দেখতে পারেন</t>
+  </si>
+  <si>
+    <t>অঁনে তো আত্তুন ও অঁনোর মাইফোয়ারেই বেশি দেইত ফারন</t>
+  </si>
+  <si>
+    <t>আমার কথার তো কোনো গুরুত্ব নেই, আপনি তো আপনার ছেলের কথাই শুনবেন</t>
+  </si>
+  <si>
+    <t>আঁর হতার তো হনো গুরুত্ব নেই, অঁনে তো অঁনোর ফোয়ার হতাই উনিবেন</t>
+  </si>
+  <si>
+    <t>লেবুর রস দিয়ে গরম গরম ছটপটি অনেক মজা লাগে</t>
+  </si>
+  <si>
+    <t>লেবুর রস দি গরম গরম ছটফডি বত মজা লাগে</t>
+  </si>
+  <si>
+    <t>ঘরে এত আজে বাজে খরচ করলে বেতনের টাকা তো দশদিনও যাবে না</t>
+  </si>
+  <si>
+    <t>ঘরোত এতো আজে বাজে হরচ গরিলি বেতনুর টিয়া তো দশদিনও ন যাইবু</t>
+  </si>
+  <si>
+    <t>রক্তের সম্পর্কের টান সবচেয়ে বেশি হয়</t>
+  </si>
+  <si>
+    <t>রক্তোর সম্পর্কর টান বিয়াজ্ঞুনুত্তুন বেশি অয়</t>
+  </si>
+  <si>
+    <t>ঘরে অনেক বেশি মাছি, খাবারগুলো ঢেকে রাখ</t>
+  </si>
+  <si>
+    <t>ঘরোত বত বেশি মাছি, হানা এগিন ঢাহি রাহো</t>
+  </si>
+  <si>
+    <t>কে পাদ দিয়েছে? এত গন্ধ কেন?</t>
+  </si>
+  <si>
+    <t>হনে ফাইদ্দি দে? এল্লেত গন্ধ কা?</t>
+  </si>
+  <si>
+    <t>মাথায় তেল দিলে অনেক আরাম লাগে</t>
+  </si>
+  <si>
+    <t>মাথাত তেল দিলি বত আরাম লাগে</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় আম্মু মাথায় তেল দিয়ে চুল আঁচড়ে দিতেন</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে আম্মু মাথাত তেল দি চুল আঁচুরি দিতো</t>
+  </si>
+  <si>
+    <t>আমি সাঁতার জানি না, সেজন্য পুকুরে নামতে পারব না</t>
+  </si>
+  <si>
+    <t>আঁই আছুরিত ন জানি, এতেল্লে ফইরুত নামিত ন ফাইজ্জুম</t>
+  </si>
+  <si>
+    <t>এবারের ঈদের পাঞ্জাবীটা অনেক সুন্দর হয়েছে</t>
+  </si>
+  <si>
+    <t>এবারোর ঈদুর পাঞ্জাবী ইবে বত সুন্দর অইয়্যি</t>
+  </si>
+  <si>
+    <t>ময়লাগুলো কোথায় রাখব মা?</t>
+  </si>
+  <si>
+    <t>হাচারা এগিন হনডে রাইক্কুম আম্মু?</t>
+  </si>
+  <si>
+    <t>আমি আম্মুকে বলেছিলাম, কিন্তু উনি রাজি হচ্ছেন না</t>
+  </si>
+  <si>
+    <t>আঁই আম্মুরে হইলাম, কিন্তু ইবে রাজি ন অর</t>
+  </si>
+  <si>
+    <t>বন্ধু, এবার ঈদে আমাকে এক জোড়া জুতা গিফট কর</t>
+  </si>
+  <si>
+    <t>বন্ধু, এবার ঈদুত আঁরে এক জোরা জুতা গিফট গর</t>
+  </si>
+  <si>
+    <t>ঘড়িটা তো অনেক সুন্দর! কত নিয়েছে এটা?</t>
+  </si>
+  <si>
+    <t>ঘড়ি ইবে তো বত সুন্দর! হতো লইয়্যি ইবে?</t>
+  </si>
+  <si>
+    <t>শার্টটা অনেক সুন্দর, কিন্তু তোর গায়ে মানায়নি</t>
+  </si>
+  <si>
+    <t>শার্ট ইবে বত সুন্দর, কিন্তু তুর গা'ত ন মানার</t>
+  </si>
+  <si>
+    <t>বন্ধু, ভাবির হাতের রান্না তো সেই মজা</t>
+  </si>
+  <si>
+    <t>বন্ধু, ভাবির আতোর রান্না তো সেই মজা</t>
+  </si>
+  <si>
+    <t>বিল থেকে কতগুলো টাকি মাছ ধরে এনেছি, এগুলো ভাল করে ধুয়ে মসলা দিয়ে তেলে ভেজে ফেল</t>
+  </si>
+  <si>
+    <t>বিলুত্তুন হদোজ্ঞুন টাই মাছ ধরি আইন্নি, এগুন ভালা গরি ধুয় মসল্লা দি তেলুত ভাজি ফেলো</t>
+  </si>
+  <si>
+    <t>কিরে বন্ধু! তুই নাকি লুকাই লুকাই প্রেম করছিস?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">কিরে বন্ধু! তুই বলে গুজি গুজি প্রেম গরর? </t>
+  </si>
+  <si>
+    <t>ভালো হয়ে যা বন্ধু, প্রেম করা ভালো না</t>
+  </si>
+  <si>
+    <t>ভালা অই যা বন্ধু, প্রেম গরন ভালা ন</t>
+  </si>
+  <si>
+    <t>আমি মামির সাথে কথা বলেছি, মামি বলছে তুমি চাইলে আমার সাথে বাসা দেখতে যেতে পার</t>
+  </si>
+  <si>
+    <t>আঁই মামির লগে হতা হইলাম, মামি হদ্দে তুঁই চাইলি আঁর লগে বাসা চাইতু যাইত পারো</t>
+  </si>
+  <si>
+    <t>হাসতে হাসতে আমার পেট ব্যথা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আ'সতে আ'সতে আঁর পেট ব্যথা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>প্রেম করিও না, প্রেম করলে তোমার সুন্দর জীবনটা নষ্ট হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>প্রেম ন গইজ্জো, প্রেম গরিলি তোঁয়ার সুন্দর জীবন ইয়েন নষ্ট অই যাইবু</t>
+  </si>
+  <si>
+    <t>এত কষ্ট পাওয়ার পরও কেন মানুষ প্রেমে পড়ে?</t>
+  </si>
+  <si>
+    <t>এদিজ্ঞিন হষ্ট ফাইবের পরও কেনে মানুষ প্রেমুত পরে?</t>
+  </si>
+  <si>
+    <t>নতুন নতুন প্রেমে পড়লে নাকি দুনিয়াটা রঙ্গিন লাগে</t>
+  </si>
+  <si>
+    <t>নয়া নয়া প্রেমুত ফরিলি বলে দুনিয়া দারি রঙ্গিন লাগে</t>
+  </si>
+  <si>
+    <t>আর কত বাটপারি করবি বন্ধু? এবার ভাল হয়ে যা</t>
+  </si>
+  <si>
+    <t>আর হত বাটফারি গরিবি বন্ধু? এবার ভালা অই যা</t>
+  </si>
+  <si>
+    <t>ভাত কি এখন নিয়ে আসব?</t>
+  </si>
+  <si>
+    <t>ভাত কি এহন লই আইসসুম</t>
+  </si>
+  <si>
+    <t>কিছু লাগলে আমাকে জানাবেন</t>
+  </si>
+  <si>
+    <t>কিছু লাগিলি আঁরে জানাইয়্যুন</t>
+  </si>
+  <si>
+    <t>শরীরটা বেশি দুর্বল লাগছে আজ</t>
+  </si>
+  <si>
+    <t>শরীর ইয়েন বেশি দুর্বল লাগের আজিয়ে</t>
+  </si>
+  <si>
+    <t>এত মজার বেগুন ভাজা আমি আগে কখনো খাইনি</t>
+  </si>
+  <si>
+    <t>এল্লেত মজার বেগুন ভাজা আঁই আগে হনোদিন ন হাই</t>
+  </si>
+  <si>
+    <t>মাংস বেশি নিস না, ওপর থেকে অল্প নে</t>
+  </si>
+  <si>
+    <t>গুস্ত বেশি ন লইস, উদ্দিত্তুন এক্কানা গরি ল</t>
+  </si>
+  <si>
+    <t>বাইরে যা ইচ্ছা কর, কিন্তু ঘরে অশান্তি করা যাবে না</t>
+  </si>
+  <si>
+    <t>বাইরে যেল্লেত ইচ্ছে গর, কিন্তু ঘরোত অশান্তি গরন যাইতু ন</t>
+  </si>
+  <si>
+    <t>আমার এক খালামণি ছিলেন, যিনি মুড়ি দিয়ে চা খেতেন</t>
+  </si>
+  <si>
+    <t>আঁর উজ্ঞো হালা আছিল, যিবে মুরি দি চা হাইতু</t>
   </si>
 </sst>
 </file>
@@ -10355,204 +10681,404 @@
       </c>
     </row>
     <row r="652" ht="25" customHeight="1" spans="1:2">
-      <c r="A652" s="2"/>
-      <c r="B652" s="2"/>
+      <c r="A652" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>1298</v>
+      </c>
     </row>
     <row r="653" ht="25" customHeight="1" spans="1:2">
-      <c r="A653" s="2"/>
-      <c r="B653" s="2"/>
+      <c r="A653" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>1300</v>
+      </c>
     </row>
     <row r="654" ht="25" customHeight="1" spans="1:2">
-      <c r="A654" s="2"/>
-      <c r="B654" s="2"/>
+      <c r="A654" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>1302</v>
+      </c>
     </row>
     <row r="655" ht="25" customHeight="1" spans="1:2">
-      <c r="A655" s="2"/>
-      <c r="B655" s="2"/>
+      <c r="A655" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1304</v>
+      </c>
     </row>
     <row r="656" ht="25" customHeight="1" spans="1:2">
-      <c r="A656" s="2"/>
-      <c r="B656" s="2"/>
+      <c r="A656" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>1306</v>
+      </c>
     </row>
     <row r="657" ht="25" customHeight="1" spans="1:2">
-      <c r="A657" s="2"/>
-      <c r="B657" s="2"/>
+      <c r="A657" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>1308</v>
+      </c>
     </row>
     <row r="658" ht="25" customHeight="1" spans="1:2">
-      <c r="A658" s="2"/>
-      <c r="B658" s="2"/>
+      <c r="A658" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>1310</v>
+      </c>
     </row>
     <row r="659" ht="25" customHeight="1" spans="1:2">
-      <c r="A659" s="2"/>
-      <c r="B659" s="2"/>
+      <c r="A659" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="660" ht="25" customHeight="1" spans="1:2">
-      <c r="A660" s="2"/>
-      <c r="B660" s="2"/>
+      <c r="A660" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>1314</v>
+      </c>
     </row>
     <row r="661" ht="25" customHeight="1" spans="1:2">
-      <c r="A661" s="2"/>
-      <c r="B661" s="2"/>
+      <c r="A661" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>1316</v>
+      </c>
     </row>
     <row r="662" ht="25" customHeight="1" spans="1:2">
-      <c r="A662" s="2"/>
-      <c r="B662" s="2"/>
+      <c r="A662" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>1318</v>
+      </c>
     </row>
     <row r="663" ht="25" customHeight="1" spans="1:2">
-      <c r="A663" s="2"/>
-      <c r="B663" s="2"/>
+      <c r="A663" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1320</v>
+      </c>
     </row>
     <row r="664" ht="25" customHeight="1" spans="1:2">
-      <c r="A664" s="2"/>
-      <c r="B664" s="2"/>
+      <c r="A664" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1322</v>
+      </c>
     </row>
     <row r="665" ht="25" customHeight="1" spans="1:2">
-      <c r="A665" s="2"/>
-      <c r="B665" s="2"/>
+      <c r="A665" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>1324</v>
+      </c>
     </row>
     <row r="666" ht="25" customHeight="1" spans="1:2">
-      <c r="A666" s="2"/>
-      <c r="B666" s="2"/>
+      <c r="A666" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>1326</v>
+      </c>
     </row>
     <row r="667" ht="25" customHeight="1" spans="1:2">
-      <c r="A667" s="2"/>
-      <c r="B667" s="2"/>
+      <c r="A667" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>1328</v>
+      </c>
     </row>
     <row r="668" ht="25" customHeight="1" spans="1:2">
-      <c r="A668" s="2"/>
-      <c r="B668" s="2"/>
+      <c r="A668" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>1330</v>
+      </c>
     </row>
     <row r="669" ht="25" customHeight="1" spans="1:2">
-      <c r="A669" s="2"/>
-      <c r="B669" s="2"/>
+      <c r="A669" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>1332</v>
+      </c>
     </row>
     <row r="670" ht="25" customHeight="1" spans="1:2">
-      <c r="A670" s="2"/>
-      <c r="B670" s="2"/>
+      <c r="A670" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>1334</v>
+      </c>
     </row>
     <row r="671" ht="25" customHeight="1" spans="1:2">
-      <c r="A671" s="2"/>
-      <c r="B671" s="2"/>
+      <c r="A671" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="672" ht="25" customHeight="1" spans="1:2">
-      <c r="A672" s="2"/>
-      <c r="B672" s="2"/>
+      <c r="A672" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>1338</v>
+      </c>
     </row>
     <row r="673" ht="25" customHeight="1" spans="1:2">
-      <c r="A673" s="2"/>
-      <c r="B673" s="2"/>
+      <c r="A673" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>1340</v>
+      </c>
     </row>
     <row r="674" ht="25" customHeight="1" spans="1:2">
-      <c r="A674" s="2"/>
-      <c r="B674" s="2"/>
+      <c r="A674" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>1342</v>
+      </c>
     </row>
     <row r="675" ht="25" customHeight="1" spans="1:2">
-      <c r="A675" s="2"/>
-      <c r="B675" s="2"/>
+      <c r="A675" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>1344</v>
+      </c>
     </row>
     <row r="676" ht="25" customHeight="1" spans="1:2">
-      <c r="A676" s="2"/>
-      <c r="B676" s="2"/>
+      <c r="A676" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>1346</v>
+      </c>
     </row>
     <row r="677" ht="25" customHeight="1" spans="1:2">
-      <c r="A677" s="2"/>
-      <c r="B677" s="2"/>
+      <c r="A677" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="678" ht="25" customHeight="1" spans="1:2">
-      <c r="A678" s="2"/>
-      <c r="B678" s="2"/>
+      <c r="A678" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>1350</v>
+      </c>
     </row>
     <row r="679" ht="25" customHeight="1" spans="1:2">
-      <c r="A679" s="2"/>
-      <c r="B679" s="2"/>
+      <c r="A679" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>1352</v>
+      </c>
     </row>
     <row r="680" ht="25" customHeight="1" spans="1:2">
-      <c r="A680" s="2"/>
-      <c r="B680" s="2"/>
+      <c r="A680" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>1354</v>
+      </c>
     </row>
     <row r="681" ht="25" customHeight="1" spans="1:2">
-      <c r="A681" s="2"/>
-      <c r="B681" s="2"/>
+      <c r="A681" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>1356</v>
+      </c>
     </row>
     <row r="682" ht="25" customHeight="1" spans="1:2">
-      <c r="A682" s="2"/>
-      <c r="B682" s="2"/>
+      <c r="A682" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>1358</v>
+      </c>
     </row>
     <row r="683" ht="25" customHeight="1" spans="1:2">
-      <c r="A683" s="2"/>
-      <c r="B683" s="2"/>
+      <c r="A683" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>1360</v>
+      </c>
     </row>
     <row r="684" ht="25" customHeight="1" spans="1:2">
-      <c r="A684" s="2"/>
-      <c r="B684" s="2"/>
+      <c r="A684" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>1362</v>
+      </c>
     </row>
     <row r="685" ht="25" customHeight="1" spans="1:2">
-      <c r="A685" s="2"/>
-      <c r="B685" s="2"/>
+      <c r="A685" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1364</v>
+      </c>
     </row>
     <row r="686" ht="25" customHeight="1" spans="1:2">
-      <c r="A686" s="2"/>
-      <c r="B686" s="2"/>
+      <c r="A686" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>1366</v>
+      </c>
     </row>
     <row r="687" ht="25" customHeight="1" spans="1:2">
-      <c r="A687" s="2"/>
-      <c r="B687" s="2"/>
+      <c r="A687" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>1368</v>
+      </c>
     </row>
     <row r="688" ht="25" customHeight="1" spans="1:2">
-      <c r="A688" s="2"/>
-      <c r="B688" s="2"/>
+      <c r="A688" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>1370</v>
+      </c>
     </row>
     <row r="689" ht="25" customHeight="1" spans="1:2">
-      <c r="A689" s="2"/>
-      <c r="B689" s="2"/>
+      <c r="A689" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1372</v>
+      </c>
     </row>
     <row r="690" ht="25" customHeight="1" spans="1:2">
-      <c r="A690" s="2"/>
-      <c r="B690" s="2"/>
+      <c r="A690" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>1374</v>
+      </c>
     </row>
     <row r="691" ht="25" customHeight="1" spans="1:2">
-      <c r="A691" s="2"/>
-      <c r="B691" s="2"/>
+      <c r="A691" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>1376</v>
+      </c>
     </row>
     <row r="692" ht="25" customHeight="1" spans="1:2">
-      <c r="A692" s="2"/>
-      <c r="B692" s="2"/>
+      <c r="A692" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>1378</v>
+      </c>
     </row>
     <row r="693" ht="25" customHeight="1" spans="1:2">
-      <c r="A693" s="2"/>
-      <c r="B693" s="2"/>
+      <c r="A693" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>1380</v>
+      </c>
     </row>
     <row r="694" ht="25" customHeight="1" spans="1:2">
-      <c r="A694" s="2"/>
-      <c r="B694" s="2"/>
+      <c r="A694" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>1382</v>
+      </c>
     </row>
     <row r="695" ht="25" customHeight="1" spans="1:2">
-      <c r="A695" s="2"/>
-      <c r="B695" s="2"/>
+      <c r="A695" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1384</v>
+      </c>
     </row>
     <row r="696" ht="25" customHeight="1" spans="1:2">
-      <c r="A696" s="2"/>
-      <c r="B696" s="2"/>
+      <c r="A696" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1386</v>
+      </c>
     </row>
     <row r="697" ht="25" customHeight="1" spans="1:2">
-      <c r="A697" s="2"/>
-      <c r="B697" s="2"/>
+      <c r="A697" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>1388</v>
+      </c>
     </row>
     <row r="698" ht="25" customHeight="1" spans="1:2">
-      <c r="A698" s="2"/>
-      <c r="B698" s="2"/>
+      <c r="A698" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1390</v>
+      </c>
     </row>
     <row r="699" ht="25" customHeight="1" spans="1:2">
-      <c r="A699" s="2"/>
-      <c r="B699" s="2"/>
+      <c r="A699" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>1392</v>
+      </c>
     </row>
     <row r="700" ht="25" customHeight="1" spans="1:2">
-      <c r="A700" s="2"/>
-      <c r="B700" s="2"/>
+      <c r="A700" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>1394</v>
+      </c>
     </row>
     <row r="701" ht="25" customHeight="1" spans="1:2">
-      <c r="A701" s="2"/>
-      <c r="B701" s="2"/>
+      <c r="A701" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>1396</v>
+      </c>
     </row>
     <row r="702" ht="25" customHeight="1" spans="1:2">
       <c r="A702" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1437">
   <si>
     <t>bangla</t>
   </si>
@@ -4296,6 +4296,146 @@
   </si>
   <si>
     <t>আঁর উজ্ঞো হালা আছিল, যিবে মুরি দি চা হাইতু</t>
+  </si>
+  <si>
+    <t>ছেলেমেয়ের জন্য মা ছায়ার মতো</t>
+  </si>
+  <si>
+    <t>ফুত জি'র লাই মা ছায়ার মতন</t>
+  </si>
+  <si>
+    <t>মা না থাকলে বোঝা যায় মায়ের গুরুত্ব কত</t>
+  </si>
+  <si>
+    <t>মা ন থাহিলি বুঝা যায় মা'র গুরুত্ব হতো</t>
+  </si>
+  <si>
+    <t>বাসা খুঁজতে খুঁজতে ক্লান্ত হয়ে গেছি, তাও একটা ভালো বাসা পাইনি</t>
+  </si>
+  <si>
+    <t>বাসা তোওয়াইতে তোওয়াইতে অরান অই গেই, তাও এক্কান গম বাসা ন পাই</t>
+  </si>
+  <si>
+    <t>মায়ের সাথে থাকলে অনেক ঝগড়া হয়, কিন্তু মায়ের থেকে দূরে থাকলে তখন মায়ের কথা মনে পড়ে</t>
+  </si>
+  <si>
+    <t>মা'র লগে থাহিলি বত হইজ্জে অই, কিন্তু মা'ত্তুন দুরে থাহিলি তহন মা'র হতা মনুত ফরে</t>
+  </si>
+  <si>
+    <t>আত্মীয়ের মধ্যে আত্মীয়তা করা ঠিক না</t>
+  </si>
+  <si>
+    <t>আত্মীয়ের মধ্যে আত্মীয়তা গরন ভালা ন</t>
+  </si>
+  <si>
+    <t>কি রান্না করেন দেখতে আসছি</t>
+  </si>
+  <si>
+    <t>কি রান্না গরন চাইতাম আইসসি</t>
+  </si>
+  <si>
+    <t>তুমি এখন ভাত খেও না, আমি একটু পর আলু ভর্তা করে দিচ্ছি</t>
+  </si>
+  <si>
+    <t>তুঁই এহন ভাত ন হাইয়্যু, আঁই এক্কানা ফর আলু ভত্তা গরি দির</t>
+  </si>
+  <si>
+    <t>আজকে অনেকদিন পর ঘরের সবাই একসাথে হলাম</t>
+  </si>
+  <si>
+    <t>আজিয়ে বতদিন ফর ঘরোর বিয়াক একলগে আইলাম</t>
+  </si>
+  <si>
+    <t>ছোট বাচ্চাটা আমার গায়ের ওপর প্রস্রাব করে দিয়েছে</t>
+  </si>
+  <si>
+    <t>গুরো ফোয়া ইবে আঁর গার উদ্দি মুতি দিয়্যি</t>
+  </si>
+  <si>
+    <r>
+      <t>ছোটবেলায় আমাদের পায়খানা</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>প্রস্রাব আম্মু পরিষ্কার করতেন</t>
+    </r>
+  </si>
+  <si>
+    <t>গুরো থাকতে আঁরার গু-মুত আম্মু সাফ গইত্তো</t>
+  </si>
+  <si>
+    <t>ভাইয়া, তোমাকে আম্মু ডাকছে</t>
+  </si>
+  <si>
+    <t>ভাইয়ে, তোঁয়ারে আম্মু ডাহের</t>
+  </si>
+  <si>
+    <t>হুট করেই রুমে ঢুকে পড়িস কেন? দরজা নক করতে পারিস না?</t>
+  </si>
+  <si>
+    <t>বুঢ়ুর গরি রুমুত কা ঢুকি পরস? দরজা নক গরিত ন পারস?</t>
+  </si>
+  <si>
+    <t>তোর জন্য কিছু আনিনি, এখন এখান থেকে যা</t>
+  </si>
+  <si>
+    <t>তুর লাই কিছু নো আনি, এহন এত্তুন যা</t>
+  </si>
+  <si>
+    <t>ভুল কি আমি একা করেছি?</t>
+  </si>
+  <si>
+    <t>ভুল কি আঁই এহেল্লে গইজ্জি?</t>
+  </si>
+  <si>
+    <t>আমি তো আর ইচ্ছা করে সেটা এখানে আনিনি</t>
+  </si>
+  <si>
+    <t>আঁই তো আর ইচ্ছে গরি ইয়েন এনডে ন আনি</t>
+  </si>
+  <si>
+    <t>তুই যা শুরু করলি শাকিল, একদিন তো আমার মান সম্মান খেয়ে ফেলবি</t>
+  </si>
+  <si>
+    <t>তুই যা শুরু গইজ্জুস শাকিল, একদিন তো আঁর মান সম্মান হাই ফেলাইবি</t>
+  </si>
+  <si>
+    <t>আমার কাছে টাকা পয়সার থেকে মান সম্মান বেশি গুরুত্বপূর্ণ</t>
+  </si>
+  <si>
+    <t>আঁর হাছে টিয়া ফুইশেত্তুন মান সম্মান বেশি গুরুত্বপুর্ণ</t>
+  </si>
+  <si>
+    <t>তোর শাশুড়ি তো ফোন ধরে না</t>
+  </si>
+  <si>
+    <t>তুর অরি তো ফোন ন ধরে</t>
+  </si>
+  <si>
+    <t>আমাকে একটু মাংসের ঝোল দাও</t>
+  </si>
+  <si>
+    <t>আঁরে এক্কানা গুস্তর সুরগো দও</t>
+  </si>
+  <si>
+    <t>অসুখ নিয়ে বসে থাকা ভালো না</t>
+  </si>
+  <si>
+    <t>অসুখ লই বই থাহন ভালা ন</t>
   </si>
 </sst>
 </file>
@@ -11081,84 +11221,164 @@
       </c>
     </row>
     <row r="702" ht="25" customHeight="1" spans="1:2">
-      <c r="A702" s="2"/>
-      <c r="B702" s="2"/>
+      <c r="A702" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>1398</v>
+      </c>
     </row>
     <row r="703" ht="25" customHeight="1" spans="1:2">
-      <c r="A703" s="2"/>
-      <c r="B703" s="2"/>
+      <c r="A703" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>1400</v>
+      </c>
     </row>
     <row r="704" ht="25" customHeight="1" spans="1:2">
-      <c r="A704" s="2"/>
-      <c r="B704" s="2"/>
+      <c r="A704" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1402</v>
+      </c>
     </row>
     <row r="705" ht="25" customHeight="1" spans="1:2">
-      <c r="A705" s="2"/>
-      <c r="B705" s="2"/>
+      <c r="A705" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>1404</v>
+      </c>
     </row>
     <row r="706" ht="25" customHeight="1" spans="1:2">
-      <c r="A706" s="2"/>
-      <c r="B706" s="2"/>
+      <c r="A706" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="707" ht="25" customHeight="1" spans="1:2">
-      <c r="A707" s="2"/>
-      <c r="B707" s="2"/>
+      <c r="A707" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>1408</v>
+      </c>
     </row>
     <row r="708" ht="25" customHeight="1" spans="1:2">
-      <c r="A708" s="2"/>
-      <c r="B708" s="2"/>
+      <c r="A708" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1410</v>
+      </c>
     </row>
     <row r="709" ht="25" customHeight="1" spans="1:2">
-      <c r="A709" s="2"/>
-      <c r="B709" s="2"/>
+      <c r="A709" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1412</v>
+      </c>
     </row>
     <row r="710" ht="25" customHeight="1" spans="1:2">
-      <c r="A710" s="2"/>
-      <c r="B710" s="2"/>
+      <c r="A710" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>1414</v>
+      </c>
     </row>
     <row r="711" ht="25" customHeight="1" spans="1:2">
-      <c r="A711" s="2"/>
-      <c r="B711" s="2"/>
+      <c r="A711" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>1416</v>
+      </c>
     </row>
     <row r="712" ht="25" customHeight="1" spans="1:2">
-      <c r="A712" s="2"/>
-      <c r="B712" s="2"/>
+      <c r="A712" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>1418</v>
+      </c>
     </row>
     <row r="713" ht="25" customHeight="1" spans="1:2">
-      <c r="A713" s="2"/>
-      <c r="B713" s="2"/>
+      <c r="A713" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>1420</v>
+      </c>
     </row>
     <row r="714" ht="25" customHeight="1" spans="1:2">
-      <c r="A714" s="2"/>
-      <c r="B714" s="2"/>
+      <c r="A714" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="715" ht="25" customHeight="1" spans="1:2">
-      <c r="A715" s="2"/>
-      <c r="B715" s="2"/>
+      <c r="A715" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="716" ht="25" customHeight="1" spans="1:2">
-      <c r="A716" s="2"/>
-      <c r="B716" s="2"/>
+      <c r="A716" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>1426</v>
+      </c>
     </row>
     <row r="717" ht="25" customHeight="1" spans="1:2">
-      <c r="A717" s="2"/>
-      <c r="B717" s="2"/>
+      <c r="A717" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="718" ht="25" customHeight="1" spans="1:2">
-      <c r="A718" s="2"/>
-      <c r="B718" s="2"/>
+      <c r="A718" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>1430</v>
+      </c>
     </row>
     <row r="719" ht="25" customHeight="1" spans="1:2">
-      <c r="A719" s="2"/>
-      <c r="B719" s="2"/>
+      <c r="A719" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>1432</v>
+      </c>
     </row>
     <row r="720" ht="25" customHeight="1" spans="1:2">
-      <c r="A720" s="2"/>
-      <c r="B720" s="2"/>
+      <c r="A720" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>1434</v>
+      </c>
     </row>
     <row r="721" ht="25" customHeight="1" spans="1:2">
-      <c r="A721" s="2"/>
-      <c r="B721" s="2"/>
+      <c r="A721" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>1436</v>
+      </c>
     </row>
     <row r="722" ht="25" customHeight="1" spans="1:2">
       <c r="A722" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1517">
   <si>
     <t>bangla</t>
   </si>
@@ -1791,7 +1791,7 @@
     <t>জলদি আই, দেরি হলে মা গালি দিবে</t>
   </si>
   <si>
-    <t>হারা আই, দেরি অইলি আম্মু গাইল দিবো</t>
+    <t>হারা আই, দেরি অইলি আম্মু গেইল দিবো</t>
   </si>
   <si>
     <t>অনেকগুলো কাপড় জমে আছে</t>
@@ -2277,7 +2277,7 @@
     <t>সারাদিন এত কাজ করি তাও কাজ গুলো শেষ হচ্ছে না</t>
   </si>
   <si>
-    <t>পুরোদিন এত হাজ গরি ত হাজ এগিন শেষ ন অর</t>
+    <t>আরাদিন এত হাজ গরি ত হাজ এগিন শেষ ন অর</t>
   </si>
   <si>
     <t>আমাকে কিছু কাজ করে দাও, আমি টাকা দিব তোমাকে</t>
@@ -2883,7 +2883,7 @@
     <t>আমার কালো শার্টটি কোথায়? খুঁজে পাচ্ছি না যে</t>
   </si>
   <si>
-    <t>আঁর হালা শার্ট ইবে হনডে? থোয়াই ন পাইদ্দি</t>
+    <t>আঁর হালা শার্ট ইবে হনডে? থোওয়াই ন পাইদ্দি</t>
   </si>
   <si>
     <t>আমার হাত পা ব্যথা করছে</t>
@@ -2925,7 +2925,7 @@
     <t>সারাদিন কম্পিউটারে বসে বসে কী করো?</t>
   </si>
   <si>
-    <t>পুরোদিন কম্পিউটারোত বই বই কি গরো?</t>
+    <t>আরাদিন কম্পিউটারোত বই বই কি গরো?</t>
   </si>
   <si>
     <t>বাসে বসে অনেকক্ষণ অপেক্ষা করতে হয়েছে</t>
@@ -4353,6 +4353,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
       <t>ছোটবেলায় আমাদের পায়খানা</t>
     </r>
     <r>
@@ -4436,6 +4442,246 @@
   </si>
   <si>
     <t>অসুখ লই বই থাহন ভালা ন</t>
+  </si>
+  <si>
+    <t>আপনার মেয়েকে আমার অনেক ভাল লেগেছে</t>
+  </si>
+  <si>
+    <t>অঁনোর মাইফোয়ারে আত্তুন বত ভালা লেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>এরা দুই ভাই অনেক দুষ্টু</t>
+  </si>
+  <si>
+    <t>ইতারা দুনু ভাই বত জারগো</t>
+  </si>
+  <si>
+    <t>সে তোমার আংকেলের সাথে ঝগড়া করতে চাচ্ছে</t>
+  </si>
+  <si>
+    <t>ইতে তোঁয়ার আংকেলুর লগে হইজ্জে গইত্তো চার</t>
+  </si>
+  <si>
+    <t>ওরা দুজন মিলে আমার পিছে লাগছে</t>
+  </si>
+  <si>
+    <t>ইতারা দুনু জন মিলি আঁর পিছুদ্দি লেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>কিছু খেয়ে একটু ঘুমা, বাইরে কোথাও যাস না</t>
+  </si>
+  <si>
+    <t>কিছু হাই রে এক্কানা ঘুম যা, বাদ্দি হনোমিক্কে ন যাইস</t>
+  </si>
+  <si>
+    <t>এখন দিনকাল ভালো না, বাইরে বের হবি না</t>
+  </si>
+  <si>
+    <t>এহন দিনহাল ভালা ন, বাদ্দি বাইর ন অইস</t>
+  </si>
+  <si>
+    <t>আমাদের বাড়ির পাশে একটা পাহাড় আছে</t>
+  </si>
+  <si>
+    <t>আঁরো বারির পাশে উজ্ঞো পা'র আছে</t>
+  </si>
+  <si>
+    <t>এই কাপড়গুলো ধুতে হবে না, এগুলো আজকে পরব</t>
+  </si>
+  <si>
+    <t>হর এগুন ধুঅন ফইত্তো ন, এগুন আজিয়ে ফইজ্জুম</t>
+  </si>
+  <si>
+    <t>কতগুলো নতুন কাপড় নিতে হবে</t>
+  </si>
+  <si>
+    <t>হদোজ্ঞুন নতুন হর লন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমার সব কাপড় পুরাতন হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আঁর বিয়াক হর ফুরন অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আসার সময় মনে করে কাঁচা মরিচ আর টমেটো নিয়ে আসিও</t>
+  </si>
+  <si>
+    <t>আইবের সমত মনোত গরি কেঁচা মরিচ আর হাট্টা বেইয়্যুন লই আইসসু</t>
+  </si>
+  <si>
+    <t>আমি মনে করেছিলাম আজকে গাড়ি চলবে না</t>
+  </si>
+  <si>
+    <t>আঁই মনে গইজ্জিলাম আজিয়ে গারি ন চলিবু</t>
+  </si>
+  <si>
+    <t>আগামীকাল থেকে হরতাল, সেজন্য গাড়ি চলবে না</t>
+  </si>
+  <si>
+    <t>হালিয়েত্তুন অরতাল, এতেল্লে গারি ন চলিবু</t>
+  </si>
+  <si>
+    <t>আমার ছোট চাচাটা বেশি শয়তান, সবসময় আব্বুর সাথে ঝগড়া করে</t>
+  </si>
+  <si>
+    <t>আঁর গুরো চাচা ইবে বেশি শতান, সবসময় আব্বুর লগে হইজ্জে গরে</t>
+  </si>
+  <si>
+    <t>আমার তাড়াতাড়ি কিছু একটা করতে হবে</t>
+  </si>
+  <si>
+    <t>আত্তুন তারাতারি কিছু এক্কান গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমার পরিবার আমার দিকে তাকিয়ে আছে</t>
+  </si>
+  <si>
+    <t>আঁর পরিবার আঁর মিক্কে চাই থেইক্কি</t>
+  </si>
+  <si>
+    <t>বন্ধু, যদি পারিস তাহলে আমাকে একটা চাকরি খুঁজে দে</t>
+  </si>
+  <si>
+    <t>বন্ধু, যরি পারুস তইলি আঁরে এক্কান ছরি থোওয়াই দে</t>
+  </si>
+  <si>
+    <t>আমি যদি চাকরি না করি, তাহলে আমার পরিবার কষ্ট পাবে</t>
+  </si>
+  <si>
+    <t>আঁই যদি ছরি ন গরি, তইলি আঁর পরিবার হষ্ট ফাইবু</t>
+  </si>
+  <si>
+    <t>জমিদার আংকেল বলছে ব্যাচেলর ভাড়া দেবে না</t>
+  </si>
+  <si>
+    <t>জমিদার আংকেল হইয়্যি ব্যাচেলার ভারা দিতু ন</t>
+  </si>
+  <si>
+    <t>এভাবে আস্তে আস্তে কাজ করলে সারাদিন চলে যাবে</t>
+  </si>
+  <si>
+    <t>এন গরি আস্তে আস্তে হাম গরিলি পুরোদিন চলি যাইবু</t>
+  </si>
+  <si>
+    <t>কাপড়গুলো আমি এসে ধুব</t>
+  </si>
+  <si>
+    <t>হর এগিন আঁই আইরে ধুইয়্যুম</t>
+  </si>
+  <si>
+    <t>ওর সাহস কত! আমার নাম ধরে ডাকে</t>
+  </si>
+  <si>
+    <t>ইতের সাহস হতো! আঁর নাম ধরি ডাহে</t>
+  </si>
+  <si>
+    <t>এভাবে কাজ করলে শেষ হবে না</t>
+  </si>
+  <si>
+    <t>এন গরি হাম গরিলি শেষ ন অইবু</t>
+  </si>
+  <si>
+    <t>আমাদের অন্যভাবে কাজ করতে হবে</t>
+  </si>
+  <si>
+    <t>আরাত্তুন অন্যভাবে হাম গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>তুই আব্বুর পকেট থেকে টাকা নিয়েছিস যে আমি আব্বুকে বলে দেব</t>
+  </si>
+  <si>
+    <t>তুই আব্বুর পকেটুত্তুন টিয়া লইয়্যুস যে আঁই আব্বুরে হই দিয়্যুম</t>
+  </si>
+  <si>
+    <t>এরা দুই ভাই একসাথে হলেই ঝগড়া শুরু হয়ে যায়</t>
+  </si>
+  <si>
+    <t>এতারা দুনু ভাই একলগে অইলিই হইজ্জে শুরু অই যাই</t>
+  </si>
+  <si>
+    <t>ভাই-বোন মিলে মিশে থাকলে বাইরের কেউ ক্ষতি করতে পারবে না</t>
+  </si>
+  <si>
+    <t>ভাই-বইন মিলি মিশি থাহিলি বাইরুর কিয়াই হতি গরিত ন ফারিবু</t>
+  </si>
+  <si>
+    <t>ঘরের সবচেয়ে ছোট ছেলেটা অনেক দুষ্টু হয়</t>
+  </si>
+  <si>
+    <t>ঘরোর বিয়াজ্ঞুনুত্তুন গুরো ফোয়া ইবে বত জারগো অই</t>
+  </si>
+  <si>
+    <t>ঘর ওটাতে থাকার মতো অবস্থা নেই, চারদিকে অনেক ময়লা</t>
+  </si>
+  <si>
+    <t>ঘর ইয়েনুত থাহিবের মতোন অবস্থা নেই, চেরিমিক্কে বত হাচারা</t>
+  </si>
+  <si>
+    <t>আসার সময় ঘরে তালা মেরে আসিস, না হলে চোর এসে চুরি করে সব নিয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আইবের সমত ঘরোত তালা মারি আইস, নইলি চোর আই রে বিয়াক চুরি গরি লই যাইবু</t>
+  </si>
+  <si>
+    <t>কিছুদিন কাপড় ধুতে হয়নি, তাই গায়ের ব্যথা একটু কমেছে</t>
+  </si>
+  <si>
+    <t>কিছুদিন হর ধুঅন ন পরে, এতেল্লে গা'র ব্যথা এক্কানা হইম্মি</t>
+  </si>
+  <si>
+    <t>বাজারে যাওয়ার সময় ৫০০ টাকা হারিয়ে ফেলেছি</t>
+  </si>
+  <si>
+    <t>বাজারোত যাইবের সমত ৫০০ টিয়া আঝায় ফেলাই</t>
+  </si>
+  <si>
+    <t>ঘরে চোর ঢুকে সব জিনিস নিয়ে গেছে</t>
+  </si>
+  <si>
+    <t>ঘরোত চোর ঢুকি বিয়াক জিনিস লই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সবকিছুর শুরু যেমন আছে, শেষও তেমনই আছে</t>
+  </si>
+  <si>
+    <t>বিয়াক কিছুর শুরু যেল্লেত আছে, শেষও এল্লেত আছে</t>
+  </si>
+  <si>
+    <t>এটা কীভাবে খায় যে?</t>
+  </si>
+  <si>
+    <t>ইবে কেনে হায় দে?</t>
+  </si>
+  <si>
+    <t>আমিও কিছু বলছি না, আর তুইও যেমন ইচ্ছা তেমন করছিস</t>
+  </si>
+  <si>
+    <t>আঁই ও কিছু ন হইর, আর তুই ও যেল্লেত ইচ্ছে এল্লেত গরর</t>
+  </si>
+  <si>
+    <t>আমাদের পেয়ারা গাছে সবসময় পেয়ারা ধরে</t>
+  </si>
+  <si>
+    <t>আঁরো গুয়াছি গাছোত সবসময় গুয়াছি ধরে</t>
+  </si>
+  <si>
+    <t>আমাদের বাড়ির পিছনে আরেকটা বাড়ি আছে</t>
+  </si>
+  <si>
+    <t>আঁরো বারির পিছুদ্দি আরেক্কান বারি আছে</t>
+  </si>
+  <si>
+    <t>পাশের বাড়ির মেয়েগুলো প্রতিদিন আমাদের পেয়ারা গাছ থেকে পেয়ারা চুরি করে</t>
+  </si>
+  <si>
+    <t>পাশোর বারির মাইফোয়া এগুন আঁরো গুয়াছি গাছুত্তুন গুয়াছি চুরি গরে</t>
+  </si>
+  <si>
+    <t>ওদেরকে একবার আমার বড় আপু অনেক বকা দিয়েছিল</t>
+  </si>
+  <si>
+    <t>ইতারারে একবার আঁর বরো আফা বত গেইল দিয়্যিল</t>
   </si>
 </sst>
 </file>
@@ -11381,164 +11627,324 @@
       </c>
     </row>
     <row r="722" ht="25" customHeight="1" spans="1:2">
-      <c r="A722" s="2"/>
-      <c r="B722" s="2"/>
+      <c r="A722" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>1438</v>
+      </c>
     </row>
     <row r="723" ht="25" customHeight="1" spans="1:2">
-      <c r="A723" s="2"/>
-      <c r="B723" s="2"/>
+      <c r="A723" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>1440</v>
+      </c>
     </row>
     <row r="724" ht="25" customHeight="1" spans="1:2">
-      <c r="A724" s="2"/>
-      <c r="B724" s="2"/>
+      <c r="A724" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1442</v>
+      </c>
     </row>
     <row r="725" ht="25" customHeight="1" spans="1:2">
-      <c r="A725" s="2"/>
-      <c r="B725" s="2"/>
+      <c r="A725" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1444</v>
+      </c>
     </row>
     <row r="726" ht="25" customHeight="1" spans="1:2">
-      <c r="A726" s="2"/>
-      <c r="B726" s="2"/>
+      <c r="A726" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1446</v>
+      </c>
     </row>
     <row r="727" ht="25" customHeight="1" spans="1:2">
-      <c r="A727" s="2"/>
-      <c r="B727" s="2"/>
+      <c r="A727" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1448</v>
+      </c>
     </row>
     <row r="728" ht="25" customHeight="1" spans="1:2">
-      <c r="A728" s="2"/>
-      <c r="B728" s="2"/>
+      <c r="A728" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1450</v>
+      </c>
     </row>
     <row r="729" ht="25" customHeight="1" spans="1:2">
-      <c r="A729" s="2"/>
-      <c r="B729" s="2"/>
+      <c r="A729" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1452</v>
+      </c>
     </row>
     <row r="730" ht="25" customHeight="1" spans="1:2">
-      <c r="A730" s="2"/>
-      <c r="B730" s="2"/>
+      <c r="A730" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="731" ht="25" customHeight="1" spans="1:2">
-      <c r="A731" s="2"/>
-      <c r="B731" s="2"/>
+      <c r="A731" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1456</v>
+      </c>
     </row>
     <row r="732" ht="25" customHeight="1" spans="1:2">
-      <c r="A732" s="2"/>
-      <c r="B732" s="2"/>
+      <c r="A732" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1458</v>
+      </c>
     </row>
     <row r="733" ht="25" customHeight="1" spans="1:2">
-      <c r="A733" s="2"/>
-      <c r="B733" s="2"/>
+      <c r="A733" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1460</v>
+      </c>
     </row>
     <row r="734" ht="25" customHeight="1" spans="1:2">
-      <c r="A734" s="2"/>
-      <c r="B734" s="2"/>
+      <c r="A734" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1462</v>
+      </c>
     </row>
     <row r="735" ht="25" customHeight="1" spans="1:2">
-      <c r="A735" s="2"/>
-      <c r="B735" s="2"/>
+      <c r="A735" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1464</v>
+      </c>
     </row>
     <row r="736" ht="25" customHeight="1" spans="1:2">
-      <c r="A736" s="2"/>
-      <c r="B736" s="2"/>
+      <c r="A736" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>1466</v>
+      </c>
     </row>
     <row r="737" ht="25" customHeight="1" spans="1:2">
-      <c r="A737" s="2"/>
-      <c r="B737" s="2"/>
+      <c r="A737" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>1468</v>
+      </c>
     </row>
     <row r="738" ht="25" customHeight="1" spans="1:2">
-      <c r="A738" s="2"/>
-      <c r="B738" s="2"/>
+      <c r="A738" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>1470</v>
+      </c>
     </row>
     <row r="739" ht="25" customHeight="1" spans="1:2">
-      <c r="A739" s="2"/>
-      <c r="B739" s="2"/>
+      <c r="A739" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>1472</v>
+      </c>
     </row>
     <row r="740" ht="25" customHeight="1" spans="1:2">
-      <c r="A740" s="2"/>
-      <c r="B740" s="2"/>
+      <c r="A740" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="741" ht="25" customHeight="1" spans="1:2">
-      <c r="A741" s="2"/>
-      <c r="B741" s="2"/>
+      <c r="A741" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1476</v>
+      </c>
     </row>
     <row r="742" ht="25" customHeight="1" spans="1:2">
-      <c r="A742" s="2"/>
-      <c r="B742" s="2"/>
+      <c r="A742" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>1478</v>
+      </c>
     </row>
     <row r="743" ht="25" customHeight="1" spans="1:2">
-      <c r="A743" s="2"/>
-      <c r="B743" s="2"/>
+      <c r="A743" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>1480</v>
+      </c>
     </row>
     <row r="744" ht="25" customHeight="1" spans="1:2">
-      <c r="A744" s="2"/>
-      <c r="B744" s="2"/>
+      <c r="A744" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>1482</v>
+      </c>
     </row>
     <row r="745" ht="25" customHeight="1" spans="1:2">
-      <c r="A745" s="2"/>
-      <c r="B745" s="2"/>
+      <c r="A745" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1484</v>
+      </c>
     </row>
     <row r="746" ht="25" customHeight="1" spans="1:2">
-      <c r="A746" s="2"/>
-      <c r="B746" s="2"/>
+      <c r="A746" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1486</v>
+      </c>
     </row>
     <row r="747" ht="25" customHeight="1" spans="1:2">
-      <c r="A747" s="2"/>
-      <c r="B747" s="2"/>
+      <c r="A747" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1488</v>
+      </c>
     </row>
     <row r="748" ht="25" customHeight="1" spans="1:2">
-      <c r="A748" s="2"/>
-      <c r="B748" s="2"/>
+      <c r="A748" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>1490</v>
+      </c>
     </row>
     <row r="749" ht="25" customHeight="1" spans="1:2">
-      <c r="A749" s="2"/>
-      <c r="B749" s="2"/>
+      <c r="A749" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>1492</v>
+      </c>
     </row>
     <row r="750" ht="25" customHeight="1" spans="1:2">
-      <c r="A750" s="2"/>
-      <c r="B750" s="2"/>
+      <c r="A750" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>1494</v>
+      </c>
     </row>
     <row r="751" ht="25" customHeight="1" spans="1:2">
-      <c r="A751" s="2"/>
-      <c r="B751" s="2"/>
+      <c r="A751" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>1496</v>
+      </c>
     </row>
     <row r="752" ht="25" customHeight="1" spans="1:2">
-      <c r="A752" s="2"/>
-      <c r="B752" s="2"/>
+      <c r="A752" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>1498</v>
+      </c>
     </row>
     <row r="753" ht="25" customHeight="1" spans="1:2">
-      <c r="A753" s="2"/>
-      <c r="B753" s="2"/>
+      <c r="A753" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>1500</v>
+      </c>
     </row>
     <row r="754" ht="25" customHeight="1" spans="1:2">
-      <c r="A754" s="2"/>
-      <c r="B754" s="2"/>
+      <c r="A754" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>1502</v>
+      </c>
     </row>
     <row r="755" ht="25" customHeight="1" spans="1:2">
-      <c r="A755" s="2"/>
-      <c r="B755" s="2"/>
+      <c r="A755" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>1504</v>
+      </c>
     </row>
     <row r="756" ht="25" customHeight="1" spans="1:2">
-      <c r="A756" s="2"/>
-      <c r="B756" s="2"/>
+      <c r="A756" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>1506</v>
+      </c>
     </row>
     <row r="757" ht="25" customHeight="1" spans="1:2">
-      <c r="A757" s="2"/>
-      <c r="B757" s="2"/>
+      <c r="A757" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>1508</v>
+      </c>
     </row>
     <row r="758" ht="25" customHeight="1" spans="1:2">
-      <c r="A758" s="2"/>
-      <c r="B758" s="2"/>
+      <c r="A758" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1510</v>
+      </c>
     </row>
     <row r="759" ht="25" customHeight="1" spans="1:2">
-      <c r="A759" s="2"/>
-      <c r="B759" s="2"/>
+      <c r="A759" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>1512</v>
+      </c>
     </row>
     <row r="760" ht="25" customHeight="1" spans="1:2">
-      <c r="A760" s="2"/>
-      <c r="B760" s="2"/>
+      <c r="A760" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>1514</v>
+      </c>
     </row>
     <row r="761" ht="25" customHeight="1" spans="1:2">
-      <c r="A761" s="2"/>
-      <c r="B761" s="2"/>
+      <c r="A761" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>1516</v>
+      </c>
     </row>
     <row r="762" ht="25" customHeight="1" spans="1:2">
       <c r="A762" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="1587">
   <si>
     <t>bangla</t>
   </si>
@@ -1929,7 +1929,7 @@
     <t>আমার রান্না এখনো শেষ হয় নায়, আরেকটু অপেক্ষা কর</t>
   </si>
   <si>
-    <t>আঁর রান্না এহনো শেষ ন অই, আরেক্কানা অপেক্ষা গরো</t>
+    <t>আঁর রান্না এহনো শেষ ন অয়, আরেক্কানা অপেক্ষা গরো</t>
   </si>
   <si>
     <t>তোমাকে কতক্ষণ ধরে কল দিচ্ছি, ফোন উঠাচ্ছো না কেন?</t>
@@ -2403,7 +2403,7 @@
     <t>অনেক আশা নিয়ে গেছিলাম কিন্তু কাজটা হলো না</t>
   </si>
   <si>
-    <t>বত আশা লই রে গেইলাম কিন্তু হাজগান ন অই</t>
+    <t>বত আশা লই রে গেইলাম কিন্তু হাজগান ন অয়</t>
   </si>
   <si>
     <t>আমার মাথা এখন গরম, তোমার সাথে পরে কথা বলব</t>
@@ -2469,7 +2469,7 @@
     <t>তুই পাগল হয়েছিস যে ঘরে যানে?</t>
   </si>
   <si>
-    <t>তুই ফ অল অইয়্যুস যে ঘরোত যানে?</t>
+    <t>তুই ফঅল অইয়্যুস যে ঘরোত যানে?</t>
   </si>
   <si>
     <t>খাবার তো সব ঠান্ডা হয়ে যাচ্ছে</t>
@@ -4483,7 +4483,7 @@
     <t>আমাদের বাড়ির পাশে একটা পাহাড় আছে</t>
   </si>
   <si>
-    <t>আঁরো বারির পাশে উজ্ঞো পা'র আছে</t>
+    <t>আঁরো বারির পাশে উজ্ঞো ফা'র আছে</t>
   </si>
   <si>
     <t>এই কাপড়গুলো ধুতে হবে না, এগুলো আজকে পরব</t>
@@ -4663,7 +4663,7 @@
     <t>আমাদের পেয়ারা গাছে সবসময় পেয়ারা ধরে</t>
   </si>
   <si>
-    <t>আঁরো গুয়াছি গাছোত সবসময় গুয়াছি ধরে</t>
+    <t>আঁরো গুয়াছি গাছোত সবসময় গুয়াসি ধরে</t>
   </si>
   <si>
     <t>আমাদের বাড়ির পিছনে আরেকটা বাড়ি আছে</t>
@@ -4675,13 +4675,223 @@
     <t>পাশের বাড়ির মেয়েগুলো প্রতিদিন আমাদের পেয়ারা গাছ থেকে পেয়ারা চুরি করে</t>
   </si>
   <si>
-    <t>পাশোর বারির মাইফোয়া এগুন আঁরো গুয়াছি গাছুত্তুন গুয়াছি চুরি গরে</t>
+    <t>পাশোর বারির মাইফোয়া এগুন আঁরো গুয়াসি গাছুত্তুন গুয়াছি চুরি গরে</t>
   </si>
   <si>
     <t>ওদেরকে একবার আমার বড় আপু অনেক বকা দিয়েছিল</t>
   </si>
   <si>
     <t>ইতারারে একবার আঁর বরো আফা বত গেইল দিয়্যিল</t>
+  </si>
+  <si>
+    <t>কি হয়েছে? চুপ করে কেন আছো?</t>
+  </si>
+  <si>
+    <t>কি অইয়্যি দে? চুপ গরি কা আছো?</t>
+  </si>
+  <si>
+    <t>তুই আরও অনেক খেলা দেখাবি</t>
+  </si>
+  <si>
+    <t>তুই আরো বত খেলা দেহাবি</t>
+  </si>
+  <si>
+    <t>রমজান মিয়ার কাছে কিছু টাকা পায়</t>
+  </si>
+  <si>
+    <t>রমজান মিয়ত্তুন কিছ টিয়া ফাইর</t>
+  </si>
+  <si>
+    <t>প্রতিদিন সকালে তাড়াতাড়ি উঠে কোরআন তেলাওয়াত করবে</t>
+  </si>
+  <si>
+    <t>ফইত্তোদিন বেইন্নে তারাতারি উডি কোরআন তেলাওয়াত গরিবে</t>
+  </si>
+  <si>
+    <t>সূর্য ওঠার সময় নামাজ পড়া হারাম</t>
+  </si>
+  <si>
+    <t>সূর্য উডিবের সমত নামাজ ফরন হারাম</t>
+  </si>
+  <si>
+    <t>আসার সময় তোর মামাতো বোনকে দেখলাম গাড়িতে করে কোথায় যাচ্ছে</t>
+  </si>
+  <si>
+    <t>আইবের সমত তুর মঅতু বইনুরে দেহিলাম গারিত গরি হনডে যার</t>
+  </si>
+  <si>
+    <t>আমাকে দেখে সালাম দিয়েছে এবং ঘরের সবাই কেমন আছে জিজ্ঞেস করেছে</t>
+  </si>
+  <si>
+    <t>আঁরে দেহি সালাম দিয়ি আর ঘরোর বিয়াজ্ঞুন কেন আছে ফুস গইজ্জি</t>
+  </si>
+  <si>
+    <t>আমি বেড়াতে আসতে বললাম</t>
+  </si>
+  <si>
+    <t>আঁই বেরাইতু আইসতাম হইলাম</t>
+  </si>
+  <si>
+    <t>রান্নাঘরে ডেকচি পড়ার শব্দ হলো, মনে হয় বিড়াল ঢুকেছে</t>
+  </si>
+  <si>
+    <t>বসহানাত ডেকচি পরিবের আওয়াজ অইয়্যি, মনে অই বিলেই ঢুইক্কি</t>
+  </si>
+  <si>
+    <t>এই বিড়ালটা এত দুষ্টু, মাছ ভেজে রেখেছিলাম যে ওখান থেকে চুরি করে খেয়ে ফেলেছে</t>
+  </si>
+  <si>
+    <t>এই বিলেই ইবে এল্লেত জারগো, মাছ ভাজি রাইক্কিলাম দে এত্তুন চুরি গরি হায় ফেলাইয়্যি</t>
+  </si>
+  <si>
+    <t>এই বিড়ালটা একবার আমার আম্মুকে কামড় দিয়েছিল</t>
+  </si>
+  <si>
+    <t>এই বিলেই ইবে একবার আঁর আম্মুরে হঁঅর দিয়্যিল</t>
+  </si>
+  <si>
+    <t>বিড়ালের কামড় খেয়ে আম্মু এক মাস হাসপাতালে ছিল</t>
+  </si>
+  <si>
+    <t>বিলের হঁঅর হায় আম্মু এক মাস হাসপাতালুত আছিল</t>
+  </si>
+  <si>
+    <t>এরা কারা? কোথা থেকে এলো?</t>
+  </si>
+  <si>
+    <t>ইতারা হন? হত্তোন আইসসি?</t>
+  </si>
+  <si>
+    <t>খেজুরের রস দিয়ে ভাপা পিঠা খেতে সেই মজা</t>
+  </si>
+  <si>
+    <t>হাঁজুর রস দি ধু পিডে হাইতু সেই মজা</t>
+  </si>
+  <si>
+    <t>এই কুকুরটার শরীর থেকে অনেক গন্ধ যাচ্ছে</t>
+  </si>
+  <si>
+    <t>এই কুত্তো ইবের গা'আত্তুন বত বাশ যার</t>
+  </si>
+  <si>
+    <t>অনেক বেশি কুয়াশা, কুয়াশার জন্য সূর্য দেখা যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>বত বেশি হুয়া, হুয়ার লাই সূর্য দেহা ন যার</t>
+  </si>
+  <si>
+    <t>ওর মাথা ঠিক নাই, মাথা ঠিক থাকলে এমন কথা বলত?</t>
+  </si>
+  <si>
+    <t>ইতের মাথা ঠিক নেই, মাথা ঠিক থাহিলি এল্লেত হতা হইতু?</t>
+  </si>
+  <si>
+    <t>নিজে কী বলছে সেটার ঠিক নাই, আবার আমাকে বলছে পাগল</t>
+  </si>
+  <si>
+    <t>নিজে কি হর ইয়েনুর ঠিক নেই, আবার আঁরে হর ফঅল</t>
+  </si>
+  <si>
+    <t>ছেলেটা শুধু এদিক সেদিক ঘুরছে</t>
+  </si>
+  <si>
+    <t>ফোয়া ইবে উদো ইক্কেত্তুন উইক্কে ঘুরের</t>
+  </si>
+  <si>
+    <t>আমি ছেলে হতাম তাহলে অনেক কিছু করতে পারতাম</t>
+  </si>
+  <si>
+    <t>আঁই যদি মরতফোয়া অইতাম তইলি বত কিছু গরিত ফাইত্তাম</t>
+  </si>
+  <si>
+    <t>এগুলো ওখান থেকে কীভাবে পড়ে গেল?</t>
+  </si>
+  <si>
+    <t>এগুন অত্তুন কেনে ফরি গেইয়্যি?</t>
+  </si>
+  <si>
+    <t>পিঠা খাবি বলে এখন কোথায় চলে গেছিস?</t>
+  </si>
+  <si>
+    <t>পিডে হাবি হইয়্যিরে এহন হনডে চলি গেইয়্যুস?</t>
+  </si>
+  <si>
+    <t>মা, আমি আজকে যাব না, আগামিকাল আসব</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁই আজিয়ে ন যাইয়্যুম, হালিয়ে আইসসুম</t>
+  </si>
+  <si>
+    <t>আমার জন্য যে পিঠাগুলো বানিয়েছেন, সেগুলো ফ্রিজে রেখে দেন</t>
+  </si>
+  <si>
+    <t>আঁর লাই যে পিডেগিন বানাইয়্যুন, এগিন ফ্রিজুত রাহি দন</t>
+  </si>
+  <si>
+    <t>কাশি বেশি হচ্ছে, একটা কফ সিরাপ খাওয়া দরকার</t>
+  </si>
+  <si>
+    <t>হাশি বেশি অর, উজ্ঞো হফ সিরেপ হন দরহার</t>
+  </si>
+  <si>
+    <t>এটা কি? আজকে প্রথম শুনলাম</t>
+  </si>
+  <si>
+    <t>ইবে কি? আজিয়ে প্রথম উনিলাম</t>
+  </si>
+  <si>
+    <t>এটা কি? আজকে প্রথম দেখলাম</t>
+  </si>
+  <si>
+    <t>ইবে কি? আজিয়ে প্রথম দেহিলাম</t>
+  </si>
+  <si>
+    <t>গরমকাল চলে আসছে, আজকে ফ্যানটা পরিষ্কার করতে হবে</t>
+  </si>
+  <si>
+    <t>গরমহাল চলি আইসসি, আজিয়ে ফ্যান ইবে সাফ গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>মাগরিবের আজান দিচ্ছে, খেলা তাড়াতাড়ি শেষ করে দাও</t>
+  </si>
+  <si>
+    <t>মাগরিবুর আজান দের, খেলা হারা শেষ গরি দে</t>
+  </si>
+  <si>
+    <t>নিজের যদি টাকা থাকত, তাহলে কারো কাছ থেকে খুঁজতে হতো না</t>
+  </si>
+  <si>
+    <t>নিজুত্তুন যদি টিয়া থাইকতু, তইলি কিয়াত্তুন হুজন ন ফইত্তু</t>
+  </si>
+  <si>
+    <t>প্রথম প্রথম একটু ভয় পেয়েছিলাম, এখন আর ভয় লাগে না</t>
+  </si>
+  <si>
+    <t>ফইল্লে ফইল্লে এক্কানা ডরাইলাম, এহন আর ডর ন লাগে</t>
+  </si>
+  <si>
+    <t>কুকুরের পেঠে নাকি ঘি হজম হয় না</t>
+  </si>
+  <si>
+    <t>কুত্তর ফেডুত বলে ঘি অজম ন অয়</t>
+  </si>
+  <si>
+    <t>গতকাল শিয়াল একটা এসে আমার সবচেয়ে বড় মুরগিটা ধরে নিয়ে গেছে</t>
+  </si>
+  <si>
+    <t>গত হালিয়ে ইয়েল উজ্ঞো আইয়্যিরে আঁর বিয়াজ্ঞুনুত্তন বরো কুরো ইবে ধরি লই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>পাহাড় থেকে প্রতিদিন রাতে শিয়াল আসে</t>
+  </si>
+  <si>
+    <t>ফা'রুত্তুন ফইত্তোদিন রাতিয়ে ইয়েল আইয়্যি</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে পাহাড় থেকে হাতি আসে, একবার একটা হাতি একজন মানুষকে মেরে ফেলেছিল</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে ফা'রুত্তুন আতি আইয়্যি, একবার উত্তো আতি উজ্ঞো মানুষ উরে মারি ফেলাইয়্যিল</t>
   </si>
 </sst>
 </file>
@@ -11947,144 +12157,284 @@
       </c>
     </row>
     <row r="762" ht="25" customHeight="1" spans="1:2">
-      <c r="A762" s="2"/>
-      <c r="B762" s="2"/>
+      <c r="A762" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>1518</v>
+      </c>
     </row>
     <row r="763" ht="25" customHeight="1" spans="1:2">
-      <c r="A763" s="2"/>
-      <c r="B763" s="2"/>
+      <c r="A763" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>1520</v>
+      </c>
     </row>
     <row r="764" ht="25" customHeight="1" spans="1:2">
-      <c r="A764" s="2"/>
-      <c r="B764" s="2"/>
+      <c r="A764" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>1522</v>
+      </c>
     </row>
     <row r="765" ht="25" customHeight="1" spans="1:2">
-      <c r="A765" s="2"/>
-      <c r="B765" s="2"/>
+      <c r="A765" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>1524</v>
+      </c>
     </row>
     <row r="766" ht="25" customHeight="1" spans="1:2">
-      <c r="A766" s="2"/>
-      <c r="B766" s="2"/>
+      <c r="A766" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>1526</v>
+      </c>
     </row>
     <row r="767" ht="25" customHeight="1" spans="1:2">
-      <c r="A767" s="2"/>
-      <c r="B767" s="2"/>
+      <c r="A767" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>1528</v>
+      </c>
     </row>
     <row r="768" ht="25" customHeight="1" spans="1:2">
-      <c r="A768" s="2"/>
-      <c r="B768" s="2"/>
+      <c r="A768" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>1530</v>
+      </c>
     </row>
     <row r="769" ht="25" customHeight="1" spans="1:2">
-      <c r="A769" s="2"/>
-      <c r="B769" s="2"/>
+      <c r="A769" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>1532</v>
+      </c>
     </row>
     <row r="770" ht="25" customHeight="1" spans="1:2">
-      <c r="A770" s="2"/>
-      <c r="B770" s="2"/>
+      <c r="A770" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>1534</v>
+      </c>
     </row>
     <row r="771" ht="25" customHeight="1" spans="1:2">
-      <c r="A771" s="2"/>
-      <c r="B771" s="2"/>
+      <c r="A771" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>1536</v>
+      </c>
     </row>
     <row r="772" ht="25" customHeight="1" spans="1:2">
-      <c r="A772" s="2"/>
-      <c r="B772" s="2"/>
+      <c r="A772" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>1538</v>
+      </c>
     </row>
     <row r="773" ht="25" customHeight="1" spans="1:2">
-      <c r="A773" s="2"/>
-      <c r="B773" s="2"/>
+      <c r="A773" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>1540</v>
+      </c>
     </row>
     <row r="774" ht="25" customHeight="1" spans="1:2">
-      <c r="A774" s="2"/>
-      <c r="B774" s="2"/>
+      <c r="A774" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>1542</v>
+      </c>
     </row>
     <row r="775" ht="25" customHeight="1" spans="1:2">
-      <c r="A775" s="2"/>
-      <c r="B775" s="2"/>
+      <c r="A775" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>1544</v>
+      </c>
     </row>
     <row r="776" ht="25" customHeight="1" spans="1:2">
-      <c r="A776" s="2"/>
-      <c r="B776" s="2"/>
+      <c r="A776" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>1546</v>
+      </c>
     </row>
     <row r="777" ht="25" customHeight="1" spans="1:2">
-      <c r="A777" s="2"/>
-      <c r="B777" s="2"/>
+      <c r="A777" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>1548</v>
+      </c>
     </row>
     <row r="778" ht="25" customHeight="1" spans="1:2">
-      <c r="A778" s="2"/>
-      <c r="B778" s="2"/>
+      <c r="A778" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>1550</v>
+      </c>
     </row>
     <row r="779" ht="25" customHeight="1" spans="1:2">
-      <c r="A779" s="2"/>
-      <c r="B779" s="2"/>
+      <c r="A779" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>1552</v>
+      </c>
     </row>
     <row r="780" ht="25" customHeight="1" spans="1:2">
-      <c r="A780" s="2"/>
-      <c r="B780" s="2"/>
+      <c r="A780" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>1554</v>
+      </c>
     </row>
     <row r="781" ht="25" customHeight="1" spans="1:2">
-      <c r="A781" s="2"/>
-      <c r="B781" s="2"/>
+      <c r="A781" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>1556</v>
+      </c>
     </row>
     <row r="782" ht="25" customHeight="1" spans="1:2">
-      <c r="A782" s="2"/>
-      <c r="B782" s="2"/>
+      <c r="A782" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>1558</v>
+      </c>
     </row>
     <row r="783" ht="25" customHeight="1" spans="1:2">
-      <c r="A783" s="2"/>
-      <c r="B783" s="2"/>
+      <c r="A783" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>1560</v>
+      </c>
     </row>
     <row r="784" ht="25" customHeight="1" spans="1:2">
-      <c r="A784" s="2"/>
-      <c r="B784" s="2"/>
+      <c r="A784" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>1562</v>
+      </c>
     </row>
     <row r="785" ht="25" customHeight="1" spans="1:2">
-      <c r="A785" s="2"/>
-      <c r="B785" s="2"/>
+      <c r="A785" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>1564</v>
+      </c>
     </row>
     <row r="786" ht="25" customHeight="1" spans="1:2">
-      <c r="A786" s="2"/>
-      <c r="B786" s="2"/>
+      <c r="A786" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>1566</v>
+      </c>
     </row>
     <row r="787" ht="25" customHeight="1" spans="1:2">
-      <c r="A787" s="2"/>
-      <c r="B787" s="2"/>
+      <c r="A787" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>1568</v>
+      </c>
     </row>
     <row r="788" ht="25" customHeight="1" spans="1:2">
-      <c r="A788" s="2"/>
-      <c r="B788" s="2"/>
+      <c r="A788" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>1570</v>
+      </c>
     </row>
     <row r="789" ht="25" customHeight="1" spans="1:2">
-      <c r="A789" s="2"/>
-      <c r="B789" s="2"/>
+      <c r="A789" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>1572</v>
+      </c>
     </row>
     <row r="790" ht="25" customHeight="1" spans="1:2">
-      <c r="A790" s="2"/>
-      <c r="B790" s="2"/>
+      <c r="A790" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>1574</v>
+      </c>
     </row>
     <row r="791" ht="25" customHeight="1" spans="1:2">
-      <c r="A791" s="2"/>
-      <c r="B791" s="2"/>
+      <c r="A791" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>1576</v>
+      </c>
     </row>
     <row r="792" ht="25" customHeight="1" spans="1:2">
-      <c r="A792" s="2"/>
-      <c r="B792" s="2"/>
+      <c r="A792" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>1578</v>
+      </c>
     </row>
     <row r="793" ht="25" customHeight="1" spans="1:2">
-      <c r="A793" s="2"/>
-      <c r="B793" s="2"/>
+      <c r="A793" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>1580</v>
+      </c>
     </row>
     <row r="794" ht="25" customHeight="1" spans="1:2">
-      <c r="A794" s="2"/>
-      <c r="B794" s="2"/>
+      <c r="A794" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>1582</v>
+      </c>
     </row>
     <row r="795" ht="25" customHeight="1" spans="1:2">
-      <c r="A795" s="2"/>
-      <c r="B795" s="2"/>
+      <c r="A795" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>1584</v>
+      </c>
     </row>
     <row r="796" ht="25" customHeight="1" spans="1:2">
-      <c r="A796" s="2"/>
-      <c r="B796" s="2"/>
+      <c r="A796" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>1586</v>
+      </c>
     </row>
     <row r="797" ht="25" customHeight="1" spans="1:2">
       <c r="A797" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="1587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="1623">
   <si>
     <t>bangla</t>
   </si>
@@ -2313,7 +2313,7 @@
     <t>আমার বুক জ্বালা করছে, মনে হয় গ্যাস্ট্রিক বেড়ে গেছে</t>
   </si>
   <si>
-    <t>আঁর বুক জ্বলের, মনে অই গ্যাস্ট্রিক বারি গেইয়্যি</t>
+    <t>আঁর বুক জ্বলের, মনে অয় গ্যাস্ট্রিক বারি গেইয়্যি</t>
   </si>
   <si>
     <t>আসলে আমি যেটা বলতে চাচ্ছিলাম</t>
@@ -4735,7 +4735,7 @@
     <t>রান্নাঘরে ডেকচি পড়ার শব্দ হলো, মনে হয় বিড়াল ঢুকেছে</t>
   </si>
   <si>
-    <t>বসহানাত ডেকচি পরিবের আওয়াজ অইয়্যি, মনে অই বিলেই ঢুইক্কি</t>
+    <t>বসহানাত ডেকচি পরিবের আওয়াজ অইয়্যি, মনে অয় বিলেই ঢুইক্কি</t>
   </si>
   <si>
     <t>এই বিড়ালটা এত দুষ্টু, মাছ ভেজে রেখেছিলাম যে ওখান থেকে চুরি করে খেয়ে ফেলেছে</t>
@@ -4892,6 +4892,114 @@
   </si>
   <si>
     <t>মাঝে মাঝে ফা'রুত্তুন আতি আইয়্যি, একবার উত্তো আতি উজ্ঞো মানুষ উরে মারি ফেলাইয়্যিল</t>
+  </si>
+  <si>
+    <t>গরুর জন্য কিছু ঘাস কেটে নিয়ে আসতে হবে</t>
+  </si>
+  <si>
+    <t>গরুর লাই কিছু কের হাডি আনন ফরিবু</t>
+  </si>
+  <si>
+    <t>তোমাকে মনে হয় কাইসার কিছু বলেছিল</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে মনে অয় কাইসার কিছু হইয়্যিল</t>
+  </si>
+  <si>
+    <t>আমাকে তাড়াতাড়ি আপডেট জানান, এখানে সবাই চিন্তায় আছে</t>
+  </si>
+  <si>
+    <t>আঁরে তারাতারি আপডেট জানোন, এনডে বিয়াজ্ঞুন চিন্তেত আছে</t>
+  </si>
+  <si>
+    <t>আরও আছে? আমি আর পারছি না</t>
+  </si>
+  <si>
+    <t>আরো আছে? আঁই আর ন ফারির</t>
+  </si>
+  <si>
+    <t>এগুলো কি পিঠা? চিতই পিঠা এখনো আছে?</t>
+  </si>
+  <si>
+    <t>এগুন কি পিডে, চিতল পিডে এহনো আছে?</t>
+  </si>
+  <si>
+    <t>দাঁড়াও, একটু অপেক্ষা করো, আগে আমারটা করে ফেলি, তারপর তোমারটা করে দেব</t>
+  </si>
+  <si>
+    <t>থিয়েও, এক্কানা অপেক্ষা গরো, আগে আঁর ইয়েন গরি ফেলাই, তারপর তোঁয়ার ইয়েন গইজ্জুম</t>
+  </si>
+  <si>
+    <t>ছেলে মানুষ করা অনেক কঠিন</t>
+  </si>
+  <si>
+    <t>মরতফোয়া মানুষ গরন বত কঠিন</t>
+  </si>
+  <si>
+    <t>ভাবি তার বাপের বাড়িতে চলে গেছে, সেজন্য আম্মুর একা সব কাজ সামলানো অনেক কঠিন হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>ভাবি ইবের বাফুর বারিত চলি গেইয়্যি, এতেল্লে আম্মুত্তুন এহেল্লে বিয়াক হাজ সামালোন বত কঠিন অই যার</t>
+  </si>
+  <si>
+    <t>আজকে ভাইয়া তার শ্বশুর বাড়ি গিয়ে ভাবিকে নিয়ে আসবে</t>
+  </si>
+  <si>
+    <t>আজিয়ে ভাইয়ে ইবের অরো বারিত যায় ভাবিরে লই আইবু</t>
+  </si>
+  <si>
+    <t>এমনি বলে যাচ্ছি আর কী, কে শোনে কার কথা</t>
+  </si>
+  <si>
+    <t>এনে হই যাইর এরি, হনে উনে হার হতা</t>
+  </si>
+  <si>
+    <t>আইডি কার্ডটা নিয়ে আসি, না হলে আবার বের করে দেবে</t>
+  </si>
+  <si>
+    <t>আইডি কার্ড ইয়েন লই আই, নইলি আবার বাইর গরি দিবু</t>
+  </si>
+  <si>
+    <t>তোর ছোট বোনটা বেশি কাবিল, সব জায়গায় কথা বলে</t>
+  </si>
+  <si>
+    <t>তুর ছোডো বইন ইতি বেশি হাবিল, বিয়াক জাগাত হতা হয়</t>
+  </si>
+  <si>
+    <t>গতকাল নেজামের ভাইকে নাকি পুলিশ ধরে নিয়ে গেছে, খবরটা একটু আগে শুনলাম</t>
+  </si>
+  <si>
+    <t>গত হালিয়ে নেজামুর ভাই উরে বলে পুলিশ ধরি লই গেইয়্যি, হবর ইয়েন এক্কানা আগে ফুইন্নি</t>
+  </si>
+  <si>
+    <t>রুটি দুটো আছে যে এগুলো খাবি?</t>
+  </si>
+  <si>
+    <t>রুটি দুওয়ো আছে দে এগুন হাবি?</t>
+  </si>
+  <si>
+    <t>সকাল সকাল খিচুড়ি খেয়ে আমার পেটের অবস্থা খারাপ</t>
+  </si>
+  <si>
+    <t>বেইন্নে ফজোরত খিচুড়ি হাইয়্যি রে আঁর পেডোর অবস্থা হারাফ</t>
+  </si>
+  <si>
+    <t>বেলকনিতে অনেক ময়লা হয়ে গেছে, ধুয়ে দিতে হবে</t>
+  </si>
+  <si>
+    <t>বেলকনিত বত হাচারা অই গেইয়্যি, ধুই দন ফরিবু</t>
+  </si>
+  <si>
+    <t>চাচি, আপনার ছেলে-মেয়ে কয়টা?</t>
+  </si>
+  <si>
+    <t>চাচি, অঁনোর ফোয়া-মাইফোয়া হওয়ো?</t>
+  </si>
+  <si>
+    <t>এটা এরকম হয়ে যাবে যে সেটা আমি আগে বুঝতে পারিনি</t>
+  </si>
+  <si>
+    <t>ইয়েন এরহম অই যাইবু দে ইয়েন আঁই বুঝিত ন ফারি</t>
   </si>
 </sst>
 </file>
@@ -12437,76 +12545,148 @@
       </c>
     </row>
     <row r="797" ht="25" customHeight="1" spans="1:2">
-      <c r="A797" s="2"/>
-      <c r="B797" s="2"/>
+      <c r="A797" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>1588</v>
+      </c>
     </row>
     <row r="798" ht="25" customHeight="1" spans="1:2">
-      <c r="A798" s="2"/>
-      <c r="B798" s="2"/>
+      <c r="A798" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>1590</v>
+      </c>
     </row>
     <row r="799" ht="25" customHeight="1" spans="1:2">
-      <c r="A799" s="2"/>
-      <c r="B799" s="2"/>
+      <c r="A799" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>1592</v>
+      </c>
     </row>
     <row r="800" ht="25" customHeight="1" spans="1:2">
-      <c r="A800" s="2"/>
-      <c r="B800" s="2"/>
+      <c r="A800" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>1594</v>
+      </c>
     </row>
     <row r="801" ht="25" customHeight="1" spans="1:2">
-      <c r="A801" s="2"/>
-      <c r="B801" s="2"/>
+      <c r="A801" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>1596</v>
+      </c>
     </row>
     <row r="802" ht="25" customHeight="1" spans="1:2">
-      <c r="A802" s="2"/>
-      <c r="B802" s="2"/>
+      <c r="A802" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>1598</v>
+      </c>
     </row>
     <row r="803" ht="25" customHeight="1" spans="1:2">
-      <c r="A803" s="2"/>
-      <c r="B803" s="2"/>
+      <c r="A803" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>1600</v>
+      </c>
     </row>
     <row r="804" ht="25" customHeight="1" spans="1:2">
-      <c r="A804" s="2"/>
-      <c r="B804" s="2"/>
+      <c r="A804" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>1602</v>
+      </c>
     </row>
     <row r="805" ht="25" customHeight="1" spans="1:2">
-      <c r="A805" s="2"/>
-      <c r="B805" s="2"/>
+      <c r="A805" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>1604</v>
+      </c>
     </row>
     <row r="806" ht="25" customHeight="1" spans="1:2">
-      <c r="A806" s="2"/>
-      <c r="B806" s="2"/>
+      <c r="A806" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>1606</v>
+      </c>
     </row>
     <row r="807" ht="25" customHeight="1" spans="1:2">
-      <c r="A807" s="2"/>
-      <c r="B807" s="2"/>
+      <c r="A807" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>1608</v>
+      </c>
     </row>
     <row r="808" ht="25" customHeight="1" spans="1:2">
-      <c r="A808" s="2"/>
-      <c r="B808" s="2"/>
+      <c r="A808" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>1610</v>
+      </c>
     </row>
     <row r="809" ht="25" customHeight="1" spans="1:2">
-      <c r="A809" s="2"/>
-      <c r="B809" s="2"/>
+      <c r="A809" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>1612</v>
+      </c>
     </row>
     <row r="810" ht="25" customHeight="1" spans="1:2">
-      <c r="A810" s="2"/>
-      <c r="B810" s="2"/>
+      <c r="A810" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>1614</v>
+      </c>
     </row>
     <row r="811" ht="25" customHeight="1" spans="1:2">
-      <c r="A811" s="2"/>
-      <c r="B811" s="2"/>
+      <c r="A811" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>1616</v>
+      </c>
     </row>
     <row r="812" ht="25" customHeight="1" spans="1:2">
-      <c r="A812" s="2"/>
-      <c r="B812" s="2"/>
+      <c r="A812" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>1618</v>
+      </c>
     </row>
     <row r="813" ht="25" customHeight="1" spans="1:2">
-      <c r="A813" s="2"/>
-      <c r="B813" s="2"/>
+      <c r="A813" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B813" s="2" t="s">
+        <v>1620</v>
+      </c>
     </row>
     <row r="814" ht="25" customHeight="1" spans="1:2">
-      <c r="A814" s="2"/>
-      <c r="B814" s="2"/>
+      <c r="A814" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>1622</v>
+      </c>
     </row>
     <row r="815" ht="25" customHeight="1" spans="1:2">
       <c r="A815" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="1623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1697">
   <si>
     <t>bangla</t>
   </si>
@@ -4879,7 +4879,7 @@
     <t>গতকাল শিয়াল একটা এসে আমার সবচেয়ে বড় মুরগিটা ধরে নিয়ে গেছে</t>
   </si>
   <si>
-    <t>গত হালিয়ে ইয়েল উজ্ঞো আইয়্যিরে আঁর বিয়াজ্ঞুনুত্তন বরো কুরো ইবে ধরি লই গেইয়্যি</t>
+    <t>গত হালিয়ে ইয়েল উজ্ঞো আইয়্যিরে আঁর বিয়াজ্ঞুনুত্তুন বরো কুরো ইবে ধরি লই গেইয়্যি</t>
   </si>
   <si>
     <t>পাহাড় থেকে প্রতিদিন রাতে শিয়াল আসে</t>
@@ -5000,6 +5000,228 @@
   </si>
   <si>
     <t>ইয়েন এরহম অই যাইবু দে ইয়েন আঁই বুঝিত ন ফারি</t>
+  </si>
+  <si>
+    <t>আমাদের মসজিদে ঈদের নামাজ তাড়াতাড়ি হয়ে যায়</t>
+  </si>
+  <si>
+    <t>আঁরার মসজিদুত ঈদুর নামাজ তারাতারি অই যায়</t>
+  </si>
+  <si>
+    <t>এই ঈদে আমরা সব বন্ধুরা একরকম পাঞ্জাবি নিয়েছি</t>
+  </si>
+  <si>
+    <t>এই ঈদুত আঁরা বিয়াক বন্ধু একি রহম পাঞ্জাবি লই</t>
+  </si>
+  <si>
+    <t>এদের দুজনের পাঞ্জাবি দেখে বোঝা যাচ্ছে এরা দুজন ভাই</t>
+  </si>
+  <si>
+    <t>ইতারা দুনুজনোর পাঞ্জাবি দেহি বুঝা যার ইতারা দুনুজন ভাই</t>
+  </si>
+  <si>
+    <t>ওকে দেখলে আমার মাথা গরম হয়ে যায়, মন চায় একটা থাপ্পড় দিই</t>
+  </si>
+  <si>
+    <t>ইতেরে দেহিলি আঁর মাথা গরম অই যায়, মন চায় উজ্ঞো সোয়ার দিই</t>
+  </si>
+  <si>
+    <t>তোমার ছোট ছেলেটা বেশি বাহানা করে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার ছোডো ফোয়া ইবে বেশি তাল গরে</t>
+  </si>
+  <si>
+    <t>মানুষজন এসে আমার ঘরটা ময়লা করে ফেলেছে</t>
+  </si>
+  <si>
+    <t>মানুষজন আইয়্যিরে আঁর ঘর ইয়েন হাচারা গরি ফেলাইয়্যি</t>
+  </si>
+  <si>
+    <t>এবার বর্ষা আসার আগে ঘরটা ঠিক করে ফেলতে হবে, না হলে বর্ষাকালে বেশি কষ্ট হবে</t>
+  </si>
+  <si>
+    <t>এবার বর্ষা আইবের আগে ঘর ইয়েন ঠিক গরি ফেলন ফরিবু, নইলি বর্ষাহালে হষ্ট অইবু</t>
+  </si>
+  <si>
+    <t>পুকুরের পানিতে বেশিক্ষণ থাকিও না, অসুখ চলে আসবে</t>
+  </si>
+  <si>
+    <t>ফইরোর ফানিত বেশিক্ষণ ন থাইক্কো, অসুখ চলি আইবু</t>
+  </si>
+  <si>
+    <t>আম্মু বেত নিয়ে আসছে, তাড়াতাড়ি পুকুর থেকে উঠে আয়</t>
+  </si>
+  <si>
+    <t>আম্মু বেত লইয়্যিরে আইয়্যির, তারাতারি ফইরোত্তুন উডি আই</t>
+  </si>
+  <si>
+    <t>পুকুরের মাছগুলো মরে যাচ্ছে, ওষুধ দিতে হবে</t>
+  </si>
+  <si>
+    <t>ফইরোর মাছ এগুন মরি যার, ওষুধ দন ফরিবু</t>
+  </si>
+  <si>
+    <t>বেশি দুষ্টামি না করে প্যান্টটা পরে নাও</t>
+  </si>
+  <si>
+    <t>বেশি যারগই ন গরি ফেন ইবে পরি লও</t>
+  </si>
+  <si>
+    <t>আমার যখন শরীর ভালো ছিল, তখন সব আমি একা করে ফেলতাম</t>
+  </si>
+  <si>
+    <t>আঁর যহন শরীর ভালা আছিল তহন বিয়াক আঁই এহেল্লে গরি ফেলাইতাম</t>
+  </si>
+  <si>
+    <t>ওকে দেখে আমার চোরের মতো লাগে</t>
+  </si>
+  <si>
+    <t>ইতেরে দেহি আত্তুন চোরুর মতন লাগে</t>
+  </si>
+  <si>
+    <t>অনেকদিন ধরে ওষুধ খাচ্ছি, তাও ভালো লাগছে না</t>
+  </si>
+  <si>
+    <t>বতদিন ধরি ওষুধ হাইর, তাও গম ন লার</t>
+  </si>
+  <si>
+    <t>চট্টগ্রামের মানুষজন মেজবান অনেক পছন্দ করে</t>
+  </si>
+  <si>
+    <t>চট্টগ্রামোর মানুষজন  মেজ্জান বত পছন্দ গরে</t>
+  </si>
+  <si>
+    <t>তোর স্বভাব-চরিত্র আমার ভালো লাগছে না, দিন দিন খারাপ হয়ে যাচ্ছিস</t>
+  </si>
+  <si>
+    <t>তোর হাস্তা-হাসিলত আত্তুন গম ন লার, দিন দিন হারাফ অই যর</t>
+  </si>
+  <si>
+    <t>এটা ফেলে দিয়েন না, এটা আমার লাগবে</t>
+  </si>
+  <si>
+    <t>ইয়েন ফেলাই নইদ্দুন, ইয়েন আত্তুন লাগিবু</t>
+  </si>
+  <si>
+    <t>তোর মনে যে এত ময়লা, সেটা আমি আগে বুঝতে পারিনি</t>
+  </si>
+  <si>
+    <t>তুর মনোত যে এদিজ্ঞিন হাচারা ইয়েন আঁই আগে ন বুঝি</t>
+  </si>
+  <si>
+    <t>আমার ভাইকে কেউ দেখতে পারলে আমার অনেক ভালো লাগে</t>
+  </si>
+  <si>
+    <t>আঁর ভাইয়্যুরে কিয়াই দেইত ফারিলি আত্তুন বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>তোমাদেরকে একটা কাজ দিয়েছিলাম, ভুলে গেছো তোমরা</t>
+  </si>
+  <si>
+    <t>তোঁয়ারারে এক্কান হাম দিইলাম, ভুলি গেইয়্যু তোঁইয়ারা</t>
+  </si>
+  <si>
+    <t>একা একা না ঘুরে আমার সাথে ঘুরতে পারো</t>
+  </si>
+  <si>
+    <t>এহেল্লে এহেল্লে ন ঘুরি আঁর লগে ঘুরিত ফারো</t>
+  </si>
+  <si>
+    <t>সারাদিন অনেক কাজের চাপ থাকে, সেজন্য সময় হয়ে উঠেনি</t>
+  </si>
+  <si>
+    <t>আরাদিন বত হাজুর চাপ থাহে, এতেল্লে সময় অই ন উডে</t>
+  </si>
+  <si>
+    <t>বিপদে পড়লে তখন মানুষের আসল চেহারা দেখা যায়</t>
+  </si>
+  <si>
+    <t>বিপদুত ফরিলি তহন  মানুষুর আসল চিয়ারা দেহা যায়</t>
+  </si>
+  <si>
+    <t>আমার সবচেয়ে খারাপ সময়ে আমার কোনো বন্ধু পাশে ছিল না</t>
+  </si>
+  <si>
+    <t>আঁর বিয়াজ্ঞুনুত্তুন হারাপ সময়ুত আঁর হনো বন্ধু পাশে ন আছিল</t>
+  </si>
+  <si>
+    <t>এই দুনিয়াতে সবাই স্বার্থপর, খারাপ সময় আসলে বোঝা যায়</t>
+  </si>
+  <si>
+    <t>এই দুনিয়েত বিয়াজ্ঞুন স্বার্থপর, হারাপ সময় আইলি বুঝা যায়</t>
+  </si>
+  <si>
+    <t>আচ্ছা ঠিক আছে, আমি কথা বলে দেখব ওর সাথে</t>
+  </si>
+  <si>
+    <t>আইচ্ছে ঠিক আছে, আঁই হতা হই চাইয়্যুম ইতের লগে</t>
+  </si>
+  <si>
+    <t>মনির আমাকে বলেছিল পারবে, কিন্তু এখন এমন কেন বলল বুঝছি না</t>
+  </si>
+  <si>
+    <t>মনির আঁরে হইয়্যিল ফারিবু, কিন্তু এহন এল্লেত কা হর ন বুঝির</t>
+  </si>
+  <si>
+    <t>আমরা অনেক সময় মানুষকে বেশি বিশ্বাস করে ফেলি, যার কারণে পরে গিয়ে কষ্ট পাই</t>
+  </si>
+  <si>
+    <t>আঁরা বত সময় মানুষ উরে বেশি বিশ্বেস গরি ফেলাই, যার হারনে পরে যাই হষ্ট পাই</t>
+  </si>
+  <si>
+    <t>বিশ্বাস জিনিসটা অনেক মূল্যবান, একবার ভেঙে গেলে শেষ</t>
+  </si>
+  <si>
+    <t>বিশ্বেস জিনিস ইয়েন বত দামি, একবার ভাঙি গেলি শেষ</t>
+  </si>
+  <si>
+    <t>আমার জন্য শুধু দোয়া করলেই হবে, আর কিছু লাগবে না</t>
+  </si>
+  <si>
+    <t>আঁর লাই উদো দোয়া গরিলিই অইবু, আর কিছু ন লাগিবু</t>
+  </si>
+  <si>
+    <t>ঢাকনা খুলিও না, পানি পড়ে যাবে</t>
+  </si>
+  <si>
+    <t>ঢাকনা ন খুইল্লো, পানি ফরি যাইবু</t>
+  </si>
+  <si>
+    <t>আরও নিচে করো, না হলে ধরতে পারব না</t>
+  </si>
+  <si>
+    <t>আরও নিচে গরো, নইলি ধরিত ন ফারিবে</t>
+  </si>
+  <si>
+    <t>এটা কী শার্ট পরেছিস! তোকে দেখে তো গ্রামের চাচাতো ভাইয়ের মতো লাগছে</t>
+  </si>
+  <si>
+    <t>ইবে কি শার্ট ফইজ্জুস দে! তুরে দেহি তো গ্রামোর চাচতো ভাইয়্যুর মতন লাগের</t>
+  </si>
+  <si>
+    <t>হিজড়াদের মতো এগুলো কী পোশাক পরেছিস?</t>
+  </si>
+  <si>
+    <t>ইজারা অক্কলোর মতন এগুন কি পোশাক ফইজ্জস?</t>
+  </si>
+  <si>
+    <t>তুমি যদি এক মাস কষ্ট করো তাহলে অনেক কিছু ঠিক হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>তুঁই যদি এক মাস হষ্ট গরো তইলি বত কিছু ঠিক অই যাইবু</t>
+  </si>
+  <si>
+    <t>হতাশ হয়ে বসে না থেকে কাজ কর</t>
+  </si>
+  <si>
+    <t>হতাশ অইয়্যিরে বই ন থাহি হাম গরো</t>
+  </si>
+  <si>
+    <t>আর অল্প বাকি, বেশিক্ষণ লাগবে না</t>
+  </si>
+  <si>
+    <t>আর এক্কানা বাকি, বেশিক্ষন ন লাগিবু</t>
   </si>
 </sst>
 </file>
@@ -12689,152 +12911,300 @@
       </c>
     </row>
     <row r="815" ht="25" customHeight="1" spans="1:2">
-      <c r="A815" s="2"/>
-      <c r="B815" s="2"/>
+      <c r="A815" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>1624</v>
+      </c>
     </row>
     <row r="816" ht="25" customHeight="1" spans="1:2">
-      <c r="A816" s="2"/>
-      <c r="B816" s="2"/>
+      <c r="A816" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>1626</v>
+      </c>
     </row>
     <row r="817" ht="25" customHeight="1" spans="1:2">
-      <c r="A817" s="2"/>
-      <c r="B817" s="2"/>
+      <c r="A817" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>1628</v>
+      </c>
     </row>
     <row r="818" ht="25" customHeight="1" spans="1:2">
-      <c r="A818" s="2"/>
-      <c r="B818" s="2"/>
+      <c r="A818" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>1630</v>
+      </c>
     </row>
     <row r="819" ht="25" customHeight="1" spans="1:2">
-      <c r="A819" s="2"/>
-      <c r="B819" s="2"/>
+      <c r="A819" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>1632</v>
+      </c>
     </row>
     <row r="820" ht="25" customHeight="1" spans="1:2">
-      <c r="A820" s="2"/>
-      <c r="B820" s="2"/>
+      <c r="A820" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>1634</v>
+      </c>
     </row>
     <row r="821" ht="25" customHeight="1" spans="1:2">
-      <c r="A821" s="2"/>
-      <c r="B821" s="2"/>
+      <c r="A821" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>1636</v>
+      </c>
     </row>
     <row r="822" ht="25" customHeight="1" spans="1:2">
-      <c r="A822" s="2"/>
-      <c r="B822" s="2"/>
+      <c r="A822" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>1638</v>
+      </c>
     </row>
     <row r="823" ht="25" customHeight="1" spans="1:2">
-      <c r="A823" s="2"/>
-      <c r="B823" s="2"/>
+      <c r="A823" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>1640</v>
+      </c>
     </row>
     <row r="824" ht="25" customHeight="1" spans="1:2">
-      <c r="A824" s="2"/>
-      <c r="B824" s="2"/>
+      <c r="A824" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>1642</v>
+      </c>
     </row>
     <row r="825" ht="25" customHeight="1" spans="1:2">
-      <c r="A825" s="2"/>
-      <c r="B825" s="2"/>
+      <c r="A825" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>1644</v>
+      </c>
     </row>
     <row r="826" ht="25" customHeight="1" spans="1:2">
-      <c r="A826" s="2"/>
-      <c r="B826" s="2"/>
+      <c r="A826" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>1646</v>
+      </c>
     </row>
     <row r="827" ht="25" customHeight="1" spans="1:2">
-      <c r="A827" s="2"/>
-      <c r="B827" s="2"/>
+      <c r="A827" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>1648</v>
+      </c>
     </row>
     <row r="828" ht="25" customHeight="1" spans="1:2">
-      <c r="A828" s="2"/>
-      <c r="B828" s="2"/>
+      <c r="A828" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>1650</v>
+      </c>
     </row>
     <row r="829" ht="25" customHeight="1" spans="1:2">
-      <c r="A829" s="2"/>
-      <c r="B829" s="2"/>
+      <c r="A829" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>1652</v>
+      </c>
     </row>
     <row r="830" ht="25" customHeight="1" spans="1:2">
-      <c r="A830" s="2"/>
-      <c r="B830" s="2"/>
+      <c r="A830" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>1654</v>
+      </c>
     </row>
     <row r="831" ht="25" customHeight="1" spans="1:2">
-      <c r="A831" s="2"/>
-      <c r="B831" s="2"/>
+      <c r="A831" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>1656</v>
+      </c>
     </row>
     <row r="832" ht="25" customHeight="1" spans="1:2">
-      <c r="A832" s="2"/>
-      <c r="B832" s="2"/>
+      <c r="A832" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>1658</v>
+      </c>
     </row>
     <row r="833" ht="25" customHeight="1" spans="1:2">
-      <c r="A833" s="2"/>
-      <c r="B833" s="2"/>
+      <c r="A833" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>1660</v>
+      </c>
     </row>
     <row r="834" ht="25" customHeight="1" spans="1:2">
-      <c r="A834" s="2"/>
-      <c r="B834" s="2"/>
+      <c r="A834" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>1662</v>
+      </c>
     </row>
     <row r="835" ht="25" customHeight="1" spans="1:2">
-      <c r="A835" s="2"/>
-      <c r="B835" s="2"/>
+      <c r="A835" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>1664</v>
+      </c>
     </row>
     <row r="836" ht="25" customHeight="1" spans="1:2">
-      <c r="A836" s="2"/>
-      <c r="B836" s="2"/>
+      <c r="A836" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>1666</v>
+      </c>
     </row>
     <row r="837" ht="25" customHeight="1" spans="1:2">
-      <c r="A837" s="2"/>
-      <c r="B837" s="2"/>
+      <c r="A837" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>1668</v>
+      </c>
     </row>
     <row r="838" ht="25" customHeight="1" spans="1:2">
-      <c r="A838" s="2"/>
-      <c r="B838" s="2"/>
+      <c r="A838" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>1670</v>
+      </c>
     </row>
     <row r="839" ht="25" customHeight="1" spans="1:2">
-      <c r="A839" s="2"/>
-      <c r="B839" s="2"/>
+      <c r="A839" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>1672</v>
+      </c>
     </row>
     <row r="840" ht="25" customHeight="1" spans="1:2">
-      <c r="A840" s="2"/>
-      <c r="B840" s="2"/>
+      <c r="A840" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>1674</v>
+      </c>
     </row>
     <row r="841" ht="25" customHeight="1" spans="1:2">
-      <c r="A841" s="2"/>
-      <c r="B841" s="2"/>
+      <c r="A841" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>1676</v>
+      </c>
     </row>
     <row r="842" ht="25" customHeight="1" spans="1:2">
-      <c r="A842" s="2"/>
-      <c r="B842" s="2"/>
+      <c r="A842" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>1678</v>
+      </c>
     </row>
     <row r="843" ht="25" customHeight="1" spans="1:2">
-      <c r="A843" s="2"/>
-      <c r="B843" s="2"/>
+      <c r="A843" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>1680</v>
+      </c>
     </row>
     <row r="844" ht="25" customHeight="1" spans="1:2">
-      <c r="A844" s="2"/>
-      <c r="B844" s="2"/>
+      <c r="A844" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>1682</v>
+      </c>
     </row>
     <row r="845" ht="25" customHeight="1" spans="1:2">
-      <c r="A845" s="2"/>
-      <c r="B845" s="2"/>
+      <c r="A845" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>1684</v>
+      </c>
     </row>
     <row r="846" ht="25" customHeight="1" spans="1:2">
-      <c r="A846" s="2"/>
-      <c r="B846" s="2"/>
+      <c r="A846" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>1686</v>
+      </c>
     </row>
     <row r="847" ht="25" customHeight="1" spans="1:2">
-      <c r="A847" s="2"/>
-      <c r="B847" s="2"/>
+      <c r="A847" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>1688</v>
+      </c>
     </row>
     <row r="848" ht="25" customHeight="1" spans="1:2">
-      <c r="A848" s="2"/>
-      <c r="B848" s="2"/>
+      <c r="A848" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>1690</v>
+      </c>
     </row>
     <row r="849" ht="25" customHeight="1" spans="1:2">
-      <c r="A849" s="2"/>
-      <c r="B849" s="2"/>
+      <c r="A849" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>1692</v>
+      </c>
     </row>
     <row r="850" ht="25" customHeight="1" spans="1:2">
-      <c r="A850" s="2"/>
-      <c r="B850" s="2"/>
+      <c r="A850" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>1694</v>
+      </c>
     </row>
     <row r="851" ht="25" customHeight="1" spans="1:2">
-      <c r="A851" s="2"/>
-      <c r="B851" s="2"/>
+      <c r="A851" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>1696</v>
+      </c>
     </row>
     <row r="852" ht="25" customHeight="1" spans="1:2">
       <c r="A852" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="1717">
   <si>
     <t>bangla</t>
   </si>
@@ -5222,6 +5222,66 @@
   </si>
   <si>
     <t>আর এক্কানা বাকি, বেশিক্ষন ন লাগিবু</t>
+  </si>
+  <si>
+    <t>খালাম্মা নাকি বেড়াতে গেছেন, আমার সাথে যেতে পারবেন না</t>
+  </si>
+  <si>
+    <t>হালাম্মা বলে বেরাইতু গেইয়্যি, আঁর লগে যাইত ন ফারিবু</t>
+  </si>
+  <si>
+    <t>আমি একা যেতে পারব, সমস্যা নাই</t>
+  </si>
+  <si>
+    <t>আঁই এহেল্লে যাইত পাইজ্জুম, সমস্যা নেই</t>
+  </si>
+  <si>
+    <t>আর দুদিন পর রমজান, এখনো রমজানের বাজার করা হয় নাই</t>
+  </si>
+  <si>
+    <t>আর দুদিন পর রমজান, এহনো রমজানুর বাজার গরা নো অয়</t>
+  </si>
+  <si>
+    <t>আমাদের মাদরাসা পুরো রমজান বন্ধ থাকবে</t>
+  </si>
+  <si>
+    <t>আঁরার মাদরাসা পুরো রমজান বন্ধ থাহিবু</t>
+  </si>
+  <si>
+    <t>রমজানে বেশি বেশি নামাজ আর জিকির করতে হবে, আর সুযোগ হলে একটা কোরআন খতম দিতে হবে</t>
+  </si>
+  <si>
+    <t>রমজানুত বেশি বেশি নামাজ আর জিকির গরন ফরিবু, আর সুযোগ অইলি উজ্ঞো কোরআন হতম দন ফরিবু</t>
+  </si>
+  <si>
+    <t>রমজান মাসে প্রতিদিন রাতে তারাবিহ নামাজ পড়তে হবে</t>
+  </si>
+  <si>
+    <t>রমজান মাসুত ফইত্তুদিন রাতিয়ে তারাবিহ নামাজ ফরন ফরিবু</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় রমজান মাসে মসজিদে তারাবিহ পড়তে গেলে অনেক দুষ্টামি করতাম</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে রমজান মাসুত মসজিদুত তারাবিহ ফইত্তু গেইলি বত যারগই গইত্তাম</t>
+  </si>
+  <si>
+    <t>আমি সাঁতার পারি না, আমাকে ধাক্কা দিস না</t>
+  </si>
+  <si>
+    <t>আঁই আছুরিত ন ফারি, আঁরে ডেক্কা ন দিস</t>
+  </si>
+  <si>
+    <t>সাইকেল চালাতে গিয়ে একবার অনেক ব্যথা পেয়েছিলাম</t>
+  </si>
+  <si>
+    <t>সাইকেল চালাইতাম যায় একবার বত ব্যথা পাইলাম</t>
+  </si>
+  <si>
+    <t>আমি সাইকেল চালাতে পারি কিন্তু বাইক চালাতে পারি না</t>
+  </si>
+  <si>
+    <t>আঁই সাইকেল চালাইত ফারি কিন্তু বাইক চালাইত ন ফারি</t>
   </si>
 </sst>
 </file>
@@ -13207,44 +13267,84 @@
       </c>
     </row>
     <row r="852" ht="25" customHeight="1" spans="1:2">
-      <c r="A852" s="2"/>
-      <c r="B852" s="2"/>
+      <c r="A852" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>1698</v>
+      </c>
     </row>
     <row r="853" ht="25" customHeight="1" spans="1:2">
-      <c r="A853" s="2"/>
-      <c r="B853" s="2"/>
+      <c r="A853" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>1700</v>
+      </c>
     </row>
     <row r="854" ht="25" customHeight="1" spans="1:2">
-      <c r="A854" s="2"/>
-      <c r="B854" s="2"/>
+      <c r="A854" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>1702</v>
+      </c>
     </row>
     <row r="855" ht="25" customHeight="1" spans="1:2">
-      <c r="A855" s="2"/>
-      <c r="B855" s="2"/>
+      <c r="A855" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>1704</v>
+      </c>
     </row>
     <row r="856" ht="25" customHeight="1" spans="1:2">
-      <c r="A856" s="2"/>
-      <c r="B856" s="2"/>
+      <c r="A856" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>1706</v>
+      </c>
     </row>
     <row r="857" ht="25" customHeight="1" spans="1:2">
-      <c r="A857" s="2"/>
-      <c r="B857" s="2"/>
+      <c r="A857" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>1708</v>
+      </c>
     </row>
     <row r="858" ht="25" customHeight="1" spans="1:2">
-      <c r="A858" s="2"/>
-      <c r="B858" s="2"/>
+      <c r="A858" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>1710</v>
+      </c>
     </row>
     <row r="859" ht="25" customHeight="1" spans="1:2">
-      <c r="A859" s="2"/>
-      <c r="B859" s="2"/>
+      <c r="A859" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>1712</v>
+      </c>
     </row>
     <row r="860" ht="25" customHeight="1" spans="1:2">
-      <c r="A860" s="2"/>
-      <c r="B860" s="2"/>
+      <c r="A860" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>1714</v>
+      </c>
     </row>
     <row r="861" ht="25" customHeight="1" spans="1:2">
-      <c r="A861" s="2"/>
-      <c r="B861" s="2"/>
+      <c r="A861" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>1716</v>
+      </c>
     </row>
     <row r="862" ht="25" customHeight="1" spans="1:2">
       <c r="A862" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="1737">
   <si>
     <t>bangla</t>
   </si>
@@ -5282,6 +5282,66 @@
   </si>
   <si>
     <t>আঁই সাইকেল চালাইত ফারি কিন্তু বাইক চালাইত ন ফারি</t>
+  </si>
+  <si>
+    <t>আপু, তুমি আমাকে পড়াটা একটু বুঝিয়ে দাও</t>
+  </si>
+  <si>
+    <t>আফা, তুঁই আঁরে পরাগান এক্কানা বুঝায় দও</t>
+  </si>
+  <si>
+    <t>এই অধ্যায়টা অনেক বেশি কঠিন, কিছু বুঝছি না</t>
+  </si>
+  <si>
+    <t>এই অধ্যায় ইবে বেশি কঠিন, কিছু ন বুঝির</t>
+  </si>
+  <si>
+    <t>আরও তিনটা অধ্যায় পড়তে হবে যদি পরীক্ষায় পাশ করতে চাও</t>
+  </si>
+  <si>
+    <t>আরও তিন্নো অধ্যায় ফরন ফরিবু যদি পরীক্ষেত পাশ গইত্তাম চও</t>
+  </si>
+  <si>
+    <t>তোমার মাথায় কি কোন বুদ্ধি নাই?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার মাথাত কি হনো বুদ্ধি নেই?</t>
+  </si>
+  <si>
+    <t>রান্না মাত্র শেষ হলো, এখন খেয়ে ফেলবেন?</t>
+  </si>
+  <si>
+    <t>রান্না মাত্র শেষ অইয়্যি, এহন হাই ফেলাইবেন?</t>
+  </si>
+  <si>
+    <t>আমি আজকে খাব না, বেশি মোটা হয়ে যাচ্ছি দিন দিন</t>
+  </si>
+  <si>
+    <t>আঁই আজিয়ে হাইতাম নো, বেশি মোটা অই যাইর দিন দিন</t>
+  </si>
+  <si>
+    <t>তোমার বাড়ি কি কলেজের পাশে?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার বারি কি কলেজুর পাশে?</t>
+  </si>
+  <si>
+    <t>আমার বাড়ি থেকে স্কুল অনেক দুরে, যেতে অনেক কষ্ট হয়</t>
+  </si>
+  <si>
+    <t>আঁর বারিত্তুন স্কুল বত দুরে, যাইতু হষ্ট অই</t>
+  </si>
+  <si>
+    <t>আমাদের বাড়ি থেকে স্কুলে যাওয়ার রাস্তাটা মাটির, যার কারণে বর্ষাকালে স্কুলে যেতে অনেক কষ্ট হয়</t>
+  </si>
+  <si>
+    <t>আঁরার বারিত্তুন স্কুলুত যাইবের রাস্তা ইবে মেডির, যার হারনে বর্ষাহালে স্কুলুত যাইতে বত হষ্ট অয়</t>
+  </si>
+  <si>
+    <t>তোমরা ভাই-বোন কয়জন?</t>
+  </si>
+  <si>
+    <t>তোঁয়ারা ভাই-বইন হতোজন?</t>
   </si>
 </sst>
 </file>
@@ -13347,44 +13407,84 @@
       </c>
     </row>
     <row r="862" ht="25" customHeight="1" spans="1:2">
-      <c r="A862" s="2"/>
-      <c r="B862" s="2"/>
+      <c r="A862" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>1718</v>
+      </c>
     </row>
     <row r="863" ht="25" customHeight="1" spans="1:2">
-      <c r="A863" s="2"/>
-      <c r="B863" s="2"/>
+      <c r="A863" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>1720</v>
+      </c>
     </row>
     <row r="864" ht="25" customHeight="1" spans="1:2">
-      <c r="A864" s="2"/>
-      <c r="B864" s="2"/>
+      <c r="A864" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>1722</v>
+      </c>
     </row>
     <row r="865" ht="25" customHeight="1" spans="1:2">
-      <c r="A865" s="2"/>
-      <c r="B865" s="2"/>
+      <c r="A865" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>1724</v>
+      </c>
     </row>
     <row r="866" ht="25" customHeight="1" spans="1:2">
-      <c r="A866" s="2"/>
-      <c r="B866" s="2"/>
+      <c r="A866" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>1726</v>
+      </c>
     </row>
     <row r="867" ht="25" customHeight="1" spans="1:2">
-      <c r="A867" s="2"/>
-      <c r="B867" s="2"/>
+      <c r="A867" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>1728</v>
+      </c>
     </row>
     <row r="868" ht="25" customHeight="1" spans="1:2">
-      <c r="A868" s="2"/>
-      <c r="B868" s="2"/>
+      <c r="A868" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>1730</v>
+      </c>
     </row>
     <row r="869" ht="25" customHeight="1" spans="1:2">
-      <c r="A869" s="2"/>
-      <c r="B869" s="2"/>
+      <c r="A869" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>1732</v>
+      </c>
     </row>
     <row r="870" ht="25" customHeight="1" spans="1:2">
-      <c r="A870" s="2"/>
-      <c r="B870" s="2"/>
+      <c r="A870" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>1734</v>
+      </c>
     </row>
     <row r="871" ht="25" customHeight="1" spans="1:2">
-      <c r="A871" s="2"/>
-      <c r="B871" s="2"/>
+      <c r="A871" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>1736</v>
+      </c>
     </row>
     <row r="872" ht="25" customHeight="1" spans="1:2">
       <c r="A872" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="1783">
   <si>
     <t>bangla</t>
   </si>
@@ -2811,7 +2811,7 @@
     <t>দরজা খুলে দেখি একটা সুন্দরী মেয়ে দাঁড়িয়ে আছে</t>
   </si>
   <si>
-    <t>দরজা খুলি দেহি উজ্ঞো সুন্দরী মাইফোয়া থিয়েই আছে</t>
+    <t>দরজা খুলি দেহি উজ্ঞো সুন্দরী মাইফুয়া থিয়েই আছে</t>
   </si>
   <si>
     <t>দরজার বাইরে একটা ভিক্কুক দাঁড়ায় আছে, চাল গুলো উনাকে দিয়ে আসো</t>
@@ -4011,7 +4011,7 @@
     <t>মেয়েটা একদম তার মায়ের মতো হয়েছে</t>
   </si>
   <si>
-    <t>মাইফোয়া একদম ইতির মা'র মতন অইয়্যি</t>
+    <t>মাইফুয়া একদম ইতির মা'র মতন অইয়্যি</t>
   </si>
   <si>
     <t>স্বভাব চরিত্র তো সব তোর ভাইয়ের মতো হয়েছে</t>
@@ -4103,7 +4103,7 @@
     <t>আপনি তো আমার থেকেও আপনার মেয়েকেই বেশি দেখতে পারেন</t>
   </si>
   <si>
-    <t>অঁনে তো আত্তুন ও অঁনোর মাইফোয়ারেই বেশি দেইত ফারন</t>
+    <t>অঁনে তো আত্তুন ও অঁনোর মাইফুয়ারেই বেশি দেইত ফারন</t>
   </si>
   <si>
     <t>আমার কথার তো কোনো গুরুত্ব নেই, আপনি তো আপনার ছেলের কথাই শুনবেন</t>
@@ -4447,7 +4447,7 @@
     <t>আপনার মেয়েকে আমার অনেক ভাল লেগেছে</t>
   </si>
   <si>
-    <t>অঁনোর মাইফোয়ারে আত্তুন বত ভালা লেইজ্ঞি</t>
+    <t>অঁনোর মাইফুয়ারে আত্তুন বত ভালা লেইজ্ঞি</t>
   </si>
   <si>
     <t>এরা দুই ভাই অনেক দুষ্টু</t>
@@ -4675,7 +4675,7 @@
     <t>পাশের বাড়ির মেয়েগুলো প্রতিদিন আমাদের পেয়ারা গাছ থেকে পেয়ারা চুরি করে</t>
   </si>
   <si>
-    <t>পাশোর বারির মাইফোয়া এগুন আঁরো গুয়াসি গাছুত্তুন গুয়াছি চুরি গরে</t>
+    <t>পাশোর বারির মাইফুয়া এগুন আঁরো গুয়াসি গাছুত্তুন গুয়াছি চুরি গরে</t>
   </si>
   <si>
     <t>ওদেরকে একবার আমার বড় আপু অনেক বকা দিয়েছিল</t>
@@ -4993,7 +4993,7 @@
     <t>চাচি, আপনার ছেলে-মেয়ে কয়টা?</t>
   </si>
   <si>
-    <t>চাচি, অঁনোর ফোয়া-মাইফোয়া হওয়ো?</t>
+    <t>চাচি, অঁনোর ফোয়া-মাইফুয়া হওয়ো?</t>
   </si>
   <si>
     <t>এটা এরকম হয়ে যাবে যে সেটা আমি আগে বুঝতে পারিনি</t>
@@ -5342,6 +5342,144 @@
   </si>
   <si>
     <t>তোঁয়ারা ভাই-বইন হতোজন?</t>
+  </si>
+  <si>
+    <t>তোর রেজাল্ট কখন দেবে? পাশ করবি তো এবার?</t>
+  </si>
+  <si>
+    <t>তুর রেজাল্ট হত্তে দিবু? পাশ গরিবিনি এবার?</t>
+  </si>
+  <si>
+    <t>যে পরীক্ষা দিয়েছি, মনে তো হয় না পাশ করব</t>
+  </si>
+  <si>
+    <t>যে পরীক্ষে দিই, মনে তো ন অয় পাশ গইজ্জুম</t>
+  </si>
+  <si>
+    <t>এটা আমার জন্য নিয়েছি, এটা আমি কাউকে দেব না</t>
+  </si>
+  <si>
+    <t>ইবে আঁর লাই লই, ইবে আঁই কিয়ারে দিতাম নো</t>
+  </si>
+  <si>
+    <t>এখন আমার যে ঘুম পাচ্ছে, মনে হচ্ছে না ঘুমালে মাথা ঘুরে পড়ে যাব</t>
+  </si>
+  <si>
+    <t>এহন আত্তুন যে ঘুম পার, মনে অদ্দে ঘুম ন যাইলি মাথা ঘুরি ফরি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>এখন আম্মু বাজারে গেছে আর আমি রান্না করছি</t>
+  </si>
+  <si>
+    <t>এহন আম্মু বাজারুত গেইয়্যি আর আঁই রান্না গরির</t>
+  </si>
+  <si>
+    <t>কিরে, কী হয়েছে তোমার! তুমি কি আমার কোনো কথায় রাগ করেছো?</t>
+  </si>
+  <si>
+    <t>কিরে, কেন অইয়্যিদে তোঁয়াত্তন! তুঁই কি আঁর হনো হতাত গুসসা অইয়্যু?</t>
+  </si>
+  <si>
+    <t>আমি বাজারে যেতে পারব না, আমার অনেক কাজ বাকি আছে</t>
+  </si>
+  <si>
+    <t>আঁই বাজারুত যাইত ন পাইজ্জুম, আত্তুন বত হাম বাকি আছে</t>
+  </si>
+  <si>
+    <t>আর এটা যদি আমি না আনতাম, তাহলে তোমার কষ্ট করে আবার আনতে হতো না?</t>
+  </si>
+  <si>
+    <t>আর ইয়েন যদি আঁই নো আইন্তাম, তইলি তোঁয়াত্তুন হষ্ট গরি আবার আনন ন ফইত্তো?</t>
+  </si>
+  <si>
+    <t>যেন তোমার কষ্ট না হয় সেজন্য আমি নিয়ে আসছি</t>
+  </si>
+  <si>
+    <t>যেন তোঁয়াত্তুন হষ্ট ন আয় এতেল্লে আঁই লই আইসসি</t>
+  </si>
+  <si>
+    <t>দেওয়ালের ওপর কাপড় একটা শুকাতে দিয়েছিলাম, পরে গিয়ে দেখি কেউ ওটা নিচে ফেলে দিয়েছে</t>
+  </si>
+  <si>
+    <t>দেওয়ালুর উদ্দি হর উজ্ঞো ফুয়ত দিলাম, ফরুদ্দি যাই সাইদ্দি হনে ইয়েন নিচে ফেলাই দিইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার মনে হচ্ছে মেয়েটা তোকে যাদু করেছে</t>
+  </si>
+  <si>
+    <t>আত্তুন মনে অদ্দে মাইফুয়া ইবে তুরে যাদু গইজ্জি</t>
+  </si>
+  <si>
+    <t>যদি যাদু না করত, তাহলে তুই এরকম পাগল হয়ে যেতি না</t>
+  </si>
+  <si>
+    <t>যদি যাদু ন গইত্তো, তইলি তুই এল্লেত ফঅল অই ন যাইতি</t>
+  </si>
+  <si>
+    <t>যাদু করে আমার সংসারটা শেষ করে দিছে</t>
+  </si>
+  <si>
+    <t>যাদু গরি আঁর সংসার ইয়েন শেষ গরি দিইয়্যি</t>
+  </si>
+  <si>
+    <t>কেউ আমাদের ওপর যাদু করেছে, না হলে আমাদের মধ্যে এত ঝগড়া কেন হচ্ছে?</t>
+  </si>
+  <si>
+    <t>কিয়াই আঁরার উদ্দি যাদু গইজ্জি, নইলি আঁরার ভিতুর এল্লেত হইজ্জে কা অর?</t>
+  </si>
+  <si>
+    <t>আজকে সেহরি খাওয়ার জন্য উঠতে পারিনি, সেজন্য কিছু না খেয়ে রোজা রেখেছি</t>
+  </si>
+  <si>
+    <t>আজিয়ে সেহেরি হাইবের লাই উডিত ন ফারি, এতেল্লে কিছু ন হাই রোজা রাইক্কি</t>
+  </si>
+  <si>
+    <t>জুতা গুলো যদি না পরিস, তাহলে কাউকে দিয়ে দিতে পারিস না?</t>
+  </si>
+  <si>
+    <t>জুতা এগিন যদি ন ফরুস, তইলি কিয়ারে দিই ফেলাইত ন ফারুস?</t>
+  </si>
+  <si>
+    <t>নিজেও কষ্ট পাচ্ছিস এবং আমাকেও কষ্ট দিচ্ছিস</t>
+  </si>
+  <si>
+    <t>নিজেও হষ্ট ফর আর আঁরেও হষ্ট দর</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে নিজের উপর অনেক রাগ উঠে</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে নিজুর উদ্দি বত গুসসা উডে</t>
+  </si>
+  <si>
+    <t>মশা কতগুলো আজকে বেশি জালাচ্ছে</t>
+  </si>
+  <si>
+    <t>মুশা হদুজ্ঞুন আজিয়ে বেশি জালার</t>
+  </si>
+  <si>
+    <t>ভাত খাওয়ার পর তরকারিগুলো গরম করে রাখিও, না হলে নষ্ট হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>ভাত হাইবের পর তারহারি এগিন গরম গরি রাইক্কো, নইলি নষ্ট অই যাইবু</t>
+  </si>
+  <si>
+    <t>প্রতিদিন সকালে উঠে চিন্তা করি যে আজকে সারাদিন অনেক কাজ করব, কিন্তু কাজের কাজ কিছুই হয় না</t>
+  </si>
+  <si>
+    <t>ফইত্তুদিন বেইন্নে উডি চিন্তে গরিদি আজিয়ে আরাদিন বত হাম গইজ্জুম, কিন্তু হাজুর হজ কিছুই ন অয়</t>
+  </si>
+  <si>
+    <t>মামুন ওখানে কি করছে সেটা তো আমি জানি না</t>
+  </si>
+  <si>
+    <t>মামুন অনডে কি গরের ইয়েন তো আঁই ন জানি</t>
+  </si>
+  <si>
+    <t>ওকে বলেছিলাম আমার সাথে চলে আসার জন্য, কিন্তু আসেনি</t>
+  </si>
+  <si>
+    <t>ইতেরে হইলাম দে আঁর ফুয়ারে চলি আইবের লাই, কিন্তু নো আইয়্যি</t>
   </si>
 </sst>
 </file>
@@ -13487,96 +13625,188 @@
       </c>
     </row>
     <row r="872" ht="25" customHeight="1" spans="1:2">
-      <c r="A872" s="2"/>
-      <c r="B872" s="2"/>
+      <c r="A872" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>1738</v>
+      </c>
     </row>
     <row r="873" ht="25" customHeight="1" spans="1:2">
-      <c r="A873" s="2"/>
-      <c r="B873" s="2"/>
+      <c r="A873" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>1740</v>
+      </c>
     </row>
     <row r="874" ht="25" customHeight="1" spans="1:2">
-      <c r="A874" s="2"/>
-      <c r="B874" s="2"/>
+      <c r="A874" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>1742</v>
+      </c>
     </row>
     <row r="875" ht="25" customHeight="1" spans="1:2">
-      <c r="A875" s="2"/>
-      <c r="B875" s="2"/>
+      <c r="A875" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>1744</v>
+      </c>
     </row>
     <row r="876" ht="25" customHeight="1" spans="1:2">
-      <c r="A876" s="2"/>
-      <c r="B876" s="2"/>
+      <c r="A876" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>1746</v>
+      </c>
     </row>
     <row r="877" ht="25" customHeight="1" spans="1:2">
-      <c r="A877" s="2"/>
-      <c r="B877" s="2"/>
+      <c r="A877" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>1748</v>
+      </c>
     </row>
     <row r="878" ht="25" customHeight="1" spans="1:2">
-      <c r="A878" s="2"/>
-      <c r="B878" s="2"/>
+      <c r="A878" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>1750</v>
+      </c>
     </row>
     <row r="879" ht="25" customHeight="1" spans="1:2">
-      <c r="A879" s="2"/>
-      <c r="B879" s="2"/>
+      <c r="A879" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>1752</v>
+      </c>
     </row>
     <row r="880" ht="25" customHeight="1" spans="1:2">
-      <c r="A880" s="2"/>
-      <c r="B880" s="2"/>
+      <c r="A880" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>1754</v>
+      </c>
     </row>
     <row r="881" ht="25" customHeight="1" spans="1:2">
-      <c r="A881" s="2"/>
-      <c r="B881" s="2"/>
+      <c r="A881" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>1756</v>
+      </c>
     </row>
     <row r="882" ht="25" customHeight="1" spans="1:2">
-      <c r="A882" s="2"/>
-      <c r="B882" s="2"/>
+      <c r="A882" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>1758</v>
+      </c>
     </row>
     <row r="883" ht="25" customHeight="1" spans="1:2">
-      <c r="A883" s="2"/>
-      <c r="B883" s="2"/>
+      <c r="A883" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>1760</v>
+      </c>
     </row>
     <row r="884" ht="25" customHeight="1" spans="1:2">
-      <c r="A884" s="2"/>
-      <c r="B884" s="2"/>
+      <c r="A884" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>1762</v>
+      </c>
     </row>
     <row r="885" ht="25" customHeight="1" spans="1:2">
-      <c r="A885" s="2"/>
-      <c r="B885" s="2"/>
+      <c r="A885" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>1764</v>
+      </c>
     </row>
     <row r="886" ht="25" customHeight="1" spans="1:2">
-      <c r="A886" s="2"/>
-      <c r="B886" s="2"/>
+      <c r="A886" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>1766</v>
+      </c>
     </row>
     <row r="887" ht="25" customHeight="1" spans="1:2">
-      <c r="A887" s="2"/>
-      <c r="B887" s="2"/>
+      <c r="A887" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>1768</v>
+      </c>
     </row>
     <row r="888" ht="25" customHeight="1" spans="1:2">
-      <c r="A888" s="2"/>
-      <c r="B888" s="2"/>
+      <c r="A888" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>1770</v>
+      </c>
     </row>
     <row r="889" ht="25" customHeight="1" spans="1:2">
-      <c r="A889" s="2"/>
-      <c r="B889" s="2"/>
+      <c r="A889" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>1772</v>
+      </c>
     </row>
     <row r="890" ht="25" customHeight="1" spans="1:2">
-      <c r="A890" s="2"/>
-      <c r="B890" s="2"/>
+      <c r="A890" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>1774</v>
+      </c>
     </row>
     <row r="891" ht="25" customHeight="1" spans="1:2">
-      <c r="A891" s="2"/>
-      <c r="B891" s="2"/>
+      <c r="A891" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>1776</v>
+      </c>
     </row>
     <row r="892" ht="25" customHeight="1" spans="1:2">
-      <c r="A892" s="2"/>
-      <c r="B892" s="2"/>
+      <c r="A892" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>1778</v>
+      </c>
     </row>
     <row r="893" ht="25" customHeight="1" spans="1:2">
-      <c r="A893" s="2"/>
-      <c r="B893" s="2"/>
+      <c r="A893" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>1780</v>
+      </c>
     </row>
     <row r="894" ht="25" customHeight="1" spans="1:2">
-      <c r="A894" s="2"/>
-      <c r="B894" s="2"/>
+      <c r="A894" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>1782</v>
+      </c>
     </row>
     <row r="895" ht="25" customHeight="1" spans="1:2">
       <c r="A895" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="1783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="1841">
   <si>
     <t>bangla</t>
   </si>
@@ -5480,6 +5480,180 @@
   </si>
   <si>
     <t>ইতেরে হইলাম দে আঁর ফুয়ারে চলি আইবের লাই, কিন্তু নো আইয়্যি</t>
+  </si>
+  <si>
+    <t>সকালে পান্তা ভাত খেয়ে একটু ঘুমিয়েছিলাম, কখন যে দুপুর হয়ে গেল বুঝতেই পারলাম না</t>
+  </si>
+  <si>
+    <t>বেইন্নে পানি ভাত হাইয়্যিরে এক্কানা ঘুম গেইলাম, হত্তে যে দুইজ্জে অই গেইয়্যি বুঝিত ন ফারি</t>
+  </si>
+  <si>
+    <t>গ্যাস শেষ হয়ে গেছে, তাই এখন মাটির চুলায় রান্না করতে হবে</t>
+  </si>
+  <si>
+    <t>গ্যাস শেষ অই গেইয়্যি, এতেল্লে এহন মেডির চুলোত রান্না গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>তোদের দুজনের মধ্যে কী সমস্যা, সবসময় ঝগড়া কেন করিস?</t>
+  </si>
+  <si>
+    <t>তুরা দুনুজনুর মাঝে কী সমাস্যা, সবসময় হইজ্জে কা গরস?</t>
+  </si>
+  <si>
+    <t>আপু, তোমার বাচ্চা পায়খানা করে দিয়েছে</t>
+  </si>
+  <si>
+    <t>আফা, তোঁয়ার ফুয়া ফেহেনা গরি দিইয়্যি</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় নাকি তুই বিছানায় প্রস্রাব করে দিতি?</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে বলে তুই বিছেনুত মুতি দিতি?</t>
+  </si>
+  <si>
+    <t>এই বিড়ালটা ঘরের ভেতর পায়খানা করে দিয়েছে</t>
+  </si>
+  <si>
+    <t>এই বিলে ইবে ঘরুর ভিতুর ফেহেনা গরি দিইয়্যি</t>
+  </si>
+  <si>
+    <t>পায়খানাগুলো তাড়াতাড়ি পরিষ্কার করে ফেল, আমার বমি আসছে</t>
+  </si>
+  <si>
+    <t>ফেহেনা এগিন তারাতারি সাফ গরি ফেলা, আত্তুন বুমি আইয়্যির</t>
+  </si>
+  <si>
+    <t>কাপড় এটার দাম কত ভাই?</t>
+  </si>
+  <si>
+    <t>হর ইবের দাম হত বদ্দা?</t>
+  </si>
+  <si>
+    <t>কাপড় এটার দাম বেশি, আমি নিব না এটা</t>
+  </si>
+  <si>
+    <t>হর ইবের দাম বেশি, আঁই লইতাম নো ইবে</t>
+  </si>
+  <si>
+    <t>দাম বেশি কম বলেছেন ভাই</t>
+  </si>
+  <si>
+    <t>দাম বেশি হম হইয়্যুন বদ্দা</t>
+  </si>
+  <si>
+    <t>তোর আপুর জন্য একটা শাড়ি কিনেছি, পছন্দ হয় কিনা দেখ</t>
+  </si>
+  <si>
+    <t>তুর আফার লাই এক্কান শারি কিন্নি, পছন্দ অয় না চা</t>
+  </si>
+  <si>
+    <t>এই দোকানের কাপড়গুলো অনেক দামি, আমরা অন্য দোকানে দেখি</t>
+  </si>
+  <si>
+    <t>এই দোয়ানুর হর এগিন বত দামি, আঁরা অন্য দোয়ানুত চাই</t>
+  </si>
+  <si>
+    <t>কাপড় আর ইফতারিগুলো নিয়ে তোর আপুর ওখানে দিয়ে আয়</t>
+  </si>
+  <si>
+    <t>হর আর ইফতেরি এগিন লই তুর আফার এনডে দি আয়</t>
+  </si>
+  <si>
+    <t>সব কিনেছি, কিন্তু এখনো জুতা কিনিনি</t>
+  </si>
+  <si>
+    <t>বিয়াক কিন্নি, কিন্তু এহনো জুতা ন কিনি</t>
+  </si>
+  <si>
+    <t>২০০ টাকার জুতা, বলছে ৬০০ টাকা!</t>
+  </si>
+  <si>
+    <t>২০০ টিয়ার জুতা, হদ্দে ৬০০ টিয়া</t>
+  </si>
+  <si>
+    <t>একদাম ৫০০ টাকা রাখব, এর থেকে কমাতে পারব না</t>
+  </si>
+  <si>
+    <t>একদাম ৫০০ টিয়া রাইক্কুম, ইয়াত্তুন হমাইত ন ফাইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমি ৩০০ টাকা দিব, যদি পারেন দিয়ে দেন</t>
+  </si>
+  <si>
+    <t>আঁই ৩০০ টিয়া দিইয়্যুম, যদি ফারো দিই দন</t>
+  </si>
+  <si>
+    <t>পুরো মার্কেট ঘুরেছি, কিন্তু পছন্দের একটা কাপড়ও পাই নাই</t>
+  </si>
+  <si>
+    <t>পুরো মার্কেট ঘুইজ্জি, কিন্তু পছন্দর উজ্ঞো হর অ নো পাই</t>
+  </si>
+  <si>
+    <t>মার্কেটে জিনিসপত্রের দাম আগুনের মতো</t>
+  </si>
+  <si>
+    <t>মার্কেটুত জিনিসপত্রর দাম অইনুর মতন</t>
+  </si>
+  <si>
+    <t>এবার ঈদের বাজার জহুর মার্কেট থেকে করব, ওখানে জিনিস একটু সস্তা দামে পাওয়া যায়</t>
+  </si>
+  <si>
+    <t>এবার ঈদুর বাজার জহুর মার্কেটুত্তুন গইজ্জুম, এনডে জিনিস এক্কানা অস্তা দামে পা যায়</t>
+  </si>
+  <si>
+    <t>বালি আর্কেডে যাব না এবার, গত বছর পাঞ্জাবি একটা নিয়ে ঠকেছি ওখান থেকে</t>
+  </si>
+  <si>
+    <t>বালি আর্কেডুত যাইতাম ন এবার, গত বছর পাঞ্জাবি উজ্ঞো লই ঠইক্কিলাম এত্তুন</t>
+  </si>
+  <si>
+    <t>এত দামাদামি না করে ৫০০ টাকা রাখব কাপড়টা, নিয়ে নিন</t>
+  </si>
+  <si>
+    <t>এল্লেত দামাদামি ন গরি ৫০০ টিয়া রাইক্কুম হর ইবে, লই লন</t>
+  </si>
+  <si>
+    <t>আলিয়ার জুতাগুলো ছোট হয়েছে, ওগুলো পরিবর্তন করে আনতে হবে</t>
+  </si>
+  <si>
+    <t>আলিয়ার জুতা এগিন ছুডো অইয়্যি, এগিন বদলাই আনন ফরিবু</t>
+  </si>
+  <si>
+    <t>দোকানের নামটা আমার মনে পড়ছে না এই মুহূর্তে</t>
+  </si>
+  <si>
+    <t>দোয়ানুর নাম ইয়েন আত্তুন মনোত ন ফরের এই মুহূর্তত</t>
+  </si>
+  <si>
+    <t>আমি আর করিম মার্কেটে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই আর করিম মার্কেটুত যাইর</t>
+  </si>
+  <si>
+    <t>এক কেজি গাজরের দাম কত?</t>
+  </si>
+  <si>
+    <t>এক কেজি গাজরুর দাম হত?</t>
+  </si>
+  <si>
+    <t>শসাগুলোর দাম বেশি বলেছেন, আরেকটু কমিয়ে রাখেন</t>
+  </si>
+  <si>
+    <t>শসা এগুনুর দাম বেশি হইতে হইয়্যুন, আরেক্কানা হমাই রাহন</t>
+  </si>
+  <si>
+    <t>মেয়েদের সাথে মার্কেটে গেলে সারাদিন ঘুরতে হয়</t>
+  </si>
+  <si>
+    <t>আমি সহজে মেয়েদের সাথে মার্কেটে যেতে চাই না</t>
+  </si>
+  <si>
+    <t>একবার আপুদের সাথে মার্কেটে গিয়েছিলাম, সারাদিন হাটতে হাটতে আমার পা ব্যথা হয়ে গিয়েছিল সেদিন</t>
+  </si>
+  <si>
+    <t>হকার মার্কেটে অনেক জ্যাম, মানুষের ধাক্কাধাক্কির জন্য হাটা যাচ্ছিল না</t>
   </si>
 </sst>
 </file>
@@ -13809,127 +13983,243 @@
       </c>
     </row>
     <row r="895" ht="25" customHeight="1" spans="1:2">
-      <c r="A895" s="2"/>
-      <c r="B895" s="2"/>
+      <c r="A895" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>1784</v>
+      </c>
     </row>
     <row r="896" ht="25" customHeight="1" spans="1:2">
-      <c r="A896" s="2"/>
-      <c r="B896" s="2"/>
+      <c r="A896" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>1786</v>
+      </c>
     </row>
     <row r="897" ht="25" customHeight="1" spans="1:2">
-      <c r="A897" s="2"/>
-      <c r="B897" s="2"/>
+      <c r="A897" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>1788</v>
+      </c>
     </row>
     <row r="898" ht="25" customHeight="1" spans="1:2">
-      <c r="A898" s="2"/>
-      <c r="B898" s="2"/>
+      <c r="A898" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>1790</v>
+      </c>
     </row>
     <row r="899" ht="25" customHeight="1" spans="1:2">
-      <c r="A899" s="2"/>
-      <c r="B899" s="2"/>
+      <c r="A899" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>1792</v>
+      </c>
     </row>
     <row r="900" ht="25" customHeight="1" spans="1:2">
-      <c r="A900" s="2"/>
-      <c r="B900" s="2"/>
+      <c r="A900" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>1794</v>
+      </c>
     </row>
     <row r="901" ht="25" customHeight="1" spans="1:2">
-      <c r="A901" s="2"/>
-      <c r="B901" s="2"/>
+      <c r="A901" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>1796</v>
+      </c>
     </row>
     <row r="902" ht="25" customHeight="1" spans="1:2">
-      <c r="A902" s="2"/>
-      <c r="B902" s="2"/>
+      <c r="A902" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>1798</v>
+      </c>
     </row>
     <row r="903" ht="25" customHeight="1" spans="1:2">
-      <c r="A903" s="2"/>
-      <c r="B903" s="2"/>
+      <c r="A903" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>1800</v>
+      </c>
     </row>
     <row r="904" ht="25" customHeight="1" spans="1:2">
-      <c r="A904" s="2"/>
-      <c r="B904" s="2"/>
+      <c r="A904" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>1802</v>
+      </c>
     </row>
     <row r="905" ht="25" customHeight="1" spans="1:2">
-      <c r="A905" s="2"/>
-      <c r="B905" s="2"/>
+      <c r="A905" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>1804</v>
+      </c>
     </row>
     <row r="906" ht="25" customHeight="1" spans="1:2">
-      <c r="A906" s="2"/>
-      <c r="B906" s="2"/>
+      <c r="A906" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>1806</v>
+      </c>
     </row>
     <row r="907" ht="25" customHeight="1" spans="1:2">
-      <c r="A907" s="2"/>
-      <c r="B907" s="2"/>
+      <c r="A907" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>1808</v>
+      </c>
     </row>
     <row r="908" ht="25" customHeight="1" spans="1:2">
-      <c r="A908" s="2"/>
-      <c r="B908" s="2"/>
+      <c r="A908" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>1810</v>
+      </c>
     </row>
     <row r="909" ht="25" customHeight="1" spans="1:2">
-      <c r="A909" s="2"/>
-      <c r="B909" s="2"/>
+      <c r="A909" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>1812</v>
+      </c>
     </row>
     <row r="910" ht="25" customHeight="1" spans="1:2">
-      <c r="A910" s="2"/>
-      <c r="B910" s="2"/>
+      <c r="A910" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>1814</v>
+      </c>
     </row>
     <row r="911" ht="25" customHeight="1" spans="1:2">
-      <c r="A911" s="2"/>
-      <c r="B911" s="2"/>
+      <c r="A911" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>1816</v>
+      </c>
     </row>
     <row r="912" ht="25" customHeight="1" spans="1:2">
-      <c r="A912" s="2"/>
-      <c r="B912" s="2"/>
+      <c r="A912" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>1818</v>
+      </c>
     </row>
     <row r="913" ht="25" customHeight="1" spans="1:2">
-      <c r="A913" s="2"/>
-      <c r="B913" s="2"/>
+      <c r="A913" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>1820</v>
+      </c>
     </row>
     <row r="914" ht="25" customHeight="1" spans="1:2">
-      <c r="A914" s="2"/>
-      <c r="B914" s="2"/>
+      <c r="A914" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>1822</v>
+      </c>
     </row>
     <row r="915" ht="25" customHeight="1" spans="1:2">
-      <c r="A915" s="2"/>
-      <c r="B915" s="2"/>
+      <c r="A915" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>1824</v>
+      </c>
     </row>
     <row r="916" ht="25" customHeight="1" spans="1:2">
-      <c r="A916" s="2"/>
-      <c r="B916" s="2"/>
+      <c r="A916" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>1826</v>
+      </c>
     </row>
     <row r="917" ht="25" customHeight="1" spans="1:2">
-      <c r="A917" s="2"/>
-      <c r="B917" s="2"/>
+      <c r="A917" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>1828</v>
+      </c>
     </row>
     <row r="918" ht="25" customHeight="1" spans="1:2">
-      <c r="A918" s="2"/>
-      <c r="B918" s="2"/>
+      <c r="A918" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>1830</v>
+      </c>
     </row>
     <row r="919" ht="25" customHeight="1" spans="1:2">
-      <c r="A919" s="2"/>
-      <c r="B919" s="2"/>
+      <c r="A919" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>1832</v>
+      </c>
     </row>
     <row r="920" ht="25" customHeight="1" spans="1:2">
-      <c r="A920" s="2"/>
-      <c r="B920" s="2"/>
+      <c r="A920" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>1834</v>
+      </c>
     </row>
     <row r="921" ht="25" customHeight="1" spans="1:2">
-      <c r="A921" s="2"/>
-      <c r="B921" s="2"/>
+      <c r="A921" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>1836</v>
+      </c>
     </row>
     <row r="922" ht="25" customHeight="1" spans="1:2">
-      <c r="A922" s="2"/>
+      <c r="A922" s="2" t="s">
+        <v>1837</v>
+      </c>
       <c r="B922" s="2"/>
     </row>
     <row r="923" ht="25" customHeight="1" spans="1:2">
-      <c r="A923" s="2"/>
+      <c r="A923" s="2" t="s">
+        <v>1838</v>
+      </c>
       <c r="B923" s="2"/>
     </row>
     <row r="924" ht="25" customHeight="1" spans="1:2">
-      <c r="A924" s="2"/>
+      <c r="A924" s="2" t="s">
+        <v>1839</v>
+      </c>
       <c r="B924" s="2"/>
     </row>
     <row r="925" ht="25" customHeight="1" spans="1:2">
-      <c r="A925" s="2"/>
+      <c r="A925" s="2" t="s">
+        <v>1840</v>
+      </c>
       <c r="B925" s="2"/>
     </row>
     <row r="926" ht="25" customHeight="1" spans="1:2">

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="1841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="1877">
   <si>
     <t>bangla</t>
   </si>
@@ -5647,13 +5647,121 @@
     <t>মেয়েদের সাথে মার্কেটে গেলে সারাদিন ঘুরতে হয়</t>
   </si>
   <si>
-    <t>আমি সহজে মেয়েদের সাথে মার্কেটে যেতে চাই না</t>
-  </si>
-  <si>
-    <t>একবার আপুদের সাথে মার্কেটে গিয়েছিলাম, সারাদিন হাটতে হাটতে আমার পা ব্যথা হয়ে গিয়েছিল সেদিন</t>
-  </si>
-  <si>
-    <t>হকার মার্কেটে অনেক জ্যাম, মানুষের ধাক্কাধাক্কির জন্য হাটা যাচ্ছিল না</t>
+    <t>মাইফুয়ার লগে  মার্কেটুত গেলি আরাদিন ঘুরন ফরে</t>
+  </si>
+  <si>
+    <t>আমি সহজে মেয়েদের সাথে মার্কেটে যেতে চাই না</t>
+  </si>
+  <si>
+    <t>আঁই সহজে মাইফুয়ার লগে মার্কেটুত যাইতাম ন চাই</t>
+  </si>
+  <si>
+    <t>একবার আপুদের সাথে মার্কেটে গিয়েছিলাম, সারাদিন হাঁটতে হাঁটতে আমার পা ব্যথা হয়ে গিয়েছিল সেদিন।</t>
+  </si>
+  <si>
+    <t>একবার আফা তারার লগে মার্কেটুত গেইলাম, আরাদিন আটতে আটতে আঁর টেং বিশ অই গেইয়্যিল এদিন্নে</t>
+  </si>
+  <si>
+    <t>হকার মার্কেটে অনেক জ্যাম, মানুষের ধাক্কাধাক্কির জন্য হাঁটা যাচ্ছিল না</t>
+  </si>
+  <si>
+    <t>হকার মার্কেটুত বত জাম, মানুষুর ডেক্কাডেক্কির লাই আডন ন যার</t>
+  </si>
+  <si>
+    <t>আপুরা এইদিকে আসেন, ভালো কাপড় সবগুলো এইদিকে</t>
+  </si>
+  <si>
+    <t>আফা তারা ইক্কে আইয়্যুন, ভালা হর বিয়াজ্ঞিন ইনদি</t>
+  </si>
+  <si>
+    <t>দুইটা কিনলে সাথে একটা ফ্রি</t>
+  </si>
+  <si>
+    <t>দুওয়ো কিনিলি লগে উজ্ঞো ফ্রি</t>
+  </si>
+  <si>
+    <t>মার্কেটের সব দোকানের চেয়ে আমরা সবচেয়ে সস্তায় দিচ্ছি</t>
+  </si>
+  <si>
+    <t>মার্কেটর বিয়াক দোয়ানুত্তুন আঁরা বিয়াজ্ঞুনুত্তুন অস্তা দির</t>
+  </si>
+  <si>
+    <t>আমার হলুদ রঙের কাপড় ভালো লাগে না</t>
+  </si>
+  <si>
+    <t>আত্তুন অলিদ্দে কালারুর হর গম ন লাগে</t>
+  </si>
+  <si>
+    <t>তোমাকে সবুজ রঙের কাপড়ে অনেক মানাবে</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে সবুজ রঙুর হরে বত মানাইবু</t>
+  </si>
+  <si>
+    <t>সাদা রঙের পাঞ্জাবিতে শুধু দাগ লেগে যায়</t>
+  </si>
+  <si>
+    <t>সাদা রঙুর পাঞ্জাবিত উদো দাগ লাগি যায়</t>
+  </si>
+  <si>
+    <t>দাম এত বেশি কেন বলছো? আরেকটু কমিয়ে রাখো</t>
+  </si>
+  <si>
+    <t>দাম এল্লেত বেশি কা হর? আরেক্কানা হমাই রাহো</t>
+  </si>
+  <si>
+    <t>দেখে দেখে নেন, বেছে বেছে নেন, একদাম ২০০ টাকা</t>
+  </si>
+  <si>
+    <t>সাই সাই লন, বাছি বাছি লন, একদাম ২০০ টিয়া</t>
+  </si>
+  <si>
+    <t>দেরি করলে আর পাবেন না, শেষ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>দেরি গরিলি আর ন ফাইবেন, শেষ অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমার থেকে একবার নিলে বারবার নিতে মন চাইবে</t>
+  </si>
+  <si>
+    <t>আত্তুন একবার লইলি বারবার লইতু মন চাইবু</t>
+  </si>
+  <si>
+    <t>দোকান আরেকটায় দেখেছি দাম অনেক কম, তুমি এত বেশি কেন নিচ্ছো?</t>
+  </si>
+  <si>
+    <t>দোয়ান আরেক্কান উত চাইলাম দাম বত হম, তুঁই এল্লেত বেশি কা লর?</t>
+  </si>
+  <si>
+    <t>এগুলো তো ভাই সব পুরাতন মডেলের শার্ট</t>
+  </si>
+  <si>
+    <t>এগুন তো বদ্দা ফুরন মডেলুর শার্ট</t>
+  </si>
+  <si>
+    <t>একটা ভালো কোয়ালিটির প্যান্ট দেখান</t>
+  </si>
+  <si>
+    <t>উজ্ঞো ভালা কোয়ালিটির ফেন দেহন</t>
+  </si>
+  <si>
+    <t>আমার ছেলের জন্য একটা জামা নিয়েছিলাম, কিন্তু ওটা ছোট হচ্ছে</t>
+  </si>
+  <si>
+    <t>আঁর ফুয়ার লাই উজ্ঞো হুত্তা লইলাম, কিন্তু ইবে ছোড অর</t>
+  </si>
+  <si>
+    <t>ফুল হাতা গেঞ্জিগুলো ভাঁজ করে রাখো</t>
+  </si>
+  <si>
+    <t>ফুল আতা গেঞ্জি এগুন ভাঁজ গরি রাহো</t>
+  </si>
+  <si>
+    <t>মেয়েটা হাত মোজা পড়েছিল</t>
+  </si>
+  <si>
+    <t>মাইফুয়া ইবে আত মৌজো ফইজ্জিল</t>
   </si>
 </sst>
 </file>
@@ -14202,89 +14310,161 @@
       <c r="A922" s="2" t="s">
         <v>1837</v>
       </c>
-      <c r="B922" s="2"/>
+      <c r="B922" s="2" t="s">
+        <v>1838</v>
+      </c>
     </row>
     <row r="923" ht="25" customHeight="1" spans="1:2">
       <c r="A923" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B923" s="2"/>
+        <v>1839</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>1840</v>
+      </c>
     </row>
     <row r="924" ht="25" customHeight="1" spans="1:2">
       <c r="A924" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="B924" s="2"/>
+        <v>1841</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>1842</v>
+      </c>
     </row>
     <row r="925" ht="25" customHeight="1" spans="1:2">
       <c r="A925" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B925" s="2"/>
+        <v>1843</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>1844</v>
+      </c>
     </row>
     <row r="926" ht="25" customHeight="1" spans="1:2">
-      <c r="A926" s="2"/>
-      <c r="B926" s="2"/>
+      <c r="A926" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>1846</v>
+      </c>
     </row>
     <row r="927" ht="25" customHeight="1" spans="1:2">
-      <c r="A927" s="2"/>
-      <c r="B927" s="2"/>
+      <c r="A927" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>1848</v>
+      </c>
     </row>
     <row r="928" ht="25" customHeight="1" spans="1:2">
-      <c r="A928" s="2"/>
-      <c r="B928" s="2"/>
+      <c r="A928" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>1850</v>
+      </c>
     </row>
     <row r="929" ht="25" customHeight="1" spans="1:2">
-      <c r="A929" s="2"/>
-      <c r="B929" s="2"/>
+      <c r="A929" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>1852</v>
+      </c>
     </row>
     <row r="930" ht="25" customHeight="1" spans="1:2">
-      <c r="A930" s="2"/>
-      <c r="B930" s="2"/>
+      <c r="A930" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>1854</v>
+      </c>
     </row>
     <row r="931" ht="25" customHeight="1" spans="1:2">
-      <c r="A931" s="2"/>
-      <c r="B931" s="2"/>
+      <c r="A931" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>1856</v>
+      </c>
     </row>
     <row r="932" ht="25" customHeight="1" spans="1:2">
-      <c r="A932" s="2"/>
-      <c r="B932" s="2"/>
+      <c r="A932" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>1858</v>
+      </c>
     </row>
     <row r="933" ht="25" customHeight="1" spans="1:2">
-      <c r="A933" s="2"/>
-      <c r="B933" s="2"/>
+      <c r="A933" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B933" s="2" t="s">
+        <v>1860</v>
+      </c>
     </row>
     <row r="934" ht="25" customHeight="1" spans="1:2">
-      <c r="A934" s="2"/>
-      <c r="B934" s="2"/>
+      <c r="A934" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>1862</v>
+      </c>
     </row>
     <row r="935" ht="25" customHeight="1" spans="1:2">
-      <c r="A935" s="2"/>
-      <c r="B935" s="2"/>
+      <c r="A935" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>1864</v>
+      </c>
     </row>
     <row r="936" ht="25" customHeight="1" spans="1:2">
-      <c r="A936" s="2"/>
-      <c r="B936" s="2"/>
+      <c r="A936" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>1866</v>
+      </c>
     </row>
     <row r="937" ht="25" customHeight="1" spans="1:2">
-      <c r="A937" s="2"/>
-      <c r="B937" s="2"/>
+      <c r="A937" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>1868</v>
+      </c>
     </row>
     <row r="938" ht="25" customHeight="1" spans="1:2">
-      <c r="A938" s="2"/>
-      <c r="B938" s="2"/>
+      <c r="A938" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>1870</v>
+      </c>
     </row>
     <row r="939" ht="25" customHeight="1" spans="1:2">
-      <c r="A939" s="2"/>
-      <c r="B939" s="2"/>
+      <c r="A939" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>1872</v>
+      </c>
     </row>
     <row r="940" ht="25" customHeight="1" spans="1:2">
-      <c r="A940" s="2"/>
-      <c r="B940" s="2"/>
+      <c r="A940" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>1874</v>
+      </c>
     </row>
     <row r="941" ht="25" customHeight="1" spans="1:2">
-      <c r="A941" s="2"/>
-      <c r="B941" s="2"/>
+      <c r="A941" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>1876</v>
+      </c>
     </row>
     <row r="942" ht="25" customHeight="1" spans="1:2">
       <c r="A942" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="1877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="1891">
   <si>
     <t>bangla</t>
   </si>
@@ -5762,6 +5762,48 @@
   </si>
   <si>
     <t>মাইফুয়া ইবে আত মৌজো ফইজ্জিল</t>
+  </si>
+  <si>
+    <t>প্যান্টটা আমার লম্বা হবে</t>
+  </si>
+  <si>
+    <t>ফেন ইবে আত্তুন লাম্বা অইবু</t>
+  </si>
+  <si>
+    <t>আমাদের এখানে অনেক বড় একটা মার্কেট খুলেছে</t>
+  </si>
+  <si>
+    <t>আঁরার এনডে বত বরো উজ্ঞো মার্কেট খুইল্লি</t>
+  </si>
+  <si>
+    <t>তোমাকে আর কোনো টাকা দেব না আমি, তুমি শপিং করে করে সব টাকা শেষ করে ফেলো</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে আর হনো টিয়া দিতাম ন আঁই, তুঁই শপিং গরি গরি বিয়াক টিয়া শেষ গরি ফেলো</t>
+  </si>
+  <si>
+    <t>শুধু শপিং করলে তো হবে না, ঘরে মাছ-মাংস কিছু নেই</t>
+  </si>
+  <si>
+    <t>উদো শপিং গরিলি তো ন অইবু, ঘরোত মাছ-গুস্ত কিছু নেই</t>
+  </si>
+  <si>
+    <t>লাউটা কচি আছে, এটা দাও আমাকে</t>
+  </si>
+  <si>
+    <t>হদু ইবে হরা আছে, ইবে দও আঁরে</t>
+  </si>
+  <si>
+    <t>ছোলার ডাল আর আনিও না, খেয়ে আমার পেট খারাপ হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>চনাড্ডেইল আর ন আইন্নো, হাইয়্যিরে আঁর পেট হারাফ অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বাজারে কি কোনো ভালো মাছ ওঠেনি? পচা মাছ কতগুলো কেন নিয়ে এসেছেন?</t>
+  </si>
+  <si>
+    <t>বাজারুত কি হনো ভালা মাছ ন উডে? পুচা মাছ হদুজ্ঞুন কিল্লে লই আইসসুন?</t>
   </si>
 </sst>
 </file>
@@ -14467,32 +14509,60 @@
       </c>
     </row>
     <row r="942" ht="25" customHeight="1" spans="1:2">
-      <c r="A942" s="2"/>
-      <c r="B942" s="2"/>
+      <c r="A942" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>1878</v>
+      </c>
     </row>
     <row r="943" ht="25" customHeight="1" spans="1:2">
-      <c r="A943" s="2"/>
-      <c r="B943" s="2"/>
+      <c r="A943" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>1880</v>
+      </c>
     </row>
     <row r="944" ht="25" customHeight="1" spans="1:2">
-      <c r="A944" s="2"/>
-      <c r="B944" s="2"/>
+      <c r="A944" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>1882</v>
+      </c>
     </row>
     <row r="945" ht="25" customHeight="1" spans="1:2">
-      <c r="A945" s="2"/>
-      <c r="B945" s="2"/>
+      <c r="A945" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B945" s="2" t="s">
+        <v>1884</v>
+      </c>
     </row>
     <row r="946" ht="25" customHeight="1" spans="1:2">
-      <c r="A946" s="2"/>
-      <c r="B946" s="2"/>
+      <c r="A946" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>1886</v>
+      </c>
     </row>
     <row r="947" ht="25" customHeight="1" spans="1:2">
-      <c r="A947" s="2"/>
-      <c r="B947" s="2"/>
+      <c r="A947" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>1888</v>
+      </c>
     </row>
     <row r="948" ht="25" customHeight="1" spans="1:2">
-      <c r="A948" s="2"/>
-      <c r="B948" s="2"/>
+      <c r="A948" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>1890</v>
+      </c>
     </row>
     <row r="949" ht="25" customHeight="1" spans="1:2">
       <c r="A949" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="1936">
   <si>
     <t>bangla</t>
   </si>
@@ -5804,6 +5804,141 @@
   </si>
   <si>
     <t>বাজারুত কি হনো ভালা মাছ ন উডে? পুচা মাছ হদুজ্ঞুন কিল্লে লই আইসসুন?</t>
+  </si>
+  <si>
+    <t>এটা কি একদাম, নাকি কম হবে?</t>
+  </si>
+  <si>
+    <t>ইবে কি একদাম, নাকি হম অইবু?</t>
+  </si>
+  <si>
+    <t>একদাম বলে বলে বেশি নিচ্ছেন, আমি নেব না আপনার দোকান থেকে</t>
+  </si>
+  <si>
+    <t>একদাম হই হই বেশি লইতে লাইজ্ঞুন, আঁই লইতাম ন অঁনোর দোয়ানুত্তুন</t>
+  </si>
+  <si>
+    <t>এই দোকান থেকে না নিয়ে সামনের দোকান থেকে নিলে ভাল হবে</t>
+  </si>
+  <si>
+    <t>এই দোয়ান ইয়েনুত্তুন ন লইয়্যিরে সামনুর দোয়ানুত্তুন লইলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>ঠিক আছে, এটা প্যাকেট করে দেন</t>
+  </si>
+  <si>
+    <t>ঠিক আছে, ইবে প্যাকেট গরি দন</t>
+  </si>
+  <si>
+    <t>কাপড় এটা তো ধোয়ার পরে রঙ উঠে যাবে</t>
+  </si>
+  <si>
+    <t>শাড়ি এটার কাপড় ভাল হবে মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>আপনি যে দাম বলেছেন, আমার মুখ দিয়ে তো আর কথা বের হচ্ছেনা</t>
+  </si>
+  <si>
+    <t>আগে যে শাড়িটা নিয়েছিলাম ওটার মতো আরেকটা শাড়ি দাও</t>
+  </si>
+  <si>
+    <t>আমি সবসময় তোমার দোকান থেকে কাপড় নি, এবার দাম কম রাখতে হবে</t>
+  </si>
+  <si>
+    <t>এবার রমজানে পিয়াজের দাম আগুনের মতো</t>
+  </si>
+  <si>
+    <t>লেবু নাকি ৪টা একশ টাকা</t>
+  </si>
+  <si>
+    <t>কি লেবুর শরবত খাবো, বাজারে লেবুর যে দাম!</t>
+  </si>
+  <si>
+    <t>বাজারে সিন্ডিকেট বেড়ে গেছে, এদের কারনে সব জিনিসের দাম বেশি</t>
+  </si>
+  <si>
+    <t>সবকিছুর দাম বেশি, সেজন্য এক কেজি আলু নিয়ে চলে আসলাম</t>
+  </si>
+  <si>
+    <t>অন্য কোন দোকানে না গিয়ে আপনার দোকানে চলে আসলাম</t>
+  </si>
+  <si>
+    <t>আপনার দোকানের জিনিস ভাল বলে এখানে আসলাম</t>
+  </si>
+  <si>
+    <t>আজকে দাম একটু কমাই রাখেন, আরেকবার আসলে তখন বেশি রাখিয়েন</t>
+  </si>
+  <si>
+    <t>পরিচিত মানুষ থেকে এত বেশি লাভ করার দরকার নেই</t>
+  </si>
+  <si>
+    <t>আপনারা পরিচিত মানুষদের থেকে টাকা আরো বেশি নেন</t>
+  </si>
+  <si>
+    <t>এতদিন ধরে আপনার দোকান থেকে শপিং করি, আর আপনি আমার থেকে দাম বেশি নিচ্ছেন!</t>
+  </si>
+  <si>
+    <t>পরিচিত বললে আপনারা আরো দাম বেশি রাখেন</t>
+  </si>
+  <si>
+    <t>আমি আগে আরো অনেকবার আপনার দোকান থেকে বাজার করেছি</t>
+  </si>
+  <si>
+    <t>হাঁস গুলোর দাম কত ভাই?</t>
+  </si>
+  <si>
+    <t>কি কাপড় দিছেন ভাই, একবার ধোয়ার পর রঙ উঠে গেছে</t>
+  </si>
+  <si>
+    <t>এই কারনে আমি এই দোকানে আসতে চাই না</t>
+  </si>
+  <si>
+    <t>বাজারে এখন সব জিনিসে ভেজাল, কোন কিছু কিনতে মন চাই না</t>
+  </si>
+  <si>
+    <t>একসাথে তিনটা নিলে কি দাম একটু কমাই রাখবেন?</t>
+  </si>
+  <si>
+    <t>পুরো মার্কেট খুজেছি, তারপরও এই ডিজাইনের কোন শাড়ি পাই নাই</t>
+  </si>
+  <si>
+    <t>দরদাম করতে না জানলে তো টাকা বেশি নিয়ে ফেলবে</t>
+  </si>
+  <si>
+    <t>পশের দোকানে দেখলাম এই জামাটার দাম অনেক কম, আপনি বেশি বলছেন কেন?</t>
+  </si>
+  <si>
+    <t>কালো রঙের থ্রি-পিস তোমাকে অনেক মানাবে</t>
+  </si>
+  <si>
+    <t>আজকে যা শপিং করলাম, মনে হয় এক বছর না করলেও চলবে</t>
+  </si>
+  <si>
+    <t>ইফতারের পরে মার্কেটে মানুষ বেশি থাকবে</t>
+  </si>
+  <si>
+    <t>কাপড়ের দাম শুনে তো আমার ভয় লাগছে</t>
+  </si>
+  <si>
+    <t>আপনার দোকানে ছোট বাচ্চাদের কাপড়ের কালেকশন কেমন?</t>
+  </si>
+  <si>
+    <t>তোমার দোকানের কাপড়গুলো আমার পছন্দ হচ্ছে না</t>
+  </si>
+  <si>
+    <t>আর দুদিন পর আসেন, দুদিন পর অনেক ভাল ভাল কাপড় আসবে</t>
+  </si>
+  <si>
+    <t>আমাকে আর দুইশ টাকা ফেরত দেন</t>
+  </si>
+  <si>
+    <t>আপনি তো দাম আপনারটা ধরে বসে আছেন, আমাকে কিছু বলার সুযোগ দিচ্ছেন না</t>
+  </si>
+  <si>
+    <t>ভাই, দাম আমি একটা বলব?</t>
+  </si>
+  <si>
+    <t>এত বেশি দাম বললে তো বিক্রি করতে পারবেন না</t>
   </si>
 </sst>
 </file>
@@ -14565,167 +14700,257 @@
       </c>
     </row>
     <row r="949" ht="25" customHeight="1" spans="1:2">
-      <c r="A949" s="2"/>
-      <c r="B949" s="2"/>
+      <c r="A949" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B949" s="2" t="s">
+        <v>1892</v>
+      </c>
     </row>
     <row r="950" ht="25" customHeight="1" spans="1:2">
-      <c r="A950" s="2"/>
-      <c r="B950" s="2"/>
+      <c r="A950" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B950" s="2" t="s">
+        <v>1894</v>
+      </c>
     </row>
     <row r="951" ht="25" customHeight="1" spans="1:2">
-      <c r="A951" s="2"/>
-      <c r="B951" s="2"/>
+      <c r="A951" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B951" s="2" t="s">
+        <v>1896</v>
+      </c>
     </row>
     <row r="952" ht="25" customHeight="1" spans="1:2">
-      <c r="A952" s="2"/>
-      <c r="B952" s="2"/>
+      <c r="A952" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B952" s="2" t="s">
+        <v>1898</v>
+      </c>
     </row>
     <row r="953" ht="25" customHeight="1" spans="1:2">
-      <c r="A953" s="2"/>
+      <c r="A953" s="2" t="s">
+        <v>1899</v>
+      </c>
       <c r="B953" s="2"/>
     </row>
     <row r="954" ht="25" customHeight="1" spans="1:2">
-      <c r="A954" s="2"/>
+      <c r="A954" s="2" t="s">
+        <v>1900</v>
+      </c>
       <c r="B954" s="2"/>
     </row>
     <row r="955" ht="25" customHeight="1" spans="1:2">
-      <c r="A955" s="2"/>
+      <c r="A955" s="2" t="s">
+        <v>1901</v>
+      </c>
       <c r="B955" s="2"/>
     </row>
     <row r="956" ht="25" customHeight="1" spans="1:2">
-      <c r="A956" s="2"/>
+      <c r="A956" s="2" t="s">
+        <v>1902</v>
+      </c>
       <c r="B956" s="2"/>
     </row>
     <row r="957" ht="25" customHeight="1" spans="1:2">
-      <c r="A957" s="2"/>
+      <c r="A957" s="2" t="s">
+        <v>1903</v>
+      </c>
       <c r="B957" s="2"/>
     </row>
     <row r="958" ht="25" customHeight="1" spans="1:2">
-      <c r="A958" s="2"/>
+      <c r="A958" s="2" t="s">
+        <v>1904</v>
+      </c>
       <c r="B958" s="2"/>
     </row>
     <row r="959" ht="25" customHeight="1" spans="1:2">
-      <c r="A959" s="2"/>
+      <c r="A959" s="2" t="s">
+        <v>1905</v>
+      </c>
       <c r="B959" s="2"/>
     </row>
     <row r="960" ht="25" customHeight="1" spans="1:2">
-      <c r="A960" s="2"/>
+      <c r="A960" s="2" t="s">
+        <v>1906</v>
+      </c>
       <c r="B960" s="2"/>
     </row>
     <row r="961" ht="25" customHeight="1" spans="1:2">
-      <c r="A961" s="2"/>
+      <c r="A961" s="2" t="s">
+        <v>1907</v>
+      </c>
       <c r="B961" s="2"/>
     </row>
     <row r="962" ht="25" customHeight="1" spans="1:2">
-      <c r="A962" s="2"/>
+      <c r="A962" s="2" t="s">
+        <v>1908</v>
+      </c>
       <c r="B962" s="2"/>
     </row>
     <row r="963" ht="25" customHeight="1" spans="1:2">
-      <c r="A963" s="2"/>
+      <c r="A963" s="2" t="s">
+        <v>1909</v>
+      </c>
       <c r="B963" s="2"/>
     </row>
     <row r="964" ht="25" customHeight="1" spans="1:2">
-      <c r="A964" s="2"/>
+      <c r="A964" s="2" t="s">
+        <v>1910</v>
+      </c>
       <c r="B964" s="2"/>
     </row>
     <row r="965" ht="25" customHeight="1" spans="1:2">
-      <c r="A965" s="2"/>
+      <c r="A965" s="2" t="s">
+        <v>1911</v>
+      </c>
       <c r="B965" s="2"/>
     </row>
     <row r="966" ht="25" customHeight="1" spans="1:2">
-      <c r="A966" s="2"/>
+      <c r="A966" s="2" t="s">
+        <v>1912</v>
+      </c>
       <c r="B966" s="2"/>
     </row>
     <row r="967" ht="25" customHeight="1" spans="1:2">
-      <c r="A967" s="2"/>
+      <c r="A967" s="2" t="s">
+        <v>1913</v>
+      </c>
       <c r="B967" s="2"/>
     </row>
     <row r="968" ht="25" customHeight="1" spans="1:2">
-      <c r="A968" s="2"/>
+      <c r="A968" s="2" t="s">
+        <v>1914</v>
+      </c>
       <c r="B968" s="2"/>
     </row>
     <row r="969" ht="25" customHeight="1" spans="1:2">
-      <c r="A969" s="2"/>
+      <c r="A969" s="2" t="s">
+        <v>1915</v>
+      </c>
       <c r="B969" s="2"/>
     </row>
     <row r="970" ht="25" customHeight="1" spans="1:2">
-      <c r="A970" s="2"/>
+      <c r="A970" s="2" t="s">
+        <v>1916</v>
+      </c>
       <c r="B970" s="2"/>
     </row>
     <row r="971" ht="25" customHeight="1" spans="1:2">
-      <c r="A971" s="2"/>
+      <c r="A971" s="2" t="s">
+        <v>1917</v>
+      </c>
       <c r="B971" s="2"/>
     </row>
     <row r="972" ht="25" customHeight="1" spans="1:2">
-      <c r="A972" s="2"/>
+      <c r="A972" s="2" t="s">
+        <v>1918</v>
+      </c>
       <c r="B972" s="2"/>
     </row>
     <row r="973" ht="25" customHeight="1" spans="1:2">
-      <c r="A973" s="2"/>
+      <c r="A973" s="2" t="s">
+        <v>1919</v>
+      </c>
       <c r="B973" s="2"/>
     </row>
     <row r="974" ht="25" customHeight="1" spans="1:2">
-      <c r="A974" s="2"/>
+      <c r="A974" s="2" t="s">
+        <v>1920</v>
+      </c>
       <c r="B974" s="2"/>
     </row>
     <row r="975" ht="25" customHeight="1" spans="1:2">
-      <c r="A975" s="2"/>
+      <c r="A975" s="2" t="s">
+        <v>1921</v>
+      </c>
       <c r="B975" s="2"/>
     </row>
     <row r="976" ht="25" customHeight="1" spans="1:2">
-      <c r="A976" s="2"/>
+      <c r="A976" s="2" t="s">
+        <v>1922</v>
+      </c>
       <c r="B976" s="2"/>
     </row>
     <row r="977" ht="25" customHeight="1" spans="1:2">
-      <c r="A977" s="2"/>
+      <c r="A977" s="2" t="s">
+        <v>1923</v>
+      </c>
       <c r="B977" s="2"/>
     </row>
     <row r="978" ht="25" customHeight="1" spans="1:2">
-      <c r="A978" s="2"/>
+      <c r="A978" s="2" t="s">
+        <v>1924</v>
+      </c>
       <c r="B978" s="2"/>
     </row>
     <row r="979" ht="25" customHeight="1" spans="1:2">
-      <c r="A979" s="2"/>
+      <c r="A979" s="2" t="s">
+        <v>1925</v>
+      </c>
       <c r="B979" s="2"/>
     </row>
     <row r="980" ht="25" customHeight="1" spans="1:2">
-      <c r="A980" s="2"/>
+      <c r="A980" s="2" t="s">
+        <v>1926</v>
+      </c>
       <c r="B980" s="2"/>
     </row>
     <row r="981" ht="25" customHeight="1" spans="1:2">
-      <c r="A981" s="2"/>
+      <c r="A981" s="2" t="s">
+        <v>1927</v>
+      </c>
       <c r="B981" s="2"/>
     </row>
     <row r="982" ht="25" customHeight="1" spans="1:2">
-      <c r="A982" s="2"/>
+      <c r="A982" s="2" t="s">
+        <v>1928</v>
+      </c>
       <c r="B982" s="2"/>
     </row>
     <row r="983" ht="25" customHeight="1" spans="1:2">
-      <c r="A983" s="2"/>
+      <c r="A983" s="2" t="s">
+        <v>1929</v>
+      </c>
       <c r="B983" s="2"/>
     </row>
     <row r="984" ht="25" customHeight="1" spans="1:2">
-      <c r="A984" s="2"/>
+      <c r="A984" s="2" t="s">
+        <v>1930</v>
+      </c>
       <c r="B984" s="2"/>
     </row>
     <row r="985" ht="25" customHeight="1" spans="1:2">
-      <c r="A985" s="2"/>
+      <c r="A985" s="2" t="s">
+        <v>1931</v>
+      </c>
       <c r="B985" s="2"/>
     </row>
     <row r="986" ht="25" customHeight="1" spans="1:2">
-      <c r="A986" s="2"/>
+      <c r="A986" s="2" t="s">
+        <v>1932</v>
+      </c>
       <c r="B986" s="2"/>
     </row>
     <row r="987" ht="25" customHeight="1" spans="1:2">
-      <c r="A987" s="2"/>
+      <c r="A987" s="2" t="s">
+        <v>1933</v>
+      </c>
       <c r="B987" s="2"/>
     </row>
     <row r="988" ht="25" customHeight="1" spans="1:2">
-      <c r="A988" s="2"/>
+      <c r="A988" s="2" t="s">
+        <v>1934</v>
+      </c>
       <c r="B988" s="2"/>
     </row>
     <row r="989" ht="25" customHeight="1" spans="1:2">
-      <c r="A989" s="2"/>
+      <c r="A989" s="2" t="s">
+        <v>1935</v>
+      </c>
       <c r="B989" s="2"/>
     </row>
     <row r="990" ht="25" customHeight="1" spans="1:2">

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="1936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="2056">
   <si>
     <t>bangla</t>
   </si>
@@ -938,13 +938,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SolaimanLipi"/>
-        <charset val="134"/>
-      </rPr>
-      <t>যহনই মনে অইবু হারায় ফেলাইয়্যো, তহনই এক্কানা থামি রে নিজোরে ফুসর গরো</t>
+      <t>যহনই মনে অইবু আঝাই ফেলাইয়্যো, তহনই এক্কানা থামি রে নিজোরে ফুসর গরো</t>
     </r>
     <r>
       <rPr>
@@ -1524,7 +1518,7 @@
     <t>এল্লেত মরার মতোন হনে ঘুম যায়! হারা উঠ ঘুমুত্তোন</t>
   </si>
   <si>
-    <t xml:space="preserve">যেভাবেই হোক সন্ধার আগে সব কাজ শেষ করতে হবে </t>
+    <t xml:space="preserve">যেভাবেই হোক সন্ধ্যার আগে সব কাজ শেষ করতে হবে </t>
   </si>
   <si>
     <t>যেনগরি অক আজুইন্নের আগে বিয়াক হাম শেষ গরন পরিবো</t>
@@ -2253,7 +2247,7 @@
     <t>ইরফানকে একদিন বাসায় বেড়াতে আসতে বল, অনেক দিন ধরে ছেলেটা বাসায় আসেনা</t>
   </si>
   <si>
-    <t>ইরফান উরে একদিন বাসাত বেরাইতু আইসতো হ, বতদিন ধরি ফুয়া ইবে বাসাত ন আইয়্যি</t>
+    <t>ইরফান উরে একদিন বাসাত বেরাইতু আইসতো হ, বতদিন ধরি ফুওয়া ইবে বাসাত ন আইয়্যি</t>
   </si>
   <si>
     <t>আমি একটু মিনহাজের বাসায় যাচ্ছি, আসতে দেরি হবে</t>
@@ -2271,7 +2265,7 @@
     <t>আমার এক আন্টি আমাকে অনেক দেখতে পারে, একদম নিজের ছেলের মত মনে করে</t>
   </si>
   <si>
-    <t>আঁর উজ্ঞো আন্টি আঁরে বত দেইত পারে, এব্বেরে নিজোর ফুয়ার মতন মনে গরে</t>
+    <t>আঁর উজ্ঞো আন্টি আঁরে বত দেইত পারে, এব্বেরে নিজোর ফুওয়ার মতন মনে গরে</t>
   </si>
   <si>
     <t>সারাদিন এত কাজ করি তাও কাজ গুলো শেষ হচ্ছে না</t>
@@ -3381,7 +3375,7 @@
     <t>ছেলেটাকে ডিম দিতে হবে, বেশি দুর্বল হয়ে গেছে</t>
   </si>
   <si>
-    <t>ফুয়া ইবেরে ডিম দন ফরিবু, বেশি দুর্বল অই গেইয়্যি</t>
+    <t>ফুওয়া ইবেরে ডিম দন ফরিবু, বেশি দুর্বল অই গেইয়্যি</t>
   </si>
   <si>
     <t>বারবার বারণ করি, তাও আমার কথা শোনো না</t>
@@ -3849,7 +3843,7 @@
     <t>আপনার ছোট ছেলে তো সাত সকালে বের হয়ে গেছে</t>
   </si>
   <si>
-    <t>অঁনোর গুরো ফুয়া ইবে তো বেইন্নে ফজোরত বাইর অই গেইয়্যি</t>
+    <t>অঁনোর গুরো ফুওয়া ইবে তো বেইন্নে ফজোরত বাইর অই গেইয়্যি</t>
   </si>
   <si>
     <t>সারাদিন শুধু এই বাগান আর ওই বাগানে ঘুরাঘুরি করো</t>
@@ -3993,7 +3987,7 @@
     <t>বাবা যেরকম ছেলেও সেরকম হয়েছে</t>
   </si>
   <si>
-    <t>বাফ যেরহম ফোয়া ও সেরহম অইয়্যি</t>
+    <t>বাফ যেরহম ফোওয়া ও সেরহম অইয়্যি</t>
   </si>
   <si>
     <t>আমার মা সবসময় চায় যেন আমরা তিন ভাই একসাথে থাকি</t>
@@ -4109,7 +4103,7 @@
     <t>আমার কথার তো কোনো গুরুত্ব নেই, আপনি তো আপনার ছেলের কথাই শুনবেন</t>
   </si>
   <si>
-    <t>আঁর হতার তো হনো গুরুত্ব নেই, অঁনে তো অঁনোর ফোয়ার হতাই উনিবেন</t>
+    <t>আঁর হতার তো হনো গুরুত্ব নেই, অঁনে তো অঁনোর ফোওয়ার হতাই উনিবেন</t>
   </si>
   <si>
     <t>লেবুর রস দিয়ে গরম গরম ছটপটি অনেক মজা লাগে</t>
@@ -4609,7 +4603,7 @@
     <t>ঘরের সবচেয়ে ছোট ছেলেটা অনেক দুষ্টু হয়</t>
   </si>
   <si>
-    <t>ঘরোর বিয়াজ্ঞুনুত্তুন গুরো ফোয়া ইবে বত জারগো অই</t>
+    <t>ঘরোর বিয়াজ্ঞুনুত্তুন গুরো ফোওয়া ইবে বত জারগো অই</t>
   </si>
   <si>
     <t>ঘর ওটাতে থাকার মতো অবস্থা নেই, চারদিকে অনেক ময়লা</t>
@@ -4795,13 +4789,13 @@
     <t>ছেলেটা শুধু এদিক সেদিক ঘুরছে</t>
   </si>
   <si>
-    <t>ফোয়া ইবে উদো ইক্কেত্তুন উইক্কে ঘুরের</t>
+    <t>ফোওয়া ইবে উদো ইক্কেত্তুন উইক্কে ঘুরের</t>
   </si>
   <si>
     <t>আমি ছেলে হতাম তাহলে অনেক কিছু করতে পারতাম</t>
   </si>
   <si>
-    <t>আঁই যদি মরতফোয়া অইতাম তইলি বত কিছু গরিত ফাইত্তাম</t>
+    <t>আঁই যদি মরতফোওয়া অইতাম তইলি বত কিছু গরিত ফাইত্তাম</t>
   </si>
   <si>
     <t>এগুলো ওখান থেকে কীভাবে পড়ে গেল?</t>
@@ -4933,7 +4927,7 @@
     <t>ছেলে মানুষ করা অনেক কঠিন</t>
   </si>
   <si>
-    <t>মরতফোয়া মানুষ গরন বত কঠিন</t>
+    <t>মরতফোওয়া মানুষ গরন বত কঠিন</t>
   </si>
   <si>
     <t>ভাবি তার বাপের বাড়িতে চলে গেছে, সেজন্য আম্মুর একা সব কাজ সামলানো অনেক কঠিন হয়ে যাচ্ছে</t>
@@ -4993,7 +4987,7 @@
     <t>চাচি, আপনার ছেলে-মেয়ে কয়টা?</t>
   </si>
   <si>
-    <t>চাচি, অঁনোর ফোয়া-মাইফুয়া হওয়ো?</t>
+    <t>চাচি, অঁনোর ফোওয়া-মাইফুয়া হওয়ো?</t>
   </si>
   <si>
     <t>এটা এরকম হয়ে যাবে যে সেটা আমি আগে বুঝতে পারিনি</t>
@@ -5029,7 +5023,7 @@
     <t>তোমার ছোট ছেলেটা বেশি বাহানা করে</t>
   </si>
   <si>
-    <t>তোঁয়ার ছোডো ফোয়া ইবে বেশি তাল গরে</t>
+    <t>তোঁয়ার ছোডো ফোওয়া ইবে বেশি তাল গরে</t>
   </si>
   <si>
     <t>মানুষজন এসে আমার ঘরটা ময়লা করে ফেলেছে</t>
@@ -5119,7 +5113,7 @@
     <t>তোমাদেরকে একটা কাজ দিয়েছিলাম, ভুলে গেছো তোমরা</t>
   </si>
   <si>
-    <t>তোঁয়ারারে এক্কান হাম দিইলাম, ভুলি গেইয়্যু তোঁইয়ারা</t>
+    <t>তোঁয়ারারে এক্কান হাম দিইলাম, ভুলি গেইয়্যু তোঁয়ারা</t>
   </si>
   <si>
     <t>একা একা না ঘুরে আমার সাথে ঘুরতে পারো</t>
@@ -5749,7 +5743,7 @@
     <t>আমার ছেলের জন্য একটা জামা নিয়েছিলাম, কিন্তু ওটা ছোট হচ্ছে</t>
   </si>
   <si>
-    <t>আঁর ফুয়ার লাই উজ্ঞো হুত্তা লইলাম, কিন্তু ইবে ছোড অর</t>
+    <t>আঁর ফুওয়ার লাই উজ্ঞো হুত্তা লইলাম, কিন্তু ইবে ছোড অর</t>
   </si>
   <si>
     <t>ফুল হাতা গেঞ্জিগুলো ভাঁজ করে রাখো</t>
@@ -5830,115 +5824,475 @@
     <t>ঠিক আছে, ইবে প্যাকেট গরি দন</t>
   </si>
   <si>
-    <t>কাপড় এটা তো ধোয়ার পরে রঙ উঠে যাবে</t>
-  </si>
-  <si>
-    <t>শাড়ি এটার কাপড় ভাল হবে মনে হচ্ছে</t>
-  </si>
-  <si>
-    <t>আপনি যে দাম বলেছেন, আমার মুখ দিয়ে তো আর কথা বের হচ্ছেনা</t>
-  </si>
-  <si>
-    <t>আগে যে শাড়িটা নিয়েছিলাম ওটার মতো আরেকটা শাড়ি দাও</t>
-  </si>
-  <si>
-    <t>আমি সবসময় তোমার দোকান থেকে কাপড় নি, এবার দাম কম রাখতে হবে</t>
-  </si>
-  <si>
-    <t>এবার রমজানে পিয়াজের দাম আগুনের মতো</t>
+    <t>কাপড়টা তো ধোয়ার পরে রঙ উঠে যাবে</t>
+  </si>
+  <si>
+    <t>হর ইবে তো ধোঅনুর পরে রঙ উডি যাইবু</t>
+  </si>
+  <si>
+    <t>শাড়িটার কাপড় ভালো হবে মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>শারি ইবের হর ভালা অইবু মনে অর</t>
+  </si>
+  <si>
+    <t>আপনি যে দাম বলেছেন, আমার মুখ দিয়ে তো আর কথা বের হচ্ছে না</t>
+  </si>
+  <si>
+    <t>অঁনে যে দাম হইয়্যুন, আঁর মুখুদ্দি তো আর হতা বাইর ন অর</t>
+  </si>
+  <si>
+    <t>আগে যে শাড়িটা নিয়েছিলাম, ওটার মতো আরেকটা শাড়ি দিন</t>
+  </si>
+  <si>
+    <t>আগে যে শারি গান লইলাম, ইয়েনুর মতন আরেক্কান শারি দন</t>
+  </si>
+  <si>
+    <t>আমি সবসময় তোমার দোকান থেকে কাপড় নিই, এবার দাম কম রাখতে হবে</t>
+  </si>
+  <si>
+    <t>আঁই সবসময় তোঁয়ার দোয়ানুত্তুন হর লই, এবার দাম হম রাহন ফরিবু</t>
+  </si>
+  <si>
+    <t>এবার রমজানে পেঁয়াজের দাম আগুনের মতো</t>
+  </si>
+  <si>
+    <t>এবার রমজানুত পিয়েজুর দাম অইনুর মতন</t>
   </si>
   <si>
     <t>লেবু নাকি ৪টা একশ টাকা</t>
   </si>
   <si>
+    <t>লেবু বলে ৪গো একশ টিয়া</t>
+  </si>
+  <si>
     <t>কি লেবুর শরবত খাবো, বাজারে লেবুর যে দাম!</t>
   </si>
   <si>
-    <t>বাজারে সিন্ডিকেট বেড়ে গেছে, এদের কারনে সব জিনিসের দাম বেশি</t>
-  </si>
-  <si>
-    <t>সবকিছুর দাম বেশি, সেজন্য এক কেজি আলু নিয়ে চলে আসলাম</t>
-  </si>
-  <si>
-    <t>অন্য কোন দোকানে না গিয়ে আপনার দোকানে চলে আসলাম</t>
+    <t>কি লেবুর শরবত হইয়্যুম, বাজারুত লেবুর যে দাম!</t>
+  </si>
+  <si>
+    <t>বাজারে সিন্ডিকেট বেড়ে গেছে, এদের কারণে সব জিনিসের দাম বেশি</t>
+  </si>
+  <si>
+    <t>বাজারুত সিন্ডিকেট বারি গেইয়্যি, ইতারার হারনে বিয়াক জিনিসুর দাম বেশি</t>
+  </si>
+  <si>
+    <t>সবকিছুর দাম বেশি, সেজন্য এক কেজি আলু নিয়ে চলে এলাম</t>
+  </si>
+  <si>
+    <t>বিয়াক কিছুর দাম বেশি, এতেল্লে এক কেজি আলু লইয়্যিরে চলি আইস্যি</t>
+  </si>
+  <si>
+    <t>অন্য কোনো দোকানে না গিয়ে আপনার দোকানে চলে এলাম</t>
+  </si>
+  <si>
+    <t>অন্য হনো দোয়ানুত ন যায় অঁনোর দোয়ানুত চলি আইস্যি</t>
   </si>
   <si>
     <t>আপনার দোকানের জিনিস ভাল বলে এখানে আসলাম</t>
   </si>
   <si>
+    <t>অঁনোর দোয়ানুর জিনিস ভালা বলি এনডে আইস্যি</t>
+  </si>
+  <si>
     <t>আজকে দাম একটু কমাই রাখেন, আরেকবার আসলে তখন বেশি রাখিয়েন</t>
   </si>
   <si>
+    <t>আজিয়ে দাম এক্কানা হমাই রাহন, আরেকবার আইলি এত্তে বেশি রাইক্কোন</t>
+  </si>
+  <si>
     <t>পরিচিত মানুষ থেকে এত বেশি লাভ করার দরকার নেই</t>
   </si>
   <si>
+    <t>পরিচিত মানুষ উত্তুন এল্লেত বেশি লাভ গরন উর দরহার নেই</t>
+  </si>
+  <si>
     <t>আপনারা পরিচিত মানুষদের থেকে টাকা আরো বেশি নেন</t>
   </si>
   <si>
-    <t>এতদিন ধরে আপনার দোকান থেকে শপিং করি, আর আপনি আমার থেকে দাম বেশি নিচ্ছেন!</t>
+    <t>অঁনেরা পরিচিত মানুষ উত্তুন টিয়া আরো বেশি লন</t>
+  </si>
+  <si>
+    <t>এতদিন ধরে আপনার দোকান থেকে কেনাকাটা করি, আর আপনি আমার কাছ থেকে দাম বেশি নিচ্ছেন!</t>
+  </si>
+  <si>
+    <t>এতদিন ধরি অঁনোর দোয়ানুত্তুন কেনাকাটা গরি, আর অঁনে আত্তুন দাম বেশি লইতে লাইজ্ঞুন!</t>
   </si>
   <si>
     <t>পরিচিত বললে আপনারা আরো দাম বেশি রাখেন</t>
   </si>
   <si>
+    <t>পরিচিত হইলি অঁনেরা আরো দাম বেশি রাহন</t>
+  </si>
+  <si>
     <t>আমি আগে আরো অনেকবার আপনার দোকান থেকে বাজার করেছি</t>
   </si>
   <si>
+    <t>আঁই আগে আরো বতবার অঁনোর দোয়ানত্তুন বাজার গইজ্জি</t>
+  </si>
+  <si>
     <t>হাঁস গুলোর দাম কত ভাই?</t>
   </si>
   <si>
+    <t>আঁস এগুনোর দাম হত বদ্দা?</t>
+  </si>
+  <si>
     <t>কি কাপড় দিছেন ভাই, একবার ধোয়ার পর রঙ উঠে গেছে</t>
   </si>
   <si>
-    <t>এই কারনে আমি এই দোকানে আসতে চাই না</t>
-  </si>
-  <si>
-    <t>বাজারে এখন সব জিনিসে ভেজাল, কোন কিছু কিনতে মন চাই না</t>
-  </si>
-  <si>
-    <t>একসাথে তিনটা নিলে কি দাম একটু কমাই রাখবেন?</t>
+    <t>কি হর দিয়্যুন বদ্দা, একবার ধু'অনুর পর রঙ উডি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এই কারণে আমি এই দোকানে আসতে চাই না</t>
+  </si>
+  <si>
+    <t>এই হারনে আঁই এই দোয়ানুত আইসতু ন চাই</t>
+  </si>
+  <si>
+    <t>বাজারে এখন সব জিনিসে ভেজাল, কোনো কিছু কিনতে মন চায় না</t>
+  </si>
+  <si>
+    <t>বাজারুত এহন বিয়াক জিনিসুত ভেজাল, হনো কিছু কিনতু মনে ন চায়</t>
+  </si>
+  <si>
+    <t>একসাথে তিনটা নিলে কি দাম একটু কম রাখবেন?</t>
+  </si>
+  <si>
+    <t>এক্কোওয়ারে তিন্নো লইলি কি দাম এক্কানা হম রাহিবেন?</t>
   </si>
   <si>
     <t>পুরো মার্কেট খুজেছি, তারপরও এই ডিজাইনের কোন শাড়ি পাই নাই</t>
   </si>
   <si>
+    <t>ফুরো মার্কেট তোওয়াই, তারপরও এই ডিজাইনুর হনো শারি ন ফাই</t>
+  </si>
+  <si>
     <t>দরদাম করতে না জানলে তো টাকা বেশি নিয়ে ফেলবে</t>
   </si>
   <si>
+    <t>দরদাম গরিত ন জানিলি তো টিয়া বেশি লই ফেলাইবু</t>
+  </si>
+  <si>
     <t>পশের দোকানে দেখলাম এই জামাটার দাম অনেক কম, আপনি বেশি বলছেন কেন?</t>
   </si>
   <si>
+    <t>পাশোর দোয়ানুত দেহিলাম এই হুত্তা ইবের দাম বত হম, অঁনে বেশি কা হইতে লেইজ্ঞুন?</t>
+  </si>
+  <si>
     <t>কালো রঙের থ্রি-পিস তোমাকে অনেক মানাবে</t>
   </si>
   <si>
+    <t>হালা রঙ উর থ্রি-পিস তোঁয়ারে বত মানাইবু</t>
+  </si>
+  <si>
     <t>আজকে যা শপিং করলাম, মনে হয় এক বছর না করলেও চলবে</t>
   </si>
   <si>
+    <t>আজিয়ে যা শপিং গইজ্জি, মনে অয় এক বছর ন গরিলিও চলিবু</t>
+  </si>
+  <si>
     <t>ইফতারের পরে মার্কেটে মানুষ বেশি থাকবে</t>
   </si>
   <si>
+    <t>ইফতেরুর ফরে মার্কেটুত মানুষ বেশি থাহিবু</t>
+  </si>
+  <si>
     <t>কাপড়ের দাম শুনে তো আমার ভয় লাগছে</t>
   </si>
   <si>
+    <t>হরুর দাম উনি তো আত্তুন ডর লাগের</t>
+  </si>
+  <si>
     <t>আপনার দোকানে ছোট বাচ্চাদের কাপড়ের কালেকশন কেমন?</t>
   </si>
   <si>
+    <t>অঁনোর দোয়ানুত গুরো ফোওয়া অলুর হরুর কালেকশন কেন?</t>
+  </si>
+  <si>
     <t>তোমার দোকানের কাপড়গুলো আমার পছন্দ হচ্ছে না</t>
   </si>
   <si>
+    <t>তোঁয়ার দোয়ানুর হর এগিন আত্তুন পছন্দ ন অর</t>
+  </si>
+  <si>
     <t>আর দুদিন পর আসেন, দুদিন পর অনেক ভাল ভাল কাপড় আসবে</t>
   </si>
   <si>
+    <t>আর দুদিন পর আইয়্যুন, দুদিন পর বত ভালা ভালা হর আইবু</t>
+  </si>
+  <si>
     <t>আমাকে আর দুইশ টাকা ফেরত দেন</t>
   </si>
   <si>
+    <t>আঁরে আর দুইশ টিয়া ফেরত দন</t>
+  </si>
+  <si>
     <t>আপনি তো দাম আপনারটা ধরে বসে আছেন, আমাকে কিছু বলার সুযোগ দিচ্ছেন না</t>
   </si>
   <si>
+    <t>অঁনে তো দাম অঁনোরগান ধরি বই থেইক্কুন, আঁরে কিছু হইবের সুযোগ নইদ্দে লেইজ্ঞুন</t>
+  </si>
+  <si>
     <t>ভাই, দাম আমি একটা বলব?</t>
   </si>
   <si>
+    <t>বদ্দা, দাম আঁই এক্কান হইয়্যুম?</t>
+  </si>
+  <si>
     <t>এত বেশি দাম বললে তো বিক্রি করতে পারবেন না</t>
+  </si>
+  <si>
+    <t>এল্লেত বেশি দাম হইলি তো বেচিত ন ফারিবেন</t>
+  </si>
+  <si>
+    <t>আমি গত মাসেও আপনার থেকে একটা পাঞ্জাবি নিয়েছিলাম, এবার একটু কমে রাখেন</t>
+  </si>
+  <si>
+    <t>আঁই গত মাসুতও অঁনোত্তুন উজ্ঞো পাঞ্জাবি লইলাম, এবার এক্কানা হমে রাহন</t>
+  </si>
+  <si>
+    <t>গতবার কাপড় কিনার সময় বলেছিলেন এবার দাম কম রাখবেন</t>
+  </si>
+  <si>
+    <t>গতবার হর কিনিবের সমত হইলেন এবার দাম হম রাহিবেন</t>
+  </si>
+  <si>
+    <t>আমার সময় কম, তাই বেশি দামাদামি করতে চায় না</t>
+  </si>
+  <si>
+    <t>আঁর সময় হম, এতেল্লে বেশি দামাদামি গইত্তাম ন চায়</t>
+  </si>
+  <si>
+    <t>সন্ধ্যার পর মার্কেট বন্ধ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আজুইন্নের পর মার্কেট বন্ধ অই যাইবু</t>
+  </si>
+  <si>
+    <t>সরকার নতুন নিয়ম করেছে মার্কেট দ্রুত বন্ধ করে দেওয়ার</t>
+  </si>
+  <si>
+    <t>সরকারে নতুম নিয়ম গইজ্জি মার্কেট হারা বন্ধ গরি দিবের</t>
+  </si>
+  <si>
+    <t>দোকানদার দুপুরের খাবার খেতে গেছে, আপনারা একটু বসুন</t>
+  </si>
+  <si>
+    <t>দোয়ানদার দুইজ্জের হানা হাইতু গেইয়্যি, অঁনেরা এক্কানা বইয়্যুন</t>
+  </si>
+  <si>
+    <t>আন্টি, আপনি তো এখন আর আমাদের কাছ থেকে কিছু কেনেন না</t>
+  </si>
+  <si>
+    <t>আন্টি, অঁনে তো এহন আর আঁরাত্তুন কিছু ন কিনন</t>
+  </si>
+  <si>
+    <t>তোমার দোকানের ছেলেটার ব্যবহার ভালো লাগেনি আমার</t>
+  </si>
+  <si>
+    <t>তোঁয়ার দোয়ানুর ফোওয়া ইবের বেবার ভালা ন লাগে আত্তুন</t>
+  </si>
+  <si>
+    <t>কাস্টমারের সাথে ভালোভাবে ব্যবহার করতে হবে, তাহলে বিক্রি বেশি হবে</t>
+  </si>
+  <si>
+    <t>কাস্টোমারুর লগে ভালাগরি বেবার গরন ফরিবু, তইলি বেছা বেশি অইবু</t>
+  </si>
+  <si>
+    <t>আজকে দোকানে কোনো কাস্টমার নেই, সব কাস্টমার গেল কোথায়?</t>
+  </si>
+  <si>
+    <t>আজিয়ে দোয়ানুত হনো কাস্টমার নেই, বিয়াক কাস্টমার গেইয়্যি হনডে?</t>
+  </si>
+  <si>
+    <t>দরজায় দাঁড়িয়ে কাস্টমার ডাক, না হলে আসবে না</t>
+  </si>
+  <si>
+    <t>দরজাত থিয়েই কাস্টোমার ডাক, নইলি ন আইবু</t>
+  </si>
+  <si>
+    <t>এই ছেলেটা প্রতিবার জিনিস দেখে চলে যায়, কোনো সময় কিছু কিনে না</t>
+  </si>
+  <si>
+    <t>এই ফোওয়া ইবে পইত্তোবার জিনিস সাই চলি যায়, হনো সময় কিছু ন কিনে</t>
+  </si>
+  <si>
+    <t>আজকে ছোট আপুর শ্বশুরবাড়ি থেকে মেহমান আসবে, তাই আম্মু সকাল থেকে অনেক ব্যস্ত</t>
+  </si>
+  <si>
+    <t>আজিয়ে ছোডো আপার অরো বারিত্তুন মেমান আইবু, এতেল্লে আম্মু বেইন্নেত্তুন বত ব্যস্ত</t>
+  </si>
+  <si>
+    <t>তুই আজকে নিউ মার্কেট যাবি? যদি যাস তাহলে আমার ছেলের জন্য একটা টি-শার্ট কিনে আনিস</t>
+  </si>
+  <si>
+    <t>তুই আজিয়ে নিউ মার্কেট যাবি? যদি যস তইলি আঁর ফোওয়ার লাই উজ্ঞো টি-শার্ট কিনি আনিস</t>
+  </si>
+  <si>
+    <t>আমার বেশি মাথাব্যথা করছে, তাই আজকে মার্কেটে যাব না</t>
+  </si>
+  <si>
+    <t>আত্তুন বেশি মাথাব্যথা গরের, এতেল্লে আজিয়ে মার্কেটুত যাইতাম নো</t>
+  </si>
+  <si>
+    <t>অনলাইন থেকে একটা জামা অর্ডার দিয়েছি</t>
+  </si>
+  <si>
+    <t>অনলাইন উত্তুন উজ্ঞো হুত্তা অর্ডার দিই</t>
+  </si>
+  <si>
+    <t>এত তাড়াতাড়ি গিয়ে লাভ নেই, দোকান খুলবে ১০টার পরে</t>
+  </si>
+  <si>
+    <t>এল্লেত তারাতারি যাই লাভ নেই, দোয়ান খুলিবু ১০টার ফর</t>
+  </si>
+  <si>
+    <t>তোমার শ্বশুরবাড়ি থেকে মেহমান আসবে, তাই বাজার থেকে মাংস নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>তোঁয়ার অরো বারিত্তুন মেমান আইবু, এতেল্লে বাজারুত্তুন গোস্ত লই আইয়্যু</t>
+  </si>
+  <si>
+    <t>মাংস বিক্রেতাগুলো বেশি খারাপ</t>
+  </si>
+  <si>
+    <t>গোস্ত বিয়ারি এগুন বেশি হারাফ</t>
+  </si>
+  <si>
+    <t>আজকে আর কোন অর্ডার নিব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে আর হনো অর্ডার লইতাম নো</t>
+  </si>
+  <si>
+    <t>একটু বসেন, দোকানদার ভাত খেতে গেছেন</t>
+  </si>
+  <si>
+    <t>এক্কানা বইয়্যুন, দোয়ানদার ভাত হাইতু গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এই মাসে ইনকাম একটু কম হয়েছে, তাই বাজার একটু কম আনতে হবে</t>
+  </si>
+  <si>
+    <t>এই শাড়িটার দাম কত, একটু বলবেন?</t>
+  </si>
+  <si>
+    <t>শারি ইয়েনুর দাম হতো, এক্কানা হইবেন?</t>
+  </si>
+  <si>
+    <t>বাজার করে আসার সময় ৫০০ টাকার একটা নোট হারিয়ে ফেলেছি</t>
+  </si>
+  <si>
+    <t>বাজারুত্তুন আইবের সমত ৫০০ টিয়ার নোট এক্কান আঝাই ফেলাই</t>
+  </si>
+  <si>
+    <t>মাছগুলো দেখে মনে হচ্ছে নষ্ট হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>মাছ এগুন দেহি মনে অদ্দে নষ্ট অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আপনার কাছে কি সুতির পাঞ্জাবি আছে?</t>
+  </si>
+  <si>
+    <t>অঁনোর হাছে কি সুতোর পাঞ্জাবি আছে?</t>
+  </si>
+  <si>
+    <t>ভাই এগুলো কি দেখাচ্ছেন? সুতির শাড়ি দেখান</t>
+  </si>
+  <si>
+    <t>বদ্দা এগিন ক দেহাইতে লাইজ্ঞুন? সুতোর শারি দেহন</t>
+  </si>
+  <si>
+    <t>বড় মাছটার দাম কত ভাই?</t>
+  </si>
+  <si>
+    <t>বরো মাছ ইবের দাম হতো বদ্দা?</t>
+  </si>
+  <si>
+    <t>ভাইয়া, এগুলো সাগরের মাছ, তাই দাম বেশি</t>
+  </si>
+  <si>
+    <t>ভাইয়ে, এগুন সাগরুর মাছ, এতেল্লে দাম বেশি</t>
+  </si>
+  <si>
+    <t>আপনি আমার পুরোনো কাস্টমার, তাই দাম বেশি বলব না</t>
+  </si>
+  <si>
+    <t>অঁনে আঁর ফুরন কাস্টোমার, এতেল্লে দাম বেশি হইতাম নো</t>
+  </si>
+  <si>
+    <t>এই গেঞ্জিটা একবার ব্যবহার করে দেখেন, যদি ভালো না লাগে তাহলে ফেরত নেব</t>
+  </si>
+  <si>
+    <t>গেঞ্জি ইবে একবার বেবার গরি সন, যদি ভালা ন লাগে তইলি ফেরত লইয়্যুম</t>
+  </si>
+  <si>
+    <t>এত দাম দিয়ে কিনলে আমার পোষাবে না</t>
+  </si>
+  <si>
+    <t>এল্লেত দাম দি লইলি আত্তুন ন পোষাইবু</t>
+  </si>
+  <si>
+    <t>এই কাপড়ের কোনো দিনও রং উঠবে না, আমি গ্যারান্টি দিলাম</t>
+  </si>
+  <si>
+    <t>হর ইবের হনো দিনও রং ন উড়িবু, আঁই গ্যারান্টি দিলাম</t>
+  </si>
+  <si>
+    <t>ভাই, একটু কম করে দিলে নিয়ে যাব</t>
+  </si>
+  <si>
+    <t>বদ্দা, এক্কানা হম গরি দিলি লই যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>এই জামাটা একটু বড় সাইজে পাওয়া যাবে?</t>
+  </si>
+  <si>
+    <t>হুত্তা ইবে এক্কানা বরো সাইজুর পন যাইবু?</t>
+  </si>
+  <si>
+    <t>এই আমগুলো কি আজকের তোলা?</t>
+  </si>
+  <si>
+    <t>আম এগুন কি আজিয়ের তোলা?</t>
+  </si>
+  <si>
+    <t>অন্য কেউ হলে ১০০০ টাকা বলতাম, আপনাকে দেখে কম বললাম</t>
+  </si>
+  <si>
+    <t>অন্য কিয়াই অইলি ১০০০ টিয়া হইতাম, অঁনোরে দেহি হম হইলাম</t>
+  </si>
+  <si>
+    <t>ক্যাশ দিলে কি একটু ছাড় পাওয়া যাবে?</t>
+  </si>
+  <si>
+    <t>ক্যাশ দিলি কি এক্কানা ছার পন যাইবু?</t>
+  </si>
+  <si>
+    <t>আপনি আজকের প্রথম কাস্টমার, তাই ফেরত দিতে চাচ্ছি না</t>
+  </si>
+  <si>
+    <t>অঁনে আজিয়ের প্রথম কাস্টোমার, এতেল্লে ফেরত দিতাম ন চাইর</t>
+  </si>
+  <si>
+    <t>ড্রেসটা পছন্দ না হলে কি ফেরত দিতে পারব?</t>
+  </si>
+  <si>
+    <t>ড্রেস ইবে পছন্দ ন অইলি কি ফেরত দিত পাইজ্জুম?</t>
+  </si>
+  <si>
+    <t>আপু, এটা বাসায় নিয়ে গিয়ে পরে দেখেন, যদি সাইজ না হয় তাহলে চেঞ্জ করে দেব</t>
+  </si>
+  <si>
+    <t>আপা, ইবে বাসাত লই যায় পরি চন, যদি সাইজ ন অয় তইলি চেঞ্জ গরি দিয়্যুম</t>
+  </si>
+  <si>
+    <t>ডেলিভারি পেতে কত দিন লাগবে?</t>
+  </si>
+  <si>
+    <t>ডেলিভারি পাইতে হতদিন লাগিবু?</t>
   </si>
 </sst>
 </file>
@@ -6589,7 +6943,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -7109,7 +7463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1001"/>
+  <dimension ref="A1:B2001"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="90.7777777777778" customWidth="1"/>
@@ -14735,271 +15089,4513 @@
       <c r="A953" s="2" t="s">
         <v>1899</v>
       </c>
-      <c r="B953" s="2"/>
+      <c r="B953" s="2" t="s">
+        <v>1900</v>
+      </c>
     </row>
     <row r="954" ht="25" customHeight="1" spans="1:2">
       <c r="A954" s="2" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B954" s="2"/>
+        <v>1901</v>
+      </c>
+      <c r="B954" s="2" t="s">
+        <v>1902</v>
+      </c>
     </row>
     <row r="955" ht="25" customHeight="1" spans="1:2">
       <c r="A955" s="2" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B955" s="2"/>
+        <v>1903</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>1904</v>
+      </c>
     </row>
     <row r="956" ht="25" customHeight="1" spans="1:2">
       <c r="A956" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="B956" s="2"/>
+        <v>1905</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>1906</v>
+      </c>
     </row>
     <row r="957" ht="25" customHeight="1" spans="1:2">
       <c r="A957" s="2" t="s">
-        <v>1903</v>
-      </c>
-      <c r="B957" s="2"/>
+        <v>1907</v>
+      </c>
+      <c r="B957" s="2" t="s">
+        <v>1908</v>
+      </c>
     </row>
     <row r="958" ht="25" customHeight="1" spans="1:2">
       <c r="A958" s="2" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B958" s="2"/>
+        <v>1909</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>1910</v>
+      </c>
     </row>
     <row r="959" ht="25" customHeight="1" spans="1:2">
       <c r="A959" s="2" t="s">
-        <v>1905</v>
-      </c>
-      <c r="B959" s="2"/>
+        <v>1911</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>1912</v>
+      </c>
     </row>
     <row r="960" ht="25" customHeight="1" spans="1:2">
       <c r="A960" s="2" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B960" s="2"/>
+        <v>1913</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>1914</v>
+      </c>
     </row>
     <row r="961" ht="25" customHeight="1" spans="1:2">
       <c r="A961" s="2" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B961" s="2"/>
+        <v>1915</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>1916</v>
+      </c>
     </row>
     <row r="962" ht="25" customHeight="1" spans="1:2">
       <c r="A962" s="2" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B962" s="2"/>
+        <v>1917</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>1918</v>
+      </c>
     </row>
     <row r="963" ht="25" customHeight="1" spans="1:2">
       <c r="A963" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B963" s="2"/>
+        <v>1919</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>1920</v>
+      </c>
     </row>
     <row r="964" ht="25" customHeight="1" spans="1:2">
       <c r="A964" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B964" s="2"/>
+        <v>1921</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>1922</v>
+      </c>
     </row>
     <row r="965" ht="25" customHeight="1" spans="1:2">
       <c r="A965" s="2" t="s">
-        <v>1911</v>
-      </c>
-      <c r="B965" s="2"/>
+        <v>1923</v>
+      </c>
+      <c r="B965" s="2" t="s">
+        <v>1924</v>
+      </c>
     </row>
     <row r="966" ht="25" customHeight="1" spans="1:2">
       <c r="A966" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B966" s="2"/>
+        <v>1925</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>1926</v>
+      </c>
     </row>
     <row r="967" ht="25" customHeight="1" spans="1:2">
       <c r="A967" s="2" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B967" s="2"/>
+        <v>1927</v>
+      </c>
+      <c r="B967" s="2" t="s">
+        <v>1928</v>
+      </c>
     </row>
     <row r="968" ht="25" customHeight="1" spans="1:2">
       <c r="A968" s="2" t="s">
-        <v>1914</v>
-      </c>
-      <c r="B968" s="2"/>
+        <v>1929</v>
+      </c>
+      <c r="B968" s="2" t="s">
+        <v>1930</v>
+      </c>
     </row>
     <row r="969" ht="25" customHeight="1" spans="1:2">
       <c r="A969" s="2" t="s">
-        <v>1915</v>
-      </c>
-      <c r="B969" s="2"/>
+        <v>1931</v>
+      </c>
+      <c r="B969" s="2" t="s">
+        <v>1932</v>
+      </c>
     </row>
     <row r="970" ht="25" customHeight="1" spans="1:2">
       <c r="A970" s="2" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B970" s="2"/>
+        <v>1933</v>
+      </c>
+      <c r="B970" s="2" t="s">
+        <v>1934</v>
+      </c>
     </row>
     <row r="971" ht="25" customHeight="1" spans="1:2">
       <c r="A971" s="2" t="s">
-        <v>1917</v>
-      </c>
-      <c r="B971" s="2"/>
+        <v>1935</v>
+      </c>
+      <c r="B971" s="2" t="s">
+        <v>1936</v>
+      </c>
     </row>
     <row r="972" ht="25" customHeight="1" spans="1:2">
       <c r="A972" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B972" s="2"/>
+        <v>1937</v>
+      </c>
+      <c r="B972" s="2" t="s">
+        <v>1938</v>
+      </c>
     </row>
     <row r="973" ht="25" customHeight="1" spans="1:2">
       <c r="A973" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="B973" s="2"/>
+        <v>1939</v>
+      </c>
+      <c r="B973" s="2" t="s">
+        <v>1940</v>
+      </c>
     </row>
     <row r="974" ht="25" customHeight="1" spans="1:2">
       <c r="A974" s="2" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B974" s="2"/>
+        <v>1941</v>
+      </c>
+      <c r="B974" s="2" t="s">
+        <v>1942</v>
+      </c>
     </row>
     <row r="975" ht="25" customHeight="1" spans="1:2">
       <c r="A975" s="2" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B975" s="2"/>
+        <v>1943</v>
+      </c>
+      <c r="B975" s="2" t="s">
+        <v>1944</v>
+      </c>
     </row>
     <row r="976" ht="25" customHeight="1" spans="1:2">
       <c r="A976" s="2" t="s">
-        <v>1922</v>
-      </c>
-      <c r="B976" s="2"/>
+        <v>1945</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>1946</v>
+      </c>
     </row>
     <row r="977" ht="25" customHeight="1" spans="1:2">
       <c r="A977" s="2" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B977" s="2"/>
+        <v>1947</v>
+      </c>
+      <c r="B977" s="2" t="s">
+        <v>1948</v>
+      </c>
     </row>
     <row r="978" ht="25" customHeight="1" spans="1:2">
       <c r="A978" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B978" s="2"/>
+        <v>1949</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>1950</v>
+      </c>
     </row>
     <row r="979" ht="25" customHeight="1" spans="1:2">
       <c r="A979" s="2" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B979" s="2"/>
+        <v>1951</v>
+      </c>
+      <c r="B979" s="2" t="s">
+        <v>1952</v>
+      </c>
     </row>
     <row r="980" ht="25" customHeight="1" spans="1:2">
       <c r="A980" s="2" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B980" s="2"/>
+        <v>1953</v>
+      </c>
+      <c r="B980" s="2" t="s">
+        <v>1954</v>
+      </c>
     </row>
     <row r="981" ht="25" customHeight="1" spans="1:2">
       <c r="A981" s="2" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B981" s="2"/>
+        <v>1955</v>
+      </c>
+      <c r="B981" s="2" t="s">
+        <v>1956</v>
+      </c>
     </row>
     <row r="982" ht="25" customHeight="1" spans="1:2">
       <c r="A982" s="2" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B982" s="2"/>
+        <v>1957</v>
+      </c>
+      <c r="B982" s="2" t="s">
+        <v>1958</v>
+      </c>
     </row>
     <row r="983" ht="25" customHeight="1" spans="1:2">
       <c r="A983" s="2" t="s">
-        <v>1929</v>
-      </c>
-      <c r="B983" s="2"/>
+        <v>1959</v>
+      </c>
+      <c r="B983" s="2" t="s">
+        <v>1960</v>
+      </c>
     </row>
     <row r="984" ht="25" customHeight="1" spans="1:2">
       <c r="A984" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B984" s="2"/>
+        <v>1961</v>
+      </c>
+      <c r="B984" s="2" t="s">
+        <v>1962</v>
+      </c>
     </row>
     <row r="985" ht="25" customHeight="1" spans="1:2">
       <c r="A985" s="2" t="s">
-        <v>1931</v>
-      </c>
-      <c r="B985" s="2"/>
+        <v>1963</v>
+      </c>
+      <c r="B985" s="2" t="s">
+        <v>1964</v>
+      </c>
     </row>
     <row r="986" ht="25" customHeight="1" spans="1:2">
       <c r="A986" s="2" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B986" s="2"/>
+        <v>1965</v>
+      </c>
+      <c r="B986" s="2" t="s">
+        <v>1966</v>
+      </c>
     </row>
     <row r="987" ht="25" customHeight="1" spans="1:2">
       <c r="A987" s="2" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B987" s="2"/>
+        <v>1967</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>1968</v>
+      </c>
     </row>
     <row r="988" ht="25" customHeight="1" spans="1:2">
       <c r="A988" s="2" t="s">
-        <v>1934</v>
-      </c>
-      <c r="B988" s="2"/>
+        <v>1969</v>
+      </c>
+      <c r="B988" s="2" t="s">
+        <v>1970</v>
+      </c>
     </row>
     <row r="989" ht="25" customHeight="1" spans="1:2">
       <c r="A989" s="2" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B989" s="2"/>
+        <v>1971</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>1972</v>
+      </c>
     </row>
     <row r="990" ht="25" customHeight="1" spans="1:2">
-      <c r="A990" s="2"/>
-      <c r="B990" s="2"/>
+      <c r="A990" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B990" s="2" t="s">
+        <v>1974</v>
+      </c>
     </row>
     <row r="991" ht="25" customHeight="1" spans="1:2">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
+      <c r="A991" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>1976</v>
+      </c>
     </row>
     <row r="992" ht="25" customHeight="1" spans="1:2">
-      <c r="A992" s="2"/>
-      <c r="B992" s="2"/>
+      <c r="A992" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>1978</v>
+      </c>
     </row>
     <row r="993" ht="25" customHeight="1" spans="1:2">
-      <c r="A993" s="2"/>
-      <c r="B993" s="2"/>
+      <c r="A993" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>1980</v>
+      </c>
     </row>
     <row r="994" ht="25" customHeight="1" spans="1:2">
-      <c r="A994" s="2"/>
-      <c r="B994" s="2"/>
+      <c r="A994" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B994" s="2" t="s">
+        <v>1982</v>
+      </c>
     </row>
     <row r="995" ht="25" customHeight="1" spans="1:2">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
+      <c r="A995" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>1984</v>
+      </c>
     </row>
     <row r="996" ht="25" customHeight="1" spans="1:2">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
+      <c r="A996" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B996" s="2" t="s">
+        <v>1986</v>
+      </c>
     </row>
     <row r="997" ht="25" customHeight="1" spans="1:2">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
+      <c r="A997" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>1988</v>
+      </c>
     </row>
     <row r="998" ht="25" customHeight="1" spans="1:2">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
+      <c r="A998" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B998" s="2" t="s">
+        <v>1990</v>
+      </c>
     </row>
     <row r="999" ht="25" customHeight="1" spans="1:2">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
+      <c r="A999" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>1992</v>
+      </c>
     </row>
     <row r="1000" ht="25" customHeight="1" spans="1:2">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
+      <c r="A1000" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1000" s="2" t="s">
+        <v>1994</v>
+      </c>
     </row>
     <row r="1001" ht="25" customHeight="1" spans="1:2">
-      <c r="A1001" s="2"/>
-      <c r="B1001" s="2"/>
+      <c r="A1001" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1002" ht="25" customHeight="1" spans="1:2">
+      <c r="A1002" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1002" s="2" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="1003" ht="25" customHeight="1" spans="1:2">
+      <c r="A1003" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1003" s="2" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1004" ht="25" customHeight="1" spans="1:2">
+      <c r="A1004" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1004" s="2" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="1005" ht="25" customHeight="1" spans="1:2">
+      <c r="A1005" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1005" s="2" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1006" ht="25" customHeight="1" spans="1:2">
+      <c r="A1006" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1007" ht="25" customHeight="1" spans="1:2">
+      <c r="A1007" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1007" s="2" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="1008" ht="25" customHeight="1" spans="1:2">
+      <c r="A1008" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1008" s="2" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1009" ht="25" customHeight="1" spans="1:2">
+      <c r="A1009" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1009" s="2" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1010" ht="25" customHeight="1" spans="1:2">
+      <c r="A1010" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1010" s="2" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="1011" ht="25" customHeight="1" spans="1:2">
+      <c r="A1011" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1011" s="2" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="1012" ht="25" customHeight="1" spans="1:2">
+      <c r="A1012" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B1012" s="2" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="1013" ht="25" customHeight="1" spans="1:2">
+      <c r="A1013" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B1013" s="2" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="1014" ht="25" customHeight="1" spans="1:2">
+      <c r="A1014" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1014" s="2" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1015" ht="25" customHeight="1" spans="1:2">
+      <c r="A1015" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B1015" s="2" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1016" ht="25" customHeight="1" spans="1:2">
+      <c r="A1016" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1016" s="2" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1017" ht="25" customHeight="1" spans="1:2">
+      <c r="A1017" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B1017" s="2" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="1018" ht="25" customHeight="1" spans="1:2">
+      <c r="A1018" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1018" s="2" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="1019" ht="25" customHeight="1" spans="1:2">
+      <c r="A1019" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B1019" s="2" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="1020" ht="25" customHeight="1" spans="1:2">
+      <c r="A1020" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B1020" s="2" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="1021" ht="25" customHeight="1" spans="1:2">
+      <c r="A1021" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B1021" s="2" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1022" ht="25" customHeight="1" spans="1:2">
+      <c r="A1022" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B1022" s="2" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="1023" ht="25" customHeight="1" spans="1:2">
+      <c r="A1023" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1023" s="2" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="1024" ht="25" customHeight="1" spans="1:2">
+      <c r="A1024" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1024" s="2" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="1025" ht="25" customHeight="1" spans="1:2">
+      <c r="A1025" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1025" s="2" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="1026" ht="25" customHeight="1" spans="1:2">
+      <c r="A1026" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B1026" s="2" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="1027" ht="25" customHeight="1" spans="1:2">
+      <c r="A1027" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B1027" s="2" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="1028" ht="25" customHeight="1" spans="1:2">
+      <c r="A1028" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1028" s="2" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="1029" ht="25" customHeight="1" spans="1:2">
+      <c r="A1029" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1029" s="2" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="1030" ht="25" customHeight="1" spans="1:2">
+      <c r="A1030" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B1030" s="2" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1031" ht="25" customHeight="1" spans="1:2">
+      <c r="A1031" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B1031" s="2" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="1032" ht="25" customHeight="1" spans="1:2">
+      <c r="A1032" s="2"/>
+      <c r="B1032" s="2"/>
+    </row>
+    <row r="1033" ht="25" customHeight="1" spans="1:2">
+      <c r="A1033" s="2"/>
+      <c r="B1033" s="2"/>
+    </row>
+    <row r="1034" ht="25" customHeight="1" spans="1:2">
+      <c r="A1034" s="2"/>
+      <c r="B1034" s="2"/>
+    </row>
+    <row r="1035" ht="25" customHeight="1" spans="1:2">
+      <c r="A1035" s="2"/>
+      <c r="B1035" s="2"/>
+    </row>
+    <row r="1036" ht="25" customHeight="1" spans="1:2">
+      <c r="A1036" s="2"/>
+      <c r="B1036" s="2"/>
+    </row>
+    <row r="1037" ht="25" customHeight="1" spans="1:2">
+      <c r="A1037" s="2"/>
+      <c r="B1037" s="2"/>
+    </row>
+    <row r="1038" ht="25" customHeight="1" spans="1:2">
+      <c r="A1038" s="2"/>
+      <c r="B1038" s="2"/>
+    </row>
+    <row r="1039" ht="25" customHeight="1" spans="1:2">
+      <c r="A1039" s="2"/>
+      <c r="B1039" s="2"/>
+    </row>
+    <row r="1040" ht="25" customHeight="1" spans="1:2">
+      <c r="A1040" s="2"/>
+      <c r="B1040" s="2"/>
+    </row>
+    <row r="1041" ht="25" customHeight="1" spans="1:2">
+      <c r="A1041" s="2"/>
+      <c r="B1041" s="2"/>
+    </row>
+    <row r="1042" ht="25" customHeight="1" spans="1:2">
+      <c r="A1042" s="2"/>
+      <c r="B1042" s="2"/>
+    </row>
+    <row r="1043" ht="25" customHeight="1" spans="1:2">
+      <c r="A1043" s="2"/>
+      <c r="B1043" s="2"/>
+    </row>
+    <row r="1044" ht="25" customHeight="1" spans="1:2">
+      <c r="A1044" s="2"/>
+      <c r="B1044" s="2"/>
+    </row>
+    <row r="1045" ht="25" customHeight="1" spans="1:2">
+      <c r="A1045" s="2"/>
+      <c r="B1045" s="2"/>
+    </row>
+    <row r="1046" ht="25" customHeight="1" spans="1:2">
+      <c r="A1046" s="2"/>
+      <c r="B1046" s="2"/>
+    </row>
+    <row r="1047" ht="25" customHeight="1" spans="1:2">
+      <c r="A1047" s="2"/>
+      <c r="B1047" s="2"/>
+    </row>
+    <row r="1048" ht="25" customHeight="1" spans="1:2">
+      <c r="A1048" s="2"/>
+      <c r="B1048" s="2"/>
+    </row>
+    <row r="1049" ht="25" customHeight="1" spans="1:2">
+      <c r="A1049" s="2"/>
+      <c r="B1049" s="2"/>
+    </row>
+    <row r="1050" ht="25" customHeight="1" spans="1:2">
+      <c r="A1050" s="2"/>
+      <c r="B1050" s="2"/>
+    </row>
+    <row r="1051" ht="25" customHeight="1" spans="1:2">
+      <c r="A1051" s="2"/>
+      <c r="B1051" s="2"/>
+    </row>
+    <row r="1052" ht="25" customHeight="1" spans="1:2">
+      <c r="A1052" s="2"/>
+      <c r="B1052" s="2"/>
+    </row>
+    <row r="1053" ht="25" customHeight="1" spans="1:2">
+      <c r="A1053" s="2"/>
+      <c r="B1053" s="2"/>
+    </row>
+    <row r="1054" ht="25" customHeight="1" spans="1:2">
+      <c r="A1054" s="2"/>
+      <c r="B1054" s="2"/>
+    </row>
+    <row r="1055" ht="25" customHeight="1" spans="1:2">
+      <c r="A1055" s="2"/>
+      <c r="B1055" s="2"/>
+    </row>
+    <row r="1056" ht="25" customHeight="1" spans="1:2">
+      <c r="A1056" s="2"/>
+      <c r="B1056" s="2"/>
+    </row>
+    <row r="1057" ht="25" customHeight="1" spans="1:2">
+      <c r="A1057" s="2"/>
+      <c r="B1057" s="2"/>
+    </row>
+    <row r="1058" ht="25" customHeight="1" spans="1:2">
+      <c r="A1058" s="2"/>
+      <c r="B1058" s="2"/>
+    </row>
+    <row r="1059" ht="25" customHeight="1" spans="1:2">
+      <c r="A1059" s="2"/>
+      <c r="B1059" s="2"/>
+    </row>
+    <row r="1060" ht="25" customHeight="1" spans="1:2">
+      <c r="A1060" s="2"/>
+      <c r="B1060" s="2"/>
+    </row>
+    <row r="1061" ht="25" customHeight="1" spans="1:2">
+      <c r="A1061" s="2"/>
+      <c r="B1061" s="2"/>
+    </row>
+    <row r="1062" ht="25" customHeight="1" spans="1:2">
+      <c r="A1062" s="2"/>
+      <c r="B1062" s="2"/>
+    </row>
+    <row r="1063" ht="25" customHeight="1" spans="1:2">
+      <c r="A1063" s="2"/>
+      <c r="B1063" s="2"/>
+    </row>
+    <row r="1064" ht="25" customHeight="1" spans="1:2">
+      <c r="A1064" s="2"/>
+      <c r="B1064" s="2"/>
+    </row>
+    <row r="1065" ht="25" customHeight="1" spans="1:2">
+      <c r="A1065" s="2"/>
+      <c r="B1065" s="2"/>
+    </row>
+    <row r="1066" ht="25" customHeight="1" spans="1:2">
+      <c r="A1066" s="2"/>
+      <c r="B1066" s="2"/>
+    </row>
+    <row r="1067" ht="25" customHeight="1" spans="1:2">
+      <c r="A1067" s="2"/>
+      <c r="B1067" s="2"/>
+    </row>
+    <row r="1068" ht="25" customHeight="1" spans="1:2">
+      <c r="A1068" s="2"/>
+      <c r="B1068" s="2"/>
+    </row>
+    <row r="1069" ht="25" customHeight="1" spans="1:2">
+      <c r="A1069" s="2"/>
+      <c r="B1069" s="2"/>
+    </row>
+    <row r="1070" ht="25" customHeight="1" spans="1:2">
+      <c r="A1070" s="2"/>
+      <c r="B1070" s="2"/>
+    </row>
+    <row r="1071" ht="25" customHeight="1" spans="1:2">
+      <c r="A1071" s="2"/>
+      <c r="B1071" s="2"/>
+    </row>
+    <row r="1072" ht="25" customHeight="1" spans="1:2">
+      <c r="A1072" s="2"/>
+      <c r="B1072" s="2"/>
+    </row>
+    <row r="1073" ht="25" customHeight="1" spans="1:2">
+      <c r="A1073" s="2"/>
+      <c r="B1073" s="2"/>
+    </row>
+    <row r="1074" ht="25" customHeight="1" spans="1:2">
+      <c r="A1074" s="2"/>
+      <c r="B1074" s="2"/>
+    </row>
+    <row r="1075" ht="25" customHeight="1" spans="1:2">
+      <c r="A1075" s="2"/>
+      <c r="B1075" s="2"/>
+    </row>
+    <row r="1076" ht="25" customHeight="1" spans="1:2">
+      <c r="A1076" s="2"/>
+      <c r="B1076" s="2"/>
+    </row>
+    <row r="1077" ht="25" customHeight="1" spans="1:2">
+      <c r="A1077" s="2"/>
+      <c r="B1077" s="2"/>
+    </row>
+    <row r="1078" ht="25" customHeight="1" spans="1:2">
+      <c r="A1078" s="2"/>
+      <c r="B1078" s="2"/>
+    </row>
+    <row r="1079" ht="25" customHeight="1" spans="1:2">
+      <c r="A1079" s="2"/>
+      <c r="B1079" s="2"/>
+    </row>
+    <row r="1080" ht="25" customHeight="1" spans="1:2">
+      <c r="A1080" s="2"/>
+      <c r="B1080" s="2"/>
+    </row>
+    <row r="1081" ht="25" customHeight="1" spans="1:2">
+      <c r="A1081" s="2"/>
+      <c r="B1081" s="2"/>
+    </row>
+    <row r="1082" ht="25" customHeight="1" spans="1:2">
+      <c r="A1082" s="2"/>
+      <c r="B1082" s="2"/>
+    </row>
+    <row r="1083" ht="25" customHeight="1" spans="1:2">
+      <c r="A1083" s="2"/>
+      <c r="B1083" s="2"/>
+    </row>
+    <row r="1084" ht="25" customHeight="1" spans="1:2">
+      <c r="A1084" s="2"/>
+      <c r="B1084" s="2"/>
+    </row>
+    <row r="1085" ht="25" customHeight="1" spans="1:2">
+      <c r="A1085" s="2"/>
+      <c r="B1085" s="2"/>
+    </row>
+    <row r="1086" ht="25" customHeight="1" spans="1:2">
+      <c r="A1086" s="2"/>
+      <c r="B1086" s="2"/>
+    </row>
+    <row r="1087" ht="25" customHeight="1" spans="1:2">
+      <c r="A1087" s="2"/>
+      <c r="B1087" s="2"/>
+    </row>
+    <row r="1088" ht="25" customHeight="1" spans="1:2">
+      <c r="A1088" s="2"/>
+      <c r="B1088" s="2"/>
+    </row>
+    <row r="1089" ht="25" customHeight="1" spans="1:2">
+      <c r="A1089" s="2"/>
+      <c r="B1089" s="2"/>
+    </row>
+    <row r="1090" ht="25" customHeight="1" spans="1:2">
+      <c r="A1090" s="2"/>
+      <c r="B1090" s="2"/>
+    </row>
+    <row r="1091" ht="25" customHeight="1" spans="1:2">
+      <c r="A1091" s="2"/>
+      <c r="B1091" s="2"/>
+    </row>
+    <row r="1092" ht="25" customHeight="1" spans="1:2">
+      <c r="A1092" s="2"/>
+      <c r="B1092" s="2"/>
+    </row>
+    <row r="1093" ht="25" customHeight="1" spans="1:2">
+      <c r="A1093" s="2"/>
+      <c r="B1093" s="2"/>
+    </row>
+    <row r="1094" ht="25" customHeight="1" spans="1:2">
+      <c r="A1094" s="2"/>
+      <c r="B1094" s="2"/>
+    </row>
+    <row r="1095" ht="25" customHeight="1" spans="1:2">
+      <c r="A1095" s="2"/>
+      <c r="B1095" s="2"/>
+    </row>
+    <row r="1096" ht="25" customHeight="1" spans="1:2">
+      <c r="A1096" s="2"/>
+      <c r="B1096" s="2"/>
+    </row>
+    <row r="1097" ht="25" customHeight="1" spans="1:2">
+      <c r="A1097" s="2"/>
+      <c r="B1097" s="2"/>
+    </row>
+    <row r="1098" ht="25" customHeight="1" spans="1:2">
+      <c r="A1098" s="2"/>
+      <c r="B1098" s="2"/>
+    </row>
+    <row r="1099" ht="25" customHeight="1" spans="1:2">
+      <c r="A1099" s="2"/>
+      <c r="B1099" s="2"/>
+    </row>
+    <row r="1100" ht="25" customHeight="1" spans="1:2">
+      <c r="A1100" s="2"/>
+      <c r="B1100" s="2"/>
+    </row>
+    <row r="1101" ht="25" customHeight="1" spans="1:2">
+      <c r="A1101" s="2"/>
+      <c r="B1101" s="2"/>
+    </row>
+    <row r="1102" ht="25" customHeight="1" spans="1:2">
+      <c r="A1102" s="2"/>
+      <c r="B1102" s="2"/>
+    </row>
+    <row r="1103" ht="25" customHeight="1" spans="1:2">
+      <c r="A1103" s="2"/>
+      <c r="B1103" s="2"/>
+    </row>
+    <row r="1104" ht="25" customHeight="1" spans="1:2">
+      <c r="A1104" s="2"/>
+      <c r="B1104" s="2"/>
+    </row>
+    <row r="1105" ht="25" customHeight="1" spans="1:2">
+      <c r="A1105" s="2"/>
+      <c r="B1105" s="2"/>
+    </row>
+    <row r="1106" ht="25" customHeight="1" spans="1:2">
+      <c r="A1106" s="2"/>
+      <c r="B1106" s="2"/>
+    </row>
+    <row r="1107" ht="25" customHeight="1" spans="1:2">
+      <c r="A1107" s="2"/>
+      <c r="B1107" s="2"/>
+    </row>
+    <row r="1108" ht="25" customHeight="1" spans="1:2">
+      <c r="A1108" s="2"/>
+      <c r="B1108" s="2"/>
+    </row>
+    <row r="1109" ht="25" customHeight="1" spans="1:2">
+      <c r="A1109" s="2"/>
+      <c r="B1109" s="2"/>
+    </row>
+    <row r="1110" ht="25" customHeight="1" spans="1:2">
+      <c r="A1110" s="2"/>
+      <c r="B1110" s="2"/>
+    </row>
+    <row r="1111" ht="25" customHeight="1" spans="1:2">
+      <c r="A1111" s="2"/>
+      <c r="B1111" s="2"/>
+    </row>
+    <row r="1112" ht="25" customHeight="1" spans="1:2">
+      <c r="A1112" s="2"/>
+      <c r="B1112" s="2"/>
+    </row>
+    <row r="1113" ht="25" customHeight="1" spans="1:2">
+      <c r="A1113" s="2"/>
+      <c r="B1113" s="2"/>
+    </row>
+    <row r="1114" ht="25" customHeight="1" spans="1:2">
+      <c r="A1114" s="2"/>
+      <c r="B1114" s="2"/>
+    </row>
+    <row r="1115" ht="25" customHeight="1" spans="1:2">
+      <c r="A1115" s="2"/>
+      <c r="B1115" s="2"/>
+    </row>
+    <row r="1116" ht="25" customHeight="1" spans="1:2">
+      <c r="A1116" s="2"/>
+      <c r="B1116" s="2"/>
+    </row>
+    <row r="1117" ht="25" customHeight="1" spans="1:2">
+      <c r="A1117" s="2"/>
+      <c r="B1117" s="2"/>
+    </row>
+    <row r="1118" ht="25" customHeight="1" spans="1:2">
+      <c r="A1118" s="2"/>
+      <c r="B1118" s="2"/>
+    </row>
+    <row r="1119" ht="25" customHeight="1" spans="1:2">
+      <c r="A1119" s="2"/>
+      <c r="B1119" s="2"/>
+    </row>
+    <row r="1120" ht="25" customHeight="1" spans="1:2">
+      <c r="A1120" s="2"/>
+      <c r="B1120" s="2"/>
+    </row>
+    <row r="1121" ht="25" customHeight="1" spans="1:2">
+      <c r="A1121" s="2"/>
+      <c r="B1121" s="2"/>
+    </row>
+    <row r="1122" ht="25" customHeight="1" spans="1:2">
+      <c r="A1122" s="2"/>
+      <c r="B1122" s="2"/>
+    </row>
+    <row r="1123" ht="25" customHeight="1" spans="1:2">
+      <c r="A1123" s="2"/>
+      <c r="B1123" s="2"/>
+    </row>
+    <row r="1124" ht="25" customHeight="1" spans="1:2">
+      <c r="A1124" s="2"/>
+      <c r="B1124" s="2"/>
+    </row>
+    <row r="1125" ht="25" customHeight="1" spans="1:2">
+      <c r="A1125" s="2"/>
+      <c r="B1125" s="2"/>
+    </row>
+    <row r="1126" ht="25" customHeight="1" spans="1:2">
+      <c r="A1126" s="2"/>
+      <c r="B1126" s="2"/>
+    </row>
+    <row r="1127" ht="25" customHeight="1" spans="1:2">
+      <c r="A1127" s="2"/>
+      <c r="B1127" s="2"/>
+    </row>
+    <row r="1128" ht="25" customHeight="1" spans="1:2">
+      <c r="A1128" s="2"/>
+      <c r="B1128" s="2"/>
+    </row>
+    <row r="1129" ht="25" customHeight="1" spans="1:2">
+      <c r="A1129" s="2"/>
+      <c r="B1129" s="2"/>
+    </row>
+    <row r="1130" ht="25" customHeight="1" spans="1:2">
+      <c r="A1130" s="2"/>
+      <c r="B1130" s="2"/>
+    </row>
+    <row r="1131" ht="25" customHeight="1" spans="1:2">
+      <c r="A1131" s="2"/>
+      <c r="B1131" s="2"/>
+    </row>
+    <row r="1132" ht="25" customHeight="1" spans="1:2">
+      <c r="A1132" s="2"/>
+      <c r="B1132" s="2"/>
+    </row>
+    <row r="1133" ht="25" customHeight="1" spans="1:2">
+      <c r="A1133" s="2"/>
+      <c r="B1133" s="2"/>
+    </row>
+    <row r="1134" ht="25" customHeight="1" spans="1:2">
+      <c r="A1134" s="2"/>
+      <c r="B1134" s="2"/>
+    </row>
+    <row r="1135" ht="25" customHeight="1" spans="1:2">
+      <c r="A1135" s="2"/>
+      <c r="B1135" s="2"/>
+    </row>
+    <row r="1136" ht="25" customHeight="1" spans="1:2">
+      <c r="A1136" s="2"/>
+      <c r="B1136" s="2"/>
+    </row>
+    <row r="1137" ht="25" customHeight="1" spans="1:2">
+      <c r="A1137" s="2"/>
+      <c r="B1137" s="2"/>
+    </row>
+    <row r="1138" ht="25" customHeight="1" spans="1:2">
+      <c r="A1138" s="2"/>
+      <c r="B1138" s="2"/>
+    </row>
+    <row r="1139" ht="25" customHeight="1" spans="1:2">
+      <c r="A1139" s="2"/>
+      <c r="B1139" s="2"/>
+    </row>
+    <row r="1140" ht="25" customHeight="1" spans="1:2">
+      <c r="A1140" s="2"/>
+      <c r="B1140" s="2"/>
+    </row>
+    <row r="1141" ht="25" customHeight="1" spans="1:2">
+      <c r="A1141" s="2"/>
+      <c r="B1141" s="2"/>
+    </row>
+    <row r="1142" ht="25" customHeight="1" spans="1:2">
+      <c r="A1142" s="2"/>
+      <c r="B1142" s="2"/>
+    </row>
+    <row r="1143" ht="25" customHeight="1" spans="1:2">
+      <c r="A1143" s="2"/>
+      <c r="B1143" s="2"/>
+    </row>
+    <row r="1144" ht="25" customHeight="1" spans="1:2">
+      <c r="A1144" s="2"/>
+      <c r="B1144" s="2"/>
+    </row>
+    <row r="1145" ht="25" customHeight="1" spans="1:2">
+      <c r="A1145" s="2"/>
+      <c r="B1145" s="2"/>
+    </row>
+    <row r="1146" ht="25" customHeight="1" spans="1:2">
+      <c r="A1146" s="2"/>
+      <c r="B1146" s="2"/>
+    </row>
+    <row r="1147" ht="25" customHeight="1" spans="1:2">
+      <c r="A1147" s="2"/>
+      <c r="B1147" s="2"/>
+    </row>
+    <row r="1148" ht="25" customHeight="1" spans="1:2">
+      <c r="A1148" s="2"/>
+      <c r="B1148" s="2"/>
+    </row>
+    <row r="1149" ht="25" customHeight="1" spans="1:2">
+      <c r="A1149" s="2"/>
+      <c r="B1149" s="2"/>
+    </row>
+    <row r="1150" ht="25" customHeight="1" spans="1:2">
+      <c r="A1150" s="2"/>
+      <c r="B1150" s="2"/>
+    </row>
+    <row r="1151" ht="25" customHeight="1" spans="1:2">
+      <c r="A1151" s="2"/>
+      <c r="B1151" s="2"/>
+    </row>
+    <row r="1152" ht="25" customHeight="1" spans="1:2">
+      <c r="A1152" s="2"/>
+      <c r="B1152" s="2"/>
+    </row>
+    <row r="1153" ht="25" customHeight="1" spans="1:2">
+      <c r="A1153" s="2"/>
+      <c r="B1153" s="2"/>
+    </row>
+    <row r="1154" ht="25" customHeight="1" spans="1:2">
+      <c r="A1154" s="2"/>
+      <c r="B1154" s="2"/>
+    </row>
+    <row r="1155" ht="25" customHeight="1" spans="1:2">
+      <c r="A1155" s="2"/>
+      <c r="B1155" s="2"/>
+    </row>
+    <row r="1156" ht="25" customHeight="1" spans="1:2">
+      <c r="A1156" s="2"/>
+      <c r="B1156" s="2"/>
+    </row>
+    <row r="1157" ht="25" customHeight="1" spans="1:2">
+      <c r="A1157" s="2"/>
+      <c r="B1157" s="2"/>
+    </row>
+    <row r="1158" ht="25" customHeight="1" spans="1:2">
+      <c r="A1158" s="2"/>
+      <c r="B1158" s="2"/>
+    </row>
+    <row r="1159" ht="25" customHeight="1" spans="1:2">
+      <c r="A1159" s="2"/>
+      <c r="B1159" s="2"/>
+    </row>
+    <row r="1160" ht="25" customHeight="1" spans="1:2">
+      <c r="A1160" s="2"/>
+      <c r="B1160" s="2"/>
+    </row>
+    <row r="1161" ht="25" customHeight="1" spans="1:2">
+      <c r="A1161" s="2"/>
+      <c r="B1161" s="2"/>
+    </row>
+    <row r="1162" ht="25" customHeight="1" spans="1:2">
+      <c r="A1162" s="2"/>
+      <c r="B1162" s="2"/>
+    </row>
+    <row r="1163" ht="25" customHeight="1" spans="1:2">
+      <c r="A1163" s="2"/>
+      <c r="B1163" s="2"/>
+    </row>
+    <row r="1164" ht="25" customHeight="1" spans="1:2">
+      <c r="A1164" s="2"/>
+      <c r="B1164" s="2"/>
+    </row>
+    <row r="1165" ht="25" customHeight="1" spans="1:2">
+      <c r="A1165" s="2"/>
+      <c r="B1165" s="2"/>
+    </row>
+    <row r="1166" ht="25" customHeight="1" spans="1:2">
+      <c r="A1166" s="2"/>
+      <c r="B1166" s="2"/>
+    </row>
+    <row r="1167" ht="25" customHeight="1" spans="1:2">
+      <c r="A1167" s="2"/>
+      <c r="B1167" s="2"/>
+    </row>
+    <row r="1168" ht="25" customHeight="1" spans="1:2">
+      <c r="A1168" s="2"/>
+      <c r="B1168" s="2"/>
+    </row>
+    <row r="1169" ht="25" customHeight="1" spans="1:2">
+      <c r="A1169" s="2"/>
+      <c r="B1169" s="2"/>
+    </row>
+    <row r="1170" ht="25" customHeight="1" spans="1:2">
+      <c r="A1170" s="2"/>
+      <c r="B1170" s="2"/>
+    </row>
+    <row r="1171" ht="25" customHeight="1" spans="1:2">
+      <c r="A1171" s="2"/>
+      <c r="B1171" s="2"/>
+    </row>
+    <row r="1172" ht="25" customHeight="1" spans="1:2">
+      <c r="A1172" s="2"/>
+      <c r="B1172" s="2"/>
+    </row>
+    <row r="1173" ht="25" customHeight="1" spans="1:2">
+      <c r="A1173" s="2"/>
+      <c r="B1173" s="2"/>
+    </row>
+    <row r="1174" ht="25" customHeight="1" spans="1:2">
+      <c r="A1174" s="2"/>
+      <c r="B1174" s="2"/>
+    </row>
+    <row r="1175" ht="25" customHeight="1" spans="1:2">
+      <c r="A1175" s="2"/>
+      <c r="B1175" s="2"/>
+    </row>
+    <row r="1176" ht="25" customHeight="1" spans="1:2">
+      <c r="A1176" s="2"/>
+      <c r="B1176" s="2"/>
+    </row>
+    <row r="1177" ht="25" customHeight="1" spans="1:2">
+      <c r="A1177" s="2"/>
+      <c r="B1177" s="2"/>
+    </row>
+    <row r="1178" ht="25" customHeight="1" spans="1:2">
+      <c r="A1178" s="2"/>
+      <c r="B1178" s="2"/>
+    </row>
+    <row r="1179" ht="25" customHeight="1" spans="1:2">
+      <c r="A1179" s="2"/>
+      <c r="B1179" s="2"/>
+    </row>
+    <row r="1180" ht="25" customHeight="1" spans="1:2">
+      <c r="A1180" s="2"/>
+      <c r="B1180" s="2"/>
+    </row>
+    <row r="1181" ht="25" customHeight="1" spans="1:2">
+      <c r="A1181" s="2"/>
+      <c r="B1181" s="2"/>
+    </row>
+    <row r="1182" ht="25" customHeight="1" spans="1:2">
+      <c r="A1182" s="2"/>
+      <c r="B1182" s="2"/>
+    </row>
+    <row r="1183" ht="25" customHeight="1" spans="1:2">
+      <c r="A1183" s="2"/>
+      <c r="B1183" s="2"/>
+    </row>
+    <row r="1184" ht="25" customHeight="1" spans="1:2">
+      <c r="A1184" s="2"/>
+      <c r="B1184" s="2"/>
+    </row>
+    <row r="1185" ht="25" customHeight="1" spans="1:2">
+      <c r="A1185" s="2"/>
+      <c r="B1185" s="2"/>
+    </row>
+    <row r="1186" ht="25" customHeight="1" spans="1:2">
+      <c r="A1186" s="2"/>
+      <c r="B1186" s="2"/>
+    </row>
+    <row r="1187" ht="25" customHeight="1" spans="1:2">
+      <c r="A1187" s="2"/>
+      <c r="B1187" s="2"/>
+    </row>
+    <row r="1188" ht="25" customHeight="1" spans="1:2">
+      <c r="A1188" s="2"/>
+      <c r="B1188" s="2"/>
+    </row>
+    <row r="1189" ht="25" customHeight="1" spans="1:2">
+      <c r="A1189" s="2"/>
+      <c r="B1189" s="2"/>
+    </row>
+    <row r="1190" ht="25" customHeight="1" spans="1:2">
+      <c r="A1190" s="2"/>
+      <c r="B1190" s="2"/>
+    </row>
+    <row r="1191" ht="25" customHeight="1" spans="1:2">
+      <c r="A1191" s="2"/>
+      <c r="B1191" s="2"/>
+    </row>
+    <row r="1192" ht="25" customHeight="1" spans="1:2">
+      <c r="A1192" s="2"/>
+      <c r="B1192" s="2"/>
+    </row>
+    <row r="1193" ht="25" customHeight="1" spans="1:2">
+      <c r="A1193" s="2"/>
+      <c r="B1193" s="2"/>
+    </row>
+    <row r="1194" ht="25" customHeight="1" spans="1:2">
+      <c r="A1194" s="2"/>
+      <c r="B1194" s="2"/>
+    </row>
+    <row r="1195" ht="25" customHeight="1" spans="1:2">
+      <c r="A1195" s="2"/>
+      <c r="B1195" s="2"/>
+    </row>
+    <row r="1196" ht="25" customHeight="1" spans="1:2">
+      <c r="A1196" s="2"/>
+      <c r="B1196" s="2"/>
+    </row>
+    <row r="1197" ht="25" customHeight="1" spans="1:2">
+      <c r="A1197" s="2"/>
+      <c r="B1197" s="2"/>
+    </row>
+    <row r="1198" ht="25" customHeight="1" spans="1:2">
+      <c r="A1198" s="2"/>
+      <c r="B1198" s="2"/>
+    </row>
+    <row r="1199" ht="25" customHeight="1" spans="1:2">
+      <c r="A1199" s="2"/>
+      <c r="B1199" s="2"/>
+    </row>
+    <row r="1200" ht="25" customHeight="1" spans="1:2">
+      <c r="A1200" s="2"/>
+      <c r="B1200" s="2"/>
+    </row>
+    <row r="1201" ht="25" customHeight="1" spans="1:2">
+      <c r="A1201" s="2"/>
+      <c r="B1201" s="2"/>
+    </row>
+    <row r="1202" ht="25" customHeight="1" spans="1:2">
+      <c r="A1202" s="2"/>
+      <c r="B1202" s="2"/>
+    </row>
+    <row r="1203" ht="25" customHeight="1" spans="1:2">
+      <c r="A1203" s="2"/>
+      <c r="B1203" s="2"/>
+    </row>
+    <row r="1204" ht="25" customHeight="1" spans="1:2">
+      <c r="A1204" s="2"/>
+      <c r="B1204" s="2"/>
+    </row>
+    <row r="1205" ht="25" customHeight="1" spans="1:2">
+      <c r="A1205" s="2"/>
+      <c r="B1205" s="2"/>
+    </row>
+    <row r="1206" ht="25" customHeight="1" spans="1:2">
+      <c r="A1206" s="2"/>
+      <c r="B1206" s="2"/>
+    </row>
+    <row r="1207" ht="25" customHeight="1" spans="1:2">
+      <c r="A1207" s="2"/>
+      <c r="B1207" s="2"/>
+    </row>
+    <row r="1208" ht="25" customHeight="1" spans="1:2">
+      <c r="A1208" s="2"/>
+      <c r="B1208" s="2"/>
+    </row>
+    <row r="1209" ht="25" customHeight="1" spans="1:2">
+      <c r="A1209" s="2"/>
+      <c r="B1209" s="2"/>
+    </row>
+    <row r="1210" ht="25" customHeight="1" spans="1:2">
+      <c r="A1210" s="2"/>
+      <c r="B1210" s="2"/>
+    </row>
+    <row r="1211" ht="25" customHeight="1" spans="1:2">
+      <c r="A1211" s="2"/>
+      <c r="B1211" s="2"/>
+    </row>
+    <row r="1212" ht="25" customHeight="1" spans="1:2">
+      <c r="A1212" s="2"/>
+      <c r="B1212" s="2"/>
+    </row>
+    <row r="1213" ht="25" customHeight="1" spans="1:2">
+      <c r="A1213" s="2"/>
+      <c r="B1213" s="2"/>
+    </row>
+    <row r="1214" ht="25" customHeight="1" spans="1:2">
+      <c r="A1214" s="2"/>
+      <c r="B1214" s="2"/>
+    </row>
+    <row r="1215" ht="25" customHeight="1" spans="1:2">
+      <c r="A1215" s="2"/>
+      <c r="B1215" s="2"/>
+    </row>
+    <row r="1216" ht="25" customHeight="1" spans="1:2">
+      <c r="A1216" s="2"/>
+      <c r="B1216" s="2"/>
+    </row>
+    <row r="1217" ht="25" customHeight="1" spans="1:2">
+      <c r="A1217" s="2"/>
+      <c r="B1217" s="2"/>
+    </row>
+    <row r="1218" ht="25" customHeight="1" spans="1:2">
+      <c r="A1218" s="2"/>
+      <c r="B1218" s="2"/>
+    </row>
+    <row r="1219" ht="25" customHeight="1" spans="1:2">
+      <c r="A1219" s="2"/>
+      <c r="B1219" s="2"/>
+    </row>
+    <row r="1220" ht="25" customHeight="1" spans="1:2">
+      <c r="A1220" s="2"/>
+      <c r="B1220" s="2"/>
+    </row>
+    <row r="1221" ht="25" customHeight="1" spans="1:2">
+      <c r="A1221" s="2"/>
+      <c r="B1221" s="2"/>
+    </row>
+    <row r="1222" ht="25" customHeight="1" spans="1:2">
+      <c r="A1222" s="2"/>
+      <c r="B1222" s="2"/>
+    </row>
+    <row r="1223" ht="25" customHeight="1" spans="1:2">
+      <c r="A1223" s="2"/>
+      <c r="B1223" s="2"/>
+    </row>
+    <row r="1224" ht="25" customHeight="1" spans="1:2">
+      <c r="A1224" s="2"/>
+      <c r="B1224" s="2"/>
+    </row>
+    <row r="1225" ht="25" customHeight="1" spans="1:2">
+      <c r="A1225" s="2"/>
+      <c r="B1225" s="2"/>
+    </row>
+    <row r="1226" ht="25" customHeight="1" spans="1:2">
+      <c r="A1226" s="2"/>
+      <c r="B1226" s="2"/>
+    </row>
+    <row r="1227" ht="25" customHeight="1" spans="1:2">
+      <c r="A1227" s="2"/>
+      <c r="B1227" s="2"/>
+    </row>
+    <row r="1228" ht="25" customHeight="1" spans="1:2">
+      <c r="A1228" s="2"/>
+      <c r="B1228" s="2"/>
+    </row>
+    <row r="1229" ht="25" customHeight="1" spans="1:2">
+      <c r="A1229" s="2"/>
+      <c r="B1229" s="2"/>
+    </row>
+    <row r="1230" ht="25" customHeight="1" spans="1:2">
+      <c r="A1230" s="2"/>
+      <c r="B1230" s="2"/>
+    </row>
+    <row r="1231" ht="25" customHeight="1" spans="1:2">
+      <c r="A1231" s="2"/>
+      <c r="B1231" s="2"/>
+    </row>
+    <row r="1232" ht="25" customHeight="1" spans="1:2">
+      <c r="A1232" s="2"/>
+      <c r="B1232" s="2"/>
+    </row>
+    <row r="1233" ht="25" customHeight="1" spans="1:2">
+      <c r="A1233" s="2"/>
+      <c r="B1233" s="2"/>
+    </row>
+    <row r="1234" ht="25" customHeight="1" spans="1:2">
+      <c r="A1234" s="2"/>
+      <c r="B1234" s="2"/>
+    </row>
+    <row r="1235" ht="25" customHeight="1" spans="1:2">
+      <c r="A1235" s="2"/>
+      <c r="B1235" s="2"/>
+    </row>
+    <row r="1236" ht="25" customHeight="1" spans="1:2">
+      <c r="A1236" s="2"/>
+      <c r="B1236" s="2"/>
+    </row>
+    <row r="1237" ht="25" customHeight="1" spans="1:2">
+      <c r="A1237" s="2"/>
+      <c r="B1237" s="2"/>
+    </row>
+    <row r="1238" ht="25" customHeight="1" spans="1:2">
+      <c r="A1238" s="2"/>
+      <c r="B1238" s="2"/>
+    </row>
+    <row r="1239" ht="25" customHeight="1" spans="1:2">
+      <c r="A1239" s="2"/>
+      <c r="B1239" s="2"/>
+    </row>
+    <row r="1240" ht="25" customHeight="1" spans="1:2">
+      <c r="A1240" s="2"/>
+      <c r="B1240" s="2"/>
+    </row>
+    <row r="1241" ht="25" customHeight="1" spans="1:2">
+      <c r="A1241" s="2"/>
+      <c r="B1241" s="2"/>
+    </row>
+    <row r="1242" ht="25" customHeight="1" spans="1:2">
+      <c r="A1242" s="2"/>
+      <c r="B1242" s="2"/>
+    </row>
+    <row r="1243" ht="25" customHeight="1" spans="1:2">
+      <c r="A1243" s="2"/>
+      <c r="B1243" s="2"/>
+    </row>
+    <row r="1244" ht="25" customHeight="1" spans="1:2">
+      <c r="A1244" s="2"/>
+      <c r="B1244" s="2"/>
+    </row>
+    <row r="1245" ht="25" customHeight="1" spans="1:2">
+      <c r="A1245" s="2"/>
+      <c r="B1245" s="2"/>
+    </row>
+    <row r="1246" ht="25" customHeight="1" spans="1:2">
+      <c r="A1246" s="2"/>
+      <c r="B1246" s="2"/>
+    </row>
+    <row r="1247" ht="25" customHeight="1" spans="1:2">
+      <c r="A1247" s="2"/>
+      <c r="B1247" s="2"/>
+    </row>
+    <row r="1248" ht="25" customHeight="1" spans="1:2">
+      <c r="A1248" s="2"/>
+      <c r="B1248" s="2"/>
+    </row>
+    <row r="1249" ht="25" customHeight="1" spans="1:2">
+      <c r="A1249" s="2"/>
+      <c r="B1249" s="2"/>
+    </row>
+    <row r="1250" ht="25" customHeight="1" spans="1:2">
+      <c r="A1250" s="2"/>
+      <c r="B1250" s="2"/>
+    </row>
+    <row r="1251" ht="25" customHeight="1" spans="1:2">
+      <c r="A1251" s="2"/>
+      <c r="B1251" s="2"/>
+    </row>
+    <row r="1252" ht="25" customHeight="1" spans="1:2">
+      <c r="A1252" s="2"/>
+      <c r="B1252" s="2"/>
+    </row>
+    <row r="1253" ht="25" customHeight="1" spans="1:2">
+      <c r="A1253" s="2"/>
+      <c r="B1253" s="2"/>
+    </row>
+    <row r="1254" ht="25" customHeight="1" spans="1:2">
+      <c r="A1254" s="2"/>
+      <c r="B1254" s="2"/>
+    </row>
+    <row r="1255" ht="25" customHeight="1" spans="1:2">
+      <c r="A1255" s="2"/>
+      <c r="B1255" s="2"/>
+    </row>
+    <row r="1256" ht="25" customHeight="1" spans="1:2">
+      <c r="A1256" s="2"/>
+      <c r="B1256" s="2"/>
+    </row>
+    <row r="1257" ht="25" customHeight="1" spans="1:2">
+      <c r="A1257" s="2"/>
+      <c r="B1257" s="2"/>
+    </row>
+    <row r="1258" ht="25" customHeight="1" spans="1:2">
+      <c r="A1258" s="2"/>
+      <c r="B1258" s="2"/>
+    </row>
+    <row r="1259" ht="25" customHeight="1" spans="1:2">
+      <c r="A1259" s="2"/>
+      <c r="B1259" s="2"/>
+    </row>
+    <row r="1260" ht="25" customHeight="1" spans="1:2">
+      <c r="A1260" s="2"/>
+      <c r="B1260" s="2"/>
+    </row>
+    <row r="1261" ht="25" customHeight="1" spans="1:2">
+      <c r="A1261" s="2"/>
+      <c r="B1261" s="2"/>
+    </row>
+    <row r="1262" ht="25" customHeight="1" spans="1:2">
+      <c r="A1262" s="2"/>
+      <c r="B1262" s="2"/>
+    </row>
+    <row r="1263" ht="25" customHeight="1" spans="1:2">
+      <c r="A1263" s="2"/>
+      <c r="B1263" s="2"/>
+    </row>
+    <row r="1264" ht="25" customHeight="1" spans="1:2">
+      <c r="A1264" s="2"/>
+      <c r="B1264" s="2"/>
+    </row>
+    <row r="1265" ht="25" customHeight="1" spans="1:2">
+      <c r="A1265" s="2"/>
+      <c r="B1265" s="2"/>
+    </row>
+    <row r="1266" ht="25" customHeight="1" spans="1:2">
+      <c r="A1266" s="2"/>
+      <c r="B1266" s="2"/>
+    </row>
+    <row r="1267" ht="25" customHeight="1" spans="1:2">
+      <c r="A1267" s="2"/>
+      <c r="B1267" s="2"/>
+    </row>
+    <row r="1268" ht="25" customHeight="1" spans="1:2">
+      <c r="A1268" s="2"/>
+      <c r="B1268" s="2"/>
+    </row>
+    <row r="1269" ht="25" customHeight="1" spans="1:2">
+      <c r="A1269" s="2"/>
+      <c r="B1269" s="2"/>
+    </row>
+    <row r="1270" ht="25" customHeight="1" spans="1:2">
+      <c r="A1270" s="2"/>
+      <c r="B1270" s="2"/>
+    </row>
+    <row r="1271" ht="25" customHeight="1" spans="1:2">
+      <c r="A1271" s="2"/>
+      <c r="B1271" s="2"/>
+    </row>
+    <row r="1272" ht="25" customHeight="1" spans="1:2">
+      <c r="A1272" s="2"/>
+      <c r="B1272" s="2"/>
+    </row>
+    <row r="1273" ht="25" customHeight="1" spans="1:2">
+      <c r="A1273" s="2"/>
+      <c r="B1273" s="2"/>
+    </row>
+    <row r="1274" ht="25" customHeight="1" spans="1:2">
+      <c r="A1274" s="2"/>
+      <c r="B1274" s="2"/>
+    </row>
+    <row r="1275" ht="25" customHeight="1" spans="1:2">
+      <c r="A1275" s="2"/>
+      <c r="B1275" s="2"/>
+    </row>
+    <row r="1276" ht="25" customHeight="1" spans="1:2">
+      <c r="A1276" s="2"/>
+      <c r="B1276" s="2"/>
+    </row>
+    <row r="1277" ht="25" customHeight="1" spans="1:2">
+      <c r="A1277" s="2"/>
+      <c r="B1277" s="2"/>
+    </row>
+    <row r="1278" ht="25" customHeight="1" spans="1:2">
+      <c r="A1278" s="2"/>
+      <c r="B1278" s="2"/>
+    </row>
+    <row r="1279" ht="25" customHeight="1" spans="1:2">
+      <c r="A1279" s="2"/>
+      <c r="B1279" s="2"/>
+    </row>
+    <row r="1280" ht="25" customHeight="1" spans="1:2">
+      <c r="A1280" s="2"/>
+      <c r="B1280" s="2"/>
+    </row>
+    <row r="1281" ht="25" customHeight="1" spans="1:2">
+      <c r="A1281" s="2"/>
+      <c r="B1281" s="2"/>
+    </row>
+    <row r="1282" ht="25" customHeight="1" spans="1:2">
+      <c r="A1282" s="2"/>
+      <c r="B1282" s="2"/>
+    </row>
+    <row r="1283" ht="25" customHeight="1" spans="1:2">
+      <c r="A1283" s="2"/>
+      <c r="B1283" s="2"/>
+    </row>
+    <row r="1284" ht="25" customHeight="1" spans="1:2">
+      <c r="A1284" s="2"/>
+      <c r="B1284" s="2"/>
+    </row>
+    <row r="1285" ht="25" customHeight="1" spans="1:2">
+      <c r="A1285" s="2"/>
+      <c r="B1285" s="2"/>
+    </row>
+    <row r="1286" ht="25" customHeight="1" spans="1:2">
+      <c r="A1286" s="2"/>
+      <c r="B1286" s="2"/>
+    </row>
+    <row r="1287" ht="25" customHeight="1" spans="1:2">
+      <c r="A1287" s="2"/>
+      <c r="B1287" s="2"/>
+    </row>
+    <row r="1288" ht="25" customHeight="1" spans="1:2">
+      <c r="A1288" s="2"/>
+      <c r="B1288" s="2"/>
+    </row>
+    <row r="1289" ht="25" customHeight="1" spans="1:2">
+      <c r="A1289" s="2"/>
+      <c r="B1289" s="2"/>
+    </row>
+    <row r="1290" ht="25" customHeight="1" spans="1:2">
+      <c r="A1290" s="2"/>
+      <c r="B1290" s="2"/>
+    </row>
+    <row r="1291" ht="25" customHeight="1" spans="1:2">
+      <c r="A1291" s="2"/>
+      <c r="B1291" s="2"/>
+    </row>
+    <row r="1292" ht="25" customHeight="1" spans="1:2">
+      <c r="A1292" s="2"/>
+      <c r="B1292" s="2"/>
+    </row>
+    <row r="1293" ht="25" customHeight="1" spans="1:2">
+      <c r="A1293" s="2"/>
+      <c r="B1293" s="2"/>
+    </row>
+    <row r="1294" ht="25" customHeight="1" spans="1:2">
+      <c r="A1294" s="2"/>
+      <c r="B1294" s="2"/>
+    </row>
+    <row r="1295" ht="25" customHeight="1" spans="1:2">
+      <c r="A1295" s="2"/>
+      <c r="B1295" s="2"/>
+    </row>
+    <row r="1296" ht="25" customHeight="1" spans="1:2">
+      <c r="A1296" s="2"/>
+      <c r="B1296" s="2"/>
+    </row>
+    <row r="1297" ht="25" customHeight="1" spans="1:2">
+      <c r="A1297" s="2"/>
+      <c r="B1297" s="2"/>
+    </row>
+    <row r="1298" ht="25" customHeight="1" spans="1:2">
+      <c r="A1298" s="2"/>
+      <c r="B1298" s="2"/>
+    </row>
+    <row r="1299" ht="25" customHeight="1" spans="1:2">
+      <c r="A1299" s="2"/>
+      <c r="B1299" s="2"/>
+    </row>
+    <row r="1300" ht="25" customHeight="1" spans="1:2">
+      <c r="A1300" s="2"/>
+      <c r="B1300" s="2"/>
+    </row>
+    <row r="1301" ht="25" customHeight="1" spans="1:2">
+      <c r="A1301" s="2"/>
+      <c r="B1301" s="2"/>
+    </row>
+    <row r="1302" ht="25" customHeight="1" spans="1:2">
+      <c r="A1302" s="2"/>
+      <c r="B1302" s="2"/>
+    </row>
+    <row r="1303" ht="25" customHeight="1" spans="1:2">
+      <c r="A1303" s="2"/>
+      <c r="B1303" s="2"/>
+    </row>
+    <row r="1304" ht="25" customHeight="1" spans="1:2">
+      <c r="A1304" s="2"/>
+      <c r="B1304" s="2"/>
+    </row>
+    <row r="1305" ht="25" customHeight="1" spans="1:2">
+      <c r="A1305" s="2"/>
+      <c r="B1305" s="2"/>
+    </row>
+    <row r="1306" ht="25" customHeight="1" spans="1:2">
+      <c r="A1306" s="2"/>
+      <c r="B1306" s="2"/>
+    </row>
+    <row r="1307" ht="25" customHeight="1" spans="1:2">
+      <c r="A1307" s="2"/>
+      <c r="B1307" s="2"/>
+    </row>
+    <row r="1308" ht="25" customHeight="1" spans="1:2">
+      <c r="A1308" s="2"/>
+      <c r="B1308" s="2"/>
+    </row>
+    <row r="1309" ht="25" customHeight="1" spans="1:2">
+      <c r="A1309" s="2"/>
+      <c r="B1309" s="2"/>
+    </row>
+    <row r="1310" ht="25" customHeight="1" spans="1:2">
+      <c r="A1310" s="2"/>
+      <c r="B1310" s="2"/>
+    </row>
+    <row r="1311" ht="25" customHeight="1" spans="1:2">
+      <c r="A1311" s="2"/>
+      <c r="B1311" s="2"/>
+    </row>
+    <row r="1312" ht="25" customHeight="1" spans="1:2">
+      <c r="A1312" s="2"/>
+      <c r="B1312" s="2"/>
+    </row>
+    <row r="1313" ht="25" customHeight="1" spans="1:2">
+      <c r="A1313" s="2"/>
+      <c r="B1313" s="2"/>
+    </row>
+    <row r="1314" ht="25" customHeight="1" spans="1:2">
+      <c r="A1314" s="2"/>
+      <c r="B1314" s="2"/>
+    </row>
+    <row r="1315" ht="25" customHeight="1" spans="1:2">
+      <c r="A1315" s="2"/>
+      <c r="B1315" s="2"/>
+    </row>
+    <row r="1316" ht="25" customHeight="1" spans="1:2">
+      <c r="A1316" s="2"/>
+      <c r="B1316" s="2"/>
+    </row>
+    <row r="1317" ht="25" customHeight="1" spans="1:2">
+      <c r="A1317" s="2"/>
+      <c r="B1317" s="2"/>
+    </row>
+    <row r="1318" ht="25" customHeight="1" spans="1:2">
+      <c r="A1318" s="2"/>
+      <c r="B1318" s="2"/>
+    </row>
+    <row r="1319" ht="25" customHeight="1" spans="1:2">
+      <c r="A1319" s="2"/>
+      <c r="B1319" s="2"/>
+    </row>
+    <row r="1320" ht="25" customHeight="1" spans="1:2">
+      <c r="A1320" s="2"/>
+      <c r="B1320" s="2"/>
+    </row>
+    <row r="1321" ht="25" customHeight="1" spans="1:2">
+      <c r="A1321" s="2"/>
+      <c r="B1321" s="2"/>
+    </row>
+    <row r="1322" ht="25" customHeight="1" spans="1:2">
+      <c r="A1322" s="2"/>
+      <c r="B1322" s="2"/>
+    </row>
+    <row r="1323" ht="25" customHeight="1" spans="1:2">
+      <c r="A1323" s="2"/>
+      <c r="B1323" s="2"/>
+    </row>
+    <row r="1324" ht="25" customHeight="1" spans="1:2">
+      <c r="A1324" s="2"/>
+      <c r="B1324" s="2"/>
+    </row>
+    <row r="1325" ht="25" customHeight="1" spans="1:2">
+      <c r="A1325" s="2"/>
+      <c r="B1325" s="2"/>
+    </row>
+    <row r="1326" ht="25" customHeight="1" spans="1:2">
+      <c r="A1326" s="2"/>
+      <c r="B1326" s="2"/>
+    </row>
+    <row r="1327" ht="25" customHeight="1" spans="1:2">
+      <c r="A1327" s="2"/>
+      <c r="B1327" s="2"/>
+    </row>
+    <row r="1328" ht="25" customHeight="1" spans="1:2">
+      <c r="A1328" s="2"/>
+      <c r="B1328" s="2"/>
+    </row>
+    <row r="1329" ht="25" customHeight="1" spans="1:2">
+      <c r="A1329" s="2"/>
+      <c r="B1329" s="2"/>
+    </row>
+    <row r="1330" ht="25" customHeight="1" spans="1:2">
+      <c r="A1330" s="2"/>
+      <c r="B1330" s="2"/>
+    </row>
+    <row r="1331" ht="25" customHeight="1" spans="1:2">
+      <c r="A1331" s="2"/>
+      <c r="B1331" s="2"/>
+    </row>
+    <row r="1332" ht="25" customHeight="1" spans="1:2">
+      <c r="A1332" s="2"/>
+      <c r="B1332" s="2"/>
+    </row>
+    <row r="1333" ht="25" customHeight="1" spans="1:2">
+      <c r="A1333" s="2"/>
+      <c r="B1333" s="2"/>
+    </row>
+    <row r="1334" ht="25" customHeight="1" spans="1:2">
+      <c r="A1334" s="2"/>
+      <c r="B1334" s="2"/>
+    </row>
+    <row r="1335" ht="25" customHeight="1" spans="1:2">
+      <c r="A1335" s="2"/>
+      <c r="B1335" s="2"/>
+    </row>
+    <row r="1336" ht="25" customHeight="1" spans="1:2">
+      <c r="A1336" s="2"/>
+      <c r="B1336" s="2"/>
+    </row>
+    <row r="1337" ht="25" customHeight="1" spans="1:2">
+      <c r="A1337" s="2"/>
+      <c r="B1337" s="2"/>
+    </row>
+    <row r="1338" ht="25" customHeight="1" spans="1:2">
+      <c r="A1338" s="2"/>
+      <c r="B1338" s="2"/>
+    </row>
+    <row r="1339" ht="25" customHeight="1" spans="1:2">
+      <c r="A1339" s="2"/>
+      <c r="B1339" s="2"/>
+    </row>
+    <row r="1340" ht="25" customHeight="1" spans="1:2">
+      <c r="A1340" s="2"/>
+      <c r="B1340" s="2"/>
+    </row>
+    <row r="1341" ht="25" customHeight="1" spans="1:2">
+      <c r="A1341" s="2"/>
+      <c r="B1341" s="2"/>
+    </row>
+    <row r="1342" ht="25" customHeight="1" spans="1:2">
+      <c r="A1342" s="2"/>
+      <c r="B1342" s="2"/>
+    </row>
+    <row r="1343" ht="25" customHeight="1" spans="1:2">
+      <c r="A1343" s="2"/>
+      <c r="B1343" s="2"/>
+    </row>
+    <row r="1344" ht="25" customHeight="1" spans="1:2">
+      <c r="A1344" s="2"/>
+      <c r="B1344" s="2"/>
+    </row>
+    <row r="1345" ht="25" customHeight="1" spans="1:2">
+      <c r="A1345" s="2"/>
+      <c r="B1345" s="2"/>
+    </row>
+    <row r="1346" ht="25" customHeight="1" spans="1:2">
+      <c r="A1346" s="2"/>
+      <c r="B1346" s="2"/>
+    </row>
+    <row r="1347" ht="25" customHeight="1" spans="1:2">
+      <c r="A1347" s="2"/>
+      <c r="B1347" s="2"/>
+    </row>
+    <row r="1348" ht="25" customHeight="1" spans="1:2">
+      <c r="A1348" s="2"/>
+      <c r="B1348" s="2"/>
+    </row>
+    <row r="1349" ht="25" customHeight="1" spans="1:2">
+      <c r="A1349" s="2"/>
+      <c r="B1349" s="2"/>
+    </row>
+    <row r="1350" ht="25" customHeight="1" spans="1:2">
+      <c r="A1350" s="2"/>
+      <c r="B1350" s="2"/>
+    </row>
+    <row r="1351" ht="25" customHeight="1" spans="1:2">
+      <c r="A1351" s="2"/>
+      <c r="B1351" s="2"/>
+    </row>
+    <row r="1352" ht="25" customHeight="1" spans="1:2">
+      <c r="A1352" s="2"/>
+      <c r="B1352" s="2"/>
+    </row>
+    <row r="1353" ht="25" customHeight="1" spans="1:2">
+      <c r="A1353" s="2"/>
+      <c r="B1353" s="2"/>
+    </row>
+    <row r="1354" ht="25" customHeight="1" spans="1:2">
+      <c r="A1354" s="2"/>
+      <c r="B1354" s="2"/>
+    </row>
+    <row r="1355" ht="25" customHeight="1" spans="1:2">
+      <c r="A1355" s="2"/>
+      <c r="B1355" s="2"/>
+    </row>
+    <row r="1356" ht="25" customHeight="1" spans="1:2">
+      <c r="A1356" s="2"/>
+      <c r="B1356" s="2"/>
+    </row>
+    <row r="1357" ht="25" customHeight="1" spans="1:2">
+      <c r="A1357" s="2"/>
+      <c r="B1357" s="2"/>
+    </row>
+    <row r="1358" ht="25" customHeight="1" spans="1:2">
+      <c r="A1358" s="2"/>
+      <c r="B1358" s="2"/>
+    </row>
+    <row r="1359" ht="25" customHeight="1" spans="1:2">
+      <c r="A1359" s="2"/>
+      <c r="B1359" s="2"/>
+    </row>
+    <row r="1360" ht="25" customHeight="1" spans="1:2">
+      <c r="A1360" s="2"/>
+      <c r="B1360" s="2"/>
+    </row>
+    <row r="1361" ht="25" customHeight="1" spans="1:2">
+      <c r="A1361" s="2"/>
+      <c r="B1361" s="2"/>
+    </row>
+    <row r="1362" ht="25" customHeight="1" spans="1:2">
+      <c r="A1362" s="2"/>
+      <c r="B1362" s="2"/>
+    </row>
+    <row r="1363" ht="25" customHeight="1" spans="1:2">
+      <c r="A1363" s="2"/>
+      <c r="B1363" s="2"/>
+    </row>
+    <row r="1364" ht="25" customHeight="1" spans="1:2">
+      <c r="A1364" s="2"/>
+      <c r="B1364" s="2"/>
+    </row>
+    <row r="1365" ht="25" customHeight="1" spans="1:2">
+      <c r="A1365" s="2"/>
+      <c r="B1365" s="2"/>
+    </row>
+    <row r="1366" ht="25" customHeight="1" spans="1:2">
+      <c r="A1366" s="2"/>
+      <c r="B1366" s="2"/>
+    </row>
+    <row r="1367" ht="25" customHeight="1" spans="1:2">
+      <c r="A1367" s="2"/>
+      <c r="B1367" s="2"/>
+    </row>
+    <row r="1368" ht="25" customHeight="1" spans="1:2">
+      <c r="A1368" s="2"/>
+      <c r="B1368" s="2"/>
+    </row>
+    <row r="1369" ht="25" customHeight="1" spans="1:2">
+      <c r="A1369" s="2"/>
+      <c r="B1369" s="2"/>
+    </row>
+    <row r="1370" ht="25" customHeight="1" spans="1:2">
+      <c r="A1370" s="2"/>
+      <c r="B1370" s="2"/>
+    </row>
+    <row r="1371" ht="25" customHeight="1" spans="1:2">
+      <c r="A1371" s="2"/>
+      <c r="B1371" s="2"/>
+    </row>
+    <row r="1372" ht="25" customHeight="1" spans="1:2">
+      <c r="A1372" s="2"/>
+      <c r="B1372" s="2"/>
+    </row>
+    <row r="1373" ht="25" customHeight="1" spans="1:2">
+      <c r="A1373" s="2"/>
+      <c r="B1373" s="2"/>
+    </row>
+    <row r="1374" ht="25" customHeight="1" spans="1:2">
+      <c r="A1374" s="2"/>
+      <c r="B1374" s="2"/>
+    </row>
+    <row r="1375" ht="25" customHeight="1" spans="1:2">
+      <c r="A1375" s="2"/>
+      <c r="B1375" s="2"/>
+    </row>
+    <row r="1376" ht="25" customHeight="1" spans="1:2">
+      <c r="A1376" s="2"/>
+      <c r="B1376" s="2"/>
+    </row>
+    <row r="1377" ht="25" customHeight="1" spans="1:2">
+      <c r="A1377" s="2"/>
+      <c r="B1377" s="2"/>
+    </row>
+    <row r="1378" ht="25" customHeight="1" spans="1:2">
+      <c r="A1378" s="2"/>
+      <c r="B1378" s="2"/>
+    </row>
+    <row r="1379" ht="25" customHeight="1" spans="1:2">
+      <c r="A1379" s="2"/>
+      <c r="B1379" s="2"/>
+    </row>
+    <row r="1380" ht="25" customHeight="1" spans="1:2">
+      <c r="A1380" s="2"/>
+      <c r="B1380" s="2"/>
+    </row>
+    <row r="1381" ht="25" customHeight="1" spans="1:2">
+      <c r="A1381" s="2"/>
+      <c r="B1381" s="2"/>
+    </row>
+    <row r="1382" ht="25" customHeight="1" spans="1:2">
+      <c r="A1382" s="2"/>
+      <c r="B1382" s="2"/>
+    </row>
+    <row r="1383" ht="25" customHeight="1" spans="1:2">
+      <c r="A1383" s="2"/>
+      <c r="B1383" s="2"/>
+    </row>
+    <row r="1384" ht="25" customHeight="1" spans="1:2">
+      <c r="A1384" s="2"/>
+      <c r="B1384" s="2"/>
+    </row>
+    <row r="1385" ht="25" customHeight="1" spans="1:2">
+      <c r="A1385" s="2"/>
+      <c r="B1385" s="2"/>
+    </row>
+    <row r="1386" ht="25" customHeight="1" spans="1:2">
+      <c r="A1386" s="2"/>
+      <c r="B1386" s="2"/>
+    </row>
+    <row r="1387" ht="25" customHeight="1" spans="1:2">
+      <c r="A1387" s="2"/>
+      <c r="B1387" s="2"/>
+    </row>
+    <row r="1388" ht="25" customHeight="1" spans="1:2">
+      <c r="A1388" s="2"/>
+      <c r="B1388" s="2"/>
+    </row>
+    <row r="1389" ht="25" customHeight="1" spans="1:2">
+      <c r="A1389" s="2"/>
+      <c r="B1389" s="2"/>
+    </row>
+    <row r="1390" ht="25" customHeight="1" spans="1:2">
+      <c r="A1390" s="2"/>
+      <c r="B1390" s="2"/>
+    </row>
+    <row r="1391" ht="25" customHeight="1" spans="1:2">
+      <c r="A1391" s="2"/>
+      <c r="B1391" s="2"/>
+    </row>
+    <row r="1392" ht="25" customHeight="1" spans="1:2">
+      <c r="A1392" s="2"/>
+      <c r="B1392" s="2"/>
+    </row>
+    <row r="1393" ht="25" customHeight="1" spans="1:2">
+      <c r="A1393" s="2"/>
+      <c r="B1393" s="2"/>
+    </row>
+    <row r="1394" ht="25" customHeight="1" spans="1:2">
+      <c r="A1394" s="2"/>
+      <c r="B1394" s="2"/>
+    </row>
+    <row r="1395" ht="25" customHeight="1" spans="1:2">
+      <c r="A1395" s="2"/>
+      <c r="B1395" s="2"/>
+    </row>
+    <row r="1396" ht="25" customHeight="1" spans="1:2">
+      <c r="A1396" s="2"/>
+      <c r="B1396" s="2"/>
+    </row>
+    <row r="1397" ht="25" customHeight="1" spans="1:2">
+      <c r="A1397" s="2"/>
+      <c r="B1397" s="2"/>
+    </row>
+    <row r="1398" ht="25" customHeight="1" spans="1:2">
+      <c r="A1398" s="2"/>
+      <c r="B1398" s="2"/>
+    </row>
+    <row r="1399" ht="25" customHeight="1" spans="1:2">
+      <c r="A1399" s="2"/>
+      <c r="B1399" s="2"/>
+    </row>
+    <row r="1400" ht="25" customHeight="1" spans="1:2">
+      <c r="A1400" s="2"/>
+      <c r="B1400" s="2"/>
+    </row>
+    <row r="1401" ht="25" customHeight="1" spans="1:2">
+      <c r="A1401" s="2"/>
+      <c r="B1401" s="2"/>
+    </row>
+    <row r="1402" ht="25" customHeight="1" spans="1:2">
+      <c r="A1402" s="2"/>
+      <c r="B1402" s="2"/>
+    </row>
+    <row r="1403" ht="25" customHeight="1" spans="1:2">
+      <c r="A1403" s="2"/>
+      <c r="B1403" s="2"/>
+    </row>
+    <row r="1404" ht="25" customHeight="1" spans="1:2">
+      <c r="A1404" s="2"/>
+      <c r="B1404" s="2"/>
+    </row>
+    <row r="1405" ht="25" customHeight="1" spans="1:2">
+      <c r="A1405" s="2"/>
+      <c r="B1405" s="2"/>
+    </row>
+    <row r="1406" ht="25" customHeight="1" spans="1:2">
+      <c r="A1406" s="2"/>
+      <c r="B1406" s="2"/>
+    </row>
+    <row r="1407" ht="25" customHeight="1" spans="1:2">
+      <c r="A1407" s="2"/>
+      <c r="B1407" s="2"/>
+    </row>
+    <row r="1408" ht="25" customHeight="1" spans="1:2">
+      <c r="A1408" s="2"/>
+      <c r="B1408" s="2"/>
+    </row>
+    <row r="1409" ht="25" customHeight="1" spans="1:2">
+      <c r="A1409" s="2"/>
+      <c r="B1409" s="2"/>
+    </row>
+    <row r="1410" ht="25" customHeight="1" spans="1:2">
+      <c r="A1410" s="2"/>
+      <c r="B1410" s="2"/>
+    </row>
+    <row r="1411" ht="25" customHeight="1" spans="1:2">
+      <c r="A1411" s="2"/>
+      <c r="B1411" s="2"/>
+    </row>
+    <row r="1412" ht="25" customHeight="1" spans="1:2">
+      <c r="A1412" s="2"/>
+      <c r="B1412" s="2"/>
+    </row>
+    <row r="1413" ht="25" customHeight="1" spans="1:2">
+      <c r="A1413" s="2"/>
+      <c r="B1413" s="2"/>
+    </row>
+    <row r="1414" ht="25" customHeight="1" spans="1:2">
+      <c r="A1414" s="2"/>
+      <c r="B1414" s="2"/>
+    </row>
+    <row r="1415" ht="25" customHeight="1" spans="1:2">
+      <c r="A1415" s="2"/>
+      <c r="B1415" s="2"/>
+    </row>
+    <row r="1416" ht="25" customHeight="1" spans="1:2">
+      <c r="A1416" s="2"/>
+      <c r="B1416" s="2"/>
+    </row>
+    <row r="1417" ht="25" customHeight="1" spans="1:2">
+      <c r="A1417" s="2"/>
+      <c r="B1417" s="2"/>
+    </row>
+    <row r="1418" ht="25" customHeight="1" spans="1:2">
+      <c r="A1418" s="2"/>
+      <c r="B1418" s="2"/>
+    </row>
+    <row r="1419" ht="25" customHeight="1" spans="1:2">
+      <c r="A1419" s="2"/>
+      <c r="B1419" s="2"/>
+    </row>
+    <row r="1420" ht="25" customHeight="1" spans="1:2">
+      <c r="A1420" s="2"/>
+      <c r="B1420" s="2"/>
+    </row>
+    <row r="1421" ht="25" customHeight="1" spans="1:2">
+      <c r="A1421" s="2"/>
+      <c r="B1421" s="2"/>
+    </row>
+    <row r="1422" ht="25" customHeight="1" spans="1:2">
+      <c r="A1422" s="2"/>
+      <c r="B1422" s="2"/>
+    </row>
+    <row r="1423" ht="25" customHeight="1" spans="1:2">
+      <c r="A1423" s="2"/>
+      <c r="B1423" s="2"/>
+    </row>
+    <row r="1424" ht="25" customHeight="1" spans="1:2">
+      <c r="A1424" s="2"/>
+      <c r="B1424" s="2"/>
+    </row>
+    <row r="1425" ht="25" customHeight="1" spans="1:2">
+      <c r="A1425" s="2"/>
+      <c r="B1425" s="2"/>
+    </row>
+    <row r="1426" ht="25" customHeight="1" spans="1:2">
+      <c r="A1426" s="2"/>
+      <c r="B1426" s="2"/>
+    </row>
+    <row r="1427" ht="25" customHeight="1" spans="1:2">
+      <c r="A1427" s="2"/>
+      <c r="B1427" s="2"/>
+    </row>
+    <row r="1428" ht="25" customHeight="1" spans="1:2">
+      <c r="A1428" s="2"/>
+      <c r="B1428" s="2"/>
+    </row>
+    <row r="1429" ht="25" customHeight="1" spans="1:2">
+      <c r="A1429" s="2"/>
+      <c r="B1429" s="2"/>
+    </row>
+    <row r="1430" ht="25" customHeight="1" spans="1:2">
+      <c r="A1430" s="2"/>
+      <c r="B1430" s="2"/>
+    </row>
+    <row r="1431" ht="25" customHeight="1" spans="1:2">
+      <c r="A1431" s="2"/>
+      <c r="B1431" s="2"/>
+    </row>
+    <row r="1432" ht="25" customHeight="1" spans="1:2">
+      <c r="A1432" s="2"/>
+      <c r="B1432" s="2"/>
+    </row>
+    <row r="1433" ht="25" customHeight="1" spans="1:2">
+      <c r="A1433" s="2"/>
+      <c r="B1433" s="2"/>
+    </row>
+    <row r="1434" ht="25" customHeight="1" spans="1:2">
+      <c r="A1434" s="2"/>
+      <c r="B1434" s="2"/>
+    </row>
+    <row r="1435" ht="25" customHeight="1" spans="1:2">
+      <c r="A1435" s="2"/>
+      <c r="B1435" s="2"/>
+    </row>
+    <row r="1436" ht="25" customHeight="1" spans="1:2">
+      <c r="A1436" s="2"/>
+      <c r="B1436" s="2"/>
+    </row>
+    <row r="1437" ht="25" customHeight="1" spans="1:2">
+      <c r="A1437" s="2"/>
+      <c r="B1437" s="2"/>
+    </row>
+    <row r="1438" ht="25" customHeight="1" spans="1:2">
+      <c r="A1438" s="2"/>
+      <c r="B1438" s="2"/>
+    </row>
+    <row r="1439" ht="25" customHeight="1" spans="1:2">
+      <c r="A1439" s="2"/>
+      <c r="B1439" s="2"/>
+    </row>
+    <row r="1440" ht="25" customHeight="1" spans="1:2">
+      <c r="A1440" s="2"/>
+      <c r="B1440" s="2"/>
+    </row>
+    <row r="1441" ht="25" customHeight="1" spans="1:2">
+      <c r="A1441" s="2"/>
+      <c r="B1441" s="2"/>
+    </row>
+    <row r="1442" ht="25" customHeight="1" spans="1:2">
+      <c r="A1442" s="2"/>
+      <c r="B1442" s="2"/>
+    </row>
+    <row r="1443" ht="25" customHeight="1" spans="1:2">
+      <c r="A1443" s="2"/>
+      <c r="B1443" s="2"/>
+    </row>
+    <row r="1444" ht="25" customHeight="1" spans="1:2">
+      <c r="A1444" s="2"/>
+      <c r="B1444" s="2"/>
+    </row>
+    <row r="1445" ht="25" customHeight="1" spans="1:2">
+      <c r="A1445" s="2"/>
+      <c r="B1445" s="2"/>
+    </row>
+    <row r="1446" ht="25" customHeight="1" spans="1:2">
+      <c r="A1446" s="2"/>
+      <c r="B1446" s="2"/>
+    </row>
+    <row r="1447" ht="25" customHeight="1" spans="1:2">
+      <c r="A1447" s="2"/>
+      <c r="B1447" s="2"/>
+    </row>
+    <row r="1448" ht="25" customHeight="1" spans="1:2">
+      <c r="A1448" s="2"/>
+      <c r="B1448" s="2"/>
+    </row>
+    <row r="1449" ht="25" customHeight="1" spans="1:2">
+      <c r="A1449" s="2"/>
+      <c r="B1449" s="2"/>
+    </row>
+    <row r="1450" ht="25" customHeight="1" spans="1:2">
+      <c r="A1450" s="2"/>
+      <c r="B1450" s="2"/>
+    </row>
+    <row r="1451" ht="25" customHeight="1" spans="1:2">
+      <c r="A1451" s="2"/>
+      <c r="B1451" s="2"/>
+    </row>
+    <row r="1452" ht="25" customHeight="1" spans="1:2">
+      <c r="A1452" s="2"/>
+      <c r="B1452" s="2"/>
+    </row>
+    <row r="1453" ht="25" customHeight="1" spans="1:2">
+      <c r="A1453" s="2"/>
+      <c r="B1453" s="2"/>
+    </row>
+    <row r="1454" ht="25" customHeight="1" spans="1:2">
+      <c r="A1454" s="2"/>
+      <c r="B1454" s="2"/>
+    </row>
+    <row r="1455" ht="25" customHeight="1" spans="1:2">
+      <c r="A1455" s="2"/>
+      <c r="B1455" s="2"/>
+    </row>
+    <row r="1456" ht="25" customHeight="1" spans="1:2">
+      <c r="A1456" s="2"/>
+      <c r="B1456" s="2"/>
+    </row>
+    <row r="1457" ht="25" customHeight="1" spans="1:2">
+      <c r="A1457" s="2"/>
+      <c r="B1457" s="2"/>
+    </row>
+    <row r="1458" ht="25" customHeight="1" spans="1:2">
+      <c r="A1458" s="2"/>
+      <c r="B1458" s="2"/>
+    </row>
+    <row r="1459" ht="25" customHeight="1" spans="1:2">
+      <c r="A1459" s="2"/>
+      <c r="B1459" s="2"/>
+    </row>
+    <row r="1460" ht="25" customHeight="1" spans="1:2">
+      <c r="A1460" s="2"/>
+      <c r="B1460" s="2"/>
+    </row>
+    <row r="1461" ht="25" customHeight="1" spans="1:2">
+      <c r="A1461" s="2"/>
+      <c r="B1461" s="2"/>
+    </row>
+    <row r="1462" ht="25" customHeight="1" spans="1:2">
+      <c r="A1462" s="2"/>
+      <c r="B1462" s="2"/>
+    </row>
+    <row r="1463" ht="25" customHeight="1" spans="1:2">
+      <c r="A1463" s="2"/>
+      <c r="B1463" s="2"/>
+    </row>
+    <row r="1464" ht="25" customHeight="1" spans="1:2">
+      <c r="A1464" s="2"/>
+      <c r="B1464" s="2"/>
+    </row>
+    <row r="1465" ht="25" customHeight="1" spans="1:2">
+      <c r="A1465" s="2"/>
+      <c r="B1465" s="2"/>
+    </row>
+    <row r="1466" ht="25" customHeight="1" spans="1:2">
+      <c r="A1466" s="2"/>
+      <c r="B1466" s="2"/>
+    </row>
+    <row r="1467" ht="25" customHeight="1" spans="1:2">
+      <c r="A1467" s="2"/>
+      <c r="B1467" s="2"/>
+    </row>
+    <row r="1468" ht="25" customHeight="1" spans="1:2">
+      <c r="A1468" s="2"/>
+      <c r="B1468" s="2"/>
+    </row>
+    <row r="1469" ht="25" customHeight="1" spans="1:2">
+      <c r="A1469" s="2"/>
+      <c r="B1469" s="2"/>
+    </row>
+    <row r="1470" ht="25" customHeight="1" spans="1:2">
+      <c r="A1470" s="2"/>
+      <c r="B1470" s="2"/>
+    </row>
+    <row r="1471" ht="25" customHeight="1" spans="1:2">
+      <c r="A1471" s="2"/>
+      <c r="B1471" s="2"/>
+    </row>
+    <row r="1472" ht="25" customHeight="1" spans="1:2">
+      <c r="A1472" s="2"/>
+      <c r="B1472" s="2"/>
+    </row>
+    <row r="1473" ht="25" customHeight="1" spans="1:2">
+      <c r="A1473" s="2"/>
+      <c r="B1473" s="2"/>
+    </row>
+    <row r="1474" ht="25" customHeight="1" spans="1:2">
+      <c r="A1474" s="2"/>
+      <c r="B1474" s="2"/>
+    </row>
+    <row r="1475" ht="25" customHeight="1" spans="1:2">
+      <c r="A1475" s="2"/>
+      <c r="B1475" s="2"/>
+    </row>
+    <row r="1476" ht="25" customHeight="1" spans="1:2">
+      <c r="A1476" s="2"/>
+      <c r="B1476" s="2"/>
+    </row>
+    <row r="1477" ht="25" customHeight="1" spans="1:2">
+      <c r="A1477" s="2"/>
+      <c r="B1477" s="2"/>
+    </row>
+    <row r="1478" ht="25" customHeight="1" spans="1:2">
+      <c r="A1478" s="2"/>
+      <c r="B1478" s="2"/>
+    </row>
+    <row r="1479" ht="25" customHeight="1" spans="1:2">
+      <c r="A1479" s="2"/>
+      <c r="B1479" s="2"/>
+    </row>
+    <row r="1480" ht="25" customHeight="1" spans="1:2">
+      <c r="A1480" s="2"/>
+      <c r="B1480" s="2"/>
+    </row>
+    <row r="1481" ht="25" customHeight="1" spans="1:2">
+      <c r="A1481" s="2"/>
+      <c r="B1481" s="2"/>
+    </row>
+    <row r="1482" ht="25" customHeight="1" spans="1:2">
+      <c r="A1482" s="2"/>
+      <c r="B1482" s="2"/>
+    </row>
+    <row r="1483" ht="25" customHeight="1" spans="1:2">
+      <c r="A1483" s="2"/>
+      <c r="B1483" s="2"/>
+    </row>
+    <row r="1484" ht="25" customHeight="1" spans="1:2">
+      <c r="A1484" s="2"/>
+      <c r="B1484" s="2"/>
+    </row>
+    <row r="1485" ht="25" customHeight="1" spans="1:2">
+      <c r="A1485" s="2"/>
+      <c r="B1485" s="2"/>
+    </row>
+    <row r="1486" ht="25" customHeight="1" spans="1:2">
+      <c r="A1486" s="2"/>
+      <c r="B1486" s="2"/>
+    </row>
+    <row r="1487" ht="25" customHeight="1" spans="1:2">
+      <c r="A1487" s="2"/>
+      <c r="B1487" s="2"/>
+    </row>
+    <row r="1488" ht="25" customHeight="1" spans="1:2">
+      <c r="A1488" s="2"/>
+      <c r="B1488" s="2"/>
+    </row>
+    <row r="1489" ht="25" customHeight="1" spans="1:2">
+      <c r="A1489" s="2"/>
+      <c r="B1489" s="2"/>
+    </row>
+    <row r="1490" ht="25" customHeight="1" spans="1:2">
+      <c r="A1490" s="2"/>
+      <c r="B1490" s="2"/>
+    </row>
+    <row r="1491" ht="25" customHeight="1" spans="1:2">
+      <c r="A1491" s="2"/>
+      <c r="B1491" s="2"/>
+    </row>
+    <row r="1492" ht="25" customHeight="1" spans="1:2">
+      <c r="A1492" s="2"/>
+      <c r="B1492" s="2"/>
+    </row>
+    <row r="1493" ht="25" customHeight="1" spans="1:2">
+      <c r="A1493" s="2"/>
+      <c r="B1493" s="2"/>
+    </row>
+    <row r="1494" ht="25" customHeight="1" spans="1:2">
+      <c r="A1494" s="2"/>
+      <c r="B1494" s="2"/>
+    </row>
+    <row r="1495" ht="25" customHeight="1" spans="1:2">
+      <c r="A1495" s="2"/>
+      <c r="B1495" s="2"/>
+    </row>
+    <row r="1496" ht="25" customHeight="1" spans="1:2">
+      <c r="A1496" s="2"/>
+      <c r="B1496" s="2"/>
+    </row>
+    <row r="1497" ht="25" customHeight="1" spans="1:2">
+      <c r="A1497" s="2"/>
+      <c r="B1497" s="2"/>
+    </row>
+    <row r="1498" ht="25" customHeight="1" spans="1:2">
+      <c r="A1498" s="2"/>
+      <c r="B1498" s="2"/>
+    </row>
+    <row r="1499" ht="25" customHeight="1" spans="1:2">
+      <c r="A1499" s="2"/>
+      <c r="B1499" s="2"/>
+    </row>
+    <row r="1500" ht="25" customHeight="1" spans="1:2">
+      <c r="A1500" s="2"/>
+      <c r="B1500" s="2"/>
+    </row>
+    <row r="1501" ht="25" customHeight="1" spans="1:2">
+      <c r="A1501" s="2"/>
+      <c r="B1501" s="2"/>
+    </row>
+    <row r="1502" ht="25" customHeight="1" spans="1:2">
+      <c r="A1502" s="2"/>
+      <c r="B1502" s="2"/>
+    </row>
+    <row r="1503" ht="25" customHeight="1" spans="1:2">
+      <c r="A1503" s="2"/>
+      <c r="B1503" s="2"/>
+    </row>
+    <row r="1504" ht="25" customHeight="1" spans="1:2">
+      <c r="A1504" s="2"/>
+      <c r="B1504" s="2"/>
+    </row>
+    <row r="1505" ht="25" customHeight="1" spans="1:2">
+      <c r="A1505" s="2"/>
+      <c r="B1505" s="2"/>
+    </row>
+    <row r="1506" ht="25" customHeight="1" spans="1:2">
+      <c r="A1506" s="2"/>
+      <c r="B1506" s="2"/>
+    </row>
+    <row r="1507" ht="25" customHeight="1" spans="1:2">
+      <c r="A1507" s="2"/>
+      <c r="B1507" s="2"/>
+    </row>
+    <row r="1508" ht="25" customHeight="1" spans="1:2">
+      <c r="A1508" s="2"/>
+      <c r="B1508" s="2"/>
+    </row>
+    <row r="1509" ht="25" customHeight="1" spans="1:2">
+      <c r="A1509" s="2"/>
+      <c r="B1509" s="2"/>
+    </row>
+    <row r="1510" ht="25" customHeight="1" spans="1:2">
+      <c r="A1510" s="2"/>
+      <c r="B1510" s="2"/>
+    </row>
+    <row r="1511" ht="25" customHeight="1" spans="1:2">
+      <c r="A1511" s="2"/>
+      <c r="B1511" s="2"/>
+    </row>
+    <row r="1512" ht="25" customHeight="1" spans="1:2">
+      <c r="A1512" s="2"/>
+      <c r="B1512" s="2"/>
+    </row>
+    <row r="1513" ht="25" customHeight="1" spans="1:2">
+      <c r="A1513" s="2"/>
+      <c r="B1513" s="2"/>
+    </row>
+    <row r="1514" ht="25" customHeight="1" spans="1:2">
+      <c r="A1514" s="2"/>
+      <c r="B1514" s="2"/>
+    </row>
+    <row r="1515" ht="25" customHeight="1" spans="1:2">
+      <c r="A1515" s="2"/>
+      <c r="B1515" s="2"/>
+    </row>
+    <row r="1516" ht="25" customHeight="1" spans="1:2">
+      <c r="A1516" s="2"/>
+      <c r="B1516" s="2"/>
+    </row>
+    <row r="1517" ht="25" customHeight="1" spans="1:2">
+      <c r="A1517" s="2"/>
+      <c r="B1517" s="2"/>
+    </row>
+    <row r="1518" ht="25" customHeight="1" spans="1:2">
+      <c r="A1518" s="2"/>
+      <c r="B1518" s="2"/>
+    </row>
+    <row r="1519" ht="25" customHeight="1" spans="1:2">
+      <c r="A1519" s="2"/>
+      <c r="B1519" s="2"/>
+    </row>
+    <row r="1520" ht="25" customHeight="1" spans="1:2">
+      <c r="A1520" s="2"/>
+      <c r="B1520" s="2"/>
+    </row>
+    <row r="1521" ht="25" customHeight="1" spans="1:2">
+      <c r="A1521" s="2"/>
+      <c r="B1521" s="2"/>
+    </row>
+    <row r="1522" ht="25" customHeight="1" spans="1:2">
+      <c r="A1522" s="2"/>
+      <c r="B1522" s="2"/>
+    </row>
+    <row r="1523" ht="25" customHeight="1" spans="1:2">
+      <c r="A1523" s="2"/>
+      <c r="B1523" s="2"/>
+    </row>
+    <row r="1524" ht="25" customHeight="1" spans="1:2">
+      <c r="A1524" s="2"/>
+      <c r="B1524" s="2"/>
+    </row>
+    <row r="1525" ht="25" customHeight="1" spans="1:2">
+      <c r="A1525" s="2"/>
+      <c r="B1525" s="2"/>
+    </row>
+    <row r="1526" ht="25" customHeight="1" spans="1:2">
+      <c r="A1526" s="2"/>
+      <c r="B1526" s="2"/>
+    </row>
+    <row r="1527" ht="25" customHeight="1" spans="1:2">
+      <c r="A1527" s="2"/>
+      <c r="B1527" s="2"/>
+    </row>
+    <row r="1528" ht="25" customHeight="1" spans="1:2">
+      <c r="A1528" s="2"/>
+      <c r="B1528" s="2"/>
+    </row>
+    <row r="1529" ht="25" customHeight="1" spans="1:2">
+      <c r="A1529" s="2"/>
+      <c r="B1529" s="2"/>
+    </row>
+    <row r="1530" ht="25" customHeight="1" spans="1:2">
+      <c r="A1530" s="2"/>
+      <c r="B1530" s="2"/>
+    </row>
+    <row r="1531" ht="25" customHeight="1" spans="1:2">
+      <c r="A1531" s="2"/>
+      <c r="B1531" s="2"/>
+    </row>
+    <row r="1532" ht="25" customHeight="1" spans="1:2">
+      <c r="A1532" s="2"/>
+      <c r="B1532" s="2"/>
+    </row>
+    <row r="1533" ht="25" customHeight="1" spans="1:2">
+      <c r="A1533" s="2"/>
+      <c r="B1533" s="2"/>
+    </row>
+    <row r="1534" ht="25" customHeight="1" spans="1:2">
+      <c r="A1534" s="2"/>
+      <c r="B1534" s="2"/>
+    </row>
+    <row r="1535" ht="25" customHeight="1" spans="1:2">
+      <c r="A1535" s="2"/>
+      <c r="B1535" s="2"/>
+    </row>
+    <row r="1536" ht="25" customHeight="1" spans="1:2">
+      <c r="A1536" s="2"/>
+      <c r="B1536" s="2"/>
+    </row>
+    <row r="1537" ht="25" customHeight="1" spans="1:2">
+      <c r="A1537" s="2"/>
+      <c r="B1537" s="2"/>
+    </row>
+    <row r="1538" ht="25" customHeight="1" spans="1:2">
+      <c r="A1538" s="2"/>
+      <c r="B1538" s="2"/>
+    </row>
+    <row r="1539" ht="25" customHeight="1" spans="1:2">
+      <c r="A1539" s="2"/>
+      <c r="B1539" s="2"/>
+    </row>
+    <row r="1540" ht="25" customHeight="1" spans="1:2">
+      <c r="A1540" s="2"/>
+      <c r="B1540" s="2"/>
+    </row>
+    <row r="1541" ht="25" customHeight="1" spans="1:2">
+      <c r="A1541" s="2"/>
+      <c r="B1541" s="2"/>
+    </row>
+    <row r="1542" ht="25" customHeight="1" spans="1:2">
+      <c r="A1542" s="2"/>
+      <c r="B1542" s="2"/>
+    </row>
+    <row r="1543" ht="25" customHeight="1" spans="1:2">
+      <c r="A1543" s="2"/>
+      <c r="B1543" s="2"/>
+    </row>
+    <row r="1544" ht="25" customHeight="1" spans="1:2">
+      <c r="A1544" s="2"/>
+      <c r="B1544" s="2"/>
+    </row>
+    <row r="1545" ht="25" customHeight="1" spans="1:2">
+      <c r="A1545" s="2"/>
+      <c r="B1545" s="2"/>
+    </row>
+    <row r="1546" ht="25" customHeight="1" spans="1:2">
+      <c r="A1546" s="2"/>
+      <c r="B1546" s="2"/>
+    </row>
+    <row r="1547" ht="25" customHeight="1" spans="1:2">
+      <c r="A1547" s="2"/>
+      <c r="B1547" s="2"/>
+    </row>
+    <row r="1548" ht="25" customHeight="1" spans="1:2">
+      <c r="A1548" s="2"/>
+      <c r="B1548" s="2"/>
+    </row>
+    <row r="1549" ht="25" customHeight="1" spans="1:2">
+      <c r="A1549" s="2"/>
+      <c r="B1549" s="2"/>
+    </row>
+    <row r="1550" ht="25" customHeight="1" spans="1:2">
+      <c r="A1550" s="2"/>
+      <c r="B1550" s="2"/>
+    </row>
+    <row r="1551" ht="25" customHeight="1" spans="1:2">
+      <c r="A1551" s="2"/>
+      <c r="B1551" s="2"/>
+    </row>
+    <row r="1552" ht="25" customHeight="1" spans="1:2">
+      <c r="A1552" s="2"/>
+      <c r="B1552" s="2"/>
+    </row>
+    <row r="1553" ht="25" customHeight="1" spans="1:2">
+      <c r="A1553" s="2"/>
+      <c r="B1553" s="2"/>
+    </row>
+    <row r="1554" ht="25" customHeight="1" spans="1:2">
+      <c r="A1554" s="2"/>
+      <c r="B1554" s="2"/>
+    </row>
+    <row r="1555" ht="25" customHeight="1" spans="1:2">
+      <c r="A1555" s="2"/>
+      <c r="B1555" s="2"/>
+    </row>
+    <row r="1556" ht="25" customHeight="1" spans="1:2">
+      <c r="A1556" s="2"/>
+      <c r="B1556" s="2"/>
+    </row>
+    <row r="1557" ht="25" customHeight="1" spans="1:2">
+      <c r="A1557" s="2"/>
+      <c r="B1557" s="2"/>
+    </row>
+    <row r="1558" ht="25" customHeight="1" spans="1:2">
+      <c r="A1558" s="2"/>
+      <c r="B1558" s="2"/>
+    </row>
+    <row r="1559" ht="25" customHeight="1" spans="1:2">
+      <c r="A1559" s="2"/>
+      <c r="B1559" s="2"/>
+    </row>
+    <row r="1560" ht="25" customHeight="1" spans="1:2">
+      <c r="A1560" s="2"/>
+      <c r="B1560" s="2"/>
+    </row>
+    <row r="1561" ht="25" customHeight="1" spans="1:2">
+      <c r="A1561" s="2"/>
+      <c r="B1561" s="2"/>
+    </row>
+    <row r="1562" ht="25" customHeight="1" spans="1:2">
+      <c r="A1562" s="2"/>
+      <c r="B1562" s="2"/>
+    </row>
+    <row r="1563" ht="25" customHeight="1" spans="1:2">
+      <c r="A1563" s="2"/>
+      <c r="B1563" s="2"/>
+    </row>
+    <row r="1564" ht="25" customHeight="1" spans="1:2">
+      <c r="A1564" s="2"/>
+      <c r="B1564" s="2"/>
+    </row>
+    <row r="1565" ht="25" customHeight="1" spans="1:2">
+      <c r="A1565" s="2"/>
+      <c r="B1565" s="2"/>
+    </row>
+    <row r="1566" ht="25" customHeight="1" spans="1:2">
+      <c r="A1566" s="2"/>
+      <c r="B1566" s="2"/>
+    </row>
+    <row r="1567" ht="25" customHeight="1" spans="1:2">
+      <c r="A1567" s="2"/>
+      <c r="B1567" s="2"/>
+    </row>
+    <row r="1568" ht="25" customHeight="1" spans="1:2">
+      <c r="A1568" s="2"/>
+      <c r="B1568" s="2"/>
+    </row>
+    <row r="1569" ht="25" customHeight="1" spans="1:2">
+      <c r="A1569" s="2"/>
+      <c r="B1569" s="2"/>
+    </row>
+    <row r="1570" ht="25" customHeight="1" spans="1:2">
+      <c r="A1570" s="2"/>
+      <c r="B1570" s="2"/>
+    </row>
+    <row r="1571" ht="25" customHeight="1" spans="1:2">
+      <c r="A1571" s="2"/>
+      <c r="B1571" s="2"/>
+    </row>
+    <row r="1572" ht="25" customHeight="1" spans="1:2">
+      <c r="A1572" s="2"/>
+      <c r="B1572" s="2"/>
+    </row>
+    <row r="1573" ht="25" customHeight="1" spans="1:2">
+      <c r="A1573" s="2"/>
+      <c r="B1573" s="2"/>
+    </row>
+    <row r="1574" ht="25" customHeight="1" spans="1:2">
+      <c r="A1574" s="2"/>
+      <c r="B1574" s="2"/>
+    </row>
+    <row r="1575" ht="25" customHeight="1" spans="1:2">
+      <c r="A1575" s="2"/>
+      <c r="B1575" s="2"/>
+    </row>
+    <row r="1576" ht="25" customHeight="1" spans="1:2">
+      <c r="A1576" s="2"/>
+      <c r="B1576" s="2"/>
+    </row>
+    <row r="1577" ht="25" customHeight="1" spans="1:2">
+      <c r="A1577" s="2"/>
+      <c r="B1577" s="2"/>
+    </row>
+    <row r="1578" ht="25" customHeight="1" spans="1:2">
+      <c r="A1578" s="2"/>
+      <c r="B1578" s="2"/>
+    </row>
+    <row r="1579" ht="25" customHeight="1" spans="1:2">
+      <c r="A1579" s="2"/>
+      <c r="B1579" s="2"/>
+    </row>
+    <row r="1580" ht="25" customHeight="1" spans="1:2">
+      <c r="A1580" s="2"/>
+      <c r="B1580" s="2"/>
+    </row>
+    <row r="1581" ht="25" customHeight="1" spans="1:2">
+      <c r="A1581" s="2"/>
+      <c r="B1581" s="2"/>
+    </row>
+    <row r="1582" ht="25" customHeight="1" spans="1:2">
+      <c r="A1582" s="2"/>
+      <c r="B1582" s="2"/>
+    </row>
+    <row r="1583" ht="25" customHeight="1" spans="1:2">
+      <c r="A1583" s="2"/>
+      <c r="B1583" s="2"/>
+    </row>
+    <row r="1584" ht="25" customHeight="1" spans="1:2">
+      <c r="A1584" s="2"/>
+      <c r="B1584" s="2"/>
+    </row>
+    <row r="1585" ht="25" customHeight="1" spans="1:2">
+      <c r="A1585" s="2"/>
+      <c r="B1585" s="2"/>
+    </row>
+    <row r="1586" ht="25" customHeight="1" spans="1:2">
+      <c r="A1586" s="2"/>
+      <c r="B1586" s="2"/>
+    </row>
+    <row r="1587" ht="25" customHeight="1" spans="1:2">
+      <c r="A1587" s="2"/>
+      <c r="B1587" s="2"/>
+    </row>
+    <row r="1588" ht="25" customHeight="1" spans="1:2">
+      <c r="A1588" s="2"/>
+      <c r="B1588" s="2"/>
+    </row>
+    <row r="1589" ht="25" customHeight="1" spans="1:2">
+      <c r="A1589" s="2"/>
+      <c r="B1589" s="2"/>
+    </row>
+    <row r="1590" ht="25" customHeight="1" spans="1:2">
+      <c r="A1590" s="2"/>
+      <c r="B1590" s="2"/>
+    </row>
+    <row r="1591" ht="25" customHeight="1" spans="1:2">
+      <c r="A1591" s="2"/>
+      <c r="B1591" s="2"/>
+    </row>
+    <row r="1592" ht="25" customHeight="1" spans="1:2">
+      <c r="A1592" s="2"/>
+      <c r="B1592" s="2"/>
+    </row>
+    <row r="1593" ht="25" customHeight="1" spans="1:2">
+      <c r="A1593" s="2"/>
+      <c r="B1593" s="2"/>
+    </row>
+    <row r="1594" ht="25" customHeight="1" spans="1:2">
+      <c r="A1594" s="2"/>
+      <c r="B1594" s="2"/>
+    </row>
+    <row r="1595" ht="25" customHeight="1" spans="1:2">
+      <c r="A1595" s="2"/>
+      <c r="B1595" s="2"/>
+    </row>
+    <row r="1596" ht="25" customHeight="1" spans="1:2">
+      <c r="A1596" s="2"/>
+      <c r="B1596" s="2"/>
+    </row>
+    <row r="1597" ht="25" customHeight="1" spans="1:2">
+      <c r="A1597" s="2"/>
+      <c r="B1597" s="2"/>
+    </row>
+    <row r="1598" ht="25" customHeight="1" spans="1:2">
+      <c r="A1598" s="2"/>
+      <c r="B1598" s="2"/>
+    </row>
+    <row r="1599" ht="25" customHeight="1" spans="1:2">
+      <c r="A1599" s="2"/>
+      <c r="B1599" s="2"/>
+    </row>
+    <row r="1600" ht="25" customHeight="1" spans="1:2">
+      <c r="A1600" s="2"/>
+      <c r="B1600" s="2"/>
+    </row>
+    <row r="1601" ht="25" customHeight="1" spans="1:2">
+      <c r="A1601" s="2"/>
+      <c r="B1601" s="2"/>
+    </row>
+    <row r="1602" ht="25" customHeight="1" spans="1:2">
+      <c r="A1602" s="2"/>
+      <c r="B1602" s="2"/>
+    </row>
+    <row r="1603" ht="25" customHeight="1" spans="1:2">
+      <c r="A1603" s="2"/>
+      <c r="B1603" s="2"/>
+    </row>
+    <row r="1604" ht="25" customHeight="1" spans="1:2">
+      <c r="A1604" s="2"/>
+      <c r="B1604" s="2"/>
+    </row>
+    <row r="1605" ht="25" customHeight="1" spans="1:2">
+      <c r="A1605" s="2"/>
+      <c r="B1605" s="2"/>
+    </row>
+    <row r="1606" ht="25" customHeight="1" spans="1:2">
+      <c r="A1606" s="2"/>
+      <c r="B1606" s="2"/>
+    </row>
+    <row r="1607" ht="25" customHeight="1" spans="1:2">
+      <c r="A1607" s="2"/>
+      <c r="B1607" s="2"/>
+    </row>
+    <row r="1608" ht="25" customHeight="1" spans="1:2">
+      <c r="A1608" s="2"/>
+      <c r="B1608" s="2"/>
+    </row>
+    <row r="1609" ht="25" customHeight="1" spans="1:2">
+      <c r="A1609" s="2"/>
+      <c r="B1609" s="2"/>
+    </row>
+    <row r="1610" ht="25" customHeight="1" spans="1:2">
+      <c r="A1610" s="2"/>
+      <c r="B1610" s="2"/>
+    </row>
+    <row r="1611" ht="25" customHeight="1" spans="1:2">
+      <c r="A1611" s="2"/>
+      <c r="B1611" s="2"/>
+    </row>
+    <row r="1612" ht="25" customHeight="1" spans="1:2">
+      <c r="A1612" s="2"/>
+      <c r="B1612" s="2"/>
+    </row>
+    <row r="1613" ht="25" customHeight="1" spans="1:2">
+      <c r="A1613" s="2"/>
+      <c r="B1613" s="2"/>
+    </row>
+    <row r="1614" ht="25" customHeight="1" spans="1:2">
+      <c r="A1614" s="2"/>
+      <c r="B1614" s="2"/>
+    </row>
+    <row r="1615" ht="25" customHeight="1" spans="1:2">
+      <c r="A1615" s="2"/>
+      <c r="B1615" s="2"/>
+    </row>
+    <row r="1616" ht="25" customHeight="1" spans="1:2">
+      <c r="A1616" s="2"/>
+      <c r="B1616" s="2"/>
+    </row>
+    <row r="1617" ht="25" customHeight="1" spans="1:2">
+      <c r="A1617" s="2"/>
+      <c r="B1617" s="2"/>
+    </row>
+    <row r="1618" ht="25" customHeight="1" spans="1:2">
+      <c r="A1618" s="2"/>
+      <c r="B1618" s="2"/>
+    </row>
+    <row r="1619" ht="25" customHeight="1" spans="1:2">
+      <c r="A1619" s="2"/>
+      <c r="B1619" s="2"/>
+    </row>
+    <row r="1620" ht="25" customHeight="1" spans="1:2">
+      <c r="A1620" s="2"/>
+      <c r="B1620" s="2"/>
+    </row>
+    <row r="1621" ht="25" customHeight="1" spans="1:2">
+      <c r="A1621" s="2"/>
+      <c r="B1621" s="2"/>
+    </row>
+    <row r="1622" ht="25" customHeight="1" spans="1:2">
+      <c r="A1622" s="2"/>
+      <c r="B1622" s="2"/>
+    </row>
+    <row r="1623" ht="25" customHeight="1" spans="1:2">
+      <c r="A1623" s="2"/>
+      <c r="B1623" s="2"/>
+    </row>
+    <row r="1624" ht="25" customHeight="1" spans="1:2">
+      <c r="A1624" s="2"/>
+      <c r="B1624" s="2"/>
+    </row>
+    <row r="1625" ht="25" customHeight="1" spans="1:2">
+      <c r="A1625" s="2"/>
+      <c r="B1625" s="2"/>
+    </row>
+    <row r="1626" ht="25" customHeight="1" spans="1:2">
+      <c r="A1626" s="2"/>
+      <c r="B1626" s="2"/>
+    </row>
+    <row r="1627" ht="25" customHeight="1" spans="1:2">
+      <c r="A1627" s="2"/>
+      <c r="B1627" s="2"/>
+    </row>
+    <row r="1628" ht="25" customHeight="1" spans="1:2">
+      <c r="A1628" s="2"/>
+      <c r="B1628" s="2"/>
+    </row>
+    <row r="1629" ht="25" customHeight="1" spans="1:2">
+      <c r="A1629" s="2"/>
+      <c r="B1629" s="2"/>
+    </row>
+    <row r="1630" ht="25" customHeight="1" spans="1:2">
+      <c r="A1630" s="2"/>
+      <c r="B1630" s="2"/>
+    </row>
+    <row r="1631" ht="25" customHeight="1" spans="1:2">
+      <c r="A1631" s="2"/>
+      <c r="B1631" s="2"/>
+    </row>
+    <row r="1632" ht="25" customHeight="1" spans="1:2">
+      <c r="A1632" s="2"/>
+      <c r="B1632" s="2"/>
+    </row>
+    <row r="1633" ht="25" customHeight="1" spans="1:2">
+      <c r="A1633" s="2"/>
+      <c r="B1633" s="2"/>
+    </row>
+    <row r="1634" ht="25" customHeight="1" spans="1:2">
+      <c r="A1634" s="2"/>
+      <c r="B1634" s="2"/>
+    </row>
+    <row r="1635" ht="25" customHeight="1" spans="1:2">
+      <c r="A1635" s="2"/>
+      <c r="B1635" s="2"/>
+    </row>
+    <row r="1636" ht="25" customHeight="1" spans="1:2">
+      <c r="A1636" s="2"/>
+      <c r="B1636" s="2"/>
+    </row>
+    <row r="1637" ht="25" customHeight="1" spans="1:2">
+      <c r="A1637" s="2"/>
+      <c r="B1637" s="2"/>
+    </row>
+    <row r="1638" ht="25" customHeight="1" spans="1:2">
+      <c r="A1638" s="2"/>
+      <c r="B1638" s="2"/>
+    </row>
+    <row r="1639" ht="25" customHeight="1" spans="1:2">
+      <c r="A1639" s="2"/>
+      <c r="B1639" s="2"/>
+    </row>
+    <row r="1640" ht="25" customHeight="1" spans="1:2">
+      <c r="A1640" s="2"/>
+      <c r="B1640" s="2"/>
+    </row>
+    <row r="1641" ht="25" customHeight="1" spans="1:2">
+      <c r="A1641" s="2"/>
+      <c r="B1641" s="2"/>
+    </row>
+    <row r="1642" ht="25" customHeight="1" spans="1:2">
+      <c r="A1642" s="2"/>
+      <c r="B1642" s="2"/>
+    </row>
+    <row r="1643" ht="25" customHeight="1" spans="1:2">
+      <c r="A1643" s="2"/>
+      <c r="B1643" s="2"/>
+    </row>
+    <row r="1644" ht="25" customHeight="1" spans="1:2">
+      <c r="A1644" s="2"/>
+      <c r="B1644" s="2"/>
+    </row>
+    <row r="1645" ht="25" customHeight="1" spans="1:2">
+      <c r="A1645" s="2"/>
+      <c r="B1645" s="2"/>
+    </row>
+    <row r="1646" ht="25" customHeight="1" spans="1:2">
+      <c r="A1646" s="2"/>
+      <c r="B1646" s="2"/>
+    </row>
+    <row r="1647" ht="25" customHeight="1" spans="1:2">
+      <c r="A1647" s="2"/>
+      <c r="B1647" s="2"/>
+    </row>
+    <row r="1648" ht="25" customHeight="1" spans="1:2">
+      <c r="A1648" s="2"/>
+      <c r="B1648" s="2"/>
+    </row>
+    <row r="1649" ht="25" customHeight="1" spans="1:2">
+      <c r="A1649" s="2"/>
+      <c r="B1649" s="2"/>
+    </row>
+    <row r="1650" ht="25" customHeight="1" spans="1:2">
+      <c r="A1650" s="2"/>
+      <c r="B1650" s="2"/>
+    </row>
+    <row r="1651" ht="25" customHeight="1" spans="1:2">
+      <c r="A1651" s="2"/>
+      <c r="B1651" s="2"/>
+    </row>
+    <row r="1652" ht="25" customHeight="1" spans="1:2">
+      <c r="A1652" s="2"/>
+      <c r="B1652" s="2"/>
+    </row>
+    <row r="1653" ht="25" customHeight="1" spans="1:2">
+      <c r="A1653" s="2"/>
+      <c r="B1653" s="2"/>
+    </row>
+    <row r="1654" ht="25" customHeight="1" spans="1:2">
+      <c r="A1654" s="2"/>
+      <c r="B1654" s="2"/>
+    </row>
+    <row r="1655" ht="25" customHeight="1" spans="1:2">
+      <c r="A1655" s="2"/>
+      <c r="B1655" s="2"/>
+    </row>
+    <row r="1656" ht="25" customHeight="1" spans="1:2">
+      <c r="A1656" s="2"/>
+      <c r="B1656" s="2"/>
+    </row>
+    <row r="1657" ht="25" customHeight="1" spans="1:2">
+      <c r="A1657" s="2"/>
+      <c r="B1657" s="2"/>
+    </row>
+    <row r="1658" ht="25" customHeight="1" spans="1:2">
+      <c r="A1658" s="2"/>
+      <c r="B1658" s="2"/>
+    </row>
+    <row r="1659" ht="25" customHeight="1" spans="1:2">
+      <c r="A1659" s="2"/>
+      <c r="B1659" s="2"/>
+    </row>
+    <row r="1660" ht="25" customHeight="1" spans="1:2">
+      <c r="A1660" s="2"/>
+      <c r="B1660" s="2"/>
+    </row>
+    <row r="1661" ht="25" customHeight="1" spans="1:2">
+      <c r="A1661" s="2"/>
+      <c r="B1661" s="2"/>
+    </row>
+    <row r="1662" ht="25" customHeight="1" spans="1:2">
+      <c r="A1662" s="2"/>
+      <c r="B1662" s="2"/>
+    </row>
+    <row r="1663" ht="25" customHeight="1" spans="1:2">
+      <c r="A1663" s="2"/>
+      <c r="B1663" s="2"/>
+    </row>
+    <row r="1664" ht="25" customHeight="1" spans="1:2">
+      <c r="A1664" s="2"/>
+      <c r="B1664" s="2"/>
+    </row>
+    <row r="1665" ht="25" customHeight="1" spans="1:2">
+      <c r="A1665" s="2"/>
+      <c r="B1665" s="2"/>
+    </row>
+    <row r="1666" ht="25" customHeight="1" spans="1:2">
+      <c r="A1666" s="2"/>
+      <c r="B1666" s="2"/>
+    </row>
+    <row r="1667" ht="25" customHeight="1" spans="1:2">
+      <c r="A1667" s="2"/>
+      <c r="B1667" s="2"/>
+    </row>
+    <row r="1668" ht="25" customHeight="1" spans="1:2">
+      <c r="A1668" s="2"/>
+      <c r="B1668" s="2"/>
+    </row>
+    <row r="1669" ht="25" customHeight="1" spans="1:2">
+      <c r="A1669" s="2"/>
+      <c r="B1669" s="2"/>
+    </row>
+    <row r="1670" ht="25" customHeight="1" spans="1:2">
+      <c r="A1670" s="2"/>
+      <c r="B1670" s="2"/>
+    </row>
+    <row r="1671" ht="25" customHeight="1" spans="1:2">
+      <c r="A1671" s="2"/>
+      <c r="B1671" s="2"/>
+    </row>
+    <row r="1672" ht="25" customHeight="1" spans="1:2">
+      <c r="A1672" s="2"/>
+      <c r="B1672" s="2"/>
+    </row>
+    <row r="1673" ht="25" customHeight="1" spans="1:2">
+      <c r="A1673" s="2"/>
+      <c r="B1673" s="2"/>
+    </row>
+    <row r="1674" ht="25" customHeight="1" spans="1:2">
+      <c r="A1674" s="2"/>
+      <c r="B1674" s="2"/>
+    </row>
+    <row r="1675" ht="25" customHeight="1" spans="1:2">
+      <c r="A1675" s="2"/>
+      <c r="B1675" s="2"/>
+    </row>
+    <row r="1676" ht="25" customHeight="1" spans="1:2">
+      <c r="A1676" s="2"/>
+      <c r="B1676" s="2"/>
+    </row>
+    <row r="1677" ht="25" customHeight="1" spans="1:2">
+      <c r="A1677" s="2"/>
+      <c r="B1677" s="2"/>
+    </row>
+    <row r="1678" ht="25" customHeight="1" spans="1:2">
+      <c r="A1678" s="2"/>
+      <c r="B1678" s="2"/>
+    </row>
+    <row r="1679" ht="25" customHeight="1" spans="1:2">
+      <c r="A1679" s="2"/>
+      <c r="B1679" s="2"/>
+    </row>
+    <row r="1680" ht="25" customHeight="1" spans="1:2">
+      <c r="A1680" s="2"/>
+      <c r="B1680" s="2"/>
+    </row>
+    <row r="1681" ht="25" customHeight="1" spans="1:2">
+      <c r="A1681" s="2"/>
+      <c r="B1681" s="2"/>
+    </row>
+    <row r="1682" ht="25" customHeight="1" spans="1:2">
+      <c r="A1682" s="2"/>
+      <c r="B1682" s="2"/>
+    </row>
+    <row r="1683" ht="25" customHeight="1" spans="1:2">
+      <c r="A1683" s="2"/>
+      <c r="B1683" s="2"/>
+    </row>
+    <row r="1684" ht="25" customHeight="1" spans="1:2">
+      <c r="A1684" s="2"/>
+      <c r="B1684" s="2"/>
+    </row>
+    <row r="1685" ht="25" customHeight="1" spans="1:2">
+      <c r="A1685" s="2"/>
+      <c r="B1685" s="2"/>
+    </row>
+    <row r="1686" ht="25" customHeight="1" spans="1:2">
+      <c r="A1686" s="2"/>
+      <c r="B1686" s="2"/>
+    </row>
+    <row r="1687" ht="25" customHeight="1" spans="1:2">
+      <c r="A1687" s="2"/>
+      <c r="B1687" s="2"/>
+    </row>
+    <row r="1688" ht="25" customHeight="1" spans="1:2">
+      <c r="A1688" s="2"/>
+      <c r="B1688" s="2"/>
+    </row>
+    <row r="1689" ht="25" customHeight="1" spans="1:2">
+      <c r="A1689" s="2"/>
+      <c r="B1689" s="2"/>
+    </row>
+    <row r="1690" ht="25" customHeight="1" spans="1:2">
+      <c r="A1690" s="2"/>
+      <c r="B1690" s="2"/>
+    </row>
+    <row r="1691" ht="25" customHeight="1" spans="1:2">
+      <c r="A1691" s="2"/>
+      <c r="B1691" s="2"/>
+    </row>
+    <row r="1692" ht="25" customHeight="1" spans="1:2">
+      <c r="A1692" s="2"/>
+      <c r="B1692" s="2"/>
+    </row>
+    <row r="1693" ht="25" customHeight="1" spans="1:2">
+      <c r="A1693" s="2"/>
+      <c r="B1693" s="2"/>
+    </row>
+    <row r="1694" ht="25" customHeight="1" spans="1:2">
+      <c r="A1694" s="2"/>
+      <c r="B1694" s="2"/>
+    </row>
+    <row r="1695" ht="25" customHeight="1" spans="1:2">
+      <c r="A1695" s="2"/>
+      <c r="B1695" s="2"/>
+    </row>
+    <row r="1696" ht="25" customHeight="1" spans="1:2">
+      <c r="A1696" s="2"/>
+      <c r="B1696" s="2"/>
+    </row>
+    <row r="1697" ht="25" customHeight="1" spans="1:2">
+      <c r="A1697" s="2"/>
+      <c r="B1697" s="2"/>
+    </row>
+    <row r="1698" ht="25" customHeight="1" spans="1:2">
+      <c r="A1698" s="2"/>
+      <c r="B1698" s="2"/>
+    </row>
+    <row r="1699" ht="25" customHeight="1" spans="1:2">
+      <c r="A1699" s="2"/>
+      <c r="B1699" s="2"/>
+    </row>
+    <row r="1700" ht="25" customHeight="1" spans="1:2">
+      <c r="A1700" s="2"/>
+      <c r="B1700" s="2"/>
+    </row>
+    <row r="1701" ht="25" customHeight="1" spans="1:2">
+      <c r="A1701" s="2"/>
+      <c r="B1701" s="2"/>
+    </row>
+    <row r="1702" ht="25" customHeight="1" spans="1:2">
+      <c r="A1702" s="2"/>
+      <c r="B1702" s="2"/>
+    </row>
+    <row r="1703" ht="25" customHeight="1" spans="1:2">
+      <c r="A1703" s="2"/>
+      <c r="B1703" s="2"/>
+    </row>
+    <row r="1704" ht="25" customHeight="1" spans="1:2">
+      <c r="A1704" s="2"/>
+      <c r="B1704" s="2"/>
+    </row>
+    <row r="1705" ht="25" customHeight="1" spans="1:2">
+      <c r="A1705" s="2"/>
+      <c r="B1705" s="2"/>
+    </row>
+    <row r="1706" ht="25" customHeight="1" spans="1:2">
+      <c r="A1706" s="2"/>
+      <c r="B1706" s="2"/>
+    </row>
+    <row r="1707" ht="25" customHeight="1" spans="1:2">
+      <c r="A1707" s="2"/>
+      <c r="B1707" s="2"/>
+    </row>
+    <row r="1708" ht="25" customHeight="1" spans="1:2">
+      <c r="A1708" s="2"/>
+      <c r="B1708" s="2"/>
+    </row>
+    <row r="1709" ht="25" customHeight="1" spans="1:2">
+      <c r="A1709" s="2"/>
+      <c r="B1709" s="2"/>
+    </row>
+    <row r="1710" ht="25" customHeight="1" spans="1:2">
+      <c r="A1710" s="2"/>
+      <c r="B1710" s="2"/>
+    </row>
+    <row r="1711" ht="25" customHeight="1" spans="1:2">
+      <c r="A1711" s="2"/>
+      <c r="B1711" s="2"/>
+    </row>
+    <row r="1712" ht="25" customHeight="1" spans="1:2">
+      <c r="A1712" s="2"/>
+      <c r="B1712" s="2"/>
+    </row>
+    <row r="1713" ht="25" customHeight="1" spans="1:2">
+      <c r="A1713" s="2"/>
+      <c r="B1713" s="2"/>
+    </row>
+    <row r="1714" ht="25" customHeight="1" spans="1:2">
+      <c r="A1714" s="2"/>
+      <c r="B1714" s="2"/>
+    </row>
+    <row r="1715" ht="25" customHeight="1" spans="1:2">
+      <c r="A1715" s="2"/>
+      <c r="B1715" s="2"/>
+    </row>
+    <row r="1716" ht="25" customHeight="1" spans="1:2">
+      <c r="A1716" s="2"/>
+      <c r="B1716" s="2"/>
+    </row>
+    <row r="1717" ht="25" customHeight="1" spans="1:2">
+      <c r="A1717" s="2"/>
+      <c r="B1717" s="2"/>
+    </row>
+    <row r="1718" ht="25" customHeight="1" spans="1:2">
+      <c r="A1718" s="2"/>
+      <c r="B1718" s="2"/>
+    </row>
+    <row r="1719" ht="25" customHeight="1" spans="1:2">
+      <c r="A1719" s="2"/>
+      <c r="B1719" s="2"/>
+    </row>
+    <row r="1720" ht="25" customHeight="1" spans="1:2">
+      <c r="A1720" s="2"/>
+      <c r="B1720" s="2"/>
+    </row>
+    <row r="1721" ht="25" customHeight="1" spans="1:2">
+      <c r="A1721" s="2"/>
+      <c r="B1721" s="2"/>
+    </row>
+    <row r="1722" ht="25" customHeight="1" spans="1:2">
+      <c r="A1722" s="2"/>
+      <c r="B1722" s="2"/>
+    </row>
+    <row r="1723" ht="25" customHeight="1" spans="1:2">
+      <c r="A1723" s="2"/>
+      <c r="B1723" s="2"/>
+    </row>
+    <row r="1724" ht="25" customHeight="1" spans="1:2">
+      <c r="A1724" s="2"/>
+      <c r="B1724" s="2"/>
+    </row>
+    <row r="1725" ht="25" customHeight="1" spans="1:2">
+      <c r="A1725" s="2"/>
+      <c r="B1725" s="2"/>
+    </row>
+    <row r="1726" ht="25" customHeight="1" spans="1:2">
+      <c r="A1726" s="2"/>
+      <c r="B1726" s="2"/>
+    </row>
+    <row r="1727" ht="25" customHeight="1" spans="1:2">
+      <c r="A1727" s="2"/>
+      <c r="B1727" s="2"/>
+    </row>
+    <row r="1728" ht="25" customHeight="1" spans="1:2">
+      <c r="A1728" s="2"/>
+      <c r="B1728" s="2"/>
+    </row>
+    <row r="1729" ht="25" customHeight="1" spans="1:2">
+      <c r="A1729" s="2"/>
+      <c r="B1729" s="2"/>
+    </row>
+    <row r="1730" ht="25" customHeight="1" spans="1:2">
+      <c r="A1730" s="2"/>
+      <c r="B1730" s="2"/>
+    </row>
+    <row r="1731" ht="25" customHeight="1" spans="1:2">
+      <c r="A1731" s="2"/>
+      <c r="B1731" s="2"/>
+    </row>
+    <row r="1732" ht="25" customHeight="1" spans="1:2">
+      <c r="A1732" s="2"/>
+      <c r="B1732" s="2"/>
+    </row>
+    <row r="1733" ht="25" customHeight="1" spans="1:2">
+      <c r="A1733" s="2"/>
+      <c r="B1733" s="2"/>
+    </row>
+    <row r="1734" ht="25" customHeight="1" spans="1:2">
+      <c r="A1734" s="2"/>
+      <c r="B1734" s="2"/>
+    </row>
+    <row r="1735" ht="25" customHeight="1" spans="1:2">
+      <c r="A1735" s="2"/>
+      <c r="B1735" s="2"/>
+    </row>
+    <row r="1736" ht="25" customHeight="1" spans="1:2">
+      <c r="A1736" s="2"/>
+      <c r="B1736" s="2"/>
+    </row>
+    <row r="1737" ht="25" customHeight="1" spans="1:2">
+      <c r="A1737" s="2"/>
+      <c r="B1737" s="2"/>
+    </row>
+    <row r="1738" ht="25" customHeight="1" spans="1:2">
+      <c r="A1738" s="2"/>
+      <c r="B1738" s="2"/>
+    </row>
+    <row r="1739" ht="25" customHeight="1" spans="1:2">
+      <c r="A1739" s="2"/>
+      <c r="B1739" s="2"/>
+    </row>
+    <row r="1740" ht="25" customHeight="1" spans="1:2">
+      <c r="A1740" s="2"/>
+      <c r="B1740" s="2"/>
+    </row>
+    <row r="1741" ht="25" customHeight="1" spans="1:2">
+      <c r="A1741" s="2"/>
+      <c r="B1741" s="2"/>
+    </row>
+    <row r="1742" ht="25" customHeight="1" spans="1:2">
+      <c r="A1742" s="2"/>
+      <c r="B1742" s="2"/>
+    </row>
+    <row r="1743" ht="25" customHeight="1" spans="1:2">
+      <c r="A1743" s="2"/>
+      <c r="B1743" s="2"/>
+    </row>
+    <row r="1744" ht="25" customHeight="1" spans="1:2">
+      <c r="A1744" s="2"/>
+      <c r="B1744" s="2"/>
+    </row>
+    <row r="1745" ht="25" customHeight="1" spans="1:2">
+      <c r="A1745" s="2"/>
+      <c r="B1745" s="2"/>
+    </row>
+    <row r="1746" ht="25" customHeight="1" spans="1:2">
+      <c r="A1746" s="2"/>
+      <c r="B1746" s="2"/>
+    </row>
+    <row r="1747" ht="25" customHeight="1" spans="1:2">
+      <c r="A1747" s="2"/>
+      <c r="B1747" s="2"/>
+    </row>
+    <row r="1748" ht="25" customHeight="1" spans="1:2">
+      <c r="A1748" s="2"/>
+      <c r="B1748" s="2"/>
+    </row>
+    <row r="1749" ht="25" customHeight="1" spans="1:2">
+      <c r="A1749" s="2"/>
+      <c r="B1749" s="2"/>
+    </row>
+    <row r="1750" ht="25" customHeight="1" spans="1:2">
+      <c r="A1750" s="2"/>
+      <c r="B1750" s="2"/>
+    </row>
+    <row r="1751" ht="25" customHeight="1" spans="1:2">
+      <c r="A1751" s="2"/>
+      <c r="B1751" s="2"/>
+    </row>
+    <row r="1752" ht="25" customHeight="1" spans="1:2">
+      <c r="A1752" s="2"/>
+      <c r="B1752" s="2"/>
+    </row>
+    <row r="1753" ht="25" customHeight="1" spans="1:2">
+      <c r="A1753" s="2"/>
+      <c r="B1753" s="2"/>
+    </row>
+    <row r="1754" ht="25" customHeight="1" spans="1:2">
+      <c r="A1754" s="2"/>
+      <c r="B1754" s="2"/>
+    </row>
+    <row r="1755" ht="25" customHeight="1" spans="1:2">
+      <c r="A1755" s="2"/>
+      <c r="B1755" s="2"/>
+    </row>
+    <row r="1756" ht="25" customHeight="1" spans="1:2">
+      <c r="A1756" s="2"/>
+      <c r="B1756" s="2"/>
+    </row>
+    <row r="1757" ht="25" customHeight="1" spans="1:2">
+      <c r="A1757" s="2"/>
+      <c r="B1757" s="2"/>
+    </row>
+    <row r="1758" ht="25" customHeight="1" spans="1:2">
+      <c r="A1758" s="2"/>
+      <c r="B1758" s="2"/>
+    </row>
+    <row r="1759" ht="25" customHeight="1" spans="1:2">
+      <c r="A1759" s="2"/>
+      <c r="B1759" s="2"/>
+    </row>
+    <row r="1760" ht="25" customHeight="1" spans="1:2">
+      <c r="A1760" s="2"/>
+      <c r="B1760" s="2"/>
+    </row>
+    <row r="1761" ht="25" customHeight="1" spans="1:2">
+      <c r="A1761" s="2"/>
+      <c r="B1761" s="2"/>
+    </row>
+    <row r="1762" ht="25" customHeight="1" spans="1:2">
+      <c r="A1762" s="2"/>
+      <c r="B1762" s="2"/>
+    </row>
+    <row r="1763" ht="25" customHeight="1" spans="1:2">
+      <c r="A1763" s="2"/>
+      <c r="B1763" s="2"/>
+    </row>
+    <row r="1764" ht="25" customHeight="1" spans="1:2">
+      <c r="A1764" s="2"/>
+      <c r="B1764" s="2"/>
+    </row>
+    <row r="1765" ht="25" customHeight="1" spans="1:2">
+      <c r="A1765" s="2"/>
+      <c r="B1765" s="2"/>
+    </row>
+    <row r="1766" ht="25" customHeight="1" spans="1:2">
+      <c r="A1766" s="2"/>
+      <c r="B1766" s="2"/>
+    </row>
+    <row r="1767" ht="25" customHeight="1" spans="1:2">
+      <c r="A1767" s="2"/>
+      <c r="B1767" s="2"/>
+    </row>
+    <row r="1768" ht="25" customHeight="1" spans="1:2">
+      <c r="A1768" s="2"/>
+      <c r="B1768" s="2"/>
+    </row>
+    <row r="1769" ht="25" customHeight="1" spans="1:2">
+      <c r="A1769" s="2"/>
+      <c r="B1769" s="2"/>
+    </row>
+    <row r="1770" ht="25" customHeight="1" spans="1:2">
+      <c r="A1770" s="2"/>
+      <c r="B1770" s="2"/>
+    </row>
+    <row r="1771" ht="25" customHeight="1" spans="1:2">
+      <c r="A1771" s="2"/>
+      <c r="B1771" s="2"/>
+    </row>
+    <row r="1772" ht="25" customHeight="1" spans="1:2">
+      <c r="A1772" s="2"/>
+      <c r="B1772" s="2"/>
+    </row>
+    <row r="1773" ht="25" customHeight="1" spans="1:2">
+      <c r="A1773" s="2"/>
+      <c r="B1773" s="2"/>
+    </row>
+    <row r="1774" ht="25" customHeight="1" spans="1:2">
+      <c r="A1774" s="2"/>
+      <c r="B1774" s="2"/>
+    </row>
+    <row r="1775" ht="25" customHeight="1" spans="1:2">
+      <c r="A1775" s="2"/>
+      <c r="B1775" s="2"/>
+    </row>
+    <row r="1776" ht="25" customHeight="1" spans="1:2">
+      <c r="A1776" s="2"/>
+      <c r="B1776" s="2"/>
+    </row>
+    <row r="1777" ht="25" customHeight="1" spans="1:2">
+      <c r="A1777" s="2"/>
+      <c r="B1777" s="2"/>
+    </row>
+    <row r="1778" ht="25" customHeight="1" spans="1:2">
+      <c r="A1778" s="2"/>
+      <c r="B1778" s="2"/>
+    </row>
+    <row r="1779" ht="25" customHeight="1" spans="1:2">
+      <c r="A1779" s="2"/>
+      <c r="B1779" s="2"/>
+    </row>
+    <row r="1780" ht="25" customHeight="1" spans="1:2">
+      <c r="A1780" s="2"/>
+      <c r="B1780" s="2"/>
+    </row>
+    <row r="1781" ht="25" customHeight="1" spans="1:2">
+      <c r="A1781" s="2"/>
+      <c r="B1781" s="2"/>
+    </row>
+    <row r="1782" ht="25" customHeight="1" spans="1:2">
+      <c r="A1782" s="2"/>
+      <c r="B1782" s="2"/>
+    </row>
+    <row r="1783" ht="25" customHeight="1" spans="1:2">
+      <c r="A1783" s="2"/>
+      <c r="B1783" s="2"/>
+    </row>
+    <row r="1784" ht="25" customHeight="1" spans="1:2">
+      <c r="A1784" s="2"/>
+      <c r="B1784" s="2"/>
+    </row>
+    <row r="1785" ht="25" customHeight="1" spans="1:2">
+      <c r="A1785" s="2"/>
+      <c r="B1785" s="2"/>
+    </row>
+    <row r="1786" ht="25" customHeight="1" spans="1:2">
+      <c r="A1786" s="2"/>
+      <c r="B1786" s="2"/>
+    </row>
+    <row r="1787" ht="25" customHeight="1" spans="1:2">
+      <c r="A1787" s="2"/>
+      <c r="B1787" s="2"/>
+    </row>
+    <row r="1788" ht="25" customHeight="1" spans="1:2">
+      <c r="A1788" s="2"/>
+      <c r="B1788" s="2"/>
+    </row>
+    <row r="1789" ht="25" customHeight="1" spans="1:2">
+      <c r="A1789" s="2"/>
+      <c r="B1789" s="2"/>
+    </row>
+    <row r="1790" ht="25" customHeight="1" spans="1:2">
+      <c r="A1790" s="2"/>
+      <c r="B1790" s="2"/>
+    </row>
+    <row r="1791" ht="25" customHeight="1" spans="1:2">
+      <c r="A1791" s="2"/>
+      <c r="B1791" s="2"/>
+    </row>
+    <row r="1792" ht="25" customHeight="1" spans="1:2">
+      <c r="A1792" s="2"/>
+      <c r="B1792" s="2"/>
+    </row>
+    <row r="1793" ht="25" customHeight="1" spans="1:2">
+      <c r="A1793" s="2"/>
+      <c r="B1793" s="2"/>
+    </row>
+    <row r="1794" ht="25" customHeight="1" spans="1:2">
+      <c r="A1794" s="2"/>
+      <c r="B1794" s="2"/>
+    </row>
+    <row r="1795" ht="25" customHeight="1" spans="1:2">
+      <c r="A1795" s="2"/>
+      <c r="B1795" s="2"/>
+    </row>
+    <row r="1796" ht="25" customHeight="1" spans="1:2">
+      <c r="A1796" s="2"/>
+      <c r="B1796" s="2"/>
+    </row>
+    <row r="1797" ht="25" customHeight="1" spans="1:2">
+      <c r="A1797" s="2"/>
+      <c r="B1797" s="2"/>
+    </row>
+    <row r="1798" ht="25" customHeight="1" spans="1:2">
+      <c r="A1798" s="2"/>
+      <c r="B1798" s="2"/>
+    </row>
+    <row r="1799" ht="25" customHeight="1" spans="1:2">
+      <c r="A1799" s="2"/>
+      <c r="B1799" s="2"/>
+    </row>
+    <row r="1800" ht="25" customHeight="1" spans="1:2">
+      <c r="A1800" s="2"/>
+      <c r="B1800" s="2"/>
+    </row>
+    <row r="1801" ht="25" customHeight="1" spans="1:2">
+      <c r="A1801" s="2"/>
+      <c r="B1801" s="2"/>
+    </row>
+    <row r="1802" ht="25" customHeight="1" spans="1:2">
+      <c r="A1802" s="2"/>
+      <c r="B1802" s="2"/>
+    </row>
+    <row r="1803" ht="25" customHeight="1" spans="1:2">
+      <c r="A1803" s="2"/>
+      <c r="B1803" s="2"/>
+    </row>
+    <row r="1804" ht="25" customHeight="1" spans="1:2">
+      <c r="A1804" s="2"/>
+      <c r="B1804" s="2"/>
+    </row>
+    <row r="1805" ht="25" customHeight="1" spans="1:2">
+      <c r="A1805" s="2"/>
+      <c r="B1805" s="2"/>
+    </row>
+    <row r="1806" ht="25" customHeight="1" spans="1:2">
+      <c r="A1806" s="2"/>
+      <c r="B1806" s="2"/>
+    </row>
+    <row r="1807" ht="25" customHeight="1" spans="1:2">
+      <c r="A1807" s="2"/>
+      <c r="B1807" s="2"/>
+    </row>
+    <row r="1808" ht="25" customHeight="1" spans="1:2">
+      <c r="A1808" s="2"/>
+      <c r="B1808" s="2"/>
+    </row>
+    <row r="1809" ht="25" customHeight="1" spans="1:2">
+      <c r="A1809" s="2"/>
+      <c r="B1809" s="2"/>
+    </row>
+    <row r="1810" ht="25" customHeight="1" spans="1:2">
+      <c r="A1810" s="2"/>
+      <c r="B1810" s="2"/>
+    </row>
+    <row r="1811" ht="25" customHeight="1" spans="1:2">
+      <c r="A1811" s="2"/>
+      <c r="B1811" s="2"/>
+    </row>
+    <row r="1812" ht="25" customHeight="1" spans="1:2">
+      <c r="A1812" s="2"/>
+      <c r="B1812" s="2"/>
+    </row>
+    <row r="1813" ht="25" customHeight="1" spans="1:2">
+      <c r="A1813" s="2"/>
+      <c r="B1813" s="2"/>
+    </row>
+    <row r="1814" ht="25" customHeight="1" spans="1:2">
+      <c r="A1814" s="2"/>
+      <c r="B1814" s="2"/>
+    </row>
+    <row r="1815" ht="25" customHeight="1" spans="1:2">
+      <c r="A1815" s="2"/>
+      <c r="B1815" s="2"/>
+    </row>
+    <row r="1816" ht="25" customHeight="1" spans="1:2">
+      <c r="A1816" s="2"/>
+      <c r="B1816" s="2"/>
+    </row>
+    <row r="1817" ht="25" customHeight="1" spans="1:2">
+      <c r="A1817" s="2"/>
+      <c r="B1817" s="2"/>
+    </row>
+    <row r="1818" ht="25" customHeight="1" spans="1:2">
+      <c r="A1818" s="2"/>
+      <c r="B1818" s="2"/>
+    </row>
+    <row r="1819" ht="25" customHeight="1" spans="1:2">
+      <c r="A1819" s="2"/>
+      <c r="B1819" s="2"/>
+    </row>
+    <row r="1820" ht="25" customHeight="1" spans="1:2">
+      <c r="A1820" s="2"/>
+      <c r="B1820" s="2"/>
+    </row>
+    <row r="1821" ht="25" customHeight="1" spans="1:2">
+      <c r="A1821" s="2"/>
+      <c r="B1821" s="2"/>
+    </row>
+    <row r="1822" ht="25" customHeight="1" spans="1:2">
+      <c r="A1822" s="2"/>
+      <c r="B1822" s="2"/>
+    </row>
+    <row r="1823" ht="25" customHeight="1" spans="1:2">
+      <c r="A1823" s="2"/>
+      <c r="B1823" s="2"/>
+    </row>
+    <row r="1824" ht="25" customHeight="1" spans="1:2">
+      <c r="A1824" s="2"/>
+      <c r="B1824" s="2"/>
+    </row>
+    <row r="1825" ht="25" customHeight="1" spans="1:2">
+      <c r="A1825" s="2"/>
+      <c r="B1825" s="2"/>
+    </row>
+    <row r="1826" ht="25" customHeight="1" spans="1:2">
+      <c r="A1826" s="2"/>
+      <c r="B1826" s="2"/>
+    </row>
+    <row r="1827" ht="25" customHeight="1" spans="1:2">
+      <c r="A1827" s="2"/>
+      <c r="B1827" s="2"/>
+    </row>
+    <row r="1828" ht="25" customHeight="1" spans="1:2">
+      <c r="A1828" s="2"/>
+      <c r="B1828" s="2"/>
+    </row>
+    <row r="1829" ht="25" customHeight="1" spans="1:2">
+      <c r="A1829" s="2"/>
+      <c r="B1829" s="2"/>
+    </row>
+    <row r="1830" ht="25" customHeight="1" spans="1:2">
+      <c r="A1830" s="2"/>
+      <c r="B1830" s="2"/>
+    </row>
+    <row r="1831" ht="25" customHeight="1" spans="1:2">
+      <c r="A1831" s="2"/>
+      <c r="B1831" s="2"/>
+    </row>
+    <row r="1832" ht="25" customHeight="1" spans="1:2">
+      <c r="A1832" s="2"/>
+      <c r="B1832" s="2"/>
+    </row>
+    <row r="1833" ht="25" customHeight="1" spans="1:2">
+      <c r="A1833" s="2"/>
+      <c r="B1833" s="2"/>
+    </row>
+    <row r="1834" ht="25" customHeight="1" spans="1:2">
+      <c r="A1834" s="2"/>
+      <c r="B1834" s="2"/>
+    </row>
+    <row r="1835" ht="25" customHeight="1" spans="1:2">
+      <c r="A1835" s="2"/>
+      <c r="B1835" s="2"/>
+    </row>
+    <row r="1836" ht="25" customHeight="1" spans="1:2">
+      <c r="A1836" s="2"/>
+      <c r="B1836" s="2"/>
+    </row>
+    <row r="1837" ht="25" customHeight="1" spans="1:2">
+      <c r="A1837" s="2"/>
+      <c r="B1837" s="2"/>
+    </row>
+    <row r="1838" ht="25" customHeight="1" spans="1:2">
+      <c r="A1838" s="2"/>
+      <c r="B1838" s="2"/>
+    </row>
+    <row r="1839" ht="25" customHeight="1" spans="1:2">
+      <c r="A1839" s="2"/>
+      <c r="B1839" s="2"/>
+    </row>
+    <row r="1840" ht="25" customHeight="1" spans="1:2">
+      <c r="A1840" s="2"/>
+      <c r="B1840" s="2"/>
+    </row>
+    <row r="1841" ht="25" customHeight="1" spans="1:2">
+      <c r="A1841" s="2"/>
+      <c r="B1841" s="2"/>
+    </row>
+    <row r="1842" ht="25" customHeight="1" spans="1:2">
+      <c r="A1842" s="2"/>
+      <c r="B1842" s="2"/>
+    </row>
+    <row r="1843" ht="25" customHeight="1" spans="1:2">
+      <c r="A1843" s="2"/>
+      <c r="B1843" s="2"/>
+    </row>
+    <row r="1844" ht="25" customHeight="1" spans="1:2">
+      <c r="A1844" s="2"/>
+      <c r="B1844" s="2"/>
+    </row>
+    <row r="1845" ht="25" customHeight="1" spans="1:2">
+      <c r="A1845" s="2"/>
+      <c r="B1845" s="2"/>
+    </row>
+    <row r="1846" ht="25" customHeight="1" spans="1:2">
+      <c r="A1846" s="2"/>
+      <c r="B1846" s="2"/>
+    </row>
+    <row r="1847" ht="25" customHeight="1" spans="1:2">
+      <c r="A1847" s="2"/>
+      <c r="B1847" s="2"/>
+    </row>
+    <row r="1848" ht="25" customHeight="1" spans="1:2">
+      <c r="A1848" s="2"/>
+      <c r="B1848" s="2"/>
+    </row>
+    <row r="1849" ht="25" customHeight="1" spans="1:2">
+      <c r="A1849" s="2"/>
+      <c r="B1849" s="2"/>
+    </row>
+    <row r="1850" ht="25" customHeight="1" spans="1:2">
+      <c r="A1850" s="2"/>
+      <c r="B1850" s="2"/>
+    </row>
+    <row r="1851" ht="25" customHeight="1" spans="1:2">
+      <c r="A1851" s="2"/>
+      <c r="B1851" s="2"/>
+    </row>
+    <row r="1852" ht="25" customHeight="1" spans="1:2">
+      <c r="A1852" s="2"/>
+      <c r="B1852" s="2"/>
+    </row>
+    <row r="1853" ht="25" customHeight="1" spans="1:2">
+      <c r="A1853" s="2"/>
+      <c r="B1853" s="2"/>
+    </row>
+    <row r="1854" ht="25" customHeight="1" spans="1:2">
+      <c r="A1854" s="2"/>
+      <c r="B1854" s="2"/>
+    </row>
+    <row r="1855" ht="25" customHeight="1" spans="1:2">
+      <c r="A1855" s="2"/>
+      <c r="B1855" s="2"/>
+    </row>
+    <row r="1856" ht="25" customHeight="1" spans="1:2">
+      <c r="A1856" s="2"/>
+      <c r="B1856" s="2"/>
+    </row>
+    <row r="1857" ht="25" customHeight="1" spans="1:2">
+      <c r="A1857" s="2"/>
+      <c r="B1857" s="2"/>
+    </row>
+    <row r="1858" ht="25" customHeight="1" spans="1:2">
+      <c r="A1858" s="2"/>
+      <c r="B1858" s="2"/>
+    </row>
+    <row r="1859" ht="25" customHeight="1" spans="1:2">
+      <c r="A1859" s="2"/>
+      <c r="B1859" s="2"/>
+    </row>
+    <row r="1860" ht="25" customHeight="1" spans="1:2">
+      <c r="A1860" s="2"/>
+      <c r="B1860" s="2"/>
+    </row>
+    <row r="1861" ht="25" customHeight="1" spans="1:2">
+      <c r="A1861" s="2"/>
+      <c r="B1861" s="2"/>
+    </row>
+    <row r="1862" ht="25" customHeight="1" spans="1:2">
+      <c r="A1862" s="2"/>
+      <c r="B1862" s="2"/>
+    </row>
+    <row r="1863" ht="25" customHeight="1" spans="1:2">
+      <c r="A1863" s="2"/>
+      <c r="B1863" s="2"/>
+    </row>
+    <row r="1864" ht="25" customHeight="1" spans="1:2">
+      <c r="A1864" s="2"/>
+      <c r="B1864" s="2"/>
+    </row>
+    <row r="1865" ht="25" customHeight="1" spans="1:2">
+      <c r="A1865" s="2"/>
+      <c r="B1865" s="2"/>
+    </row>
+    <row r="1866" ht="25" customHeight="1" spans="1:2">
+      <c r="A1866" s="2"/>
+      <c r="B1866" s="2"/>
+    </row>
+    <row r="1867" ht="25" customHeight="1" spans="1:2">
+      <c r="A1867" s="2"/>
+      <c r="B1867" s="2"/>
+    </row>
+    <row r="1868" ht="25" customHeight="1" spans="1:2">
+      <c r="A1868" s="2"/>
+      <c r="B1868" s="2"/>
+    </row>
+    <row r="1869" ht="25" customHeight="1" spans="1:2">
+      <c r="A1869" s="2"/>
+      <c r="B1869" s="2"/>
+    </row>
+    <row r="1870" ht="25" customHeight="1" spans="1:2">
+      <c r="A1870" s="2"/>
+      <c r="B1870" s="2"/>
+    </row>
+    <row r="1871" ht="25" customHeight="1" spans="1:2">
+      <c r="A1871" s="2"/>
+      <c r="B1871" s="2"/>
+    </row>
+    <row r="1872" ht="25" customHeight="1" spans="1:2">
+      <c r="A1872" s="2"/>
+      <c r="B1872" s="2"/>
+    </row>
+    <row r="1873" ht="25" customHeight="1" spans="1:2">
+      <c r="A1873" s="2"/>
+      <c r="B1873" s="2"/>
+    </row>
+    <row r="1874" ht="25" customHeight="1" spans="1:2">
+      <c r="A1874" s="2"/>
+      <c r="B1874" s="2"/>
+    </row>
+    <row r="1875" ht="25" customHeight="1" spans="1:2">
+      <c r="A1875" s="2"/>
+      <c r="B1875" s="2"/>
+    </row>
+    <row r="1876" ht="25" customHeight="1" spans="1:2">
+      <c r="A1876" s="2"/>
+      <c r="B1876" s="2"/>
+    </row>
+    <row r="1877" ht="25" customHeight="1" spans="1:2">
+      <c r="A1877" s="2"/>
+      <c r="B1877" s="2"/>
+    </row>
+    <row r="1878" ht="25" customHeight="1" spans="1:2">
+      <c r="A1878" s="2"/>
+      <c r="B1878" s="2"/>
+    </row>
+    <row r="1879" ht="25" customHeight="1" spans="1:2">
+      <c r="A1879" s="2"/>
+      <c r="B1879" s="2"/>
+    </row>
+    <row r="1880" ht="25" customHeight="1" spans="1:2">
+      <c r="A1880" s="2"/>
+      <c r="B1880" s="2"/>
+    </row>
+    <row r="1881" ht="25" customHeight="1" spans="1:2">
+      <c r="A1881" s="2"/>
+      <c r="B1881" s="2"/>
+    </row>
+    <row r="1882" ht="25" customHeight="1" spans="1:2">
+      <c r="A1882" s="2"/>
+      <c r="B1882" s="2"/>
+    </row>
+    <row r="1883" ht="25" customHeight="1" spans="1:2">
+      <c r="A1883" s="2"/>
+      <c r="B1883" s="2"/>
+    </row>
+    <row r="1884" ht="25" customHeight="1" spans="1:2">
+      <c r="A1884" s="2"/>
+      <c r="B1884" s="2"/>
+    </row>
+    <row r="1885" ht="25" customHeight="1" spans="1:2">
+      <c r="A1885" s="2"/>
+      <c r="B1885" s="2"/>
+    </row>
+    <row r="1886" ht="25" customHeight="1" spans="1:2">
+      <c r="A1886" s="2"/>
+      <c r="B1886" s="2"/>
+    </row>
+    <row r="1887" ht="25" customHeight="1" spans="1:2">
+      <c r="A1887" s="2"/>
+      <c r="B1887" s="2"/>
+    </row>
+    <row r="1888" ht="25" customHeight="1" spans="1:2">
+      <c r="A1888" s="2"/>
+      <c r="B1888" s="2"/>
+    </row>
+    <row r="1889" ht="25" customHeight="1" spans="1:2">
+      <c r="A1889" s="2"/>
+      <c r="B1889" s="2"/>
+    </row>
+    <row r="1890" ht="25" customHeight="1" spans="1:2">
+      <c r="A1890" s="2"/>
+      <c r="B1890" s="2"/>
+    </row>
+    <row r="1891" ht="25" customHeight="1" spans="1:2">
+      <c r="A1891" s="2"/>
+      <c r="B1891" s="2"/>
+    </row>
+    <row r="1892" ht="25" customHeight="1" spans="1:2">
+      <c r="A1892" s="2"/>
+      <c r="B1892" s="2"/>
+    </row>
+    <row r="1893" ht="25" customHeight="1" spans="1:2">
+      <c r="A1893" s="2"/>
+      <c r="B1893" s="2"/>
+    </row>
+    <row r="1894" ht="25" customHeight="1" spans="1:2">
+      <c r="A1894" s="2"/>
+      <c r="B1894" s="2"/>
+    </row>
+    <row r="1895" ht="25" customHeight="1" spans="1:2">
+      <c r="A1895" s="2"/>
+      <c r="B1895" s="2"/>
+    </row>
+    <row r="1896" ht="25" customHeight="1" spans="1:2">
+      <c r="A1896" s="2"/>
+      <c r="B1896" s="2"/>
+    </row>
+    <row r="1897" ht="25" customHeight="1" spans="1:2">
+      <c r="A1897" s="2"/>
+      <c r="B1897" s="2"/>
+    </row>
+    <row r="1898" ht="25" customHeight="1" spans="1:2">
+      <c r="A1898" s="2"/>
+      <c r="B1898" s="2"/>
+    </row>
+    <row r="1899" ht="25" customHeight="1" spans="1:2">
+      <c r="A1899" s="2"/>
+      <c r="B1899" s="2"/>
+    </row>
+    <row r="1900" ht="25" customHeight="1" spans="1:2">
+      <c r="A1900" s="2"/>
+      <c r="B1900" s="2"/>
+    </row>
+    <row r="1901" ht="25" customHeight="1" spans="1:2">
+      <c r="A1901" s="2"/>
+      <c r="B1901" s="2"/>
+    </row>
+    <row r="1902" ht="25" customHeight="1" spans="1:2">
+      <c r="A1902" s="2"/>
+      <c r="B1902" s="2"/>
+    </row>
+    <row r="1903" ht="25" customHeight="1" spans="1:2">
+      <c r="A1903" s="2"/>
+      <c r="B1903" s="2"/>
+    </row>
+    <row r="1904" ht="25" customHeight="1" spans="1:2">
+      <c r="A1904" s="2"/>
+      <c r="B1904" s="2"/>
+    </row>
+    <row r="1905" ht="25" customHeight="1" spans="1:2">
+      <c r="A1905" s="2"/>
+      <c r="B1905" s="2"/>
+    </row>
+    <row r="1906" ht="25" customHeight="1" spans="1:2">
+      <c r="A1906" s="2"/>
+      <c r="B1906" s="2"/>
+    </row>
+    <row r="1907" ht="25" customHeight="1" spans="1:2">
+      <c r="A1907" s="2"/>
+      <c r="B1907" s="2"/>
+    </row>
+    <row r="1908" ht="25" customHeight="1" spans="1:2">
+      <c r="A1908" s="2"/>
+      <c r="B1908" s="2"/>
+    </row>
+    <row r="1909" ht="25" customHeight="1" spans="1:2">
+      <c r="A1909" s="2"/>
+      <c r="B1909" s="2"/>
+    </row>
+    <row r="1910" ht="25" customHeight="1" spans="1:2">
+      <c r="A1910" s="2"/>
+      <c r="B1910" s="2"/>
+    </row>
+    <row r="1911" ht="25" customHeight="1" spans="1:2">
+      <c r="A1911" s="2"/>
+      <c r="B1911" s="2"/>
+    </row>
+    <row r="1912" ht="25" customHeight="1" spans="1:2">
+      <c r="A1912" s="2"/>
+      <c r="B1912" s="2"/>
+    </row>
+    <row r="1913" ht="25" customHeight="1" spans="1:2">
+      <c r="A1913" s="2"/>
+      <c r="B1913" s="2"/>
+    </row>
+    <row r="1914" ht="25" customHeight="1" spans="1:2">
+      <c r="A1914" s="2"/>
+      <c r="B1914" s="2"/>
+    </row>
+    <row r="1915" ht="25" customHeight="1" spans="1:2">
+      <c r="A1915" s="2"/>
+      <c r="B1915" s="2"/>
+    </row>
+    <row r="1916" ht="25" customHeight="1" spans="1:2">
+      <c r="A1916" s="2"/>
+      <c r="B1916" s="2"/>
+    </row>
+    <row r="1917" ht="25" customHeight="1" spans="1:2">
+      <c r="A1917" s="2"/>
+      <c r="B1917" s="2"/>
+    </row>
+    <row r="1918" ht="25" customHeight="1" spans="1:2">
+      <c r="A1918" s="2"/>
+      <c r="B1918" s="2"/>
+    </row>
+    <row r="1919" ht="25" customHeight="1" spans="1:2">
+      <c r="A1919" s="2"/>
+      <c r="B1919" s="2"/>
+    </row>
+    <row r="1920" ht="25" customHeight="1" spans="1:2">
+      <c r="A1920" s="2"/>
+      <c r="B1920" s="2"/>
+    </row>
+    <row r="1921" ht="25" customHeight="1" spans="1:2">
+      <c r="A1921" s="2"/>
+      <c r="B1921" s="2"/>
+    </row>
+    <row r="1922" ht="25" customHeight="1" spans="1:2">
+      <c r="A1922" s="2"/>
+      <c r="B1922" s="2"/>
+    </row>
+    <row r="1923" ht="25" customHeight="1" spans="1:2">
+      <c r="A1923" s="2"/>
+      <c r="B1923" s="2"/>
+    </row>
+    <row r="1924" ht="25" customHeight="1" spans="1:2">
+      <c r="A1924" s="2"/>
+      <c r="B1924" s="2"/>
+    </row>
+    <row r="1925" ht="25" customHeight="1" spans="1:2">
+      <c r="A1925" s="2"/>
+      <c r="B1925" s="2"/>
+    </row>
+    <row r="1926" ht="25" customHeight="1" spans="1:2">
+      <c r="A1926" s="2"/>
+      <c r="B1926" s="2"/>
+    </row>
+    <row r="1927" ht="25" customHeight="1" spans="1:2">
+      <c r="A1927" s="2"/>
+      <c r="B1927" s="2"/>
+    </row>
+    <row r="1928" ht="25" customHeight="1" spans="1:2">
+      <c r="A1928" s="2"/>
+      <c r="B1928" s="2"/>
+    </row>
+    <row r="1929" ht="25" customHeight="1" spans="1:2">
+      <c r="A1929" s="2"/>
+      <c r="B1929" s="2"/>
+    </row>
+    <row r="1930" ht="25" customHeight="1" spans="1:2">
+      <c r="A1930" s="2"/>
+      <c r="B1930" s="2"/>
+    </row>
+    <row r="1931" ht="25" customHeight="1" spans="1:2">
+      <c r="A1931" s="2"/>
+      <c r="B1931" s="2"/>
+    </row>
+    <row r="1932" ht="25" customHeight="1" spans="1:2">
+      <c r="A1932" s="2"/>
+      <c r="B1932" s="2"/>
+    </row>
+    <row r="1933" ht="25" customHeight="1" spans="1:2">
+      <c r="A1933" s="2"/>
+      <c r="B1933" s="2"/>
+    </row>
+    <row r="1934" ht="25" customHeight="1" spans="1:2">
+      <c r="A1934" s="2"/>
+      <c r="B1934" s="2"/>
+    </row>
+    <row r="1935" ht="25" customHeight="1" spans="1:2">
+      <c r="A1935" s="2"/>
+      <c r="B1935" s="2"/>
+    </row>
+    <row r="1936" ht="25" customHeight="1" spans="1:2">
+      <c r="A1936" s="2"/>
+      <c r="B1936" s="2"/>
+    </row>
+    <row r="1937" ht="25" customHeight="1" spans="1:2">
+      <c r="A1937" s="2"/>
+      <c r="B1937" s="2"/>
+    </row>
+    <row r="1938" ht="25" customHeight="1" spans="1:2">
+      <c r="A1938" s="2"/>
+      <c r="B1938" s="2"/>
+    </row>
+    <row r="1939" ht="25" customHeight="1" spans="1:2">
+      <c r="A1939" s="2"/>
+      <c r="B1939" s="2"/>
+    </row>
+    <row r="1940" ht="25" customHeight="1" spans="1:2">
+      <c r="A1940" s="2"/>
+      <c r="B1940" s="2"/>
+    </row>
+    <row r="1941" ht="25" customHeight="1" spans="1:2">
+      <c r="A1941" s="2"/>
+      <c r="B1941" s="2"/>
+    </row>
+    <row r="1942" ht="25" customHeight="1" spans="1:2">
+      <c r="A1942" s="2"/>
+      <c r="B1942" s="2"/>
+    </row>
+    <row r="1943" ht="25" customHeight="1" spans="1:2">
+      <c r="A1943" s="2"/>
+      <c r="B1943" s="2"/>
+    </row>
+    <row r="1944" ht="25" customHeight="1" spans="1:2">
+      <c r="A1944" s="2"/>
+      <c r="B1944" s="2"/>
+    </row>
+    <row r="1945" ht="25" customHeight="1" spans="1:2">
+      <c r="A1945" s="2"/>
+      <c r="B1945" s="2"/>
+    </row>
+    <row r="1946" ht="25" customHeight="1" spans="1:2">
+      <c r="A1946" s="2"/>
+      <c r="B1946" s="2"/>
+    </row>
+    <row r="1947" ht="25" customHeight="1" spans="1:2">
+      <c r="A1947" s="2"/>
+      <c r="B1947" s="2"/>
+    </row>
+    <row r="1948" ht="25" customHeight="1" spans="1:2">
+      <c r="A1948" s="2"/>
+      <c r="B1948" s="2"/>
+    </row>
+    <row r="1949" ht="25" customHeight="1" spans="1:2">
+      <c r="A1949" s="2"/>
+      <c r="B1949" s="2"/>
+    </row>
+    <row r="1950" ht="25" customHeight="1" spans="1:2">
+      <c r="A1950" s="2"/>
+      <c r="B1950" s="2"/>
+    </row>
+    <row r="1951" ht="25" customHeight="1" spans="1:2">
+      <c r="A1951" s="2"/>
+      <c r="B1951" s="2"/>
+    </row>
+    <row r="1952" ht="25" customHeight="1" spans="1:2">
+      <c r="A1952" s="2"/>
+      <c r="B1952" s="2"/>
+    </row>
+    <row r="1953" ht="25" customHeight="1" spans="1:2">
+      <c r="A1953" s="2"/>
+      <c r="B1953" s="2"/>
+    </row>
+    <row r="1954" ht="25" customHeight="1" spans="1:2">
+      <c r="A1954" s="2"/>
+      <c r="B1954" s="2"/>
+    </row>
+    <row r="1955" ht="25" customHeight="1" spans="1:2">
+      <c r="A1955" s="2"/>
+      <c r="B1955" s="2"/>
+    </row>
+    <row r="1956" ht="25" customHeight="1" spans="1:2">
+      <c r="A1956" s="2"/>
+      <c r="B1956" s="2"/>
+    </row>
+    <row r="1957" ht="25" customHeight="1" spans="1:2">
+      <c r="A1957" s="2"/>
+      <c r="B1957" s="2"/>
+    </row>
+    <row r="1958" ht="25" customHeight="1" spans="1:2">
+      <c r="A1958" s="2"/>
+      <c r="B1958" s="2"/>
+    </row>
+    <row r="1959" ht="25" customHeight="1" spans="1:2">
+      <c r="A1959" s="2"/>
+      <c r="B1959" s="2"/>
+    </row>
+    <row r="1960" ht="25" customHeight="1" spans="1:2">
+      <c r="A1960" s="2"/>
+      <c r="B1960" s="2"/>
+    </row>
+    <row r="1961" ht="25" customHeight="1" spans="1:2">
+      <c r="A1961" s="2"/>
+      <c r="B1961" s="2"/>
+    </row>
+    <row r="1962" ht="25" customHeight="1" spans="1:2">
+      <c r="A1962" s="2"/>
+      <c r="B1962" s="2"/>
+    </row>
+    <row r="1963" ht="25" customHeight="1" spans="1:2">
+      <c r="A1963" s="2"/>
+      <c r="B1963" s="2"/>
+    </row>
+    <row r="1964" ht="25" customHeight="1" spans="1:2">
+      <c r="A1964" s="2"/>
+      <c r="B1964" s="2"/>
+    </row>
+    <row r="1965" ht="25" customHeight="1" spans="1:2">
+      <c r="A1965" s="2"/>
+      <c r="B1965" s="2"/>
+    </row>
+    <row r="1966" ht="25" customHeight="1" spans="1:2">
+      <c r="A1966" s="2"/>
+      <c r="B1966" s="2"/>
+    </row>
+    <row r="1967" ht="25" customHeight="1" spans="1:2">
+      <c r="A1967" s="2"/>
+      <c r="B1967" s="2"/>
+    </row>
+    <row r="1968" ht="25" customHeight="1" spans="1:2">
+      <c r="A1968" s="2"/>
+      <c r="B1968" s="2"/>
+    </row>
+    <row r="1969" ht="25" customHeight="1" spans="1:2">
+      <c r="A1969" s="2"/>
+      <c r="B1969" s="2"/>
+    </row>
+    <row r="1970" ht="25" customHeight="1" spans="1:2">
+      <c r="A1970" s="2"/>
+      <c r="B1970" s="2"/>
+    </row>
+    <row r="1971" ht="25" customHeight="1" spans="1:2">
+      <c r="A1971" s="2"/>
+      <c r="B1971" s="2"/>
+    </row>
+    <row r="1972" ht="25" customHeight="1" spans="1:2">
+      <c r="A1972" s="2"/>
+      <c r="B1972" s="2"/>
+    </row>
+    <row r="1973" ht="25" customHeight="1" spans="1:2">
+      <c r="A1973" s="2"/>
+      <c r="B1973" s="2"/>
+    </row>
+    <row r="1974" ht="25" customHeight="1" spans="1:2">
+      <c r="A1974" s="2"/>
+      <c r="B1974" s="2"/>
+    </row>
+    <row r="1975" ht="25" customHeight="1" spans="1:2">
+      <c r="A1975" s="2"/>
+      <c r="B1975" s="2"/>
+    </row>
+    <row r="1976" ht="25" customHeight="1" spans="1:2">
+      <c r="A1976" s="2"/>
+      <c r="B1976" s="2"/>
+    </row>
+    <row r="1977" ht="25" customHeight="1" spans="1:2">
+      <c r="A1977" s="2"/>
+      <c r="B1977" s="2"/>
+    </row>
+    <row r="1978" ht="25" customHeight="1" spans="1:2">
+      <c r="A1978" s="2"/>
+      <c r="B1978" s="2"/>
+    </row>
+    <row r="1979" ht="25" customHeight="1" spans="1:2">
+      <c r="A1979" s="2"/>
+      <c r="B1979" s="2"/>
+    </row>
+    <row r="1980" ht="25" customHeight="1" spans="1:2">
+      <c r="A1980" s="2"/>
+      <c r="B1980" s="2"/>
+    </row>
+    <row r="1981" ht="25" customHeight="1" spans="1:2">
+      <c r="A1981" s="2"/>
+      <c r="B1981" s="2"/>
+    </row>
+    <row r="1982" ht="25" customHeight="1" spans="1:2">
+      <c r="A1982" s="2"/>
+      <c r="B1982" s="2"/>
+    </row>
+    <row r="1983" ht="25" customHeight="1" spans="1:2">
+      <c r="A1983" s="2"/>
+      <c r="B1983" s="2"/>
+    </row>
+    <row r="1984" ht="25" customHeight="1" spans="1:2">
+      <c r="A1984" s="2"/>
+      <c r="B1984" s="2"/>
+    </row>
+    <row r="1985" ht="25" customHeight="1" spans="1:2">
+      <c r="A1985" s="2"/>
+      <c r="B1985" s="2"/>
+    </row>
+    <row r="1986" ht="25" customHeight="1" spans="1:2">
+      <c r="A1986" s="2"/>
+      <c r="B1986" s="2"/>
+    </row>
+    <row r="1987" ht="25" customHeight="1" spans="1:2">
+      <c r="A1987" s="2"/>
+      <c r="B1987" s="2"/>
+    </row>
+    <row r="1988" ht="25" customHeight="1" spans="1:2">
+      <c r="A1988" s="2"/>
+      <c r="B1988" s="2"/>
+    </row>
+    <row r="1989" ht="25" customHeight="1" spans="1:2">
+      <c r="A1989" s="2"/>
+      <c r="B1989" s="2"/>
+    </row>
+    <row r="1990" ht="25" customHeight="1" spans="1:2">
+      <c r="A1990" s="2"/>
+      <c r="B1990" s="2"/>
+    </row>
+    <row r="1991" ht="25" customHeight="1" spans="1:2">
+      <c r="A1991" s="2"/>
+      <c r="B1991" s="2"/>
+    </row>
+    <row r="1992" ht="25" customHeight="1" spans="1:2">
+      <c r="A1992" s="2"/>
+      <c r="B1992" s="2"/>
+    </row>
+    <row r="1993" ht="25" customHeight="1" spans="1:2">
+      <c r="A1993" s="2"/>
+      <c r="B1993" s="2"/>
+    </row>
+    <row r="1994" ht="25" customHeight="1" spans="1:2">
+      <c r="A1994" s="2"/>
+      <c r="B1994" s="2"/>
+    </row>
+    <row r="1995" ht="25" customHeight="1" spans="1:2">
+      <c r="A1995" s="2"/>
+      <c r="B1995" s="2"/>
+    </row>
+    <row r="1996" ht="25" customHeight="1" spans="1:2">
+      <c r="A1996" s="2"/>
+      <c r="B1996" s="2"/>
+    </row>
+    <row r="1997" ht="25" customHeight="1" spans="1:2">
+      <c r="A1997" s="2"/>
+      <c r="B1997" s="2"/>
+    </row>
+    <row r="1998" ht="25" customHeight="1" spans="1:2">
+      <c r="A1998" s="2"/>
+      <c r="B1998" s="2"/>
+    </row>
+    <row r="1999" ht="25" customHeight="1" spans="1:2">
+      <c r="A1999" s="2"/>
+      <c r="B1999" s="2"/>
+    </row>
+    <row r="2000" ht="25" customHeight="1" spans="1:2">
+      <c r="A2000" s="2"/>
+      <c r="B2000" s="2"/>
+    </row>
+    <row r="2001" ht="25" customHeight="1" spans="1:2">
+      <c r="A2001" s="2"/>
+      <c r="B2001" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="2296">
   <si>
     <t>bangla</t>
   </si>
@@ -194,13 +194,13 @@
     <t>সমস্যা নাই, আঁই তোঁয়ার লাই অপেক্ষা গইজ্জুম</t>
   </si>
   <si>
-    <t>আমি আগামিকাল আসব</t>
+    <t>আমি আগামীকাল আসব</t>
   </si>
   <si>
     <t>আঁই হালিইয়্যে আইসসুম</t>
   </si>
   <si>
-    <t>সমস্যা নাই, তুমি আগামিকাল আসতে পারবে</t>
+    <t>সমস্যা নাই, তুমি আগামীকাল আসতে পারবে</t>
   </si>
   <si>
     <t>সমস্যা নাই, তুঁই হালিইয়্যে আইত ফারিবে</t>
@@ -242,7 +242,7 @@
     <t>তোঁয়ার দিনহাল কেন যার?</t>
   </si>
   <si>
-    <t>আপনি আগামিকাল আসতে পারবেন?</t>
+    <t>আপনি আগামীকাল আসতে পারবেন?</t>
   </si>
   <si>
     <t>অঁনে হালিইয়্যে আইত ফারিবেন?</t>
@@ -476,7 +476,7 @@
     <t>তোঁয়ার হতা উনি রে আঁর বুকোত ব্যাথা শুরু অই গেইয়্যি</t>
   </si>
   <si>
-    <t>আগামিকাল আমার সাথে দেখা করিও</t>
+    <t>আগামীকাল আমার সাথে দেখা করিও</t>
   </si>
   <si>
     <t>হালিয়্যে আঁর লগে দেহা গইজ্জো</t>
@@ -938,6 +938,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
       <t>যহনই মনে অইবু আঝাই ফেলাইয়্যো, তহনই এক্কানা থামি রে নিজোরে ফুসর গরো</t>
     </r>
     <r>
@@ -1023,7 +1029,7 @@
     <t>তুমি অনেক পরিবর্তন হয়ে গেছো, আমাকে আর আগের মতো ভালোবাসো না</t>
   </si>
   <si>
-    <t>তুঁই বত বদলাই গেইয়্যু, আঁরে আর আগোর মতোন ভালো নবাসো</t>
+    <t>তুঁই বত বদলাই গেইয়্যু, আঁরে আর আগোর মতন ভালো নবাসো</t>
   </si>
   <si>
     <t>আজকে শুক্রবার, সেজন্য আজকে জুমার নামাজ পড়তে হবে</t>
@@ -1296,7 +1302,7 @@
     <t>ফজোরত নামাজ পরি আডিলি বত ভালা লাগে</t>
   </si>
   <si>
-    <t>আগামিকাল পরিক্ষা, সেজন্য সকালে জলদি উঠতে হবে</t>
+    <t>আগামীকাল পরিক্ষা, সেজন্য সকালে জলদি উঠতে হবে</t>
   </si>
   <si>
     <t>হালিয়ে পরিক্ষে, এতেল্লে বেইন্নে তারাতারি উডোন পরিবো</t>
@@ -1602,7 +1608,7 @@
     <t>বাজারোর লিস্ট আগেত্তোন তৈরি ন গরিলি বত সময় দরহারি জিনিস কিনতে ভুলি যায়</t>
   </si>
   <si>
-    <t>আগামিকাল পরিক্ষা, কিন্তু আমার পড়তে মন চাচ্ছে না</t>
+    <t>আগামীকাল পরিক্ষা, কিন্তু আমার পড়তে মন চাচ্ছে না</t>
   </si>
   <si>
     <t>হালিয়ে পরিক্ষে, কিন্তু আত্তুন  পইত্তো মনে ন হর</t>
@@ -2031,7 +2037,7 @@
     <t>সবাই বাড়িতে চলে গেছে, শুধু আমি একা আছি</t>
   </si>
   <si>
-    <t>বিয়াজ্ঞুন বারিত চলি গেইয়্যি, শুধু আঁই এহেল্লে আছি</t>
+    <t>বিয়াজ্ঞুন বারিত চলি গেইয়্যি, উধো আঁই এহেল্লে আছি</t>
   </si>
   <si>
     <t>বারান্দায় মেহমান বসে আছে, গিয়ে নাস্তা দিয়ে আসো</t>
@@ -2760,7 +2766,7 @@
     <t>আঁর আত ব্যথা গরের, আজিয়ে আর ন পারির</t>
   </si>
   <si>
-    <t>বাকি কাজগুলো আগামিকাল দেখব</t>
+    <t>বাকি কাজগুলো আগামীকাল দেখব</t>
   </si>
   <si>
     <t>বাকি হাম এগিন হালিয়ে চাইয়্যুম</t>
@@ -2973,7 +2979,7 @@
     <t>রাতের জন্য ফুলকপির তরকারি আর বেগুন ভর্তা আছে</t>
   </si>
   <si>
-    <t>রাতিয়ের লাই ফুলহপির তরহারি আর বেইয়ুন চান্নি আছে</t>
+    <t>রাতিয়ের লাই ফুলহপ্পির তরহারি আর বেইয়ুন চান্নি আছে</t>
   </si>
   <si>
     <t>দুপুরে ভাত খেয়ে একটু বিশ্রাম নিলে ভাল লাগে</t>
@@ -3795,7 +3801,7 @@
     <t>আমার ছোট ভাই শুধু বাবাকে ভয় পায়</t>
   </si>
   <si>
-    <t>আঁর ছোডো ভাই উদো আব্বুরে ডরাই দে</t>
+    <t>আঁর ছোডো ভাই উধো আব্বুরে ডরাই দে</t>
   </si>
   <si>
     <t>আমার বড় আপু আর ছোট আপু সবসময় ঝগড়া করে</t>
@@ -3849,7 +3855,7 @@
     <t>সারাদিন শুধু এই বাগান আর ওই বাগানে ঘুরাঘুরি করো</t>
   </si>
   <si>
-    <t>আরাদিন উদো এই বাগান আর ওই বাগানুত ঘুরোঘুরি গরো</t>
+    <t>আরাদিন উধো এই বাগান আর ওই বাগানুত ঘুরোঘুরি গরো</t>
   </si>
   <si>
     <t>নিজের ঘরে থাকলে নিজের মতো করে থাকা যায়</t>
@@ -3861,13 +3867,13 @@
     <t>এখন আর নানুর বাড়িতে আগের মতো ভালো লাগে না</t>
   </si>
   <si>
-    <t>এহন আর নানারো বারিত আগোর মতোন ভালা ন লাগে</t>
+    <t>এহন আর নানারো বারিত আগোর মতন ভালা ন লাগে</t>
   </si>
   <si>
     <t>বান্দরের মতো শুধু গাছে গাছে ঘোরে, কোনোদিন পরে হাত পা ভাঙবে কে জানে</t>
   </si>
   <si>
-    <t>বান্দরোর মতোন উদো গাছে গাছে ঘুরে, হনদিন ফরি আত টেং ভাঙিবু হনে জানে</t>
+    <t>বান্দরোর মতোন উধো গাছে গাছে ঘুরে, হনদিন ফরি আত টেং ভাঙিবু হনে জানে</t>
   </si>
   <si>
     <t>আমি ছোটবেলায় তোদের মতো এত দুষ্টু ছিলাম না</t>
@@ -3993,7 +3999,7 @@
     <t>আমার মা সবসময় চায় যেন আমরা তিন ভাই একসাথে থাকি</t>
   </si>
   <si>
-    <t>আঁর মা সবসময় চায় যেন্‌ আরা তিন ভাই এক্কোওয়ারে থাহি</t>
+    <t>আঁর মা সবসময় চায় যেন আঁরা তিন ভাই এক্কোওয়ারে থাহি</t>
   </si>
   <si>
     <t>আমি রমিজের মা, রাতুলের দাদি</t>
@@ -4789,7 +4795,7 @@
     <t>ছেলেটা শুধু এদিক সেদিক ঘুরছে</t>
   </si>
   <si>
-    <t>ফোওয়া ইবে উদো ইক্কেত্তুন উইক্কে ঘুরের</t>
+    <t>ফোওয়া ইবে উধো ইক্কেত্তুন উইক্কে ঘুরের</t>
   </si>
   <si>
     <t>আমি ছেলে হতাম তাহলে অনেক কিছু করতে পারতাম</t>
@@ -4810,7 +4816,7 @@
     <t>পিডে হাবি হইয়্যিরে এহন হনডে চলি গেইয়্যুস?</t>
   </si>
   <si>
-    <t>মা, আমি আজকে যাব না, আগামিকাল আসব</t>
+    <t>মা, আমি আজকে যাব না, আগামীকাল আসব</t>
   </si>
   <si>
     <t>আম্মু, আঁই আজিয়ে ন যাইয়্যুম, হালিয়ে আইসসুম</t>
@@ -5173,7 +5179,7 @@
     <t>আমার জন্য শুধু দোয়া করলেই হবে, আর কিছু লাগবে না</t>
   </si>
   <si>
-    <t>আঁর লাই উদো দোয়া গরিলিই অইবু, আর কিছু ন লাগিবু</t>
+    <t>আঁর লাই উধো দোয়া গরিলিই অইবু, আর কিছু ন লাগিবু</t>
   </si>
   <si>
     <t>ঢাকনা খুলিও না, পানি পড়ে যাবে</t>
@@ -5695,7 +5701,7 @@
     <t>সাদা রঙের পাঞ্জাবিতে শুধু দাগ লেগে যায়</t>
   </si>
   <si>
-    <t>সাদা রঙুর পাঞ্জাবিত উদো দাগ লাগি যায়</t>
+    <t>সাদা রঙুর পাঞ্জাবিত উধো দাগ লাগি যায়</t>
   </si>
   <si>
     <t>দাম এত বেশি কেন বলছো? আরেকটু কমিয়ে রাখো</t>
@@ -5779,7 +5785,7 @@
     <t>শুধু শপিং করলে তো হবে না, ঘরে মাছ-মাংস কিছু নেই</t>
   </si>
   <si>
-    <t>উদো শপিং গরিলি তো ন অইবু, ঘরোত মাছ-গুস্ত কিছু নেই</t>
+    <t>উধো শপিং গরিলি তো ন অইবু, ঘরোত মাছ-গুস্ত কিছু নেই</t>
   </si>
   <si>
     <t>লাউটা কচি আছে, এটা দাও আমাকে</t>
@@ -6293,6 +6299,726 @@
   </si>
   <si>
     <t>ডেলিভারি পাইতে হতদিন লাগিবু?</t>
+  </si>
+  <si>
+    <t>এবার শীতের কালেকশন কেমন আসছে?</t>
+  </si>
+  <si>
+    <t>এবার শীতুর কালেকশন কেন আইসসি?</t>
+  </si>
+  <si>
+    <t>মাছ কিনলে অবশ্যই আসার সময় কেটে নিয়ে আসবেন</t>
+  </si>
+  <si>
+    <t>মাছ কিনিলি অবশ্যই আইবের সমত হাডি লই আইবেন</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> আপনাদের অনলাইন শপে অর্ডার করেছিলাম কিন্তু তিন দিন পরেও ডেলিভারি পাইনি</t>
+  </si>
+  <si>
+    <t>অঁনোরার অনলাইন শ'পুত অর্ডার গইজ্জিলাম কিন্তু তিন দিন পরও ডেলিভারি ন পাই</t>
+  </si>
+  <si>
+    <t>আমার বাজেট বেশি নেই, পাঁচশো টাকার মধ্যে কি ভালো কিছু দেখাতে পারবেন?</t>
+  </si>
+  <si>
+    <t>আঁর বাজেট বেশি নেই, পাঁশশো টিয়ার মধ্যে কি ভালা কিছু দেহাইত ফারিবেন?</t>
+  </si>
+  <si>
+    <t>এই পাঞ্জাবিটা আমি পরে দেখতে চাই, ট্রায়াল রুম কোনদিকে?</t>
+  </si>
+  <si>
+    <t>এই পাঞ্জাবি ইবে আঁই পরি চাইতাম চাইর, ট্রায়াল রুম হুনদি?</t>
+  </si>
+  <si>
+    <t>ল্যাপটপের সাথে গ্যারান্টি কার্ডটাও দিয়ে দেন</t>
+  </si>
+  <si>
+    <t>ল্যাপটপুর লগে গ্যারান্টি কার্ড ইয়েনও দি দন</t>
+  </si>
+  <si>
+    <t>কার্ড দিয়ে পেমেন্ট করা যাবে এখানে?</t>
+  </si>
+  <si>
+    <t>কার্ড দি পেমেন্ট গরন যাইবু এনডে?</t>
+  </si>
+  <si>
+    <t>আমি মানিব্যাগ আনতে ভুলে গেছি, টাকা কি বিকাশে দিয়ে দেব?</t>
+  </si>
+  <si>
+    <t>আঁই মানিব্যাগ আনিবের লাই ভুলি গেই, টিয়া কি বিকাশুত দি দিয়্যুম?</t>
+  </si>
+  <si>
+    <t>এই মোবাইলটার ব্যাটারি ব্যাকআপ কেমন?</t>
+  </si>
+  <si>
+    <t>এই মোবাইল ইবের ব্যাটারি ব্যাকাপ কেন?</t>
+  </si>
+  <si>
+    <t>আমি গত সপ্তাহে এখান থেকে একটা শার্ট কিনেছিলাম, কিন্তু সেটা একবার ধোয়ার পরেই নষ্ট হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আঁই গত সপ্তাত এত্তুন উজ্ঞো শার্ট কিন্নিলাম, কিন্তু ইবে একবার ধুঅন পরেই নষ্ট অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার বোনের বিয়েতে দেওয়ার জন্য কিছু ভালো গিফট আইটেম দেখান</t>
+  </si>
+  <si>
+    <t>আঁর বইনুর বিয়েত দিবের লাই কিছু ভালা গিপট আইটেম দেহন</t>
+  </si>
+  <si>
+    <t>আজকে পরিচিত হোন, সামনের বার আসলে বেশি নিয়েন</t>
+  </si>
+  <si>
+    <t>আজিয়ে পরিচিত অন, সামনোর বার আইলি বেশি লইয়্যুন</t>
+  </si>
+  <si>
+    <t>এখানের দোকানদারগুলো সব সিন্ডিকেট</t>
+  </si>
+  <si>
+    <t>এনডের দোয়ানদার এগুন বিয়াক সিন্ডিকেট</t>
+  </si>
+  <si>
+    <t>এটা গত বছরের ডিজাইন, অন্য ডিজাইন দেখান</t>
+  </si>
+  <si>
+    <t>ইবে গত বছরুর ডিজাইন, অন্য ডিজাইন দেহন</t>
+  </si>
+  <si>
+    <t>আমাকে বোকা বানানো এত সহজ না, আমি কাপড় দেখলেই কোয়ালিটি বুঝে যাই</t>
+  </si>
+  <si>
+    <t>আঁরে বোকা বানন এতো সোজা নো, আঁই হর দেহিলিই কোয়ালিটি বুঝি যাই</t>
+  </si>
+  <si>
+    <t>এই শার্টটা নেন, গরমে পরে আরাম পাবেন</t>
+  </si>
+  <si>
+    <t>এই শার্ট ইবে লন, গরমুত পরি আরাম ফাইবেন</t>
+  </si>
+  <si>
+    <t>এই কাপড়গুলো নতুন নাকি পুরাতন?</t>
+  </si>
+  <si>
+    <t>এই হর এগুন নতুন নাকি ফুরন?</t>
+  </si>
+  <si>
+    <t>গত বছরের তুলনায় এ বছর কাপড়ের দাম অনেক বেশি</t>
+  </si>
+  <si>
+    <t>গত বছরুর তুলনায় এবছর হর উর দাম বত বেশি</t>
+  </si>
+  <si>
+    <t>ভাই, এটা একদম অরিজিনাল গার্মেন্টসের মাল</t>
+  </si>
+  <si>
+    <t>বদ্দা, ইবে একদম অরিজিনাল গার্মেন্টস উর মাল</t>
+  </si>
+  <si>
+    <t>আপা, থ্রি-পিসগুলো একদম অরিজিনাল, রং উঠবে না</t>
+  </si>
+  <si>
+    <t>আফা, থ্রি-পিস এগুন একদম অরিজিনাল, রঙ ন উডিবু</t>
+  </si>
+  <si>
+    <t>জুতাগুলো ভাই আমরা ঢাকা থেকে অর্ডার করে আনি</t>
+  </si>
+  <si>
+    <t>জুতা এগিন বদ্দা আঁরা ঢাহাত্তুন অর্ডার গরি আনি</t>
+  </si>
+  <si>
+    <t>সরি ভাই, আর কম হবে না</t>
+  </si>
+  <si>
+    <t>সরি বদ্দা, আর হম ন অইবু</t>
+  </si>
+  <si>
+    <t>আপনি যে দামটা বলছেন, ওটা আমাদের কেনা রেট থেকেও কম</t>
+  </si>
+  <si>
+    <t>অঁনে যে দাম হইয়্যুন, ইয়েন আঁরার কিনা রেট উত্তুনও হম</t>
+  </si>
+  <si>
+    <t>আরেকটু বাড়িয়ে পারলে নিয়ে যান</t>
+  </si>
+  <si>
+    <t>আরেক্কানা বারায় ফারিলি লই যন</t>
+  </si>
+  <si>
+    <t>আমরা লাভ খুব কম করি, তারমধ্যে আপনি আমাদের পরিচিত কাষ্টমার</t>
+  </si>
+  <si>
+    <t>আঁরা লাভ বত হম গরি, এন্ডেরমধ্যে অঁনে আঁরার পরিচিত কাষ্টমার</t>
+  </si>
+  <si>
+    <t>আর একশ টাকা ফেরত দেন, আমার গাড়িভাড়া নেই</t>
+  </si>
+  <si>
+    <t>আর একশ টিয়া ফেরত দন, আত্তুন গারিভারা নেই</t>
+  </si>
+  <si>
+    <t>এর থেকে কমে বিক্রি করলে আমাদের আর ব্যবসা করা হবে না</t>
+  </si>
+  <si>
+    <t>ইয়াত্তুন হমে বেছিলি আরাত্তুন আর ব্যবসা গরন ন অইবু</t>
+  </si>
+  <si>
+    <t>আপনারা তো রমজানের এক মাসের লাভ দিয়ে সারা বছর চলতে পারবেন</t>
+  </si>
+  <si>
+    <t>অঁনেরা তো রমজানুর এক মাসুর লাভ দি আরা বছর চলিত পারিবেন</t>
+  </si>
+  <si>
+    <t>আপু, দাম কিন্তু অনেক কম দিচ্ছেন, আমার এখানে এক টাকাও লাভ হবে না</t>
+  </si>
+  <si>
+    <t>আফা, দাম কিন্তু বত হম দিতে লেইজ্ঞুন, আঁর এনডে এক টিয়াও লাভ ন অইবু</t>
+  </si>
+  <si>
+    <t>কসম করে বলছি ভাই, এই কাপড়ে আমার বেশি লাভ হবে না</t>
+  </si>
+  <si>
+    <t>কসম গরি হইদ্দি বদ্দা, এই হর উত আত্তুন বেশি লাভ ন অইবু</t>
+  </si>
+  <si>
+    <t>আর কত লাভ করবেন আপনারা, এত টাকা নিয়ে কী কবরে যাবেন?</t>
+  </si>
+  <si>
+    <t>আর হত লাভ গরিবেন অঁনেরা, এত টিয়া লই কী হবরুত যাইবেন?</t>
+  </si>
+  <si>
+    <t>আরেকটু কম দামি থেকে দেখান, আমার বাজেট একটু কম</t>
+  </si>
+  <si>
+    <t>আরেক্কানা হম দামি দেহন, আঁর বাজেট এক্কানা হম</t>
+  </si>
+  <si>
+    <t>এখন জিনিসপত্রের দাম বেশি, ঈদের পর দাম কমবে</t>
+  </si>
+  <si>
+    <t>এহন জিনিসপত্রর দাম বেশি, ঈদুর পর দাম হমিবু</t>
+  </si>
+  <si>
+    <t>আপু, টাটকা মাছ খেতে চাইলে এইদিকে আসেন</t>
+  </si>
+  <si>
+    <t>আফা, টাটকা মাছ হাইতু চাইলি ইনদি আইয়্যুন</t>
+  </si>
+  <si>
+    <t>ওর থেকে নিয়েন না, ওর মাছগুলো গতকালের মাছ</t>
+  </si>
+  <si>
+    <t>ইতেত্তুন ন লইয়্যুন, ইতের মাছ এগুন গত হালিয়ের মাছ</t>
+  </si>
+  <si>
+    <t>আমারগুলো একদম টাটকা সবজি, কিছুক্ষণ আগেই ক্ষেত থেকে এনেছি</t>
+  </si>
+  <si>
+    <t>আঁর এগিন একদম টাটকা সবজি, এক্কানা আগেই ক্ষেতিত্তুন এইন্নি</t>
+  </si>
+  <si>
+    <t>ভাইয়া, এগুলো একদম ফ্রেশ তরকারি, কোনো ফরমালিন দিইনি</t>
+  </si>
+  <si>
+    <t>বদ্দা, এগিন একদম ফ্রেশ তরহারি, হনো ফরমালিন ন দিই</t>
+  </si>
+  <si>
+    <t>এই কচুশাকগুলো এক বান্ডিল কত টাকা?</t>
+  </si>
+  <si>
+    <t>এই হচুশাক এগিন এক বুধা হত টিয়া?</t>
+  </si>
+  <si>
+    <t>ঈদের দিন রান্না করার জন্য পোলাওয়ের চাল নিয়ে আসেন</t>
+  </si>
+  <si>
+    <t>ঈদুর দিন রান্না গরিবের লাই পোলও উর চইল লই আইয়্যুন</t>
+  </si>
+  <si>
+    <t>মুরগি কিনলে ওখান থেকে জবাই করে আনিয়েন, এখানে জবাই করতে পারব না</t>
+  </si>
+  <si>
+    <t>কুরো কিনিলি এত্তুন জুওয়ারাই আইন্নুন, এনডে জুওয়ারাইত ন ফাইজ্জুম</t>
+  </si>
+  <si>
+    <t>মুরগি কাটার সময় পাশে দাঁড়িয়ে থেকো, ওরা সুযোগ পেলে মাংস চুরি করে</t>
+  </si>
+  <si>
+    <t>মুরগি হাডিবের সমত ডাহুদ্দি থিয়েই থেইক্কো, ইতারা সুযোগ পাইলি মাংস চুরি গরে</t>
+  </si>
+  <si>
+    <t>মুরগির পাগুলো আনিয়েন না, ওগুলো রেডি করা ঝামেলা</t>
+  </si>
+  <si>
+    <t>কুরোর টেং এগিন ন আইন্নুন, এগিন রেডি গরন ঝামিলে</t>
+  </si>
+  <si>
+    <t>মুরগির পিসগুলো মিডিয়াম সাইজের করতে বলিও</t>
+  </si>
+  <si>
+    <t>মুরগির পিস এগিন মিডিয়াম সাইজুর গইত্তো হইয়্যো</t>
+  </si>
+  <si>
+    <t>তোর বাবাকে বল যেন মাছ বাজার থেকে কেটে আনে</t>
+  </si>
+  <si>
+    <t>তোর বাফুরে হ যেন মাছ বাজারুত্তুন হাডি আনে</t>
+  </si>
+  <si>
+    <t>ভাইয়া, আমাকে এক কেজি পোলাওয়ের চাল আর এক লিটার খাঁটি সরিষার তেল দেন</t>
+  </si>
+  <si>
+    <t>ভাইয়া, আঁরে এক কেজি পোলও উর চইল আর এক লিটার হাঁটি সরিষার তেল দন</t>
+  </si>
+  <si>
+    <t>সাথে আদা-রসুন আর ৫০০ গ্রামের একটা খাঁটি গাওয়া ঘি দিয়েন</t>
+  </si>
+  <si>
+    <t>লগে আদা-রসুন আর ৫০০ গ্রামুর উজ্ঞো হাঁটি গাওয়া ঘি দন</t>
+  </si>
+  <si>
+    <t>ভাই, পাওরুটি এটা কখনের? মেয়াদ আছে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, পওরুটি ইবে হত্তের? মিয়াদ আছে না?</t>
+  </si>
+  <si>
+    <t>লাভ কম, মাস শেষে দোকান ভাড়াও উঠে না</t>
+  </si>
+  <si>
+    <t>লাভ হম, মাস শেষে দোয়ান ভারাও ন উডে</t>
+  </si>
+  <si>
+    <t>ব্যবসায় বেশি লস খেয়েছি, দোকানটা মনে হয় আর রাখতে পারব না</t>
+  </si>
+  <si>
+    <t>ব্যবসাত বেশি লস হায়, দোয়ান ইয়েন মনে অয় আর রাহিত ন পাইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমার দোকানটা বিক্রি করে দেব, কোনো ভালো কাস্টমার পেলে জানাবেন</t>
+  </si>
+  <si>
+    <t>আঁর দোয়ান ইয়েন বেছি দিয়্যুম, হনো ভালা কাস্টমার পাইলি জানাইয়্যুন</t>
+  </si>
+  <si>
+    <t>এখন বিক্রি কম, কাস্টমার নেই</t>
+  </si>
+  <si>
+    <t>এহন বেছা হম, কাস্টমার নেই</t>
+  </si>
+  <si>
+    <t>মুলা কেজি কত করে? আমাকে এক কেজি দেন</t>
+  </si>
+  <si>
+    <t>মুলো কেজি হত গরি? আঁরে এক কেজি দন</t>
+  </si>
+  <si>
+    <t>মাছগুলো কি ফার্মের, নাকি দেশি?</t>
+  </si>
+  <si>
+    <t>মাছ এগুন কি ফার্মুর, নাকি দেশি?</t>
+  </si>
+  <si>
+    <t>ব্যবসায় আগের মতো লাভ নেই, দোকান বেশি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>ব্যবসাত আগোর মতন লাভ নেই, দোয়ান বেশি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বেশি দামাদামি করবেন না, এগুলো একদম টাটকা সবজি</t>
+  </si>
+  <si>
+    <t>বেশি দামাদামি ন গইজ্জুন, এগিন একদম টাটকা সবজি</t>
+  </si>
+  <si>
+    <t>ফুলকপি কত করে? ভিতরে পোকা হবে না তো?</t>
+  </si>
+  <si>
+    <t>ফুলহপ্পি হত গরি? ভিতুরে ফুক অইবু না হনো?</t>
+  </si>
+  <si>
+    <t>মাছগুলো একদম জীবিত, নড়ছে দেখেন</t>
+  </si>
+  <si>
+    <t>মাছ এগুন এব্বেরে জিয়াতা, নরেদ্দে সো</t>
+  </si>
+  <si>
+    <t>এগুলো সাগরের মাছ, দাম কম হবে না</t>
+  </si>
+  <si>
+    <t>এগুন সাগরুর মাছ, দাম হম ন আইবু</t>
+  </si>
+  <si>
+    <t>আমার মেয়ের স্কুলের জন্য একটা ভালো মানের ব্যাগ দেখাতে পারবেন?</t>
+  </si>
+  <si>
+    <t>আঁর মাইফুয়ার স্কুলুর লাই উজ্ঞো ভালা মানুর ব্যাগ দেহাইত ফারিবেন?</t>
+  </si>
+  <si>
+    <t>ভাই, মাছটা একটু ভালো করে পরিষ্কার করে কেটে দিন, আঁশ যেন না থাকে</t>
+  </si>
+  <si>
+    <t>বদ্দা, মাছ ইবে এক্কানা ভালা গরি পরিষ্কার গরি হাডি দন, আঁশ যেন ন থাহে</t>
+  </si>
+  <si>
+    <t>এখন আর আগের মতো অনলাইন বিজনেসে লাভ নেই</t>
+  </si>
+  <si>
+    <t>এহন আর আগের মতন অনলাইন বিজনেস উত লাভ নেই</t>
+  </si>
+  <si>
+    <t>বাকি দিলে ব্যবসা করা যাবে না</t>
+  </si>
+  <si>
+    <t>বেইক্কে দিলি ব্যবসা গরন যাইতু ন</t>
+  </si>
+  <si>
+    <t>ঋণ নিয়ে ব্যবসা করতে গেলে ব্যবসায় উন্নতি করা যাবে না</t>
+  </si>
+  <si>
+    <t>হজ্জো লই ব্যবসা গইত্তো যাইলি ব্যবসাত উন্নাতি গরন যাইতু ন</t>
+  </si>
+  <si>
+    <t>এগুলো ব্যবসার টাকা ভাই, এগুলো ধার দিতে পারব না</t>
+  </si>
+  <si>
+    <t>এগুন ব্যবসার টিয়া ভাই, এগুন উধোর দিত পাইত্তাম ন</t>
+  </si>
+  <si>
+    <t>এই বাজারে কি কোনো নির্দিষ্ট দোকান আছে, যেখানে তাজা সবজি সবসময় পাওয়া যায়?</t>
+  </si>
+  <si>
+    <t>এই বাজারুত কি হনো নির্দিষ্ট দোয়ান আছে, যেনডে তাজা সবজি সবসময় পন যায়?</t>
+  </si>
+  <si>
+    <t>এই মোবাইল ফোনটার ক্যামেরা কেমন? কারণ আমি ছবি তোলার জন্যই কিনতে চাইছি</t>
+  </si>
+  <si>
+    <t>এই মোবাইল ফোন ইবের ক্যামেরা কেন? হারন আঁই ছবি তোলিবের লাই কিনতাম চাইদ্দি</t>
+  </si>
+  <si>
+    <t>আমার বাজেট বেশি নেই, সেজন্য এটা নিতে পারব না</t>
+  </si>
+  <si>
+    <t>আঁর বাজেট বেশি নেই, এতেল্লে ইবে লইত পাইত্তাম ন</t>
+  </si>
+  <si>
+    <t>এটা আমার বন্ধুর দোকান, সবাই এখান থেকে বাজার করিস</t>
+  </si>
+  <si>
+    <t>ইয়েন আঁর বন্ধুর দোয়ান, বিয়াজ্ঞুন এত্তুন বাজার গরিস</t>
+  </si>
+  <si>
+    <t>ব্যবসা করতে চাইলে অভিজ্ঞতা লাগে</t>
+  </si>
+  <si>
+    <t>ব্যবসা গইত্তো চাইলি অভিজ্ঞতা লাগে</t>
+  </si>
+  <si>
+    <t>গরুটা দেখে তো মনে হয় না বয়স হয়েছে, দাম এত বেশি কেন চাচ্ছেন?</t>
+  </si>
+  <si>
+    <t>গরু ইবে দেহি তো মনে ন অর বয়স বেশি অইয়্যি, দাম এল্লেত বেশি কা চাইতে লেইজ্ঞুন?</t>
+  </si>
+  <si>
+    <t>বন্ধু চল, সামনের মাসে একটা টুর দিই</t>
+  </si>
+  <si>
+    <t>বন্ধু চল, সামনোর মাসুত উজ্ঞো টুর দি</t>
+  </si>
+  <si>
+    <t>আমার কাছে এখন টাকা নেই, সেজন্য কোথাও যাওয়ার কথা চিন্তা করছি না</t>
+  </si>
+  <si>
+    <t>আঁর হাছে এহন টিয়া নেই, এতেল্লে হনোমিক্কে যাইবের হতা চিন্তে ন গরির</t>
+  </si>
+  <si>
+    <t>সামনের মাসে আমি বেশি ব্যস্ত থাকব, সেজন্য টুরে যেতে পারব না</t>
+  </si>
+  <si>
+    <t>সামনুর মাসুত আঁই বেশি বিজি থেইক্কুম, এতেল্লে টুরুত যাইত পাইত্তাম ন</t>
+  </si>
+  <si>
+    <t>টুরে যাওয়ার প্ল্যান করলে সবাই যাবে বলে, কিন্তু যাওয়ার সময় কাউকে খুঁজে পাওয়া যায় না</t>
+  </si>
+  <si>
+    <t>টুরুত যাইবের প্ল্যান গরিলি বিয়াজ্ঞুন যাইবু হয়, কিন্তু যাইবের সমত কিয়ারে তোওয়াই পন ন যায়</t>
+  </si>
+  <si>
+    <t>এই মাসে কক্সবাজারে অনেক জ্যাম হবে, সামনের মাসে যাব</t>
+  </si>
+  <si>
+    <t>এই মাসুত কক্সবাজারুত বত জাম অইবু, সামনুর মাসুত যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>কক্সবাজার না গিয়ে অন্য কোথাও গেলে ভাল হবে</t>
+  </si>
+  <si>
+    <t>কক্সবাজার ন যাই অন্য হনোমিক্কে গেলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>চলো, আমরা দুজন মিলে কোথাও ঘুরে আসি</t>
+  </si>
+  <si>
+    <t>চলো, আঁরা দুনুজন মিলি হনোমিক্কে ঘুরি আয়</t>
+  </si>
+  <si>
+    <t>তুমি যদি না যাও, তাহলে আমিও যাব না</t>
+  </si>
+  <si>
+    <t>তুঁই যদি ন যও, তইলি আঁই ও যাইতাম ন</t>
+  </si>
+  <si>
+    <t>ওখানে যদি তুমি না থাক, তাহলে আমার একদম ভালো লাগবে না</t>
+  </si>
+  <si>
+    <t>এনডে যদি তুঁই ন থাহ, তইলি আত্তুন এব্বেরে ভালা ন লাগিবু</t>
+  </si>
+  <si>
+    <t>আগে বলো টুরে তুমি যাচ্ছ কি না, কারণ তুমি না গেলে আমিও যাব না</t>
+  </si>
+  <si>
+    <t>আগে হ টুরুত তুঁই যাইতে লেইজ্ঞু কিনা, হারন তুঁই ন যাইলি আঁই ও যাইতাম ন</t>
+  </si>
+  <si>
+    <t>আমার মতে বান্দরবান থেকে কক্সবাজার যাওয়া ভালো হবে</t>
+  </si>
+  <si>
+    <t>আঁর মতে বান্দরবান উত্তুন কক্সবাজার যন ভালা অইবু</t>
+  </si>
+  <si>
+    <t>আমাদের এখানে ঘুরার জন্য অনেক জায়গা আছে, আশা করি তোমার ভালো লাগবে</t>
+  </si>
+  <si>
+    <t>আঁরার এনডে ঘুরিবের লাই বত জাগা আছে, আশা গরি তোঁয়ার ভালা লাগিবু</t>
+  </si>
+  <si>
+    <t>আচ্ছা আমরা বাসে যাচ্ছি নাকি ট্রেনে যাচ্ছি?</t>
+  </si>
+  <si>
+    <t>আইচ্ছে আঁরা বাসে যাইর নাকি ট্রেনে যাইর?</t>
+  </si>
+  <si>
+    <t>আমার বাসে ভালো লাগে না, ট্রেনে যাব চিন্তা করছি</t>
+  </si>
+  <si>
+    <t>আত্তুন বাসুত ভালা ন লাগে, ট্রেনুত যাইয়্যুম চিন্তে গরির</t>
+  </si>
+  <si>
+    <t>বাসে অনেকক্ষণ ধরে যাত্রা করলে আমার বমি আসে</t>
+  </si>
+  <si>
+    <t>বাসুত বত হতক্ষন ধরি যাত্রা গরিলি আত্তুন বুমি আইয়্যি</t>
+  </si>
+  <si>
+    <t>তাহলে তুই ট্রেনের টিকিট কেটে ফেল সবার জন্য, আমরা সময়মতো বের হয়ে যাব</t>
+  </si>
+  <si>
+    <t>তইলি তুই ট্রেনুর টিকেট হাডি ফেলা বিয়াজ্ঞুনুর লাই, আঁরা সময়মতো বাইর অই যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমরা পাঁচজন যাব, তাই পাঁচটা টিকেট একসাথে কাটতে চাই</t>
+  </si>
+  <si>
+    <t>আঁরা পাচজন যাইয়্যুম, এতেল্লে পাচছান টিকেট একলগে হাইট্টাম চাইর</t>
+  </si>
+  <si>
+    <t>ভাই, আমাদের সিটগুলো পাশাপাশি রাখার চেষ্টা করিয়েন</t>
+  </si>
+  <si>
+    <t>বদ্দা, আঁরার সিট এগিন পাশাপাশি রাহিবের চেষ্টা গইজ্জুন</t>
+  </si>
+  <si>
+    <t>অনেকক্ষণ ধরে বাসে চড়তে হবে, তাই খাওয়ার জন্য কিছু নিয়ে নে</t>
+  </si>
+  <si>
+    <t>বত হতক্ষন ধরি বাসুত চরন পরিবু, এতেল্লে হাইবের লাই কিছু লই ল</t>
+  </si>
+  <si>
+    <t>বাসে চড়তে না পারলে তোদেরকে কে টুরে যেতে বলল?</t>
+  </si>
+  <si>
+    <t>বাসুত চরিত ন ফারিলি তোরারে হনে টুরুত যাইতু হইয়্যি?</t>
+  </si>
+  <si>
+    <t>যারা যারা টুরে যাবি, সবাই আজকের মধ্যে টাকা দিয়ে দিস</t>
+  </si>
+  <si>
+    <t>যারা যারা টুরুত যাইবি, বিয়াজ্ঞুন আজিয়ের মধ্যে টিয়া দি দিস</t>
+  </si>
+  <si>
+    <t>আজকে টিকিট কেটে ফেলতে হবে, সেজন্য সবাই আজকের মধ্যে টাকাটা দিয়ে দিস</t>
+  </si>
+  <si>
+    <t>আজিয়ের মধ্যে টিকেট হাডি ফেলন ফরিবু, এতেল্লে বিয়াজ্ঞুন আজিয়ের অধ্যে টিয়াগুন দি দিস</t>
+  </si>
+  <si>
+    <t>সব ঠিকঠাক থাকলে আমরা আগামীকাল সকাল সকাল বের হয়ে যাব</t>
+  </si>
+  <si>
+    <t>বিয়াক ঠিকঠাক থাহিলি আঁরা হালিয়ে সকাল সকাল বাইর অই যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমরা ওখানে শুধু দুদিন থাকব, তাই বেশি জিনিস নিয়ে যেতে হবে না</t>
+  </si>
+  <si>
+    <t>আঁরা এনডে উধো দুদিন থাইক্কুম, এতেল্লে বেশি জিনিস লই যন ন ফরিবু</t>
+  </si>
+  <si>
+    <t>ভাই, ঢাকা থেকে চট্টগ্রামের বাস কখন ছাড়বে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, ঢাহাত্তুন চট্টগ্রামুর বাস হত্তে ছারিবু?</t>
+  </si>
+  <si>
+    <t>কমলাপুর স্টেশন থেকে সিলেটের টিকিট কি এখনো পাওয়া যাচ্ছে?</t>
+  </si>
+  <si>
+    <t>কমলাপুর স্টেশন উত্তুন সিলেটুর টিকেট কি এহনো পন যার?</t>
+  </si>
+  <si>
+    <t>এই বাসে কি এসি আছে, কারণ গরমের মধ্যে যেতে অনেক কষ্ট হবে</t>
+  </si>
+  <si>
+    <t>এই বাসুত কি এসি আছে, হারন গরমুর মধ্যে যাইতে বত হষ্ট অইবু</t>
+  </si>
+  <si>
+    <t>এসি বাসের টিকিটের দাম একটু বেশি, আমরা নরমাল বাসে করে যাব</t>
+  </si>
+  <si>
+    <t>এসি বাসুর টিকেট উর দাম এক্কানা বেশি, আঁরা নরমাল বাসুত গরি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমার কিছু কাজ বাকি আছে, সেগুলো শেষ করে তারপর বের হচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁর কিছু হাজ বাকি আছে, এগিন শেষ গরি তারপর বাইর অইর</t>
+  </si>
+  <si>
+    <t>মুরাদ বলল, তুমি নাকি ১০ তারিখে ঢাকায় চলে যাচ্ছ?</t>
+  </si>
+  <si>
+    <t>মুরাদ হইয়্যি, তুঁই বলে ১০ তারিখ ঢাহা চলি যার?</t>
+  </si>
+  <si>
+    <t>১০ তারিখ নাকি সারা দেশে হরতাল দিয়েছে, ওইদিন যেও না</t>
+  </si>
+  <si>
+    <t>১০ তারিখ বলে সারা দেশ উত হরতাল দিইয়্যি, ওইদিন ন যাইয়্যু</t>
+  </si>
+  <si>
+    <t>আমাদের সিট একসাথে পড়েছে, যেতে যেতে আমরা অনেক গল্প করব</t>
+  </si>
+  <si>
+    <t>আঁরার সিট একলগে ফইজ্জি, যাইতে যাইতে আঁরা বত গল্প গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আজকের মধ্যে সবকিছু গুছিয়ে ফেলতে হবে, যেন আগামীকাল সকালে বের হয়ে যেতে পারি</t>
+  </si>
+  <si>
+    <t>আজিয়ের মধ্যে বিয়াক কিছু গুছায় ফেলন ফরিবু, যেন হালিয়ে বেইন্নে বাইর অই যাইত পারি</t>
+  </si>
+  <si>
+    <t>আমাদের সময় কম, যা করার তারাতারি করতে হবে</t>
+  </si>
+  <si>
+    <t>আঁরার সময় হম, যা গরার হারা গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমরা রাতের ট্রেনে যাব, দিনের বেলায় অনেক গরম</t>
+  </si>
+  <si>
+    <t>আঁরা রাতিয়ের ট্রেনুত যাইয়্যুম, দিনুত বত গরম</t>
+  </si>
+  <si>
+    <t>বৃষ্টির মধ্যে ট্রেন জার্নি অনেক মজা হবে</t>
+  </si>
+  <si>
+    <t>ঝরোর মধ্যে ট্রেন জার্নি বত মজা অইবু</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম-কক্সবাজার রোড অনেক বিপদজনক, এই রোডে প্রতিদিন এক্সিডেন্ট হয়</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম-কক্সবাজার রোড বত বিপদজনক, এই রোড উত ফইত্তুদিন এক্সিডেন্ট অয়</t>
+  </si>
+  <si>
+    <t>কক্সবাজার যাওয়ার জন্য কোন বাস সবচেয়ে ভালো হবে?</t>
+  </si>
+  <si>
+    <t>কক্সবাজার যাইবের লাই হন বাস বিয়াজ্ঞুনুত্তুন ভালা অইবু?</t>
+  </si>
+  <si>
+    <t>হানিফ বাসে যাব না, এই বাসগুলো অনেক জোরে চালায় আর বেশি এক্সিডেন্ট করে</t>
+  </si>
+  <si>
+    <t>হানিফ বাসুত ন যাইয়্যুম, এই বাস এগিন বত জোরে চলায় আর বেশি এক্সিডেন্ট গরে</t>
+  </si>
+  <si>
+    <t>আমি আর জীবনে তোদের সাথে কোথাও যাব না, একবার গিয়ে শিক্ষা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আঁই আর জীবনুত তোরার লগে হনোমিক্কে যাইতাম ন, একবার যায় শিক্ষা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>তুমি যদি একা যাও, তাহলে রাতের বাসে যেও না</t>
+  </si>
+  <si>
+    <t>তুঁই যদি এহেল্লে যও, তইলি রাতিয়ের বাসুত ন যাইয়্যু</t>
+  </si>
+  <si>
+    <t>রাতের বাস জার্নি একটু বিপদজনক, তাই সাবধান থাকা উচিত</t>
+  </si>
+  <si>
+    <t>রাতিয়ের বাস জার্নি এক্কানা বিপদজনক, এতেল্লে সাবধান থাহন উচিত</t>
+  </si>
+  <si>
+    <t>আজকে যেহেতু দেরি হয়ে গেছে, তাই আমরা আগামীকাল বের হব</t>
+  </si>
+  <si>
+    <t>আজিয়ে যেহেতু দেরি অই গেইয়্যি, এতেল্লে আঁরা হালিয়ে বাইর অইয়্যুম</t>
+  </si>
+  <si>
+    <t>ছেলেমেয়ে একসাথে দূরে ঘুরতে যাওয়া ঠিক না</t>
+  </si>
+  <si>
+    <t>ফোওয়া-মাইফুয়া একলগে দুরে ঘুইত্তু যন ঠিক ন</t>
+  </si>
+  <si>
+    <t>আমি সবাইকে ফোন করে দিয়েছি, কিছুক্ষণের মধ্যে সবাই চলে আসবে</t>
+  </si>
+  <si>
+    <t>আঁই বিয়াজ্ঞুনুরে ফোন গরি দি, কিছুক্ষনের মধ্যে বিয়াজ্ঞুন চলি আইবু</t>
+  </si>
+  <si>
+    <t>টাকা বেশি লাগবেনা, আমরা বেশি দুরে যাব না</t>
+  </si>
+  <si>
+    <t>টিয়া বেশি ন লাগিবু, আঁরা বেশি দুরে ন যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমি কোনো দিন লঞ্চে চড়িনি, এবার না হয় লঞ্চে করেই যাই</t>
+  </si>
+  <si>
+    <t>আঁই হনোদিন লঞ্চ উত ন চরি, এবার নইতু লঞ্চ উত গরি যাই</t>
+  </si>
+  <si>
+    <t>আমার সাথে ছোট বাচ্চা আছে, তাই একটু সামনের সিট দিলে ভালো হতো</t>
+  </si>
+  <si>
+    <t>আঁর লগে ছোডো ফোওয়া আছে, এতেল্লে এক্কানা সামনুর সিট দিলি ভালা অইতু</t>
+  </si>
+  <si>
+    <t>স্টেশনে পৌঁছাতে কতক্ষণ লাগবে? দেরি হলে কিন্তু ট্রেন মিস হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>স্টেশনুত পৌছতে হতক্ষন লাগিবু? দেরি অইলি কিন্তু ট্রেন মিস অই যাইবু</t>
+  </si>
+  <si>
+    <t>রাস্তায় জ্যাম হলে পাঠাও করে চলে আসো</t>
+  </si>
+  <si>
+    <t>রাস্তাত জ্যাম অইলি পাঠাও গরি চলি আইয়্যু</t>
   </si>
 </sst>
 </file>
@@ -15718,484 +16444,964 @@
       </c>
     </row>
     <row r="1032" ht="25" customHeight="1" spans="1:2">
-      <c r="A1032" s="2"/>
-      <c r="B1032" s="2"/>
+      <c r="A1032" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1032" s="2" t="s">
+        <v>2057</v>
+      </c>
     </row>
     <row r="1033" ht="25" customHeight="1" spans="1:2">
-      <c r="A1033" s="2"/>
-      <c r="B1033" s="2"/>
+      <c r="A1033" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1033" s="2" t="s">
+        <v>2059</v>
+      </c>
     </row>
     <row r="1034" ht="25" customHeight="1" spans="1:2">
-      <c r="A1034" s="2"/>
-      <c r="B1034" s="2"/>
+      <c r="A1034" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1034" s="2" t="s">
+        <v>2061</v>
+      </c>
     </row>
     <row r="1035" ht="25" customHeight="1" spans="1:2">
-      <c r="A1035" s="2"/>
-      <c r="B1035" s="2"/>
+      <c r="A1035" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1035" s="2" t="s">
+        <v>2063</v>
+      </c>
     </row>
     <row r="1036" ht="25" customHeight="1" spans="1:2">
-      <c r="A1036" s="2"/>
-      <c r="B1036" s="2"/>
+      <c r="A1036" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1036" s="2" t="s">
+        <v>2065</v>
+      </c>
     </row>
     <row r="1037" ht="25" customHeight="1" spans="1:2">
-      <c r="A1037" s="2"/>
-      <c r="B1037" s="2"/>
+      <c r="A1037" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>2067</v>
+      </c>
     </row>
     <row r="1038" ht="25" customHeight="1" spans="1:2">
-      <c r="A1038" s="2"/>
-      <c r="B1038" s="2"/>
+      <c r="A1038" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1038" s="2" t="s">
+        <v>2069</v>
+      </c>
     </row>
     <row r="1039" ht="25" customHeight="1" spans="1:2">
-      <c r="A1039" s="2"/>
-      <c r="B1039" s="2"/>
+      <c r="A1039" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1039" s="2" t="s">
+        <v>2071</v>
+      </c>
     </row>
     <row r="1040" ht="25" customHeight="1" spans="1:2">
-      <c r="A1040" s="2"/>
-      <c r="B1040" s="2"/>
+      <c r="A1040" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>2073</v>
+      </c>
     </row>
     <row r="1041" ht="25" customHeight="1" spans="1:2">
-      <c r="A1041" s="2"/>
-      <c r="B1041" s="2"/>
+      <c r="A1041" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>2075</v>
+      </c>
     </row>
     <row r="1042" ht="25" customHeight="1" spans="1:2">
-      <c r="A1042" s="2"/>
-      <c r="B1042" s="2"/>
+      <c r="A1042" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>2077</v>
+      </c>
     </row>
     <row r="1043" ht="25" customHeight="1" spans="1:2">
-      <c r="A1043" s="2"/>
-      <c r="B1043" s="2"/>
+      <c r="A1043" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>2079</v>
+      </c>
     </row>
     <row r="1044" ht="25" customHeight="1" spans="1:2">
-      <c r="A1044" s="2"/>
-      <c r="B1044" s="2"/>
+      <c r="A1044" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>2081</v>
+      </c>
     </row>
     <row r="1045" ht="25" customHeight="1" spans="1:2">
-      <c r="A1045" s="2"/>
-      <c r="B1045" s="2"/>
+      <c r="A1045" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>2083</v>
+      </c>
     </row>
     <row r="1046" ht="25" customHeight="1" spans="1:2">
-      <c r="A1046" s="2"/>
-      <c r="B1046" s="2"/>
+      <c r="A1046" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>2085</v>
+      </c>
     </row>
     <row r="1047" ht="25" customHeight="1" spans="1:2">
-      <c r="A1047" s="2"/>
-      <c r="B1047" s="2"/>
+      <c r="A1047" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>2087</v>
+      </c>
     </row>
     <row r="1048" ht="25" customHeight="1" spans="1:2">
-      <c r="A1048" s="2"/>
-      <c r="B1048" s="2"/>
+      <c r="A1048" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>2089</v>
+      </c>
     </row>
     <row r="1049" ht="25" customHeight="1" spans="1:2">
-      <c r="A1049" s="2"/>
-      <c r="B1049" s="2"/>
+      <c r="A1049" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>2091</v>
+      </c>
     </row>
     <row r="1050" ht="25" customHeight="1" spans="1:2">
-      <c r="A1050" s="2"/>
-      <c r="B1050" s="2"/>
+      <c r="A1050" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>2093</v>
+      </c>
     </row>
     <row r="1051" ht="25" customHeight="1" spans="1:2">
-      <c r="A1051" s="2"/>
-      <c r="B1051" s="2"/>
+      <c r="A1051" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>2095</v>
+      </c>
     </row>
     <row r="1052" ht="25" customHeight="1" spans="1:2">
-      <c r="A1052" s="2"/>
-      <c r="B1052" s="2"/>
+      <c r="A1052" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1052" s="2" t="s">
+        <v>2097</v>
+      </c>
     </row>
     <row r="1053" ht="25" customHeight="1" spans="1:2">
-      <c r="A1053" s="2"/>
-      <c r="B1053" s="2"/>
+      <c r="A1053" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1053" s="2" t="s">
+        <v>2099</v>
+      </c>
     </row>
     <row r="1054" ht="25" customHeight="1" spans="1:2">
-      <c r="A1054" s="2"/>
-      <c r="B1054" s="2"/>
+      <c r="A1054" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1054" s="2" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="1055" ht="25" customHeight="1" spans="1:2">
-      <c r="A1055" s="2"/>
-      <c r="B1055" s="2"/>
+      <c r="A1055" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1055" s="2" t="s">
+        <v>2103</v>
+      </c>
     </row>
     <row r="1056" ht="25" customHeight="1" spans="1:2">
-      <c r="A1056" s="2"/>
-      <c r="B1056" s="2"/>
+      <c r="A1056" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1056" s="2" t="s">
+        <v>2105</v>
+      </c>
     </row>
     <row r="1057" ht="25" customHeight="1" spans="1:2">
-      <c r="A1057" s="2"/>
-      <c r="B1057" s="2"/>
+      <c r="A1057" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1057" s="2" t="s">
+        <v>2107</v>
+      </c>
     </row>
     <row r="1058" ht="25" customHeight="1" spans="1:2">
-      <c r="A1058" s="2"/>
-      <c r="B1058" s="2"/>
+      <c r="A1058" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1058" s="2" t="s">
+        <v>2109</v>
+      </c>
     </row>
     <row r="1059" ht="25" customHeight="1" spans="1:2">
-      <c r="A1059" s="2"/>
-      <c r="B1059" s="2"/>
+      <c r="A1059" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1059" s="2" t="s">
+        <v>2111</v>
+      </c>
     </row>
     <row r="1060" ht="25" customHeight="1" spans="1:2">
-      <c r="A1060" s="2"/>
-      <c r="B1060" s="2"/>
+      <c r="A1060" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1060" s="2" t="s">
+        <v>2113</v>
+      </c>
     </row>
     <row r="1061" ht="25" customHeight="1" spans="1:2">
-      <c r="A1061" s="2"/>
-      <c r="B1061" s="2"/>
+      <c r="A1061" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1061" s="2" t="s">
+        <v>2115</v>
+      </c>
     </row>
     <row r="1062" ht="25" customHeight="1" spans="1:2">
-      <c r="A1062" s="2"/>
-      <c r="B1062" s="2"/>
+      <c r="A1062" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1062" s="2" t="s">
+        <v>2117</v>
+      </c>
     </row>
     <row r="1063" ht="25" customHeight="1" spans="1:2">
-      <c r="A1063" s="2"/>
-      <c r="B1063" s="2"/>
+      <c r="A1063" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1063" s="2" t="s">
+        <v>2119</v>
+      </c>
     </row>
     <row r="1064" ht="25" customHeight="1" spans="1:2">
-      <c r="A1064" s="2"/>
-      <c r="B1064" s="2"/>
+      <c r="A1064" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1064" s="2" t="s">
+        <v>2121</v>
+      </c>
     </row>
     <row r="1065" ht="25" customHeight="1" spans="1:2">
-      <c r="A1065" s="2"/>
-      <c r="B1065" s="2"/>
+      <c r="A1065" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1065" s="2" t="s">
+        <v>2123</v>
+      </c>
     </row>
     <row r="1066" ht="25" customHeight="1" spans="1:2">
-      <c r="A1066" s="2"/>
-      <c r="B1066" s="2"/>
+      <c r="A1066" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1066" s="2" t="s">
+        <v>2125</v>
+      </c>
     </row>
     <row r="1067" ht="25" customHeight="1" spans="1:2">
-      <c r="A1067" s="2"/>
-      <c r="B1067" s="2"/>
+      <c r="A1067" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1067" s="2" t="s">
+        <v>2127</v>
+      </c>
     </row>
     <row r="1068" ht="25" customHeight="1" spans="1:2">
-      <c r="A1068" s="2"/>
-      <c r="B1068" s="2"/>
+      <c r="A1068" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1068" s="2" t="s">
+        <v>2129</v>
+      </c>
     </row>
     <row r="1069" ht="25" customHeight="1" spans="1:2">
-      <c r="A1069" s="2"/>
-      <c r="B1069" s="2"/>
+      <c r="A1069" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1069" s="2" t="s">
+        <v>2131</v>
+      </c>
     </row>
     <row r="1070" ht="25" customHeight="1" spans="1:2">
-      <c r="A1070" s="2"/>
-      <c r="B1070" s="2"/>
+      <c r="A1070" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1070" s="2" t="s">
+        <v>2133</v>
+      </c>
     </row>
     <row r="1071" ht="25" customHeight="1" spans="1:2">
-      <c r="A1071" s="2"/>
-      <c r="B1071" s="2"/>
+      <c r="A1071" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1071" s="2" t="s">
+        <v>2135</v>
+      </c>
     </row>
     <row r="1072" ht="25" customHeight="1" spans="1:2">
-      <c r="A1072" s="2"/>
-      <c r="B1072" s="2"/>
+      <c r="A1072" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1072" s="2" t="s">
+        <v>2137</v>
+      </c>
     </row>
     <row r="1073" ht="25" customHeight="1" spans="1:2">
-      <c r="A1073" s="2"/>
-      <c r="B1073" s="2"/>
+      <c r="A1073" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1073" s="2" t="s">
+        <v>2139</v>
+      </c>
     </row>
     <row r="1074" ht="25" customHeight="1" spans="1:2">
-      <c r="A1074" s="2"/>
-      <c r="B1074" s="2"/>
+      <c r="A1074" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1074" s="2" t="s">
+        <v>2141</v>
+      </c>
     </row>
     <row r="1075" ht="25" customHeight="1" spans="1:2">
-      <c r="A1075" s="2"/>
-      <c r="B1075" s="2"/>
+      <c r="A1075" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B1075" s="2" t="s">
+        <v>2143</v>
+      </c>
     </row>
     <row r="1076" ht="25" customHeight="1" spans="1:2">
-      <c r="A1076" s="2"/>
-      <c r="B1076" s="2"/>
+      <c r="A1076" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1076" s="2" t="s">
+        <v>2145</v>
+      </c>
     </row>
     <row r="1077" ht="25" customHeight="1" spans="1:2">
-      <c r="A1077" s="2"/>
-      <c r="B1077" s="2"/>
+      <c r="A1077" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B1077" s="2" t="s">
+        <v>2147</v>
+      </c>
     </row>
     <row r="1078" ht="25" customHeight="1" spans="1:2">
-      <c r="A1078" s="2"/>
-      <c r="B1078" s="2"/>
+      <c r="A1078" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1078" s="2" t="s">
+        <v>2149</v>
+      </c>
     </row>
     <row r="1079" ht="25" customHeight="1" spans="1:2">
-      <c r="A1079" s="2"/>
-      <c r="B1079" s="2"/>
+      <c r="A1079" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1079" s="2" t="s">
+        <v>2151</v>
+      </c>
     </row>
     <row r="1080" ht="25" customHeight="1" spans="1:2">
-      <c r="A1080" s="2"/>
-      <c r="B1080" s="2"/>
+      <c r="A1080" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1080" s="2" t="s">
+        <v>2153</v>
+      </c>
     </row>
     <row r="1081" ht="25" customHeight="1" spans="1:2">
-      <c r="A1081" s="2"/>
-      <c r="B1081" s="2"/>
+      <c r="A1081" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1081" s="2" t="s">
+        <v>2155</v>
+      </c>
     </row>
     <row r="1082" ht="25" customHeight="1" spans="1:2">
-      <c r="A1082" s="2"/>
-      <c r="B1082" s="2"/>
+      <c r="A1082" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1082" s="2" t="s">
+        <v>2157</v>
+      </c>
     </row>
     <row r="1083" ht="25" customHeight="1" spans="1:2">
-      <c r="A1083" s="2"/>
-      <c r="B1083" s="2"/>
+      <c r="A1083" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1083" s="2" t="s">
+        <v>2159</v>
+      </c>
     </row>
     <row r="1084" ht="25" customHeight="1" spans="1:2">
-      <c r="A1084" s="2"/>
-      <c r="B1084" s="2"/>
+      <c r="A1084" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1084" s="2" t="s">
+        <v>2161</v>
+      </c>
     </row>
     <row r="1085" ht="25" customHeight="1" spans="1:2">
-      <c r="A1085" s="2"/>
-      <c r="B1085" s="2"/>
+      <c r="A1085" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1085" s="2" t="s">
+        <v>2163</v>
+      </c>
     </row>
     <row r="1086" ht="25" customHeight="1" spans="1:2">
-      <c r="A1086" s="2"/>
-      <c r="B1086" s="2"/>
+      <c r="A1086" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1086" s="2" t="s">
+        <v>2165</v>
+      </c>
     </row>
     <row r="1087" ht="25" customHeight="1" spans="1:2">
-      <c r="A1087" s="2"/>
-      <c r="B1087" s="2"/>
+      <c r="A1087" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1087" s="2" t="s">
+        <v>2167</v>
+      </c>
     </row>
     <row r="1088" ht="25" customHeight="1" spans="1:2">
-      <c r="A1088" s="2"/>
-      <c r="B1088" s="2"/>
+      <c r="A1088" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1088" s="2" t="s">
+        <v>2169</v>
+      </c>
     </row>
     <row r="1089" ht="25" customHeight="1" spans="1:2">
-      <c r="A1089" s="2"/>
-      <c r="B1089" s="2"/>
+      <c r="A1089" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1089" s="2" t="s">
+        <v>2171</v>
+      </c>
     </row>
     <row r="1090" ht="25" customHeight="1" spans="1:2">
-      <c r="A1090" s="2"/>
-      <c r="B1090" s="2"/>
+      <c r="A1090" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1090" s="2" t="s">
+        <v>2173</v>
+      </c>
     </row>
     <row r="1091" ht="25" customHeight="1" spans="1:2">
-      <c r="A1091" s="2"/>
-      <c r="B1091" s="2"/>
+      <c r="A1091" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B1091" s="2" t="s">
+        <v>2175</v>
+      </c>
     </row>
     <row r="1092" ht="25" customHeight="1" spans="1:2">
-      <c r="A1092" s="2"/>
-      <c r="B1092" s="2"/>
+      <c r="A1092" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1092" s="2" t="s">
+        <v>2177</v>
+      </c>
     </row>
     <row r="1093" ht="25" customHeight="1" spans="1:2">
-      <c r="A1093" s="2"/>
-      <c r="B1093" s="2"/>
+      <c r="A1093" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1093" s="2" t="s">
+        <v>2179</v>
+      </c>
     </row>
     <row r="1094" ht="25" customHeight="1" spans="1:2">
-      <c r="A1094" s="2"/>
-      <c r="B1094" s="2"/>
+      <c r="A1094" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1094" s="2" t="s">
+        <v>2181</v>
+      </c>
     </row>
     <row r="1095" ht="25" customHeight="1" spans="1:2">
-      <c r="A1095" s="2"/>
-      <c r="B1095" s="2"/>
+      <c r="A1095" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1095" s="2" t="s">
+        <v>2183</v>
+      </c>
     </row>
     <row r="1096" ht="25" customHeight="1" spans="1:2">
-      <c r="A1096" s="2"/>
-      <c r="B1096" s="2"/>
+      <c r="A1096" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1096" s="2" t="s">
+        <v>2185</v>
+      </c>
     </row>
     <row r="1097" ht="25" customHeight="1" spans="1:2">
-      <c r="A1097" s="2"/>
-      <c r="B1097" s="2"/>
+      <c r="A1097" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1097" s="2" t="s">
+        <v>2187</v>
+      </c>
     </row>
     <row r="1098" ht="25" customHeight="1" spans="1:2">
-      <c r="A1098" s="2"/>
-      <c r="B1098" s="2"/>
+      <c r="A1098" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1098" s="2" t="s">
+        <v>2189</v>
+      </c>
     </row>
     <row r="1099" ht="25" customHeight="1" spans="1:2">
-      <c r="A1099" s="2"/>
-      <c r="B1099" s="2"/>
+      <c r="A1099" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1099" s="2" t="s">
+        <v>2191</v>
+      </c>
     </row>
     <row r="1100" ht="25" customHeight="1" spans="1:2">
-      <c r="A1100" s="2"/>
-      <c r="B1100" s="2"/>
+      <c r="A1100" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1100" s="2" t="s">
+        <v>2193</v>
+      </c>
     </row>
     <row r="1101" ht="25" customHeight="1" spans="1:2">
-      <c r="A1101" s="2"/>
-      <c r="B1101" s="2"/>
+      <c r="A1101" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1101" s="2" t="s">
+        <v>2195</v>
+      </c>
     </row>
     <row r="1102" ht="25" customHeight="1" spans="1:2">
-      <c r="A1102" s="2"/>
-      <c r="B1102" s="2"/>
+      <c r="A1102" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1102" s="2" t="s">
+        <v>2197</v>
+      </c>
     </row>
     <row r="1103" ht="25" customHeight="1" spans="1:2">
-      <c r="A1103" s="2"/>
-      <c r="B1103" s="2"/>
+      <c r="A1103" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1103" s="2" t="s">
+        <v>2199</v>
+      </c>
     </row>
     <row r="1104" ht="25" customHeight="1" spans="1:2">
-      <c r="A1104" s="2"/>
-      <c r="B1104" s="2"/>
+      <c r="A1104" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1104" s="2" t="s">
+        <v>2201</v>
+      </c>
     </row>
     <row r="1105" ht="25" customHeight="1" spans="1:2">
-      <c r="A1105" s="2"/>
-      <c r="B1105" s="2"/>
+      <c r="A1105" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1105" s="2" t="s">
+        <v>2203</v>
+      </c>
     </row>
     <row r="1106" ht="25" customHeight="1" spans="1:2">
-      <c r="A1106" s="2"/>
-      <c r="B1106" s="2"/>
+      <c r="A1106" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1106" s="2" t="s">
+        <v>2205</v>
+      </c>
     </row>
     <row r="1107" ht="25" customHeight="1" spans="1:2">
-      <c r="A1107" s="2"/>
-      <c r="B1107" s="2"/>
+      <c r="A1107" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1107" s="2" t="s">
+        <v>2207</v>
+      </c>
     </row>
     <row r="1108" ht="25" customHeight="1" spans="1:2">
-      <c r="A1108" s="2"/>
-      <c r="B1108" s="2"/>
+      <c r="A1108" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1108" s="2" t="s">
+        <v>2209</v>
+      </c>
     </row>
     <row r="1109" ht="25" customHeight="1" spans="1:2">
-      <c r="A1109" s="2"/>
-      <c r="B1109" s="2"/>
+      <c r="A1109" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B1109" s="2" t="s">
+        <v>2211</v>
+      </c>
     </row>
     <row r="1110" ht="25" customHeight="1" spans="1:2">
-      <c r="A1110" s="2"/>
-      <c r="B1110" s="2"/>
+      <c r="A1110" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B1110" s="2" t="s">
+        <v>2213</v>
+      </c>
     </row>
     <row r="1111" ht="25" customHeight="1" spans="1:2">
-      <c r="A1111" s="2"/>
-      <c r="B1111" s="2"/>
+      <c r="A1111" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B1111" s="2" t="s">
+        <v>2215</v>
+      </c>
     </row>
     <row r="1112" ht="25" customHeight="1" spans="1:2">
-      <c r="A1112" s="2"/>
-      <c r="B1112" s="2"/>
+      <c r="A1112" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B1112" s="2" t="s">
+        <v>2217</v>
+      </c>
     </row>
     <row r="1113" ht="25" customHeight="1" spans="1:2">
-      <c r="A1113" s="2"/>
-      <c r="B1113" s="2"/>
+      <c r="A1113" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B1113" s="2" t="s">
+        <v>2219</v>
+      </c>
     </row>
     <row r="1114" ht="25" customHeight="1" spans="1:2">
-      <c r="A1114" s="2"/>
-      <c r="B1114" s="2"/>
+      <c r="A1114" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1114" s="2" t="s">
+        <v>2221</v>
+      </c>
     </row>
     <row r="1115" ht="25" customHeight="1" spans="1:2">
-      <c r="A1115" s="2"/>
-      <c r="B1115" s="2"/>
+      <c r="A1115" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1115" s="2" t="s">
+        <v>2223</v>
+      </c>
     </row>
     <row r="1116" ht="25" customHeight="1" spans="1:2">
-      <c r="A1116" s="2"/>
-      <c r="B1116" s="2"/>
+      <c r="A1116" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1116" s="2" t="s">
+        <v>2225</v>
+      </c>
     </row>
     <row r="1117" ht="25" customHeight="1" spans="1:2">
-      <c r="A1117" s="2"/>
-      <c r="B1117" s="2"/>
+      <c r="A1117" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1117" s="2" t="s">
+        <v>2227</v>
+      </c>
     </row>
     <row r="1118" ht="25" customHeight="1" spans="1:2">
-      <c r="A1118" s="2"/>
-      <c r="B1118" s="2"/>
+      <c r="A1118" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B1118" s="2" t="s">
+        <v>2229</v>
+      </c>
     </row>
     <row r="1119" ht="25" customHeight="1" spans="1:2">
-      <c r="A1119" s="2"/>
-      <c r="B1119" s="2"/>
+      <c r="A1119" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B1119" s="2" t="s">
+        <v>2231</v>
+      </c>
     </row>
     <row r="1120" ht="25" customHeight="1" spans="1:2">
-      <c r="A1120" s="2"/>
-      <c r="B1120" s="2"/>
+      <c r="A1120" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B1120" s="2" t="s">
+        <v>2233</v>
+      </c>
     </row>
     <row r="1121" ht="25" customHeight="1" spans="1:2">
-      <c r="A1121" s="2"/>
-      <c r="B1121" s="2"/>
+      <c r="A1121" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1121" s="2" t="s">
+        <v>2235</v>
+      </c>
     </row>
     <row r="1122" ht="25" customHeight="1" spans="1:2">
-      <c r="A1122" s="2"/>
-      <c r="B1122" s="2"/>
+      <c r="A1122" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B1122" s="2" t="s">
+        <v>2237</v>
+      </c>
     </row>
     <row r="1123" ht="25" customHeight="1" spans="1:2">
-      <c r="A1123" s="2"/>
-      <c r="B1123" s="2"/>
+      <c r="A1123" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B1123" s="2" t="s">
+        <v>2239</v>
+      </c>
     </row>
     <row r="1124" ht="25" customHeight="1" spans="1:2">
-      <c r="A1124" s="2"/>
-      <c r="B1124" s="2"/>
+      <c r="A1124" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1124" s="2" t="s">
+        <v>2241</v>
+      </c>
     </row>
     <row r="1125" ht="25" customHeight="1" spans="1:2">
-      <c r="A1125" s="2"/>
-      <c r="B1125" s="2"/>
+      <c r="A1125" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1125" s="2" t="s">
+        <v>2243</v>
+      </c>
     </row>
     <row r="1126" ht="25" customHeight="1" spans="1:2">
-      <c r="A1126" s="2"/>
-      <c r="B1126" s="2"/>
+      <c r="A1126" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1126" s="2" t="s">
+        <v>2245</v>
+      </c>
     </row>
     <row r="1127" ht="25" customHeight="1" spans="1:2">
-      <c r="A1127" s="2"/>
-      <c r="B1127" s="2"/>
+      <c r="A1127" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B1127" s="2" t="s">
+        <v>2247</v>
+      </c>
     </row>
     <row r="1128" ht="25" customHeight="1" spans="1:2">
-      <c r="A1128" s="2"/>
-      <c r="B1128" s="2"/>
+      <c r="A1128" s="2" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B1128" s="2" t="s">
+        <v>2249</v>
+      </c>
     </row>
     <row r="1129" ht="25" customHeight="1" spans="1:2">
-      <c r="A1129" s="2"/>
-      <c r="B1129" s="2"/>
+      <c r="A1129" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1129" s="2" t="s">
+        <v>2251</v>
+      </c>
     </row>
     <row r="1130" ht="25" customHeight="1" spans="1:2">
-      <c r="A1130" s="2"/>
-      <c r="B1130" s="2"/>
+      <c r="A1130" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1130" s="2" t="s">
+        <v>2253</v>
+      </c>
     </row>
     <row r="1131" ht="25" customHeight="1" spans="1:2">
-      <c r="A1131" s="2"/>
-      <c r="B1131" s="2"/>
+      <c r="A1131" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1131" s="2" t="s">
+        <v>2255</v>
+      </c>
     </row>
     <row r="1132" ht="25" customHeight="1" spans="1:2">
-      <c r="A1132" s="2"/>
-      <c r="B1132" s="2"/>
+      <c r="A1132" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B1132" s="2" t="s">
+        <v>2257</v>
+      </c>
     </row>
     <row r="1133" ht="25" customHeight="1" spans="1:2">
-      <c r="A1133" s="2"/>
-      <c r="B1133" s="2"/>
+      <c r="A1133" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B1133" s="2" t="s">
+        <v>2259</v>
+      </c>
     </row>
     <row r="1134" ht="25" customHeight="1" spans="1:2">
-      <c r="A1134" s="2"/>
-      <c r="B1134" s="2"/>
+      <c r="A1134" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1134" s="2" t="s">
+        <v>2261</v>
+      </c>
     </row>
     <row r="1135" ht="25" customHeight="1" spans="1:2">
-      <c r="A1135" s="2"/>
-      <c r="B1135" s="2"/>
+      <c r="A1135" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1135" s="2" t="s">
+        <v>2263</v>
+      </c>
     </row>
     <row r="1136" ht="25" customHeight="1" spans="1:2">
-      <c r="A1136" s="2"/>
-      <c r="B1136" s="2"/>
+      <c r="A1136" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1136" s="2" t="s">
+        <v>2265</v>
+      </c>
     </row>
     <row r="1137" ht="25" customHeight="1" spans="1:2">
-      <c r="A1137" s="2"/>
-      <c r="B1137" s="2"/>
+      <c r="A1137" s="2" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1137" s="2" t="s">
+        <v>2267</v>
+      </c>
     </row>
     <row r="1138" ht="25" customHeight="1" spans="1:2">
-      <c r="A1138" s="2"/>
-      <c r="B1138" s="2"/>
+      <c r="A1138" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1138" s="2" t="s">
+        <v>2269</v>
+      </c>
     </row>
     <row r="1139" ht="25" customHeight="1" spans="1:2">
-      <c r="A1139" s="2"/>
-      <c r="B1139" s="2"/>
+      <c r="A1139" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1139" s="2" t="s">
+        <v>2271</v>
+      </c>
     </row>
     <row r="1140" ht="25" customHeight="1" spans="1:2">
-      <c r="A1140" s="2"/>
-      <c r="B1140" s="2"/>
+      <c r="A1140" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1140" s="2" t="s">
+        <v>2273</v>
+      </c>
     </row>
     <row r="1141" ht="25" customHeight="1" spans="1:2">
-      <c r="A1141" s="2"/>
-      <c r="B1141" s="2"/>
+      <c r="A1141" s="2" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B1141" s="2" t="s">
+        <v>2275</v>
+      </c>
     </row>
     <row r="1142" ht="25" customHeight="1" spans="1:2">
-      <c r="A1142" s="2"/>
-      <c r="B1142" s="2"/>
+      <c r="A1142" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1142" s="2" t="s">
+        <v>2277</v>
+      </c>
     </row>
     <row r="1143" ht="25" customHeight="1" spans="1:2">
-      <c r="A1143" s="2"/>
-      <c r="B1143" s="2"/>
+      <c r="A1143" s="2" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B1143" s="2" t="s">
+        <v>2279</v>
+      </c>
     </row>
     <row r="1144" ht="25" customHeight="1" spans="1:2">
-      <c r="A1144" s="2"/>
-      <c r="B1144" s="2"/>
+      <c r="A1144" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1144" s="2" t="s">
+        <v>2281</v>
+      </c>
     </row>
     <row r="1145" ht="25" customHeight="1" spans="1:2">
-      <c r="A1145" s="2"/>
-      <c r="B1145" s="2"/>
+      <c r="A1145" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1145" s="2" t="s">
+        <v>2283</v>
+      </c>
     </row>
     <row r="1146" ht="25" customHeight="1" spans="1:2">
-      <c r="A1146" s="2"/>
-      <c r="B1146" s="2"/>
+      <c r="A1146" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1146" s="2" t="s">
+        <v>2285</v>
+      </c>
     </row>
     <row r="1147" ht="25" customHeight="1" spans="1:2">
-      <c r="A1147" s="2"/>
-      <c r="B1147" s="2"/>
+      <c r="A1147" s="2" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1147" s="2" t="s">
+        <v>2287</v>
+      </c>
     </row>
     <row r="1148" ht="25" customHeight="1" spans="1:2">
-      <c r="A1148" s="2"/>
-      <c r="B1148" s="2"/>
+      <c r="A1148" s="2" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1148" s="2" t="s">
+        <v>2289</v>
+      </c>
     </row>
     <row r="1149" ht="25" customHeight="1" spans="1:2">
-      <c r="A1149" s="2"/>
-      <c r="B1149" s="2"/>
+      <c r="A1149" s="2" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B1149" s="2" t="s">
+        <v>2291</v>
+      </c>
     </row>
     <row r="1150" ht="25" customHeight="1" spans="1:2">
-      <c r="A1150" s="2"/>
-      <c r="B1150" s="2"/>
+      <c r="A1150" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1150" s="2" t="s">
+        <v>2293</v>
+      </c>
     </row>
     <row r="1151" ht="25" customHeight="1" spans="1:2">
-      <c r="A1151" s="2"/>
-      <c r="B1151" s="2"/>
+      <c r="A1151" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1151" s="2" t="s">
+        <v>2295</v>
+      </c>
     </row>
     <row r="1152" ht="25" customHeight="1" spans="1:2">
       <c r="A1152" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="2296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="2423">
   <si>
     <t>bangla</t>
   </si>
@@ -4891,7 +4891,7 @@
     <t>মাঝে মাঝে পাহাড় থেকে হাতি আসে, একবার একটা হাতি একজন মানুষকে মেরে ফেলেছিল</t>
   </si>
   <si>
-    <t>মাঝে মাঝে ফা'রুত্তুন আতি আইয়্যি, একবার উত্তো আতি উজ্ঞো মানুষ উরে মারি ফেলাইয়্যিল</t>
+    <t>মাঝে মাঝে ফা'রুত্তুন আতি আইয়্যি, একবার উজ্ঞো আতি মানুষ উজ্ঞোরে মারি ফেলাইয়্যিল</t>
   </si>
   <si>
     <t>গরুর জন্য কিছু ঘাস কেটে নিয়ে আসতে হবে</t>
@@ -7019,6 +7019,387 @@
   </si>
   <si>
     <t>রাস্তাত জ্যাম অইলি পাঠাও গরি চলি আইয়্যু</t>
+  </si>
+  <si>
+    <t>ঢাকা থেকে রাজশাহী যেতে ট্রেনে কত ঘণ্টা লাগে সাধারণত?</t>
+  </si>
+  <si>
+    <t>ঢাহাত্তুন রাজশাহী যাইতে ট্রেনুত হত ঘন্ডা লাগে সাধারণত</t>
+  </si>
+  <si>
+    <t>আমি দুপুর ২টার ট্রেনের টিকিট কেটে রেখেছি, তুমি সময়মতো চলে আসিও</t>
+  </si>
+  <si>
+    <t>আঁই দুইজ্জে ২টার ট্রেনুর টিকেট হাডি রেইক্কি, তুঁই সময়মতো চলি আইসসো</t>
+  </si>
+  <si>
+    <t>ভাই, বাসস্ট্যান্ড থেকে হোটেলে যেতে কি রিকশা পাওয়া যাবে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, বাসস্ট্যান্ড উত্তুন হোটেল উত যাইতে কি রিকশা পন যাইবু?</t>
+  </si>
+  <si>
+    <t>না ভাই, এখানে কোনো রিকশা নেই, আপনাকে হেঁটেই হোটেলে যেতে হবে</t>
+  </si>
+  <si>
+    <t>না বদ্দা, এনডে হনো রিকশা নেই, অঁনুত্তুন আডিইরে হোটেল উত যন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমার ব্যাগটা বেশি ভারী, আমাকে একটু হেল্প করেন</t>
+  </si>
+  <si>
+    <t>আঁর ব্যাগ ইবে বেশি ভারী, আঁরে এক্কানা হেল্প গরন</t>
+  </si>
+  <si>
+    <t>তোকে বলেছিলাম জিনিস কম আনতে, এখন এত ভারী ব্যাগ নিয়ে পাহাড়ে উঠব কীভাবে?</t>
+  </si>
+  <si>
+    <t>তোরে হইলাম জিনিস হম আনিবের লাই, এহন এল্লেত ভারী ব্যাগ লই ফা'রুত উইট্টুম কেনে?</t>
+  </si>
+  <si>
+    <t>পাহাড়ে বেশি ওপরে ওঠা ঠিক হবে না</t>
+  </si>
+  <si>
+    <t>ফা'রুত বেশি উরে উডন ঠিক ন অইবু</t>
+  </si>
+  <si>
+    <t>আমি প্রথমবারের মতো কক্সবাজার যাচ্ছি, তাই বেশি উত্তেজিত</t>
+  </si>
+  <si>
+    <t>আঁই প্রথমবারুর মত কক্সবাজার যাইর, এতেল্লে বেশি উত্তেজিত</t>
+  </si>
+  <si>
+    <t>তুমি তো এখনো সেন্ট মার্টিন যাওনি, গেলে বুঝতে সুন্দর কাকে বলে</t>
+  </si>
+  <si>
+    <t>তুঁই তো এহনো সেন্ট মার্টিন ন যও, গেলি বুইজতে সুন্দর হারে হয়</t>
+  </si>
+  <si>
+    <t>সেন্ট মার্টিন অনেক সুন্দর একটা দ্বীপ, চাইলে ঘুরে আসতে পারিস</t>
+  </si>
+  <si>
+    <t>সেন্ট মার্টিন বত সুন্দর এক্কান দ্বীপ, চাইলি ঘুরি আইত পারুস</t>
+  </si>
+  <si>
+    <t>আমার ইচ্ছা একদিন পুরো পৃথিবী ঘুরে দেখব</t>
+  </si>
+  <si>
+    <t>আঁর ইচ্ছে একদিন পুরো পৃথিবী ঘুরি চাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমি এখন থেকে টাকা জমাচ্ছি, যেন বন্ধে কোথাও একটু ঘুরে আসতে পারি</t>
+  </si>
+  <si>
+    <t>আঁই এহনুত্তুন টিয়া জমাইর, যেন বন্ধত হনোমিক্কে এক্কানা ঘুরি আইত ফারি</t>
+  </si>
+  <si>
+    <t>আমার লাগেজটা কোনদিকে রাখব? বাসে কি লাগেজ রাখার জায়গা আছে?</t>
+  </si>
+  <si>
+    <t>আঁর লাগেজ ইবে হুনদি রাইক্কুম? বাসুত কি লাগেজ রাহিবের জাগা আছে?</t>
+  </si>
+  <si>
+    <t>আমার লাগেজ একটু বড়, সেজন্য এটা এখানে রাখতে সমস্যা হচ্ছে</t>
+  </si>
+  <si>
+    <t>আঁর লাগেজ এক্কানা বরো, এতেল্লে ইবে এনডে রাইখতে সমস্যা অর</t>
+  </si>
+  <si>
+    <t>বেশি ভোরে বের হইস না, ভোরে গাড়ি পাওয়া যাবে না</t>
+  </si>
+  <si>
+    <t>বেশি ফোওয়াত্তে বাইর ন অইস, ফোওয়াত্তে গারি ফা ন যাইবু</t>
+  </si>
+  <si>
+    <t>একটা রিকশা নিয়ে মুরাদপুর চলে আয়, আমি ওখানে দাঁড়িয়ে আছি</t>
+  </si>
+  <si>
+    <t>এক্কান রিকশে লই মুরাদপুর চলি আয়, আঁই এনডে থিয়েই আছি</t>
+  </si>
+  <si>
+    <t>এবার কাপ্তাই লেকে গেলে নৌকা নিয়ে ঘুরব</t>
+  </si>
+  <si>
+    <t>এবার কাপ্তাই লেকুত গেলি নৌকো লই ঘুইজ্জুম</t>
+  </si>
+  <si>
+    <t>এরা নৌকা ভাড়া বেশি চাচ্ছে, চল আমরা অন্য নৌকা দেখি</t>
+  </si>
+  <si>
+    <t>ইতারা নৌকো ভারা বেশি চার, চল আঁরা অন্য নৌকো চায়</t>
+  </si>
+  <si>
+    <t>আমি নৌকায় চড়তে পারব না, আমার ভয় লাগে</t>
+  </si>
+  <si>
+    <t>আঁই নৌকোত চরিত ন ফাইজ্জুম, আত্তুন ডর লাগে</t>
+  </si>
+  <si>
+    <t>এই ট্রেনে কি খাবারের ব্যবস্থা আছে? নাকি কিনে নিয়ে যেতে হবে?</t>
+  </si>
+  <si>
+    <t>এই ট্রেনুত কি হানার ব্যবস্থা আছে? নাকি কিনি লই যন ফরিবু?</t>
+  </si>
+  <si>
+    <t>আপনারা এত এত ভাড়া নেন, কিন্তু খাবারের মান ভালো না</t>
+  </si>
+  <si>
+    <t>অঁনেরা এদুজ্ঞুন এদুজ্ঞুন ভারা লন, কিন্তু হানার মান ভালা ন</t>
+  </si>
+  <si>
+    <t>আমাদের বাস কুমিল্লায় একটা হোটেলে থামবে, আমরা ওখান থেকে রাতের খাবার খেয়ে নেব</t>
+  </si>
+  <si>
+    <t>আঁরার বাস কুমিল্লেত এক্কান হোটেলুত থামিবু, আঁরা এনডেত্তুন রাতিয়ের হানা হায় লইয়্যুম</t>
+  </si>
+  <si>
+    <t>সেন্ট মার্টিন যাওয়ার জন্য টেকনাফ থেকে জাহাজ সকালে কখন ছাড়ে?</t>
+  </si>
+  <si>
+    <t>সেন্ট মার্টিন যাইবের লাই টেকনাফ উত্তুন জাচ বেইন্নে হত্তে চারে?</t>
+  </si>
+  <si>
+    <t>ভাই, ঢাকায় যাওয়ার শেষ বাস কয়টা বাজে ছাড়বে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, ঢাহা যাইবের শেষ বাস হয়টা বাজে ছারিবু?</t>
+  </si>
+  <si>
+    <t>আজকে আর কোনো ঢাকার বাস বাকি নেই, সবগুলো চলে গেছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে আর হনো ঢাহার বাস বাকি নেই, বিয়াজ্ঞিন চলি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>যদি বাস না পাই, তাহলে আমাদের ট্রেনে যেতে হবে</t>
+  </si>
+  <si>
+    <t>যদি বাস ন পাই, তইলি আরাত্তুন ট্রেনুত যন ফরিবু</t>
+  </si>
+  <si>
+    <t>ভাই, বাস ছাড়তে আর কতক্ষণ সময় বাকি আছে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, বাস ছারিবের লাই আর হতক্ষন সময় বাকি আছে?</t>
+  </si>
+  <si>
+    <t>যদি সময় বেশি থাকে, তাহলে আমি একটু নাস্তা করে আসি</t>
+  </si>
+  <si>
+    <t>যদি সময় বেশি থাহে, তইলি আঁই এক্কানা নাস্তা গরি আয়</t>
+  </si>
+  <si>
+    <t>এই হোটেলের খাবার ভাল না, আমরা সামনের হোটেলে যায়</t>
+  </si>
+  <si>
+    <t>এই হোটেলুর হানা ভালা ন, আঁরা সামনুর হোটেলুত যায়</t>
+  </si>
+  <si>
+    <t>তুমি রাস্তা পার হলেই আমাকে দেখতে পাবে, আমি ফুলকলির সামনে দাঁড়িয়ে আছি</t>
+  </si>
+  <si>
+    <t>তুঁই রাস্তা পার অইলিই আঁরা দেহিবে, আঁই ফুলকলির সামনে থিয়েই আছি</t>
+  </si>
+  <si>
+    <t>এই ঈদে আমরা একটা ফ্যামিলি টুর দেব</t>
+  </si>
+  <si>
+    <t>এই ঈদুত আঁরা উজ্ঞো ফ্যামেলি টুর দিয়্যুম</t>
+  </si>
+  <si>
+    <t>চিন্তা করছি এই ঈদে ফ্যামিলি নিয়ে সেন্ট মার্টিন ঘুরে আসব</t>
+  </si>
+  <si>
+    <t>চিন্তে গরির এই ঈদুত ফ্যামেলি লই সেন্ট মার্টিন ঘুরি আইসসুম</t>
+  </si>
+  <si>
+    <t>আমি ঈদের ছুটিতে বাড়ি যাব, তাই আগে থেকে টিকিট কেটে রাখতে হবে</t>
+  </si>
+  <si>
+    <t>আঁই ঈদুর ছুটিত বারি যাইয়্যুম, এতেল্লে আগে ভাগে টিকেট হাডি রাহন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমাদের গ্রুপে আমরা বিশজন আছি, পুরো বাস ভাড়া নিলে কত পড়বে?</t>
+  </si>
+  <si>
+    <t>আঁরার গ্রুপুত আঁরা বিশজন আছি, পুরো বাস ভারা লইলি হতো ফরিবু?</t>
+  </si>
+  <si>
+    <t>আমাদের একটা বাস দিয়ে হবেনা, দুইটা লাগবে</t>
+  </si>
+  <si>
+    <t>আরাত্তুন এক্কান বাস দি ন অইবু, দুইয়েন লাগিবু</t>
+  </si>
+  <si>
+    <t>আল্লাহর অনেক বড় রহমত, আজকে অনেক বড় এক্সিডেন্ট থেকে বেঁচে গেছি</t>
+  </si>
+  <si>
+    <t>আল্লার বত বরো রহমত, আজিয়ে বত বরো এক্সিডেন্ট উত্তুন বাচি গেই</t>
+  </si>
+  <si>
+    <t>দূরে কোথাও গেলে ঘর থেকে দোয়া পড়ে বের হতে হয়</t>
+  </si>
+  <si>
+    <t>দুরে হনোমিক্কে গেলি ঘরুত্তুন দোয়া পরি বাইর অন ফরে</t>
+  </si>
+  <si>
+    <t>আমাদের বাস ড্রাইভার অনেক স্পিডে বাস চালাচ্ছিল</t>
+  </si>
+  <si>
+    <t>আঁরার বাস ড্রাইভার বত স্পিডে বাস চালার</t>
+  </si>
+  <si>
+    <t>আমরা অনেক মানা করার পরও ড্রাইভার গাড়ি স্লো করেনি</t>
+  </si>
+  <si>
+    <t>আঁরা বত মানা গরনুর পরও ড্রাইভার গারি স্লো ন গরে</t>
+  </si>
+  <si>
+    <t>ভাই, গাবতলী বাস টার্মিনাল থেকে কুষ্টিয়ার বাস কোথা থেকে ছাড়ে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, গাবতলী বাস টার্মিনাল উত্তুন কষ্টিয়ার বাস হত্তুন ছারে?</t>
+  </si>
+  <si>
+    <t>নদীপথে যাওয়াটা কতটা নিরাপদ, বিশেষ করে বর্ষার মৌসুমে?</t>
+  </si>
+  <si>
+    <t>দইজ্জে দি যন হতটা নিরাপদ, বিশেষ গরি বর্ষাহালে?</t>
+  </si>
+  <si>
+    <t>ঢাকা থেকে খুলনা যেতে ট্রেনে এবং বাসে কোনটায় কম সময় লাগে?</t>
+  </si>
+  <si>
+    <t>ঢাহাত্তুন খুলনা যাইতে ট্রেনুত এবং বাসুত হন্নানুত হম সময় লাগে?</t>
+  </si>
+  <si>
+    <t>এই হোটেলটা স্টেশনের কাছে কি না দেখো, কারণ ভোরেই ট্রেন ধরতে হবে</t>
+  </si>
+  <si>
+    <t>এই হোটেল ইয়েন স্টেশনুর হাছে আছে কিনা স, হারন ফোওয়াত্তেই ট্রেন ধরন ফরিবু</t>
+  </si>
+  <si>
+    <t>এই বাসটা কি সরাসরি যাবে, নাকি মাঝখানে অনেক জায়গায় থামবে?</t>
+  </si>
+  <si>
+    <t>এই বাস ইয়েন কি সরাসরি যাইবু, নাকি মাঝুদ্দি বত জাগাত থামিবু?</t>
+  </si>
+  <si>
+    <t>ভাই, সদরঘাট লঞ্চ টার্মিনাল থেকে বরিশালের লঞ্চ কখন ছাড়ে রাতে?</t>
+  </si>
+  <si>
+    <t>বদ্দা, সদরঘাট লঞ্চ টার্মিনালুত্তুন বারিশালুর লঞ্চ হত্তে ছারে রাতিয়ে?</t>
+  </si>
+  <si>
+    <t>আমার টিকেট হারিয়ে গেছে, এখন কি নতুন করে কিনতে হবে নাকি অন্য কোনো ব্যবস্থা আছে?</t>
+  </si>
+  <si>
+    <t>আঁর টিকেট আঝি গেইয়্যি, এহন কি নতুন গরি কিনন ফরিবু নাকি অন্য হনো ব্যবাস্থা আছে?</t>
+  </si>
+  <si>
+    <t>ভাই, আমাকে নতুন ব্রিজে নামিয়ে দিয়েন, যদি ঘুমিয়ে যাই</t>
+  </si>
+  <si>
+    <t>বদ্দা, আঁরে নতুন ব্রিজ নামায় দিইয়্যুন যদি ঘুমায় যাই</t>
+  </si>
+  <si>
+    <t>বাসে ঘুমানো ভালো না, টাকা-পয়সা আর ব্যাগ চুরি হয়ে যেতে পারে</t>
+  </si>
+  <si>
+    <t>বাসুত ঘুম যন ভালা ন, টিয়া-ফুইশে আর ব্যাগ চুরি অই যাইত পারে</t>
+  </si>
+  <si>
+    <t>একবার আমার এক স্যারের ফোন বাসে চুরি হয়ে গিয়েছিল</t>
+  </si>
+  <si>
+    <t>একবার আঁর উজ্ঞো স্যার উর ফোন বাসুত চুরি অই গেইয়্যিল</t>
+  </si>
+  <si>
+    <t>কী সমস্যা ভাই, বাস ছাড়তে এত দেরি কেন?</t>
+  </si>
+  <si>
+    <t>কি সমস্যা বদ্দা, বাস ছারতে এল্লেত দেরি কা?</t>
+  </si>
+  <si>
+    <t>আমার একটা গুরুত্বপূর্ণ কাজ আছে, যদি দেরি হয় তাহলে আমি ভাড়া দিব না</t>
+  </si>
+  <si>
+    <t>আপনি একটু শান্ত হন, বাস ১০ মিনিটের মধ্যে ছেড়ে দিবে</t>
+  </si>
+  <si>
+    <t>এখন রাত হয়ে গেছে, তাই ভাড়া একটু বেশি দিতে হবে</t>
+  </si>
+  <si>
+    <t>আজকে ঈদের দিন, তাই ভাড়া ডাবল</t>
+  </si>
+  <si>
+    <t>এই রাস্তা দিয়ে রাতে চলাচল নিরাপদ না</t>
+  </si>
+  <si>
+    <t>ভাই, গাড়ি অন্য রাস্তা দিয়ে নিয়ে যান, শুনেছি এই রাস্তায় নাকি চুর ডাকাতের ভয় আছে</t>
+  </si>
+  <si>
+    <t>ভাই, বাস তো ভরে গেছে, এবার ছেড়ে দেন</t>
+  </si>
+  <si>
+    <t>আর কত মানুষ নিবেন, এখানে যায়গা কোথায়?</t>
+  </si>
+  <si>
+    <t>ড্রাইভার কই? গাড়ি ছাড়ে না কেন এখনো?</t>
+  </si>
+  <si>
+    <t>লোকাল বাসে উঠলে এই সমস্যা, জায়গায় জায়গায় দাঁড়ায় থাকে</t>
+  </si>
+  <si>
+    <t>আমাকে মনে করে আমিরাবাদ নামিয়ে দিয়েন, আমি জায়গা চিনি না তাই</t>
+  </si>
+  <si>
+    <t>আপনাকে ৫০ টাকা দিয়েছিলাম, ১০ টাকা ফেরত দিতে ভুলে গেছেন</t>
+  </si>
+  <si>
+    <t>বাসে সিট খালি আছে? আমি দাড়িয়ে যেতে পারব না</t>
+  </si>
+  <si>
+    <t>এখনো আমরা অর্ধেক ও যাই নাই, আরো অনেক পথ বাকি আছে</t>
+  </si>
+  <si>
+    <t>আমার বমি আসবে মনে হচ্ছে, তোর কাছে আছার আছে?</t>
+  </si>
+  <si>
+    <t>সামনে একটা এক্সিডেন্ট হয়েছে, তাই রাস্তায় জ্যাম লেগে আছে</t>
+  </si>
+  <si>
+    <t>রাস্তায় বড় বড় ট্রাকগুলো দেখলে আমার ভয় লাগে</t>
+  </si>
+  <si>
+    <t>আমাদেরকে আগে থেকে হোটেল বুক করে ফেলতে হবে, নাহয় ওখানে গিয়ে ঝামেলায় পড়ে যাব</t>
+  </si>
+  <si>
+    <t>আমরা তিনজন বন্ধু, আমাদের কে একটা বড় রুম দিলেই হবে</t>
+  </si>
+  <si>
+    <t>রুমের সাথে এটাচ ওয়াশরুম আছে কিনা দেখতে হবে</t>
+  </si>
+  <si>
+    <t>আমাদের রুমে অবশ্যই এটাচ ওয়াশরুম থাকতে হবে, নাহয় আমরা রুম নিব না</t>
+  </si>
+  <si>
+    <t>ভাই, বৃষ্টি চলে আসছে, একটু বাসের জানালাগুলো বন্ধ করে দেন</t>
+  </si>
+  <si>
+    <t>আমরা বান্দরবান যেতে চাচ্ছি, দিনে গিয়ে কি দিনে ফিরে আসতে পারব?</t>
+  </si>
+  <si>
+    <t>এতো খুশি হয়ে লাভ নেই, টুরে যাচ্ছিনা আমরা</t>
+  </si>
+  <si>
+    <t>আমার ঘরে ঝামেলা করছে, তাই যেতে পারছিনা</t>
+  </si>
+  <si>
+    <t>বেছে থাকলে ইনশাআল্লাহ সামনের বছুর সবাই মিলে যাব</t>
+  </si>
+  <si>
+    <t>তুই তো বিয়ে করে একদম চেঞ্জ হয়ে গেছিস, তোর সাথে কোথাও যাওয়া হয় না অনেকদিন</t>
   </si>
 </sst>
 </file>
@@ -17404,311 +17785,565 @@
       </c>
     </row>
     <row r="1152" ht="25" customHeight="1" spans="1:2">
-      <c r="A1152" s="2"/>
-      <c r="B1152" s="2"/>
+      <c r="A1152" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1152" s="2" t="s">
+        <v>2297</v>
+      </c>
     </row>
     <row r="1153" ht="25" customHeight="1" spans="1:2">
-      <c r="A1153" s="2"/>
-      <c r="B1153" s="2"/>
+      <c r="A1153" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1153" s="2" t="s">
+        <v>2299</v>
+      </c>
     </row>
     <row r="1154" ht="25" customHeight="1" spans="1:2">
-      <c r="A1154" s="2"/>
-      <c r="B1154" s="2"/>
+      <c r="A1154" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1154" s="2" t="s">
+        <v>2301</v>
+      </c>
     </row>
     <row r="1155" ht="25" customHeight="1" spans="1:2">
-      <c r="A1155" s="2"/>
-      <c r="B1155" s="2"/>
+      <c r="A1155" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1155" s="2" t="s">
+        <v>2303</v>
+      </c>
     </row>
     <row r="1156" ht="25" customHeight="1" spans="1:2">
-      <c r="A1156" s="2"/>
-      <c r="B1156" s="2"/>
+      <c r="A1156" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1156" s="2" t="s">
+        <v>2305</v>
+      </c>
     </row>
     <row r="1157" ht="25" customHeight="1" spans="1:2">
-      <c r="A1157" s="2"/>
-      <c r="B1157" s="2"/>
+      <c r="A1157" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B1157" s="2" t="s">
+        <v>2307</v>
+      </c>
     </row>
     <row r="1158" ht="25" customHeight="1" spans="1:2">
-      <c r="A1158" s="2"/>
-      <c r="B1158" s="2"/>
+      <c r="A1158" s="2" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1158" s="2" t="s">
+        <v>2309</v>
+      </c>
     </row>
     <row r="1159" ht="25" customHeight="1" spans="1:2">
-      <c r="A1159" s="2"/>
-      <c r="B1159" s="2"/>
+      <c r="A1159" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B1159" s="2" t="s">
+        <v>2311</v>
+      </c>
     </row>
     <row r="1160" ht="25" customHeight="1" spans="1:2">
-      <c r="A1160" s="2"/>
-      <c r="B1160" s="2"/>
+      <c r="A1160" s="2" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1160" s="2" t="s">
+        <v>2313</v>
+      </c>
     </row>
     <row r="1161" ht="25" customHeight="1" spans="1:2">
-      <c r="A1161" s="2"/>
-      <c r="B1161" s="2"/>
+      <c r="A1161" s="2" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B1161" s="2" t="s">
+        <v>2315</v>
+      </c>
     </row>
     <row r="1162" ht="25" customHeight="1" spans="1:2">
-      <c r="A1162" s="2"/>
-      <c r="B1162" s="2"/>
+      <c r="A1162" s="2" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1162" s="2" t="s">
+        <v>2317</v>
+      </c>
     </row>
     <row r="1163" ht="25" customHeight="1" spans="1:2">
-      <c r="A1163" s="2"/>
-      <c r="B1163" s="2"/>
+      <c r="A1163" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1163" s="2" t="s">
+        <v>2319</v>
+      </c>
     </row>
     <row r="1164" ht="25" customHeight="1" spans="1:2">
-      <c r="A1164" s="2"/>
-      <c r="B1164" s="2"/>
+      <c r="A1164" s="2" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1164" s="2" t="s">
+        <v>2321</v>
+      </c>
     </row>
     <row r="1165" ht="25" customHeight="1" spans="1:2">
-      <c r="A1165" s="2"/>
-      <c r="B1165" s="2"/>
+      <c r="A1165" s="2" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1165" s="2" t="s">
+        <v>2323</v>
+      </c>
     </row>
     <row r="1166" ht="25" customHeight="1" spans="1:2">
-      <c r="A1166" s="2"/>
-      <c r="B1166" s="2"/>
+      <c r="A1166" s="2" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B1166" s="2" t="s">
+        <v>2325</v>
+      </c>
     </row>
     <row r="1167" ht="25" customHeight="1" spans="1:2">
-      <c r="A1167" s="2"/>
-      <c r="B1167" s="2"/>
+      <c r="A1167" s="2" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B1167" s="2" t="s">
+        <v>2327</v>
+      </c>
     </row>
     <row r="1168" ht="25" customHeight="1" spans="1:2">
-      <c r="A1168" s="2"/>
-      <c r="B1168" s="2"/>
+      <c r="A1168" s="2" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1168" s="2" t="s">
+        <v>2329</v>
+      </c>
     </row>
     <row r="1169" ht="25" customHeight="1" spans="1:2">
-      <c r="A1169" s="2"/>
-      <c r="B1169" s="2"/>
+      <c r="A1169" s="2" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B1169" s="2" t="s">
+        <v>2331</v>
+      </c>
     </row>
     <row r="1170" ht="25" customHeight="1" spans="1:2">
-      <c r="A1170" s="2"/>
-      <c r="B1170" s="2"/>
+      <c r="A1170" s="2" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B1170" s="2" t="s">
+        <v>2333</v>
+      </c>
     </row>
     <row r="1171" ht="25" customHeight="1" spans="1:2">
-      <c r="A1171" s="2"/>
-      <c r="B1171" s="2"/>
+      <c r="A1171" s="2" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B1171" s="2" t="s">
+        <v>2335</v>
+      </c>
     </row>
     <row r="1172" ht="25" customHeight="1" spans="1:2">
-      <c r="A1172" s="2"/>
-      <c r="B1172" s="2"/>
+      <c r="A1172" s="2" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B1172" s="2" t="s">
+        <v>2337</v>
+      </c>
     </row>
     <row r="1173" ht="25" customHeight="1" spans="1:2">
-      <c r="A1173" s="2"/>
-      <c r="B1173" s="2"/>
+      <c r="A1173" s="2" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1173" s="2" t="s">
+        <v>2339</v>
+      </c>
     </row>
     <row r="1174" ht="25" customHeight="1" spans="1:2">
-      <c r="A1174" s="2"/>
-      <c r="B1174" s="2"/>
+      <c r="A1174" s="2" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B1174" s="2" t="s">
+        <v>2341</v>
+      </c>
     </row>
     <row r="1175" ht="25" customHeight="1" spans="1:2">
-      <c r="A1175" s="2"/>
-      <c r="B1175" s="2"/>
+      <c r="A1175" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B1175" s="2" t="s">
+        <v>2343</v>
+      </c>
     </row>
     <row r="1176" ht="25" customHeight="1" spans="1:2">
-      <c r="A1176" s="2"/>
-      <c r="B1176" s="2"/>
+      <c r="A1176" s="2" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B1176" s="2" t="s">
+        <v>2345</v>
+      </c>
     </row>
     <row r="1177" ht="25" customHeight="1" spans="1:2">
-      <c r="A1177" s="2"/>
-      <c r="B1177" s="2"/>
+      <c r="A1177" s="2" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1177" s="2" t="s">
+        <v>2347</v>
+      </c>
     </row>
     <row r="1178" ht="25" customHeight="1" spans="1:2">
-      <c r="A1178" s="2"/>
-      <c r="B1178" s="2"/>
+      <c r="A1178" s="2" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B1178" s="2" t="s">
+        <v>2349</v>
+      </c>
     </row>
     <row r="1179" ht="25" customHeight="1" spans="1:2">
-      <c r="A1179" s="2"/>
-      <c r="B1179" s="2"/>
+      <c r="A1179" s="2" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B1179" s="2" t="s">
+        <v>2351</v>
+      </c>
     </row>
     <row r="1180" ht="25" customHeight="1" spans="1:2">
-      <c r="A1180" s="2"/>
-      <c r="B1180" s="2"/>
+      <c r="A1180" s="2" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B1180" s="2" t="s">
+        <v>2353</v>
+      </c>
     </row>
     <row r="1181" ht="25" customHeight="1" spans="1:2">
-      <c r="A1181" s="2"/>
-      <c r="B1181" s="2"/>
+      <c r="A1181" s="2" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1181" s="2" t="s">
+        <v>2355</v>
+      </c>
     </row>
     <row r="1182" ht="25" customHeight="1" spans="1:2">
-      <c r="A1182" s="2"/>
-      <c r="B1182" s="2"/>
+      <c r="A1182" s="2" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B1182" s="2" t="s">
+        <v>2357</v>
+      </c>
     </row>
     <row r="1183" ht="25" customHeight="1" spans="1:2">
-      <c r="A1183" s="2"/>
-      <c r="B1183" s="2"/>
+      <c r="A1183" s="2" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B1183" s="2" t="s">
+        <v>2359</v>
+      </c>
     </row>
     <row r="1184" ht="25" customHeight="1" spans="1:2">
-      <c r="A1184" s="2"/>
-      <c r="B1184" s="2"/>
+      <c r="A1184" s="2" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B1184" s="2" t="s">
+        <v>2361</v>
+      </c>
     </row>
     <row r="1185" ht="25" customHeight="1" spans="1:2">
-      <c r="A1185" s="2"/>
-      <c r="B1185" s="2"/>
+      <c r="A1185" s="2" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B1185" s="2" t="s">
+        <v>2363</v>
+      </c>
     </row>
     <row r="1186" ht="25" customHeight="1" spans="1:2">
-      <c r="A1186" s="2"/>
-      <c r="B1186" s="2"/>
+      <c r="A1186" s="2" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1186" s="2" t="s">
+        <v>2365</v>
+      </c>
     </row>
     <row r="1187" ht="25" customHeight="1" spans="1:2">
-      <c r="A1187" s="2"/>
-      <c r="B1187" s="2"/>
+      <c r="A1187" s="2" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B1187" s="2" t="s">
+        <v>2367</v>
+      </c>
     </row>
     <row r="1188" ht="25" customHeight="1" spans="1:2">
-      <c r="A1188" s="2"/>
-      <c r="B1188" s="2"/>
+      <c r="A1188" s="2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B1188" s="2" t="s">
+        <v>2369</v>
+      </c>
     </row>
     <row r="1189" ht="25" customHeight="1" spans="1:2">
-      <c r="A1189" s="2"/>
-      <c r="B1189" s="2"/>
+      <c r="A1189" s="2" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B1189" s="2" t="s">
+        <v>2371</v>
+      </c>
     </row>
     <row r="1190" ht="25" customHeight="1" spans="1:2">
-      <c r="A1190" s="2"/>
-      <c r="B1190" s="2"/>
+      <c r="A1190" s="2" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1190" s="2" t="s">
+        <v>2373</v>
+      </c>
     </row>
     <row r="1191" ht="25" customHeight="1" spans="1:2">
-      <c r="A1191" s="2"/>
-      <c r="B1191" s="2"/>
+      <c r="A1191" s="2" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1191" s="2" t="s">
+        <v>2375</v>
+      </c>
     </row>
     <row r="1192" ht="25" customHeight="1" spans="1:2">
-      <c r="A1192" s="2"/>
-      <c r="B1192" s="2"/>
+      <c r="A1192" s="2" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B1192" s="2" t="s">
+        <v>2377</v>
+      </c>
     </row>
     <row r="1193" ht="25" customHeight="1" spans="1:2">
-      <c r="A1193" s="2"/>
-      <c r="B1193" s="2"/>
+      <c r="A1193" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B1193" s="2" t="s">
+        <v>2379</v>
+      </c>
     </row>
     <row r="1194" ht="25" customHeight="1" spans="1:2">
-      <c r="A1194" s="2"/>
-      <c r="B1194" s="2"/>
+      <c r="A1194" s="2" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B1194" s="2" t="s">
+        <v>2381</v>
+      </c>
     </row>
     <row r="1195" ht="25" customHeight="1" spans="1:2">
-      <c r="A1195" s="2"/>
-      <c r="B1195" s="2"/>
+      <c r="A1195" s="2" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B1195" s="2" t="s">
+        <v>2383</v>
+      </c>
     </row>
     <row r="1196" ht="25" customHeight="1" spans="1:2">
-      <c r="A1196" s="2"/>
-      <c r="B1196" s="2"/>
+      <c r="A1196" s="2" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B1196" s="2" t="s">
+        <v>2385</v>
+      </c>
     </row>
     <row r="1197" ht="25" customHeight="1" spans="1:2">
-      <c r="A1197" s="2"/>
-      <c r="B1197" s="2"/>
+      <c r="A1197" s="2" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1197" s="2" t="s">
+        <v>2387</v>
+      </c>
     </row>
     <row r="1198" ht="25" customHeight="1" spans="1:2">
-      <c r="A1198" s="2"/>
-      <c r="B1198" s="2"/>
+      <c r="A1198" s="2" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B1198" s="2" t="s">
+        <v>2389</v>
+      </c>
     </row>
     <row r="1199" ht="25" customHeight="1" spans="1:2">
-      <c r="A1199" s="2"/>
-      <c r="B1199" s="2"/>
+      <c r="A1199" s="2" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B1199" s="2" t="s">
+        <v>2391</v>
+      </c>
     </row>
     <row r="1200" ht="25" customHeight="1" spans="1:2">
-      <c r="A1200" s="2"/>
-      <c r="B1200" s="2"/>
+      <c r="A1200" s="2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B1200" s="2" t="s">
+        <v>2393</v>
+      </c>
     </row>
     <row r="1201" ht="25" customHeight="1" spans="1:2">
-      <c r="A1201" s="2"/>
-      <c r="B1201" s="2"/>
+      <c r="A1201" s="2" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B1201" s="2" t="s">
+        <v>2395</v>
+      </c>
     </row>
     <row r="1202" ht="25" customHeight="1" spans="1:2">
-      <c r="A1202" s="2"/>
+      <c r="A1202" s="2" t="s">
+        <v>2396</v>
+      </c>
       <c r="B1202" s="2"/>
     </row>
     <row r="1203" ht="25" customHeight="1" spans="1:2">
-      <c r="A1203" s="2"/>
+      <c r="A1203" s="2" t="s">
+        <v>2397</v>
+      </c>
       <c r="B1203" s="2"/>
     </row>
     <row r="1204" ht="25" customHeight="1" spans="1:2">
-      <c r="A1204" s="2"/>
+      <c r="A1204" s="2" t="s">
+        <v>2398</v>
+      </c>
       <c r="B1204" s="2"/>
     </row>
     <row r="1205" ht="25" customHeight="1" spans="1:2">
-      <c r="A1205" s="2"/>
+      <c r="A1205" s="2" t="s">
+        <v>2399</v>
+      </c>
       <c r="B1205" s="2"/>
     </row>
     <row r="1206" ht="25" customHeight="1" spans="1:2">
-      <c r="A1206" s="2"/>
+      <c r="A1206" s="2" t="s">
+        <v>2400</v>
+      </c>
       <c r="B1206" s="2"/>
     </row>
     <row r="1207" ht="25" customHeight="1" spans="1:2">
-      <c r="A1207" s="2"/>
+      <c r="A1207" s="2" t="s">
+        <v>2401</v>
+      </c>
       <c r="B1207" s="2"/>
     </row>
     <row r="1208" ht="25" customHeight="1" spans="1:2">
-      <c r="A1208" s="2"/>
+      <c r="A1208" s="2" t="s">
+        <v>2402</v>
+      </c>
       <c r="B1208" s="2"/>
     </row>
     <row r="1209" ht="25" customHeight="1" spans="1:2">
-      <c r="A1209" s="2"/>
+      <c r="A1209" s="2" t="s">
+        <v>2403</v>
+      </c>
       <c r="B1209" s="2"/>
     </row>
     <row r="1210" ht="25" customHeight="1" spans="1:2">
-      <c r="A1210" s="2"/>
+      <c r="A1210" s="2" t="s">
+        <v>2404</v>
+      </c>
       <c r="B1210" s="2"/>
     </row>
     <row r="1211" ht="25" customHeight="1" spans="1:2">
-      <c r="A1211" s="2"/>
+      <c r="A1211" s="2" t="s">
+        <v>2405</v>
+      </c>
       <c r="B1211" s="2"/>
     </row>
     <row r="1212" ht="25" customHeight="1" spans="1:2">
-      <c r="A1212" s="2"/>
+      <c r="A1212" s="2" t="s">
+        <v>2406</v>
+      </c>
       <c r="B1212" s="2"/>
     </row>
     <row r="1213" ht="25" customHeight="1" spans="1:2">
-      <c r="A1213" s="2"/>
+      <c r="A1213" s="2" t="s">
+        <v>2407</v>
+      </c>
       <c r="B1213" s="2"/>
     </row>
     <row r="1214" ht="25" customHeight="1" spans="1:2">
-      <c r="A1214" s="2"/>
+      <c r="A1214" s="2" t="s">
+        <v>2408</v>
+      </c>
       <c r="B1214" s="2"/>
     </row>
     <row r="1215" ht="25" customHeight="1" spans="1:2">
-      <c r="A1215" s="2"/>
+      <c r="A1215" s="2" t="s">
+        <v>2409</v>
+      </c>
       <c r="B1215" s="2"/>
     </row>
     <row r="1216" ht="25" customHeight="1" spans="1:2">
-      <c r="A1216" s="2"/>
+      <c r="A1216" s="2" t="s">
+        <v>2410</v>
+      </c>
       <c r="B1216" s="2"/>
     </row>
     <row r="1217" ht="25" customHeight="1" spans="1:2">
-      <c r="A1217" s="2"/>
+      <c r="A1217" s="2" t="s">
+        <v>2411</v>
+      </c>
       <c r="B1217" s="2"/>
     </row>
     <row r="1218" ht="25" customHeight="1" spans="1:2">
-      <c r="A1218" s="2"/>
+      <c r="A1218" s="2" t="s">
+        <v>2412</v>
+      </c>
       <c r="B1218" s="2"/>
     </row>
     <row r="1219" ht="25" customHeight="1" spans="1:2">
-      <c r="A1219" s="2"/>
+      <c r="A1219" s="2" t="s">
+        <v>2413</v>
+      </c>
       <c r="B1219" s="2"/>
     </row>
     <row r="1220" ht="25" customHeight="1" spans="1:2">
-      <c r="A1220" s="2"/>
+      <c r="A1220" s="2" t="s">
+        <v>2414</v>
+      </c>
       <c r="B1220" s="2"/>
     </row>
     <row r="1221" ht="25" customHeight="1" spans="1:2">
-      <c r="A1221" s="2"/>
+      <c r="A1221" s="2" t="s">
+        <v>2415</v>
+      </c>
       <c r="B1221" s="2"/>
     </row>
     <row r="1222" ht="25" customHeight="1" spans="1:2">
-      <c r="A1222" s="2"/>
+      <c r="A1222" s="2" t="s">
+        <v>2416</v>
+      </c>
       <c r="B1222" s="2"/>
     </row>
     <row r="1223" ht="25" customHeight="1" spans="1:2">
-      <c r="A1223" s="2"/>
+      <c r="A1223" s="2" t="s">
+        <v>2417</v>
+      </c>
       <c r="B1223" s="2"/>
     </row>
     <row r="1224" ht="25" customHeight="1" spans="1:2">
-      <c r="A1224" s="2"/>
+      <c r="A1224" s="2" t="s">
+        <v>2418</v>
+      </c>
       <c r="B1224" s="2"/>
     </row>
     <row r="1225" ht="25" customHeight="1" spans="1:2">
-      <c r="A1225" s="2"/>
+      <c r="A1225" s="2" t="s">
+        <v>2419</v>
+      </c>
       <c r="B1225" s="2"/>
     </row>
     <row r="1226" ht="25" customHeight="1" spans="1:2">
-      <c r="A1226" s="2"/>
+      <c r="A1226" s="2" t="s">
+        <v>2420</v>
+      </c>
       <c r="B1226" s="2"/>
     </row>
     <row r="1227" ht="25" customHeight="1" spans="1:2">
-      <c r="A1227" s="2"/>
+      <c r="A1227" s="2" t="s">
+        <v>2421</v>
+      </c>
       <c r="B1227" s="2"/>
     </row>
     <row r="1228" ht="25" customHeight="1" spans="1:2">
-      <c r="A1228" s="2"/>
+      <c r="A1228" s="2" t="s">
+        <v>2422</v>
+      </c>
       <c r="B1228" s="2"/>
     </row>
     <row r="1229" ht="25" customHeight="1" spans="1:2">

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="2423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="2596">
   <si>
     <t>bangla</t>
   </si>
@@ -2223,13 +2223,13 @@
     <t>রাঙামাটি না গিয়ে বান্দরবান গেলে ভাল হবে</t>
   </si>
   <si>
-    <t>রাঙামাটি ন যায় বান্দরবান যাইলি ভালা অইবু</t>
+    <t>রাঙামাটি ন যায় বান্দরবন যাইলি ভালা অইবু</t>
   </si>
   <si>
     <t>বাবা আমার কিছু টাকা লাগবে, বন্ধুদের সাথে বান্দরবান ঘুরতে যাব</t>
   </si>
   <si>
-    <t>আব্বু আত্তুন কিছু টিয়া লাগিবো, বন্ধু অক্কলোর লাই বান্দরবান ঘুইত্তাম যাইয়্যুম</t>
+    <t>আব্বু আত্তুন কিছু টিয়া লাগিবো, বন্ধু অক্কলোর লাই বান্দরবন ঘুইত্তাম যাইয়্যুম</t>
   </si>
   <si>
     <t>কানের নিছে দুইটা থাপ্পর দিব যদি আবার টাকার কথা বলিস</t>
@@ -3477,13 +3477,13 @@
     <t>এটা কি বাসার দারোয়ান?</t>
   </si>
   <si>
-    <t>ইবে কি বাসার দারোয়ান?</t>
+    <t>ইবে কি বাসার দারোওয়ান?</t>
   </si>
   <si>
     <t>দারোয়ানের ভাব দেখে মনে হচ্ছে যেন বাসার মালিক</t>
   </si>
   <si>
-    <t>দারোয়ানুর ভাব দেহি মনে অদ্দে বাসার মালিক</t>
+    <t>দারোওয়ানুর ভাব দেহি মনে অদ্দে বাসার মালিক</t>
   </si>
   <si>
     <t>অফিসের বসকে বলে কিছুদিনের জন্য ছুটি নাও, সবাই মিলে দূরে কোথাও ঘুরতে যাব</t>
@@ -3831,7 +3831,7 @@
     <t>শুনেছি তোমার বড় ভাইয়ের নাকি চাকরি হয়েছে?</t>
   </si>
   <si>
-    <t>উইন্নি তোঁয়ার বদ্দার বলে ছরি অইয়্যি?</t>
+    <t>উইন্নি তোঁয়ার বদ্দার বলে চরি অইয়্যি?</t>
   </si>
   <si>
     <t>বড় ভাইয়ের শ্বশুরবাড়ি অনেক দূরে</t>
@@ -4543,13 +4543,13 @@
     <t>বন্ধু, যদি পারিস তাহলে আমাকে একটা চাকরি খুঁজে দে</t>
   </si>
   <si>
-    <t>বন্ধু, যরি পারুস তইলি আঁরে এক্কান ছরি থোওয়াই দে</t>
+    <t>বন্ধু, যরি পারুস তইলি আঁরে এক্কান চরি থোওয়াই দে</t>
   </si>
   <si>
     <t>আমি যদি চাকরি না করি, তাহলে আমার পরিবার কষ্ট পাবে</t>
   </si>
   <si>
-    <t>আঁই যদি ছরি ন গরি, তইলি আঁর পরিবার হষ্ট ফাইবু</t>
+    <t>আঁই যদি চরি ন গরি, তইলি আঁর পরিবার হষ্ট ফাইবু</t>
   </si>
   <si>
     <t>জমিদার আংকেল বলছে ব্যাচেলর ভাড়া দেবে না</t>
@@ -6784,7 +6784,7 @@
     <t>আমার মতে বান্দরবান থেকে কক্সবাজার যাওয়া ভালো হবে</t>
   </si>
   <si>
-    <t>আঁর মতে বান্দরবান উত্তুন কক্সবাজার যন ভালা অইবু</t>
+    <t>আঁর মতে বান্দরবন উত্তুন কক্সবাজার যন ভালা অইবু</t>
   </si>
   <si>
     <t>আমাদের এখানে ঘুরার জন্য অনেক জায়গা আছে, আশা করি তোমার ভালো লাগবে</t>
@@ -7321,85 +7321,604 @@
     <t>কি সমস্যা বদ্দা, বাস ছারতে এল্লেত দেরি কা?</t>
   </si>
   <si>
-    <t>আমার একটা গুরুত্বপূর্ণ কাজ আছে, যদি দেরি হয় তাহলে আমি ভাড়া দিব না</t>
-  </si>
-  <si>
-    <t>আপনি একটু শান্ত হন, বাস ১০ মিনিটের মধ্যে ছেড়ে দিবে</t>
+    <t>আমার একটা গুরুত্বপূর্ণ কাজ আছে, যদি দেরি হয় তাহলে আমি ভাড়া দেব না</t>
+  </si>
+  <si>
+    <t>আত্তুন এক্কান গুরুত্বপুর্ণ হাজ আছে, যদি দেরি অয় তইলি আঁই ভারা দিতাম ন</t>
+  </si>
+  <si>
+    <t>আপনি একটু শান্ত হন, বাস ১০ মিনিটের মধ্যে ছেড়ে দেবে</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা শান্ত অন, বাস ১০ মিনিটুর মধ্যে ছারি দিবু</t>
   </si>
   <si>
     <t>এখন রাত হয়ে গেছে, তাই ভাড়া একটু বেশি দিতে হবে</t>
   </si>
   <si>
+    <t>এহন রাইত অই গেইয়্যি, এতেল্লে ভারা এক্কানা বেশি দন ফরিবু</t>
+  </si>
+  <si>
     <t>আজকে ঈদের দিন, তাই ভাড়া ডাবল</t>
   </si>
   <si>
+    <t>আজিয়ে ঈদুর দিন, এতেল্লে ভারা ডবল</t>
+  </si>
+  <si>
     <t>এই রাস্তা দিয়ে রাতে চলাচল নিরাপদ না</t>
   </si>
   <si>
-    <t>ভাই, গাড়ি অন্য রাস্তা দিয়ে নিয়ে যান, শুনেছি এই রাস্তায় নাকি চুর ডাকাতের ভয় আছে</t>
+    <t xml:space="preserve">এই রাস্তা দি রাতিয়ে চলাচল নিরাপদ ন </t>
+  </si>
+  <si>
+    <t>ভাই, গাড়ি অন্য রাস্তা দিয়ে নিয়ে যান, শুনেছি এই রাস্তায় নাকি চোর-ডাকাতের ভয় আছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, গারি অন্য রাস্তা দি লই যন, উইন্নি এই রাস্তাত নাকি চোর-ডাহাইতুর ডর আছে</t>
   </si>
   <si>
     <t>ভাই, বাস তো ভরে গেছে, এবার ছেড়ে দেন</t>
   </si>
   <si>
-    <t>আর কত মানুষ নিবেন, এখানে যায়গা কোথায়?</t>
-  </si>
-  <si>
-    <t>ড্রাইভার কই? গাড়ি ছাড়ে না কেন এখনো?</t>
-  </si>
-  <si>
-    <t>লোকাল বাসে উঠলে এই সমস্যা, জায়গায় জায়গায় দাঁড়ায় থাকে</t>
-  </si>
-  <si>
-    <t>আমাকে মনে করে আমিরাবাদ নামিয়ে দিয়েন, আমি জায়গা চিনি না তাই</t>
+    <t>বদ্দা, বাস তো ভরি গেইয়্যি, এবার ছারি দন</t>
+  </si>
+  <si>
+    <t>আর কত মানুষ নেবেন, এখানে জায়গা কোথায়?</t>
+  </si>
+  <si>
+    <t>আর হতো মানুষ লইবেন, এনডে জাগা হনডে?</t>
+  </si>
+  <si>
+    <t>ড্রাইভার কোথায়? গাড়ি ছাড়ছে না কেন এখনো?</t>
+  </si>
+  <si>
+    <t>ড্রাইভার হনডে? গারি ন ছারের কা এহনো?</t>
+  </si>
+  <si>
+    <t>লোকাল বাসে উঠলে এই সমস্যা, জায়গায় জায়গায় দাঁড়িয়ে থাকে</t>
+  </si>
+  <si>
+    <t>লোকাল বাসুত উডিলি এই সমস্যা, জাগাত জাগাত থিয়েই থাহে</t>
+  </si>
+  <si>
+    <t>আমাকে মনে করে আমিরাবাদে নামিয়ে দিয়েন, আমি জায়গা চিনি না তাই</t>
+  </si>
+  <si>
+    <t>আঁরে মনোত গরি আমিরেবাদ নামাই দিয়্যুন, আঁই জাগা ন চিনি এতেল্লে</t>
   </si>
   <si>
     <t>আপনাকে ৫০ টাকা দিয়েছিলাম, ১০ টাকা ফেরত দিতে ভুলে গেছেন</t>
   </si>
   <si>
-    <t>বাসে সিট খালি আছে? আমি দাড়িয়ে যেতে পারব না</t>
-  </si>
-  <si>
-    <t>এখনো আমরা অর্ধেক ও যাই নাই, আরো অনেক পথ বাকি আছে</t>
-  </si>
-  <si>
-    <t>আমার বমি আসবে মনে হচ্ছে, তোর কাছে আছার আছে?</t>
+    <t>অঁনোরে ৫০ টিয়া দিলাম, ১০ টিয়া ফেরত দিতু ভুলি গেইয়্যুন</t>
+  </si>
+  <si>
+    <t>বাসে সিট খালি আছে? আমি দাঁড়িয়ে যেতে পারব না</t>
+  </si>
+  <si>
+    <t>বাসুত সিট হালি আছে? আঁই থিয়েই যাইত ফাইত্তাম নো</t>
+  </si>
+  <si>
+    <t>এখনো আমরা অর্ধেকও যাইনি, আরও অনেক পথ বাকি আছে</t>
+  </si>
+  <si>
+    <t>এহনো আঁরা অদ্দকও নো যাই, আরও বত পথ বাকি আছে</t>
+  </si>
+  <si>
+    <t>আমার বমি আসবে মনে হচ্ছে, তোর কাছে আচার আছে?</t>
+  </si>
+  <si>
+    <t>আত্তুন বুমি আইবু মনে অর, তোর হাছে আচার আছে?</t>
   </si>
   <si>
     <t>সামনে একটা এক্সিডেন্ট হয়েছে, তাই রাস্তায় জ্যাম লেগে আছে</t>
   </si>
   <si>
+    <t>সাম্মোদ্দি এক্কান এক্সিডেন্ট অইয়্যি, এতেল্লে রাস্তাত জাম লাগি থেইক্কি</t>
+  </si>
+  <si>
     <t>রাস্তায় বড় বড় ট্রাকগুলো দেখলে আমার ভয় লাগে</t>
   </si>
   <si>
-    <t>আমাদেরকে আগে থেকে হোটেল বুক করে ফেলতে হবে, নাহয় ওখানে গিয়ে ঝামেলায় পড়ে যাব</t>
-  </si>
-  <si>
-    <t>আমরা তিনজন বন্ধু, আমাদের কে একটা বড় রুম দিলেই হবে</t>
-  </si>
-  <si>
-    <t>রুমের সাথে এটাচ ওয়াশরুম আছে কিনা দেখতে হবে</t>
-  </si>
-  <si>
-    <t>আমাদের রুমে অবশ্যই এটাচ ওয়াশরুম থাকতে হবে, নাহয় আমরা রুম নিব না</t>
+    <t>রাস্তাত বরো বরো ট্রাক এগুন দেহিলি আত্তুন ডর লাগে</t>
+  </si>
+  <si>
+    <t>আমাদের আগে থেকে হোটেল বুক করে ফেলতে হবে, না হলে ওখানে গিয়ে ঝামেলায় পড়ে যাব</t>
+  </si>
+  <si>
+    <t>আরাত্তুন আগুত্তোন হোটেল বুক গরি ফেলন ফরিবু, ন অইলি এনডে যাই ঝামিলেত ফরি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমরা তিনজন বন্ধু, আমাদের একটা বড় রুম দিলেই হবে</t>
+  </si>
+  <si>
+    <t>আঁরা তিনজন বন্ধু, আঁরারে এক্কান বরো রুম দিলিই অইবু</t>
+  </si>
+  <si>
+    <t>রুমের সাথে অ্যাটাচড ওয়াশরুম আছে কি না দেখতে হবে</t>
+  </si>
+  <si>
+    <t>রুমুর লগে এটাচ ওয়াশরুম আছেনা সন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমাদের রুমে অবশ্যই অ্যাটাচড ওয়াশরুম থাকতে হবে, না হলে আমরা রুম নেব না</t>
+  </si>
+  <si>
+    <t>আঁরার রুমুত অবশ্যই এটাচ ওয়াশরুম থাহন ফরিবু, নইলি আঁরা রুম লইতাম নো</t>
   </si>
   <si>
     <t>ভাই, বৃষ্টি চলে আসছে, একটু বাসের জানালাগুলো বন্ধ করে দেন</t>
   </si>
   <si>
+    <t>বদ্দা, বৃষ্টি চলি আইসসি, এক্কানা বাসুর জানালা এগিন বন্ধ গরি দন</t>
+  </si>
+  <si>
     <t>আমরা বান্দরবান যেতে চাচ্ছি, দিনে গিয়ে কি দিনে ফিরে আসতে পারব?</t>
   </si>
   <si>
-    <t>এতো খুশি হয়ে লাভ নেই, টুরে যাচ্ছিনা আমরা</t>
-  </si>
-  <si>
-    <t>আমার ঘরে ঝামেলা করছে, তাই যেতে পারছিনা</t>
-  </si>
-  <si>
-    <t>বেছে থাকলে ইনশাআল্লাহ সামনের বছুর সবাই মিলে যাব</t>
-  </si>
-  <si>
-    <t>তুই তো বিয়ে করে একদম চেঞ্জ হয়ে গেছিস, তোর সাথে কোথাও যাওয়া হয় না অনেকদিন</t>
+    <t>আঁরা বান্দরবন  যেতাম চাইর, দিনুত যাই কি দিনুত ফিরি আইত ফাইজ্জুম?</t>
+  </si>
+  <si>
+    <t>এত খুশি হয়ে লাভ নেই, টুরে যাচ্ছি না আমরা</t>
+  </si>
+  <si>
+    <t>এল্লেত খুশি অই লাভ নেই, টুরুত ন যাইর আঁরা</t>
+  </si>
+  <si>
+    <t>আমার ঘরে ঝামেলা করছে, তাই যেতে পারছি না</t>
+  </si>
+  <si>
+    <t>আঁরো ঘরুত ঝামিলে গরের, এতেল্লে যাইত ন ফারির</t>
+  </si>
+  <si>
+    <t>বেঁচে থাকলে ইনশাআল্লাহ সামনের বছর সবাই মিলে যাব</t>
+  </si>
+  <si>
+    <t>বাচি থাহিলি ইনশাআল্লাহ সামনুর বছর বিয়াজ্ঞুন মিলি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>তুই তো বিয়ে করে একদম চেঞ্জ হয়ে গেছিস, তোর সাথে কোথাও যাওয়া হয় না অনেক দিন</t>
+  </si>
+  <si>
+    <t>তুই তো বিয়ে গরি একদম চেঞ্জ অই গেইয়্যুস, তোর লগে হনোমিক্কে যন ন অয় বতদিন</t>
+  </si>
+  <si>
+    <t>ভাই, বাসের দরজাটা এবার বন্ধ করে দেন, মানুষ আর নেবেন না</t>
+  </si>
+  <si>
+    <t>বদ্দা, বাসুর দরজা ইয়েন এবার বন্ধ গরি দন, মানুষ আর ন লইয়্যুন</t>
+  </si>
+  <si>
+    <t>ড্রাইভারকে বলেন গাড়ি আরও আস্তে চালাতে</t>
+  </si>
+  <si>
+    <t>ড্রাইভার উরে হন গারি আরো আস্তে চলাইতু</t>
+  </si>
+  <si>
+    <t>আমরা এই রাস্তা দিয়ে না গিয়ে অন্য রাস্তা দিয়ে গেলে আরও তাড়াতাড়ি পৌঁছাব</t>
+  </si>
+  <si>
+    <t>আঁরা এই রাস্তা দি ন যাই অন্য রাস্তা দি গেলি আরো তারাতারাই পৌইচ্ছুম</t>
+  </si>
+  <si>
+    <t>একবার চেক করে দেখ, সবাই বাসে উঠছে কি না</t>
+  </si>
+  <si>
+    <t>একবার চেক গরি স, বিয়াজ্ঞুন বাসুত উইঠটি কিনা</t>
+  </si>
+  <si>
+    <t>তোমরা বিকাল ৫টা পর্যন্ত যত ইচ্ছা ঘোরাঘুরি কর সমস্যা নেই, কিন্তু ৫টায় সবাই বাসে চলে আসবে</t>
+  </si>
+  <si>
+    <t>তোঁয়ারা বিকেল ৫টা পর্যন্ত যত ইচ্ছে ঘোরাঘুরি গরো সমস্যা নেই, কিন্তু ৫টায় বিয়াজ্ঞুন বাসুত চলি আইবে</t>
+  </si>
+  <si>
+    <t>আমার নতুন চাকরি হয়েছে ঢাকায়, তাই আজকে রাতে ট্রেনে উঠতে হবে</t>
+  </si>
+  <si>
+    <t>আত্তুন নতুন চরি অইয়্যি ঢাহাত, এতেল্লে আজিয়ে রাতিয়ে ট্রেনুত উডন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমার ৩ তারিখ একটা গুরুত্বপূর্ণ ইন্টারভিউ আছে, সেটার জন্য ঢাকা যেতে হবে</t>
+  </si>
+  <si>
+    <t>আত্তুন ৩ তারিখ এক্কান গুরুত্বপুর্ণ ইন্টারভিউ আছে, ইয়েনুর লাই ঢাহা যন ফরিবু</t>
+  </si>
+  <si>
+    <t>সামনেই পেট্রোল পাম্প আছে, ওখান থেকেই পেট্রোল নেওয়া যাবে</t>
+  </si>
+  <si>
+    <t>সামনেই পেট্রোল পাম্প আছে, এত্তুন পেট্রোল লন যাইবু</t>
+  </si>
+  <si>
+    <t>সামনে কি কোনো পেট্রোল পাম্প আছে? আমার গাড়ির তেল শেষ হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>সামনে কি হনো পেট্রোল পাম্প আছে? আঁর গারির তেল শেষ অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমাদের বাস সামনের মসজিদে কিছুক্ষণ থামবে, যারা নামাজ পড়তে চান তারা পড়ে ফেলতে পারেন</t>
+  </si>
+  <si>
+    <t>আঁরার বাস সামনুর মসজিদুত হতক্ষন থিয়েইবু, যারা নামাজ ফইত্তো চন ইতারা ফরি ফেলাইত ফারিবে</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম থেকে সিলেট অনেক দূরে, আমরা কাছে কোথাও যাই</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম উত্তুন সিলেট বত দূরে, আঁরা হাছে হনোমিক্কে যাই</t>
+  </si>
+  <si>
+    <t>আমাদের আরও দুজন বাকি আছে, ওরা পটিয়া থেকে উঠবে</t>
+  </si>
+  <si>
+    <t>আরাত্তুন আরো দুইজন বাকি আছে, ইতারা পটিয়েত্তুন উডিবু</t>
+  </si>
+  <si>
+    <t>মনে করে চার্জার আর পাওয়ার ব্যাংক নিও, ওখানে চার্জ দেওয়ার ব্যবস্থা নেই</t>
+  </si>
+  <si>
+    <t>মনোত গরি চার্জার আর পাওয়ার ব্যাংক লইয়্যু, এনডে চার্জ দিবের ব্যবস্থা নেই</t>
+  </si>
+  <si>
+    <t>আমরা যেখানে যাচ্ছি সেখানে নেটওয়ার্কে অনেক সমস্যা হয়</t>
+  </si>
+  <si>
+    <t>আঁরা যেনডে যাইর এনডে নেটওয়ার্ক উত বত সমস্যা অয়</t>
+  </si>
+  <si>
+    <t>অনেক বেশি জার্নি হয়ে গেছে, আজকের দিনটা রেস্ট নিতে হবে</t>
+  </si>
+  <si>
+    <t>বত বেশি জার্নি অই গেইয়্যি, আজিয়ের দিন ইয়েন রেস্ট লন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমরা যতটা মনে করেছিলাম এটা তার থেকেও অনেক বেশি দূরে</t>
+  </si>
+  <si>
+    <t>আঁরা যেরহম মনে গইজ্জিলাম ইয়েন ইয়াত্তুনও বত বেশি দুরে</t>
+  </si>
+  <si>
+    <t>ভাই, সামনে রাস্তা ভাঙা, গাড়ি আর সামনে যেতে পারবে না</t>
+  </si>
+  <si>
+    <t>বদ্দা, সামনে রাস্তা ভাঙা, গারি আর সামনে যাইত ন ফারিবু</t>
+  </si>
+  <si>
+    <t>আপনাদের এখান থেকে সামনের পথটা হেঁটেই যেতে হবে</t>
+  </si>
+  <si>
+    <t>অঁনেরাত্তুন এনডেত্তুন সামনুর পথ ইয়েন আডিই যন ফরিবু</t>
+  </si>
+  <si>
+    <t>সামনে কিছুদূর হাঁটলে আপনারা আপনাদের হোটেলে পৌঁছে যাবেন</t>
+  </si>
+  <si>
+    <t>সামনে হদ্দুর আডিলি অঁনেরা অঁনেরার হোটেলুত পৌছি যাইবেন</t>
+  </si>
+  <si>
+    <t>সামনে একজন মানুষ দেখতে পাচ্ছি, চল উনার কাছ থেকেই জিজ্ঞেস করি</t>
+  </si>
+  <si>
+    <t>সামনে উজ্ঞো মানুষ দেহির, চল ইবেত্তুনই ফুসর লই</t>
+  </si>
+  <si>
+    <t>আরেকটু কষ্ট করে হাঁটো, আমরা কাছাকাছি চলে এসেছি</t>
+  </si>
+  <si>
+    <t>আরেক্কানা হষ্ট গরি আডো, আঁরা হাছাহাছি চলি আইসসি</t>
+  </si>
+  <si>
+    <t>আমার নাম রফিক, আমি এই গ্রামে বেড়াতে এসেছি। তুমি কি আমাকে এই গ্রামটা ঘুরে দেখাবে?</t>
+  </si>
+  <si>
+    <t>আঁর নাম রফিক, আঁই এই গ্রামুত বেরাইতাম আইসসি। তুঁই কি আঁরে এই গ্রাম ইয়েন ঘুরি দেহাইবে?</t>
+  </si>
+  <si>
+    <t>গত বছরের মতো এবারও আমরা সমুদ্রপাড়ে গিয়ে পিকনিক করব</t>
+  </si>
+  <si>
+    <t>গত বছরুর মতন এবারও আঁরা সমুদ্রা ফারুত যাই পিকনিক গইজ্জুম</t>
+  </si>
+  <si>
+    <t>বাস কি সামনের স্টেশনে থামবে? নামাজের সময় হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>বাস কি সামনুর স্টেশনুত থামিবু? নামাজুর সময় অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>ভাই, আসেন আমাদের বাসে উঠেন, আমাদের বাসে নামাজ পড়ার সুবিধা আছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, আইয়্যুন আঁরার বাসুত উডোন, আঁরার বাসুত নামাজ ফরিবের সুবিধে আছে</t>
+  </si>
+  <si>
+    <t>আমরা নতুন ব্রিজ দিয়ে না গিয়ে টানেল দিয়ে যাব</t>
+  </si>
+  <si>
+    <t>আঁরা নতুন ব্রিজ দি ন যাই টানেল দি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>সিএনজি নিয়ে মুরাদপুর থেকে নিউ মার্কেটে গেলে ভাড়া কত পড়বে?</t>
+  </si>
+  <si>
+    <t>সিএনজি লই মুরাদপুর উত্তুন নিউ মার্কেটুত গেলি ভারা হতো ফরিবু?</t>
+  </si>
+  <si>
+    <t>ট্রেনের ভেতরে আর জায়গা নেই, ছাদে উঠতে হবে</t>
+  </si>
+  <si>
+    <t>ট্রেনুর ভিতুরে আর জাগা নেই, ছাদুত উডন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমরা বাসে যাই, ট্রেনের ছাদে ওঠা ঝুঁকিপূর্ণ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আঁরা বাসুত যাই, ট্রেনুর ছাদুত উডন রিস্ক অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমার ঘুম চলে আসছিল, কখন যে ঢাকায় পৌঁছে গেছি বুঝতেই পারিনি</t>
+  </si>
+  <si>
+    <t>আঁর ঘুম চলি আইসসিল, হত্তে যে ঢাহাত পৌছি গেই বুঝিতিই ন ফারি</t>
+  </si>
+  <si>
+    <t>মা, আমার জন্য দোয়া করিও, আজকে একটা ইন্টারভিউ দিতে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁর লাই দোয়া গইজ্জো, আজিয়ে এক্কান ইন্টারভিউ দিতাম যাইর</t>
+  </si>
+  <si>
+    <t>তানিয়ার মা নাকি অসুস্থ, তাই সে যেতে পারবে না</t>
+  </si>
+  <si>
+    <t>তানিয়ের মা বলে অসুস্থ, এতেল্লে ইতি যাইত ন ফারিবু</t>
+  </si>
+  <si>
+    <t>আমাদের গ্রুপে যারা যারা আছে সবাইকে মেসেজ দে</t>
+  </si>
+  <si>
+    <t>আঁরার গ্রুপুত যারা আছে বিয়াগুনুরে মেসেজ দে</t>
+  </si>
+  <si>
+    <t>আলিফারা সবাই যাচ্ছে, তুই যাবি না?</t>
+  </si>
+  <si>
+    <t>আলিফা তারা বিয়াজ্ঞুন যার, তুই ন যাবি?</t>
+  </si>
+  <si>
+    <t>আমার ঘোরাঘুরি ভালো লাগে না, আমার বাসায় বসে থাকতেই ভালো লাগে</t>
+  </si>
+  <si>
+    <t>আত্তুন ঘোরাঘুরি ভালা ন লাগে, আত্তুন বাসাত বই থাকতেই ভালা লাগে</t>
+  </si>
+  <si>
+    <t>পিকনিক করার জন্য একটা নিরিবিলি জায়গা খুঁজে বের কর</t>
+  </si>
+  <si>
+    <t>পিকনিক গরিবের লাই এক্কান নিরিবিলি জাগা থোওয়াই বাইর গর</t>
+  </si>
+  <si>
+    <t>আমরা সব স্কুল ফ্রেন্ড মিলে পিকনিকে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁরা বিয়াজ্ঞুন স্কুল ফ্রেন্ড মিলি পিকনিকুত যাইর</t>
+  </si>
+  <si>
+    <t>পিকনিক শেষে আমরা সমুদ্রপাড়ে সবাই মিলে ফুটবল খেলব</t>
+  </si>
+  <si>
+    <t>পিকনিক শেষে আঁরা সাগরুর ফারুত বিয়াজ্ঞুন মিলি ফটবল খেইল্লুম</t>
+  </si>
+  <si>
+    <t>সারাদিন ঘরে কেন বসে থাক, একটু বাইরে ঘুরে আসতে পার না?</t>
+  </si>
+  <si>
+    <t>আরাদিন ঘরুত কা বই থাহো, এক্কানা বাইরে ঘুরি আইত ন পারো?</t>
+  </si>
+  <si>
+    <t>তোমার বয়সে আমি বন্ধুদের নিয়ে কত ঘোরাঘুরি করেছি</t>
+  </si>
+  <si>
+    <t>তোঁয়ার বয়সুত আঁই বন্ধু অক্কল লই হতো ঘোরাঘুরি গইজ্জি</t>
+  </si>
+  <si>
+    <t>এখন বয়স হয়েছে, তাই ওভাবে ঘোরাঘুরি করা হয় না</t>
+  </si>
+  <si>
+    <t>এহন বয়স অইয়্যি, এতেল্লে ওভাবে ঘোরাঘুরি গরা ন অয়</t>
+  </si>
+  <si>
+    <t>আমি দুদিনের জন্য তোর ভাবিকে নিয়ে একটু ঘুরতে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই দুদিনুর লাই তোর ভাবিরে লই এক্কানা ঘুইত্তাম যাইর</t>
+  </si>
+  <si>
+    <t>আমাদের যদি ফিরতে দেরি হয়ে যায়, তাহলে তুই খেয়ে ঘুমিয়ে যাস</t>
+  </si>
+  <si>
+    <t>আরাত্তুন যদি ফিত্তে দেরি অই যাই, তইলি তুই হাইয়্যিরে ঘুমাই যাইস</t>
+  </si>
+  <si>
+    <t>দারোয়ানকে বলিও যেন গেট বন্ধ না করে, আমার ফিরতে একটু দেরি হবে</t>
+  </si>
+  <si>
+    <t>দারোওয়ান উরে হইয়্যো যেন গেইট বন্ধ ন গরে, আত্তুন ফিত্তে এক্কানা দেরি অইবু</t>
+  </si>
+  <si>
+    <t>আজকে অফিসে একটা গুরুত্বপূর্ণ মিটিং আছে, একটু দোয়া করিও</t>
+  </si>
+  <si>
+    <t>আজিয়ে অফিসুত এক্কান গুরুত্বপুর্ণ মিটিং আছে, এক্কানা দোয়া গইজ্জো</t>
+  </si>
+  <si>
+    <t>তুমি একটু অপেক্ষা করো, আমরা একসাথে যাব</t>
+  </si>
+  <si>
+    <t>তুঁই এক্কানা অপেক্ষা গরো, আঁরা একলগে যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>অফিস থেকে গাড়ি দিয়েছে, আজকে থেকে বাসায় আসতে আর দেরি হবে না</t>
+  </si>
+  <si>
+    <t>আফিসুত্তুন গারি দিইয়্যি, আজিয়েত্তুন বাসাত আসতে আর দেরি ন অইবু</t>
+  </si>
+  <si>
+    <t>চলো, সামনের মাসে দুবাই ঘুরে আসি, তোমার মন ভালো হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>চলো, সামনুর মাসুত দুবাই ঘুরি আয়, তোঁয়ার মন ভালা অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমরা দুবাই না গিয়ে আরও কম টাকায় অন্য কোথাও ঘুরে আসতে পারি</t>
+  </si>
+  <si>
+    <t>আঁরা দুবাই ন যাই আরও হম টিয়া দি অন্য হনোমিক্কে ঘুরি আইত ফারি</t>
+  </si>
+  <si>
+    <t>এত টাকা খরচ করে বিদেশ ঘুরতে যাওয়ার দরকার নেই, আমরা দেশে কোনো একটা সুন্দর জায়গায় ঘুরে আসতে পারি</t>
+  </si>
+  <si>
+    <t>এতো টিয়া হরচ গরি বিদেশ ঘুইত্তো যাইবের দরহার নেই, আঁরা দেশুত হনো এক্কান সুন্দর জাগাত ঘুরি আইত ফারি</t>
+  </si>
+  <si>
+    <t>আমার অফিসের একটা কাজে দেশের বাইরে যেতে হবে, তুমি একা ঘর সামলাতে পারবে তো?</t>
+  </si>
+  <si>
+    <t>আঁর অফিসুর এক্কান হাজে দেশুর বাইরে যন ফরিবু, তুঁই এহেল্লে ঘর সামলাইত ফারিবে তো?</t>
+  </si>
+  <si>
+    <t>আমরা সামনের বছর ইনশাআল্লাহ দুজন মিলে হজ করতে যাব</t>
+  </si>
+  <si>
+    <t>আঁরা সামনুর বছর ইনশাআল্লাহ দুনুজন মিলি হজ গইত্তাম যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমার একটা স্বপ্ন সৌদি আরবে গিয়ে মক্কা শরিফে হজ করা</t>
+  </si>
+  <si>
+    <t>আঁর এক্কান স্বপ্ন সৌদি আরবুত যাই মক্কা শরিফুত হজ গরন</t>
+  </si>
+  <si>
+    <t>শুনলাম তুমি নাকি ওমরাহ করতে সৌদি আরবে যাচ্ছ?</t>
+  </si>
+  <si>
+    <t>উইন্নিলাম তুঁই নাকি ওমরাহ গইত্তো সৌদি আরবুত যার?</t>
+  </si>
+  <si>
+    <t>আমার দাদার বাড়ি নোয়াখালী, এবার ঈদে আমরা সেখানে যাব</t>
+  </si>
+  <si>
+    <t>আঁর দাদার বারি নোয়াহালী, এবার ঈদুত আঁরা এনডে যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>ভাই, বাসের এসিটা অন করেন, অনেক গরম লাগছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, বাসুর এসি ইবে অন গরন, বত গরম লাগের</t>
+  </si>
+  <si>
+    <t>এবার রাজশাহী গেলে বেশি করে রাজশাহীর আম আর লিচু নিয়ে আসব</t>
+  </si>
+  <si>
+    <t>এবার রাজশাহীত গেলি বেশি গরি রাজশাহীর আম আর লেচু লই আইসসুম</t>
+  </si>
+  <si>
+    <t>রাজশাহী লিচু আর আমের জন্য বিখ্যাত</t>
+  </si>
+  <si>
+    <t>রাজশাহী লেচু আর আমুর লাই বিখ্যাত</t>
+  </si>
+  <si>
+    <t>এখন কালুরঘাট ব্রিজের কাজ চলছে, তাই আপাতত ফেরি নিয়ে নদী পার হতে হবে</t>
+  </si>
+  <si>
+    <t>এহন হালুরঘাট ব্রিজুর হাজ চলের, এতেল্লে আপাতত ফেরি লই দইজ্জে ফার অন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমার পাসপোর্ট আর সব কাগজপত্র রেডি, ভিসা আসলে চলে যাব</t>
+  </si>
+  <si>
+    <t>আঁর পাসপোর্ট আর বিয়াক হাগজপত্র রেডি, ভিসে আইলি চলি যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>স্টুডেন্ট ভিসা নিয়ে ইতালি গেলে কেমন হবে?</t>
+  </si>
+  <si>
+    <t>স্টুডেন্ট ভিসে লই ইতালি গেলি কেন অইবু</t>
+  </si>
+  <si>
+    <t>আমার ইউরোপে যাওয়ার ইচ্ছা, কোন দেশে গেলে ভালো হবে?</t>
+  </si>
+  <si>
+    <t>আত্তুন ইঊরুপুত যাইবের ইচ্ছে, হন দেশুত গেলি ভালা অইবু?</t>
+  </si>
+  <si>
+    <t>আমার ছেলে কাতারে থাকে, ওখানে ব্যবসা করে</t>
+  </si>
+  <si>
+    <t>আঁর ফোওয়া কাতারুত থাহে, এনডে ব্যবসা গরে</t>
+  </si>
+  <si>
+    <t>ভাইয়া, এবার দেশে আসার সময় আমার জন্য একটা দামি ফোন নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>ভাইয়া, এবার দেশুত আইবের সমত আঁর লাই উজ্ঞো দামি ফোন লই আইসসো</t>
+  </si>
+  <si>
+    <t>বিদেশে গেলে আমার কথা মনে থাকবে তো?</t>
+  </si>
+  <si>
+    <t>বিদেশুত গেলি আঁর হতা মনুত থাহিবু তো?</t>
+  </si>
+  <si>
+    <t>এবার কি কুতুবদিয়া ওরশে যাবি?</t>
+  </si>
+  <si>
+    <t>এবার কি কুতুবদিয়ে ওরশত যাবি?</t>
+  </si>
+  <si>
+    <t>কুতুবদিয়া যেতে চাইলে নৌকা নিয়ে যেতে হবে, যেটা অনেক ঝুঁকিপূর্ণ</t>
+  </si>
+  <si>
+    <t>কুতুবদিয়ে যেতু চাইলি নৌকো লই যন ফরিবু, যিয়েন বত রিস্ক</t>
+  </si>
+  <si>
+    <t>এখন সমুদ্র উত্তাল, অনেক বড় বড় ঢেউ উঠছে</t>
+  </si>
+  <si>
+    <t>এহন সাগর গরম, বত বরো বরো ঢেউ উডের</t>
+  </si>
+  <si>
+    <t>প্রতিবছর কুতুবদিয়া যাওয়ার সময় নৌকা ডুবে মানুষ মারা যায়</t>
+  </si>
+  <si>
+    <t>ফইত্তো বছর কুতুবদিয়ে যাইবের সমত নৌকো ডুফি মানুষ মরি যায়</t>
+  </si>
+  <si>
+    <t>শুনলাম যারা সমুদ্রে মাছ ধরতে যায়, তাদেরকে অনেক সময় ডাকাতের কবলে পড়তে হয়</t>
+  </si>
+  <si>
+    <t>উইন্নি যারা সাগরুত মাছ ধইত্তো যায়, ইতারারে বত সময় ডাহাইতুর কবল উত ফরন ফরে</t>
+  </si>
+  <si>
+    <t>এখন বর্ষাকাল, তাই বান্দরবানের পাহাড়ে না গেলে ভালো হবে</t>
+  </si>
+  <si>
+    <t>এহন বর্ষাহাল, এতেল্লে বান্দরবন ফারুত ন যাইলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>একবার পাহাড়ে উঠতে গিয়ে হোঁচট খেয়ে পড়ে গিয়েছিলাম</t>
+  </si>
+  <si>
+    <t>একবার ফারুত উইটতু যাই উচট হায় ফরি গেইলাম</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম বিশ্ববিদ্যালয়ের পাহাড়ে অনেক সাপ আছে, আমরা যখন ওখানে ঘুরতে গিয়েছিলাম তখন শুনেছিলাম</t>
+  </si>
+  <si>
+    <t>চট্টগ্রাম বিশ্ববিদ্যালয়ুর ফারুত বত আফ আছে, আঁরা যহন এনডে ঘুইত্তো গেইলাম তহন উইন্নিলাম</t>
   </si>
 </sst>
 </file>
@@ -18188,455 +18707,801 @@
       <c r="A1202" s="2" t="s">
         <v>2396</v>
       </c>
-      <c r="B1202" s="2"/>
+      <c r="B1202" s="2" t="s">
+        <v>2397</v>
+      </c>
     </row>
     <row r="1203" ht="25" customHeight="1" spans="1:2">
       <c r="A1203" s="2" t="s">
-        <v>2397</v>
-      </c>
-      <c r="B1203" s="2"/>
+        <v>2398</v>
+      </c>
+      <c r="B1203" s="2" t="s">
+        <v>2399</v>
+      </c>
     </row>
     <row r="1204" ht="25" customHeight="1" spans="1:2">
       <c r="A1204" s="2" t="s">
-        <v>2398</v>
-      </c>
-      <c r="B1204" s="2"/>
+        <v>2400</v>
+      </c>
+      <c r="B1204" s="2" t="s">
+        <v>2401</v>
+      </c>
     </row>
     <row r="1205" ht="25" customHeight="1" spans="1:2">
       <c r="A1205" s="2" t="s">
-        <v>2399</v>
-      </c>
-      <c r="B1205" s="2"/>
+        <v>2402</v>
+      </c>
+      <c r="B1205" s="2" t="s">
+        <v>2403</v>
+      </c>
     </row>
     <row r="1206" ht="25" customHeight="1" spans="1:2">
       <c r="A1206" s="2" t="s">
-        <v>2400</v>
-      </c>
-      <c r="B1206" s="2"/>
+        <v>2404</v>
+      </c>
+      <c r="B1206" s="2" t="s">
+        <v>2405</v>
+      </c>
     </row>
     <row r="1207" ht="25" customHeight="1" spans="1:2">
       <c r="A1207" s="2" t="s">
-        <v>2401</v>
-      </c>
-      <c r="B1207" s="2"/>
+        <v>2406</v>
+      </c>
+      <c r="B1207" s="2" t="s">
+        <v>2407</v>
+      </c>
     </row>
     <row r="1208" ht="25" customHeight="1" spans="1:2">
       <c r="A1208" s="2" t="s">
-        <v>2402</v>
-      </c>
-      <c r="B1208" s="2"/>
+        <v>2408</v>
+      </c>
+      <c r="B1208" s="2" t="s">
+        <v>2409</v>
+      </c>
     </row>
     <row r="1209" ht="25" customHeight="1" spans="1:2">
       <c r="A1209" s="2" t="s">
-        <v>2403</v>
-      </c>
-      <c r="B1209" s="2"/>
+        <v>2410</v>
+      </c>
+      <c r="B1209" s="2" t="s">
+        <v>2411</v>
+      </c>
     </row>
     <row r="1210" ht="25" customHeight="1" spans="1:2">
       <c r="A1210" s="2" t="s">
-        <v>2404</v>
-      </c>
-      <c r="B1210" s="2"/>
+        <v>2412</v>
+      </c>
+      <c r="B1210" s="2" t="s">
+        <v>2413</v>
+      </c>
     </row>
     <row r="1211" ht="25" customHeight="1" spans="1:2">
       <c r="A1211" s="2" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B1211" s="2"/>
+        <v>2414</v>
+      </c>
+      <c r="B1211" s="2" t="s">
+        <v>2415</v>
+      </c>
     </row>
     <row r="1212" ht="25" customHeight="1" spans="1:2">
       <c r="A1212" s="2" t="s">
-        <v>2406</v>
-      </c>
-      <c r="B1212" s="2"/>
+        <v>2416</v>
+      </c>
+      <c r="B1212" s="2" t="s">
+        <v>2417</v>
+      </c>
     </row>
     <row r="1213" ht="25" customHeight="1" spans="1:2">
       <c r="A1213" s="2" t="s">
-        <v>2407</v>
-      </c>
-      <c r="B1213" s="2"/>
+        <v>2418</v>
+      </c>
+      <c r="B1213" s="2" t="s">
+        <v>2419</v>
+      </c>
     </row>
     <row r="1214" ht="25" customHeight="1" spans="1:2">
       <c r="A1214" s="2" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B1214" s="2"/>
+        <v>2420</v>
+      </c>
+      <c r="B1214" s="2" t="s">
+        <v>2421</v>
+      </c>
     </row>
     <row r="1215" ht="25" customHeight="1" spans="1:2">
       <c r="A1215" s="2" t="s">
-        <v>2409</v>
-      </c>
-      <c r="B1215" s="2"/>
+        <v>2422</v>
+      </c>
+      <c r="B1215" s="2" t="s">
+        <v>2423</v>
+      </c>
     </row>
     <row r="1216" ht="25" customHeight="1" spans="1:2">
       <c r="A1216" s="2" t="s">
-        <v>2410</v>
-      </c>
-      <c r="B1216" s="2"/>
+        <v>2424</v>
+      </c>
+      <c r="B1216" s="2" t="s">
+        <v>2425</v>
+      </c>
     </row>
     <row r="1217" ht="25" customHeight="1" spans="1:2">
       <c r="A1217" s="2" t="s">
-        <v>2411</v>
-      </c>
-      <c r="B1217" s="2"/>
+        <v>2426</v>
+      </c>
+      <c r="B1217" s="2" t="s">
+        <v>2427</v>
+      </c>
     </row>
     <row r="1218" ht="25" customHeight="1" spans="1:2">
       <c r="A1218" s="2" t="s">
-        <v>2412</v>
-      </c>
-      <c r="B1218" s="2"/>
+        <v>2428</v>
+      </c>
+      <c r="B1218" s="2" t="s">
+        <v>2429</v>
+      </c>
     </row>
     <row r="1219" ht="25" customHeight="1" spans="1:2">
       <c r="A1219" s="2" t="s">
-        <v>2413</v>
-      </c>
-      <c r="B1219" s="2"/>
+        <v>2430</v>
+      </c>
+      <c r="B1219" s="2" t="s">
+        <v>2431</v>
+      </c>
     </row>
     <row r="1220" ht="25" customHeight="1" spans="1:2">
       <c r="A1220" s="2" t="s">
-        <v>2414</v>
-      </c>
-      <c r="B1220" s="2"/>
+        <v>2432</v>
+      </c>
+      <c r="B1220" s="2" t="s">
+        <v>2433</v>
+      </c>
     </row>
     <row r="1221" ht="25" customHeight="1" spans="1:2">
       <c r="A1221" s="2" t="s">
-        <v>2415</v>
-      </c>
-      <c r="B1221" s="2"/>
+        <v>2434</v>
+      </c>
+      <c r="B1221" s="2" t="s">
+        <v>2435</v>
+      </c>
     </row>
     <row r="1222" ht="25" customHeight="1" spans="1:2">
       <c r="A1222" s="2" t="s">
-        <v>2416</v>
-      </c>
-      <c r="B1222" s="2"/>
+        <v>2436</v>
+      </c>
+      <c r="B1222" s="2" t="s">
+        <v>2437</v>
+      </c>
     </row>
     <row r="1223" ht="25" customHeight="1" spans="1:2">
       <c r="A1223" s="2" t="s">
-        <v>2417</v>
-      </c>
-      <c r="B1223" s="2"/>
+        <v>2438</v>
+      </c>
+      <c r="B1223" s="2" t="s">
+        <v>2439</v>
+      </c>
     </row>
     <row r="1224" ht="25" customHeight="1" spans="1:2">
       <c r="A1224" s="2" t="s">
-        <v>2418</v>
-      </c>
-      <c r="B1224" s="2"/>
+        <v>2440</v>
+      </c>
+      <c r="B1224" s="2" t="s">
+        <v>2441</v>
+      </c>
     </row>
     <row r="1225" ht="25" customHeight="1" spans="1:2">
       <c r="A1225" s="2" t="s">
-        <v>2419</v>
-      </c>
-      <c r="B1225" s="2"/>
+        <v>2442</v>
+      </c>
+      <c r="B1225" s="2" t="s">
+        <v>2443</v>
+      </c>
     </row>
     <row r="1226" ht="25" customHeight="1" spans="1:2">
       <c r="A1226" s="2" t="s">
-        <v>2420</v>
-      </c>
-      <c r="B1226" s="2"/>
+        <v>2444</v>
+      </c>
+      <c r="B1226" s="2" t="s">
+        <v>2445</v>
+      </c>
     </row>
     <row r="1227" ht="25" customHeight="1" spans="1:2">
       <c r="A1227" s="2" t="s">
-        <v>2421</v>
-      </c>
-      <c r="B1227" s="2"/>
+        <v>2446</v>
+      </c>
+      <c r="B1227" s="2" t="s">
+        <v>2447</v>
+      </c>
     </row>
     <row r="1228" ht="25" customHeight="1" spans="1:2">
       <c r="A1228" s="2" t="s">
-        <v>2422</v>
-      </c>
-      <c r="B1228" s="2"/>
+        <v>2448</v>
+      </c>
+      <c r="B1228" s="2" t="s">
+        <v>2449</v>
+      </c>
     </row>
     <row r="1229" ht="25" customHeight="1" spans="1:2">
-      <c r="A1229" s="2"/>
-      <c r="B1229" s="2"/>
+      <c r="A1229" s="2" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B1229" s="2" t="s">
+        <v>2451</v>
+      </c>
     </row>
     <row r="1230" ht="25" customHeight="1" spans="1:2">
-      <c r="A1230" s="2"/>
-      <c r="B1230" s="2"/>
+      <c r="A1230" s="2" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1230" s="2" t="s">
+        <v>2453</v>
+      </c>
     </row>
     <row r="1231" ht="25" customHeight="1" spans="1:2">
-      <c r="A1231" s="2"/>
-      <c r="B1231" s="2"/>
+      <c r="A1231" s="2" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1231" s="2" t="s">
+        <v>2455</v>
+      </c>
     </row>
     <row r="1232" ht="25" customHeight="1" spans="1:2">
-      <c r="A1232" s="2"/>
-      <c r="B1232" s="2"/>
+      <c r="A1232" s="2" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B1232" s="2" t="s">
+        <v>2457</v>
+      </c>
     </row>
     <row r="1233" ht="25" customHeight="1" spans="1:2">
-      <c r="A1233" s="2"/>
-      <c r="B1233" s="2"/>
+      <c r="A1233" s="2" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B1233" s="2" t="s">
+        <v>2459</v>
+      </c>
     </row>
     <row r="1234" ht="25" customHeight="1" spans="1:2">
-      <c r="A1234" s="2"/>
-      <c r="B1234" s="2"/>
+      <c r="A1234" s="2" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B1234" s="2" t="s">
+        <v>2461</v>
+      </c>
     </row>
     <row r="1235" ht="25" customHeight="1" spans="1:2">
-      <c r="A1235" s="2"/>
-      <c r="B1235" s="2"/>
+      <c r="A1235" s="2" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B1235" s="2" t="s">
+        <v>2463</v>
+      </c>
     </row>
     <row r="1236" ht="25" customHeight="1" spans="1:2">
-      <c r="A1236" s="2"/>
-      <c r="B1236" s="2"/>
+      <c r="A1236" s="2" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B1236" s="2" t="s">
+        <v>2465</v>
+      </c>
     </row>
     <row r="1237" ht="25" customHeight="1" spans="1:2">
-      <c r="A1237" s="2"/>
-      <c r="B1237" s="2"/>
+      <c r="A1237" s="2" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B1237" s="2" t="s">
+        <v>2467</v>
+      </c>
     </row>
     <row r="1238" ht="25" customHeight="1" spans="1:2">
-      <c r="A1238" s="2"/>
-      <c r="B1238" s="2"/>
+      <c r="A1238" s="2" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B1238" s="2" t="s">
+        <v>2469</v>
+      </c>
     </row>
     <row r="1239" ht="25" customHeight="1" spans="1:2">
-      <c r="A1239" s="2"/>
-      <c r="B1239" s="2"/>
+      <c r="A1239" s="2" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B1239" s="2" t="s">
+        <v>2471</v>
+      </c>
     </row>
     <row r="1240" ht="25" customHeight="1" spans="1:2">
-      <c r="A1240" s="2"/>
-      <c r="B1240" s="2"/>
+      <c r="A1240" s="2" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B1240" s="2" t="s">
+        <v>2473</v>
+      </c>
     </row>
     <row r="1241" ht="25" customHeight="1" spans="1:2">
-      <c r="A1241" s="2"/>
-      <c r="B1241" s="2"/>
+      <c r="A1241" s="2" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B1241" s="2" t="s">
+        <v>2475</v>
+      </c>
     </row>
     <row r="1242" ht="25" customHeight="1" spans="1:2">
-      <c r="A1242" s="2"/>
-      <c r="B1242" s="2"/>
+      <c r="A1242" s="2" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B1242" s="2" t="s">
+        <v>2477</v>
+      </c>
     </row>
     <row r="1243" ht="25" customHeight="1" spans="1:2">
-      <c r="A1243" s="2"/>
-      <c r="B1243" s="2"/>
+      <c r="A1243" s="2" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B1243" s="2" t="s">
+        <v>2479</v>
+      </c>
     </row>
     <row r="1244" ht="25" customHeight="1" spans="1:2">
-      <c r="A1244" s="2"/>
-      <c r="B1244" s="2"/>
+      <c r="A1244" s="2" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B1244" s="2" t="s">
+        <v>2481</v>
+      </c>
     </row>
     <row r="1245" ht="25" customHeight="1" spans="1:2">
-      <c r="A1245" s="2"/>
-      <c r="B1245" s="2"/>
+      <c r="A1245" s="2" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B1245" s="2" t="s">
+        <v>2483</v>
+      </c>
     </row>
     <row r="1246" ht="25" customHeight="1" spans="1:2">
-      <c r="A1246" s="2"/>
-      <c r="B1246" s="2"/>
+      <c r="A1246" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B1246" s="2" t="s">
+        <v>2485</v>
+      </c>
     </row>
     <row r="1247" ht="25" customHeight="1" spans="1:2">
-      <c r="A1247" s="2"/>
-      <c r="B1247" s="2"/>
+      <c r="A1247" s="2" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B1247" s="2" t="s">
+        <v>2487</v>
+      </c>
     </row>
     <row r="1248" ht="25" customHeight="1" spans="1:2">
-      <c r="A1248" s="2"/>
-      <c r="B1248" s="2"/>
+      <c r="A1248" s="2" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B1248" s="2" t="s">
+        <v>2489</v>
+      </c>
     </row>
     <row r="1249" ht="25" customHeight="1" spans="1:2">
-      <c r="A1249" s="2"/>
-      <c r="B1249" s="2"/>
+      <c r="A1249" s="2" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B1249" s="2" t="s">
+        <v>2491</v>
+      </c>
     </row>
     <row r="1250" ht="25" customHeight="1" spans="1:2">
-      <c r="A1250" s="2"/>
-      <c r="B1250" s="2"/>
+      <c r="A1250" s="2" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B1250" s="2" t="s">
+        <v>2493</v>
+      </c>
     </row>
     <row r="1251" ht="25" customHeight="1" spans="1:2">
-      <c r="A1251" s="2"/>
-      <c r="B1251" s="2"/>
+      <c r="A1251" s="2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B1251" s="2" t="s">
+        <v>2495</v>
+      </c>
     </row>
     <row r="1252" ht="25" customHeight="1" spans="1:2">
-      <c r="A1252" s="2"/>
-      <c r="B1252" s="2"/>
+      <c r="A1252" s="2" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B1252" s="2" t="s">
+        <v>2497</v>
+      </c>
     </row>
     <row r="1253" ht="25" customHeight="1" spans="1:2">
-      <c r="A1253" s="2"/>
-      <c r="B1253" s="2"/>
+      <c r="A1253" s="2" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B1253" s="2" t="s">
+        <v>2499</v>
+      </c>
     </row>
     <row r="1254" ht="25" customHeight="1" spans="1:2">
-      <c r="A1254" s="2"/>
-      <c r="B1254" s="2"/>
+      <c r="A1254" s="2" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B1254" s="2" t="s">
+        <v>2501</v>
+      </c>
     </row>
     <row r="1255" ht="25" customHeight="1" spans="1:2">
-      <c r="A1255" s="2"/>
-      <c r="B1255" s="2"/>
+      <c r="A1255" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B1255" s="2" t="s">
+        <v>2503</v>
+      </c>
     </row>
     <row r="1256" ht="25" customHeight="1" spans="1:2">
-      <c r="A1256" s="2"/>
-      <c r="B1256" s="2"/>
+      <c r="A1256" s="2" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B1256" s="2" t="s">
+        <v>2505</v>
+      </c>
     </row>
     <row r="1257" ht="25" customHeight="1" spans="1:2">
-      <c r="A1257" s="2"/>
-      <c r="B1257" s="2"/>
+      <c r="A1257" s="2" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B1257" s="2" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="1258" ht="25" customHeight="1" spans="1:2">
-      <c r="A1258" s="2"/>
-      <c r="B1258" s="2"/>
+      <c r="A1258" s="2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B1258" s="2" t="s">
+        <v>2509</v>
+      </c>
     </row>
     <row r="1259" ht="25" customHeight="1" spans="1:2">
-      <c r="A1259" s="2"/>
-      <c r="B1259" s="2"/>
+      <c r="A1259" s="2" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B1259" s="2" t="s">
+        <v>2511</v>
+      </c>
     </row>
     <row r="1260" ht="25" customHeight="1" spans="1:2">
-      <c r="A1260" s="2"/>
-      <c r="B1260" s="2"/>
+      <c r="A1260" s="2" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B1260" s="2" t="s">
+        <v>2513</v>
+      </c>
     </row>
     <row r="1261" ht="25" customHeight="1" spans="1:2">
-      <c r="A1261" s="2"/>
-      <c r="B1261" s="2"/>
+      <c r="A1261" s="2" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B1261" s="2" t="s">
+        <v>2515</v>
+      </c>
     </row>
     <row r="1262" ht="25" customHeight="1" spans="1:2">
-      <c r="A1262" s="2"/>
-      <c r="B1262" s="2"/>
+      <c r="A1262" s="2" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B1262" s="2" t="s">
+        <v>2517</v>
+      </c>
     </row>
     <row r="1263" ht="25" customHeight="1" spans="1:2">
-      <c r="A1263" s="2"/>
-      <c r="B1263" s="2"/>
+      <c r="A1263" s="2" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B1263" s="2" t="s">
+        <v>2519</v>
+      </c>
     </row>
     <row r="1264" ht="25" customHeight="1" spans="1:2">
-      <c r="A1264" s="2"/>
-      <c r="B1264" s="2"/>
+      <c r="A1264" s="2" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B1264" s="2" t="s">
+        <v>2521</v>
+      </c>
     </row>
     <row r="1265" ht="25" customHeight="1" spans="1:2">
-      <c r="A1265" s="2"/>
-      <c r="B1265" s="2"/>
+      <c r="A1265" s="2" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B1265" s="2" t="s">
+        <v>2523</v>
+      </c>
     </row>
     <row r="1266" ht="25" customHeight="1" spans="1:2">
-      <c r="A1266" s="2"/>
-      <c r="B1266" s="2"/>
+      <c r="A1266" s="2" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B1266" s="2" t="s">
+        <v>2525</v>
+      </c>
     </row>
     <row r="1267" ht="25" customHeight="1" spans="1:2">
-      <c r="A1267" s="2"/>
-      <c r="B1267" s="2"/>
+      <c r="A1267" s="2" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B1267" s="2" t="s">
+        <v>2527</v>
+      </c>
     </row>
     <row r="1268" ht="25" customHeight="1" spans="1:2">
-      <c r="A1268" s="2"/>
-      <c r="B1268" s="2"/>
+      <c r="A1268" s="2" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B1268" s="2" t="s">
+        <v>2529</v>
+      </c>
     </row>
     <row r="1269" ht="25" customHeight="1" spans="1:2">
-      <c r="A1269" s="2"/>
-      <c r="B1269" s="2"/>
+      <c r="A1269" s="2" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B1269" s="2" t="s">
+        <v>2531</v>
+      </c>
     </row>
     <row r="1270" ht="25" customHeight="1" spans="1:2">
-      <c r="A1270" s="2"/>
-      <c r="B1270" s="2"/>
+      <c r="A1270" s="2" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B1270" s="2" t="s">
+        <v>2533</v>
+      </c>
     </row>
     <row r="1271" ht="25" customHeight="1" spans="1:2">
-      <c r="A1271" s="2"/>
-      <c r="B1271" s="2"/>
+      <c r="A1271" s="2" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B1271" s="2" t="s">
+        <v>2535</v>
+      </c>
     </row>
     <row r="1272" ht="25" customHeight="1" spans="1:2">
-      <c r="A1272" s="2"/>
-      <c r="B1272" s="2"/>
+      <c r="A1272" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B1272" s="2" t="s">
+        <v>2537</v>
+      </c>
     </row>
     <row r="1273" ht="25" customHeight="1" spans="1:2">
-      <c r="A1273" s="2"/>
-      <c r="B1273" s="2"/>
+      <c r="A1273" s="2" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B1273" s="2" t="s">
+        <v>2539</v>
+      </c>
     </row>
     <row r="1274" ht="25" customHeight="1" spans="1:2">
-      <c r="A1274" s="2"/>
-      <c r="B1274" s="2"/>
+      <c r="A1274" s="2" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B1274" s="2" t="s">
+        <v>2541</v>
+      </c>
     </row>
     <row r="1275" ht="25" customHeight="1" spans="1:2">
-      <c r="A1275" s="2"/>
-      <c r="B1275" s="2"/>
+      <c r="A1275" s="2" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B1275" s="2" t="s">
+        <v>2543</v>
+      </c>
     </row>
     <row r="1276" ht="25" customHeight="1" spans="1:2">
-      <c r="A1276" s="2"/>
-      <c r="B1276" s="2"/>
+      <c r="A1276" s="2" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B1276" s="2" t="s">
+        <v>2545</v>
+      </c>
     </row>
     <row r="1277" ht="25" customHeight="1" spans="1:2">
-      <c r="A1277" s="2"/>
-      <c r="B1277" s="2"/>
+      <c r="A1277" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B1277" s="2" t="s">
+        <v>2547</v>
+      </c>
     </row>
     <row r="1278" ht="25" customHeight="1" spans="1:2">
-      <c r="A1278" s="2"/>
-      <c r="B1278" s="2"/>
+      <c r="A1278" s="2" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B1278" s="2" t="s">
+        <v>2549</v>
+      </c>
     </row>
     <row r="1279" ht="25" customHeight="1" spans="1:2">
-      <c r="A1279" s="2"/>
-      <c r="B1279" s="2"/>
+      <c r="A1279" s="2" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B1279" s="2" t="s">
+        <v>2551</v>
+      </c>
     </row>
     <row r="1280" ht="25" customHeight="1" spans="1:2">
-      <c r="A1280" s="2"/>
-      <c r="B1280" s="2"/>
+      <c r="A1280" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B1280" s="2" t="s">
+        <v>2553</v>
+      </c>
     </row>
     <row r="1281" ht="25" customHeight="1" spans="1:2">
-      <c r="A1281" s="2"/>
-      <c r="B1281" s="2"/>
+      <c r="A1281" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B1281" s="2" t="s">
+        <v>2555</v>
+      </c>
     </row>
     <row r="1282" ht="25" customHeight="1" spans="1:2">
-      <c r="A1282" s="2"/>
-      <c r="B1282" s="2"/>
+      <c r="A1282" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B1282" s="2" t="s">
+        <v>2557</v>
+      </c>
     </row>
     <row r="1283" ht="25" customHeight="1" spans="1:2">
-      <c r="A1283" s="2"/>
-      <c r="B1283" s="2"/>
+      <c r="A1283" s="2" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B1283" s="2" t="s">
+        <v>2559</v>
+      </c>
     </row>
     <row r="1284" ht="25" customHeight="1" spans="1:2">
-      <c r="A1284" s="2"/>
-      <c r="B1284" s="2"/>
+      <c r="A1284" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B1284" s="2" t="s">
+        <v>2561</v>
+      </c>
     </row>
     <row r="1285" ht="25" customHeight="1" spans="1:2">
-      <c r="A1285" s="2"/>
-      <c r="B1285" s="2"/>
+      <c r="A1285" s="2" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B1285" s="2" t="s">
+        <v>2563</v>
+      </c>
     </row>
     <row r="1286" ht="25" customHeight="1" spans="1:2">
-      <c r="A1286" s="2"/>
-      <c r="B1286" s="2"/>
+      <c r="A1286" s="2" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B1286" s="2" t="s">
+        <v>2565</v>
+      </c>
     </row>
     <row r="1287" ht="25" customHeight="1" spans="1:2">
-      <c r="A1287" s="2"/>
-      <c r="B1287" s="2"/>
+      <c r="A1287" s="2" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B1287" s="2" t="s">
+        <v>2567</v>
+      </c>
     </row>
     <row r="1288" ht="25" customHeight="1" spans="1:2">
-      <c r="A1288" s="2"/>
-      <c r="B1288" s="2"/>
+      <c r="A1288" s="2" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B1288" s="2" t="s">
+        <v>2569</v>
+      </c>
     </row>
     <row r="1289" ht="25" customHeight="1" spans="1:2">
-      <c r="A1289" s="2"/>
-      <c r="B1289" s="2"/>
+      <c r="A1289" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B1289" s="2" t="s">
+        <v>2571</v>
+      </c>
     </row>
     <row r="1290" ht="25" customHeight="1" spans="1:2">
-      <c r="A1290" s="2"/>
-      <c r="B1290" s="2"/>
+      <c r="A1290" s="2" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B1290" s="2" t="s">
+        <v>2573</v>
+      </c>
     </row>
     <row r="1291" ht="25" customHeight="1" spans="1:2">
-      <c r="A1291" s="2"/>
-      <c r="B1291" s="2"/>
+      <c r="A1291" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B1291" s="2" t="s">
+        <v>2575</v>
+      </c>
     </row>
     <row r="1292" ht="25" customHeight="1" spans="1:2">
-      <c r="A1292" s="2"/>
-      <c r="B1292" s="2"/>
+      <c r="A1292" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B1292" s="2" t="s">
+        <v>2577</v>
+      </c>
     </row>
     <row r="1293" ht="25" customHeight="1" spans="1:2">
-      <c r="A1293" s="2"/>
-      <c r="B1293" s="2"/>
+      <c r="A1293" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B1293" s="2" t="s">
+        <v>2579</v>
+      </c>
     </row>
     <row r="1294" ht="25" customHeight="1" spans="1:2">
-      <c r="A1294" s="2"/>
-      <c r="B1294" s="2"/>
+      <c r="A1294" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B1294" s="2" t="s">
+        <v>2581</v>
+      </c>
     </row>
     <row r="1295" ht="25" customHeight="1" spans="1:2">
-      <c r="A1295" s="2"/>
-      <c r="B1295" s="2"/>
+      <c r="A1295" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B1295" s="2" t="s">
+        <v>2583</v>
+      </c>
     </row>
     <row r="1296" ht="25" customHeight="1" spans="1:2">
-      <c r="A1296" s="2"/>
-      <c r="B1296" s="2"/>
+      <c r="A1296" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B1296" s="2" t="s">
+        <v>2585</v>
+      </c>
     </row>
     <row r="1297" ht="25" customHeight="1" spans="1:2">
-      <c r="A1297" s="2"/>
-      <c r="B1297" s="2"/>
+      <c r="A1297" s="2" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B1297" s="2" t="s">
+        <v>2587</v>
+      </c>
     </row>
     <row r="1298" ht="25" customHeight="1" spans="1:2">
-      <c r="A1298" s="2"/>
-      <c r="B1298" s="2"/>
+      <c r="A1298" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B1298" s="2" t="s">
+        <v>2589</v>
+      </c>
     </row>
     <row r="1299" ht="25" customHeight="1" spans="1:2">
-      <c r="A1299" s="2"/>
-      <c r="B1299" s="2"/>
+      <c r="A1299" s="2" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B1299" s="2" t="s">
+        <v>2591</v>
+      </c>
     </row>
     <row r="1300" ht="25" customHeight="1" spans="1:2">
-      <c r="A1300" s="2"/>
-      <c r="B1300" s="2"/>
+      <c r="A1300" s="2" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B1300" s="2" t="s">
+        <v>2593</v>
+      </c>
     </row>
     <row r="1301" ht="25" customHeight="1" spans="1:2">
-      <c r="A1301" s="2"/>
-      <c r="B1301" s="2"/>
+      <c r="A1301" s="2" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B1301" s="2" t="s">
+        <v>2595</v>
+      </c>
     </row>
     <row r="1302" ht="25" customHeight="1" spans="1:2">
       <c r="A1302" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="2596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="3196">
   <si>
     <t>bangla</t>
   </si>
@@ -371,7 +371,7 @@
     <t>আশা করি খুব শীঘ্রই আবার দেখা হবে, ভালো থাকবেন</t>
   </si>
   <si>
-    <t xml:space="preserve">আশা গরি বত জলদি আবার দেহা অইবু, ভালা থাইক্কুন </t>
+    <t>আশা গরি বত জলদি আবার দেহা অইবু, ভালা থাইক্কুন</t>
   </si>
   <si>
     <t>দিনকাল কেমন যাচ্ছে? সবকিছু ঠিকাছে?</t>
@@ -398,10 +398,10 @@
     <t>অঁনোরে বতদিন নো দেহি, এতোদিন হনডে আছিলেন?</t>
   </si>
   <si>
-    <t xml:space="preserve">কিরে বন্ধু! কি হয়েছে তুর? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">কিরে বন্ধু! কি অইয়্যিদে তুর? </t>
+    <t>কিরে বন্ধু! কি হয়েছে তুর?</t>
+  </si>
+  <si>
+    <t>কিরে বন্ধু! কি অইয়্যিদে তুর?</t>
   </si>
   <si>
     <t>তোকে দেখে অসুস্থ মনে হচ্ছে</t>
@@ -1233,7 +1233,7 @@
     <t>আমি বাজার করতে যাচ্ছি ভাই, তুই কোথায় যাচ্ছিস?</t>
   </si>
   <si>
-    <t>আই বাজার গইত্তাম যাইর বদ্দা, তুই হনডে যোর?</t>
+    <t>আঁই বাজার গইত্তাম যাইর বদ্দা, তুই হনডে যোর?</t>
   </si>
   <si>
     <t>যাওয়ার সময় আলিয়াকেও সাথে নিয়ে যেও</t>
@@ -1503,7 +1503,7 @@
     <t>আজকে আমার পা ব্যথা করছে, রান্না না হয় তুমি কর</t>
   </si>
   <si>
-    <t>আজিয়ে আঁর টেং ব্যথা গরের, রান্না নয়তো তুঁই গরো</t>
+    <t>আজিয়ে আঁর টেঙ ব্যথা গরের, রান্না নয়তো তুঁই গরো</t>
   </si>
   <si>
     <t>চল, আজকে বাইরে থেকে খেয়ে আসি, ঘরের খাবার আর ভাল লাগছেনা</t>
@@ -3471,7 +3471,7 @@
     <t>রান্না করা শেষ, এখন আগুন নিভিয়ে দাও</t>
   </si>
   <si>
-    <t xml:space="preserve">রান্না গরা শেষ, এহন অইন নিফেই দ </t>
+    <t>রান্না গরা শেষ, এহন অইন নিফেই দ</t>
   </si>
   <si>
     <t>এটা কি বাসার দারোয়ান?</t>
@@ -4211,7 +4211,7 @@
     <t>কিরে বন্ধু! তুই নাকি লুকাই লুকাই প্রেম করছিস?</t>
   </si>
   <si>
-    <t xml:space="preserve">কিরে বন্ধু! তুই বলে গুজি গুজি প্রেম গরর? </t>
+    <t>কিরে বন্ধু! তুই বলে গুজি গুজি প্রেম গরর?</t>
   </si>
   <si>
     <t>ভালো হয়ে যা বন্ধু, প্রেম করা ভালো না</t>
@@ -5005,7 +5005,7 @@
     <t>আমাদের মসজিদে ঈদের নামাজ তাড়াতাড়ি হয়ে যায়</t>
   </si>
   <si>
-    <t>আঁরার মসজিদুত ঈদুর নামাজ তারাতারি অই যায়</t>
+    <t>আঁরার মসইদুত ঈদুর নামাজ তারাতারি অই যায়</t>
   </si>
   <si>
     <t>এই ঈদে আমরা সব বন্ধুরা একরকম পাঞ্জাবি নিয়েছি</t>
@@ -5263,7 +5263,7 @@
     <t>ছোটবেলায় রমজান মাসে মসজিদে তারাবিহ পড়তে গেলে অনেক দুষ্টামি করতাম</t>
   </si>
   <si>
-    <t>গুরো থাকতে রমজান মাসুত মসজিদুত তারাবিহ ফইত্তু গেইলি বত যারগই গইত্তাম</t>
+    <t>গুরো থাকতে রমজান মাসুত মসইদুত তারাবিহ ফইত্তু গেইলি বত যারগই গইত্তাম</t>
   </si>
   <si>
     <t>আমি সাঁতার পারি না, আমাকে ধাক্কা দিস না</t>
@@ -7348,7 +7348,7 @@
     <t>এই রাস্তা দিয়ে রাতে চলাচল নিরাপদ না</t>
   </si>
   <si>
-    <t xml:space="preserve">এই রাস্তা দি রাতিয়ে চলাচল নিরাপদ ন </t>
+    <t>এই রাস্তা দি রাতিয়ে চলাচল নিরাপদ ন</t>
   </si>
   <si>
     <t>ভাই, গাড়ি অন্য রাস্তা দিয়ে নিয়ে যান, শুনেছি এই রাস্তায় নাকি চোর-ডাকাতের ভয় আছে</t>
@@ -7540,7 +7540,7 @@
     <t>আমাদের বাস সামনের মসজিদে কিছুক্ষণ থামবে, যারা নামাজ পড়তে চান তারা পড়ে ফেলতে পারেন</t>
   </si>
   <si>
-    <t>আঁরার বাস সামনুর মসজিদুত হতক্ষন থিয়েইবু, যারা নামাজ ফইত্তো চন ইতারা ফরি ফেলাইত ফারিবে</t>
+    <t>আঁরার বাস সামনুর মসইদুত হতক্ষন থিয়েইবু, যারা নামাজ ফইত্তো চন ইতারা ফরি ফেলাইত ফারিবে</t>
   </si>
   <si>
     <t>চট্টগ্রাম থেকে সিলেট অনেক দূরে, আমরা কাছে কোথাও যাই</t>
@@ -7919,6 +7919,1806 @@
   </si>
   <si>
     <t>চট্টগ্রাম বিশ্ববিদ্যালয়ুর ফারুত বত আফ আছে, আঁরা যহন এনডে ঘুইত্তো গেইলাম তহন উইন্নিলাম</t>
+  </si>
+  <si>
+    <t>আজকের আবহাওয়া দেখে মনে হচ্ছে ছাতা ছাড়া বের হওয়া ঠিক হবে না</t>
+  </si>
+  <si>
+    <t>আজিয়ের আবাহাওয়া দেহি মনে অরদে ছাতি ছাড়া বাইর অন ঠিক ন অইবু</t>
+  </si>
+  <si>
+    <t>বর্ষাকাল চলে আসছে, এবার ভালো দেখে একটা ছাতা কিনতে হবে</t>
+  </si>
+  <si>
+    <t>বর্ষাহাল চলি আইসসি, এবার ভালা মিক্কে চায় এক্কান ছাতি কিনন ফরিবু</t>
+  </si>
+  <si>
+    <t>কিছুক্ষণের মধ্যে বৃষ্টি আসতে পারে, ছাতাটা নিয়ে যাও</t>
+  </si>
+  <si>
+    <t>কিছুক্ষনের মধ্যে ঝর আইত ফারে, ছাতি ইয়েন লই যও</t>
+  </si>
+  <si>
+    <t>আজকে সকাল থেকেই আকাশ মেঘলা, মনে হচ্ছে বিকেলের দিকে ভারী বৃষ্টি হবে</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেইন্নেত্তুন আকাশ মৌলো, মনে অদ্দে বিকেলুর ইক্কে বেশ গরি বৃষ্টি অইবু</t>
+  </si>
+  <si>
+    <t>একটু বৃষ্টি পড়লেই চট্টগ্রাম ডুবে যায়</t>
+  </si>
+  <si>
+    <t>এক্কানা ঝর ফরিলিই চট্টগ্রাম ডুফি যায়</t>
+  </si>
+  <si>
+    <t>বর্ষাকালে শহরে হাঁটাচলা করা বিরক্তিকর, চারদিকে নর্দমার পানি</t>
+  </si>
+  <si>
+    <t>বর্ষাহালে শ'রুত আডাচলা গরন বিরক্তিকর, চেরুমিক্কে নালার পানি</t>
+  </si>
+  <si>
+    <t>এই গরমে বাইরে বের হওয়া সত্যিই অনেক কষ্টের, রোদের তাপ সহ্য করা যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>এই গরোমত বাইরে বাইর অন সত্যিই বত হষ্টর, রইদুর তাপ সইয্য গরন ন যার</t>
+  </si>
+  <si>
+    <t>শীতের সকালে কুয়াশার মধ্যে হাঁটতে বের হলে মনটা অনেক ভালো লাগে</t>
+  </si>
+  <si>
+    <t>শীতুর সকালে হুয়ার মধ্যে আডিতু বাইর অইলি মন ইয়েন বত ভালা লাগে</t>
+  </si>
+  <si>
+    <t>আজকে এত রোদ উঠেছে যে মাঠে কাজ করা কৃষকদের খুব কষ্ট হচ্ছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে এল্লেত রইদ উইট্টি দে মাডুত হাজ গরা কৃষক অক্কল উত্তুন বত হষ্ট অর</t>
+  </si>
+  <si>
+    <t>কাল রাতে এত জোরে বজ্রপাত হয়েছিল যে ঘুম ভেঙে গিয়েছিল</t>
+  </si>
+  <si>
+    <t>হালিয়ে রাতিয়ে এল্লেত জোরে টাডাল পইজ্জিল দে ঘুম ভাঙি গেইয়্যিল</t>
+  </si>
+  <si>
+    <t>বাইরে বেশি বজ্রপাত হচ্ছে, এখন বের হওয়া ঠিক হবে না</t>
+  </si>
+  <si>
+    <t>বাইরে বেশি টাডাল পরের, এহন বাইর অন ঠিক ন অইবু</t>
+  </si>
+  <si>
+    <t>বৃষ্টির পরে রাস্তায় যে কাদা হয়, তাতে চলাচল করা সত্যিই অনেক ঝামেলার</t>
+  </si>
+  <si>
+    <t>বৃষ্টির পরে রাস্তাত যে ফুট অয়, এগিনুত আডাচলা গরন সত্যিই বত ঝামিলের</t>
+  </si>
+  <si>
+    <t>এই বছর শীত অনেক দেরিতে এসেছে, ডিসেম্বর শেষ হয়ে গেলেও ঠান্ডা পড়েনি</t>
+  </si>
+  <si>
+    <t>এই বছর শীত বত দেরিত আইসসি, ডিসেম্বর শেষ অই গেলিও ঠান্ডা ন ফরে</t>
+  </si>
+  <si>
+    <t>বৈশাখ মাসে কালবৈশাখী ঝড় হয়</t>
+  </si>
+  <si>
+    <t>বৈশাখ মাসুত হালবৈশাখী ঝর অয়</t>
+  </si>
+  <si>
+    <t>বর্ষাকাল আসলে আমাদের বেড়িবাঁধ ভেঙে যায়</t>
+  </si>
+  <si>
+    <t>বর্ষাহাল আইলি আঁরার হাডি ভাঙি যায়</t>
+  </si>
+  <si>
+    <t>গত বছর বর্ষাকালে বেড়িবাঁধ ভেঙে পুরো গ্রাম পানিতে ডুবে গিয়েছিল</t>
+  </si>
+  <si>
+    <t>গত বছর বর্ষাহালে হাডি ভাঙি পুরো গ্রাম পানিত ডুফি গেইয়্যিল</t>
+  </si>
+  <si>
+    <t>জোয়ারের পানি ঢুকে আমার সব ক্ষেত নষ্ট করে দিল</t>
+  </si>
+  <si>
+    <t>জোয়ারুর পানি ঢুকি আঁর বিয়াক ক্ষেতি নষ্ট গরি দিয়্যি</t>
+  </si>
+  <si>
+    <t>টিভির খবরে দেখলাম, আমাদের এলাকায় ১০ নম্বর মহাবিপদ সংকেত দিয়েছে</t>
+  </si>
+  <si>
+    <t>টিভির হবোরত দেইক্কিলাম, আঁরার এলাকাত ১০ নম্বর মহাবিপদ সংকেত দিইয়্যি</t>
+  </si>
+  <si>
+    <t>বসন্তকাল আমার সবচেয়ে বেশি ভালো লাগে</t>
+  </si>
+  <si>
+    <t>বসন্তহাল আঁর বিয়াজ্ঞুনুত্তুন বেশি ভালা লাগে</t>
+  </si>
+  <si>
+    <t>এই বছর বন্যার পানি এত বেশি উঠেছে যে অনেক বাড়ি পানিতে ডুবে গেছে</t>
+  </si>
+  <si>
+    <t>এই বছর বন্যার পানি এতো বেশি উইট্টি দে বত বারি পানিত ডুফি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বাইরে অনেক বেশি গরম, একটা ছাতা নিয়ে যাও</t>
+  </si>
+  <si>
+    <t>বাইরে বত বেশি গরম, এক্কান ছাতি লই যও</t>
+  </si>
+  <si>
+    <t>এই গরমের মধ্যে মাঠে কাজ করা অনেক কষ্টকর</t>
+  </si>
+  <si>
+    <t>এই গরমুর মধ্যে মাডুত হাজ গরন বত হষ্টকর</t>
+  </si>
+  <si>
+    <t>আমি জানি না এরা কীভাবে এই গরমের মধ্যে মাঠে ফুটবল খেলছে</t>
+  </si>
+  <si>
+    <t>আঁই ন জানি ইতারা কেন গরি এই গরমুর মধ্যে মাডুত ফুটবল খেলের</t>
+  </si>
+  <si>
+    <t>আকাশ অনেক মেঘলা হয়ে গেছে, চল আজ আর না খেলি</t>
+  </si>
+  <si>
+    <t>আকাশ বত মৌলো অই গেইয়্যি, চল আজিয়ে আর ন খেলি</t>
+  </si>
+  <si>
+    <t>বৃষ্টির মধ্যে খেললে অসুস্থ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>বৃষ্টির মধ্যে খেলিলি অসুস্থ অই যাইবে</t>
+  </si>
+  <si>
+    <t>বৃষ্টিতে ভিজে ঘরে গেলে আম্মু অনেক বকা দেবে</t>
+  </si>
+  <si>
+    <t>ঝরুত ভিজি ঘরুত গেলি আম্মু বত বকা দিবু</t>
+  </si>
+  <si>
+    <t>শীতকালে অনেক রকমের পিঠা পাওয়া যায়</t>
+  </si>
+  <si>
+    <t>শীতহালে বত রহমুর পিডে পন যায়</t>
+  </si>
+  <si>
+    <t>আমার নানু যখন বেঁচে ছিলেন, তখন উনি আমাদের পিঠা বানিয়ে খাওয়াতেন</t>
+  </si>
+  <si>
+    <t>আঁর নানু যহন বাছি আছিল, তহন ইবে আঁরারে পিডে বানাই হাবাইতু</t>
+  </si>
+  <si>
+    <t>শীতকালে পুকুরে নেমে গোসল করা অনেক বিরক্তিকর</t>
+  </si>
+  <si>
+    <t>শীতহালে ফইরোত নামি গোসল গরন বত বিরক্তিকর</t>
+  </si>
+  <si>
+    <t>বর্ষাকাল আসার আগেই ঘরের কাজ শেষ করতে হবে</t>
+  </si>
+  <si>
+    <t>বর্ষাহাল আইবের আগেই ঘরুর হাজ শেষ গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>গরম বেশি পড়ার কারণে স্কুল-কলেজ বন্ধ করে দিয়েছে</t>
+  </si>
+  <si>
+    <t>গরম বেশি ফরিবের হারনে স্কুল-কলেজ বন্ধ গরি দিইয়্যি</t>
+  </si>
+  <si>
+    <t>এই গরমে সব স্কুল-কলেজ বন্ধ, কিন্তু আমাদের কলেজে এখনো ক্লাস হচ্ছে</t>
+  </si>
+  <si>
+    <t>এই গরমুত বিয়াক স্কুল-কলেজ বন্ধ, কিন্তু আঁরার কলেজুত এহনো ক্লাস অর</t>
+  </si>
+  <si>
+    <t>এই বছর তো অনেক কম শীত পড়ছে, গত বছর আরও বেশি পড়েছিল</t>
+  </si>
+  <si>
+    <t>এই বছর তো বত হম শীত ফইজ্জি, গত বছর আরও বেশি ফইজ্জিল</t>
+  </si>
+  <si>
+    <t>রাস্তার পাশে একজন মানুষ বসে আছে, তার খুব ঠান্ডা লাগছে</t>
+  </si>
+  <si>
+    <t>রাস্তার পাশে একজন মানুষ বই থেইক্কি, ইবেত্তুন বত ঠান্ডা লাগের</t>
+  </si>
+  <si>
+    <t>বাইরে অনেক ঠান্ডা, এই কম্বলটা মানুষটাকে দিয়ে আয়</t>
+  </si>
+  <si>
+    <t>বাইরে বত ঠান্ডা, এই হম্বল ইয়েন মানুষ ইবেরে দি আইয়্যু</t>
+  </si>
+  <si>
+    <t>গাড়ি চালিয়ে আসার সময় কুয়াশার কারণে সামনে রাস্তা দেখতে পাচ্ছিলাম না</t>
+  </si>
+  <si>
+    <t>গারি চালাই আইবের সমত হুয়ার হারনে সামনে রাস্তা ন দেহির</t>
+  </si>
+  <si>
+    <t>কুয়াশা এত বেশি যে সামনে কী আছে কিছু বোঝা যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>হুয়া এত বেশি দে সামনে কি আছে কি আছে কিছু বুঝা ন যার</t>
+  </si>
+  <si>
+    <t>আমি চিন্তা করছি এবার শীতের ছুটিতে আমার দাদুকে একবার গিয়ে দেখে আসব</t>
+  </si>
+  <si>
+    <t>আঁই চিনতে গরির এবার শীতুর ছুটিত আঁর দাদুরে একবার যাই সাই আইসসুম</t>
+  </si>
+  <si>
+    <t>আমার দাদু নাকি অনেক অসুস্থ, বৃষ্টি কমলে এক ফাঁকে গিয়ে দেখে আসব</t>
+  </si>
+  <si>
+    <t>আঁর দাদু নাকি বত অসুস্থ, বৃষ্টি হমিলি এক ফাকে যাই চাই আইসসুম</t>
+  </si>
+  <si>
+    <t>এবার ঘরের ছালাটা ঠিক করতে হবে, নাহয় বর্ষাকালে পানি পড়বে</t>
+  </si>
+  <si>
+    <t xml:space="preserve">এবার ঘরুর ছাল ইয়েন ঠিক গরন ফরিবু, নইলি বর্ষাহালে পানি ফরিবু </t>
+  </si>
+  <si>
+    <t>এ বছর বৃষ্টি বেশি হওয়ার কারণে ফসলের অনেক ক্ষতি হয়েছে</t>
+  </si>
+  <si>
+    <t>এ বছর ঝর বেশি ফরিবের হারনে ফসলুর বত হতি অইয়্যি</t>
+  </si>
+  <si>
+    <t>আমাদের এখানে যেহেতু বৃষ্টি কম হয়, সেহেতু বৃষ্টি পড়লে আমাদের বৃষ্টির পানি ধরে রাখতে হবে</t>
+  </si>
+  <si>
+    <t>আঁরার এনডে যেহেতু বৃষ্টি হম অয়, এতেল্লে ঝর ফরিলি আঁরাত্তুন ঝরুর পানি ধরি রাহন ফরিবু</t>
+  </si>
+  <si>
+    <t>সন্ধ্যায় ঝড় আসতে পারে, নৌকা নিয়ে নদীতে না যাওয়াই ভালো</t>
+  </si>
+  <si>
+    <t>আজুইন্নে ঝর আইত পারে, নৌকো লই দইজ্জেত ন যনই ভালা</t>
+  </si>
+  <si>
+    <t>টিভির খবরে দেখলাম, এই সপ্তাহ আবহাওয়া খারাপ থাকবে</t>
+  </si>
+  <si>
+    <t>টিভির হবোরত দেইক্কিলাম, এই সপ্তাত আবাহাওয়া হারাফ থাহিবু</t>
+  </si>
+  <si>
+    <t>গত কয়েক বছর ধরে ঈদের দিন প্রচুর বৃষ্টি হচ্ছে</t>
+  </si>
+  <si>
+    <t>গত হয়েক বছর ধরি ঈদুর দিন প্রচুর বৃষ্টি অর</t>
+  </si>
+  <si>
+    <t>ঈদের দিন বৃষ্টি পড়লে ঈদের মজাটাই নষ্ট হয়ে যায়</t>
+  </si>
+  <si>
+    <t>ঈদুর দিন ঝর ফরিলি ঈদুর মজাগানই নষ্ট অই যায়</t>
+  </si>
+  <si>
+    <t>১৯৯১ সালের বন্যায় লাখ লাখ মানুষ মারা গিয়েছিল</t>
+  </si>
+  <si>
+    <t>১৯৯১ সালুত বন্যাত লাখ লাখ মানুষ মারা গেইয়্যিল</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় আম্মুর কাছে ১৯৯১ সালের বন্যার কথা শুনেছিলাম</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে আম্মুর হাছে ১৯৯১ সালুর হথা উইন্নিলাম</t>
+  </si>
+  <si>
+    <t>বন্যার পানিতে অনেক মানুষ মারা গেছে, আর অনেক ঘরবাড়ি ও ফসলের ক্ষতি হয়েছে</t>
+  </si>
+  <si>
+    <t>বন্যার পানিত বত মানুষ মারা গেইয়্যি, বত ঘরবারি আর ফসলুর হতি অইয়্যি</t>
+  </si>
+  <si>
+    <t>বন্যার পানিতে যাদের ক্ষতি হয়েছে, তাদেরকে সরকারের পক্ষ থেকে কিছু টাকা ক্ষতিপূরণ দেওয়া হবে</t>
+  </si>
+  <si>
+    <t>বন্যার পানিত যারার হতি অইয়্যি, ইতারারে সরকারুর পক্ষত্তুন কিছু টিয়া হতিফুরন দিবু</t>
+  </si>
+  <si>
+    <t>গরম দিন দিন বেড়ে যাচ্ছে, সামনে কী হবে আল্লাহই ভালো জানেন</t>
+  </si>
+  <si>
+    <t>গরম দিন দিন বারি যার, সামনে কি অইবু আল্লাহই ভালা জানে</t>
+  </si>
+  <si>
+    <t>গরম কমলে তারপর কাঁঠাল খাব</t>
+  </si>
+  <si>
+    <t>গরম হমিলি তারপর হাট্টল হাইয়্যুম</t>
+  </si>
+  <si>
+    <t>শীতকালে ঠান্ডা পানি খেলে গলা ব্যথা হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>শীতহালে ঠান্ডা পানি হাইলি গলা ব্যথা অই যাইবু</t>
+  </si>
+  <si>
+    <t>আন্টি বলল, তুই নাকি শীতকালে গোসল করিস না?</t>
+  </si>
+  <si>
+    <t>আন্টি হইয়্যি তুই বলে শীতহালে গোসল ন গরস?</t>
+  </si>
+  <si>
+    <t>শীতকালে টাটকা টাটকা সবজি পাওয়া যায়</t>
+  </si>
+  <si>
+    <t>শীতহালে টাটকা টাটকা সবজি পন যায়</t>
+  </si>
+  <si>
+    <t>বাইরের রোদ থেকে ঘরে এসে ঠিকমতো দেখতে পারছি না</t>
+  </si>
+  <si>
+    <t>বাইরুর রইদুত্তুন ঘরুত আই ঠিকমতো ন দেহির</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টির মধ্যে বাইক নিয়ে কোথায় যাচ্ছিস?</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টির মধ্যে বাইক লই হনডে যদ্দে?</t>
+  </si>
+  <si>
+    <t>বন্ধুর সঙ্গে বাইক নিয়ে বের হয়েছিলাম, রাস্তায় হঠাৎ বৃষ্টি চলে আসে</t>
+  </si>
+  <si>
+    <t xml:space="preserve">বন্ধুর লগে বাইক লই বাইর অইলাম, রাস্তাত হঠাৎ ঝর চলি আইসসি </t>
+  </si>
+  <si>
+    <t>ছাতা ছাড়া বের হয়েছিলাম, বৃষ্টি আসার কারণে পুরো ভিজে গেছি</t>
+  </si>
+  <si>
+    <t>ছাতি ছারা বাইর অইয়্যিলাম, ঝর আইবের হারনে পুরো ভিজি গেই</t>
+  </si>
+  <si>
+    <t>সকালে বের হওয়ার সময় মনে হয়েছিল বৃষ্টি আসবে না, কিন্তু বের হওয়ার কিছুক্ষণের মধ্যেই বৃষ্টি চলে আসে</t>
+  </si>
+  <si>
+    <t>বেইন্নে বাইর অইবের সমত মনে অইয়্যিল ঝর নো আইবু, কিন্তু বাইর অইবের কিছুক্ষনুর মধ্যেই ঝর চলি আইসসি</t>
+  </si>
+  <si>
+    <t>আমাদের একজন গণিত স্যার ছিলেন, উনি ঝড়-তুফানের মধ্যেও ক্লাসে চলে আসতেন</t>
+  </si>
+  <si>
+    <t>আরাত্তুন উজ্ঞো গণিত স্যার আছিল, ইবে ঝর-তুওয়োনুর মধ্যেও ক্লাসুত চলি আইসতো</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় আল্লাহর কাছে দোয়া করতাম, যেন বন্যা এসে স্কুল ডুবিয়ে দেয়</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে আল্লাহর হাছে দোয়া গইত্তাম যেন বন্যা আই স্কুল ডুফোই দেই</t>
+  </si>
+  <si>
+    <t>তুই তো দেখছি আমাদের গণিত স্যারের মতো বন্যার মধ্যেও ক্লাসে চলে আসছিস</t>
+  </si>
+  <si>
+    <t>তুই তো দেহির আঁরার গণিত স্যারোর মতন বন্যার মধ্যেও ক্লাসুত চলি আইসসুছ</t>
+  </si>
+  <si>
+    <t>বাতাস বেশি হওয়ার কারণে ছাতাটা ভেঙে গেল</t>
+  </si>
+  <si>
+    <t>বাতাস বেশি অইবের হারনে ছাতিগান ভাঙি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>তোকে বারবার বলেছি ছাতাটা নিয়ে বের হইস না, এখন আমার এত দামি ছাতাটা ভেঙে গেল</t>
+  </si>
+  <si>
+    <t>তোরে বারবার হইলাম দে ছাতি ইয়েন লই বাইর ন অইস, এহন আঁর এল্লেত দামি ছাতিগান ভাঙি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>ঘরের সব জায়গায় বৃষ্টির পানি পড়ছে, এভাবে কি থাকা যায়?</t>
+  </si>
+  <si>
+    <t>ঘরুর বিয়াক জাগাত বৃষ্টির পানি ফইজ্জি, এনগরি কি থাহন যায়?</t>
+  </si>
+  <si>
+    <t>বাইরে অনেক বজ্রপাত হচ্ছে, সাবধানে যেও</t>
+  </si>
+  <si>
+    <t>বাইরে বত টাডাল ফরের, সাবধানে যাইয়্যু</t>
+  </si>
+  <si>
+    <t>বৃষ্টির দিনে ঘরবন্দী হয়ে বসে আছি, কোনো কাজ করতে পারছি না</t>
+  </si>
+  <si>
+    <t>বৃষ্টির দিনুত ঘরবন্দী অই বই আছি, হনো হাজ গরিত ন পারির</t>
+  </si>
+  <si>
+    <t>বর্ষাকালে কাজ কম থাকে, সেজন্য বর্ষাকাল এলে আমার ভয় লাগে</t>
+  </si>
+  <si>
+    <t>বর্ষাহালে হাজ হম থাহে, এতেল্লে বর্ষাহাল আইলি আত্তুন ডর লাগে</t>
+  </si>
+  <si>
+    <t>বসন্তের বাতাসে ফুলের গন্ধ ভেসে আসছে, মনটা কেমন আনন্দে ভরে উঠছে</t>
+  </si>
+  <si>
+    <t>বসন্তর বাতাসুত ফুলুর গন্ধ বাই আইয়্যির, মন ইয়েন আনন্দে ভরি উইট্টি</t>
+  </si>
+  <si>
+    <t>ঘূর্ণিঝড়ের সতর্কবার্তা দেওয়া হয়েছে, তাই উপকূলের মানুষজন আশ্রয়কেন্দ্রে চলে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>ঘুর্ণিঝড়ুর সিংগেল দিইয়্যি, এতেল্লে কুলুর মানুষজন আশ্রয়কেন্দ্রত চলি যার</t>
+  </si>
+  <si>
+    <t>আজকে এত বেশি গরম পড়ছে যে ফ্যানের বাতাসও গরম মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে এতো বেশি গরম পরেদ্দে ফ্যানুর বাতাসও গরম মনে অর</t>
+  </si>
+  <si>
+    <t>আকাশে কালো মেঘ জমছে, মনে হচ্ছে আজকে রাতে ভারী বৃষ্টি হবে</t>
+  </si>
+  <si>
+    <t>আকাশুত হালা মৌলো জইম্মি, মনে অদ্দে আজিয়ে রাতিয়ে ভারী বৃষ্টি অইবু</t>
+  </si>
+  <si>
+    <t>বজ্রপাতের সময় খোলা মাঠে থাকা অনেক বিপজ্জনক</t>
+  </si>
+  <si>
+    <t>টাডাল ফরিবের সমত খোলা মাডুত থাহন বত বিপজ্জনক</t>
+  </si>
+  <si>
+    <t>আজকে বাতাসের গতি অনেক বেশি, গাছের ডালপালা অনেক বেশি নড়াচড়া করছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে বাতাসুর গতি বত বেশি, গাছুর ডাজ্ঞো বত বেশি লরাচরা গরের</t>
+  </si>
+  <si>
+    <t>শরৎকালের আকাশে সাদা মেঘের ভেলা দেখে মন ভালো হয়ে যায়</t>
+  </si>
+  <si>
+    <t>শরৎহালে আকাশুত সাদা মৌলোর ভেলা দেহি মন ভালা অই যায়</t>
+  </si>
+  <si>
+    <t>ঝড়ের পরে আকাশ এত পরিষ্কার হয়ে যায় যে তারাগুলো স্পষ্ট দেখা যায়</t>
+  </si>
+  <si>
+    <t>ঝরুর পরে আকাশ এতো পরিষ্কার অই যায় দে তারা এগুন স্পষ্ট দেহা যায়</t>
+  </si>
+  <si>
+    <t>আগামীকাল যদি আবহাওয়া ভালো থাকে, তাহলে আমরা পিকনিকে যাব</t>
+  </si>
+  <si>
+    <t>হালিয়ে যদি আবাহাওয়া ভালা থাহে তইলি আঁরা পিকনিকুত যাইয়্যুম</t>
+  </si>
+  <si>
+    <t>দুপুরের পর থেকে আকাশ হঠাৎ কালো হয়ে গেল, মনে হচ্ছে অনেক জোরে বৃষ্টি আসবে</t>
+  </si>
+  <si>
+    <t>দুপুরুর পরুত্তুন আকাশ হঠাৎ হালা অই গেইয়্যি, মনে অদ্দে বত জোরে ঝর আইবু</t>
+  </si>
+  <si>
+    <t>বৃষ্টির কারণে ঘন ঘন লোডশেডিং হচ্ছে</t>
+  </si>
+  <si>
+    <t>বৃষ্টির হারনে ঘন ঘন লোডশেডিং অর</t>
+  </si>
+  <si>
+    <t>আগামীকাল যদি রোদ থাকে, তাহলে মাঠের ধান কেটে রোদে শুকানো যাবে</t>
+  </si>
+  <si>
+    <t>হালিয়ে যদি রইদ থাহে, তইলি মাডোর ধান হাডি রইদুত ফোওয়োন যাইবু</t>
+  </si>
+  <si>
+    <t>আজকে তাপমাত্রা চল্লিশ ডিগ্রির কাছাকাছি, বাইরে বের হতে ভয় লাগছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে তাপমাত্রা চল্লিশ ডিগ্রির হাছাহাছি, বাইরে বের অইতু ডর লাগের</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টিতে আমাদের গ্রামের কাঁচা রাস্তা একেবারে কাদায় ভরে গেছে</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টিত আঁরার গ্রামুর কেচা রাস্তা একেবারে ফুটে ভরি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>শীতের সকালে ভোরবেলা উঠে নামাজ পড়তে যাওয়া সত্যিই অনেক কঠিন কাজ</t>
+  </si>
+  <si>
+    <t>শীতুর সকালে ফুওয়াত্তে উডি নামাজ ফইত্তো যন সত্যিই বত কঠিন হাজ</t>
+  </si>
+  <si>
+    <t>এই মাসে বৃষ্টি না হওয়ায় পুকুর আর খালের পানি শুকিয়ে যেতে শুরু করেছে</t>
+  </si>
+  <si>
+    <t>এই মাসুত বৃষ্টি ন অনে ফইর আর হালুর পানি ফুওয়েই যাইতু শুরু গইজ্জি</t>
+  </si>
+  <si>
+    <t>আজকে সকাল থেকে টিপটিপ বৃষ্টি পড়ছে, থামার কোনো লক্ষণ দেখা যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেইন্নেত্তুন ফেডের ফেডের ঝর ফরের, থামিবের হনো লক্ষন দেহা ন যার</t>
+  </si>
+  <si>
+    <t>শীতকাল আসলেই আমাদের পুকুরের পানি শুকাতে শুরু করে</t>
+  </si>
+  <si>
+    <t>শীতহাল আইলিই আঁরার ফইরুর পানি ফুওয়েই যাইতু শুরু গরে</t>
+  </si>
+  <si>
+    <t>যদি কারেন্ট না আসে, তাহলে ছাদে গিয়ে ঘুমাব</t>
+  </si>
+  <si>
+    <t>যদি কারোন ন আইয়্যি, তইলি ছাদুত যাই ঘুমাইয়্যুম</t>
+  </si>
+  <si>
+    <t>বেশি জোরে বাতাস হচ্ছে, মনে হয় আজ আর কারেন্ট আসবে না</t>
+  </si>
+  <si>
+    <t>বেশি জোরে বাতাস অর, মনে অয় আজিয়ে আর কারোন ন আইবু</t>
+  </si>
+  <si>
+    <t>গতকাল রাতে বাতাস অনেক বেশি ছিল, গাছ ভেঙে রাস্তা বন্ধ হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>হালিয়ে রাতিয়ে বাতাস বত বেশি আছিল, গাছ ভাঙি রাস্তা বন্ধ অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>খবরে শুনলাম নতুন একটা ঘূর্ণিঝড় আসছে, সবাইকে আশ্রয়কেন্দ্রে চলে যেতে বলল</t>
+  </si>
+  <si>
+    <t>হবরুত উনিলাম নতুন উজ্ঞো ঘূর্ণিঝর আইয়্যির, বিয়াজ্ঞুনুরে আশ্রয়কেন্দ্রত চলি যাইতু হইয়্যি</t>
+  </si>
+  <si>
+    <t>যারা সাগরের আশপাশে আছে, তাদের জন্য অনেক বিপজ্জনক</t>
+  </si>
+  <si>
+    <t>যারা সগরুর আশে পাশে আছে ইতারার লাই বত বিপজ্জনক</t>
+  </si>
+  <si>
+    <t>প্রতি বছর নদী ভেঙে অনেক ঘরবাড়ি নদীতে চলে যায়</t>
+  </si>
+  <si>
+    <t>ফইত্তো বছর দইজ্জে ভাঙি বত ঘরবারি দইজ্জেত চলি যায়</t>
+  </si>
+  <si>
+    <t>এখন কয়টা বাজে দেখ তো আরিফ</t>
+  </si>
+  <si>
+    <t>এহন হটা বাঝে সা তো আরিফ</t>
+  </si>
+  <si>
+    <t>আমি সর্বোচ্চ ১০টা পর্যন্ত থাকতে পারব, দেরি হলে বাসায় ঢুকতে পারব না</t>
+  </si>
+  <si>
+    <t>আঁই সর্বোচ্চ ১০টা পর্যন্ত থাহিত ফাইজ্জুম, দেরি অইলি বাসাত ঢুকিত ন পাইজ্জুম</t>
+  </si>
+  <si>
+    <t>স্যার, আমি ঠিক সময়ে বের হয়েছিলাম, কিন্তু মাঝপথে বৃষ্টি আসার কারণে দেরি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>স্যার, আঁই ঠিক সময়ে বাইর অইয়্যিলাম, কিন্তু মাঝপথুত ঝর আইবের হারনে দেরি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সত্যি বলতে আমার ওখানে যাওয়ার কোনো ইচ্ছা নেই, আপনি জোর করছেন তাই যাচ্ছি</t>
+  </si>
+  <si>
+    <t>সত্যি বলতে আত্তুন এনডে যাইবের হনো ইচ্ছে নেই, অঁনে জোর গরের এতেল্লে যাইর</t>
+  </si>
+  <si>
+    <t>বিয়ে আজ নাকি আগামীকাল?</t>
+  </si>
+  <si>
+    <t>বিয়ে আজিয়ে নাকি হালিয়ে?</t>
+  </si>
+  <si>
+    <t>আদনান বলেছিল বিয়ে আগামীকাল, তাহলে আজ এত আয়োজন কিসের?</t>
+  </si>
+  <si>
+    <t>আদনান হইয়্যিল বিয়ে হালিয়ে, তইলি আজিয়ে এল্লেত আয়োজন কিয়ুর?</t>
+  </si>
+  <si>
+    <t>আগামীকালও যদি এভাবে বৃষ্টি পড়ে, তাহলে টুরে যাব না</t>
+  </si>
+  <si>
+    <t>হালিয়েও যদি এল্লেত ঝর পরে তইলি টুরুত যাইতাম নো</t>
+  </si>
+  <si>
+    <t>আজকে সকাল থেকেই মাথা ঘুরছে, মনে হচ্ছে জ্বর আসছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেইন্নেত্তুন মাথা ঘুরার, মনে অদ্দে জ্বর আইয়্যির</t>
+  </si>
+  <si>
+    <t>কয়েকদিন ধরে ঠিকমতো ঘুম হচ্ছে না, শরীর একদম ভেঙে পড়েছে</t>
+  </si>
+  <si>
+    <t>হয়েকদিন ধরি ঠিকমতো ঘুম ন অর, শরীর এব্বেরে ভাঙি ফইজ্জি</t>
+  </si>
+  <si>
+    <t>ডাক্তার বললেন, বেশি করে বিশ্রাম নিতে হবে, শরীর দুর্বল হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>ডাক্তার হইয়্যি, বেশি গরি বিশ্রাম লন ফরিবু, শরীর দুর্বল অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>গলা ব্যথা এতটাই বেড়ে গেছে যে কথা বলতেও কষ্ট হচ্ছে</t>
+  </si>
+  <si>
+    <t>গলা ব্যথা এতটাই বারি গেইয়্যি দে হথা হইতেও হষ্ট অর</t>
+  </si>
+  <si>
+    <t>সারাদিন অফিসে কাজ করে বাড়ি ফিরলে শরীর আর চলতে চায় না</t>
+  </si>
+  <si>
+    <t>আরাদিন অফিসুত হাজ গরি বারি ফিরিলি শরীর আর চইলতো ন চায়</t>
+  </si>
+  <si>
+    <t>তোমার মলিন মুখ দেখলে আমার মন একদম খারাপ হয়ে যায়</t>
+  </si>
+  <si>
+    <t>তোঁয়ার মলিন মুখ দেহিলি আঁর মন এব্বেরে হারাপ অই যায়</t>
+  </si>
+  <si>
+    <t>তোমার হাসিমাখা চেহারাটা দেখলে সারাদিনের ক্লান্তি দূর হয়ে যায়</t>
+  </si>
+  <si>
+    <t>তোঁয়ার আসিমাখা চিয়ারা দেহিলি আরাদিনুর ক্লান্তি দুর অই যায়</t>
+  </si>
+  <si>
+    <t>ঘরে ছোট ছোট বাচ্চা থাকলে মন খারাপ করে থাকা যায় না</t>
+  </si>
+  <si>
+    <t>ঘরুত গুরো গুরো বাইচ্চে থাহিলি মন হারাপ গরি থাহন ন যায়</t>
+  </si>
+  <si>
+    <t>বাচ্চাটা কয়েকদিন ধরে জ্বরে ভুগছে, ডাক্তারের কাছে নিয়ে যেতে হবে</t>
+  </si>
+  <si>
+    <t>বাইচ্চে ইবে হয়েকদিন ধরি জ্বরুত ভুগের, ডাক্তারুর হাছে লই যন ফরিবু</t>
+  </si>
+  <si>
+    <t>আজকে হঠাৎ বুকে চাপ অনুভব করছি, কী হয়েছে বুঝছি না</t>
+  </si>
+  <si>
+    <t>আজিয়ে হঠাৎ বুকুত চাপ অনুভব গরির, কি অইয়্যি ন বুঝির</t>
+  </si>
+  <si>
+    <t>কোনো সমস্যা হয়েছে? তোমাকে দেখে চিন্তিত মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>হনো সমস্যা অইয়্যি? তোঁয়ারে দেহি চিন্তিত মনে অর</t>
+  </si>
+  <si>
+    <t>খালি পেটে আমার মাথা কাজ করে না, কিছু খেতে পারলেই শান্তি</t>
+  </si>
+  <si>
+    <t>হালি ফেডে আঁর মাথা হাজ ন গরে, কিছু হাইত ফারিলিই শান্তি</t>
+  </si>
+  <si>
+    <t>অনেকদিন পর ভালোভাবে ঘুমালাম, ঘুম থেকে উঠে শরীরটা একদম হালকা মনে হচ্ছে</t>
+  </si>
+  <si>
+    <t>বতদিন পর ভালাগরি ঘুম গেইলাম, ঘুমুত্তুন উডি শরীর ইয়েন এব্বেরে আলহা মনে অর</t>
+  </si>
+  <si>
+    <t>পেটে এত বেশি ব্যথা করছে যে বসতেও পারছি না</t>
+  </si>
+  <si>
+    <t>ফেডুত এত বেশি ব্যথা গরেদ্দে বইতও ন ফারির</t>
+  </si>
+  <si>
+    <t>দীর্ঘক্ষণ খালি পেটে থাকলে গ্যাস্ট্রিকের সমস্যা হয়</t>
+  </si>
+  <si>
+    <t>বেশিক্ষন হালি ফেডে থাহিলি গ্যাস্ট্রিকুর সমস্যা অয়</t>
+  </si>
+  <si>
+    <t>ডাক্তার বললেন, রক্তে শর্করার মাত্রা বেড়ে গেছে, খাওয়াদাওয়া নিয়ন্ত্রণ করতে হবে</t>
+  </si>
+  <si>
+    <t>ডাক্তার হইয়্যি রক্তত শর্করার মাত্রা বারি গেইয়্যি, হানাপিনে নিয়ন্ত্রণ গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>তুমি যদি নিজের খাওয়াদাওয়া নিয়ন্ত্রণ না কর, তাহলে পরে গিয়ে অনেক সমস্যা হবে</t>
+  </si>
+  <si>
+    <t>তুঁই যদি নিজুর হানাপিনে নিয়ন্ত্রন ন গরো, তইলি পরে যায় বত সমস্যা অইবু</t>
+  </si>
+  <si>
+    <t>তোমার রেজাল্ট ভালো হয়েছে দেখে আমার মনটাও ভালো হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার রেসাল্ট ভালা অইয়্যি দেহি আঁর মনগানও ভালা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>কয়েকদিন ধরে কাশি থামছে না, এই কারণে রাতে ঘুমাতে পারছি না</t>
+  </si>
+  <si>
+    <t>হয়েকদিন ধরি হাশি ন থামের, এই হারনে রাতিয়ে ঘুম যাইত ন পারির</t>
+  </si>
+  <si>
+    <t>এই কয়দিন যে ধকল গেছে আমার ওপর, ঠিকমতো ঘুমাতেও পারিনি</t>
+  </si>
+  <si>
+    <t>এই হয়দিন যে ধহল গেইয়্যি আঁর উদ্দি, ঠিকমতো ঘুমাইতও ন পারি</t>
+  </si>
+  <si>
+    <t>শরীরে এত ক্লান্তি জমে গেছে যে ছুটির দিনেও বিছানা ছেড়ে উঠতে ইচ্ছে করে না</t>
+  </si>
+  <si>
+    <t>শরীরুত এতো ক্লান্তি জমি গেইয়্যি দে ছুটির দিনুতও বিছেন ছারি উইট্টু ইচ্ছে ন গরের</t>
+  </si>
+  <si>
+    <t>আজকে মনটা খুব হালকা লাগছে, কারণ অনেকদিনের চিন্তাটা এবার শেষ হলো</t>
+  </si>
+  <si>
+    <t>আজিয়ে মন ইয়েন বত হালকা লাগের, হারন বতদিনুর চিন্তে ইয়েন এবার শেষ অইয়্যি</t>
+  </si>
+  <si>
+    <t>আজকে হাসপাতালে গিয়ে রক্ত পরীক্ষা দিয়ে এলাম, রিপোর্টের জন্য অপেক্ষায় আছি</t>
+  </si>
+  <si>
+    <t>আজিয়ে হাসপাতালুত যাই রক্ত পরীক্ষে দি আইলাম, রিপোর্ট উর অপেক্ষাত আছি</t>
+  </si>
+  <si>
+    <t>ডাক্তার সাহেব, আমি অনেকদিন ধরে বুকের ব্যথায় ভুগছি</t>
+  </si>
+  <si>
+    <t>ডাক্তার সাব, আঁই বতদিন ধরি বুকুর ব্যথায় ভুগির</t>
+  </si>
+  <si>
+    <t>আমার ডায়াবেটিস বেড়ে গেছে, আবার নিয়ন্ত্রণে আনতে হবে</t>
+  </si>
+  <si>
+    <t>আঁর ডায়বেটিস বারি গেইয়্যি, আবার নিয়ন্ত্রনুত আনন ফরিবু</t>
+  </si>
+  <si>
+    <t>জ্বর হলে কোনো কিছু খেতে মন চায় না, মুখের রুচি চলে যায়</t>
+  </si>
+  <si>
+    <t>জ্বর অইলি হনো কিছু হাইতু মনে ন চায়, মুখুর রুচি চলি যায়</t>
+  </si>
+  <si>
+    <t>আমি গত দুদিন ধরে শরীরে জ্বর নিয়ে কাজ করেছি</t>
+  </si>
+  <si>
+    <t>আঁই গত দুদিন ধরি শরীরুত জ্বর লই হাজ গরির</t>
+  </si>
+  <si>
+    <t>মানসিক চাপে থাকলে ঘুম আসে না, আর ঘুম না হলে শরীর আরও খারাপ হয়</t>
+  </si>
+  <si>
+    <t>মানসিক চাপুত থাহিলি ঘুম ন আইয়্যি, আর ঘুম ন অইলি শরীর আরও হারাপ অয়</t>
+  </si>
+  <si>
+    <t>ডাক্তার বললেন, নিয়মিত ব্যায়াম করলে এই সমস্যা অনেকটাই কমে যাবে</t>
+  </si>
+  <si>
+    <t>ডাক্তার হইয়্যি, নিয়মিত ব্যায়াম গরিলি এই সমস্যা বত হমি যাইবু</t>
+  </si>
+  <si>
+    <t>একদিন ব্যায়াম করে আমার পা আর নাড়াতে পারছি না</t>
+  </si>
+  <si>
+    <t>একদিন ব্যায়াম গরি আঁর পা আর লরাইত ন পারির</t>
+  </si>
+  <si>
+    <t>পিঠের ব্যথাটা বেশি বেড়ে গেছে, বসে বসে কাজ করার কারণে এমন হচ্ছে</t>
+  </si>
+  <si>
+    <t>পিডুর ব্যথাগান বেশি বারি গেইয়্যি, বই বই হাজ গরনুর হারনে এন অর</t>
+  </si>
+  <si>
+    <t>হাসপাতালের বেডে শুয়ে বাড়ির কথা মনে পড়লে মনটা আরও খারাপ হয়ে যায়</t>
+  </si>
+  <si>
+    <t>হাসপাতালুর বেডুত শুই বারির হথা মনুত ফরিলি মন ইয়েন আরো হারাপ অই যায়</t>
+  </si>
+  <si>
+    <t>বাইক এক্সিডেন্ট করে এক সপ্তাহ ধরে হাসপাতালের বেডে শুয়ে আছি, আমার কোনো বন্ধুই দেখতে আসল না</t>
+  </si>
+  <si>
+    <t>বাইক এক্সিডেন্ট গরি এক সপ্তাহ ধরি হাসপাতালুর বেডুত শুই আছি, আঁর হনো বন্ধুই সাইতু ন আইয়্যি</t>
+  </si>
+  <si>
+    <t>নিয়মিত কম পানি খেলে কিডনিতে সমস্যা হতে পারে</t>
+  </si>
+  <si>
+    <t>নিয়মিত হম পানি হাইলি কিডনিত সমস্যা অইত পারে</t>
+  </si>
+  <si>
+    <t>পরিবার, বন্ধু আর ভালোবাসার মানুষদের সঙ্গে সময় কাটাতে পারলে মনটা একদম ভালো হয়ে যায়</t>
+  </si>
+  <si>
+    <t>পরিবার, বন্ধু আর ভালোবাসার মানুষুর লগে সময় হাডাইত ফারিলি মন ইয়েন একদম ভালা অই যায়</t>
+  </si>
+  <si>
+    <t>অনেকদিন হয়ে গেল আমার ভালোবাসার মানুষটাকে দেখি না</t>
+  </si>
+  <si>
+    <t>বতদিন অই গেইয়্যি আঁর ভালোবাসার মানুষ ইবেরে ন দেহির</t>
+  </si>
+  <si>
+    <t>তার কথা মনে পড়লে আমার বুকটা একদম ভারী হয়ে যায়</t>
+  </si>
+  <si>
+    <t>তার হথা মনুত ফরিলি আঁর বুক ইয়েন একদম ভারী অই যায়</t>
+  </si>
+  <si>
+    <t>রোগ প্রতিরোধ ক্ষমতা বাড়াতে হলে প্রতিদিন তাজা ফলমূল এবং শাকসবজি খাওয়া দরকার</t>
+  </si>
+  <si>
+    <t>রোগ প্রতিরোধ ক্ষমতা বারাইতু চাইলি পইত্তোদিন তাজা ফলমুল আর শাকসবজি হন দরহার</t>
+  </si>
+  <si>
+    <t>ডাক্তার বললেন বেশি রাত জেগে থাকার কারণে স্বাস্থ্যের অনেক ক্ষতি হচ্ছে</t>
+  </si>
+  <si>
+    <t>ডাক্তার হইয়্যি বেশি রাইত জাগিবের হারনে স্বাইস্থর বত হতি অর</t>
+  </si>
+  <si>
+    <t>তোমাকে বলেছিলাম রাত ১০টার আগে ঘুমিয়ে যেতে, আর তুমি কিনা ফোন টিপো!</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে হইলাম দে রাতিয়ে ১০টার আগে ঘুমাই যাইতু, আর তুঁই কিন ফোন টিপো!</t>
+  </si>
+  <si>
+    <t>যারা প্রতিদিন দেরি করে ঘুমায়, তাদের ব্রেইনের ক্ষতি হয়</t>
+  </si>
+  <si>
+    <t>যারা ফইত্তোদিন দেরি গরি ঘুম যায় ইতারাত্তুন ব্রেইনুর হতি অয়</t>
+  </si>
+  <si>
+    <t>শরীরকে সুস্থ রাখার জন্য ঘুম খুবই জরুরি</t>
+  </si>
+  <si>
+    <t>শরীর উরে সুস্থ রাহিবের লাই ঘুম বেশি জরুরি</t>
+  </si>
+  <si>
+    <t>যারা নিয়মিত খেলাধুলা করে, তাদের মন আর শরীর দুটোই ভালো থাকে</t>
+  </si>
+  <si>
+    <t>যারা নিয়মিত খেলাধুলা গরে, তারার মন আর শরীর দুইয়েন ই ভালা থাহে</t>
+  </si>
+  <si>
+    <t>সারাদিন ফোনে গেমস না খেলে একটু বাইরে মাঠে গিয়ে খেলতে পারিস না</t>
+  </si>
+  <si>
+    <t>আরাদিন ফোনুত গেম ন খেলি এক্কানা বাইরে মাডুত যাই খেলিত ন পারস?</t>
+  </si>
+  <si>
+    <t>সারাদিন ফোনের দিকে তাকিয়ে থাকলে তো চোখ এমনিতেই নষ্ট হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আরাদিন ফোনুর মিক্কে সাই থাহিলি তো চোখ এনেই নষ্ট অই যাইবু</t>
+  </si>
+  <si>
+    <t>আগে মাঠে গেলে আমার সব বন্ধুদের দেখতাম, এখন সবাই নিজেদের জীবন নিয়ে ব্যস্ত</t>
+  </si>
+  <si>
+    <t>আগে মাডুত যাইলি আঁর বিয়াক বন্ধু অক্কলুরে দেহিতাম, এহন বিয়াজ্ঞুন নিজুর জীবন লই ব্যস্ত</t>
+  </si>
+  <si>
+    <t>আজকে সকালে উঠেই বমি বমি ভাব লাগছে, কিছু খেতে পারছি না</t>
+  </si>
+  <si>
+    <t>আজিয়ে বেইন্নে উডিই বুমি বুমি ভাব লাগের, কিছু হাইত ন পারির</t>
+  </si>
+  <si>
+    <t>হাঁটুতে ব্যথার কারণে সিঁড়ি বেয়ে উঠতে অনেক কষ্ট হচ্ছে</t>
+  </si>
+  <si>
+    <t>আডুর ব্যথার হারনে সিরি বাই উঠতে বত হষ্ট অর</t>
+  </si>
+  <si>
+    <t>আজকে মনটা এত খারাপ যে কারও সঙ্গে কথা বলতে ইচ্ছে করছে না</t>
+  </si>
+  <si>
+    <t>আজিয়ে মনগান এতো হারাফ দে কিয়ার লগে হথা হইতু ইচ্ছে ন গরের</t>
+  </si>
+  <si>
+    <t>ঠান্ডা লেগে নাক বন্ধ হয়ে আছে, রাতে শ্বাস নিতে কষ্ট হচ্ছে</t>
+  </si>
+  <si>
+    <t>ঠান্ডা লাগি নাক বন্ধ অই গেইয়্যি, রাতিয়ে শ্বাস লইতু হষ্ট অর</t>
+  </si>
+  <si>
+    <t>আমি দিনের পর দিন কাজ করে টাকা আয় করছি</t>
+  </si>
+  <si>
+    <t>আঁই দিনুর পর দিন হাজ গরি টিয়া হামাইর</t>
+  </si>
+  <si>
+    <t>টাকা আয় করা যে কত কষ্ট, সেটা যে আয় করে সেই জানে</t>
+  </si>
+  <si>
+    <t>টিয়া হামন যে হত হষ্ট ইয়েন যে হামাই ইতে জানে</t>
+  </si>
+  <si>
+    <t>আজকে অফিসে বসের বকা খেয়ে মেজাজ একদম খারাপ হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে অফিসুত বস উর বকা হায় মেজাজ এব্বেরে হারাপ অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার মন-মেজাজ ভালো না, আমাকে একটু একা থাকতে দাও</t>
+  </si>
+  <si>
+    <t>আঁর মন-মেজাজ ভালা ন, আঁরে এক্কানা এহেল্লে থাইকতো দও</t>
+  </si>
+  <si>
+    <t>আগে আমি কিছুক্ষণ বিশ্রাম নিই, তারপর তোমার সঙ্গে কথা বলব</t>
+  </si>
+  <si>
+    <t>আগে আঁই হতক্ষন জিরেই, তারপর তোঁয়ার লগে হথা হইয়্যুম</t>
+  </si>
+  <si>
+    <t>আমরা যদি রাগটা নিয়ন্ত্রণ করতে পারি, তাহলে আমরা অনেক ভালো থাকব</t>
+  </si>
+  <si>
+    <t>আঁরা যদি গুসসা ইয়েন নিয়ন্ত্রন গরিত পারি, তইলি আঁরা বত ভালা থাইক্কুম</t>
+  </si>
+  <si>
+    <t>রাগ আমারও আসে, কিন্তু আমি নিয়ন্ত্রণ করতে পারি</t>
+  </si>
+  <si>
+    <t>গুসসা আত্তুনও আইয়্যি, কিন্তু আঁই নিয়ন্ত্রন গরিত পারি</t>
+  </si>
+  <si>
+    <t>যারা রাগ নিয়ন্ত্রণ করতে পারে না তারা কখনো সুখী হতে পারে না</t>
+  </si>
+  <si>
+    <t>যারা গুসসা নিয়ন্ত্রন গরিত ন পারে ইতারা হনোদিন সুখী অইত ন পারে</t>
+  </si>
+  <si>
+    <t>তুমি যখন আমার মাথায় হাত বুলিয়ে দাও, তখন আমার মন থেকে সব দুঃখ চলে যায়</t>
+  </si>
+  <si>
+    <t>তুঁই যহন আঁর মাথাত আত বুলাই দও, তহন আঁর মনোত্তুন বিয়াক দুখ চলি যায়</t>
+  </si>
+  <si>
+    <t>শরীরে ভিটামিনের অভাবে চুল পড়ে যাচ্ছে, ডাক্তার সাপ্লিমেন্ট নিতে বললেন</t>
+  </si>
+  <si>
+    <t>শরীরুত ভিটেমিনুর অভাবে চুল পরি যার, ডাক্তার সাপ্লিমেন্ট লইতু হইয়্যি</t>
+  </si>
+  <si>
+    <t>আজকে আমার ছেলে প্রথমবার "বাবা" বলে ডাকল, আমার কী যে আনন্দ হচ্ছে, ভাষায় প্রকাশ করতে পারব না</t>
+  </si>
+  <si>
+    <t>আজিয়ে আঁর ফোয়া প্রথমবার বাফ হই ডেইক্কি, আত্তুন কেন যে খুশি লার ভাষায় প্রকাশ গরিত ন পাইজ্জুম</t>
+  </si>
+  <si>
+    <t>কয়েকদিন ধরে কানে একটা শোঁ শোঁ শব্দ হচ্ছে</t>
+  </si>
+  <si>
+    <t>হয়েকদিন ধরি হানুত উজ্ঞো শো শো আওয়াজ অর</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত দুশ্চিন্তা করলে মাথায় যন্ত্রণা শুরু হয়, কোনো কাজেই মন বসে না</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত দুশ্চিন্তে গরিলি মাথাত যন্ত্রনা শুরু অয়, হনো হাজুত মন ন বইয়্যি</t>
+  </si>
+  <si>
+    <t>আমি খেয়াল করলাম, তুমি কয়েকদিন ধরে মনমরা হয়ে বসে আছো</t>
+  </si>
+  <si>
+    <t>আঁই খিয়াল গইজ্জি, তুঁই হয়েকদিন ধরি মনমরা অই বই থেইক্কো</t>
+  </si>
+  <si>
+    <t>কোনো সমস্যা হয়ে থাকলে আমাকে বলতে পার, আমি তোমাকে সাহায্য করব</t>
+  </si>
+  <si>
+    <t>হনো সমস্যা অই থাহিলি আঁরে হইত পারো, আঁই তোঁয়ারে সাহায্য গইজ্জুম</t>
+  </si>
+  <si>
+    <t>তুমি মনমরা হয়ে বসে থাকলে কি আমার ভালো লাগে?</t>
+  </si>
+  <si>
+    <t>তুঁই মনমরা অই বই থাহিলি কি আত্তুন ভালা লাগে?</t>
+  </si>
+  <si>
+    <t>আমার ছেলেটার কাল সারা রাত জ্বর ছিল, এখনো কমেনি</t>
+  </si>
+  <si>
+    <t>আঁর ফোওয়ার হালিয়ে সারা রাইত জ্বর আছিল, এহনো ন হমে</t>
+  </si>
+  <si>
+    <t>শরীর সুস্থ না থাকলে পৃথিবীর সব সম্পদ থাকলেও কোনো আনন্দ পাওয়া যায় না</t>
+  </si>
+  <si>
+    <t>শরীর সুস্থ ন থাহিলি পৃথিবীর বিয়াক সম্পদ থাহিলিও হনো আনন্দ পন ন যায়</t>
+  </si>
+  <si>
+    <t>সুস্থতা হলো আল্লাহর অনেক বড় নিয়ামত, এটা যারা অসুস্থ একমাত্র তারাই ভালো বুঝবে</t>
+  </si>
+  <si>
+    <t>সুস্থতা অইলু দে আল্লার বত বরো নিয়ামত, ইয়েন যারা অসুস্থ একমাত্র ইতারাই ভালা বুঝিবু</t>
+  </si>
+  <si>
+    <t>আমাদের জীবনটা অনেক ছোট, তাই যতদিন বেঁচে আছি ভালো কাজ করা দরকার</t>
+  </si>
+  <si>
+    <t>আঁরার জীবন ইয়েন বত ছোডো, এতেল্লে যতদিন বাছি আছি ভালা হাজ গরন দরহার</t>
+  </si>
+  <si>
+    <t>যাদের মনে ময়লা আছে, তাদেরকে আমি পছন্দ করি না</t>
+  </si>
+  <si>
+    <t>যারার মনুত হাছারা আছে ইতারারে আঁই পছন্দ ন গরি</t>
+  </si>
+  <si>
+    <t>১০টা খারাপ বন্ধুর চেয়ে একটা ভালো বন্ধু হলেই যথেষ্ট</t>
+  </si>
+  <si>
+    <t>দশশো হারাপ বন্ধুর চাইতে উজ্ঞো ভালা বন্ধু অইলিই যথেষ্ট</t>
+  </si>
+  <si>
+    <t>এই জায়গাটা আমার অনেক প্রিয়। আমার যখন মন খারাপ থাকে, তখন আমি এখানে এসে বসে থাকি</t>
+  </si>
+  <si>
+    <t>এই জাগা ইয়েন আঁর বত প্রিয়, আঁর যহন মন হারাপ থাহে তহন আঁই এনডে আই বই থাহি</t>
+  </si>
+  <si>
+    <t>দেখ, যা হওয়ার হয়ে গেছে, এখন মন খারাপ করে কোনো লাভ হবে না</t>
+  </si>
+  <si>
+    <t>চা, যা অইবের অই গেইয়্যি, এহন মন হারাপ গরি হনো লাভ ন অইবু</t>
+  </si>
+  <si>
+    <t>মাছ খেতে গিয়ে গলায় কাঁটা আটকে গেছে, এখন অনেক কষ্ট পাচ্ছি</t>
+  </si>
+  <si>
+    <t>মাছ হাইতু যায় গলাত কেডা আটকি গেইয়্যি, এহন বত হষ্ট ফাইর</t>
+  </si>
+  <si>
+    <t>ইলিশ মাছ আমার খুব মজা লাগে, কিন্তু কাঁটা বেশি হওয়ার কারণে খেতে মন চায় না</t>
+  </si>
+  <si>
+    <t>ইলিশ মাছ আত্তুন বত মজা লাগে, কিন্তু কেডা বেশি অইবের হারনে হাইতু মন ন চায়</t>
+  </si>
+  <si>
+    <t>রাতে না খেয়ে ঘুমালে সকালে উঠে দুর্বল লাগবে</t>
+  </si>
+  <si>
+    <t>রাতিয়ে ন হায় ঘুমাইলি বেইন্নে উডি দুর্বল লাগিবু</t>
+  </si>
+  <si>
+    <t>খেতে মন না চাইলেও কিছু খেয়ে নে, নাহয় বিছানা থেকে উঠতে পারবি না</t>
+  </si>
+  <si>
+    <t>হাইতু মন ন চাইলিও কিছু হায় ল, নইলি বিছেনুত্তুন উডিত ন পারিবি</t>
+  </si>
+  <si>
+    <t>জ্বর হওয়ার কারণে মুখের রুচি চলে গেছে, তাই এখন কোনো কিছুর স্বাদ লাগছে না</t>
+  </si>
+  <si>
+    <t>জ্বর অইবের হারনে মুখুর রুচি চলি গেইয়্যি, এতেল্লে এহন হনো কিছুর স্বাদ ন লাগের</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত গরমে কাজ করলে শরীর থেকে পানি বেরিয়ে যায়</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত গরমুত হাজ গরিলি শরীরুত্তুন পানি বাইর অই যায়</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত বৃষ্টি পড়ার কারণে চারদিকে পানি উঠে গেছে</t>
+  </si>
+  <si>
+    <t>অতিরিক্ত ঝর ফরিবের হারনে চেরিমিক্কে পানি উডি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>শেষ কবে রোদ দেখেছি  মনে নেই আমার</t>
+  </si>
+  <si>
+    <t>শেষ হত্তে রইদ দেইক্কি মনুত নেই আত্তুন</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টির দিনে সবাই মিলে লুডু খেললে মন একদম ভালো হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এই বৃষ্টির দিনুত বিয়াজ্ঞুন মিলি লুডু খেলিলি মন এব্বেরে ভালা অই যাইবু</t>
+  </si>
+  <si>
+    <t>খেলায় হার-জিত থাকে, তাই বলে মন খারাপ করে থাকবে?</t>
+  </si>
+  <si>
+    <t>খেলাত হার-জিত থাহে, তাই বলি মন হারাপ গরি থাহিবে?</t>
+  </si>
+  <si>
+    <t>মুখে মুখে কথা বললে তো মাথা এমনিতেই খারাপ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>মুখে মুখে হতা হইলি তো মাথা এনেই হারাপ অই যাইবু</t>
+  </si>
+  <si>
+    <t>দেখো, আমার তোমার সঙ্গে মুখ লাগানোর কোনো ইচ্ছা নেই। এমনিতেই মন-মেজাজ ভালো না</t>
+  </si>
+  <si>
+    <t>স, আত্তুন তোঁয়ার লগে মুখ লাগাইবের হনো ইচ্ছে নেই, এনেই মন-মেজাজ ভালা নো</t>
+  </si>
+  <si>
+    <t>ঘরে শান্তি না থাকলে কি আর কোনো কিছু ভালো লাগে?</t>
+  </si>
+  <si>
+    <t>ঘরুত শান্তি ন থাহিলি কি আর হনো কিছু ভালা লাগে?</t>
+  </si>
+  <si>
+    <t>গত এক সপ্তাহ ধরে একটানা কাজ করে এখন একদম ক্লান্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>গত এক সপ্তাহ ধরি একটানা হাম গরি এহন এব্বেরে অরান অই গেই</t>
+  </si>
+  <si>
+    <t>গাছ থেকে পড়লে একদম হাত-পা ভেঙে যাবে</t>
+  </si>
+  <si>
+    <t>গাছুত্তুন ফরিলি এব্বেরে আত-টেং ভাঙি যাইবু</t>
+  </si>
+  <si>
+    <t>তোকে এত ওপরে কে উঠতে বলছে?</t>
+  </si>
+  <si>
+    <t>তোরে এল্লেত উরে হনে উইঠতো হইয়্যি দে?</t>
+  </si>
+  <si>
+    <t>গাছপাকা আম খেয়ে মন একদম ভালো হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>গাছফোওয়ানা আম হাই মন একদম ভালা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এটা গাছপাকা কাঁঠাল, তাই দাম বেশি হবে</t>
+  </si>
+  <si>
+    <t>ইবে গাছফোওয়ানা হাট্টল, এতেল্লে দাম বেশি অইবু</t>
+  </si>
+  <si>
+    <t>ঝড়ের সঙ্গে প্রচুর পরিমাণে বাতাস, মনে হয় এবার বন্যা আসবে</t>
+  </si>
+  <si>
+    <t>ঝরুর লগে প্রচুর পরিমানে বাতাস, মনে অই এবার বন্যা অইবু</t>
+  </si>
+  <si>
+    <t>বাতাসের কারণে আমার গাছের সব আম পড়ে গেছে</t>
+  </si>
+  <si>
+    <t>বাতাসুর হারনে আঁর গাছুর বিয়াক আম পরি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>এবার আমার ব্যবসায় একদম লস হবে, সব পেঁয়াজ পচে গেছে</t>
+  </si>
+  <si>
+    <t>এবার আঁর ব্যবসাত এব্বেরে লস অইবু, বিয়াক পিয়েজ পুচি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>তোমার কথা আমার অনেক মনে পড়ে, কিন্তু সেটা আমি প্রকাশ করি না</t>
+  </si>
+  <si>
+    <t>তোঁয়ার হতা আত্তুন বত মনুত পরে, কিন্তু ইয়েন আঁই প্রকাশ ন গরি</t>
+  </si>
+  <si>
+    <t>তুমি চলে যাওয়ার পর থেকে ঘরটা একদম খালি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>তুঁই চলি যাইবের পরুত্তুন ঘর ইয়েন এব্বেরে হালি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বাচ্চারা শুধু তোমার কথাই জিজ্ঞেস করে</t>
+  </si>
+  <si>
+    <t>বাইচ্চে অক্কল উধো তোঁয়ার হতাই ফুসর লই</t>
+  </si>
+  <si>
+    <t>তুমি মন খারাপ করো না, আমি কয়েক দিনের মধ্যে চলে আসব</t>
+  </si>
+  <si>
+    <t>তুঁই মন হারাপ ন গইজ্জো, আঁই হয়েকদিনুর মধ্যে চলি আইসসুম</t>
+  </si>
+  <si>
+    <t>আমি বের হচ্ছি, এখন এভাবে মুখ কালো করে থাকলে আমি যাব কীভাবে?</t>
+  </si>
+  <si>
+    <t>আঁই বাইর অইর, এহন এল্লেত মুখ হালা গরি থাহিলি আঁই যাইয়্যুম কেনে?</t>
+  </si>
+  <si>
+    <t>আমাদের এলাকায় রবি নেটওয়ার্ক একদম নেই</t>
+  </si>
+  <si>
+    <t>আঁরার এলাকাত রবি নেটওয়ার্ক এব্বেরে নেই</t>
+  </si>
+  <si>
+    <t>তিন দিন ধরে একটানা বৃষ্টি হচ্ছে, ঘরে বসে থাকতে আর ভালো লাগছে না</t>
+  </si>
+  <si>
+    <t>তিন দিন ধরি একটানা ঝর ফরের, ঘরুত বই থাকতে আর গম ন লার</t>
+  </si>
+  <si>
+    <t>আকাশে যে মেঘ হয়েছে, দিন নাকি রাত সেটাই বোঝা যাচ্ছে না</t>
+  </si>
+  <si>
+    <t>আকাশুত যে মৌলো অইয়্যি, দিন নাকি রাইত ইয়েনই বুঝা ন যার</t>
+  </si>
+  <si>
+    <t>তোমার মন খারাপের কারণ জানতে পারি?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার মন হারাপুর হারন জানিত পারি?</t>
+  </si>
+  <si>
+    <t>তোমার মন খারাপ দেখে তোমার জন্য বিরিয়ানি রান্না করেছি</t>
+  </si>
+  <si>
+    <t>তোঁয়ার মন হারাপ দেহি তোঁয়ার লাই বিরেনি রান্না গইজ্জি</t>
+  </si>
+  <si>
+    <t>এগুলো এখন গরম গরম খেয়ে নাও, মন ভালো হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এগিন এহন গরম গরম হাই লও, মন ভালা অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমার সঙ্গে ঝগড়া করলে কি মন ভালো হয়ে যাবে?</t>
+  </si>
+  <si>
+    <t>আঁর লগে হইজ্জে গরিলি কি মন ভালা অই যাইবু?</t>
+  </si>
+  <si>
+    <t>ঘুম থেকে ওঠার পর থেকেই মনটা কেমন জানি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>ঘুমুত্তুন উডিবের পরুত্তুনই মন ইয়েন কেন জানি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>বর্ষাকাল আসলেই আমার জন্য সমস্যা, সব কাজ বন্ধ থাকে</t>
+  </si>
+  <si>
+    <t>বর্ষাহাল আইলিই আঁর লাই সমস্যা, বিয়াক হাজ বন্ধ থাহে</t>
+  </si>
+  <si>
+    <t>তুমি আজ না যাও, তুমি চলে গেলে আমার ভালো লাগবে না</t>
+  </si>
+  <si>
+    <t>তুঁই আজিয়ে নো যও, তুঁই চলি যাইলি আত্তুন ভালা ন লাগিবু</t>
+  </si>
+  <si>
+    <t>তুমি চিন্তা করো না, আমার ফোন বন্ধ হয়ে গিয়েছিল</t>
+  </si>
+  <si>
+    <t>তুঁই চিন্তে ন গইজ্জো, আঁর ফোন বন্ধ অই গেইয়্যিল</t>
+  </si>
+  <si>
+    <t>আমার গত তিন মাস ধরে বুকে ব্যথা, মেডিকেলে গিয়ে টেস্ট করে দেখতে হবে</t>
+  </si>
+  <si>
+    <t>আঁর গত তিন মাস ধরি বুকুত ব্যথা, মেডিকেলুত যাই টেস্ট গরি চন ফরিবু</t>
+  </si>
+  <si>
+    <t>বৃষ্টিতে ভিজে এখন জ্বর চলে আসছে</t>
+  </si>
+  <si>
+    <t>বৃষ্টিত ভিজি এহন জ্বর চলি আইসসি</t>
+  </si>
+  <si>
+    <t>তোমাকে আমি বারবার বারণ করেছিলাম যে বৃষ্টিতে না ভিজতে</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে আঁই বারবার মানা গইজ্জিলাম যে বৃষ্টিত ন ভিজতু</t>
+  </si>
+  <si>
+    <t>তাড়াতাড়ি ঘরে চলে এসো, বৃষ্টিতে ভিজলে অসুখ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>তারাতারি ঘরুত চলি আইয়্যু, বৃষ্টিত ভিজিলি অসুখ অই যাইবু</t>
+  </si>
+  <si>
+    <t>মেয়েটার সারারাত জ্বর ছিল, কিছু খেতে পারেনি</t>
+  </si>
+  <si>
+    <t>মাইফুয়া ইবের আরা রাইত জ্বর আছিল, কিছু হাইত ন পারে</t>
+  </si>
+  <si>
+    <t>পায়ে খুব ব্যথা করছে, একটু টিপে দাও তো</t>
+  </si>
+  <si>
+    <t>টেং বত ব্যথা গরের, এক্কানা টিপি দও না</t>
+  </si>
+  <si>
+    <t>শরীরটা মেছমেছ করছে, কিছুক্ষণ ঘুমাতে হবে</t>
+  </si>
+  <si>
+    <t>শরীর ইয়েন মেছমেছ গরের, এক্কানা ঘুম যন ফরিবু</t>
+  </si>
+  <si>
+    <t>মাগরিবের আজান হচ্ছে, এখন বিছানা থেকে উঠে একটু বসো</t>
+  </si>
+  <si>
+    <t>মাগরিবুর আজান দের, এহন বিছেনুত্তুন উডি এক্কানা বইয়্যো</t>
+  </si>
+  <si>
+    <t>মসজিদে গিয়ে নামাজ পড়ে আসো, দেখবে মন ভালো হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>মসইদুত যাই নামাজ ফরি আইয়্যো, দেহিবে মন ভালা অই যাইবু</t>
+  </si>
+  <si>
+    <t>প্রতিদিন একই কাজ করতে করতে বিরক্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>ফইত্তোদিন একই হাজ গত্তে গত্তে বিরক্ত অই গেই</t>
+  </si>
+  <si>
+    <t>আমার ল্যাপটপ এখন বন্ধ হয়ে যাবে, অনেকক্ষণ ধরে কারেন্ট নেই</t>
+  </si>
+  <si>
+    <t>আঁর লেপটপ এহন বন্ধ অই যাইবু, বত হতক্ষন ধরি কারোন নাই</t>
+  </si>
+  <si>
+    <t>দাদুকে অনেক মিস করি, দাদু মারা যাওয়ার পর থেকে ঘরটা কেমন জানি অন্ধকার হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>দাদারে বত মিস গরির, দাদা মরি যাইবের পরুত্তুন ঘর ইয়েন কেন জানি আধার অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>নতুন জামা কিনলে আমার মন একদম ভালো হয়ে যায়</t>
+  </si>
+  <si>
+    <t>নতুন হুত্তা কিনিলি আঁর মন এব্বেরে ভালা অই যায়</t>
+  </si>
+  <si>
+    <t>সুলতান'স ডাইন থেকে কাচ্চি না খাওয়ালে আমার মন ভালো হবে না</t>
+  </si>
+  <si>
+    <t>সুলতান'স ডাইন উত্তুন কাচ্চি ন হাওয়াইলি আঁর মন ভালা অইতু নো</t>
+  </si>
+  <si>
+    <t>চল, আজ সুলতান'স ডাইন থেকে কাচ্চি বিরিয়ানি খেয়ে আসি</t>
+  </si>
+  <si>
+    <t>চল, আজিয়ে সুলতান'স ডাইন উত্তুন কাচ্চি বিরেনি হাই আই</t>
+  </si>
+  <si>
+    <t>শুনলাম এখন নাকি ওখানকার কাচ্চি আগের মতো আর ভালো না</t>
+  </si>
+  <si>
+    <t>উইন্নি এহন বলে অনডের কাচ্চি আগুর মতন আর ভালা নো</t>
+  </si>
+  <si>
+    <t>মন খারাপ থাকলে বন্ধুদের সঙ্গে ঘুরে আয়</t>
+  </si>
+  <si>
+    <t>মন হারাপ থাহিলি বন্ধু অক্কলুর লগে ঘুরি আয়</t>
+  </si>
+  <si>
+    <t>তোকে দেখলেই আমার মাথা গরম হয়ে যায়</t>
+  </si>
+  <si>
+    <t>তোরে দেহিলিই আঁর মাথা গরম অই যাই</t>
+  </si>
+  <si>
+    <t>তুই আমার চোখের সামনে থেকে সরে যা</t>
+  </si>
+  <si>
+    <t>তুই আঁর চোখুর সামনুত্তুন সরি যা</t>
+  </si>
+  <si>
+    <t>তুই কি এখন যাবি, নাকি আমার কাছে মার খাবি?</t>
+  </si>
+  <si>
+    <t>তুই কি এহন যাবি, নাকি আঁর হাছে মাইর হাবি?</t>
+  </si>
+  <si>
+    <t>তোর আব্বুর মাথা এখন গরম, তাই এখন ঘরে আসিস না</t>
+  </si>
+  <si>
+    <t>তোর বাফুর মাথা এহন গরম, এতেল্লে এহন ঘরুত ন আইস</t>
+  </si>
+  <si>
+    <t>ওরা অনেক কিছুই বলবে, ওদের কথায় কান দিয়ে লাভ নেই</t>
+  </si>
+  <si>
+    <t>ইতারা বত কিছুই হইবু, ইতারার হথাত হান দি লাভ নেই</t>
+  </si>
+  <si>
+    <t>পাগলে কী না বলে, আর ছাগলে কী না খায়</t>
+  </si>
+  <si>
+    <t>ফঅলে কী নহয় আর ছঅলে কী ন হায়</t>
+  </si>
+  <si>
+    <t>তুই কি পাগল হয়ে গেছিস! এসব কী বলিস?</t>
+  </si>
+  <si>
+    <t>তুই কি ফঅল  অই গেইয়্যুস! এগিন কি হস?</t>
+  </si>
+  <si>
+    <t>আম্মু যদি কোনোভাবে জেনে যায়, তাহলে অনেক সমস্যা হবে</t>
+  </si>
+  <si>
+    <t>আম্মু যদি হনোভাবে জানি যায়, তইলি বত সমস্যা অইবু</t>
+  </si>
+  <si>
+    <t>রিয়াল মাদ্রিদ হেরে যাওয়াতে মনটা খারাপ হয়ে গেল</t>
+  </si>
+  <si>
+    <t>রিয়াল মাদ্রিদ অডি যনে মন ইয়েন হারাপ অই গেল</t>
+  </si>
+  <si>
+    <t>আজ রিয়াল মাদ্রিদের খেলা আছে রাতে</t>
+  </si>
+  <si>
+    <t>আজিয়ে রিয়াল মাদ্রিদুর খেলা আছে রাতিয়ে</t>
+  </si>
+  <si>
+    <t>আমাদের বাসায় একটা বড় টিভি আছে, সবাই একসঙ্গে খেলা দেখব</t>
+  </si>
+  <si>
+    <t>আঁরার বাসাত বরো টিভি আছে, বিয়াজ্ঞুন একলগে খেলা চাইয়্যুম</t>
+  </si>
+  <si>
+    <t>সামনে ফুটবল বিশ্বকাপ, তাই নতুন টিভি কিনে এনেছি</t>
+  </si>
+  <si>
+    <t>সাম্মোদ্দি ফটবল বিশ্বকাপ, এতেল্লে নতুন টিভি কিনি এইন্নি</t>
+  </si>
+  <si>
+    <t>তোমার পরীক্ষা ভালো হয়েছে দেখে আমার মন এমনিতেই ভালো হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>তোঁয়ার পরীক্ষে ভালা অইয়্যি দেহি আঁর মন এনেই ভালা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>ঘরে টিভি আনলে ছেলেমেয়ের লেখাপড়ার ক্ষতি হবে</t>
+  </si>
+  <si>
+    <t>ঘরুত টিভি আনিলি ফোওয়াচার লেহাপরার হতি অইবু</t>
+  </si>
+  <si>
+    <t>বাচ্চাদের পরীক্ষা সামনে, এমন সময় ঘরে টিভি আনার কী দরকার ছিল?</t>
+  </si>
+  <si>
+    <t>বাইচ্চে অক্কলুর পরীক্ষে সাম্মোদ্দি, এন সমত ঘরুত টিভি আনিবের কি দরহার আছিল?</t>
+  </si>
+  <si>
+    <t>যদি ওদের পরীক্ষা খারাপ হয়, তাহলে আমি তোমাকেই ধরব</t>
+  </si>
+  <si>
+    <t>যদি ইতারার পরীক্ষে হারাপ অয়, তইলি আঁই তোঁয়ারেই ধইজ্জুম</t>
+  </si>
+  <si>
+    <t>এভাবে মন খারাপ করে থাকলে সামনের পরীক্ষাগুলোও খারাপ হবে</t>
+  </si>
+  <si>
+    <t>এল্লেত মন হারাপ গরি থাহিলি সামনুর পরীক্ষে এগুনও হারাপ অইবু</t>
+  </si>
+  <si>
+    <t>পরীক্ষা একটা খারাপ হয়েছে তো কী হয়েছে, সামনেরগুলো ভালো করে দাও</t>
+  </si>
+  <si>
+    <t>পরীক্ষে উজ্ঞো হারাপ অইয়্যি তো কি অইয়্যি, সামনুর এগুন ভালা গরি দও</t>
+  </si>
+  <si>
+    <t>এভাবে ভেঙে পড়লে হবে না, সবকিছু ভুলে গিয়ে সামনে এগোতে হবে</t>
+  </si>
+  <si>
+    <t>এল্লেত ভাঙি পরিলি ন অইবু, বিয়াক কিছু ভুলি যাই সামনে আগন ফরিবু</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে আল্লাহ আমাদের কাছ থেকে বিপদের মাধ্যমে পরীক্ষা নেন</t>
+  </si>
+  <si>
+    <t>মাঝে মাঝে আল্লাহ আরাত্তুন বিপদুর মাধ্যমে পরীক্ষে লই</t>
+  </si>
+  <si>
+    <t>আমাদেরকে বিপদের সময় ভেঙে না পড়ে সবর করতে হবে</t>
+  </si>
+  <si>
+    <t>আরাত্তুন বিপদুর সমত ভাঙি ন পরি সবর গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>চাকরি একটা চলে গেছে তো কী হয়েছে, আল্লাহ চাইলে আরও ভালো চাকরি আসবে</t>
+  </si>
+  <si>
+    <t>চরি এক্কান চলি গেইয়্যি তো কী অইয়্যি, আল্লাহ চাইলি আরো ভালা চরি আইবু</t>
+  </si>
+  <si>
+    <t>অতীতে কী হয়েছে সেটা না ভেবে সামনে কী হবে, সেটা চিন্তা করতে হবে</t>
+  </si>
+  <si>
+    <t>অতীতুত কি অইয়্যি ইয়েন ন ভাবি সামনে কি অইবু ইয়েন চিন্তে গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>যারা অতীত নিয়ে পড়ে থাকে, ওরা সামনে এগোতে পারে না</t>
+  </si>
+  <si>
+    <t>যারা অতীত লই ফরি থাহে ইতারা সামনে আগাইত ন পারে</t>
+  </si>
+  <si>
+    <t>আমাদের এখানে আগে ঠিক ছিল, এখন বেশি সমস্যা করছে</t>
+  </si>
+  <si>
+    <t>আঁরার এনডে আগে ঠিক আছিল, এহন বেশি সমস্যা গরের</t>
+  </si>
+  <si>
+    <t>সারাদিন কারেন্ট ছিল না, এখন একটু এসেছে, আবারও চলে গেছে</t>
+  </si>
+  <si>
+    <t>আরাদিন কারোন ন আছিল, এহন এক্কানা আইসসি, আবারও চলি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>ফুটবল খেলে পা একদম ব্যথা হয়ে গেছে, এখন হাঁটতেও পারছি না</t>
+  </si>
+  <si>
+    <t>ফুটবল খেলি টেং এব্বেরে ব্যথা অই গেইয়্যি, এহন আডিতও ন পারির</t>
+  </si>
+  <si>
+    <t>বল আস্তে মারিস, আমার পায়ে অনেক ব্যথা</t>
+  </si>
+  <si>
+    <t>বল আস্তে মারিস, আঁর টেং উত বত ব্যথা</t>
+  </si>
+  <si>
+    <t>শুরুতে সবকিছু ঠিক ছিল, এখন আস্তে আস্তে সবকিছু কেমন জানি হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>শুরুদ্দি বিয়াক কিছু ঠিক আছিল, এহন আস্তে আস্তে বিয়াক কিছু কেন জানি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার শুরু থেকেই ওর ওপর সন্দেহ ছিল</t>
+  </si>
+  <si>
+    <t>আঁর শুরুদ্দিত্তুনই ইতের উদ্দি সন্দেহ আছিল</t>
+  </si>
+  <si>
+    <t>বারবার বলেছি, শহরে গেলে মোবাইল সাবধানে রাখতে</t>
+  </si>
+  <si>
+    <t>বারবার হইলাম শরুত গেলি মোবাইল সাবধানে রাখতো</t>
+  </si>
+  <si>
+    <t>আমার কথা না শুনলে এমনই হবে</t>
+  </si>
+  <si>
+    <t>আঁর হতা ন উনিলি এরহমই অইবু</t>
+  </si>
+  <si>
+    <t>ঘরের দরজা খোলা ছিল, তাই চোর সহজেই ঘরে ঢুকতে পেরেছিল</t>
+  </si>
+  <si>
+    <t>ঘরুর দরজা খোলা আছিল, এতেল্লে চোর সহজেই ঘরুত ঢুকিত পেইজ্জিল</t>
+  </si>
+  <si>
+    <t>মোবাইল হারিয়ে গেছে, সেটার জন্য চিন্তা হচ্ছে না, আমার গুরুত্বপূর্ণ ডকুমেন্টগুলোর জন্য চিন্তা হচ্ছে</t>
+  </si>
+  <si>
+    <t>মোবাইল আঝি গেইয়্যি ইয়েন উর লাই চিন্তে ন অর, আঁর গুরুত্বপূর্ণ ডকুমেন্টস এগিনুর লাই চিন্তে লার</t>
+  </si>
+  <si>
+    <t>পরীক্ষা তো শেষ হয়ে গেল, আজকের পর থেকে আমাদের আর দেখা হবে না</t>
+  </si>
+  <si>
+    <t>পরীক্ষে তো শেষ অই গেল, আজিয়ের পর উত্তুন আঁরার আর দেহা অইতু ন</t>
+  </si>
+  <si>
+    <t>আমার ভাবতেই অবাক লাগে, চারটা বছর কত দ্রুত চলে গেল</t>
+  </si>
+  <si>
+    <t>আত্তুন ভাবতেই অবাক লাগে চেইরগান বছর হতো দ্রুত চলি গেল</t>
+  </si>
+  <si>
+    <t>এই চার বছরে যদি কারও মনে কোনো কষ্ট দিয়ে থাকি, তাহলে ক্ষমা করে দিস</t>
+  </si>
+  <si>
+    <t>এই চেইর বছরে যদি কিয়ার মনুত হনো হষ্ট দি থাহি তইলি ক্ষমা গরি দিস</t>
+  </si>
+  <si>
+    <t>সবার জন্য মন থেকে দোয়া আর ভালোবাসা থাকবে</t>
+  </si>
+  <si>
+    <t>বিয়াগুনুর লাই মনুত্তুন দোয়া আর ভালোবাসা থাহিবু</t>
+  </si>
+  <si>
+    <t>আমি যদি আগে বুঝতাম, তাহলে ওইদিকে যেতাম না</t>
+  </si>
+  <si>
+    <t>আঁই যদি আগে বুঝিতাম তইলি ওনদি ন যাইতাম</t>
+  </si>
+  <si>
+    <t>ছেলেটাকে প্রথমে আমি খারাপ মনে করেছিলাম, এখন আমার ভুল ভেঙে গেছে</t>
+  </si>
+  <si>
+    <t>ফোওয়া ইবেরে প্রথমে আঁই হারাপ মনে গইজ্জিলাম, এহন আঁর ভুল ভাঙি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমি তোমাকে অনেক কষ্ট দিয়েছি, আমাকে ক্ষমা করে দিও</t>
+  </si>
+  <si>
+    <t>আঁই তোঁয়ারে বত হষ্ট দিইয়্যি, আঁরে ক্ষমা গরি দিও</t>
+  </si>
+  <si>
+    <t>এভাবে বোকার মতো আমার দিকে না তাকিয়ে কাজ করো</t>
+  </si>
+  <si>
+    <t>এল্লেত বেকুবুর মতো আঁর মিক্কে ন চাই হাজ গরো</t>
+  </si>
+  <si>
+    <t>আমার অর্ধেক কাজ শেষ হয়ে গেছে, বাকি অর্ধেক পরে করব</t>
+  </si>
+  <si>
+    <t>আঁর অদ্ধক হাজ শেষ অই গেইয়্যি, বাকি অদ্ধক পরে গইজ্জুম</t>
+  </si>
+  <si>
+    <t>অর্ধেক কাজ করেই যেভাবে হাঁপিয়ে উঠেছি, বাকি কাজ কখন শেষ করব কে জানে</t>
+  </si>
+  <si>
+    <t>অদ্ধক হাজ গরিই যেন গরি হাপাই উইট্টি, বাকি হাজ হত্তে শেষ গইজ্জুম হনে জানে</t>
+  </si>
+  <si>
+    <t>আমার মতো ছাতা দেখি তোরও একটা আছে</t>
+  </si>
+  <si>
+    <t>আঁর মতন ছাতি দেহি তোত্তুনও এক্কান আছে</t>
+  </si>
+  <si>
+    <t>তোর ব্যাগটা কোথা থেকে কিনেছিস? অনেক সুন্দর হয়েছে</t>
+  </si>
+  <si>
+    <t>তোর ব্যাগ ইবে হত্তুন কিন্নুস? বত সুন্দর অইয়্যি</t>
+  </si>
+  <si>
+    <t>তোর মোবাইলটা কি আমার কাছে বিক্রি করবি? আমার একটা মোবাইল দরকার</t>
+  </si>
+  <si>
+    <t>তোর মোবাইল ইবে কি আঁর হাছে বেছিবি? আত্তুন উজ্ঞো মোবাইল দরহার</t>
+  </si>
+  <si>
+    <t>এটা কিনেছি বেশিদিন হয়নি, সে জন্য এখন বিক্রি করব না</t>
+  </si>
+  <si>
+    <t>ইবে কিন্নি বেশিদিন ন অর, এতেল্লে এহন বেইছতাম নো</t>
+  </si>
+  <si>
+    <t>ওর কথায় কিছু মনে করিস না, ওর মাথায় একটু সমস্যা আছে</t>
+  </si>
+  <si>
+    <t>ইতের হথায় কিছু মনে ন গরিস, ইতের মাথাত এক্কানা সমস্যা আছে</t>
+  </si>
+  <si>
+    <t>আচ্ছা, ও কি সবার সঙ্গেই এমন খারাপ ব্যবহার করে?</t>
+  </si>
+  <si>
+    <t>আইচ্ছে, ইবে কি বিয়াজ্ঞুনুর লগেই এন হারাপ বেবার গরে?</t>
+  </si>
+  <si>
+    <t>ভাই, আমি কি তোমাকে চিনি?</t>
+  </si>
+  <si>
+    <t>বদ্দা, আঁই কি তোঁয়ারে চিনি?</t>
+  </si>
+  <si>
+    <t>পাগলের সুখ নাকি মনে মনে</t>
+  </si>
+  <si>
+    <t>ফঅলুর সুখ বলে মনে মনে</t>
+  </si>
+  <si>
+    <t>এই মেয়েটা থেকে দূরে থাকিস, এর মতিগতি ভালো না</t>
+  </si>
+  <si>
+    <t>এই মাইফোওয়া ইবেত্তুন দূরে থাহিস, ইবের মতিগতি ভালা নো</t>
+  </si>
+  <si>
+    <t>তোমাকে আমি অনেক বিশ্বাস করি, দয়া করে এমন করো না</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে আঁই বত বিশ্বাস গরি, দয়া গরি এরহম ন গইজ্জো</t>
+  </si>
+  <si>
+    <t>আমাদের গ্রামে অনেকগুলো পুকুর আছে, পুকুরগুলোতে অনেক মাছ আছে</t>
+  </si>
+  <si>
+    <t>আঁরার গ্রামুত বত হদুজ্ঞুন ফইর আছে, ফইর এগুনুত বত মাছে আছে</t>
+  </si>
+  <si>
+    <t>অজু করতে কি এক বালতি পানি লাগে!</t>
+  </si>
+  <si>
+    <t>অজু গত্তে কি এক বালতি পানি লাগে!</t>
+  </si>
+  <si>
+    <t>আমার শার্টটা একটু ধুয়ে দিও তো, এটা অনেক ময়লা হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আঁর শার্ট ইবে এক্কানা ধুই দিও তো, ইবে বত হাচারা অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আমার কাপড় আমি ধোব, তোমার ধোয়ার দরকার নেই</t>
+  </si>
+  <si>
+    <t>আঁর হর আঁই ধুইয়্যুম, তোঁয়াত্তুন ধোওয়োনুর দরহার নেই</t>
+  </si>
+  <si>
+    <t>তোমার এখন থেকে কোনো কাজ করার দরকার নেই, আমি কাজের বুয়া রাখছি</t>
+  </si>
+  <si>
+    <t>তোঁয়ার এহনুত্তুন হনো হাজ গরিবের দরহার নেই, আঁই হাজুর বুয়া রাইক্কি</t>
+  </si>
+  <si>
+    <t>এগুলো শেষ করতে করতে আগামীকাল হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এগিন শেষ গত্তে গত্তে হালিয়ে অই যাইবু</t>
+  </si>
+  <si>
+    <t>আমি এখন বাড়ি চলে যাচ্ছি, বাকি কাজগুলো আগামীকাল এসে করব</t>
+  </si>
+  <si>
+    <t>আঁই এহন বারিত চলি যাইর, বাই হাম এগিন হালিয়ে আই গইজ্জুম</t>
+  </si>
+  <si>
+    <t>আমাকে আজকের কাজের টাকাগুলো দিয়ে দিন</t>
+  </si>
+  <si>
+    <t>আঁরে আজিয়ের হাজুর টিয়াগুন দি দন</t>
+  </si>
+  <si>
+    <t>তুমি কোনো চিন্তা করো না, তোমাকে প্রতিদিনের টাকা প্রতিদিনই দিয়ে দেওয়া হবে</t>
+  </si>
+  <si>
+    <t>তুঁই হনো চিন্তে ন গইজ্জো, তোঁয়ারে পইত্তোদিনুর টিয়া পইত্তোদিনই দিই দিবু</t>
+  </si>
+  <si>
+    <t>এখানে কি পানি আছে! এগুলো তো আমার পা ধুতেই শেষ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এনডে কি পানি আছে! এগিন তো আঁর টেং ধুতেই শেষ অই যাইবু</t>
+  </si>
+  <si>
+    <t>বালতিটা নিয়ে গিয়ে পাশের বাড়ির টিউবওয়েল থেকে পানি নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>বালতি ইবে লই যাই পাশুর বারির ফেইক উত্তুন পানি লই আইয়্যু</t>
+  </si>
+  <si>
+    <t>এত বড় বালতি আমি একা পারব না</t>
+  </si>
+  <si>
+    <t>এত বরো বালতি আঁই এহেল্লে পাইত্তাম নো</t>
+  </si>
+  <si>
+    <t>তোমার সঙ্গে মামুনকেও নিয়ে যাও</t>
+  </si>
+  <si>
+    <t>তোঁয়ার লগে মামুন উরেও লই যও</t>
+  </si>
+  <si>
+    <t>আলসেমি না করে তাড়াতাড়ি বাজার নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>আলসেমি ন গরি তারাতারি বাজার লই আইয়্যো</t>
+  </si>
+  <si>
+    <t>চিন্তা করছি এবার সবাইকে কাঁচা মাংস দিয়ে দেব</t>
+  </si>
+  <si>
+    <t>চিন্তে গরির এবার বিয়াজ্ঞুনুরে কেচা গুস্ত দিই দিয়্যুম</t>
+  </si>
+  <si>
+    <t>বাড়ির কাজ না করলে ম্যাম আসলে বকা দেবে</t>
+  </si>
+  <si>
+    <t>বারির হাজ ন গরিলি ম্যাম আইলি বকা দিবু</t>
+  </si>
+  <si>
+    <t>তোমার বন্ধু এত ভালো রেজাল্ট করল, আর তুমি কিনা ফেল করলা!</t>
+  </si>
+  <si>
+    <t>তোঁয়ার বন্ধু এল্লেত ভালা রেজাল্ট গইজ্জি, আর তুঁই কিনা ফেইল গইজ্জু!</t>
+  </si>
+  <si>
+    <t>বাসায় না পড়ে গেলে পরীক্ষার হলে আরেকজনের থেকে দেখে দেখে লিখতে হবে</t>
+  </si>
+  <si>
+    <t>বাসাত পরি ন গেলি পরীক্ষের হল উত আরেকজনুত্তুন সাই সাই লেহন ফরিবু</t>
   </si>
 </sst>
 </file>
@@ -19504,1204 +21304,2404 @@
       </c>
     </row>
     <row r="1302" ht="25" customHeight="1" spans="1:2">
-      <c r="A1302" s="2"/>
-      <c r="B1302" s="2"/>
+      <c r="A1302" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B1302" s="2" t="s">
+        <v>2597</v>
+      </c>
     </row>
     <row r="1303" ht="25" customHeight="1" spans="1:2">
-      <c r="A1303" s="2"/>
-      <c r="B1303" s="2"/>
+      <c r="A1303" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B1303" s="2" t="s">
+        <v>2599</v>
+      </c>
     </row>
     <row r="1304" ht="25" customHeight="1" spans="1:2">
-      <c r="A1304" s="2"/>
-      <c r="B1304" s="2"/>
+      <c r="A1304" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B1304" s="2" t="s">
+        <v>2601</v>
+      </c>
     </row>
     <row r="1305" ht="25" customHeight="1" spans="1:2">
-      <c r="A1305" s="2"/>
-      <c r="B1305" s="2"/>
+      <c r="A1305" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B1305" s="2" t="s">
+        <v>2603</v>
+      </c>
     </row>
     <row r="1306" ht="25" customHeight="1" spans="1:2">
-      <c r="A1306" s="2"/>
-      <c r="B1306" s="2"/>
+      <c r="A1306" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B1306" s="2" t="s">
+        <v>2605</v>
+      </c>
     </row>
     <row r="1307" ht="25" customHeight="1" spans="1:2">
-      <c r="A1307" s="2"/>
-      <c r="B1307" s="2"/>
+      <c r="A1307" s="2" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B1307" s="2" t="s">
+        <v>2607</v>
+      </c>
     </row>
     <row r="1308" ht="25" customHeight="1" spans="1:2">
-      <c r="A1308" s="2"/>
-      <c r="B1308" s="2"/>
+      <c r="A1308" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B1308" s="2" t="s">
+        <v>2609</v>
+      </c>
     </row>
     <row r="1309" ht="25" customHeight="1" spans="1:2">
-      <c r="A1309" s="2"/>
-      <c r="B1309" s="2"/>
+      <c r="A1309" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B1309" s="2" t="s">
+        <v>2611</v>
+      </c>
     </row>
     <row r="1310" ht="25" customHeight="1" spans="1:2">
-      <c r="A1310" s="2"/>
-      <c r="B1310" s="2"/>
+      <c r="A1310" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B1310" s="2" t="s">
+        <v>2613</v>
+      </c>
     </row>
     <row r="1311" ht="25" customHeight="1" spans="1:2">
-      <c r="A1311" s="2"/>
-      <c r="B1311" s="2"/>
+      <c r="A1311" s="2" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B1311" s="2" t="s">
+        <v>2615</v>
+      </c>
     </row>
     <row r="1312" ht="25" customHeight="1" spans="1:2">
-      <c r="A1312" s="2"/>
-      <c r="B1312" s="2"/>
+      <c r="A1312" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B1312" s="2" t="s">
+        <v>2617</v>
+      </c>
     </row>
     <row r="1313" ht="25" customHeight="1" spans="1:2">
-      <c r="A1313" s="2"/>
-      <c r="B1313" s="2"/>
+      <c r="A1313" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B1313" s="2" t="s">
+        <v>2619</v>
+      </c>
     </row>
     <row r="1314" ht="25" customHeight="1" spans="1:2">
-      <c r="A1314" s="2"/>
-      <c r="B1314" s="2"/>
+      <c r="A1314" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B1314" s="2" t="s">
+        <v>2621</v>
+      </c>
     </row>
     <row r="1315" ht="25" customHeight="1" spans="1:2">
-      <c r="A1315" s="2"/>
-      <c r="B1315" s="2"/>
+      <c r="A1315" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B1315" s="2" t="s">
+        <v>2623</v>
+      </c>
     </row>
     <row r="1316" ht="25" customHeight="1" spans="1:2">
-      <c r="A1316" s="2"/>
-      <c r="B1316" s="2"/>
+      <c r="A1316" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B1316" s="2" t="s">
+        <v>2625</v>
+      </c>
     </row>
     <row r="1317" ht="25" customHeight="1" spans="1:2">
-      <c r="A1317" s="2"/>
-      <c r="B1317" s="2"/>
+      <c r="A1317" s="2" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B1317" s="2" t="s">
+        <v>2627</v>
+      </c>
     </row>
     <row r="1318" ht="25" customHeight="1" spans="1:2">
-      <c r="A1318" s="2"/>
-      <c r="B1318" s="2"/>
+      <c r="A1318" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B1318" s="2" t="s">
+        <v>2629</v>
+      </c>
     </row>
     <row r="1319" ht="25" customHeight="1" spans="1:2">
-      <c r="A1319" s="2"/>
-      <c r="B1319" s="2"/>
+      <c r="A1319" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B1319" s="2" t="s">
+        <v>2631</v>
+      </c>
     </row>
     <row r="1320" ht="25" customHeight="1" spans="1:2">
-      <c r="A1320" s="2"/>
-      <c r="B1320" s="2"/>
+      <c r="A1320" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B1320" s="2" t="s">
+        <v>2633</v>
+      </c>
     </row>
     <row r="1321" ht="25" customHeight="1" spans="1:2">
-      <c r="A1321" s="2"/>
-      <c r="B1321" s="2"/>
+      <c r="A1321" s="2" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B1321" s="2" t="s">
+        <v>2635</v>
+      </c>
     </row>
     <row r="1322" ht="25" customHeight="1" spans="1:2">
-      <c r="A1322" s="2"/>
-      <c r="B1322" s="2"/>
+      <c r="A1322" s="2" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B1322" s="2" t="s">
+        <v>2637</v>
+      </c>
     </row>
     <row r="1323" ht="25" customHeight="1" spans="1:2">
-      <c r="A1323" s="2"/>
-      <c r="B1323" s="2"/>
+      <c r="A1323" s="2" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B1323" s="2" t="s">
+        <v>2639</v>
+      </c>
     </row>
     <row r="1324" ht="25" customHeight="1" spans="1:2">
-      <c r="A1324" s="2"/>
-      <c r="B1324" s="2"/>
+      <c r="A1324" s="2" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B1324" s="2" t="s">
+        <v>2641</v>
+      </c>
     </row>
     <row r="1325" ht="25" customHeight="1" spans="1:2">
-      <c r="A1325" s="2"/>
-      <c r="B1325" s="2"/>
+      <c r="A1325" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B1325" s="2" t="s">
+        <v>2643</v>
+      </c>
     </row>
     <row r="1326" ht="25" customHeight="1" spans="1:2">
-      <c r="A1326" s="2"/>
-      <c r="B1326" s="2"/>
+      <c r="A1326" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B1326" s="2" t="s">
+        <v>2645</v>
+      </c>
     </row>
     <row r="1327" ht="25" customHeight="1" spans="1:2">
-      <c r="A1327" s="2"/>
-      <c r="B1327" s="2"/>
+      <c r="A1327" s="2" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B1327" s="2" t="s">
+        <v>2647</v>
+      </c>
     </row>
     <row r="1328" ht="25" customHeight="1" spans="1:2">
-      <c r="A1328" s="2"/>
-      <c r="B1328" s="2"/>
+      <c r="A1328" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B1328" s="2" t="s">
+        <v>2649</v>
+      </c>
     </row>
     <row r="1329" ht="25" customHeight="1" spans="1:2">
-      <c r="A1329" s="2"/>
-      <c r="B1329" s="2"/>
+      <c r="A1329" s="2" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B1329" s="2" t="s">
+        <v>2651</v>
+      </c>
     </row>
     <row r="1330" ht="25" customHeight="1" spans="1:2">
-      <c r="A1330" s="2"/>
-      <c r="B1330" s="2"/>
+      <c r="A1330" s="2" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B1330" s="2" t="s">
+        <v>2653</v>
+      </c>
     </row>
     <row r="1331" ht="25" customHeight="1" spans="1:2">
-      <c r="A1331" s="2"/>
-      <c r="B1331" s="2"/>
+      <c r="A1331" s="2" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>2655</v>
+      </c>
     </row>
     <row r="1332" ht="25" customHeight="1" spans="1:2">
-      <c r="A1332" s="2"/>
-      <c r="B1332" s="2"/>
+      <c r="A1332" s="2" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B1332" s="2" t="s">
+        <v>2657</v>
+      </c>
     </row>
     <row r="1333" ht="25" customHeight="1" spans="1:2">
-      <c r="A1333" s="2"/>
-      <c r="B1333" s="2"/>
+      <c r="A1333" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B1333" s="2" t="s">
+        <v>2659</v>
+      </c>
     </row>
     <row r="1334" ht="25" customHeight="1" spans="1:2">
-      <c r="A1334" s="2"/>
-      <c r="B1334" s="2"/>
+      <c r="A1334" s="2" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B1334" s="2" t="s">
+        <v>2661</v>
+      </c>
     </row>
     <row r="1335" ht="25" customHeight="1" spans="1:2">
-      <c r="A1335" s="2"/>
-      <c r="B1335" s="2"/>
+      <c r="A1335" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1335" s="2" t="s">
+        <v>2663</v>
+      </c>
     </row>
     <row r="1336" ht="25" customHeight="1" spans="1:2">
-      <c r="A1336" s="2"/>
-      <c r="B1336" s="2"/>
+      <c r="A1336" s="2" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B1336" s="2" t="s">
+        <v>2665</v>
+      </c>
     </row>
     <row r="1337" ht="25" customHeight="1" spans="1:2">
-      <c r="A1337" s="2"/>
-      <c r="B1337" s="2"/>
+      <c r="A1337" s="2" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B1337" s="2" t="s">
+        <v>2667</v>
+      </c>
     </row>
     <row r="1338" ht="25" customHeight="1" spans="1:2">
-      <c r="A1338" s="2"/>
-      <c r="B1338" s="2"/>
+      <c r="A1338" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B1338" s="2" t="s">
+        <v>2669</v>
+      </c>
     </row>
     <row r="1339" ht="25" customHeight="1" spans="1:2">
-      <c r="A1339" s="2"/>
-      <c r="B1339" s="2"/>
+      <c r="A1339" s="2" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B1339" s="2" t="s">
+        <v>2671</v>
+      </c>
     </row>
     <row r="1340" ht="25" customHeight="1" spans="1:2">
-      <c r="A1340" s="2"/>
-      <c r="B1340" s="2"/>
+      <c r="A1340" s="2" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B1340" s="2" t="s">
+        <v>2673</v>
+      </c>
     </row>
     <row r="1341" ht="25" customHeight="1" spans="1:2">
-      <c r="A1341" s="2"/>
-      <c r="B1341" s="2"/>
+      <c r="A1341" s="2" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B1341" s="2" t="s">
+        <v>2675</v>
+      </c>
     </row>
     <row r="1342" ht="25" customHeight="1" spans="1:2">
-      <c r="A1342" s="2"/>
-      <c r="B1342" s="2"/>
+      <c r="A1342" s="2" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B1342" s="2" t="s">
+        <v>2677</v>
+      </c>
     </row>
     <row r="1343" ht="25" customHeight="1" spans="1:2">
-      <c r="A1343" s="2"/>
-      <c r="B1343" s="2"/>
+      <c r="A1343" s="2" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B1343" s="2" t="s">
+        <v>2679</v>
+      </c>
     </row>
     <row r="1344" ht="25" customHeight="1" spans="1:2">
-      <c r="A1344" s="2"/>
-      <c r="B1344" s="2"/>
+      <c r="A1344" s="2" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B1344" s="2" t="s">
+        <v>2681</v>
+      </c>
     </row>
     <row r="1345" ht="25" customHeight="1" spans="1:2">
-      <c r="A1345" s="2"/>
-      <c r="B1345" s="2"/>
+      <c r="A1345" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B1345" s="2" t="s">
+        <v>2683</v>
+      </c>
     </row>
     <row r="1346" ht="25" customHeight="1" spans="1:2">
-      <c r="A1346" s="2"/>
-      <c r="B1346" s="2"/>
+      <c r="A1346" s="2" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B1346" s="2" t="s">
+        <v>2685</v>
+      </c>
     </row>
     <row r="1347" ht="25" customHeight="1" spans="1:2">
-      <c r="A1347" s="2"/>
-      <c r="B1347" s="2"/>
+      <c r="A1347" s="2" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B1347" s="2" t="s">
+        <v>2687</v>
+      </c>
     </row>
     <row r="1348" ht="25" customHeight="1" spans="1:2">
-      <c r="A1348" s="2"/>
-      <c r="B1348" s="2"/>
+      <c r="A1348" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B1348" s="2" t="s">
+        <v>2689</v>
+      </c>
     </row>
     <row r="1349" ht="25" customHeight="1" spans="1:2">
-      <c r="A1349" s="2"/>
-      <c r="B1349" s="2"/>
+      <c r="A1349" s="2" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B1349" s="2" t="s">
+        <v>2691</v>
+      </c>
     </row>
     <row r="1350" ht="25" customHeight="1" spans="1:2">
-      <c r="A1350" s="2"/>
-      <c r="B1350" s="2"/>
+      <c r="A1350" s="2" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B1350" s="2" t="s">
+        <v>2693</v>
+      </c>
     </row>
     <row r="1351" ht="25" customHeight="1" spans="1:2">
-      <c r="A1351" s="2"/>
-      <c r="B1351" s="2"/>
+      <c r="A1351" s="2" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B1351" s="2" t="s">
+        <v>2695</v>
+      </c>
     </row>
     <row r="1352" ht="25" customHeight="1" spans="1:2">
-      <c r="A1352" s="2"/>
-      <c r="B1352" s="2"/>
+      <c r="A1352" s="2" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B1352" s="2" t="s">
+        <v>2697</v>
+      </c>
     </row>
     <row r="1353" ht="25" customHeight="1" spans="1:2">
-      <c r="A1353" s="2"/>
-      <c r="B1353" s="2"/>
+      <c r="A1353" s="2" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B1353" s="2" t="s">
+        <v>2699</v>
+      </c>
     </row>
     <row r="1354" ht="25" customHeight="1" spans="1:2">
-      <c r="A1354" s="2"/>
-      <c r="B1354" s="2"/>
+      <c r="A1354" s="2" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B1354" s="2" t="s">
+        <v>2701</v>
+      </c>
     </row>
     <row r="1355" ht="25" customHeight="1" spans="1:2">
-      <c r="A1355" s="2"/>
-      <c r="B1355" s="2"/>
+      <c r="A1355" s="2" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B1355" s="2" t="s">
+        <v>2703</v>
+      </c>
     </row>
     <row r="1356" ht="25" customHeight="1" spans="1:2">
-      <c r="A1356" s="2"/>
-      <c r="B1356" s="2"/>
+      <c r="A1356" s="2" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B1356" s="2" t="s">
+        <v>2705</v>
+      </c>
     </row>
     <row r="1357" ht="25" customHeight="1" spans="1:2">
-      <c r="A1357" s="2"/>
-      <c r="B1357" s="2"/>
+      <c r="A1357" s="2" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B1357" s="2" t="s">
+        <v>2707</v>
+      </c>
     </row>
     <row r="1358" ht="25" customHeight="1" spans="1:2">
-      <c r="A1358" s="2"/>
-      <c r="B1358" s="2"/>
+      <c r="A1358" s="2" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B1358" s="2" t="s">
+        <v>2709</v>
+      </c>
     </row>
     <row r="1359" ht="25" customHeight="1" spans="1:2">
-      <c r="A1359" s="2"/>
-      <c r="B1359" s="2"/>
+      <c r="A1359" s="2" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B1359" s="2" t="s">
+        <v>2711</v>
+      </c>
     </row>
     <row r="1360" ht="25" customHeight="1" spans="1:2">
-      <c r="A1360" s="2"/>
-      <c r="B1360" s="2"/>
+      <c r="A1360" s="2" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B1360" s="2" t="s">
+        <v>2713</v>
+      </c>
     </row>
     <row r="1361" ht="25" customHeight="1" spans="1:2">
-      <c r="A1361" s="2"/>
-      <c r="B1361" s="2"/>
+      <c r="A1361" s="2" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B1361" s="2" t="s">
+        <v>2715</v>
+      </c>
     </row>
     <row r="1362" ht="25" customHeight="1" spans="1:2">
-      <c r="A1362" s="2"/>
-      <c r="B1362" s="2"/>
+      <c r="A1362" s="2" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B1362" s="2" t="s">
+        <v>2717</v>
+      </c>
     </row>
     <row r="1363" ht="25" customHeight="1" spans="1:2">
-      <c r="A1363" s="2"/>
-      <c r="B1363" s="2"/>
+      <c r="A1363" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1363" s="2" t="s">
+        <v>2719</v>
+      </c>
     </row>
     <row r="1364" ht="25" customHeight="1" spans="1:2">
-      <c r="A1364" s="2"/>
-      <c r="B1364" s="2"/>
+      <c r="A1364" s="2" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B1364" s="2" t="s">
+        <v>2721</v>
+      </c>
     </row>
     <row r="1365" ht="25" customHeight="1" spans="1:2">
-      <c r="A1365" s="2"/>
-      <c r="B1365" s="2"/>
+      <c r="A1365" s="2" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1365" s="2" t="s">
+        <v>2723</v>
+      </c>
     </row>
     <row r="1366" ht="25" customHeight="1" spans="1:2">
-      <c r="A1366" s="2"/>
-      <c r="B1366" s="2"/>
+      <c r="A1366" s="2" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B1366" s="2" t="s">
+        <v>2725</v>
+      </c>
     </row>
     <row r="1367" ht="25" customHeight="1" spans="1:2">
-      <c r="A1367" s="2"/>
-      <c r="B1367" s="2"/>
+      <c r="A1367" s="2" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1367" s="2" t="s">
+        <v>2727</v>
+      </c>
     </row>
     <row r="1368" ht="25" customHeight="1" spans="1:2">
-      <c r="A1368" s="2"/>
-      <c r="B1368" s="2"/>
+      <c r="A1368" s="2" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B1368" s="2" t="s">
+        <v>2729</v>
+      </c>
     </row>
     <row r="1369" ht="25" customHeight="1" spans="1:2">
-      <c r="A1369" s="2"/>
-      <c r="B1369" s="2"/>
+      <c r="A1369" s="2" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B1369" s="2" t="s">
+        <v>2731</v>
+      </c>
     </row>
     <row r="1370" ht="25" customHeight="1" spans="1:2">
-      <c r="A1370" s="2"/>
-      <c r="B1370" s="2"/>
+      <c r="A1370" s="2" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B1370" s="2" t="s">
+        <v>2733</v>
+      </c>
     </row>
     <row r="1371" ht="25" customHeight="1" spans="1:2">
-      <c r="A1371" s="2"/>
-      <c r="B1371" s="2"/>
+      <c r="A1371" s="2" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1371" s="2" t="s">
+        <v>2735</v>
+      </c>
     </row>
     <row r="1372" ht="25" customHeight="1" spans="1:2">
-      <c r="A1372" s="2"/>
-      <c r="B1372" s="2"/>
+      <c r="A1372" s="2" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B1372" s="2" t="s">
+        <v>2737</v>
+      </c>
     </row>
     <row r="1373" ht="25" customHeight="1" spans="1:2">
-      <c r="A1373" s="2"/>
-      <c r="B1373" s="2"/>
+      <c r="A1373" s="2" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B1373" s="2" t="s">
+        <v>2739</v>
+      </c>
     </row>
     <row r="1374" ht="25" customHeight="1" spans="1:2">
-      <c r="A1374" s="2"/>
-      <c r="B1374" s="2"/>
+      <c r="A1374" s="2" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B1374" s="2" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="1375" ht="25" customHeight="1" spans="1:2">
-      <c r="A1375" s="2"/>
-      <c r="B1375" s="2"/>
+      <c r="A1375" s="2" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B1375" s="2" t="s">
+        <v>2743</v>
+      </c>
     </row>
     <row r="1376" ht="25" customHeight="1" spans="1:2">
-      <c r="A1376" s="2"/>
-      <c r="B1376" s="2"/>
+      <c r="A1376" s="2" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B1376" s="2" t="s">
+        <v>2745</v>
+      </c>
     </row>
     <row r="1377" ht="25" customHeight="1" spans="1:2">
-      <c r="A1377" s="2"/>
-      <c r="B1377" s="2"/>
+      <c r="A1377" s="2" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B1377" s="2" t="s">
+        <v>2747</v>
+      </c>
     </row>
     <row r="1378" ht="25" customHeight="1" spans="1:2">
-      <c r="A1378" s="2"/>
-      <c r="B1378" s="2"/>
+      <c r="A1378" s="2" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B1378" s="2" t="s">
+        <v>2749</v>
+      </c>
     </row>
     <row r="1379" ht="25" customHeight="1" spans="1:2">
-      <c r="A1379" s="2"/>
-      <c r="B1379" s="2"/>
+      <c r="A1379" s="2" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B1379" s="2" t="s">
+        <v>2751</v>
+      </c>
     </row>
     <row r="1380" ht="25" customHeight="1" spans="1:2">
-      <c r="A1380" s="2"/>
-      <c r="B1380" s="2"/>
+      <c r="A1380" s="2" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B1380" s="2" t="s">
+        <v>2753</v>
+      </c>
     </row>
     <row r="1381" ht="25" customHeight="1" spans="1:2">
-      <c r="A1381" s="2"/>
-      <c r="B1381" s="2"/>
+      <c r="A1381" s="2" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B1381" s="2" t="s">
+        <v>2755</v>
+      </c>
     </row>
     <row r="1382" ht="25" customHeight="1" spans="1:2">
-      <c r="A1382" s="2"/>
-      <c r="B1382" s="2"/>
+      <c r="A1382" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="B1382" s="2" t="s">
+        <v>2757</v>
+      </c>
     </row>
     <row r="1383" ht="25" customHeight="1" spans="1:2">
-      <c r="A1383" s="2"/>
-      <c r="B1383" s="2"/>
+      <c r="A1383" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="B1383" s="2" t="s">
+        <v>2759</v>
+      </c>
     </row>
     <row r="1384" ht="25" customHeight="1" spans="1:2">
-      <c r="A1384" s="2"/>
-      <c r="B1384" s="2"/>
+      <c r="A1384" s="2" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B1384" s="2" t="s">
+        <v>2761</v>
+      </c>
     </row>
     <row r="1385" ht="25" customHeight="1" spans="1:2">
-      <c r="A1385" s="2"/>
-      <c r="B1385" s="2"/>
+      <c r="A1385" s="2" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1385" s="2" t="s">
+        <v>2763</v>
+      </c>
     </row>
     <row r="1386" ht="25" customHeight="1" spans="1:2">
-      <c r="A1386" s="2"/>
-      <c r="B1386" s="2"/>
+      <c r="A1386" s="2" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B1386" s="2" t="s">
+        <v>2765</v>
+      </c>
     </row>
     <row r="1387" ht="25" customHeight="1" spans="1:2">
-      <c r="A1387" s="2"/>
-      <c r="B1387" s="2"/>
+      <c r="A1387" s="2" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B1387" s="2" t="s">
+        <v>2767</v>
+      </c>
     </row>
     <row r="1388" ht="25" customHeight="1" spans="1:2">
-      <c r="A1388" s="2"/>
-      <c r="B1388" s="2"/>
+      <c r="A1388" s="2" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B1388" s="2" t="s">
+        <v>2769</v>
+      </c>
     </row>
     <row r="1389" ht="25" customHeight="1" spans="1:2">
-      <c r="A1389" s="2"/>
-      <c r="B1389" s="2"/>
+      <c r="A1389" s="2" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B1389" s="2" t="s">
+        <v>2771</v>
+      </c>
     </row>
     <row r="1390" ht="25" customHeight="1" spans="1:2">
-      <c r="A1390" s="2"/>
-      <c r="B1390" s="2"/>
+      <c r="A1390" s="2" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B1390" s="2" t="s">
+        <v>2773</v>
+      </c>
     </row>
     <row r="1391" ht="25" customHeight="1" spans="1:2">
-      <c r="A1391" s="2"/>
-      <c r="B1391" s="2"/>
+      <c r="A1391" s="2" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B1391" s="2" t="s">
+        <v>2775</v>
+      </c>
     </row>
     <row r="1392" ht="25" customHeight="1" spans="1:2">
-      <c r="A1392" s="2"/>
-      <c r="B1392" s="2"/>
+      <c r="A1392" s="2" t="s">
+        <v>2776</v>
+      </c>
+      <c r="B1392" s="2" t="s">
+        <v>2777</v>
+      </c>
     </row>
     <row r="1393" ht="25" customHeight="1" spans="1:2">
-      <c r="A1393" s="2"/>
-      <c r="B1393" s="2"/>
+      <c r="A1393" s="2" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B1393" s="2" t="s">
+        <v>2779</v>
+      </c>
     </row>
     <row r="1394" ht="25" customHeight="1" spans="1:2">
-      <c r="A1394" s="2"/>
-      <c r="B1394" s="2"/>
+      <c r="A1394" s="2" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B1394" s="2" t="s">
+        <v>2781</v>
+      </c>
     </row>
     <row r="1395" ht="25" customHeight="1" spans="1:2">
-      <c r="A1395" s="2"/>
-      <c r="B1395" s="2"/>
+      <c r="A1395" s="2" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B1395" s="2" t="s">
+        <v>2783</v>
+      </c>
     </row>
     <row r="1396" ht="25" customHeight="1" spans="1:2">
-      <c r="A1396" s="2"/>
-      <c r="B1396" s="2"/>
+      <c r="A1396" s="2" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B1396" s="2" t="s">
+        <v>2785</v>
+      </c>
     </row>
     <row r="1397" ht="25" customHeight="1" spans="1:2">
-      <c r="A1397" s="2"/>
-      <c r="B1397" s="2"/>
+      <c r="A1397" s="2" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B1397" s="2" t="s">
+        <v>2787</v>
+      </c>
     </row>
     <row r="1398" ht="25" customHeight="1" spans="1:2">
-      <c r="A1398" s="2"/>
-      <c r="B1398" s="2"/>
+      <c r="A1398" s="2" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B1398" s="2" t="s">
+        <v>2789</v>
+      </c>
     </row>
     <row r="1399" ht="25" customHeight="1" spans="1:2">
-      <c r="A1399" s="2"/>
-      <c r="B1399" s="2"/>
+      <c r="A1399" s="2" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B1399" s="2" t="s">
+        <v>2791</v>
+      </c>
     </row>
     <row r="1400" ht="25" customHeight="1" spans="1:2">
-      <c r="A1400" s="2"/>
-      <c r="B1400" s="2"/>
+      <c r="A1400" s="2" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B1400" s="2" t="s">
+        <v>2793</v>
+      </c>
     </row>
     <row r="1401" ht="25" customHeight="1" spans="1:2">
-      <c r="A1401" s="2"/>
-      <c r="B1401" s="2"/>
+      <c r="A1401" s="2" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B1401" s="2" t="s">
+        <v>2795</v>
+      </c>
     </row>
     <row r="1402" ht="25" customHeight="1" spans="1:2">
-      <c r="A1402" s="2"/>
-      <c r="B1402" s="2"/>
+      <c r="A1402" s="2" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B1402" s="2" t="s">
+        <v>2797</v>
+      </c>
     </row>
     <row r="1403" ht="25" customHeight="1" spans="1:2">
-      <c r="A1403" s="2"/>
-      <c r="B1403" s="2"/>
+      <c r="A1403" s="2" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B1403" s="2" t="s">
+        <v>2799</v>
+      </c>
     </row>
     <row r="1404" ht="25" customHeight="1" spans="1:2">
-      <c r="A1404" s="2"/>
-      <c r="B1404" s="2"/>
+      <c r="A1404" s="2" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B1404" s="2" t="s">
+        <v>2801</v>
+      </c>
     </row>
     <row r="1405" ht="25" customHeight="1" spans="1:2">
-      <c r="A1405" s="2"/>
-      <c r="B1405" s="2"/>
+      <c r="A1405" s="2" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1405" s="2" t="s">
+        <v>2803</v>
+      </c>
     </row>
     <row r="1406" ht="25" customHeight="1" spans="1:2">
-      <c r="A1406" s="2"/>
-      <c r="B1406" s="2"/>
+      <c r="A1406" s="2" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B1406" s="2" t="s">
+        <v>2805</v>
+      </c>
     </row>
     <row r="1407" ht="25" customHeight="1" spans="1:2">
-      <c r="A1407" s="2"/>
-      <c r="B1407" s="2"/>
+      <c r="A1407" s="2" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B1407" s="2" t="s">
+        <v>2807</v>
+      </c>
     </row>
     <row r="1408" ht="25" customHeight="1" spans="1:2">
-      <c r="A1408" s="2"/>
-      <c r="B1408" s="2"/>
+      <c r="A1408" s="2" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B1408" s="2" t="s">
+        <v>2809</v>
+      </c>
     </row>
     <row r="1409" ht="25" customHeight="1" spans="1:2">
-      <c r="A1409" s="2"/>
-      <c r="B1409" s="2"/>
+      <c r="A1409" s="2" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1409" s="2" t="s">
+        <v>2811</v>
+      </c>
     </row>
     <row r="1410" ht="25" customHeight="1" spans="1:2">
-      <c r="A1410" s="2"/>
-      <c r="B1410" s="2"/>
+      <c r="A1410" s="2" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B1410" s="2" t="s">
+        <v>2813</v>
+      </c>
     </row>
     <row r="1411" ht="25" customHeight="1" spans="1:2">
-      <c r="A1411" s="2"/>
-      <c r="B1411" s="2"/>
+      <c r="A1411" s="2" t="s">
+        <v>2814</v>
+      </c>
+      <c r="B1411" s="2" t="s">
+        <v>2815</v>
+      </c>
     </row>
     <row r="1412" ht="25" customHeight="1" spans="1:2">
-      <c r="A1412" s="2"/>
-      <c r="B1412" s="2"/>
+      <c r="A1412" s="2" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B1412" s="2" t="s">
+        <v>2817</v>
+      </c>
     </row>
     <row r="1413" ht="25" customHeight="1" spans="1:2">
-      <c r="A1413" s="2"/>
-      <c r="B1413" s="2"/>
+      <c r="A1413" s="2" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B1413" s="2" t="s">
+        <v>2819</v>
+      </c>
     </row>
     <row r="1414" ht="25" customHeight="1" spans="1:2">
-      <c r="A1414" s="2"/>
-      <c r="B1414" s="2"/>
+      <c r="A1414" s="2" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B1414" s="2" t="s">
+        <v>2821</v>
+      </c>
     </row>
     <row r="1415" ht="25" customHeight="1" spans="1:2">
-      <c r="A1415" s="2"/>
-      <c r="B1415" s="2"/>
+      <c r="A1415" s="2" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B1415" s="2" t="s">
+        <v>2823</v>
+      </c>
     </row>
     <row r="1416" ht="25" customHeight="1" spans="1:2">
-      <c r="A1416" s="2"/>
-      <c r="B1416" s="2"/>
+      <c r="A1416" s="2" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B1416" s="2" t="s">
+        <v>2825</v>
+      </c>
     </row>
     <row r="1417" ht="25" customHeight="1" spans="1:2">
-      <c r="A1417" s="2"/>
-      <c r="B1417" s="2"/>
+      <c r="A1417" s="2" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B1417" s="2" t="s">
+        <v>2827</v>
+      </c>
     </row>
     <row r="1418" ht="25" customHeight="1" spans="1:2">
-      <c r="A1418" s="2"/>
-      <c r="B1418" s="2"/>
+      <c r="A1418" s="2" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B1418" s="2" t="s">
+        <v>2829</v>
+      </c>
     </row>
     <row r="1419" ht="25" customHeight="1" spans="1:2">
-      <c r="A1419" s="2"/>
-      <c r="B1419" s="2"/>
+      <c r="A1419" s="2" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B1419" s="2" t="s">
+        <v>2831</v>
+      </c>
     </row>
     <row r="1420" ht="25" customHeight="1" spans="1:2">
-      <c r="A1420" s="2"/>
-      <c r="B1420" s="2"/>
+      <c r="A1420" s="2" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B1420" s="2" t="s">
+        <v>2833</v>
+      </c>
     </row>
     <row r="1421" ht="25" customHeight="1" spans="1:2">
-      <c r="A1421" s="2"/>
-      <c r="B1421" s="2"/>
+      <c r="A1421" s="2" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B1421" s="2" t="s">
+        <v>2835</v>
+      </c>
     </row>
     <row r="1422" ht="25" customHeight="1" spans="1:2">
-      <c r="A1422" s="2"/>
-      <c r="B1422" s="2"/>
+      <c r="A1422" s="2" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B1422" s="2" t="s">
+        <v>2837</v>
+      </c>
     </row>
     <row r="1423" ht="25" customHeight="1" spans="1:2">
-      <c r="A1423" s="2"/>
-      <c r="B1423" s="2"/>
+      <c r="A1423" s="2" t="s">
+        <v>2838</v>
+      </c>
+      <c r="B1423" s="2" t="s">
+        <v>2839</v>
+      </c>
     </row>
     <row r="1424" ht="25" customHeight="1" spans="1:2">
-      <c r="A1424" s="2"/>
-      <c r="B1424" s="2"/>
+      <c r="A1424" s="2" t="s">
+        <v>2840</v>
+      </c>
+      <c r="B1424" s="2" t="s">
+        <v>2841</v>
+      </c>
     </row>
     <row r="1425" ht="25" customHeight="1" spans="1:2">
-      <c r="A1425" s="2"/>
-      <c r="B1425" s="2"/>
+      <c r="A1425" s="2" t="s">
+        <v>2842</v>
+      </c>
+      <c r="B1425" s="2" t="s">
+        <v>2843</v>
+      </c>
     </row>
     <row r="1426" ht="25" customHeight="1" spans="1:2">
-      <c r="A1426" s="2"/>
-      <c r="B1426" s="2"/>
+      <c r="A1426" s="2" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B1426" s="2" t="s">
+        <v>2845</v>
+      </c>
     </row>
     <row r="1427" ht="25" customHeight="1" spans="1:2">
-      <c r="A1427" s="2"/>
-      <c r="B1427" s="2"/>
+      <c r="A1427" s="2" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B1427" s="2" t="s">
+        <v>2847</v>
+      </c>
     </row>
     <row r="1428" ht="25" customHeight="1" spans="1:2">
-      <c r="A1428" s="2"/>
-      <c r="B1428" s="2"/>
+      <c r="A1428" s="2" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B1428" s="2" t="s">
+        <v>2849</v>
+      </c>
     </row>
     <row r="1429" ht="25" customHeight="1" spans="1:2">
-      <c r="A1429" s="2"/>
-      <c r="B1429" s="2"/>
+      <c r="A1429" s="2" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B1429" s="2" t="s">
+        <v>2851</v>
+      </c>
     </row>
     <row r="1430" ht="25" customHeight="1" spans="1:2">
-      <c r="A1430" s="2"/>
-      <c r="B1430" s="2"/>
+      <c r="A1430" s="2" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B1430" s="2" t="s">
+        <v>2853</v>
+      </c>
     </row>
     <row r="1431" ht="25" customHeight="1" spans="1:2">
-      <c r="A1431" s="2"/>
-      <c r="B1431" s="2"/>
+      <c r="A1431" s="2" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B1431" s="2" t="s">
+        <v>2855</v>
+      </c>
     </row>
     <row r="1432" ht="25" customHeight="1" spans="1:2">
-      <c r="A1432" s="2"/>
-      <c r="B1432" s="2"/>
+      <c r="A1432" s="2" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B1432" s="2" t="s">
+        <v>2857</v>
+      </c>
     </row>
     <row r="1433" ht="25" customHeight="1" spans="1:2">
-      <c r="A1433" s="2"/>
-      <c r="B1433" s="2"/>
+      <c r="A1433" s="2" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B1433" s="2" t="s">
+        <v>2859</v>
+      </c>
     </row>
     <row r="1434" ht="25" customHeight="1" spans="1:2">
-      <c r="A1434" s="2"/>
-      <c r="B1434" s="2"/>
+      <c r="A1434" s="2" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B1434" s="2" t="s">
+        <v>2861</v>
+      </c>
     </row>
     <row r="1435" ht="25" customHeight="1" spans="1:2">
-      <c r="A1435" s="2"/>
-      <c r="B1435" s="2"/>
+      <c r="A1435" s="2" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B1435" s="2" t="s">
+        <v>2863</v>
+      </c>
     </row>
     <row r="1436" ht="25" customHeight="1" spans="1:2">
-      <c r="A1436" s="2"/>
-      <c r="B1436" s="2"/>
+      <c r="A1436" s="2" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B1436" s="2" t="s">
+        <v>2865</v>
+      </c>
     </row>
     <row r="1437" ht="25" customHeight="1" spans="1:2">
-      <c r="A1437" s="2"/>
-      <c r="B1437" s="2"/>
+      <c r="A1437" s="2" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B1437" s="2" t="s">
+        <v>2867</v>
+      </c>
     </row>
     <row r="1438" ht="25" customHeight="1" spans="1:2">
-      <c r="A1438" s="2"/>
-      <c r="B1438" s="2"/>
+      <c r="A1438" s="2" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B1438" s="2" t="s">
+        <v>2869</v>
+      </c>
     </row>
     <row r="1439" ht="25" customHeight="1" spans="1:2">
-      <c r="A1439" s="2"/>
-      <c r="B1439" s="2"/>
+      <c r="A1439" s="2" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B1439" s="2" t="s">
+        <v>2871</v>
+      </c>
     </row>
     <row r="1440" ht="25" customHeight="1" spans="1:2">
-      <c r="A1440" s="2"/>
-      <c r="B1440" s="2"/>
+      <c r="A1440" s="2" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B1440" s="2" t="s">
+        <v>2873</v>
+      </c>
     </row>
     <row r="1441" ht="25" customHeight="1" spans="1:2">
-      <c r="A1441" s="2"/>
-      <c r="B1441" s="2"/>
+      <c r="A1441" s="2" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B1441" s="2" t="s">
+        <v>2875</v>
+      </c>
     </row>
     <row r="1442" ht="25" customHeight="1" spans="1:2">
-      <c r="A1442" s="2"/>
-      <c r="B1442" s="2"/>
+      <c r="A1442" s="2" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B1442" s="2" t="s">
+        <v>2877</v>
+      </c>
     </row>
     <row r="1443" ht="25" customHeight="1" spans="1:2">
-      <c r="A1443" s="2"/>
-      <c r="B1443" s="2"/>
+      <c r="A1443" s="2" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B1443" s="2" t="s">
+        <v>2879</v>
+      </c>
     </row>
     <row r="1444" ht="25" customHeight="1" spans="1:2">
-      <c r="A1444" s="2"/>
-      <c r="B1444" s="2"/>
+      <c r="A1444" s="2" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B1444" s="2" t="s">
+        <v>2881</v>
+      </c>
     </row>
     <row r="1445" ht="25" customHeight="1" spans="1:2">
-      <c r="A1445" s="2"/>
-      <c r="B1445" s="2"/>
+      <c r="A1445" s="2" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B1445" s="2" t="s">
+        <v>2883</v>
+      </c>
     </row>
     <row r="1446" ht="25" customHeight="1" spans="1:2">
-      <c r="A1446" s="2"/>
-      <c r="B1446" s="2"/>
+      <c r="A1446" s="2" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B1446" s="2" t="s">
+        <v>2885</v>
+      </c>
     </row>
     <row r="1447" ht="25" customHeight="1" spans="1:2">
-      <c r="A1447" s="2"/>
-      <c r="B1447" s="2"/>
+      <c r="A1447" s="2" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B1447" s="2" t="s">
+        <v>2887</v>
+      </c>
     </row>
     <row r="1448" ht="25" customHeight="1" spans="1:2">
-      <c r="A1448" s="2"/>
-      <c r="B1448" s="2"/>
+      <c r="A1448" s="2" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B1448" s="2" t="s">
+        <v>2889</v>
+      </c>
     </row>
     <row r="1449" ht="25" customHeight="1" spans="1:2">
-      <c r="A1449" s="2"/>
-      <c r="B1449" s="2"/>
+      <c r="A1449" s="2" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B1449" s="2" t="s">
+        <v>2891</v>
+      </c>
     </row>
     <row r="1450" ht="25" customHeight="1" spans="1:2">
-      <c r="A1450" s="2"/>
-      <c r="B1450" s="2"/>
+      <c r="A1450" s="2" t="s">
+        <v>2892</v>
+      </c>
+      <c r="B1450" s="2" t="s">
+        <v>2893</v>
+      </c>
     </row>
     <row r="1451" ht="25" customHeight="1" spans="1:2">
-      <c r="A1451" s="2"/>
-      <c r="B1451" s="2"/>
+      <c r="A1451" s="2" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B1451" s="2" t="s">
+        <v>2895</v>
+      </c>
     </row>
     <row r="1452" ht="25" customHeight="1" spans="1:2">
-      <c r="A1452" s="2"/>
-      <c r="B1452" s="2"/>
+      <c r="A1452" s="2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B1452" s="2" t="s">
+        <v>2897</v>
+      </c>
     </row>
     <row r="1453" ht="25" customHeight="1" spans="1:2">
-      <c r="A1453" s="2"/>
-      <c r="B1453" s="2"/>
+      <c r="A1453" s="2" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B1453" s="2" t="s">
+        <v>2899</v>
+      </c>
     </row>
     <row r="1454" ht="25" customHeight="1" spans="1:2">
-      <c r="A1454" s="2"/>
-      <c r="B1454" s="2"/>
+      <c r="A1454" s="2" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B1454" s="2" t="s">
+        <v>2901</v>
+      </c>
     </row>
     <row r="1455" ht="25" customHeight="1" spans="1:2">
-      <c r="A1455" s="2"/>
-      <c r="B1455" s="2"/>
+      <c r="A1455" s="2" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B1455" s="2" t="s">
+        <v>2903</v>
+      </c>
     </row>
     <row r="1456" ht="25" customHeight="1" spans="1:2">
-      <c r="A1456" s="2"/>
-      <c r="B1456" s="2"/>
+      <c r="A1456" s="2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B1456" s="2" t="s">
+        <v>2905</v>
+      </c>
     </row>
     <row r="1457" ht="25" customHeight="1" spans="1:2">
-      <c r="A1457" s="2"/>
-      <c r="B1457" s="2"/>
+      <c r="A1457" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B1457" s="2" t="s">
+        <v>2907</v>
+      </c>
     </row>
     <row r="1458" ht="25" customHeight="1" spans="1:2">
-      <c r="A1458" s="2"/>
-      <c r="B1458" s="2"/>
+      <c r="A1458" s="2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B1458" s="2" t="s">
+        <v>2909</v>
+      </c>
     </row>
     <row r="1459" ht="25" customHeight="1" spans="1:2">
-      <c r="A1459" s="2"/>
-      <c r="B1459" s="2"/>
+      <c r="A1459" s="2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1459" s="2" t="s">
+        <v>2911</v>
+      </c>
     </row>
     <row r="1460" ht="25" customHeight="1" spans="1:2">
-      <c r="A1460" s="2"/>
-      <c r="B1460" s="2"/>
+      <c r="A1460" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B1460" s="2" t="s">
+        <v>2913</v>
+      </c>
     </row>
     <row r="1461" ht="25" customHeight="1" spans="1:2">
-      <c r="A1461" s="2"/>
-      <c r="B1461" s="2"/>
+      <c r="A1461" s="2" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B1461" s="2" t="s">
+        <v>2915</v>
+      </c>
     </row>
     <row r="1462" ht="25" customHeight="1" spans="1:2">
-      <c r="A1462" s="2"/>
-      <c r="B1462" s="2"/>
+      <c r="A1462" s="2" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B1462" s="2" t="s">
+        <v>2917</v>
+      </c>
     </row>
     <row r="1463" ht="25" customHeight="1" spans="1:2">
-      <c r="A1463" s="2"/>
-      <c r="B1463" s="2"/>
+      <c r="A1463" s="2" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B1463" s="2" t="s">
+        <v>2919</v>
+      </c>
     </row>
     <row r="1464" ht="25" customHeight="1" spans="1:2">
-      <c r="A1464" s="2"/>
-      <c r="B1464" s="2"/>
+      <c r="A1464" s="2" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B1464" s="2" t="s">
+        <v>2921</v>
+      </c>
     </row>
     <row r="1465" ht="25" customHeight="1" spans="1:2">
-      <c r="A1465" s="2"/>
-      <c r="B1465" s="2"/>
+      <c r="A1465" s="2" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B1465" s="2" t="s">
+        <v>2923</v>
+      </c>
     </row>
     <row r="1466" ht="25" customHeight="1" spans="1:2">
-      <c r="A1466" s="2"/>
-      <c r="B1466" s="2"/>
+      <c r="A1466" s="2" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B1466" s="2" t="s">
+        <v>2925</v>
+      </c>
     </row>
     <row r="1467" ht="25" customHeight="1" spans="1:2">
-      <c r="A1467" s="2"/>
-      <c r="B1467" s="2"/>
+      <c r="A1467" s="2" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B1467" s="2" t="s">
+        <v>2927</v>
+      </c>
     </row>
     <row r="1468" ht="25" customHeight="1" spans="1:2">
-      <c r="A1468" s="2"/>
-      <c r="B1468" s="2"/>
+      <c r="A1468" s="2" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B1468" s="2" t="s">
+        <v>2929</v>
+      </c>
     </row>
     <row r="1469" ht="25" customHeight="1" spans="1:2">
-      <c r="A1469" s="2"/>
-      <c r="B1469" s="2"/>
+      <c r="A1469" s="2" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1469" s="2" t="s">
+        <v>2931</v>
+      </c>
     </row>
     <row r="1470" ht="25" customHeight="1" spans="1:2">
-      <c r="A1470" s="2"/>
-      <c r="B1470" s="2"/>
+      <c r="A1470" s="2" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B1470" s="2" t="s">
+        <v>2933</v>
+      </c>
     </row>
     <row r="1471" ht="25" customHeight="1" spans="1:2">
-      <c r="A1471" s="2"/>
-      <c r="B1471" s="2"/>
+      <c r="A1471" s="2" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B1471" s="2" t="s">
+        <v>2935</v>
+      </c>
     </row>
     <row r="1472" ht="25" customHeight="1" spans="1:2">
-      <c r="A1472" s="2"/>
-      <c r="B1472" s="2"/>
+      <c r="A1472" s="2" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B1472" s="2" t="s">
+        <v>2937</v>
+      </c>
     </row>
     <row r="1473" ht="25" customHeight="1" spans="1:2">
-      <c r="A1473" s="2"/>
-      <c r="B1473" s="2"/>
+      <c r="A1473" s="2" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B1473" s="2" t="s">
+        <v>2939</v>
+      </c>
     </row>
     <row r="1474" ht="25" customHeight="1" spans="1:2">
-      <c r="A1474" s="2"/>
-      <c r="B1474" s="2"/>
+      <c r="A1474" s="2" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B1474" s="2" t="s">
+        <v>2941</v>
+      </c>
     </row>
     <row r="1475" ht="25" customHeight="1" spans="1:2">
-      <c r="A1475" s="2"/>
-      <c r="B1475" s="2"/>
+      <c r="A1475" s="2" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B1475" s="2" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="1476" ht="25" customHeight="1" spans="1:2">
-      <c r="A1476" s="2"/>
-      <c r="B1476" s="2"/>
+      <c r="A1476" s="2" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B1476" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="1477" ht="25" customHeight="1" spans="1:2">
-      <c r="A1477" s="2"/>
-      <c r="B1477" s="2"/>
+      <c r="A1477" s="2" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B1477" s="2" t="s">
+        <v>2947</v>
+      </c>
     </row>
     <row r="1478" ht="25" customHeight="1" spans="1:2">
-      <c r="A1478" s="2"/>
-      <c r="B1478" s="2"/>
+      <c r="A1478" s="2" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B1478" s="2" t="s">
+        <v>2949</v>
+      </c>
     </row>
     <row r="1479" ht="25" customHeight="1" spans="1:2">
-      <c r="A1479" s="2"/>
-      <c r="B1479" s="2"/>
+      <c r="A1479" s="2" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1479" s="2" t="s">
+        <v>2951</v>
+      </c>
     </row>
     <row r="1480" ht="25" customHeight="1" spans="1:2">
-      <c r="A1480" s="2"/>
-      <c r="B1480" s="2"/>
+      <c r="A1480" s="2" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B1480" s="2" t="s">
+        <v>2953</v>
+      </c>
     </row>
     <row r="1481" ht="25" customHeight="1" spans="1:2">
-      <c r="A1481" s="2"/>
-      <c r="B1481" s="2"/>
+      <c r="A1481" s="2" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B1481" s="2" t="s">
+        <v>2955</v>
+      </c>
     </row>
     <row r="1482" ht="25" customHeight="1" spans="1:2">
-      <c r="A1482" s="2"/>
-      <c r="B1482" s="2"/>
+      <c r="A1482" s="2" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B1482" s="2" t="s">
+        <v>2957</v>
+      </c>
     </row>
     <row r="1483" ht="25" customHeight="1" spans="1:2">
-      <c r="A1483" s="2"/>
-      <c r="B1483" s="2"/>
+      <c r="A1483" s="2" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B1483" s="2" t="s">
+        <v>2959</v>
+      </c>
     </row>
     <row r="1484" ht="25" customHeight="1" spans="1:2">
-      <c r="A1484" s="2"/>
-      <c r="B1484" s="2"/>
+      <c r="A1484" s="2" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B1484" s="2" t="s">
+        <v>2961</v>
+      </c>
     </row>
     <row r="1485" ht="25" customHeight="1" spans="1:2">
-      <c r="A1485" s="2"/>
-      <c r="B1485" s="2"/>
+      <c r="A1485" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B1485" s="2" t="s">
+        <v>2963</v>
+      </c>
     </row>
     <row r="1486" ht="25" customHeight="1" spans="1:2">
-      <c r="A1486" s="2"/>
-      <c r="B1486" s="2"/>
+      <c r="A1486" s="2" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B1486" s="2" t="s">
+        <v>2965</v>
+      </c>
     </row>
     <row r="1487" ht="25" customHeight="1" spans="1:2">
-      <c r="A1487" s="2"/>
-      <c r="B1487" s="2"/>
+      <c r="A1487" s="2" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B1487" s="2" t="s">
+        <v>2967</v>
+      </c>
     </row>
     <row r="1488" ht="25" customHeight="1" spans="1:2">
-      <c r="A1488" s="2"/>
-      <c r="B1488" s="2"/>
+      <c r="A1488" s="2" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B1488" s="2" t="s">
+        <v>2969</v>
+      </c>
     </row>
     <row r="1489" ht="25" customHeight="1" spans="1:2">
-      <c r="A1489" s="2"/>
-      <c r="B1489" s="2"/>
+      <c r="A1489" s="2" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1489" s="2" t="s">
+        <v>2971</v>
+      </c>
     </row>
     <row r="1490" ht="25" customHeight="1" spans="1:2">
-      <c r="A1490" s="2"/>
-      <c r="B1490" s="2"/>
+      <c r="A1490" s="2" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B1490" s="2" t="s">
+        <v>2973</v>
+      </c>
     </row>
     <row r="1491" ht="25" customHeight="1" spans="1:2">
-      <c r="A1491" s="2"/>
-      <c r="B1491" s="2"/>
+      <c r="A1491" s="2" t="s">
+        <v>2974</v>
+      </c>
+      <c r="B1491" s="2" t="s">
+        <v>2975</v>
+      </c>
     </row>
     <row r="1492" ht="25" customHeight="1" spans="1:2">
-      <c r="A1492" s="2"/>
-      <c r="B1492" s="2"/>
+      <c r="A1492" s="2" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B1492" s="2" t="s">
+        <v>2977</v>
+      </c>
     </row>
     <row r="1493" ht="25" customHeight="1" spans="1:2">
-      <c r="A1493" s="2"/>
-      <c r="B1493" s="2"/>
+      <c r="A1493" s="2" t="s">
+        <v>2978</v>
+      </c>
+      <c r="B1493" s="2" t="s">
+        <v>2979</v>
+      </c>
     </row>
     <row r="1494" ht="25" customHeight="1" spans="1:2">
-      <c r="A1494" s="2"/>
-      <c r="B1494" s="2"/>
+      <c r="A1494" s="2" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B1494" s="2" t="s">
+        <v>2981</v>
+      </c>
     </row>
     <row r="1495" ht="25" customHeight="1" spans="1:2">
-      <c r="A1495" s="2"/>
-      <c r="B1495" s="2"/>
+      <c r="A1495" s="2" t="s">
+        <v>2982</v>
+      </c>
+      <c r="B1495" s="2" t="s">
+        <v>2983</v>
+      </c>
     </row>
     <row r="1496" ht="25" customHeight="1" spans="1:2">
-      <c r="A1496" s="2"/>
-      <c r="B1496" s="2"/>
+      <c r="A1496" s="2" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B1496" s="2" t="s">
+        <v>2985</v>
+      </c>
     </row>
     <row r="1497" ht="25" customHeight="1" spans="1:2">
-      <c r="A1497" s="2"/>
-      <c r="B1497" s="2"/>
+      <c r="A1497" s="2" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B1497" s="2" t="s">
+        <v>2987</v>
+      </c>
     </row>
     <row r="1498" ht="25" customHeight="1" spans="1:2">
-      <c r="A1498" s="2"/>
-      <c r="B1498" s="2"/>
+      <c r="A1498" s="2" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B1498" s="2" t="s">
+        <v>2989</v>
+      </c>
     </row>
     <row r="1499" ht="25" customHeight="1" spans="1:2">
-      <c r="A1499" s="2"/>
-      <c r="B1499" s="2"/>
+      <c r="A1499" s="2" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B1499" s="2" t="s">
+        <v>2991</v>
+      </c>
     </row>
     <row r="1500" ht="25" customHeight="1" spans="1:2">
-      <c r="A1500" s="2"/>
-      <c r="B1500" s="2"/>
+      <c r="A1500" s="2" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B1500" s="2" t="s">
+        <v>2993</v>
+      </c>
     </row>
     <row r="1501" ht="25" customHeight="1" spans="1:2">
-      <c r="A1501" s="2"/>
-      <c r="B1501" s="2"/>
+      <c r="A1501" s="2" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B1501" s="2" t="s">
+        <v>2995</v>
+      </c>
     </row>
     <row r="1502" ht="25" customHeight="1" spans="1:2">
-      <c r="A1502" s="2"/>
-      <c r="B1502" s="2"/>
+      <c r="A1502" s="2" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B1502" s="2" t="s">
+        <v>2997</v>
+      </c>
     </row>
     <row r="1503" ht="25" customHeight="1" spans="1:2">
-      <c r="A1503" s="2"/>
-      <c r="B1503" s="2"/>
+      <c r="A1503" s="2" t="s">
+        <v>2998</v>
+      </c>
+      <c r="B1503" s="2" t="s">
+        <v>2999</v>
+      </c>
     </row>
     <row r="1504" ht="25" customHeight="1" spans="1:2">
-      <c r="A1504" s="2"/>
-      <c r="B1504" s="2"/>
+      <c r="A1504" s="2" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B1504" s="2" t="s">
+        <v>3001</v>
+      </c>
     </row>
     <row r="1505" ht="25" customHeight="1" spans="1:2">
-      <c r="A1505" s="2"/>
-      <c r="B1505" s="2"/>
+      <c r="A1505" s="2" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B1505" s="2" t="s">
+        <v>3003</v>
+      </c>
     </row>
     <row r="1506" ht="25" customHeight="1" spans="1:2">
-      <c r="A1506" s="2"/>
-      <c r="B1506" s="2"/>
+      <c r="A1506" s="2" t="s">
+        <v>3004</v>
+      </c>
+      <c r="B1506" s="2" t="s">
+        <v>3005</v>
+      </c>
     </row>
     <row r="1507" ht="25" customHeight="1" spans="1:2">
-      <c r="A1507" s="2"/>
-      <c r="B1507" s="2"/>
+      <c r="A1507" s="2" t="s">
+        <v>3006</v>
+      </c>
+      <c r="B1507" s="2" t="s">
+        <v>3007</v>
+      </c>
     </row>
     <row r="1508" ht="25" customHeight="1" spans="1:2">
-      <c r="A1508" s="2"/>
-      <c r="B1508" s="2"/>
+      <c r="A1508" s="2" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B1508" s="2" t="s">
+        <v>3009</v>
+      </c>
     </row>
     <row r="1509" ht="25" customHeight="1" spans="1:2">
-      <c r="A1509" s="2"/>
-      <c r="B1509" s="2"/>
+      <c r="A1509" s="2" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B1509" s="2" t="s">
+        <v>3011</v>
+      </c>
     </row>
     <row r="1510" ht="25" customHeight="1" spans="1:2">
-      <c r="A1510" s="2"/>
-      <c r="B1510" s="2"/>
+      <c r="A1510" s="2" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B1510" s="2" t="s">
+        <v>3013</v>
+      </c>
     </row>
     <row r="1511" ht="25" customHeight="1" spans="1:2">
-      <c r="A1511" s="2"/>
-      <c r="B1511" s="2"/>
+      <c r="A1511" s="2" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B1511" s="2" t="s">
+        <v>3015</v>
+      </c>
     </row>
     <row r="1512" ht="25" customHeight="1" spans="1:2">
-      <c r="A1512" s="2"/>
-      <c r="B1512" s="2"/>
+      <c r="A1512" s="2" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B1512" s="2" t="s">
+        <v>3017</v>
+      </c>
     </row>
     <row r="1513" ht="25" customHeight="1" spans="1:2">
-      <c r="A1513" s="2"/>
-      <c r="B1513" s="2"/>
+      <c r="A1513" s="2" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B1513" s="2" t="s">
+        <v>3019</v>
+      </c>
     </row>
     <row r="1514" ht="25" customHeight="1" spans="1:2">
-      <c r="A1514" s="2"/>
-      <c r="B1514" s="2"/>
+      <c r="A1514" s="2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B1514" s="2" t="s">
+        <v>3021</v>
+      </c>
     </row>
     <row r="1515" ht="25" customHeight="1" spans="1:2">
-      <c r="A1515" s="2"/>
-      <c r="B1515" s="2"/>
+      <c r="A1515" s="2" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B1515" s="2" t="s">
+        <v>3023</v>
+      </c>
     </row>
     <row r="1516" ht="25" customHeight="1" spans="1:2">
-      <c r="A1516" s="2"/>
-      <c r="B1516" s="2"/>
+      <c r="A1516" s="2" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B1516" s="2" t="s">
+        <v>3025</v>
+      </c>
     </row>
     <row r="1517" ht="25" customHeight="1" spans="1:2">
-      <c r="A1517" s="2"/>
-      <c r="B1517" s="2"/>
+      <c r="A1517" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B1517" s="2" t="s">
+        <v>3027</v>
+      </c>
     </row>
     <row r="1518" ht="25" customHeight="1" spans="1:2">
-      <c r="A1518" s="2"/>
-      <c r="B1518" s="2"/>
+      <c r="A1518" s="2" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B1518" s="2" t="s">
+        <v>3029</v>
+      </c>
     </row>
     <row r="1519" ht="25" customHeight="1" spans="1:2">
-      <c r="A1519" s="2"/>
-      <c r="B1519" s="2"/>
+      <c r="A1519" s="2" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B1519" s="2" t="s">
+        <v>3031</v>
+      </c>
     </row>
     <row r="1520" ht="25" customHeight="1" spans="1:2">
-      <c r="A1520" s="2"/>
-      <c r="B1520" s="2"/>
+      <c r="A1520" s="2" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B1520" s="2" t="s">
+        <v>3033</v>
+      </c>
     </row>
     <row r="1521" ht="25" customHeight="1" spans="1:2">
-      <c r="A1521" s="2"/>
-      <c r="B1521" s="2"/>
+      <c r="A1521" s="2" t="s">
+        <v>3034</v>
+      </c>
+      <c r="B1521" s="2" t="s">
+        <v>3035</v>
+      </c>
     </row>
     <row r="1522" ht="25" customHeight="1" spans="1:2">
-      <c r="A1522" s="2"/>
-      <c r="B1522" s="2"/>
+      <c r="A1522" s="2" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B1522" s="2" t="s">
+        <v>3037</v>
+      </c>
     </row>
     <row r="1523" ht="25" customHeight="1" spans="1:2">
-      <c r="A1523" s="2"/>
-      <c r="B1523" s="2"/>
+      <c r="A1523" s="2" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B1523" s="2" t="s">
+        <v>3039</v>
+      </c>
     </row>
     <row r="1524" ht="25" customHeight="1" spans="1:2">
-      <c r="A1524" s="2"/>
-      <c r="B1524" s="2"/>
+      <c r="A1524" s="2" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B1524" s="2" t="s">
+        <v>3041</v>
+      </c>
     </row>
     <row r="1525" ht="25" customHeight="1" spans="1:2">
-      <c r="A1525" s="2"/>
-      <c r="B1525" s="2"/>
+      <c r="A1525" s="2" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B1525" s="2" t="s">
+        <v>3043</v>
+      </c>
     </row>
     <row r="1526" ht="25" customHeight="1" spans="1:2">
-      <c r="A1526" s="2"/>
-      <c r="B1526" s="2"/>
+      <c r="A1526" s="2" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1526" s="2" t="s">
+        <v>3045</v>
+      </c>
     </row>
     <row r="1527" ht="25" customHeight="1" spans="1:2">
-      <c r="A1527" s="2"/>
-      <c r="B1527" s="2"/>
+      <c r="A1527" s="2" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B1527" s="2" t="s">
+        <v>3047</v>
+      </c>
     </row>
     <row r="1528" ht="25" customHeight="1" spans="1:2">
-      <c r="A1528" s="2"/>
-      <c r="B1528" s="2"/>
+      <c r="A1528" s="2" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B1528" s="2" t="s">
+        <v>3049</v>
+      </c>
     </row>
     <row r="1529" ht="25" customHeight="1" spans="1:2">
-      <c r="A1529" s="2"/>
-      <c r="B1529" s="2"/>
+      <c r="A1529" s="2" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B1529" s="2" t="s">
+        <v>3051</v>
+      </c>
     </row>
     <row r="1530" ht="25" customHeight="1" spans="1:2">
-      <c r="A1530" s="2"/>
-      <c r="B1530" s="2"/>
+      <c r="A1530" s="2" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B1530" s="2" t="s">
+        <v>3053</v>
+      </c>
     </row>
     <row r="1531" ht="25" customHeight="1" spans="1:2">
-      <c r="A1531" s="2"/>
-      <c r="B1531" s="2"/>
+      <c r="A1531" s="2" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B1531" s="2" t="s">
+        <v>3055</v>
+      </c>
     </row>
     <row r="1532" ht="25" customHeight="1" spans="1:2">
-      <c r="A1532" s="2"/>
-      <c r="B1532" s="2"/>
+      <c r="A1532" s="2" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1532" s="2" t="s">
+        <v>3057</v>
+      </c>
     </row>
     <row r="1533" ht="25" customHeight="1" spans="1:2">
-      <c r="A1533" s="2"/>
-      <c r="B1533" s="2"/>
+      <c r="A1533" s="2" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B1533" s="2" t="s">
+        <v>3059</v>
+      </c>
     </row>
     <row r="1534" ht="25" customHeight="1" spans="1:2">
-      <c r="A1534" s="2"/>
-      <c r="B1534" s="2"/>
+      <c r="A1534" s="2" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1534" s="2" t="s">
+        <v>3061</v>
+      </c>
     </row>
     <row r="1535" ht="25" customHeight="1" spans="1:2">
-      <c r="A1535" s="2"/>
-      <c r="B1535" s="2"/>
+      <c r="A1535" s="2" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1535" s="2" t="s">
+        <v>3063</v>
+      </c>
     </row>
     <row r="1536" ht="25" customHeight="1" spans="1:2">
-      <c r="A1536" s="2"/>
-      <c r="B1536" s="2"/>
+      <c r="A1536" s="2" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1536" s="2" t="s">
+        <v>3065</v>
+      </c>
     </row>
     <row r="1537" ht="25" customHeight="1" spans="1:2">
-      <c r="A1537" s="2"/>
-      <c r="B1537" s="2"/>
+      <c r="A1537" s="2" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1537" s="2" t="s">
+        <v>3067</v>
+      </c>
     </row>
     <row r="1538" ht="25" customHeight="1" spans="1:2">
-      <c r="A1538" s="2"/>
-      <c r="B1538" s="2"/>
+      <c r="A1538" s="2" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1538" s="2" t="s">
+        <v>3069</v>
+      </c>
     </row>
     <row r="1539" ht="25" customHeight="1" spans="1:2">
-      <c r="A1539" s="2"/>
-      <c r="B1539" s="2"/>
+      <c r="A1539" s="2" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B1539" s="2" t="s">
+        <v>3071</v>
+      </c>
     </row>
     <row r="1540" ht="25" customHeight="1" spans="1:2">
-      <c r="A1540" s="2"/>
-      <c r="B1540" s="2"/>
+      <c r="A1540" s="2" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B1540" s="2" t="s">
+        <v>3073</v>
+      </c>
     </row>
     <row r="1541" ht="25" customHeight="1" spans="1:2">
-      <c r="A1541" s="2"/>
-      <c r="B1541" s="2"/>
+      <c r="A1541" s="2" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B1541" s="2" t="s">
+        <v>3075</v>
+      </c>
     </row>
     <row r="1542" ht="25" customHeight="1" spans="1:2">
-      <c r="A1542" s="2"/>
-      <c r="B1542" s="2"/>
+      <c r="A1542" s="2" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B1542" s="2" t="s">
+        <v>3077</v>
+      </c>
     </row>
     <row r="1543" ht="25" customHeight="1" spans="1:2">
-      <c r="A1543" s="2"/>
-      <c r="B1543" s="2"/>
+      <c r="A1543" s="2" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B1543" s="2" t="s">
+        <v>3079</v>
+      </c>
     </row>
     <row r="1544" ht="25" customHeight="1" spans="1:2">
-      <c r="A1544" s="2"/>
-      <c r="B1544" s="2"/>
+      <c r="A1544" s="2" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1544" s="2" t="s">
+        <v>3081</v>
+      </c>
     </row>
     <row r="1545" ht="25" customHeight="1" spans="1:2">
-      <c r="A1545" s="2"/>
-      <c r="B1545" s="2"/>
+      <c r="A1545" s="2" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B1545" s="2" t="s">
+        <v>3083</v>
+      </c>
     </row>
     <row r="1546" ht="25" customHeight="1" spans="1:2">
-      <c r="A1546" s="2"/>
-      <c r="B1546" s="2"/>
+      <c r="A1546" s="2" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1546" s="2" t="s">
+        <v>3085</v>
+      </c>
     </row>
     <row r="1547" ht="25" customHeight="1" spans="1:2">
-      <c r="A1547" s="2"/>
-      <c r="B1547" s="2"/>
+      <c r="A1547" s="2" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B1547" s="2" t="s">
+        <v>3087</v>
+      </c>
     </row>
     <row r="1548" ht="25" customHeight="1" spans="1:2">
-      <c r="A1548" s="2"/>
-      <c r="B1548" s="2"/>
+      <c r="A1548" s="2" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1548" s="2" t="s">
+        <v>3089</v>
+      </c>
     </row>
     <row r="1549" ht="25" customHeight="1" spans="1:2">
-      <c r="A1549" s="2"/>
-      <c r="B1549" s="2"/>
+      <c r="A1549" s="2" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B1549" s="2" t="s">
+        <v>3091</v>
+      </c>
     </row>
     <row r="1550" ht="25" customHeight="1" spans="1:2">
-      <c r="A1550" s="2"/>
-      <c r="B1550" s="2"/>
+      <c r="A1550" s="2" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1550" s="2" t="s">
+        <v>3093</v>
+      </c>
     </row>
     <row r="1551" ht="25" customHeight="1" spans="1:2">
-      <c r="A1551" s="2"/>
-      <c r="B1551" s="2"/>
+      <c r="A1551" s="2" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B1551" s="2" t="s">
+        <v>3095</v>
+      </c>
     </row>
     <row r="1552" ht="25" customHeight="1" spans="1:2">
-      <c r="A1552" s="2"/>
-      <c r="B1552" s="2"/>
+      <c r="A1552" s="2" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B1552" s="2" t="s">
+        <v>3097</v>
+      </c>
     </row>
     <row r="1553" ht="25" customHeight="1" spans="1:2">
-      <c r="A1553" s="2"/>
-      <c r="B1553" s="2"/>
+      <c r="A1553" s="2" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1553" s="2" t="s">
+        <v>3099</v>
+      </c>
     </row>
     <row r="1554" ht="25" customHeight="1" spans="1:2">
-      <c r="A1554" s="2"/>
-      <c r="B1554" s="2"/>
+      <c r="A1554" s="2" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B1554" s="2" t="s">
+        <v>3101</v>
+      </c>
     </row>
     <row r="1555" ht="25" customHeight="1" spans="1:2">
-      <c r="A1555" s="2"/>
-      <c r="B1555" s="2"/>
+      <c r="A1555" s="2" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B1555" s="2" t="s">
+        <v>3103</v>
+      </c>
     </row>
     <row r="1556" ht="25" customHeight="1" spans="1:2">
-      <c r="A1556" s="2"/>
-      <c r="B1556" s="2"/>
+      <c r="A1556" s="2" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B1556" s="2" t="s">
+        <v>3105</v>
+      </c>
     </row>
     <row r="1557" ht="25" customHeight="1" spans="1:2">
-      <c r="A1557" s="2"/>
-      <c r="B1557" s="2"/>
+      <c r="A1557" s="2" t="s">
+        <v>3106</v>
+      </c>
+      <c r="B1557" s="2" t="s">
+        <v>3107</v>
+      </c>
     </row>
     <row r="1558" ht="25" customHeight="1" spans="1:2">
-      <c r="A1558" s="2"/>
-      <c r="B1558" s="2"/>
+      <c r="A1558" s="2" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B1558" s="2" t="s">
+        <v>3109</v>
+      </c>
     </row>
     <row r="1559" ht="25" customHeight="1" spans="1:2">
-      <c r="A1559" s="2"/>
-      <c r="B1559" s="2"/>
+      <c r="A1559" s="2" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B1559" s="2" t="s">
+        <v>3111</v>
+      </c>
     </row>
     <row r="1560" ht="25" customHeight="1" spans="1:2">
-      <c r="A1560" s="2"/>
-      <c r="B1560" s="2"/>
+      <c r="A1560" s="2" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1560" s="2" t="s">
+        <v>3113</v>
+      </c>
     </row>
     <row r="1561" ht="25" customHeight="1" spans="1:2">
-      <c r="A1561" s="2"/>
-      <c r="B1561" s="2"/>
+      <c r="A1561" s="2" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B1561" s="2" t="s">
+        <v>3115</v>
+      </c>
     </row>
     <row r="1562" ht="25" customHeight="1" spans="1:2">
-      <c r="A1562" s="2"/>
-      <c r="B1562" s="2"/>
+      <c r="A1562" s="2" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1562" s="2" t="s">
+        <v>3117</v>
+      </c>
     </row>
     <row r="1563" ht="25" customHeight="1" spans="1:2">
-      <c r="A1563" s="2"/>
-      <c r="B1563" s="2"/>
+      <c r="A1563" s="2" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B1563" s="2" t="s">
+        <v>3119</v>
+      </c>
     </row>
     <row r="1564" ht="25" customHeight="1" spans="1:2">
-      <c r="A1564" s="2"/>
-      <c r="B1564" s="2"/>
+      <c r="A1564" s="2" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1564" s="2" t="s">
+        <v>3121</v>
+      </c>
     </row>
     <row r="1565" ht="25" customHeight="1" spans="1:2">
-      <c r="A1565" s="2"/>
-      <c r="B1565" s="2"/>
+      <c r="A1565" s="2" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B1565" s="2" t="s">
+        <v>3123</v>
+      </c>
     </row>
     <row r="1566" ht="25" customHeight="1" spans="1:2">
-      <c r="A1566" s="2"/>
-      <c r="B1566" s="2"/>
+      <c r="A1566" s="2" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1566" s="2" t="s">
+        <v>3125</v>
+      </c>
     </row>
     <row r="1567" ht="25" customHeight="1" spans="1:2">
-      <c r="A1567" s="2"/>
-      <c r="B1567" s="2"/>
+      <c r="A1567" s="2" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1567" s="2" t="s">
+        <v>3127</v>
+      </c>
     </row>
     <row r="1568" ht="25" customHeight="1" spans="1:2">
-      <c r="A1568" s="2"/>
-      <c r="B1568" s="2"/>
+      <c r="A1568" s="2" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1568" s="2" t="s">
+        <v>3129</v>
+      </c>
     </row>
     <row r="1569" ht="25" customHeight="1" spans="1:2">
-      <c r="A1569" s="2"/>
-      <c r="B1569" s="2"/>
+      <c r="A1569" s="2" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B1569" s="2" t="s">
+        <v>3131</v>
+      </c>
     </row>
     <row r="1570" ht="25" customHeight="1" spans="1:2">
-      <c r="A1570" s="2"/>
-      <c r="B1570" s="2"/>
+      <c r="A1570" s="2" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B1570" s="2" t="s">
+        <v>3133</v>
+      </c>
     </row>
     <row r="1571" ht="25" customHeight="1" spans="1:2">
-      <c r="A1571" s="2"/>
-      <c r="B1571" s="2"/>
+      <c r="A1571" s="2" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B1571" s="2" t="s">
+        <v>3135</v>
+      </c>
     </row>
     <row r="1572" ht="25" customHeight="1" spans="1:2">
-      <c r="A1572" s="2"/>
-      <c r="B1572" s="2"/>
+      <c r="A1572" s="2" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B1572" s="2" t="s">
+        <v>3137</v>
+      </c>
     </row>
     <row r="1573" ht="25" customHeight="1" spans="1:2">
-      <c r="A1573" s="2"/>
-      <c r="B1573" s="2"/>
+      <c r="A1573" s="2" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B1573" s="2" t="s">
+        <v>3139</v>
+      </c>
     </row>
     <row r="1574" ht="25" customHeight="1" spans="1:2">
-      <c r="A1574" s="2"/>
-      <c r="B1574" s="2"/>
+      <c r="A1574" s="2" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B1574" s="2" t="s">
+        <v>3141</v>
+      </c>
     </row>
     <row r="1575" ht="25" customHeight="1" spans="1:2">
-      <c r="A1575" s="2"/>
-      <c r="B1575" s="2"/>
+      <c r="A1575" s="2" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B1575" s="2" t="s">
+        <v>3143</v>
+      </c>
     </row>
     <row r="1576" ht="25" customHeight="1" spans="1:2">
-      <c r="A1576" s="2"/>
-      <c r="B1576" s="2"/>
+      <c r="A1576" s="2" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B1576" s="2" t="s">
+        <v>3145</v>
+      </c>
     </row>
     <row r="1577" ht="25" customHeight="1" spans="1:2">
-      <c r="A1577" s="2"/>
-      <c r="B1577" s="2"/>
+      <c r="A1577" s="2" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B1577" s="2" t="s">
+        <v>3147</v>
+      </c>
     </row>
     <row r="1578" ht="25" customHeight="1" spans="1:2">
-      <c r="A1578" s="2"/>
-      <c r="B1578" s="2"/>
+      <c r="A1578" s="2" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B1578" s="2" t="s">
+        <v>3149</v>
+      </c>
     </row>
     <row r="1579" ht="25" customHeight="1" spans="1:2">
-      <c r="A1579" s="2"/>
-      <c r="B1579" s="2"/>
+      <c r="A1579" s="2" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B1579" s="2" t="s">
+        <v>3151</v>
+      </c>
     </row>
     <row r="1580" ht="25" customHeight="1" spans="1:2">
-      <c r="A1580" s="2"/>
-      <c r="B1580" s="2"/>
+      <c r="A1580" s="2" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1580" s="2" t="s">
+        <v>3153</v>
+      </c>
     </row>
     <row r="1581" ht="25" customHeight="1" spans="1:2">
-      <c r="A1581" s="2"/>
-      <c r="B1581" s="2"/>
+      <c r="A1581" s="2" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1581" s="2" t="s">
+        <v>3155</v>
+      </c>
     </row>
     <row r="1582" ht="25" customHeight="1" spans="1:2">
-      <c r="A1582" s="2"/>
-      <c r="B1582" s="2"/>
+      <c r="A1582" s="2" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1582" s="2" t="s">
+        <v>3157</v>
+      </c>
     </row>
     <row r="1583" ht="25" customHeight="1" spans="1:2">
-      <c r="A1583" s="2"/>
-      <c r="B1583" s="2"/>
+      <c r="A1583" s="2" t="s">
+        <v>3158</v>
+      </c>
+      <c r="B1583" s="2" t="s">
+        <v>3159</v>
+      </c>
     </row>
     <row r="1584" ht="25" customHeight="1" spans="1:2">
-      <c r="A1584" s="2"/>
-      <c r="B1584" s="2"/>
+      <c r="A1584" s="2" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1584" s="2" t="s">
+        <v>3161</v>
+      </c>
     </row>
     <row r="1585" ht="25" customHeight="1" spans="1:2">
-      <c r="A1585" s="2"/>
-      <c r="B1585" s="2"/>
+      <c r="A1585" s="2" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B1585" s="2" t="s">
+        <v>3163</v>
+      </c>
     </row>
     <row r="1586" ht="25" customHeight="1" spans="1:2">
-      <c r="A1586" s="2"/>
-      <c r="B1586" s="2"/>
+      <c r="A1586" s="2" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1586" s="2" t="s">
+        <v>3165</v>
+      </c>
     </row>
     <row r="1587" ht="25" customHeight="1" spans="1:2">
-      <c r="A1587" s="2"/>
-      <c r="B1587" s="2"/>
+      <c r="A1587" s="2" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1587" s="2" t="s">
+        <v>3167</v>
+      </c>
     </row>
     <row r="1588" ht="25" customHeight="1" spans="1:2">
-      <c r="A1588" s="2"/>
-      <c r="B1588" s="2"/>
+      <c r="A1588" s="2" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1588" s="2" t="s">
+        <v>3169</v>
+      </c>
     </row>
     <row r="1589" ht="25" customHeight="1" spans="1:2">
-      <c r="A1589" s="2"/>
-      <c r="B1589" s="2"/>
+      <c r="A1589" s="2" t="s">
+        <v>3170</v>
+      </c>
+      <c r="B1589" s="2" t="s">
+        <v>3171</v>
+      </c>
     </row>
     <row r="1590" ht="25" customHeight="1" spans="1:2">
-      <c r="A1590" s="2"/>
-      <c r="B1590" s="2"/>
+      <c r="A1590" s="2" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1590" s="2" t="s">
+        <v>3173</v>
+      </c>
     </row>
     <row r="1591" ht="25" customHeight="1" spans="1:2">
-      <c r="A1591" s="2"/>
-      <c r="B1591" s="2"/>
+      <c r="A1591" s="2" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B1591" s="2" t="s">
+        <v>3175</v>
+      </c>
     </row>
     <row r="1592" ht="25" customHeight="1" spans="1:2">
-      <c r="A1592" s="2"/>
-      <c r="B1592" s="2"/>
+      <c r="A1592" s="2" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B1592" s="2" t="s">
+        <v>3177</v>
+      </c>
     </row>
     <row r="1593" ht="25" customHeight="1" spans="1:2">
-      <c r="A1593" s="2"/>
-      <c r="B1593" s="2"/>
+      <c r="A1593" s="2" t="s">
+        <v>3178</v>
+      </c>
+      <c r="B1593" s="2" t="s">
+        <v>3179</v>
+      </c>
     </row>
     <row r="1594" ht="25" customHeight="1" spans="1:2">
-      <c r="A1594" s="2"/>
-      <c r="B1594" s="2"/>
+      <c r="A1594" s="2" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B1594" s="2" t="s">
+        <v>3181</v>
+      </c>
     </row>
     <row r="1595" ht="25" customHeight="1" spans="1:2">
-      <c r="A1595" s="2"/>
-      <c r="B1595" s="2"/>
+      <c r="A1595" s="2" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B1595" s="2" t="s">
+        <v>3183</v>
+      </c>
     </row>
     <row r="1596" ht="25" customHeight="1" spans="1:2">
-      <c r="A1596" s="2"/>
-      <c r="B1596" s="2"/>
+      <c r="A1596" s="2" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B1596" s="2" t="s">
+        <v>3185</v>
+      </c>
     </row>
     <row r="1597" ht="25" customHeight="1" spans="1:2">
-      <c r="A1597" s="2"/>
-      <c r="B1597" s="2"/>
+      <c r="A1597" s="2" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B1597" s="2" t="s">
+        <v>3187</v>
+      </c>
     </row>
     <row r="1598" ht="25" customHeight="1" spans="1:2">
-      <c r="A1598" s="2"/>
-      <c r="B1598" s="2"/>
+      <c r="A1598" s="2" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B1598" s="2" t="s">
+        <v>3189</v>
+      </c>
     </row>
     <row r="1599" ht="25" customHeight="1" spans="1:2">
-      <c r="A1599" s="2"/>
-      <c r="B1599" s="2"/>
+      <c r="A1599" s="2" t="s">
+        <v>3190</v>
+      </c>
+      <c r="B1599" s="2" t="s">
+        <v>3191</v>
+      </c>
     </row>
     <row r="1600" ht="25" customHeight="1" spans="1:2">
-      <c r="A1600" s="2"/>
-      <c r="B1600" s="2"/>
+      <c r="A1600" s="2" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B1600" s="2" t="s">
+        <v>3193</v>
+      </c>
     </row>
     <row r="1601" ht="25" customHeight="1" spans="1:2">
-      <c r="A1601" s="2"/>
-      <c r="B1601" s="2"/>
+      <c r="A1601" s="2" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B1601" s="2" t="s">
+        <v>3195</v>
+      </c>
     </row>
     <row r="1602" ht="25" customHeight="1" spans="1:2">
       <c r="A1602" s="2"/>

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="3196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="3387">
   <si>
     <t>bangla</t>
   </si>
@@ -3831,7 +3831,7 @@
     <t>শুনেছি তোমার বড় ভাইয়ের নাকি চাকরি হয়েছে?</t>
   </si>
   <si>
-    <t>উইন্নি তোঁয়ার বদ্দার বলে চরি অইয়্যি?</t>
+    <t>উইন্নি তোঁয়ার বদ্দার বলে চঅরি অইয়্যি?</t>
   </si>
   <si>
     <t>বড় ভাইয়ের শ্বশুরবাড়ি অনেক দূরে</t>
@@ -4543,13 +4543,13 @@
     <t>বন্ধু, যদি পারিস তাহলে আমাকে একটা চাকরি খুঁজে দে</t>
   </si>
   <si>
-    <t>বন্ধু, যরি পারুস তইলি আঁরে এক্কান চরি থোওয়াই দে</t>
+    <t>বন্ধু, যরি পারুস তইলি আঁরে এক্কান চঅরি থোওয়াই দে</t>
   </si>
   <si>
     <t>আমি যদি চাকরি না করি, তাহলে আমার পরিবার কষ্ট পাবে</t>
   </si>
   <si>
-    <t>আঁই যদি চরি ন গরি, তইলি আঁর পরিবার হষ্ট ফাইবু</t>
+    <t>আঁই যদি চঅরি ন গরি, তইলি আঁর পরিবার হষ্ট ফাইবু</t>
   </si>
   <si>
     <t>জমিদার আংকেল বলছে ব্যাচেলর ভাড়া দেবে না</t>
@@ -4561,7 +4561,7 @@
     <t>এভাবে আস্তে আস্তে কাজ করলে সারাদিন চলে যাবে</t>
   </si>
   <si>
-    <t>এন গরি আস্তে আস্তে হাম গরিলি পুরোদিন চলি যাইবু</t>
+    <t>এন গরি আস্তে আস্তে হাম গরিলি ফুরোদিন চলি যাইবু</t>
   </si>
   <si>
     <t>কাপড়গুলো আমি এসে ধুব</t>
@@ -7516,7 +7516,7 @@
     <t>আমার নতুন চাকরি হয়েছে ঢাকায়, তাই আজকে রাতে ট্রেনে উঠতে হবে</t>
   </si>
   <si>
-    <t>আত্তুন নতুন চরি অইয়্যি ঢাহাত, এতেল্লে আজিয়ে রাতিয়ে ট্রেনুত উডন ফরিবু</t>
+    <t>আত্তুন নতুন চঅরি অইয়্যি ঢাহাত, এতেল্লে আজিয়ে রাতিয়ে ট্রেনুত উডন ফরিবু</t>
   </si>
   <si>
     <t>আমার ৩ তারিখ একটা গুরুত্বপূর্ণ ইন্টারভিউ আছে, সেটার জন্য ঢাকা যেতে হবে</t>
@@ -8158,7 +8158,7 @@
     <t>এবার ঘরের ছালাটা ঠিক করতে হবে, নাহয় বর্ষাকালে পানি পড়বে</t>
   </si>
   <si>
-    <t xml:space="preserve">এবার ঘরুর ছাল ইয়েন ঠিক গরন ফরিবু, নইলি বর্ষাহালে পানি ফরিবু </t>
+    <t>এবার ঘরুর ছাল ইয়েন ঠিক গরন ফরিবু, নইলি বর্ষাহালে পানি ফরিবু</t>
   </si>
   <si>
     <t>এ বছর বৃষ্টি বেশি হওয়ার কারণে ফসলের অনেক ক্ষতি হয়েছে</t>
@@ -8266,7 +8266,7 @@
     <t>বন্ধুর সঙ্গে বাইক নিয়ে বের হয়েছিলাম, রাস্তায় হঠাৎ বৃষ্টি চলে আসে</t>
   </si>
   <si>
-    <t xml:space="preserve">বন্ধুর লগে বাইক লই বাইর অইলাম, রাস্তাত হঠাৎ ঝর চলি আইসসি </t>
+    <t>বন্ধুর লগে বাইক লই বাইর অইলাম, রাস্তাত হঠাৎ ঝর চলি আইসসি</t>
   </si>
   <si>
     <t>ছাতা ছাড়া বের হয়েছিলাম, বৃষ্টি আসার কারণে পুরো ভিজে গেছি</t>
@@ -9418,7 +9418,7 @@
     <t>চাকরি একটা চলে গেছে তো কী হয়েছে, আল্লাহ চাইলে আরও ভালো চাকরি আসবে</t>
   </si>
   <si>
-    <t>চরি এক্কান চলি গেইয়্যি তো কী অইয়্যি, আল্লাহ চাইলি আরো ভালা চরি আইবু</t>
+    <t>চঅরি এক্কান চলি গেইয়্যি তো কী অইয়্যি, আল্লাহ চাইলি আরো ভালা চঅরি আইবু</t>
   </si>
   <si>
     <t>অতীতে কী হয়েছে সেটা না ভেবে সামনে কী হবে, সেটা চিন্তা করতে হবে</t>
@@ -9719,6 +9719,599 @@
   </si>
   <si>
     <t>বাসাত পরি ন গেলি পরীক্ষের হল উত আরেকজনুত্তুন সাই সাই লেহন ফরিবু</t>
+  </si>
+  <si>
+    <t>পাশের রুম থেকে একটা চেয়ার নিয়ে আসো</t>
+  </si>
+  <si>
+    <t>পাশুর রুমুত্তুন এক্কান চিয়ার লই আইয়্যো</t>
+  </si>
+  <si>
+    <t>আমি এটা খাব না, তুমি আরেকটা নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>আঁই ইবে হাইতাম নো, তুঁই আরেকগো লই আইয়্যো</t>
+  </si>
+  <si>
+    <t>এটা আমার ভালো লাগছে না, এটা এখান থেকে নিয়ে যাও</t>
+  </si>
+  <si>
+    <t>ইয়েন আত্তুন ভালা ন লার, ইয়েন এত্তুন লই যও</t>
+  </si>
+  <si>
+    <t>তুই আমার চাকর, আমি যা বলব তোকে তা শুনতে হবে</t>
+  </si>
+  <si>
+    <t>তুই আঁর চঅর, আঁই যা হইয়্যুম তোরতুন তা উনোন ফরিবু</t>
+  </si>
+  <si>
+    <t>তুই যদি আমার কথা মতো কাজ না করিস, তাহলে তোর চাকরি চলে যাবে</t>
+  </si>
+  <si>
+    <t>তুই যদি আঁর হতা মতো হাজ ন গরস, তইলি তোর চঅরি চলি যাইবু</t>
+  </si>
+  <si>
+    <t>আমি তোর মালিক, তোকে আমার কথা শুনতেই হবে</t>
+  </si>
+  <si>
+    <t>আঁই তোর মালিক, তোরতুন আঁর হতা উননই ফরিবু</t>
+  </si>
+  <si>
+    <t>তুই আমার চাকর হয়ে আমার মুখের ওপর কথা বলিস!</t>
+  </si>
+  <si>
+    <t>তুই আঁর চঅর অইয়্যিরে আঁর মুখুর উদ্দি হতা হস!</t>
+  </si>
+  <si>
+    <t>তোর এত সাহস কীভাবে হলো! আমার কথার অবাধ্য হোস!</t>
+  </si>
+  <si>
+    <t>তোর এল্লেত সাহস কেনে অইয়্যি দে! আঁর হতার অবাধ্য অস!</t>
+  </si>
+  <si>
+    <t>এই ঘরে আমি যেটা বলব, সেটাই হবে। অন্য কারও কথা এই ঘরে চলবে না</t>
+  </si>
+  <si>
+    <t>এই ঘরুত আঁই যিয়েন হইয়্যুম ইয়েন অইবু, অন্য কিয়ার হতা এই ঘরুত ন চলিবু</t>
+  </si>
+  <si>
+    <t>আমি ঘুম থেকে ওঠার আগে যেন আমার সকালের নাস্তা রেডি থাকে</t>
+  </si>
+  <si>
+    <t>আঁই ঘুমুত্তুন উডিবের আগে যেন আঁর সকালুর নাস্তা রেডি থাহে</t>
+  </si>
+  <si>
+    <t>আমার কথা মতো না চললে এই ঘর থেকে চলে যা</t>
+  </si>
+  <si>
+    <t>আঁর হতা মতন ন চিলিলি এই ঘরুত্তুন চলি যা</t>
+  </si>
+  <si>
+    <t>আমার নাস্তা করার সময় নেই, তুমি নাস্তাগুলো একটা টিফিনে করে দিয়ে দাও</t>
+  </si>
+  <si>
+    <t>আত্তুন নাস্তা গরিবের সময় নেই, তুঁই নাস্তা এগিন উজ্ঞো টিফিন গরি দি দও</t>
+  </si>
+  <si>
+    <t>তুমি কি আমার জন্য একটা কাজ করতে পারবে?</t>
+  </si>
+  <si>
+    <t>তুঁই কি আঁর লাই এক্কাম হাজ গরিত ফারিবে?</t>
+  </si>
+  <si>
+    <t>কাজটা একটু কঠিন, যদি তুমি না চাও, তাহলে আমি তোমাকে জোর করব না</t>
+  </si>
+  <si>
+    <t>হাজ ইয়েন এক্কানা কঠিন, যদি তুঁই ন চও তইলি আঁই তোঁয়ারে জোর গইত্তাম নো</t>
+  </si>
+  <si>
+    <t>আমি ড্রাইভারকে দিয়ে গাড়ি পাঠিয়ে দিচ্ছি, তুমি একটু অপেক্ষা করো</t>
+  </si>
+  <si>
+    <t>আঁই ড্রাইভার উরে দি গারি পাঠাই দি, তুঁই এক্কানা অপেক্ষা গরো</t>
+  </si>
+  <si>
+    <t>সারাদিন অফিস করে আসলাম, আমার জন্য এক কাপ কফি বানিয়ে নিয়ে এসো</t>
+  </si>
+  <si>
+    <t>আরাদিন অফিস গরি আইলাম, আঁর লাই এক হাপ কফি বানাই লই আইয়্যো</t>
+  </si>
+  <si>
+    <t>আজ থেকে তুমি প্রতিদিন সকালে হাঁটতে বের হবে</t>
+  </si>
+  <si>
+    <t>আজিয়েত্তুন তুঁই ফইত্তোদিন বেইন্নে আইট্টো বাইর অইবে</t>
+  </si>
+  <si>
+    <t>আমি তোমার বড় হিসেবে এই উপদেশটা দিলাম</t>
+  </si>
+  <si>
+    <t>আঁই তোঁয়ার বরো হিসেবে এই উপদেশ ইয়েন দিলাম</t>
+  </si>
+  <si>
+    <t>আমার মতে তোমার ওখানে না যাওয়া উচিত, কারণ ওখানে আমি একবার গিয়েছিলাম</t>
+  </si>
+  <si>
+    <t>আঁর মতে তোঁয়ার অনডে ন যন উচিত, হারন এনডে আঁই একবার গেইলাম</t>
+  </si>
+  <si>
+    <t>সবসময় হাসিখুশি থাকবা, তোমাকে হাসিখুশি দেখলে মিষ্টি লাগে</t>
+  </si>
+  <si>
+    <t>সবসময় আসিখুশি থাহিবে, তোঁয়ারে আশিখুশি দেহিলি মিষ্টি লাগে</t>
+  </si>
+  <si>
+    <t>আমাকে স্যার নিষেধ করেছিলেন, তাই এটা আমি করতে পারব না</t>
+  </si>
+  <si>
+    <t>আঁরে স্যার মানা গইজ্জিল, এতেল্লে ইয়েন আঁই গরিত ন ফাইজ্জুম</t>
+  </si>
+  <si>
+    <t>আম্মু বাসায় জলদি চলে যেতে বলেছিলেন</t>
+  </si>
+  <si>
+    <t>আম্মু বাসাত হারা চলি যাইতু হইয়্যিল</t>
+  </si>
+  <si>
+    <t>এটা করা একদম ঠিক হবে না, তুমি আরেকবার চিন্তা করে দেখো</t>
+  </si>
+  <si>
+    <t>ইয়েন গরন একদম ঠিক ন অইবু, তুঁই আরেকবার চিন্তে গরি সো</t>
+  </si>
+  <si>
+    <t>আমি যেটার জন্য ভয় পাচ্ছিলাম, সেটাই হচ্ছে। এখন যা করার ভেবেচিন্তে করতে হবে আমাদের</t>
+  </si>
+  <si>
+    <t>আঁই যিয়েনুর লাই ডরাইর ইয়েনই অর, এহন যা গরার ভাবিচিন্তে গরন ফরিবু আরাত্তুন</t>
+  </si>
+  <si>
+    <t>তুমি আরেকবার ভালো করে চেক করে দেখো</t>
+  </si>
+  <si>
+    <t>তুঁই আরেকবার ভালা গরি চেক গরি সো</t>
+  </si>
+  <si>
+    <t>লিস্টে কি আমার নাম আসেনি? এমন তো হওয়ার কথা না</t>
+  </si>
+  <si>
+    <t>লিস্ট উত কি আঁর নাম ন আইয়্যি? এরহম অইবের তো হতা নো</t>
+  </si>
+  <si>
+    <t>চুরি করে কোনো কিছু অর্জন করে কী লাভ?</t>
+  </si>
+  <si>
+    <t>চুরি গরি হনো কিছু অর্জন গরি কি লাভ?</t>
+  </si>
+  <si>
+    <t>আমি তোকে নিষেধ করার পরও ওখানে কেন গেলি?</t>
+  </si>
+  <si>
+    <t>আঁই তোরে মানা গরিবের পরও অনডে কিল্লে গেলি?</t>
+  </si>
+  <si>
+    <t>আমাদের পথ এখানেই শেষ না, আজ হেরে গেছি তো কী হয়েছে</t>
+  </si>
+  <si>
+    <t>আরার পথ এনডেই শেষ নো, আজিয়ে অডি গেই তো কী অইয়্যি</t>
+  </si>
+  <si>
+    <t>তুই এগুলো নিয়েছিস কত দিন হচ্ছে?</t>
+  </si>
+  <si>
+    <t>তুই এগিন লইয়্যুস হতদিন অর?</t>
+  </si>
+  <si>
+    <r>
+      <t>আমার তো ঠিকমতো মনে নেই, মনে হয় ১৫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
+      <t>২০ দিন হবে</t>
+    </r>
+  </si>
+  <si>
+    <t>আঁর তো ঠিকমতো মনুত নেই, মনে অয় ১৫-২০ দিন অইবু</t>
+  </si>
+  <si>
+    <t>ভাই, এক গ্লাস ঠান্ডা পানি দিন তো, খুব পানির তৃষ্ণা পেয়েছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, এক গ্লাস ঠান্ডা পানি দন তো, বত পানির তিরেশ পেইয়্যি</t>
+  </si>
+  <si>
+    <t>আম্মু, আমার জন্য একটু ভাত বেড়ে দাও, অনেক ক্ষুধা লেগেছে</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁর লাই এক্কানা ভাত বারি দও, বত ভুক গেইজ্ঞি</t>
+  </si>
+  <si>
+    <t>দরজাটা একটু বন্ধ করে দাও, বাইরে থেকে শব্দ আসছে</t>
+  </si>
+  <si>
+    <t>দরজা ইয়েন বন্ধ গরি দও, বাইরেত্তুন শব্দ আইয়্যির</t>
+  </si>
+  <si>
+    <t>বাইরে এভাবে চিৎকার করছে কে? আমার আগামীকাল পরীক্ষা</t>
+  </si>
+  <si>
+    <t>বাইরে এল্লেত চিল্লেদ্দে হনে? আঁর হালিয়ে পরীক্ষে</t>
+  </si>
+  <si>
+    <t>মা, আমার জামাকাপড়গুলো একটু গুছিয়ে রাখো তো</t>
+  </si>
+  <si>
+    <t>মা, আঁর হরচুর এগিন এক্কানা গুছাই রাহো তো</t>
+  </si>
+  <si>
+    <t>স্যার, একটু শুনুন, আমার একটা জরুরি কথা বলার ছিল</t>
+  </si>
+  <si>
+    <t>স্যার, এক্কানা উনন, আঁর এক্কান জরুরি হতা হইবের আছিল</t>
+  </si>
+  <si>
+    <t>তুমি একটু এদিকে আসো, তোমার সঙ্গে একটু কথা বলতে চায়</t>
+  </si>
+  <si>
+    <t>তুঁই এক্কানা ইক্কে আইয়্যো, তোঁয়ার লগে এক্কানা হতা হইতাম চায়</t>
+  </si>
+  <si>
+    <t>তুমি এই রাস্তা দিয়ে কোথায় যাচ্ছ?</t>
+  </si>
+  <si>
+    <t>তুঁই এই রাস্তা দি হনডে যার?</t>
+  </si>
+  <si>
+    <t>তোমার বাড়ি তো এই রাস্তা দিয়ে না, তাহলে এই রাস্তায় কী করছ?</t>
+  </si>
+  <si>
+    <t>তোঁয়ার বারি তো রাস্তা ইবে দি নো, তইলি এই রাস্তাত কি গরের?</t>
+  </si>
+  <si>
+    <t>তোমাকে তো আগে কখনো এই গ্রামে দেখিনি, তোমার বাড়ি কোথায়?</t>
+  </si>
+  <si>
+    <t>তোঁয়ারে তো আগে হনোদিন এই গ্রামুত ন দেহি, তোঁয়ার বারি হনডে?</t>
+  </si>
+  <si>
+    <t>আমার বাড়ি পাশের গ্রামে, আমি মনজুর ভাইয়ের সঙ্গে দেখা করতে এসেছি</t>
+  </si>
+  <si>
+    <t>আঁর বারি পাশুর গ্রামুত, আঁই মনজুর ভাইয়্যুর লগে দেহা গইত্তাম আইসসি</t>
+  </si>
+  <si>
+    <t>তোমার সাহস তো কম না, তুমি অন্য গ্রামের হয়ে এই গ্রামের মেয়েকে ডিস্টার্ব করো!</t>
+  </si>
+  <si>
+    <t>তোঁয়ার সাহস তো হম নো, তুঁই অন্য গ্রামুর অইয়্যিরে এই গ্রামুর মাইফোয়ারে ডিস্টার্ব গরো!</t>
+  </si>
+  <si>
+    <t>যদি ঝামেলা করতে না চাও, তাহলে এখনই এখান থেকে চলে যাও</t>
+  </si>
+  <si>
+    <t>যদি ঝামিলে গইত্তো ন চও তইলি এহনই এত্তুন চলি যও</t>
+  </si>
+  <si>
+    <t>আমি তোমার আব্বুকে চিনি, উনি তো অনেক ভালো মনের মানুষ</t>
+  </si>
+  <si>
+    <t>আঁই তোঁয়ার আব্বুরে চিনি, ইবে তো বত ভালা মনুর মানুষ</t>
+  </si>
+  <si>
+    <t>তোমার আব্বুর দিকে তাকিয়ে তোমাকে মাফ করে দিলাম</t>
+  </si>
+  <si>
+    <t>তোঁয়ার আব্বুর মিক্কে চায় তোঁয়ারে মাফ গরি দিলাম</t>
+  </si>
+  <si>
+    <t>আপু, আমার চুলটা একটু বেঁধে দাও না</t>
+  </si>
+  <si>
+    <t>আফা, আঁর চুলগিন এক্কানা বাধি দও না</t>
+  </si>
+  <si>
+    <t>তোর চুল এত এলোমেলো কেন? মাথায় তেল দিস না?</t>
+  </si>
+  <si>
+    <t>তোর চুল এতো অলফল কা? মাথাত তেল ন দস?</t>
+  </si>
+  <si>
+    <t>বাবা, স্যার বললেন স্কুলের বেতন আজ দিয়ে দিতে</t>
+  </si>
+  <si>
+    <t>বাবা, স্যার হইয়্যিল স্কুলুর বেতন আজিয়ে দি দিতো</t>
+  </si>
+  <si>
+    <t>স্কুলের বেতন না দিলে স্কুলে ঢুকতে দেবে না বলল</t>
+  </si>
+  <si>
+    <t>স্কুলুর বেতন ন দিলি স্কুতুত ঢুইকতো ন দিবু হইয়্যি</t>
+  </si>
+  <si>
+    <t>একটু জোরে কথা বলো, পেছন থেকে ঠিকমতো শুনতে পারছি না</t>
+  </si>
+  <si>
+    <t>এক্কানা জোরে হতা হও, পিছুত্তুন ঠিকমতো উনিত ন পারির</t>
+  </si>
+  <si>
+    <t>তুমি কি সবসময় এভাবে ছোট করে কথা বলো?</t>
+  </si>
+  <si>
+    <t>তুঁই কি সবসময় এল্লেত ছোডো গরি হতা হও</t>
+  </si>
+  <si>
+    <t>তোমার ভয়েস অনেক নিচু, শুনতে অনেক সমস্যা হয়</t>
+  </si>
+  <si>
+    <t>তোঁয়ার ভয়েস বত নিচু, উনতে বত সমস্যা অয়</t>
+  </si>
+  <si>
+    <t>ঝগড়া করলে তো গলার সুর একদম পরিবর্তন হয়ে যায়</t>
+  </si>
+  <si>
+    <t>হইজ্জে গরিলি তো গলার সুর এব্বেরে পরিবর্তন অই যায়</t>
+  </si>
+  <si>
+    <t>ভাই, গাড়িটা একটু সরিয়ে নিন, রাস্তা আটকে আছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, গারি ইয়েন এক্কানা সরাই লন, রাস্তা আটকি আছে</t>
+  </si>
+  <si>
+    <t>স্যার, কাগজটায় একটু সই করে দিন, দেরি হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>স্যার, হাগজ ইয়েনুত এক্কানা সই গরি দন, দেরি অই যার</t>
+  </si>
+  <si>
+    <t>তুমি যেকোনোভাবে আজকের মধ্যেই কাগজে সই করে নাও</t>
+  </si>
+  <si>
+    <t>তুঁই যেহনোভাবে আজিয়ের মধ্যেই হাগজুত সই গরি লও</t>
+  </si>
+  <si>
+    <t>আপনি একটু বসুন, আমি চা নিয়ে আসছি</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা বইয়্যুন, আঁই চা লই আইর</t>
+  </si>
+  <si>
+    <t>বাবা, তুমি যাওয়ার সময় আমাকে একটু বাজারে নামিয়ে দিও</t>
+  </si>
+  <si>
+    <t>বাবা, তুঁই যাইবের সমত আঁরে এক্কানা বাজারুত নামাই দিও</t>
+  </si>
+  <si>
+    <t>সন্ধ্যার পর দরজা-জানালা সব বন্ধ করে দিস</t>
+  </si>
+  <si>
+    <t>আজুইন্নের পর দরজা-জানালা বিয়াক বন্ধ গরি দিস</t>
+  </si>
+  <si>
+    <t>আমাদের ফিরতে দেরি হলে সন্ধ্যার আগে বাইরে থেকে সব কাপড় ঘরে ঢুকিয়ে ফেলিস</t>
+  </si>
+  <si>
+    <t>আত্তুন ফিরতে দেরি অইলি আজুইন্নের আগে বাইরেত্তুন বিয়াক হর ঢুকই ফেলাইস</t>
+  </si>
+  <si>
+    <t>আমি ডাক্তারের সিরিয়াল পেয়েছি একদম শেষে, সবই বিরক্ত লাগছে</t>
+  </si>
+  <si>
+    <t>আঁই ডাক্তারুর সিরিয়েল পাইদি এব্বেরে শেষে, বিয়াক বিরক্ত লাগের</t>
+  </si>
+  <si>
+    <t>আম্মু, আমার মাথায় একটু তেল দিয়ে দাও না</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁর মাথাত এক্কানা তেল দি দও না</t>
+  </si>
+  <si>
+    <t>তোর শাশুড়িকে বলিস সামনের মাসে বেড়াতে আসতে</t>
+  </si>
+  <si>
+    <t>তোর অরিরে হইস সামনুর মাসুত বেরাইতু আইসতো</t>
+  </si>
+  <si>
+    <t>টিভির শব্দটা একটু কমিয়ে দে, তোর আপুর পরীক্ষা</t>
+  </si>
+  <si>
+    <t>টিভির আওয়াজ এক্কানা হমাও দে, তোর আফার পরীক্ষে</t>
+  </si>
+  <si>
+    <t>আপনি একটু এখানে দাঁড়ান, আমি ডাক্তারকে ডেকে আনছি</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা এনডে থিয়ন, আঁই ডাক্তার উরে ডাহি আনির</t>
+  </si>
+  <si>
+    <t>মা, আমার ব্যাগে একটু খাবার ভরে দাও, সারাদিন বাইরে থাকব</t>
+  </si>
+  <si>
+    <t>মা, আঁর ব্যাগুত এক্কানা হানা ভরি দও, আরাদিন বাইরে থাইক্কুম</t>
+  </si>
+  <si>
+    <t>ভাই, এই ঠিকানাটা কোথায় একটু বলতে পারবেন?</t>
+  </si>
+  <si>
+    <t>বদ্দা, এই ঠিকানা ইয়েন হনডে এক্কানা হইত ফারিবেন?</t>
+  </si>
+  <si>
+    <t>বউ, রান্নায় ঝাল একটু কম দিও, গতকাল আমার পেট জ্বালা করেছিল</t>
+  </si>
+  <si>
+    <t>বউ, রান্নাত ঝাল এক্কানা হম দিও, গত হালিয়ে আঁর পেট জইল্লিল</t>
+  </si>
+  <si>
+    <t>ভাই, আরেকটু সাইড করুন আপনার গাড়িটা, রাস্তায় জ্যাম লেগে গেছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, আরেক্কানা সাইড গরন অঁনোর গারি ইয়েন, রাস্তাত জ্যাম লাগি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>আপনি একটু বাইরে যান, আমি কাপড় পাল্টে নিই</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা বাইরে যন, আঁই হর পাল্ডায় লই</t>
+  </si>
+  <si>
+    <t>ভাই, দোকান থেকে এক প্যাকেট বিস্কুট আর একটা কোল্ড ড্রিংক নিয়ে আয়</t>
+  </si>
+  <si>
+    <t>বদ্দা, দোয়ানুত্তুন এক প্যাকেট বিস্কুট আর উজ্ঞো কোল্ড ড্রিংক লই আয়</t>
+  </si>
+  <si>
+    <t>মা, আমার জামাটা একটু ইস্ত্রি করে রাখো, কাল পরতে হবে</t>
+  </si>
+  <si>
+    <t>মা, আঁর হুত্তা ইবে এক্কানা ইস্ত্রি গরি রাহো, হালিয়ে পরন ফরিবু</t>
+  </si>
+  <si>
+    <t>ভাই, একটু ডান দিকে যান, বাম দিকে রাস্তা বন্ধ আছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, এক্কানা ডান দিকে যন, বাম দিকে রাস্তা বন্ধ আছে</t>
+  </si>
+  <si>
+    <t>আমার বাসা তো ডান দিকে, আপনি বাম দিকে কেন যাচ্ছেন?</t>
+  </si>
+  <si>
+    <t>আঁর বাসা তো ডান দিকে, অঁনে বাম দিকে কিল্লে যার?</t>
+  </si>
+  <si>
+    <t>স্যার, আমার রিপোর্টটা একটু দেখেন, যদি কোনো জায়গায় ভুল থাকে তাহলে ঠিক করব</t>
+  </si>
+  <si>
+    <t>স্যার, আঁর রিপোর্ট ইয়েন এক্কানা সন, যদি হনো জাগাত ভুল থাহে তইলি ঠিক গইজ্জুম</t>
+  </si>
+  <si>
+    <t>লাইটটা একটু জ্বালিয়ে দাও, ঘরে অন্ধকার হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>লাইট ইবে এক্কানা জালাই দও, ঘরুত আধার অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>স্যার, একটু বসুন, আপনার জন্য চেয়ার নিয়ে আসছি</t>
+  </si>
+  <si>
+    <t>স্যার, এক্কানা বইয়্যুন, অঁনোর লাই চিয়ার লই আইসসি</t>
+  </si>
+  <si>
+    <t>ভাই, গানটা একটু বন্ধ করুন, ফোনে কথা বলতে পারছি না</t>
+  </si>
+  <si>
+    <t>বদ্দা, গান ইবে এক্কানা বন্ধ গরন, ফোনুত হথা হইত ন ফারির</t>
+  </si>
+  <si>
+    <t>আপনি একটু ধৈর্য ধরুন, সব ঠিকঠাক হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা ধৈর্য ধরন, বিয়াক ঠিকঠাক অই যাইবু</t>
+  </si>
+  <si>
+    <t>আম্মু, আমার পরীক্ষা আগামীকাল, তাই আজ রাতে একটু তাড়াতাড়ি খাবার দিয়ে দাও</t>
+  </si>
+  <si>
+    <t>আম্মু, আঁর পরীক্ষে হালিয়ে, এতেল্লে আজিয়ে রাতিয়ে তারাতারি হানা দি দও</t>
+  </si>
+  <si>
+    <t>স্যার, আমার সিভিটা একটু দেখেন, আর কোথাও ভুল থাকলে ঠিক করে দিন</t>
+  </si>
+  <si>
+    <t>স্যার, আঁর সিভিগান এক্কানা সন, আর হনোমিক্কে ভুল থাহিলি ঠিক গরি দন</t>
+  </si>
+  <si>
+    <t>আপু, আমার হয়ে একটু মাকে ফোন করে বলো, আজ রাতে আসতে পারব না</t>
+  </si>
+  <si>
+    <t>আফা, আঁর অইয়্যিরে এক্কানা আম্মুরে ফোন গরি হও, আজিয়ে রাতিয়ে আইত ন ফাইজ্জুম</t>
+  </si>
+  <si>
+    <t>বাবা, আমার ল্যাপটপটা একটু ঠিক করিয়ে দাও, কাল থেকে অনলাইন ক্লাস আছে</t>
+  </si>
+  <si>
+    <t>বাবা, আঁর লেপটপ ইবে এক্কানা ঠিক গরি দও, হালিয়েত্তুন অনলাইন ক্লাস আছে</t>
+  </si>
+  <si>
+    <t>একটু সামনে গিয়ে দেখ তো কেন এত জ্যাম লেগে আছে</t>
+  </si>
+  <si>
+    <t>এক্কানা সামনে যায় সা তো কিল্লে এত জ্যাম লাগি আছে</t>
+  </si>
+  <si>
+    <t>ভাই, দয়া করে একটু সরে দাঁড়ান, পেছনের মানুষগুলো সামনে আসতে পারছে না</t>
+  </si>
+  <si>
+    <t>বদ্দা, দয়া গরি এক্কানা সরি থিয়ন, পিছুদ্দির মানুষ এগুন সামনে আইত ন পারের</t>
+  </si>
+  <si>
+    <t>আপনি একটু কষ্ট করে এই ফর্মটা পূরণ করে আগামীকালের মধ্যে জমা দিয়ে দিন</t>
+  </si>
+  <si>
+    <t>অঁনে এক্কানা হষ্ট গরি এই ফর্ম ইয়েন পুরন গরি হালিয়ের মধ্যে জমা দি দন</t>
+  </si>
+  <si>
+    <t>দেরি হয়ে গেলে সমস্যা হবে, তাই যা করার জলদি করুন</t>
+  </si>
+  <si>
+    <t>দেরি অই গেলি সমস্যা অইবু, এতেল্লে যা গরার হারা গরন</t>
+  </si>
+  <si>
+    <t>ভাই, রাস্তায় এত জোরে হর্ন দেবেন না, আশেপাশের মানুষজন বিরক্ত হচ্ছে</t>
+  </si>
+  <si>
+    <t>বদ্দা, রাস্তাত এল্লেত জোরে অরন ন দিবেন, আশেপাশুর মানুষজন বিরক্ত অর</t>
+  </si>
+  <si>
+    <t>স্যার, একটু ধীরে পড়ান, এত দ্রুত বললে আমরা নোট করতে পারছি না</t>
+  </si>
+  <si>
+    <t>স্যার, এক্কানা আস্তে পরন, এল্লেত দ্রুত হইলি আঁরা নোট গরিত ন পারির</t>
+  </si>
+  <si>
+    <t>সবাই সামনে থেকে সরে দাঁড়ান, ট্রাক আসছে</t>
+  </si>
+  <si>
+    <t>বাবা, তোমার সঙ্গে আমার কিছু কথা আছে</t>
+  </si>
+  <si>
+    <t>আমি সারাদিন না খেয়ে আছি, আমাকে কিছু খেতে দিন</t>
+  </si>
+  <si>
+    <t>আম্মু, একটু কষ্ট করে আমার ঘরটা গুছিয়ে দাও, বিকেলে মেহমান আসবে</t>
+  </si>
+  <si>
+    <t>আম্মু, আমার বন্ধু বাড়িতে আসবে, আজ একটু ভালো কিছু রান্না করো</t>
+  </si>
+  <si>
+    <t>মা, আজ একটু আগে রান্না করো, বাবার অফিসে যেতে দেরি হয়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>স্যার, আমার আবেদনটা একটু ওপরে পাঠিয়ে দিন, অনেক দিন ধরে আটকে আছে</t>
+  </si>
+  <si>
+    <t>ভাই, প্লিজ রাস্তার মাঝখানে গাড়ি না রেখে পাশে সরিয়ে নিন</t>
+  </si>
+  <si>
+    <t>বাবা, আমার সাইকেলটা একটু মেরামত করিয়ে দাও, চাকা নষ্ট হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আম্মু, আমার জন্য একটু শরবত বানিয়ে দাও, অনেক গরম লাগছে</t>
+  </si>
+  <si>
+    <t>আমি হিসাব করে দেখিনি কত টাকা আছে</t>
   </si>
 </sst>
 </file>
@@ -23704,407 +24297,789 @@
       </c>
     </row>
     <row r="1602" ht="25" customHeight="1" spans="1:2">
-      <c r="A1602" s="2"/>
-      <c r="B1602" s="2"/>
+      <c r="A1602" s="2" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B1602" s="2" t="s">
+        <v>3197</v>
+      </c>
     </row>
     <row r="1603" ht="25" customHeight="1" spans="1:2">
-      <c r="A1603" s="2"/>
-      <c r="B1603" s="2"/>
+      <c r="A1603" s="2" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1603" s="2" t="s">
+        <v>3199</v>
+      </c>
     </row>
     <row r="1604" ht="25" customHeight="1" spans="1:2">
-      <c r="A1604" s="2"/>
-      <c r="B1604" s="2"/>
+      <c r="A1604" s="2" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B1604" s="2" t="s">
+        <v>3201</v>
+      </c>
     </row>
     <row r="1605" ht="25" customHeight="1" spans="1:2">
-      <c r="A1605" s="2"/>
-      <c r="B1605" s="2"/>
+      <c r="A1605" s="2" t="s">
+        <v>3202</v>
+      </c>
+      <c r="B1605" s="2" t="s">
+        <v>3203</v>
+      </c>
     </row>
     <row r="1606" ht="25" customHeight="1" spans="1:2">
-      <c r="A1606" s="2"/>
-      <c r="B1606" s="2"/>
+      <c r="A1606" s="2" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1606" s="2" t="s">
+        <v>3205</v>
+      </c>
     </row>
     <row r="1607" ht="25" customHeight="1" spans="1:2">
-      <c r="A1607" s="2"/>
-      <c r="B1607" s="2"/>
+      <c r="A1607" s="2" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B1607" s="2" t="s">
+        <v>3207</v>
+      </c>
     </row>
     <row r="1608" ht="25" customHeight="1" spans="1:2">
-      <c r="A1608" s="2"/>
-      <c r="B1608" s="2"/>
+      <c r="A1608" s="2" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B1608" s="2" t="s">
+        <v>3209</v>
+      </c>
     </row>
     <row r="1609" ht="25" customHeight="1" spans="1:2">
-      <c r="A1609" s="2"/>
-      <c r="B1609" s="2"/>
+      <c r="A1609" s="2" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B1609" s="2" t="s">
+        <v>3211</v>
+      </c>
     </row>
     <row r="1610" ht="25" customHeight="1" spans="1:2">
-      <c r="A1610" s="2"/>
-      <c r="B1610" s="2"/>
+      <c r="A1610" s="2" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B1610" s="2" t="s">
+        <v>3213</v>
+      </c>
     </row>
     <row r="1611" ht="25" customHeight="1" spans="1:2">
-      <c r="A1611" s="2"/>
-      <c r="B1611" s="2"/>
+      <c r="A1611" s="2" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B1611" s="2" t="s">
+        <v>3215</v>
+      </c>
     </row>
     <row r="1612" ht="25" customHeight="1" spans="1:2">
-      <c r="A1612" s="2"/>
-      <c r="B1612" s="2"/>
+      <c r="A1612" s="2" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B1612" s="2" t="s">
+        <v>3217</v>
+      </c>
     </row>
     <row r="1613" ht="25" customHeight="1" spans="1:2">
-      <c r="A1613" s="2"/>
-      <c r="B1613" s="2"/>
+      <c r="A1613" s="2" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B1613" s="2" t="s">
+        <v>3219</v>
+      </c>
     </row>
     <row r="1614" ht="25" customHeight="1" spans="1:2">
-      <c r="A1614" s="2"/>
-      <c r="B1614" s="2"/>
+      <c r="A1614" s="2" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B1614" s="2" t="s">
+        <v>3221</v>
+      </c>
     </row>
     <row r="1615" ht="25" customHeight="1" spans="1:2">
-      <c r="A1615" s="2"/>
-      <c r="B1615" s="2"/>
+      <c r="A1615" s="2" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B1615" s="2" t="s">
+        <v>3223</v>
+      </c>
     </row>
     <row r="1616" ht="25" customHeight="1" spans="1:2">
-      <c r="A1616" s="2"/>
-      <c r="B1616" s="2"/>
+      <c r="A1616" s="2" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B1616" s="2" t="s">
+        <v>3225</v>
+      </c>
     </row>
     <row r="1617" ht="25" customHeight="1" spans="1:2">
-      <c r="A1617" s="2"/>
-      <c r="B1617" s="2"/>
+      <c r="A1617" s="2" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B1617" s="2" t="s">
+        <v>3227</v>
+      </c>
     </row>
     <row r="1618" ht="25" customHeight="1" spans="1:2">
-      <c r="A1618" s="2"/>
-      <c r="B1618" s="2"/>
+      <c r="A1618" s="2" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B1618" s="2" t="s">
+        <v>3229</v>
+      </c>
     </row>
     <row r="1619" ht="25" customHeight="1" spans="1:2">
-      <c r="A1619" s="2"/>
-      <c r="B1619" s="2"/>
+      <c r="A1619" s="2" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B1619" s="2" t="s">
+        <v>3231</v>
+      </c>
     </row>
     <row r="1620" ht="25" customHeight="1" spans="1:2">
-      <c r="A1620" s="2"/>
-      <c r="B1620" s="2"/>
+      <c r="A1620" s="2" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B1620" s="2" t="s">
+        <v>3233</v>
+      </c>
     </row>
     <row r="1621" ht="25" customHeight="1" spans="1:2">
-      <c r="A1621" s="2"/>
-      <c r="B1621" s="2"/>
+      <c r="A1621" s="2" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B1621" s="2" t="s">
+        <v>3235</v>
+      </c>
     </row>
     <row r="1622" ht="25" customHeight="1" spans="1:2">
-      <c r="A1622" s="2"/>
-      <c r="B1622" s="2"/>
+      <c r="A1622" s="2" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B1622" s="2" t="s">
+        <v>3237</v>
+      </c>
     </row>
     <row r="1623" ht="25" customHeight="1" spans="1:2">
-      <c r="A1623" s="2"/>
-      <c r="B1623" s="2"/>
+      <c r="A1623" s="2" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B1623" s="2" t="s">
+        <v>3239</v>
+      </c>
     </row>
     <row r="1624" ht="25" customHeight="1" spans="1:2">
-      <c r="A1624" s="2"/>
-      <c r="B1624" s="2"/>
+      <c r="A1624" s="2" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B1624" s="2" t="s">
+        <v>3241</v>
+      </c>
     </row>
     <row r="1625" ht="25" customHeight="1" spans="1:2">
-      <c r="A1625" s="2"/>
-      <c r="B1625" s="2"/>
+      <c r="A1625" s="2" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B1625" s="2" t="s">
+        <v>3243</v>
+      </c>
     </row>
     <row r="1626" ht="25" customHeight="1" spans="1:2">
-      <c r="A1626" s="2"/>
-      <c r="B1626" s="2"/>
+      <c r="A1626" s="2" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B1626" s="2" t="s">
+        <v>3245</v>
+      </c>
     </row>
     <row r="1627" ht="25" customHeight="1" spans="1:2">
-      <c r="A1627" s="2"/>
-      <c r="B1627" s="2"/>
+      <c r="A1627" s="2" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B1627" s="2" t="s">
+        <v>3247</v>
+      </c>
     </row>
     <row r="1628" ht="25" customHeight="1" spans="1:2">
-      <c r="A1628" s="2"/>
-      <c r="B1628" s="2"/>
+      <c r="A1628" s="2" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1628" s="2" t="s">
+        <v>3249</v>
+      </c>
     </row>
     <row r="1629" ht="25" customHeight="1" spans="1:2">
-      <c r="A1629" s="2"/>
-      <c r="B1629" s="2"/>
+      <c r="A1629" s="2" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B1629" s="2" t="s">
+        <v>3251</v>
+      </c>
     </row>
     <row r="1630" ht="25" customHeight="1" spans="1:2">
-      <c r="A1630" s="2"/>
-      <c r="B1630" s="2"/>
+      <c r="A1630" s="2" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B1630" s="2" t="s">
+        <v>3253</v>
+      </c>
     </row>
     <row r="1631" ht="25" customHeight="1" spans="1:2">
-      <c r="A1631" s="2"/>
-      <c r="B1631" s="2"/>
+      <c r="A1631" s="2" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B1631" s="2" t="s">
+        <v>3255</v>
+      </c>
     </row>
     <row r="1632" ht="25" customHeight="1" spans="1:2">
-      <c r="A1632" s="2"/>
-      <c r="B1632" s="2"/>
+      <c r="A1632" s="2" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B1632" s="2" t="s">
+        <v>3257</v>
+      </c>
     </row>
     <row r="1633" ht="25" customHeight="1" spans="1:2">
-      <c r="A1633" s="2"/>
-      <c r="B1633" s="2"/>
+      <c r="A1633" s="2" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B1633" s="2" t="s">
+        <v>3259</v>
+      </c>
     </row>
     <row r="1634" ht="25" customHeight="1" spans="1:2">
-      <c r="A1634" s="2"/>
-      <c r="B1634" s="2"/>
+      <c r="A1634" s="2" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B1634" s="2" t="s">
+        <v>3261</v>
+      </c>
     </row>
     <row r="1635" ht="25" customHeight="1" spans="1:2">
-      <c r="A1635" s="2"/>
-      <c r="B1635" s="2"/>
+      <c r="A1635" s="2" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B1635" s="2" t="s">
+        <v>3263</v>
+      </c>
     </row>
     <row r="1636" ht="25" customHeight="1" spans="1:2">
-      <c r="A1636" s="2"/>
-      <c r="B1636" s="2"/>
+      <c r="A1636" s="2" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B1636" s="2" t="s">
+        <v>3265</v>
+      </c>
     </row>
     <row r="1637" ht="25" customHeight="1" spans="1:2">
-      <c r="A1637" s="2"/>
-      <c r="B1637" s="2"/>
+      <c r="A1637" s="2" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B1637" s="2" t="s">
+        <v>3267</v>
+      </c>
     </row>
     <row r="1638" ht="25" customHeight="1" spans="1:2">
-      <c r="A1638" s="2"/>
-      <c r="B1638" s="2"/>
+      <c r="A1638" s="2" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B1638" s="2" t="s">
+        <v>3269</v>
+      </c>
     </row>
     <row r="1639" ht="25" customHeight="1" spans="1:2">
-      <c r="A1639" s="2"/>
-      <c r="B1639" s="2"/>
+      <c r="A1639" s="2" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B1639" s="2" t="s">
+        <v>3271</v>
+      </c>
     </row>
     <row r="1640" ht="25" customHeight="1" spans="1:2">
-      <c r="A1640" s="2"/>
-      <c r="B1640" s="2"/>
+      <c r="A1640" s="2" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B1640" s="2" t="s">
+        <v>3273</v>
+      </c>
     </row>
     <row r="1641" ht="25" customHeight="1" spans="1:2">
-      <c r="A1641" s="2"/>
-      <c r="B1641" s="2"/>
+      <c r="A1641" s="2" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B1641" s="2" t="s">
+        <v>3275</v>
+      </c>
     </row>
     <row r="1642" ht="25" customHeight="1" spans="1:2">
-      <c r="A1642" s="2"/>
-      <c r="B1642" s="2"/>
+      <c r="A1642" s="2" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B1642" s="2" t="s">
+        <v>3277</v>
+      </c>
     </row>
     <row r="1643" ht="25" customHeight="1" spans="1:2">
-      <c r="A1643" s="2"/>
-      <c r="B1643" s="2"/>
+      <c r="A1643" s="2" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B1643" s="2" t="s">
+        <v>3279</v>
+      </c>
     </row>
     <row r="1644" ht="25" customHeight="1" spans="1:2">
-      <c r="A1644" s="2"/>
-      <c r="B1644" s="2"/>
+      <c r="A1644" s="2" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B1644" s="2" t="s">
+        <v>3281</v>
+      </c>
     </row>
     <row r="1645" ht="25" customHeight="1" spans="1:2">
-      <c r="A1645" s="2"/>
-      <c r="B1645" s="2"/>
+      <c r="A1645" s="2" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1645" s="2" t="s">
+        <v>3283</v>
+      </c>
     </row>
     <row r="1646" ht="25" customHeight="1" spans="1:2">
-      <c r="A1646" s="2"/>
-      <c r="B1646" s="2"/>
+      <c r="A1646" s="2" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B1646" s="2" t="s">
+        <v>3285</v>
+      </c>
     </row>
     <row r="1647" ht="25" customHeight="1" spans="1:2">
-      <c r="A1647" s="2"/>
-      <c r="B1647" s="2"/>
+      <c r="A1647" s="2" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B1647" s="2" t="s">
+        <v>3287</v>
+      </c>
     </row>
     <row r="1648" ht="25" customHeight="1" spans="1:2">
-      <c r="A1648" s="2"/>
-      <c r="B1648" s="2"/>
+      <c r="A1648" s="2" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1648" s="2" t="s">
+        <v>3289</v>
+      </c>
     </row>
     <row r="1649" ht="25" customHeight="1" spans="1:2">
-      <c r="A1649" s="2"/>
-      <c r="B1649" s="2"/>
+      <c r="A1649" s="2" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B1649" s="2" t="s">
+        <v>3291</v>
+      </c>
     </row>
     <row r="1650" ht="25" customHeight="1" spans="1:2">
-      <c r="A1650" s="2"/>
-      <c r="B1650" s="2"/>
+      <c r="A1650" s="2" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B1650" s="2" t="s">
+        <v>3293</v>
+      </c>
     </row>
     <row r="1651" ht="25" customHeight="1" spans="1:2">
-      <c r="A1651" s="2"/>
-      <c r="B1651" s="2"/>
+      <c r="A1651" s="2" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B1651" s="2" t="s">
+        <v>3295</v>
+      </c>
     </row>
     <row r="1652" ht="25" customHeight="1" spans="1:2">
-      <c r="A1652" s="2"/>
-      <c r="B1652" s="2"/>
+      <c r="A1652" s="2" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B1652" s="2" t="s">
+        <v>3297</v>
+      </c>
     </row>
     <row r="1653" ht="25" customHeight="1" spans="1:2">
-      <c r="A1653" s="2"/>
-      <c r="B1653" s="2"/>
+      <c r="A1653" s="2" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B1653" s="2" t="s">
+        <v>3299</v>
+      </c>
     </row>
     <row r="1654" ht="25" customHeight="1" spans="1:2">
-      <c r="A1654" s="2"/>
-      <c r="B1654" s="2"/>
+      <c r="A1654" s="2" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1654" s="2" t="s">
+        <v>3301</v>
+      </c>
     </row>
     <row r="1655" ht="25" customHeight="1" spans="1:2">
-      <c r="A1655" s="2"/>
-      <c r="B1655" s="2"/>
+      <c r="A1655" s="2" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1655" s="2" t="s">
+        <v>3303</v>
+      </c>
     </row>
     <row r="1656" ht="25" customHeight="1" spans="1:2">
-      <c r="A1656" s="2"/>
-      <c r="B1656" s="2"/>
+      <c r="A1656" s="2" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B1656" s="2" t="s">
+        <v>3305</v>
+      </c>
     </row>
     <row r="1657" ht="25" customHeight="1" spans="1:2">
-      <c r="A1657" s="2"/>
-      <c r="B1657" s="2"/>
+      <c r="A1657" s="2" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B1657" s="2" t="s">
+        <v>3307</v>
+      </c>
     </row>
     <row r="1658" ht="25" customHeight="1" spans="1:2">
-      <c r="A1658" s="2"/>
-      <c r="B1658" s="2"/>
+      <c r="A1658" s="2" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B1658" s="2" t="s">
+        <v>3309</v>
+      </c>
     </row>
     <row r="1659" ht="25" customHeight="1" spans="1:2">
-      <c r="A1659" s="2"/>
-      <c r="B1659" s="2"/>
+      <c r="A1659" s="2" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B1659" s="2" t="s">
+        <v>3311</v>
+      </c>
     </row>
     <row r="1660" ht="25" customHeight="1" spans="1:2">
-      <c r="A1660" s="2"/>
-      <c r="B1660" s="2"/>
+      <c r="A1660" s="2" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B1660" s="2" t="s">
+        <v>3313</v>
+      </c>
     </row>
     <row r="1661" ht="25" customHeight="1" spans="1:2">
-      <c r="A1661" s="2"/>
-      <c r="B1661" s="2"/>
+      <c r="A1661" s="2" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B1661" s="2" t="s">
+        <v>3315</v>
+      </c>
     </row>
     <row r="1662" ht="25" customHeight="1" spans="1:2">
-      <c r="A1662" s="2"/>
-      <c r="B1662" s="2"/>
+      <c r="A1662" s="2" t="s">
+        <v>3316</v>
+      </c>
+      <c r="B1662" s="2" t="s">
+        <v>3317</v>
+      </c>
     </row>
     <row r="1663" ht="25" customHeight="1" spans="1:2">
-      <c r="A1663" s="2"/>
-      <c r="B1663" s="2"/>
+      <c r="A1663" s="2" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B1663" s="2" t="s">
+        <v>3319</v>
+      </c>
     </row>
     <row r="1664" ht="25" customHeight="1" spans="1:2">
-      <c r="A1664" s="2"/>
-      <c r="B1664" s="2"/>
+      <c r="A1664" s="2" t="s">
+        <v>3320</v>
+      </c>
+      <c r="B1664" s="2" t="s">
+        <v>3321</v>
+      </c>
     </row>
     <row r="1665" ht="25" customHeight="1" spans="1:2">
-      <c r="A1665" s="2"/>
-      <c r="B1665" s="2"/>
+      <c r="A1665" s="2" t="s">
+        <v>3322</v>
+      </c>
+      <c r="B1665" s="2" t="s">
+        <v>3323</v>
+      </c>
     </row>
     <row r="1666" ht="25" customHeight="1" spans="1:2">
-      <c r="A1666" s="2"/>
-      <c r="B1666" s="2"/>
+      <c r="A1666" s="2" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B1666" s="2" t="s">
+        <v>3325</v>
+      </c>
     </row>
     <row r="1667" ht="25" customHeight="1" spans="1:2">
-      <c r="A1667" s="2"/>
-      <c r="B1667" s="2"/>
+      <c r="A1667" s="2" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B1667" s="2" t="s">
+        <v>3327</v>
+      </c>
     </row>
     <row r="1668" ht="25" customHeight="1" spans="1:2">
-      <c r="A1668" s="2"/>
-      <c r="B1668" s="2"/>
+      <c r="A1668" s="2" t="s">
+        <v>3328</v>
+      </c>
+      <c r="B1668" s="2" t="s">
+        <v>3329</v>
+      </c>
     </row>
     <row r="1669" ht="25" customHeight="1" spans="1:2">
-      <c r="A1669" s="2"/>
-      <c r="B1669" s="2"/>
+      <c r="A1669" s="2" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B1669" s="2" t="s">
+        <v>3331</v>
+      </c>
     </row>
     <row r="1670" ht="25" customHeight="1" spans="1:2">
-      <c r="A1670" s="2"/>
-      <c r="B1670" s="2"/>
+      <c r="A1670" s="2" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B1670" s="2" t="s">
+        <v>3333</v>
+      </c>
     </row>
     <row r="1671" ht="25" customHeight="1" spans="1:2">
-      <c r="A1671" s="2"/>
-      <c r="B1671" s="2"/>
+      <c r="A1671" s="2" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B1671" s="2" t="s">
+        <v>3335</v>
+      </c>
     </row>
     <row r="1672" ht="25" customHeight="1" spans="1:2">
-      <c r="A1672" s="2"/>
-      <c r="B1672" s="2"/>
+      <c r="A1672" s="2" t="s">
+        <v>3336</v>
+      </c>
+      <c r="B1672" s="2" t="s">
+        <v>3337</v>
+      </c>
     </row>
     <row r="1673" ht="25" customHeight="1" spans="1:2">
-      <c r="A1673" s="2"/>
-      <c r="B1673" s="2"/>
+      <c r="A1673" s="2" t="s">
+        <v>3338</v>
+      </c>
+      <c r="B1673" s="2" t="s">
+        <v>3339</v>
+      </c>
     </row>
     <row r="1674" ht="25" customHeight="1" spans="1:2">
-      <c r="A1674" s="2"/>
-      <c r="B1674" s="2"/>
+      <c r="A1674" s="2" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B1674" s="2" t="s">
+        <v>3341</v>
+      </c>
     </row>
     <row r="1675" ht="25" customHeight="1" spans="1:2">
-      <c r="A1675" s="2"/>
-      <c r="B1675" s="2"/>
+      <c r="A1675" s="2" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B1675" s="2" t="s">
+        <v>3343</v>
+      </c>
     </row>
     <row r="1676" ht="25" customHeight="1" spans="1:2">
-      <c r="A1676" s="2"/>
-      <c r="B1676" s="2"/>
+      <c r="A1676" s="2" t="s">
+        <v>3344</v>
+      </c>
+      <c r="B1676" s="2" t="s">
+        <v>3345</v>
+      </c>
     </row>
     <row r="1677" ht="25" customHeight="1" spans="1:2">
-      <c r="A1677" s="2"/>
-      <c r="B1677" s="2"/>
+      <c r="A1677" s="2" t="s">
+        <v>3346</v>
+      </c>
+      <c r="B1677" s="2" t="s">
+        <v>3347</v>
+      </c>
     </row>
     <row r="1678" ht="25" customHeight="1" spans="1:2">
-      <c r="A1678" s="2"/>
-      <c r="B1678" s="2"/>
+      <c r="A1678" s="2" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B1678" s="2" t="s">
+        <v>3349</v>
+      </c>
     </row>
     <row r="1679" ht="25" customHeight="1" spans="1:2">
-      <c r="A1679" s="2"/>
-      <c r="B1679" s="2"/>
+      <c r="A1679" s="2" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B1679" s="2" t="s">
+        <v>3351</v>
+      </c>
     </row>
     <row r="1680" ht="25" customHeight="1" spans="1:2">
-      <c r="A1680" s="2"/>
-      <c r="B1680" s="2"/>
+      <c r="A1680" s="2" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B1680" s="2" t="s">
+        <v>3353</v>
+      </c>
     </row>
     <row r="1681" ht="25" customHeight="1" spans="1:2">
-      <c r="A1681" s="2"/>
-      <c r="B1681" s="2"/>
+      <c r="A1681" s="2" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B1681" s="2" t="s">
+        <v>3355</v>
+      </c>
     </row>
     <row r="1682" ht="25" customHeight="1" spans="1:2">
-      <c r="A1682" s="2"/>
-      <c r="B1682" s="2"/>
+      <c r="A1682" s="2" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B1682" s="2" t="s">
+        <v>3357</v>
+      </c>
     </row>
     <row r="1683" ht="25" customHeight="1" spans="1:2">
-      <c r="A1683" s="2"/>
-      <c r="B1683" s="2"/>
+      <c r="A1683" s="2" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B1683" s="2" t="s">
+        <v>3359</v>
+      </c>
     </row>
     <row r="1684" ht="25" customHeight="1" spans="1:2">
-      <c r="A1684" s="2"/>
-      <c r="B1684" s="2"/>
+      <c r="A1684" s="2" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B1684" s="2" t="s">
+        <v>3361</v>
+      </c>
     </row>
     <row r="1685" ht="25" customHeight="1" spans="1:2">
-      <c r="A1685" s="2"/>
-      <c r="B1685" s="2"/>
+      <c r="A1685" s="2" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B1685" s="2" t="s">
+        <v>3363</v>
+      </c>
     </row>
     <row r="1686" ht="25" customHeight="1" spans="1:2">
-      <c r="A1686" s="2"/>
-      <c r="B1686" s="2"/>
+      <c r="A1686" s="2" t="s">
+        <v>3364</v>
+      </c>
+      <c r="B1686" s="2" t="s">
+        <v>3365</v>
+      </c>
     </row>
     <row r="1687" ht="25" customHeight="1" spans="1:2">
-      <c r="A1687" s="2"/>
-      <c r="B1687" s="2"/>
+      <c r="A1687" s="2" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B1687" s="2" t="s">
+        <v>3367</v>
+      </c>
     </row>
     <row r="1688" ht="25" customHeight="1" spans="1:2">
-      <c r="A1688" s="2"/>
-      <c r="B1688" s="2"/>
+      <c r="A1688" s="2" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B1688" s="2" t="s">
+        <v>3369</v>
+      </c>
     </row>
     <row r="1689" ht="25" customHeight="1" spans="1:2">
-      <c r="A1689" s="2"/>
-      <c r="B1689" s="2"/>
+      <c r="A1689" s="2" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B1689" s="2" t="s">
+        <v>3371</v>
+      </c>
     </row>
     <row r="1690" ht="25" customHeight="1" spans="1:2">
-      <c r="A1690" s="2"/>
-      <c r="B1690" s="2"/>
+      <c r="A1690" s="2" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B1690" s="2" t="s">
+        <v>3373</v>
+      </c>
     </row>
     <row r="1691" ht="25" customHeight="1" spans="1:2">
-      <c r="A1691" s="2"/>
-      <c r="B1691" s="2"/>
+      <c r="A1691" s="2" t="s">
+        <v>3374</v>
+      </c>
+      <c r="B1691" s="2" t="s">
+        <v>3375</v>
+      </c>
     </row>
     <row r="1692" ht="25" customHeight="1" spans="1:2">
-      <c r="A1692" s="2"/>
+      <c r="A1692" s="2" t="s">
+        <v>3376</v>
+      </c>
       <c r="B1692" s="2"/>
     </row>
     <row r="1693" ht="25" customHeight="1" spans="1:2">
-      <c r="A1693" s="2"/>
+      <c r="A1693" s="2" t="s">
+        <v>3377</v>
+      </c>
       <c r="B1693" s="2"/>
     </row>
     <row r="1694" ht="25" customHeight="1" spans="1:2">
-      <c r="A1694" s="2"/>
+      <c r="A1694" s="2" t="s">
+        <v>3378</v>
+      </c>
       <c r="B1694" s="2"/>
     </row>
     <row r="1695" ht="25" customHeight="1" spans="1:2">
-      <c r="A1695" s="2"/>
+      <c r="A1695" s="2" t="s">
+        <v>3379</v>
+      </c>
       <c r="B1695" s="2"/>
     </row>
     <row r="1696" ht="25" customHeight="1" spans="1:2">
-      <c r="A1696" s="2"/>
+      <c r="A1696" s="2" t="s">
+        <v>3380</v>
+      </c>
       <c r="B1696" s="2"/>
     </row>
     <row r="1697" ht="25" customHeight="1" spans="1:2">
-      <c r="A1697" s="2"/>
+      <c r="A1697" s="2" t="s">
+        <v>3381</v>
+      </c>
       <c r="B1697" s="2"/>
     </row>
     <row r="1698" ht="25" customHeight="1" spans="1:2">
-      <c r="A1698" s="2"/>
+      <c r="A1698" s="2" t="s">
+        <v>3382</v>
+      </c>
       <c r="B1698" s="2"/>
     </row>
     <row r="1699" ht="25" customHeight="1" spans="1:2">
-      <c r="A1699" s="2"/>
+      <c r="A1699" s="2" t="s">
+        <v>3383</v>
+      </c>
       <c r="B1699" s="2"/>
     </row>
     <row r="1700" ht="25" customHeight="1" spans="1:2">
-      <c r="A1700" s="2"/>
+      <c r="A1700" s="2" t="s">
+        <v>3384</v>
+      </c>
       <c r="B1700" s="2"/>
     </row>
     <row r="1701" ht="25" customHeight="1" spans="1:2">
-      <c r="A1701" s="2"/>
+      <c r="A1701" s="2" t="s">
+        <v>3385</v>
+      </c>
       <c r="B1701" s="2"/>
     </row>
     <row r="1702" ht="25" customHeight="1" spans="1:2">
-      <c r="A1702" s="2"/>
+      <c r="A1702" s="2" t="s">
+        <v>3386</v>
+      </c>
       <c r="B1702" s="2"/>
     </row>
     <row r="1703" ht="25" customHeight="1" spans="1:2">

--- a/data/canonical.xlsx
+++ b/data/canonical.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="3387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3602" uniqueCount="3596">
   <si>
     <t>bangla</t>
   </si>
@@ -1107,7 +1107,7 @@
     <t>ঢাকায় গিয়ে তো আমাদেরকে ভুলে গেছিস</t>
   </si>
   <si>
-    <t>ঢাহাত যায় রে তো আরারে ভুলি গেইয়্যুস</t>
+    <t>ঢাহাত যায় রে তো আঁরারে ভুলি গেইয়্যুস</t>
   </si>
   <si>
     <t>তুমি আজকে কোথায় গিয়েছিলে?</t>
@@ -2811,7 +2811,7 @@
     <t>দরজা খুলে দেখি একটা সুন্দরী মেয়ে দাঁড়িয়ে আছে</t>
   </si>
   <si>
-    <t>দরজা খুলি দেহি উজ্ঞো সুন্দরী মাইফুয়া থিয়েই আছে</t>
+    <t>দরজা খুলি দেহি উজ্ঞো সুন্দরী মেইফুওয়া থিয়েই আছে</t>
   </si>
   <si>
     <t>দরজার বাইরে একটা ভিক্কুক দাঁড়ায় আছে, চাল গুলো উনাকে দিয়ে আসো</t>
@@ -3903,7 +3903,7 @@
     <t>গ্রামের মেয়েরা হাঁস মুরগি পালন করে</t>
   </si>
   <si>
-    <t>গ্রামোর মাইফুয়া অক্কলে আঁস কুরো ফালে</t>
+    <t>গ্রামোর মেইফুওয়া অক্কলে আঁস কুরো ফালে</t>
   </si>
   <si>
     <t>পুকুরে অনেক বড় একটা শোল মাছ দেখেছি</t>
@@ -4011,7 +4011,7 @@
     <t>মেয়েটা একদম তার মায়ের মতো হয়েছে</t>
   </si>
   <si>
-    <t>মাইফুয়া একদম ইতির মা'র মতন অইয়্যি</t>
+    <t>মেইফুওয়া একদম ইতির মা'র মতন অইয়্যি</t>
   </si>
   <si>
     <t>স্বভাব চরিত্র তো সব তোর ভাইয়ের মতো হয়েছে</t>
@@ -4675,7 +4675,7 @@
     <t>পাশের বাড়ির মেয়েগুলো প্রতিদিন আমাদের পেয়ারা গাছ থেকে পেয়ারা চুরি করে</t>
   </si>
   <si>
-    <t>পাশোর বারির মাইফুয়া এগুন আঁরো গুয়াসি গাছুত্তুন গুয়াছি চুরি গরে</t>
+    <t>পাশোর বারির মেইফুওয়া এগুন আঁরো গুয়াসি গাছুত্তুন গুয়াছি চুরি গরে</t>
   </si>
   <si>
     <t>ওদেরকে একবার আমার বড় আপু অনেক বকা দিয়েছিল</t>
@@ -4993,7 +4993,7 @@
     <t>চাচি, আপনার ছেলে-মেয়ে কয়টা?</t>
   </si>
   <si>
-    <t>চাচি, অঁনোর ফোওয়া-মাইফুয়া হওয়ো?</t>
+    <t>চাচি, অঁনোর ফোওয়া-মেইফুওয়া হওয়ো?</t>
   </si>
   <si>
     <t>এটা এরকম হয়ে যাবে যে সেটা আমি আগে বুঝতে পারিনি</t>
@@ -5407,7 +5407,7 @@
     <t>আমার মনে হচ্ছে মেয়েটা তোকে যাদু করেছে</t>
   </si>
   <si>
-    <t>আত্তুন মনে অদ্দে মাইফুয়া ইবে তুরে যাদু গইজ্জি</t>
+    <t>আত্তুন মনে অদ্দে মেইফুওয়া ইবে তুরে যাদু গইজ্জি</t>
   </si>
   <si>
     <t>যদি যাদু না করত, তাহলে তুই এরকম পাগল হয়ে যেতি না</t>
@@ -5761,7 +5761,7 @@
     <t>মেয়েটা হাত মোজা পড়েছিল</t>
   </si>
   <si>
-    <t>মাইফুয়া ইবে আত মৌজো ফইজ্জিল</t>
+    <t>মেইফুওয়া ইবে আত মৌজো ফইজ্জিল</t>
   </si>
   <si>
     <t>প্যান্টটা আমার লম্বা হবে</t>
@@ -6982,7 +6982,7 @@
     <t>ছেলেমেয়ে একসাথে দূরে ঘুরতে যাওয়া ঠিক না</t>
   </si>
   <si>
-    <t>ফোওয়া-মাইফুয়া একলগে দুরে ঘুইত্তু যন ঠিক ন</t>
+    <t>ফোওয়া-মেইফুওয়া একলগে দুরে ঘুইত্তু যন ঠিক ন</t>
   </si>
   <si>
     <t>আমি সবাইকে ফোন করে দিয়েছি, কিছুক্ষণের মধ্যে সবাই চলে আসবে</t>
@@ -9214,7 +9214,7 @@
     <t>মেয়েটার সারারাত জ্বর ছিল, কিছু খেতে পারেনি</t>
   </si>
   <si>
-    <t>মাইফুয়া ইবের আরা রাইত জ্বর আছিল, কিছু হাইত ন পারে</t>
+    <t>মেইফুওয়া ইবের আরা রাইত জ্বর আছিল, কিছু হাইত ন পারে</t>
   </si>
   <si>
     <t>পায়ে খুব ব্যথা করছে, একটু টিপে দাও তো</t>
@@ -9604,7 +9604,7 @@
     <t>এই মেয়েটা থেকে দূরে থাকিস, এর মতিগতি ভালো না</t>
   </si>
   <si>
-    <t>এই মাইফোওয়া ইবেত্তুন দূরে থাহিস, ইবের মতিগতি ভালা নো</t>
+    <t>এই মেইফুওয়া ইবেত্তুন দূরে থাহিস, ইবের মতিগতি ভালা নো</t>
   </si>
   <si>
     <t>তোমাকে আমি অনেক বিশ্বাস করি, দয়া করে এমন করো না</t>
@@ -9892,7 +9892,7 @@
     <t>আমাদের পথ এখানেই শেষ না, আজ হেরে গেছি তো কী হয়েছে</t>
   </si>
   <si>
-    <t>আরার পথ এনডেই শেষ নো, আজিয়ে অডি গেই তো কী অইয়্যি</t>
+    <t>আঁরার পথ এনডেই শেষ নো, আজিয়ে অডি গেই তো কী অইয়্যি</t>
   </si>
   <si>
     <t>তুই এগুলো নিয়েছিস কত দিন হচ্ছে?</t>
@@ -9902,6 +9902,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SolaimanLipi"/>
+        <charset val="134"/>
+      </rPr>
       <t>আমার তো ঠিকমতো মনে নেই, মনে হয় ১৫</t>
     </r>
     <r>
@@ -9996,7 +10002,7 @@
     <t>তোমার সাহস তো কম না, তুমি অন্য গ্রামের হয়ে এই গ্রামের মেয়েকে ডিস্টার্ব করো!</t>
   </si>
   <si>
-    <t>তোঁয়ার সাহস তো হম নো, তুঁই অন্য গ্রামুর অইয়্যিরে এই গ্রামুর মাইফোয়ারে ডিস্টার্ব গরো!</t>
+    <t>তোঁয়ার সাহস তো হম নো, তুঁই অন্য গ্রামুর অইয়্যিরে এই গ্রামুর মেইফুওয়ারে ডিস্টার্ব গরো!</t>
   </si>
   <si>
     <t>যদি ঝামেলা করতে না চাও, তাহলে এখনই এখান থেকে চলে যাও</t>
@@ -10284,34 +10290,661 @@
     <t>সবাই সামনে থেকে সরে দাঁড়ান, ট্রাক আসছে</t>
   </si>
   <si>
+    <t>বিয়াজ্ঞুন সামনুত্তুন সরি থিয়ন, টেরাক আইয়্যির</t>
+  </si>
+  <si>
     <t>বাবা, তোমার সঙ্গে আমার কিছু কথা আছে</t>
   </si>
   <si>
+    <t>বাবা, তোঁয়ার লগে আঁর কিছু হতা আছিল</t>
+  </si>
+  <si>
     <t>আমি সারাদিন না খেয়ে আছি, আমাকে কিছু খেতে দিন</t>
   </si>
   <si>
+    <t>আঁই আরাদিন ন হায় আছি, আঁরে কিছু হাইতু দন</t>
+  </si>
+  <si>
     <t>আম্মু, একটু কষ্ট করে আমার ঘরটা গুছিয়ে দাও, বিকেলে মেহমান আসবে</t>
   </si>
   <si>
+    <t>আম্মু, এক্কানা হষ্ট গরি আঁর ঘরগান গুছায় দও, বিকেলে মেমাম আইবু</t>
+  </si>
+  <si>
     <t>আম্মু, আমার বন্ধু বাড়িতে আসবে, আজ একটু ভালো কিছু রান্না করো</t>
   </si>
   <si>
+    <t>আম্মু, আঁর বন্ধু বারিত আইবু, আজিয়ে এক্কানা ভালা কিছু রান্না গরো</t>
+  </si>
+  <si>
     <t>মা, আজ একটু আগে রান্না করো, বাবার অফিসে যেতে দেরি হয়ে যাচ্ছে</t>
   </si>
   <si>
+    <t>মা, আজিয়ে এক্কানা আগে রান্না গরো, বাবার অফিসুত যাইতে দেরি অই যার</t>
+  </si>
+  <si>
     <t>স্যার, আমার আবেদনটা একটু ওপরে পাঠিয়ে দিন, অনেক দিন ধরে আটকে আছে</t>
   </si>
   <si>
+    <t>স্যার, আঁর আবেদন ইয়েন এক্কানা উরে পাঠাই দন, বতদিন ধরি আটকি আছে</t>
+  </si>
+  <si>
     <t>ভাই, প্লিজ রাস্তার মাঝখানে গাড়ি না রেখে পাশে সরিয়ে নিন</t>
   </si>
   <si>
+    <t>বদ্দা, প্লিজ রাস্তার মাঝে গারি ন রাহি পাশে সরাই লন</t>
+  </si>
+  <si>
     <t>বাবা, আমার সাইকেলটা একটু মেরামত করিয়ে দাও, চাকা নষ্ট হয়ে গেছে</t>
   </si>
   <si>
+    <t>বাবা, আঁর সাইকেলগান এক্কানা মেরামত গরাই দও, চাক্কা নষ্ট অই গেইয়্যি</t>
+  </si>
+  <si>
     <t>আম্মু, আমার জন্য একটু শরবত বানিয়ে দাও, অনেক গরম লাগছে</t>
   </si>
   <si>
+    <t>আম্মু, আঁর লাই এক্কানা শরবত বানাই দও, বত গরম লাগের</t>
+  </si>
+  <si>
     <t>আমি হিসাব করে দেখিনি কত টাকা আছে</t>
+  </si>
+  <si>
+    <t>আঁই হিসেব গরি ন চায় হতো টিয়া আছে</t>
+  </si>
+  <si>
+    <t>একটু হাত লাগান, আপনি ছাড়া এটা ওপরে তোলা সম্ভব না</t>
+  </si>
+  <si>
+    <t>এক্কানা আত লাগন, অঁনে ছারা ইয়েন উরে তোলন সম্ভব নো</t>
+  </si>
+  <si>
+    <t>সায়েমকে ফোন করে জিজ্ঞেস কর, পরীক্ষা কখন সেটা</t>
+  </si>
+  <si>
+    <t>সায়েম উরে ফোন গরি ফুস গর, পরীক্ষে হত্তে ইয়েন</t>
+  </si>
+  <si>
+    <t>স্যার, পরীক্ষায় এই প্রশ্নটা আসবে কি না একটু বলবেন?</t>
+  </si>
+  <si>
+    <t>স্যার, পরীক্ষেত এই প্রশ্ন ইয়েন আইবু কিনা এক্কানা হইবেন?</t>
+  </si>
+  <si>
+    <t>আজ ক্লাসে যা পড়িয়েছে, সব আমার মাথার ওপর দিয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে ক্লাসুত যা পরাইয়্যি বিয়াক আঁর মাথার উদ্দি গেইয়্যি</t>
+  </si>
+  <si>
+    <t>নতুন স্যারের পড়াগুলো কিছু বুঝি না</t>
+  </si>
+  <si>
+    <t>নতুন স্যার উর পরা এগিন কিছু ন বুঝির</t>
+  </si>
+  <si>
+    <t>আমার তো উনার ক্লাস করলে ঘুম চলে আসে</t>
+  </si>
+  <si>
+    <t>আত্তুন তো ইবের ক্লাস গরিলি ঘুম চলি আইয়্যি</t>
+  </si>
+  <si>
+    <t>জামিল স্যারের ক্লাসে আমার খুব বিরক্ত লাগে, কী পড়ান আগামাথা বুঝি না</t>
+  </si>
+  <si>
+    <t>জামিল স্যার উর ক্লাসুত আঁর খুব বিরক্ত লাগে, কি পরাই আগামাথা ন বুঝি</t>
+  </si>
+  <si>
+    <t>স্যার, কোন টপিকগুলো পরীক্ষায় আসবে যদি বলতেন</t>
+  </si>
+  <si>
+    <t>স্যার, হন টপিকগিন পরীক্ষেত আইবু যদি হইতেন</t>
+  </si>
+  <si>
+    <t>অফিসের নতুন কলিগটা অনেক মিশুক, সবার সঙ্গে খুব তাড়াতাড়ি মিশে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>আফিসুর নতুন কলিগ ইবে বত মিশুক, বিয়াজ্ঞুনুর লগে বত তারাতারি মিশি যার</t>
+  </si>
+  <si>
+    <t>ম্যাম, আমার বন্ধু অসুস্থ, তাই আজ ক্লাস করতে পারেনি</t>
+  </si>
+  <si>
+    <t>ম্যাম, আঁর বন্ধু অসুস্থ, এতেল্লে আজিয়ে ক্লাস গরিত নো পারে</t>
+  </si>
+  <si>
+    <t>অফিসে নতুন সফটওয়্যার এসেছে, ওটা ব্যবহার করতে সমস্যা হচ্ছে</t>
+  </si>
+  <si>
+    <t>অফিসুত নতুন সফটওয়্যার আইসসি, ইবে বেবার গত্তে সমস্যা অর</t>
+  </si>
+  <si>
+    <t>ঝড় তো থামার নাম নিচ্ছে না, একটানা পড়েই যাচ্ছে</t>
+  </si>
+  <si>
+    <t>ঝর তো থামিবের নাম ন লর, একটানা পরিই যার</t>
+  </si>
+  <si>
+    <t>এভাবে আর কয়েক দিন বৃষ্টি পড়লে মাঠের সব ফসল নষ্ট হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>এন গরি আর হয়েকদিন ঝর ফরিলি মাডোর বিয়াক ফসল নষ্ট অই যাইবু</t>
+  </si>
+  <si>
+    <t>আজ কলিগের সাথে একটু ভুল-বোঝাবুঝি হয়েছে, তাই একটু মুড অফ</t>
+  </si>
+  <si>
+    <t>আজিয়ে কলিগুর লগে এক্কানা ভুল বোঝাবুঝি অইয়্যি, এতেল্লে এক্কানা মুড অফ</t>
+  </si>
+  <si>
+    <t>স্যার, আপনি বলেছিলেন ক্লাস টেস্ট না নিয়ে অ্যাসাইনমেন্ট দেবেন</t>
+  </si>
+  <si>
+    <t>স্যার, অঁনে হইলেন ক্লাস টেস্ট ন লই অ্যাসাইনমেন্ট দিবেন</t>
+  </si>
+  <si>
+    <t>আজ অ্যাসাইনমেন্ট জমা দেওয়ার শেষ দিন</t>
+  </si>
+  <si>
+    <t>আজিয়ে অ্যাসাইনমেন্ট জমা দিবের শেষ দিন</t>
+  </si>
+  <si>
+    <t>গতবার আমাদের প্রশ্ন অনেক কঠিন হয়েছিল, তাই এবার সহজ হতে হবে</t>
+  </si>
+  <si>
+    <t>গতবার আঁরার প্রশ্ন বত কঠিন অইয়্যিল, এতেল্লে এবার সহজ অন ফরিবু</t>
+  </si>
+  <si>
+    <t>স্যার, ক্লাস টেস্টের ফলাফল কবে দেবেন, অনেক দিন ধরে অপেক্ষা করছি</t>
+  </si>
+  <si>
+    <t>স্যার, ক্লাস টেস্ট উর ফলাফল হত্তে দিবেন, বত দিন ধরি অপেক্ষা গরির</t>
+  </si>
+  <si>
+    <t>তোর বাবাকে ফোন করে বল তাড়াতাড়ি চলে আসতে</t>
+  </si>
+  <si>
+    <t>তোর বাফুরে ফোন গরি হ হারা চলি আইসতু</t>
+  </si>
+  <si>
+    <t>লিখতে লিখতে আমার হাত ব্যথা হয়ে গেছে, তাও লেখা শেষ হয় না</t>
+  </si>
+  <si>
+    <t>লেখতে লেখতে আঁর আত ব্যথা অই গেইয়্যি, তাও লেহা শেষ ন অর</t>
+  </si>
+  <si>
+    <t>স্যার, আমি ওর দিকে তাকাইনি</t>
+  </si>
+  <si>
+    <t>স্যার, আঁই ইতের মিক্কে নো চাই</t>
+  </si>
+  <si>
+    <t>পরীক্ষার হলে যদি শব্দ করো, তাহলে সবার খাতা নিয়ে ফেলব</t>
+  </si>
+  <si>
+    <t>পরীক্ষের হলুত যদি শব্দ গরো, তইলি বিয়াজ্ঞুনুর হাতা লই ফেলাইয়্যুম</t>
+  </si>
+  <si>
+    <t>স্যার, আমার খাতা নেবেন না, আমি ওর থেকে দেখিনি</t>
+  </si>
+  <si>
+    <t>স্যার, আঁর হাতা ন লইয়্যুন, আঁই ইতেত্তুন নো চাই</t>
+  </si>
+  <si>
+    <t>কপি করলে করো, কিন্তু শব্দ করবে না</t>
+  </si>
+  <si>
+    <t>কপি গরিলি গরো, কিন্তু শব্দ ন গইজ্জো</t>
+  </si>
+  <si>
+    <t>স্যার, অনেকক্ষণ হয়ে গেল, এবার যদি আমার খাতাটা দিয়ে দিতেন</t>
+  </si>
+  <si>
+    <t>স্যার, বত হতক্ষন অই গেইয়্যি, এবার যদি আঁর হাতাগো দি দিতেন</t>
+  </si>
+  <si>
+    <t>ম্যাম, এমনটা আর হবে না, সত্যি বলছি</t>
+  </si>
+  <si>
+    <t>ম্যাম, এল্লেত আর ন অইবু, সত্যি হইদ্দি</t>
+  </si>
+  <si>
+    <t>আমি তোর থেকে দেখব, আর তুই রিফার থেকে দেখিস</t>
+  </si>
+  <si>
+    <t>আঁই তোত্তুন চাইয়্যুম, আর তুই রিফাত্তুন চাইস</t>
+  </si>
+  <si>
+    <t>আমি এখান থেকে দেখতে পারছি না, তুই খাতাটা আরেকটু উঁচু করে ধর</t>
+  </si>
+  <si>
+    <t>আঁই এত্তুন ন দেহির, তুই হাতাগো আরেক্কানা উরে গরি ধর</t>
+  </si>
+  <si>
+    <t>একটু সাবধানে, স্যার দেখলে দুজনেরই খাতা নিয়ে ফেলবেন</t>
+  </si>
+  <si>
+    <t>এক্কানা সাবধানে, স্যার দেহিলি দুনুজনুর হাতা লই ফেলাইবু</t>
+  </si>
+  <si>
+    <t>তুই চিন্তা করিস না, স্যার আমাদের কিছু বলবেন না</t>
+  </si>
+  <si>
+    <t>তুই চিন্তে ন গরিস, স্যার আঁরারে কিছু ন হইবু</t>
+  </si>
+  <si>
+    <t>ম্যাম, আমার মা অসুস্থ, তাই গতকাল আসতে পারিনি</t>
+  </si>
+  <si>
+    <t>ম্যাম, আঁর মা অসুস্থ, এতেল্লে গত হালিয়ে আইত ন পারি</t>
+  </si>
+  <si>
+    <t>আজ অফিসে ওভারটাইম করেছি, তাই দেরি হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আজিয়ে অফিসুত ওভারটাইম গইজ্জি, এতেল্লে দেরি অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>স্যার, এই অধ্যায়টা পরীক্ষার জন্য কতটা গুরুত্বপূর্ণ বলে মনে করেন?</t>
+  </si>
+  <si>
+    <t>স্যার, এই অধ্যায় ইবে পরীক্ষের লাই হতটা গুরুত্বপূর্ণ বলি মনে গরন?</t>
+  </si>
+  <si>
+    <t>স্যার, পরীক্ষার জন্য কোন কোন অধ্যায় পড়ে যেতে হবে?</t>
+  </si>
+  <si>
+    <t>স্যার, পরীক্ষের লাই হন হন অধ্যায় পরি যন ফরিবু?</t>
+  </si>
+  <si>
+    <t>আমাদের এবার সময় কম, তাই সিলেবাস ছোট রাখলে ভালো হবে</t>
+  </si>
+  <si>
+    <t>আঁরার এবার সময় হম, এতেল্লে সিলেবাস ছোডো রাহিলি ভালা অইবু</t>
+  </si>
+  <si>
+    <t>অফিসের কাজ এত বেশি যে ঘরে ঠিকমতো সময় দিতে পারি না</t>
+  </si>
+  <si>
+    <t>অফিসুর হাজ এব বেশি যে ঘরুত ঠিকমতো সময় দিত ন পারির</t>
+  </si>
+  <si>
+    <t>ম্যাম, পরীক্ষায় ক্যালকুলেটর ব্যবহার করতে পারব?</t>
+  </si>
+  <si>
+    <t>ম্যাম, পরীক্ষেত ক্যালকুলেটর বেবার গরিত ফাইজ্জুম?</t>
+  </si>
+  <si>
+    <t>সবার ব্যাগ আর মোবাইল ফোন সামনে এনে রাখো</t>
+  </si>
+  <si>
+    <t>বিয়াজ্ঞুনুর ব্যাগ আর মোবাইল ফোন সাম্মুদ্দি আনি রাহো</t>
+  </si>
+  <si>
+    <t>যদি পরীক্ষা চলাকালীন কারও কাছে মোবাইল ফোন পাওয়া যায়, তাহলে তাকে হল থেকে বের করে দেওয়া হবে</t>
+  </si>
+  <si>
+    <t>যদি পরীক্ষে চলাকালীন কিয়ার হাছে মোবাইল ফোন পা যায়, তইলি ইতেরে হল উত্তুন বাইর গরি দন অইবু</t>
+  </si>
+  <si>
+    <t>আজ অফিসে একটা ভুল হয়ে গেছে, বসকে কীভাবে বলব বুঝছি না</t>
+  </si>
+  <si>
+    <t>আজিয়ে অফিসুত এক্কান ভুল অই গেইয়্যি, বস উরে কেন গরি হইয়্যুম ন বুঝির</t>
+  </si>
+  <si>
+    <t>ম্যাডাম, পরীক্ষায় উত্তর বাংলায় লিখব, নাকি ইংরেজিতে লিখতে হবে?</t>
+  </si>
+  <si>
+    <t>ম্যাডাম, পরীক্ষেত উত্তর বাংলাত লেইক্কুম নাকি ইংরেজিত লেহন ফরিবু?</t>
+  </si>
+  <si>
+    <t>আমাদের ক্লাসে নতুন একজন ছাত্র ভর্তি হয়েছে</t>
+  </si>
+  <si>
+    <t>আঁরার ক্লাসুত নতুন উজ্ঞো ছাত্র ভর্তি অইয়্যি</t>
+  </si>
+  <si>
+    <t>স্যার, আমি পরীক্ষায় ভালো করতে চাই, কোন বিষয়গুলো বেশি পড়া দরকার?</t>
+  </si>
+  <si>
+    <t>স্যার, আঁই পরীক্ষেত ভালা গইত্তাম চাই, হোন বিষয়গুন বেশি ফরন উর দরহার?</t>
+  </si>
+  <si>
+    <t>আমি তোমাকে আটকে রাখতে চাই না, তোমার চলে যেতে মন চাইলে চলে যেতে পার</t>
+  </si>
+  <si>
+    <t>আঁই তোঁয়ারে আটকাই রাইখতাম ন চাই, তোঁয়াত্তুন চলি যাইতু মন চাইলি চলি যাইত পারো</t>
+  </si>
+  <si>
+    <t>ঘরের অবস্থা ভালো না, পড়াশোনার পাশাপাশি পার্টটাইম কাজ করতে হবে</t>
+  </si>
+  <si>
+    <t>ঘরুর অবস্থা ভালা নো, পরালেহার পাশাপাশি পার্টটাইম হাজ গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>এখানে আরও একটা বিপদ রয়েছে</t>
+  </si>
+  <si>
+    <t>এনডে আরও এক্কান বিপদ আছে</t>
+  </si>
+  <si>
+    <t>কোনো কিছু করার আগে আমাদেরকে এখান থেকে বের হতে হবে</t>
+  </si>
+  <si>
+    <t>হনো কিছু গরিবের আগে আরাত্তুন এত্তুন বাইর অন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমাদের হাতে এখন বেশি সময় নেই, যা করার তাড়াতাড়ি করতে হবে</t>
+  </si>
+  <si>
+    <t>আঁরার আ'তুত এহন বেশি সময় দেইন, যা গরিবের তারাতারি গরন ফরিবু</t>
+  </si>
+  <si>
+    <t>সন্ধ্যার আগে কিছু একটা করতে না পারলে সবাই এখানে আটকা পড়ব</t>
+  </si>
+  <si>
+    <t>আজুইন্নের আগে কিছু এক্কান গরিত ন পারিলি বিয়াজ্ঞুন এনডে আটকি ফইজ্জুম</t>
+  </si>
+  <si>
+    <t>আবির কাঁধে ব্যাগ নিয়ে বের হয়ে গেছে</t>
+  </si>
+  <si>
+    <t>আবির হাধুত ব্যাগ লই বাইর অই গেইয়্যি</t>
+  </si>
+  <si>
+    <t>সে কোথায় গেছে সেটা কি তুমি জানো?</t>
+  </si>
+  <si>
+    <t>ইতে হনডে গেইয়্যি ইয়েন কি তুঁই জানো?</t>
+  </si>
+  <si>
+    <t>যাওয়ার সময় আমাকে কিছু বলে যায়নি</t>
+  </si>
+  <si>
+    <t>যাইবের সমত আঁরে কিছু হই ন যায়</t>
+  </si>
+  <si>
+    <t>কিরে, তোর প্রেমিকার নাকি বিয়ে হয়ে যাচ্ছে?</t>
+  </si>
+  <si>
+    <t>কিরে, তোর প্রেমিকার বলে বিয়ে অই যার?</t>
+  </si>
+  <si>
+    <t>আরে ভাই, এত সিরিয়াস হলে চলবে না, একটু হাসুন</t>
+  </si>
+  <si>
+    <t>আরে বদ্দা, এল্লেত সিরিয়াস অইলি ন চলিবু, এক্কানা আ'সন</t>
+  </si>
+  <si>
+    <t>কিরে, ব্যাপার কী, আজ অনেক হাসিখুশি লাগছে!</t>
+  </si>
+  <si>
+    <t>কিরে, ব্যাপার কী, আজিয়ে বত আ'সিখুশি লাগের!</t>
+  </si>
+  <si>
+    <t>এত হাসিখুশি কেন? বিয়ে ঠিক হলো নাকি?</t>
+  </si>
+  <si>
+    <t>এল্লেত আ'সিখুশি কা? বিয়ে ঠিক অইয়্যি নাকি?</t>
+  </si>
+  <si>
+    <t>আমার সঙ্গে মজা করিস না, আমি এখন মজা করার মুডে নেই</t>
+  </si>
+  <si>
+    <t>আঁর লগে মজা ন গরিস, আঁই এহন মজা গরিবের মুড উত নেই</t>
+  </si>
+  <si>
+    <t>তোর বাবা নাকি আরেকটা বিয়ে করছেন? ঘটনাটা কি সত্যি?</t>
+  </si>
+  <si>
+    <t>তোর বাফ বলে আরেকগো বিয়ে গইজ্জি? ঘটনা ইয়েন কি সত্যি?</t>
+  </si>
+  <si>
+    <t>তোর বউ নাকি পাশের বাড়ির একটা ছেলের সঙ্গে পালিয়ে গেছে?</t>
+  </si>
+  <si>
+    <t>তোর বউ বলে পাশুর বারির ফোওয়ার লগে পালাই গেইয়্যি?</t>
+  </si>
+  <si>
+    <t>কী ব্যাপার! আজ এত সেজেগুজে কোথায় যাচ্ছিস?</t>
+  </si>
+  <si>
+    <t>কী ব্যাপার! আজিয়ে এত সাজিগুজি হনডে যর?</t>
+  </si>
+  <si>
+    <t>এই মেয়েটা তোকে পছন্দ করে মনে হয়</t>
+  </si>
+  <si>
+    <t>এই মেইফুওয়া ইবে তোরে পছন্দ গরে মনে অয়</t>
+  </si>
+  <si>
+    <t>তোমার সঙ্গে কথা বললে সময় যে কখন চলে যায়, বুঝতেই পারি না</t>
+  </si>
+  <si>
+    <t>তোঁয়ার লগে হতা হইলি সময় যে হত্তে চলি যায়, বুঝিতই ন পারি</t>
+  </si>
+  <si>
+    <t>কিরে বাটপার, তোর বাটপারি কেমন চলে?</t>
+  </si>
+  <si>
+    <t>কিরে বাটপার, তোর বাটপারি কেন চলের?</t>
+  </si>
+  <si>
+    <t>তোকে অনেক মিস করছি, তুই না থাকলে কাউকে জ্বালাতে পারি না</t>
+  </si>
+  <si>
+    <t>তোরে বত মিস গইজ্জি, তুই ন থাহিলি কিয়ারে জালাইত ন পারি</t>
+  </si>
+  <si>
+    <t>তোর শুধু বয়সটাই বাড়ছে, কিন্তু বুদ্ধিটা বাড়ছে না</t>
+  </si>
+  <si>
+    <t>তোর উদো বয়সই বেইজ্জি, কিন্তু বুদ্ধি ন বারের</t>
+  </si>
+  <si>
+    <t>ছোটবেলায় যেরকম বেকুব ছিলি, ঠিক এখনো সেরকম বেকুব থেকে গেছিস</t>
+  </si>
+  <si>
+    <t>গুরো থাকতে যেরহম বেকুব আছিলি, ঠিক এহনো সেরহম বেকুব থাহি গেইয়্যুস</t>
+  </si>
+  <si>
+    <t>ভাই, তুই এত খাস কীভাবে, তোরটা পেট নাকি অন্য কিছু!</t>
+  </si>
+  <si>
+    <t>বদ্দা, তুই এত হস কেনে, তোর ইবে পেট নাকি অন্য কিছু!</t>
+  </si>
+  <si>
+    <t>তুই সারাদিন এত এত খাস, তাও মোটা হোস না, আর আমি অল্প খেলেই মোটা হয়ে যাই</t>
+  </si>
+  <si>
+    <t>তুই আরাদিন এত এত হস, তাও মোটা ন অস, আর আঁই অল্প হাইলিই মোটা অই যাই</t>
+  </si>
+  <si>
+    <t>আচ্ছা, তুই যে এত খাস, সেই খাবারগুলো যায় কোথায়?</t>
+  </si>
+  <si>
+    <t>আইচ্ছে, তুই যে এত হস, এই হানা এগিন যায় হনডে?</t>
+  </si>
+  <si>
+    <t>কী রে, তোর চেহারা দেখে মনে হচ্ছে সারারাত ঘুমাসনি</t>
+  </si>
+  <si>
+    <t>কী রে, তোর চিয়ারা দেহি মনে অর আরা রাইত নো ঘুমস</t>
+  </si>
+  <si>
+    <t>সারারাত না ঘুমিয়ে কী করেছিস? কার সঙ্গে কথা বলেছিস?</t>
+  </si>
+  <si>
+    <t>আরা রাইত নো ঘুমাই কি গইজ্জুস? হার লগে হতা হইয়্যুস?</t>
+  </si>
+  <si>
+    <t>কী রে, তুই এখনো সেই পুরোনো অভ্যাস ছাড়তে পারলি না</t>
+  </si>
+  <si>
+    <t>কি রে, তুই এহনো সেই পুরন অভ্যেস ছারিত ন পারিলি</t>
+  </si>
+  <si>
+    <t>আরে, বন্ধু ছাড়া জীবনটা যেন লবণ ছাড়া তরকারির মতো</t>
+  </si>
+  <si>
+    <t>আরে, বন্ধু ছারা জীবন ইয়েন যেন লবণ ছারা তরহারির মতন</t>
+  </si>
+  <si>
+    <t>ভাই, আপনি না এলে আজকের আড্ডাটা একদম জমত না</t>
+  </si>
+  <si>
+    <t>বদ্দা, অঁনে ন আইলি আজিয়ের আড্ডা ইয়েন একদম ন জাইমতো</t>
+  </si>
+  <si>
+    <t>তুই কি সারাজীবন এরকম ছোট থেকে যাবি, নাকি একটু বড় হবি?</t>
+  </si>
+  <si>
+    <t>তুই কি আরা জীবন এরহম ছোডো থাহি যাইবি, নাকি এক্কানা বরো অইবি?</t>
+  </si>
+  <si>
+    <t>এত চিন্তা করলে মাথার চুল যা আছে সব পড়ে যাবে</t>
+  </si>
+  <si>
+    <t>এত চিন্তে গরিলি মাথাত চল যা আছে বিয়াক পরি যাইবু</t>
+  </si>
+  <si>
+    <t>ভাবি, মনে হয় বেশি টেনশন দেই, মাথার চুল তো সব পড়ে যাচ্ছে</t>
+  </si>
+  <si>
+    <t>ভাবি মনে অয় বেশি টেনশন দেই, মাথার চুল তো বিয়াক পরি যার</t>
+  </si>
+  <si>
+    <t>আপনি কি সত্যিই এটা বললেন, নাকি আমি ঘুমের মধ্যে শুনলাম?</t>
+  </si>
+  <si>
+    <t>অঁনে কি সত্যি ইয়েন হইয়্যুন, নাকি আঁই ঘুমুর মধ্যে উইন্নিলাম?</t>
+  </si>
+  <si>
+    <t>আজ সূর্য কোন দিকে উঠছে, তুই আমার বাড়িতে!</t>
+  </si>
+  <si>
+    <t>আজিয়ে সুর্য হুনদি উইট্টি, তুই আঁর বারিত!</t>
+  </si>
+  <si>
+    <t>সবসময় মজা ভালো লাগে না, আমি এখন মজা করার মুডে নেই</t>
+  </si>
+  <si>
+    <t>সবসময় মজা ভালা ন লাগে, আঁই এহন মজা গরিবের মুডুত নেই</t>
+  </si>
+  <si>
+    <t>কিরে, তোর মন কোথায়? কার কাছে চলে গেছে?</t>
+  </si>
+  <si>
+    <t>কিরে, তোর মন হনডে? হার হাছে চলি গেইয়্যি?</t>
+  </si>
+  <si>
+    <t>তোর বয়স বাড়লেও এখনো স্বভাব পরিবর্তন হয়নি</t>
+  </si>
+  <si>
+    <t>তোর বয়স বারিলিও এহনো স্বভাব পরিবর্ত্ন নো অয়</t>
+  </si>
+  <si>
+    <t>সবাই মিলে একটা গান ধর, ভালো লাগবে</t>
+  </si>
+  <si>
+    <t>বিয়াজ্ঞুন মিলি উজ্ঞো গান ধর, ভালা লাগিবু</t>
+  </si>
+  <si>
+    <t>তোর মাথায় মনে হয় কিছু নেই, কিছু থাকলে তো এমন কাজ করতিস না</t>
+  </si>
+  <si>
+    <t>তোর মাথাত মনে অয় কিছু নেই, কিছু থাহিলি তো এরহম হাজ ন গইত্তি</t>
+  </si>
+  <si>
+    <t>তোদের থেকে দূরে থাকলেই ভালো, একসঙ্গে থাকলে একটাও ভালো কথা হয় না</t>
+  </si>
+  <si>
+    <t>তোরাত্তুন দুরে থাহিলিই ভালা, একলগে থাহিলি এক্কানও ভালা হতা নো অয়</t>
+  </si>
+  <si>
+    <t>আমি আগে অনেক ভালো ছিলাম, এখন ওর সঙ্গে মিশতে মিশতে খারাপ হয়ে যাচ্ছি</t>
+  </si>
+  <si>
+    <t>আঁই আগে বত ভালা আছিলাম, এহন ইতের লগে মিশতে মিশতে হারাপ অই যাইর</t>
+  </si>
+  <si>
+    <t>মুখে বলা অনেক সহজ, করে দেখানো অনেক কঠিন</t>
+  </si>
+  <si>
+    <t>মুখে হন বত সোজা, গরি দেহন বত কঠিন</t>
+  </si>
+  <si>
+    <t>এত বকবক না করে কাজে মন দাও, সব কাজ পড়ে আছে</t>
+  </si>
+  <si>
+    <t>এত বকবক ন গরি হাজুত মন দও, বিয়াক হাজ পরি আছে</t>
+  </si>
+  <si>
+    <t>আমি তো তোমার সঙ্গে মজা করছিলাম, তুমি তো দেখি ভয় পেয়ে গেছ</t>
+  </si>
+  <si>
+    <t>আঁই তো তোঁয়ার লগে মজা গরিদ্দি, তুঁই তো দেহি ডরাই গেইয়্যো</t>
+  </si>
+  <si>
+    <t>তোর জন্য মেয়ে খুঁজতে খুঁজতে আমরা সবাই বিরক্ত হয়ে গেছি</t>
+  </si>
+  <si>
+    <t>তোর লাই মেইফুওয়া থোওয়াতে থোওয়াতে আঁরা বিয়াজ্ঞুন বিরক্ত অই গেই</t>
+  </si>
+  <si>
+    <t>মন ভালো থাকলে নাকি আশেপাশের সবকিছু সুন্দর লাগে</t>
+  </si>
+  <si>
+    <t>মন ভালা থাহিলি বলে আশেপাশের বিয়াক কিছু সুন্দর লাগে</t>
+  </si>
+  <si>
+    <t>আজ যে মেয়েটাকে দেখতে গিয়েছিলাম, ওকে ভালো মনে হলো</t>
+  </si>
+  <si>
+    <t>আজিয়ে যে মেইফুওয়ারে চাইতাম গেইলাম, ইবেরে ভালা মনে অইলু</t>
+  </si>
+  <si>
+    <t>যদি মেয়েটা ভালো হয়, তাহলে ওর সঙ্গে কথা বল</t>
+  </si>
+  <si>
+    <t>যদি মেইফুওয়া ইবে ভালা অয়, তইলি ইবের লগে হতা হো</t>
+  </si>
+  <si>
+    <t>আমাদের আরও ভালো করে খোঁজখবর নিতে হবে সামনে এগোনোর আগে</t>
+  </si>
+  <si>
+    <t>আরাত্তুন আরো ভালা গরি হোছহবর লন ফরিবু সামনে আগাইবের আগে</t>
+  </si>
+  <si>
+    <t>এই সমস্যাটার জন্য আমরা সামনে এগোতে পারছি না</t>
+  </si>
+  <si>
+    <t>এই সমস্যা ইয়েনুর লাই আঁরা সামনে আগাইত ন পারির</t>
+  </si>
+  <si>
+    <t>আস্তে আস্তে আমরা একদম শেষের দিকে চলে আসছি</t>
+  </si>
+  <si>
+    <t>আস্তে আস্তে আঁরা এব্বেরে শেষুর দিকে চলি আইসসি</t>
+  </si>
+  <si>
+    <t>আর দু-একটা শব্দ লিখলেই আমাদের ডাটাসেট সম্পূর্ণ হয়ে যাবে</t>
+  </si>
+  <si>
+    <t>আর দুই-এক্কান শব্দ লেহিলিই আঁরার ডাটাসেট সম্পূর্ণ অই যাইবু</t>
+  </si>
+  <si>
+    <t>এখন যতটুকু হয়েছে সেটা নিয়ে আমাদের বাকি কাজ শুরু করে দিতে হবে</t>
+  </si>
+  <si>
+    <t>এহন যেদ্দুর অইয়্যি ইয়েন লই আরাত্তুন বাকি হাজ শুরু গরি দন ফরিবু</t>
+  </si>
+  <si>
+    <t>আমি আপাতত এতটুকু লিখলাম, যদি সময় থাকে বাকি শব্দগুলোও লিখব</t>
+  </si>
+  <si>
+    <t>আঁই আপাতত এদ্দুর লেহিলাম, যদি সময় থাহে বাকি শব্দ এগুনও লেইক্কুম</t>
   </si>
 </sst>
 </file>
@@ -25020,463 +25653,881 @@
       <c r="A1692" s="2" t="s">
         <v>3376</v>
       </c>
-      <c r="B1692" s="2"/>
+      <c r="B1692" s="2" t="s">
+        <v>3377</v>
+      </c>
     </row>
     <row r="1693" ht="25" customHeight="1" spans="1:2">
       <c r="A1693" s="2" t="s">
-        <v>3377</v>
-      </c>
-      <c r="B1693" s="2"/>
+        <v>3378</v>
+      </c>
+      <c r="B1693" s="2" t="s">
+        <v>3379</v>
+      </c>
     </row>
     <row r="1694" ht="25" customHeight="1" spans="1:2">
       <c r="A1694" s="2" t="s">
-        <v>3378</v>
-      </c>
-      <c r="B1694" s="2"/>
+        <v>3380</v>
+      </c>
+      <c r="B1694" s="2" t="s">
+        <v>3381</v>
+      </c>
     </row>
     <row r="1695" ht="25" customHeight="1" spans="1:2">
       <c r="A1695" s="2" t="s">
-        <v>3379</v>
-      </c>
-      <c r="B1695" s="2"/>
+        <v>3382</v>
+      </c>
+      <c r="B1695" s="2" t="s">
+        <v>3383</v>
+      </c>
     </row>
     <row r="1696" ht="25" customHeight="1" spans="1:2">
       <c r="A1696" s="2" t="s">
-        <v>3380</v>
-      </c>
-      <c r="B1696" s="2"/>
+        <v>3384</v>
+      </c>
+      <c r="B1696" s="2" t="s">
+        <v>3385</v>
+      </c>
     </row>
     <row r="1697" ht="25" customHeight="1" spans="1:2">
       <c r="A1697" s="2" t="s">
-        <v>3381</v>
-      </c>
-      <c r="B1697" s="2"/>
+        <v>3386</v>
+      </c>
+      <c r="B1697" s="2" t="s">
+        <v>3387</v>
+      </c>
     </row>
     <row r="1698" ht="25" customHeight="1" spans="1:2">
       <c r="A1698" s="2" t="s">
-        <v>3382</v>
-      </c>
-      <c r="B1698" s="2"/>
+        <v>3388</v>
+      </c>
+      <c r="B1698" s="2" t="s">
+        <v>3389</v>
+      </c>
     </row>
     <row r="1699" ht="25" customHeight="1" spans="1:2">
       <c r="A1699" s="2" t="s">
-        <v>3383</v>
-      </c>
-      <c r="B1699" s="2"/>
+        <v>3390</v>
+      </c>
+      <c r="B1699" s="2" t="s">
+        <v>3391</v>
+      </c>
     </row>
     <row r="1700" ht="25" customHeight="1" spans="1:2">
       <c r="A1700" s="2" t="s">
-        <v>3384</v>
-      </c>
-      <c r="B1700" s="2"/>
+        <v>3392</v>
+      </c>
+      <c r="B1700" s="2" t="s">
+        <v>3393</v>
+      </c>
     </row>
     <row r="1701" ht="25" customHeight="1" spans="1:2">
       <c r="A1701" s="2" t="s">
-        <v>3385</v>
-      </c>
-      <c r="B1701" s="2"/>
+        <v>3394</v>
+      </c>
+      <c r="B1701" s="2" t="s">
+        <v>3395</v>
+      </c>
     </row>
     <row r="1702" ht="25" customHeight="1" spans="1:2">
       <c r="A1702" s="2" t="s">
-        <v>3386</v>
-      </c>
-      <c r="B1702" s="2"/>
+        <v>3396</v>
+      </c>
+      <c r="B1702" s="2" t="s">
+        <v>3397</v>
+      </c>
     </row>
     <row r="1703" ht="25" customHeight="1" spans="1:2">
-      <c r="A1703" s="2"/>
-      <c r="B1703" s="2"/>
+      <c r="A1703" s="2" t="s">
+        <v>3398</v>
+      </c>
+      <c r="B1703" s="2" t="s">
+        <v>3399</v>
+      </c>
     </row>
     <row r="1704" ht="25" customHeight="1" spans="1:2">
-      <c r="A1704" s="2"/>
-      <c r="B1704" s="2"/>
+      <c r="A1704" s="2" t="s">
+        <v>3400</v>
+      </c>
+      <c r="B1704" s="2" t="s">
+        <v>3401</v>
+      </c>
     </row>
     <row r="1705" ht="25" customHeight="1" spans="1:2">
-      <c r="A1705" s="2"/>
-      <c r="B1705" s="2"/>
+      <c r="A1705" s="2" t="s">
+        <v>3402</v>
+      </c>
+      <c r="B1705" s="2" t="s">
+        <v>3403</v>
+      </c>
     </row>
     <row r="1706" ht="25" customHeight="1" spans="1:2">
-      <c r="A1706" s="2"/>
-      <c r="B1706" s="2"/>
+      <c r="A1706" s="2" t="s">
+        <v>3404</v>
+      </c>
+      <c r="B1706" s="2" t="s">
+        <v>3405</v>
+      </c>
     </row>
     <row r="1707" ht="25" customHeight="1" spans="1:2">
-      <c r="A1707" s="2"/>
-      <c r="B1707" s="2"/>
+      <c r="A1707" s="2" t="s">
+        <v>3406</v>
+      </c>
+      <c r="B1707" s="2" t="s">
+        <v>3407</v>
+      </c>
     </row>
     <row r="1708" ht="25" customHeight="1" spans="1:2">
-      <c r="A1708" s="2"/>
-      <c r="B1708" s="2"/>
+      <c r="A1708" s="2" t="s">
+        <v>3408</v>
+      </c>
+      <c r="B1708" s="2" t="s">
+        <v>3409</v>
+      </c>
     </row>
     <row r="1709" ht="25" customHeight="1" spans="1:2">
-      <c r="A1709" s="2"/>
-      <c r="B1709" s="2"/>
+      <c r="A1709" s="2" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B1709" s="2" t="s">
+        <v>3411</v>
+      </c>
     </row>
     <row r="1710" ht="25" customHeight="1" spans="1:2">
-      <c r="A1710" s="2"/>
-      <c r="B1710" s="2"/>
+      <c r="A1710" s="2" t="s">
+        <v>3412</v>
+      </c>
+      <c r="B1710" s="2" t="s">
+        <v>3413</v>
+      </c>
     </row>
     <row r="1711" ht="25" customHeight="1" spans="1:2">
-      <c r="A1711" s="2"/>
-      <c r="B1711" s="2"/>
+      <c r="A1711" s="2" t="s">
+        <v>3414</v>
+      </c>
+      <c r="B1711" s="2" t="s">
+        <v>3415</v>
+      </c>
     </row>
     <row r="1712" ht="25" customHeight="1" spans="1:2">
-      <c r="A1712" s="2"/>
-      <c r="B1712" s="2"/>
+      <c r="A1712" s="2" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B1712" s="2" t="s">
+        <v>3417</v>
+      </c>
     </row>
     <row r="1713" ht="25" customHeight="1" spans="1:2">
-      <c r="A1713" s="2"/>
-      <c r="B1713" s="2"/>
+      <c r="A1713" s="2" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B1713" s="2" t="s">
+        <v>3419</v>
+      </c>
     </row>
     <row r="1714" ht="25" customHeight="1" spans="1:2">
-      <c r="A1714" s="2"/>
-      <c r="B1714" s="2"/>
+      <c r="A1714" s="2" t="s">
+        <v>3420</v>
+      </c>
+      <c r="B1714" s="2" t="s">
+        <v>3421</v>
+      </c>
     </row>
     <row r="1715" ht="25" customHeight="1" spans="1:2">
-      <c r="A1715" s="2"/>
-      <c r="B1715" s="2"/>
+      <c r="A1715" s="2" t="s">
+        <v>3422</v>
+      </c>
+      <c r="B1715" s="2" t="s">
+        <v>3423</v>
+      </c>
     </row>
     <row r="1716" ht="25" customHeight="1" spans="1:2">
-      <c r="A1716" s="2"/>
-      <c r="B1716" s="2"/>
+      <c r="A1716" s="2" t="s">
+        <v>3424</v>
+      </c>
+      <c r="B1716" s="2" t="s">
+        <v>3425</v>
+      </c>
     </row>
     <row r="1717" ht="25" customHeight="1" spans="1:2">
-      <c r="A1717" s="2"/>
-      <c r="B1717" s="2"/>
+      <c r="A1717" s="2" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B1717" s="2" t="s">
+        <v>3427</v>
+      </c>
     </row>
     <row r="1718" ht="25" customHeight="1" spans="1:2">
-      <c r="A1718" s="2"/>
-      <c r="B1718" s="2"/>
+      <c r="A1718" s="2" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B1718" s="2" t="s">
+        <v>3429</v>
+      </c>
     </row>
     <row r="1719" ht="25" customHeight="1" spans="1:2">
-      <c r="A1719" s="2"/>
-      <c r="B1719" s="2"/>
+      <c r="A1719" s="2" t="s">
+        <v>3430</v>
+      </c>
+      <c r="B1719" s="2" t="s">
+        <v>3431</v>
+      </c>
     </row>
     <row r="1720" ht="25" customHeight="1" spans="1:2">
-      <c r="A1720" s="2"/>
-      <c r="B1720" s="2"/>
+      <c r="A1720" s="2" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B1720" s="2" t="s">
+        <v>3433</v>
+      </c>
     </row>
     <row r="1721" ht="25" customHeight="1" spans="1:2">
-      <c r="A1721" s="2"/>
-      <c r="B1721" s="2"/>
+      <c r="A1721" s="2" t="s">
+        <v>3434</v>
+      </c>
+      <c r="B1721" s="2" t="s">
+        <v>3435</v>
+      </c>
     </row>
     <row r="1722" ht="25" customHeight="1" spans="1:2">
-      <c r="A1722" s="2"/>
-      <c r="B1722" s="2"/>
+      <c r="A1722" s="2" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B1722" s="2" t="s">
+        <v>3437</v>
+      </c>
     </row>
     <row r="1723" ht="25" customHeight="1" spans="1:2">
-      <c r="A1723" s="2"/>
-      <c r="B1723" s="2"/>
+      <c r="A1723" s="2" t="s">
+        <v>3438</v>
+      </c>
+      <c r="B1723" s="2" t="s">
+        <v>3439</v>
+      </c>
     </row>
     <row r="1724" ht="25" customHeight="1" spans="1:2">
-      <c r="A1724" s="2"/>
-      <c r="B1724" s="2"/>
+      <c r="A1724" s="2" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1724" s="2" t="s">
+        <v>3441</v>
+      </c>
     </row>
     <row r="1725" ht="25" customHeight="1" spans="1:2">
-      <c r="A1725" s="2"/>
-      <c r="B1725" s="2"/>
+      <c r="A1725" s="2" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B1725" s="2" t="s">
+        <v>3443</v>
+      </c>
     </row>
     <row r="1726" ht="25" customHeight="1" spans="1:2">
-      <c r="A1726" s="2"/>
-      <c r="B1726" s="2"/>
+      <c r="A1726" s="2" t="s">
+        <v>3444</v>
+      </c>
+      <c r="B1726" s="2" t="s">
+        <v>3445</v>
+      </c>
     </row>
     <row r="1727" ht="25" customHeight="1" spans="1:2">
-      <c r="A1727" s="2"/>
-      <c r="B1727" s="2"/>
+      <c r="A1727" s="2" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B1727" s="2" t="s">
+        <v>3447</v>
+      </c>
     </row>
     <row r="1728" ht="25" customHeight="1" spans="1:2">
-      <c r="A1728" s="2"/>
-      <c r="B1728" s="2"/>
+      <c r="A1728" s="2" t="s">
+        <v>3448</v>
+      </c>
+      <c r="B1728" s="2" t="s">
+        <v>3449</v>
+      </c>
     </row>
     <row r="1729" ht="25" customHeight="1" spans="1:2">
-      <c r="A1729" s="2"/>
-      <c r="B1729" s="2"/>
+      <c r="A1729" s="2" t="s">
+        <v>3450</v>
+      </c>
+      <c r="B1729" s="2" t="s">
+        <v>3451</v>
+      </c>
     </row>
     <row r="1730" ht="25" customHeight="1" spans="1:2">
-      <c r="A1730" s="2"/>
-      <c r="B1730" s="2"/>
+      <c r="A1730" s="2" t="s">
+        <v>3452</v>
+      </c>
+      <c r="B1730" s="2" t="s">
+        <v>3453</v>
+      </c>
     </row>
     <row r="1731" ht="25" customHeight="1" spans="1:2">
-      <c r="A1731" s="2"/>
-      <c r="B1731" s="2"/>
+      <c r="A1731" s="2" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B1731" s="2" t="s">
+        <v>3455</v>
+      </c>
     </row>
     <row r="1732" ht="25" customHeight="1" spans="1:2">
-      <c r="A1732" s="2"/>
-      <c r="B1732" s="2"/>
+      <c r="A1732" s="2" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B1732" s="2" t="s">
+        <v>3457</v>
+      </c>
     </row>
     <row r="1733" ht="25" customHeight="1" spans="1:2">
-      <c r="A1733" s="2"/>
-      <c r="B1733" s="2"/>
+      <c r="A1733" s="2" t="s">
+        <v>3458</v>
+      </c>
+      <c r="B1733" s="2" t="s">
+        <v>3459</v>
+      </c>
     </row>
     <row r="1734" ht="25" customHeight="1" spans="1:2">
-      <c r="A1734" s="2"/>
-      <c r="B1734" s="2"/>
+      <c r="A1734" s="2" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B1734" s="2" t="s">
+        <v>3461</v>
+      </c>
     </row>
     <row r="1735" ht="25" customHeight="1" spans="1:2">
-      <c r="A1735" s="2"/>
-      <c r="B1735" s="2"/>
+      <c r="A1735" s="2" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B1735" s="2" t="s">
+        <v>3463</v>
+      </c>
     </row>
     <row r="1736" ht="25" customHeight="1" spans="1:2">
-      <c r="A1736" s="2"/>
-      <c r="B1736" s="2"/>
+      <c r="A1736" s="2" t="s">
+        <v>3464</v>
+      </c>
+      <c r="B1736" s="2" t="s">
+        <v>3465</v>
+      </c>
     </row>
     <row r="1737" ht="25" customHeight="1" spans="1:2">
-      <c r="A1737" s="2"/>
-      <c r="B1737" s="2"/>
+      <c r="A1737" s="2" t="s">
+        <v>3466</v>
+      </c>
+      <c r="B1737" s="2" t="s">
+        <v>3467</v>
+      </c>
     </row>
     <row r="1738" ht="25" customHeight="1" spans="1:2">
-      <c r="A1738" s="2"/>
-      <c r="B1738" s="2"/>
+      <c r="A1738" s="2" t="s">
+        <v>3468</v>
+      </c>
+      <c r="B1738" s="2" t="s">
+        <v>3469</v>
+      </c>
     </row>
     <row r="1739" ht="25" customHeight="1" spans="1:2">
-      <c r="A1739" s="2"/>
-      <c r="B1739" s="2"/>
+      <c r="A1739" s="2" t="s">
+        <v>3470</v>
+      </c>
+      <c r="B1739" s="2" t="s">
+        <v>3471</v>
+      </c>
     </row>
     <row r="1740" ht="25" customHeight="1" spans="1:2">
-      <c r="A1740" s="2"/>
-      <c r="B1740" s="2"/>
+      <c r="A1740" s="2" t="s">
+        <v>3472</v>
+      </c>
+      <c r="B1740" s="2" t="s">
+        <v>3473</v>
+      </c>
     </row>
     <row r="1741" ht="25" customHeight="1" spans="1:2">
-      <c r="A1741" s="2"/>
-      <c r="B1741" s="2"/>
+      <c r="A1741" s="2" t="s">
+        <v>3474</v>
+      </c>
+      <c r="B1741" s="2" t="s">
+        <v>3475</v>
+      </c>
     </row>
     <row r="1742" ht="25" customHeight="1" spans="1:2">
-      <c r="A1742" s="2"/>
-      <c r="B1742" s="2"/>
+      <c r="A1742" s="2" t="s">
+        <v>3476</v>
+      </c>
+      <c r="B1742" s="2" t="s">
+        <v>3477</v>
+      </c>
     </row>
     <row r="1743" ht="25" customHeight="1" spans="1:2">
-      <c r="A1743" s="2"/>
-      <c r="B1743" s="2"/>
+      <c r="A1743" s="2" t="s">
+        <v>3478</v>
+      </c>
+      <c r="B1743" s="2" t="s">
+        <v>3479</v>
+      </c>
     </row>
     <row r="1744" ht="25" customHeight="1" spans="1:2">
-      <c r="A1744" s="2"/>
-      <c r="B1744" s="2"/>
+      <c r="A1744" s="2" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B1744" s="2" t="s">
+        <v>3481</v>
+      </c>
     </row>
     <row r="1745" ht="25" customHeight="1" spans="1:2">
-      <c r="A1745" s="2"/>
-      <c r="B1745" s="2"/>
+      <c r="A1745" s="2" t="s">
+        <v>3482</v>
+      </c>
+      <c r="B1745" s="2" t="s">
+        <v>3483</v>
+      </c>
     </row>
     <row r="1746" ht="25" customHeight="1" spans="1:2">
-      <c r="A1746" s="2"/>
-      <c r="B1746" s="2"/>
+      <c r="A1746" s="2" t="s">
+        <v>3484</v>
+      </c>
+      <c r="B1746" s="2" t="s">
+        <v>3485</v>
+      </c>
     </row>
     <row r="1747" ht="25" customHeight="1" spans="1:2">
-      <c r="A1747" s="2"/>
-      <c r="B1747" s="2"/>
+      <c r="A1747" s="2" t="s">
+        <v>3486</v>
+      </c>
+      <c r="B1747" s="2" t="s">
+        <v>3487</v>
+      </c>
     </row>
     <row r="1748" ht="25" customHeight="1" spans="1:2">
-      <c r="A1748" s="2"/>
-      <c r="B1748" s="2"/>
+      <c r="A1748" s="2" t="s">
+        <v>3488</v>
+      </c>
+      <c r="B1748" s="2" t="s">
+        <v>3489</v>
+      </c>
     </row>
     <row r="1749" ht="25" customHeight="1" spans="1:2">
-      <c r="A1749" s="2"/>
-      <c r="B1749" s="2"/>
+      <c r="A1749" s="2" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B1749" s="2" t="s">
+        <v>3491</v>
+      </c>
     </row>
     <row r="1750" ht="25" customHeight="1" spans="1:2">
-      <c r="A1750" s="2"/>
-      <c r="B1750" s="2"/>
+      <c r="A1750" s="2" t="s">
+        <v>3492</v>
+      </c>
+      <c r="B1750" s="2" t="s">
+        <v>3493</v>
+      </c>
     </row>
     <row r="1751" ht="25" customHeight="1" spans="1:2">
-      <c r="A1751" s="2"/>
-      <c r="B1751" s="2"/>
+      <c r="A1751" s="2" t="s">
+        <v>3494</v>
+      </c>
+      <c r="B1751" s="2" t="s">
+        <v>3495</v>
+      </c>
     </row>
     <row r="1752" ht="25" customHeight="1" spans="1:2">
-      <c r="A1752" s="2"/>
-      <c r="B1752" s="2"/>
+      <c r="A1752" s="2" t="s">
+        <v>3496</v>
+      </c>
+      <c r="B1752" s="2" t="s">
+        <v>3497</v>
+      </c>
     </row>
     <row r="1753" ht="25" customHeight="1" spans="1:2">
-      <c r="A1753" s="2"/>
-      <c r="B1753" s="2"/>
+      <c r="A1753" s="2" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B1753" s="2" t="s">
+        <v>3499</v>
+      </c>
     </row>
     <row r="1754" ht="25" customHeight="1" spans="1:2">
-      <c r="A1754" s="2"/>
-      <c r="B1754" s="2"/>
+      <c r="A1754" s="2" t="s">
+        <v>3500</v>
+      </c>
+      <c r="B1754" s="2" t="s">
+        <v>3501</v>
+      </c>
     </row>
     <row r="1755" ht="25" customHeight="1" spans="1:2">
-      <c r="A1755" s="2"/>
-      <c r="B1755" s="2"/>
+      <c r="A1755" s="2" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B1755" s="2" t="s">
+        <v>3503</v>
+      </c>
     </row>
     <row r="1756" ht="25" customHeight="1" spans="1:2">
-      <c r="A1756" s="2"/>
-      <c r="B1756" s="2"/>
+      <c r="A1756" s="2" t="s">
+        <v>3504</v>
+      </c>
+      <c r="B1756" s="2" t="s">
+        <v>3505</v>
+      </c>
     </row>
     <row r="1757" ht="25" customHeight="1" spans="1:2">
-      <c r="A1757" s="2"/>
-      <c r="B1757" s="2"/>
+      <c r="A1757" s="2" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B1757" s="2" t="s">
+        <v>3507</v>
+      </c>
     </row>
     <row r="1758" ht="25" customHeight="1" spans="1:2">
-      <c r="A1758" s="2"/>
-      <c r="B1758" s="2"/>
+      <c r="A1758" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="B1758" s="2" t="s">
+        <v>3509</v>
+      </c>
     </row>
     <row r="1759" ht="25" customHeight="1" spans="1:2">
-      <c r="A1759" s="2"/>
-      <c r="B1759" s="2"/>
+      <c r="A1759" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="B1759" s="2" t="s">
+        <v>3511</v>
+      </c>
     </row>
     <row r="1760" ht="25" customHeight="1" spans="1:2">
-      <c r="A1760" s="2"/>
-      <c r="B1760" s="2"/>
+      <c r="A1760" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="B1760" s="2" t="s">
+        <v>3513</v>
+      </c>
     </row>
     <row r="1761" ht="25" customHeight="1" spans="1:2">
-      <c r="A1761" s="2"/>
-      <c r="B1761" s="2"/>
+      <c r="A1761" s="2" t="s">
+        <v>3514</v>
+      </c>
+      <c r="B1761" s="2" t="s">
+        <v>3515</v>
+      </c>
     </row>
     <row r="1762" ht="25" customHeight="1" spans="1:2">
-      <c r="A1762" s="2"/>
-      <c r="B1762" s="2"/>
+      <c r="A1762" s="2" t="s">
+        <v>3516</v>
+      </c>
+      <c r="B1762" s="2" t="s">
+        <v>3517</v>
+      </c>
     </row>
     <row r="1763" ht="25" customHeight="1" spans="1:2">
-      <c r="A1763" s="2"/>
-      <c r="B1763" s="2"/>
+      <c r="A1763" s="2" t="s">
+        <v>3518</v>
+      </c>
+      <c r="B1763" s="2" t="s">
+        <v>3519</v>
+      </c>
     </row>
     <row r="1764" ht="25" customHeight="1" spans="1:2">
-      <c r="A1764" s="2"/>
-      <c r="B1764" s="2"/>
+      <c r="A1764" s="2" t="s">
+        <v>3520</v>
+      </c>
+      <c r="B1764" s="2" t="s">
+        <v>3521</v>
+      </c>
     </row>
     <row r="1765" ht="25" customHeight="1" spans="1:2">
-      <c r="A1765" s="2"/>
-      <c r="B1765" s="2"/>
+      <c r="A1765" s="2" t="s">
+        <v>3522</v>
+      </c>
+      <c r="B1765" s="2" t="s">
+        <v>3523</v>
+      </c>
     </row>
     <row r="1766" ht="25" customHeight="1" spans="1:2">
-      <c r="A1766" s="2"/>
-      <c r="B1766" s="2"/>
+      <c r="A1766" s="2" t="s">
+        <v>3524</v>
+      </c>
+      <c r="B1766" s="2" t="s">
+        <v>3525</v>
+      </c>
     </row>
     <row r="1767" ht="25" customHeight="1" spans="1:2">
-      <c r="A1767" s="2"/>
-      <c r="B1767" s="2"/>
+      <c r="A1767" s="2" t="s">
+        <v>3526</v>
+      </c>
+      <c r="B1767" s="2" t="s">
+        <v>3527</v>
+      </c>
     </row>
     <row r="1768" ht="25" customHeight="1" spans="1:2">
-      <c r="A1768" s="2"/>
-      <c r="B1768" s="2"/>
+      <c r="A1768" s="2" t="s">
+        <v>3528</v>
+      </c>
+      <c r="B1768" s="2" t="s">
+        <v>3529</v>
+      </c>
     </row>
     <row r="1769" ht="25" customHeight="1" spans="1:2">
-      <c r="A1769" s="2"/>
-      <c r="B1769" s="2"/>
+      <c r="A1769" s="2" t="s">
+        <v>3530</v>
+      </c>
+      <c r="B1769" s="2" t="s">
+        <v>3531</v>
+      </c>
     </row>
     <row r="1770" ht="25" customHeight="1" spans="1:2">
-      <c r="A1770" s="2"/>
-      <c r="B1770" s="2"/>
+      <c r="A1770" s="2" t="s">
+        <v>3532</v>
+      </c>
+      <c r="B1770" s="2" t="s">
+        <v>3533</v>
+      </c>
     </row>
     <row r="1771" ht="25" customHeight="1" spans="1:2">
-      <c r="A1771" s="2"/>
-      <c r="B1771" s="2"/>
+      <c r="A1771" s="2" t="s">
+        <v>3534</v>
+      </c>
+      <c r="B1771" s="2" t="s">
+        <v>3535</v>
+      </c>
     </row>
     <row r="1772" ht="25" customHeight="1" spans="1:2">
-      <c r="A1772" s="2"/>
-      <c r="B1772" s="2"/>
+      <c r="A1772" s="2" t="s">
+        <v>3536</v>
+      </c>
+      <c r="B1772" s="2" t="s">
+        <v>3537</v>
+      </c>
     </row>
     <row r="1773" ht="25" customHeight="1" spans="1:2">
-      <c r="A1773" s="2"/>
-      <c r="B1773" s="2"/>
+      <c r="A1773" s="2" t="s">
+        <v>3538</v>
+      </c>
+      <c r="B1773" s="2" t="s">
+        <v>3539</v>
+      </c>
     </row>
     <row r="1774" ht="25" customHeight="1" spans="1:2">
-      <c r="A1774" s="2"/>
-      <c r="B1774" s="2"/>
+      <c r="A1774" s="2" t="s">
+        <v>3540</v>
+      </c>
+      <c r="B1774" s="2" t="s">
+        <v>3541</v>
+      </c>
     </row>
     <row r="1775" ht="25" customHeight="1" spans="1:2">
-      <c r="A1775" s="2"/>
-      <c r="B1775" s="2"/>
+      <c r="A1775" s="2" t="s">
+        <v>3542</v>
+      </c>
+      <c r="B1775" s="2" t="s">
+        <v>3543</v>
+      </c>
     </row>
     <row r="1776" ht="25" customHeight="1" spans="1:2">
-      <c r="A1776" s="2"/>
-      <c r="B1776" s="2"/>
+      <c r="A1776" s="2" t="s">
+        <v>3544</v>
+      </c>
+      <c r="B1776" s="2" t="s">
+        <v>3545</v>
+      </c>
     </row>
     <row r="1777" ht="25" customHeight="1" spans="1:2">
-      <c r="A1777" s="2"/>
-      <c r="B1777" s="2"/>
+      <c r="A1777" s="2" t="s">
+        <v>3546</v>
+      </c>
+      <c r="B1777" s="2" t="s">
+        <v>3547</v>
+      </c>
     </row>
     <row r="1778" ht="25" customHeight="1" spans="1:2">
-      <c r="A1778" s="2"/>
-      <c r="B1778" s="2"/>
+      <c r="A1778" s="2" t="s">
+        <v>3548</v>
+      </c>
+      <c r="B1778" s="2" t="s">
+        <v>3549</v>
+      </c>
     </row>
     <row r="1779" ht="25" customHeight="1" spans="1:2">
-      <c r="A1779" s="2"/>
-      <c r="B1779" s="2"/>
+      <c r="A1779" s="2" t="s">
+        <v>3550</v>
+      </c>
+      <c r="B1779" s="2" t="s">
+        <v>3551</v>
+      </c>
     </row>
     <row r="1780" ht="25" customHeight="1" spans="1:2">
-      <c r="A1780" s="2"/>
-      <c r="B1780" s="2"/>
+      <c r="A1780" s="2" t="s">
+        <v>3552</v>
+      </c>
+      <c r="B1780" s="2" t="s">
+        <v>3553</v>
+      </c>
     </row>
     <row r="1781" ht="25" customHeight="1" spans="1:2">
-      <c r="A1781" s="2"/>
-      <c r="B1781" s="2"/>
+      <c r="A1781" s="2" t="s">
+        <v>3554</v>
+      </c>
+      <c r="B1781" s="2" t="s">
+        <v>3555</v>
+      </c>
     </row>
     <row r="1782" ht="25" customHeight="1" spans="1:2">
-      <c r="A1782" s="2"/>
-      <c r="B1782" s="2"/>
+      <c r="A1782" s="2" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B1782" s="2" t="s">
+        <v>3557</v>
+      </c>
     </row>
     <row r="1783" ht="25" customHeight="1" spans="1:2">
-      <c r="A1783" s="2"/>
-      <c r="B1783" s="2"/>
+      <c r="A1783" s="2" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B1783" s="2" t="s">
+        <v>3559</v>
+      </c>
     </row>
     <row r="1784" ht="25" customHeight="1" spans="1:2">
-      <c r="A1784" s="2"/>
-      <c r="B1784" s="2"/>
+      <c r="A1784" s="2" t="s">
+        <v>3560</v>
+      </c>
+      <c r="B1784" s="2" t="s">
+        <v>3561</v>
+      </c>
     </row>
     <row r="1785" ht="25" customHeight="1" spans="1:2">
-      <c r="A1785" s="2"/>
-      <c r="B1785" s="2"/>
+      <c r="A1785" s="2" t="s">
+        <v>3562</v>
+      </c>
+      <c r="B1785" s="2" t="s">
+        <v>3563</v>
+      </c>
     </row>
     <row r="1786" ht="25" customHeight="1" spans="1:2">
-      <c r="A1786" s="2"/>
-      <c r="B1786" s="2"/>
+      <c r="A1786" s="2" t="s">
+        <v>3564</v>
+      </c>
+      <c r="B1786" s="2" t="s">
+        <v>3565</v>
+      </c>
     </row>
     <row r="1787" ht="25" customHeight="1" spans="1:2">
-      <c r="A1787" s="2"/>
-      <c r="B1787" s="2"/>
+      <c r="A1787" s="2" t="s">
+        <v>3566</v>
+      </c>
+      <c r="B1787" s="2" t="s">
+        <v>3567</v>
+      </c>
     </row>
     <row r="1788" ht="25" customHeight="1" spans="1:2">
-      <c r="A1788" s="2"/>
-      <c r="B1788" s="2"/>
+      <c r="A1788" s="2" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B1788" s="2" t="s">
+        <v>3569</v>
+      </c>
     </row>
     <row r="1789" ht="25" customHeight="1" spans="1:2">
-      <c r="A1789" s="2"/>
-      <c r="B1789" s="2"/>
+      <c r="A1789" s="2" t="s">
+        <v>3570</v>
+      </c>
+      <c r="B1789" s="2" t="s">
+        <v>3571</v>
+      </c>
     </row>
     <row r="1790" ht="25" customHeight="1" spans="1:2">
-      <c r="A1790" s="2"/>
-      <c r="B1790" s="2"/>
+      <c r="A1790" s="2" t="s">
+        <v>3572</v>
+      </c>
+      <c r="B1790" s="2" t="s">
+        <v>3573</v>
+      </c>
     </row>
     <row r="1791" ht="25" customHeight="1" spans="1:2">
-      <c r="A1791" s="2"/>
-      <c r="B1791" s="2"/>
+      <c r="A1791" s="2" t="s">
+        <v>3574</v>
+      </c>
+      <c r="B1791" s="2" t="s">
+        <v>3575</v>
+      </c>
     </row>
     <row r="1792" ht="25" customHeight="1" spans="1:2">
-      <c r="A1792" s="2"/>
-      <c r="B1792" s="2"/>
+      <c r="A1792" s="2" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B1792" s="2" t="s">
+        <v>3577</v>
+      </c>
     </row>
     <row r="1793" ht="25" customHeight="1" spans="1:2">
-      <c r="A1793" s="2"/>
-      <c r="B1793" s="2"/>
+      <c r="A1793" s="2" t="s">
+        <v>3578</v>
+      </c>
+      <c r="B1793" s="2" t="s">
+        <v>3579</v>
+      </c>
     </row>
     <row r="1794" ht="25" customHeight="1" spans="1:2">
-      <c r="A1794" s="2"/>
-      <c r="B1794" s="2"/>
+      <c r="A1794" s="2" t="s">
+        <v>3580</v>
+      </c>
+      <c r="B1794" s="2" t="s">
+        <v>3581</v>
+      </c>
     </row>
     <row r="1795" ht="25" customHeight="1" spans="1:2">
-      <c r="A1795" s="2"/>
-      <c r="B1795" s="2"/>
+      <c r="A1795" s="2" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B1795" s="2" t="s">
+        <v>3583</v>
+      </c>
     </row>
     <row r="1796" ht="25" customHeight="1" spans="1:2">
-      <c r="A1796" s="2"/>
-      <c r="B1796" s="2"/>
+      <c r="A1796" s="2" t="s">
+        <v>3584</v>
+      </c>
+      <c r="B1796" s="2" t="s">
+        <v>3585</v>
+      </c>
     </row>
     <row r="1797" ht="25" customHeight="1" spans="1:2">
-      <c r="A1797" s="2"/>
-      <c r="B1797" s="2"/>
+      <c r="A1797" s="2" t="s">
+        <v>3586</v>
+      </c>
+      <c r="B1797" s="2" t="s">
+        <v>3587</v>
+      </c>
     </row>
     <row r="1798" ht="25" customHeight="1" spans="1:2">
-      <c r="A1798" s="2"/>
-      <c r="B1798" s="2"/>
+      <c r="A1798" s="2" t="s">
+        <v>3588</v>
+      </c>
+      <c r="B1798" s="2" t="s">
+        <v>3589</v>
+      </c>
     </row>
     <row r="1799" ht="25" customHeight="1" spans="1:2">
-      <c r="A1799" s="2"/>
-      <c r="B1799" s="2"/>
+      <c r="A1799" s="2" t="s">
+        <v>3590</v>
+      </c>
+      <c r="B1799" s="2" t="s">
+        <v>3591</v>
+      </c>
     </row>
     <row r="1800" ht="25" customHeight="1" spans="1:2">
-      <c r="A1800" s="2"/>
-      <c r="B1800" s="2"/>
+      <c r="A1800" s="2" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B1800" s="2" t="s">
+        <v>3593</v>
+      </c>
     </row>
     <row r="1801" ht="25" customHeight="1" spans="1:2">
-      <c r="A1801" s="2"/>
-      <c r="B1801" s="2"/>
+      <c r="A1801" s="2" t="s">
+        <v>3594</v>
+      </c>
+      <c r="B1801" s="2" t="s">
+        <v>3595</v>
+      </c>
     </row>
     <row r="1802" ht="25" customHeight="1" spans="1:2">
       <c r="A1802" s="2"/>
